--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="1869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="1870">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,40 +44,40 @@
     <t xml:space="preserve">BRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13994979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92740249633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52519702911377</t>
+    <t xml:space="preserve">7.13994884490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92740154266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52519655227661</t>
   </si>
   <si>
     <t xml:space="preserve">6.54154682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42873382568359</t>
+    <t xml:space="preserve">6.42873334884644</t>
   </si>
   <si>
     <t xml:space="preserve">6.60040616989136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78188800811768</t>
+    <t xml:space="preserve">6.78188848495483</t>
   </si>
   <si>
     <t xml:space="preserve">6.55135679244995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21291542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19820213317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2750449180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94641542434692</t>
+    <t xml:space="preserve">6.21291637420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19820165634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27504539489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94641447067261</t>
   </si>
   <si>
     <t xml:space="preserve">6.20310640335083</t>
@@ -86,31 +86,31 @@
     <t xml:space="preserve">6.24888563156128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30610942840576</t>
+    <t xml:space="preserve">6.30610990524292</t>
   </si>
   <si>
     <t xml:space="preserve">6.31918954849243</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38785791397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23090028762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16713666915894</t>
+    <t xml:space="preserve">6.38785839080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23090076446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16713714599609</t>
   </si>
   <si>
     <t xml:space="preserve">6.05922794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99219417572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86466646194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70443868637085</t>
+    <t xml:space="preserve">5.99219465255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86466550827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70443773269653</t>
   </si>
   <si>
     <t xml:space="preserve">5.35945844650269</t>
@@ -122,19 +122,19 @@
     <t xml:space="preserve">5.72242307662964</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67500782012939</t>
+    <t xml:space="preserve">5.67500877380371</t>
   </si>
   <si>
     <t xml:space="preserve">5.73223304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0396089553833</t>
+    <t xml:space="preserve">6.03960800170898</t>
   </si>
   <si>
     <t xml:space="preserve">5.97420978546143</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11972236633301</t>
+    <t xml:space="preserve">6.11972284317017</t>
   </si>
   <si>
     <t xml:space="preserve">6.14097690582275</t>
@@ -143,28 +143,28 @@
     <t xml:space="preserve">6.10010242462158</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2374415397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11154794692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97584438323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07394361495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12953281402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21945667266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35189008712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32409572601318</t>
+    <t xml:space="preserve">6.23744106292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11154747009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97584533691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07394313812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12953233718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21945571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35188961029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32409524917603</t>
   </si>
   <si>
     <t xml:space="preserve">7.04675626754761</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">7.1170597076416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07945394515991</t>
+    <t xml:space="preserve">7.07945489883423</t>
   </si>
   <si>
     <t xml:space="preserve">7.12032985687256</t>
@@ -185,67 +185,67 @@
     <t xml:space="preserve">7.07128000259399</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06637477874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16120433807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14321899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24949169158936</t>
+    <t xml:space="preserve">7.06637525558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16120338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14321947097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24949264526367</t>
   </si>
   <si>
     <t xml:space="preserve">7.1415843963623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22987270355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0761833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2691125869751</t>
+    <t xml:space="preserve">7.2298731803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07618284225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26911163330078</t>
   </si>
   <si>
     <t xml:space="preserve">7.15302801132202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15139293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31489133834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43097448348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40317964553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35576629638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14485502243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18899726867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16283798217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27401733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998706817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35740041732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40644931793213</t>
+    <t xml:space="preserve">7.1513934135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31489038467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43097400665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40318012237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35576581954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14485359191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18899822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16283893585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2740159034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998802185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35739994049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4064507484436</t>
   </si>
   <si>
     <t xml:space="preserve">7.42280006408691</t>
@@ -254,40 +254,40 @@
     <t xml:space="preserve">7.39337110519409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4391508102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47184896469116</t>
+    <t xml:space="preserve">7.43915128707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47185039520264</t>
   </si>
   <si>
     <t xml:space="preserve">7.51108932495117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76778078079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71546077728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63534688949585</t>
+    <t xml:space="preserve">7.76777982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71546030044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63534593582153</t>
   </si>
   <si>
     <t xml:space="preserve">7.68276119232178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7416205406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66968202590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72200155258179</t>
+    <t xml:space="preserve">7.74162149429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66968250274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72200059890747</t>
   </si>
   <si>
     <t xml:space="preserve">7.63044261932373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7105565071106</t>
+    <t xml:space="preserve">7.71055793762207</t>
   </si>
   <si>
     <t xml:space="preserve">7.85606908798218</t>
@@ -296,16 +296,16 @@
     <t xml:space="preserve">8.47736167907715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50188446044922</t>
+    <t xml:space="preserve">8.50188636779785</t>
   </si>
   <si>
     <t xml:space="preserve">8.51006126403809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55093574523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42831134796143</t>
+    <t xml:space="preserve">8.55093479156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42831039428711</t>
   </si>
   <si>
     <t xml:space="preserve">8.36291313171387</t>
@@ -314,13 +314,13 @@
     <t xml:space="preserve">8.354736328125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41196250915527</t>
+    <t xml:space="preserve">8.41196155548096</t>
   </si>
   <si>
     <t xml:space="preserve">8.5199146270752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45348262786865</t>
+    <t xml:space="preserve">8.45348167419434</t>
   </si>
   <si>
     <t xml:space="preserve">8.51161003112793</t>
@@ -329,40 +329,40 @@
     <t xml:space="preserve">8.46178531646729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47008895874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6112585067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63617038726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72751522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96002674102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86868190765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86037921905518</t>
+    <t xml:space="preserve">8.47008991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61125946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63617134094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72751426696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96002769470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86868286132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86037826538086</t>
   </si>
   <si>
     <t xml:space="preserve">8.58634662628174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27577590942383</t>
+    <t xml:space="preserve">8.27577686309814</t>
   </si>
   <si>
     <t xml:space="preserve">8.10969638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30401134490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31231307983398</t>
+    <t xml:space="preserve">8.30401039123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3123140335083</t>
   </si>
   <si>
     <t xml:space="preserve">8.60295391082764</t>
@@ -371,16 +371,16 @@
     <t xml:space="preserve">8.61956214904785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56973743438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71920967102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25916767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64134931564331</t>
+    <t xml:space="preserve">8.56973838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71921062469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25916862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64135026931763</t>
   </si>
   <si>
     <t xml:space="preserve">8.25418663024902</t>
@@ -389,70 +389,70 @@
     <t xml:space="preserve">8.0598726272583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20602321624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23757743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8472900390625</t>
+    <t xml:space="preserve">8.20602130889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23757839202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84728956222534</t>
   </si>
   <si>
     <t xml:space="preserve">7.67954874038696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67788791656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95524120330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02831649780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05488872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97849225997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14457225799561</t>
+    <t xml:space="preserve">7.67788696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95524024963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02831840515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05488777160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97849273681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14457321166992</t>
   </si>
   <si>
     <t xml:space="preserve">8.11301803588867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23425769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10471343994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21100425720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16782569885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32061958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37044239044189</t>
+    <t xml:space="preserve">8.23425674438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10471248626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21100521087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16782474517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32061862945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37044334411621</t>
   </si>
   <si>
     <t xml:space="preserve">8.50330543518066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36213684082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67769050598145</t>
+    <t xml:space="preserve">8.36213779449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67769145965576</t>
   </si>
   <si>
     <t xml:space="preserve">8.76903438568115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53652000427246</t>
+    <t xml:space="preserve">8.53652191162109</t>
   </si>
   <si>
     <t xml:space="preserve">8.55313014984131</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">8.64447498321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73581790924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68599414825439</t>
+    <t xml:space="preserve">8.73581981658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68599510192871</t>
   </si>
   <si>
     <t xml:space="preserve">8.7441234588623</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">8.6693868637085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48669719696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4451789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47839546203613</t>
+    <t xml:space="preserve">8.48669815063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44517803192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4783935546875</t>
   </si>
   <si>
     <t xml:space="preserve">8.40365791320801</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">8.65277862548828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69429874420166</t>
+    <t xml:space="preserve">8.69429779052734</t>
   </si>
   <si>
     <t xml:space="preserve">8.71090698242188</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">8.84377098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88529205322266</t>
+    <t xml:space="preserve">8.88529109954834</t>
   </si>
   <si>
     <t xml:space="preserve">8.78564262390137</t>
@@ -512,13 +512,13 @@
     <t xml:space="preserve">8.80224990844727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8188591003418</t>
+    <t xml:space="preserve">8.81885814666748</t>
   </si>
   <si>
     <t xml:space="preserve">8.90189838409424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05137157440186</t>
+    <t xml:space="preserve">9.05137062072754</t>
   </si>
   <si>
     <t xml:space="preserve">8.81055450439453</t>
@@ -527,25 +527,25 @@
     <t xml:space="preserve">8.6278657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70260238647461</t>
+    <t xml:space="preserve">8.70260334014893</t>
   </si>
   <si>
     <t xml:space="preserve">8.82716178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75242614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04306602478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14271450042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28388404846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35031700134277</t>
+    <t xml:space="preserve">8.75242710113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04306793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14271545410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2838830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35031604766846</t>
   </si>
   <si>
     <t xml:space="preserve">9.35861873626709</t>
@@ -554,13 +554,13 @@
     <t xml:space="preserve">9.15102005004883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93511295318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77733898162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19254016876221</t>
+    <t xml:space="preserve">8.93511486053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77733993530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19253730773926</t>
   </si>
   <si>
     <t xml:space="preserve">9.44996452331543</t>
@@ -572,31 +572,31 @@
     <t xml:space="preserve">9.00154590606689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13440990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91850566864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92681217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00985145568848</t>
+    <t xml:space="preserve">9.1344108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91850757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9268102645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00985240936279</t>
   </si>
   <si>
     <t xml:space="preserve">8.984938621521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76072978973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11780452728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22575664520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95172309875488</t>
+    <t xml:space="preserve">8.76073169708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1178035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.225754737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95172214508057</t>
   </si>
   <si>
     <t xml:space="preserve">9.06797885894775</t>
@@ -605,22 +605,22 @@
     <t xml:space="preserve">9.07628345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20084190368652</t>
+    <t xml:space="preserve">9.20084285736084</t>
   </si>
   <si>
     <t xml:space="preserve">9.31709957122803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36692237854004</t>
+    <t xml:space="preserve">9.36692333221436</t>
   </si>
   <si>
     <t xml:space="preserve">9.49148273468018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5496129989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96481132507324</t>
+    <t xml:space="preserve">9.54961204528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96481037139893</t>
   </si>
   <si>
     <t xml:space="preserve">10.0229406356812</t>
@@ -629,25 +629,25 @@
     <t xml:space="preserve">9.82364463806152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93989753723145</t>
+    <t xml:space="preserve">9.93990039825439</t>
   </si>
   <si>
     <t xml:space="preserve">9.98141956329346</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0063314437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0561580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2056274414062</t>
+    <t xml:space="preserve">10.0063333511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0561571121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2056283950806</t>
   </si>
   <si>
     <t xml:space="preserve">10.230541229248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2139320373535</t>
+    <t xml:space="preserve">10.2139329910278</t>
   </si>
   <si>
     <t xml:space="preserve">10.1973247528076</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">10.1225891113281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1807174682617</t>
+    <t xml:space="preserve">10.1807165145874</t>
   </si>
   <si>
     <t xml:space="preserve">10.147500038147</t>
@@ -668,16 +668,16 @@
     <t xml:space="preserve">10.2222366333008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1308927536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0976762771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84855556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3135805130005</t>
+    <t xml:space="preserve">10.1308917999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0976753234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84855651855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3135814666748</t>
   </si>
   <si>
     <t xml:space="preserve">10.0810680389404</t>
@@ -692,37 +692,37 @@
     <t xml:space="preserve">10.4464445114136</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5211801528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.38831615448</t>
+    <t xml:space="preserve">10.5211791992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3883171081543</t>
   </si>
   <si>
     <t xml:space="preserve">10.4713554382324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6872606277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.720477104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540441513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4049253463745</t>
+    <t xml:space="preserve">10.6872615814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7204790115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4049243927002</t>
   </si>
   <si>
     <t xml:space="preserve">10.6457405090332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7952127456665</t>
+    <t xml:space="preserve">10.7952136993408</t>
   </si>
   <si>
     <t xml:space="preserve">10.9612941741943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9280776977539</t>
+    <t xml:space="preserve">10.9280767440796</t>
   </si>
   <si>
     <t xml:space="preserve">10.7703008651733</t>
@@ -734,22 +734,22 @@
     <t xml:space="preserve">10.8699493408203</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7869091033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0360288619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8948621749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0443334579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2519340515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1771965026855</t>
+    <t xml:space="preserve">10.7869100570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0360298156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8948612213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0443325042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2519330978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1771974563599</t>
   </si>
   <si>
     <t xml:space="preserve">11.2270221710205</t>
@@ -758,37 +758,37 @@
     <t xml:space="preserve">11.2602376937866</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851476669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3432788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3931007385254</t>
+    <t xml:space="preserve">11.2851495742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3432779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3931016921997</t>
   </si>
   <si>
     <t xml:space="preserve">11.4512300491333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5093574523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5010547637939</t>
+    <t xml:space="preserve">11.5093584060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5010538101196</t>
   </si>
   <si>
     <t xml:space="preserve">11.5176610946655</t>
   </si>
   <si>
-    <t xml:space="preserve">11.741870880127</t>
+    <t xml:space="preserve">11.7418699264526</t>
   </si>
   <si>
     <t xml:space="preserve">11.7584781646729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.692045211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.683741569519</t>
+    <t xml:space="preserve">11.6920461654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6837425231934</t>
   </si>
   <si>
     <t xml:space="preserve">11.7252626419067</t>
@@ -797,40 +797,40 @@
     <t xml:space="preserve">11.7667827606201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7169570922852</t>
+    <t xml:space="preserve">11.7169589996338</t>
   </si>
   <si>
     <t xml:space="preserve">11.5923976898193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7003507614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.542573928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9577741622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0574226379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9162549972534</t>
+    <t xml:space="preserve">11.7003498077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5425729751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9577751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0574216842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9162540435791</t>
   </si>
   <si>
     <t xml:space="preserve">11.9909906387329</t>
   </si>
   <si>
-    <t xml:space="preserve">11.98268699646</t>
+    <t xml:space="preserve">11.9826860427856</t>
   </si>
   <si>
     <t xml:space="preserve">12.1487674713135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0491189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2899341583252</t>
+    <t xml:space="preserve">12.0491199493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2899360656738</t>
   </si>
   <si>
     <t xml:space="preserve">12.3895826339722</t>
@@ -839,55 +839,55 @@
     <t xml:space="preserve">12.3148460388184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.505841255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5390548706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2733287811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1902866363525</t>
+    <t xml:space="preserve">12.5058393478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5390539169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2733278274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1902875900269</t>
   </si>
   <si>
     <t xml:space="preserve">12.1985912322998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0823345184326</t>
+    <t xml:space="preserve">12.0823354721069</t>
   </si>
   <si>
     <t xml:space="preserve">11.64222240448</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5508766174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8083038330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9346389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9514827728271</t>
+    <t xml:space="preserve">11.550877571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8083028793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9346380233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9514837265015</t>
   </si>
   <si>
     <t xml:space="preserve">12.0609760284424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1620464324951</t>
+    <t xml:space="preserve">12.1620454788208</t>
   </si>
   <si>
     <t xml:space="preserve">11.783034324646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6566982269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7577667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5977392196655</t>
+    <t xml:space="preserve">11.6566972732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7577676773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5977401733398</t>
   </si>
   <si>
     <t xml:space="preserve">11.5640506744385</t>
@@ -896,25 +896,25 @@
     <t xml:space="preserve">11.3029546737671</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2018842697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1934623718262</t>
+    <t xml:space="preserve">11.2018852233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1934614181519</t>
   </si>
   <si>
     <t xml:space="preserve">11.0334348678589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9576320648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2355737686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4208688735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2271518707275</t>
+    <t xml:space="preserve">10.9576330184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2355728149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4208679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2271528244019</t>
   </si>
   <si>
     <t xml:space="preserve">11.2861080169678</t>
@@ -923,19 +923,19 @@
     <t xml:space="preserve">11.1681938171387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9239416122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0250110626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7639150619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9492092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5786218643188</t>
+    <t xml:space="preserve">10.923942565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0250120162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7639169692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9492111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5786209106445</t>
   </si>
   <si>
     <t xml:space="preserve">10.7891836166382</t>
@@ -944,34 +944,34 @@
     <t xml:space="preserve">10.7386484146118</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6544227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7554941177368</t>
+    <t xml:space="preserve">10.6544246673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7554931640625</t>
   </si>
   <si>
     <t xml:space="preserve">11.4292907714844</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5219383239746</t>
+    <t xml:space="preserve">11.5219373703003</t>
   </si>
   <si>
     <t xml:space="preserve">11.2945308685303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6398525238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4629793167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.412446975708</t>
+    <t xml:space="preserve">11.639853477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4629802703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4124460220337</t>
   </si>
   <si>
     <t xml:space="preserve">11.3619108200073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3197984695435</t>
+    <t xml:space="preserve">11.3197994232178</t>
   </si>
   <si>
     <t xml:space="preserve">11.2103071212769</t>
@@ -980,19 +980,19 @@
     <t xml:space="preserve">10.9997444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9913234710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0081672668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8902530670166</t>
+    <t xml:space="preserve">10.991322517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0081663131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8902540206909</t>
   </si>
   <si>
     <t xml:space="preserve">10.9323644638062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8734064102173</t>
+    <t xml:space="preserve">10.8734073638916</t>
   </si>
   <si>
     <t xml:space="preserve">10.8818311691284</t>
@@ -1001,10 +1001,10 @@
     <t xml:space="preserve">10.6796913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7807598114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8649864196777</t>
+    <t xml:space="preserve">10.78076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8649854660034</t>
   </si>
   <si>
     <t xml:space="preserve">10.7049579620361</t>
@@ -1016,22 +1016,22 @@
     <t xml:space="preserve">11.2608404159546</t>
   </si>
   <si>
-    <t xml:space="preserve">11.151349067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0839700698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0502805709839</t>
+    <t xml:space="preserve">11.1513500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0839691162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0502796173096</t>
   </si>
   <si>
     <t xml:space="preserve">11.2524185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3282222747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.378755569458</t>
+    <t xml:space="preserve">11.328221321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3787574768066</t>
   </si>
   <si>
     <t xml:space="preserve">11.3956003189087</t>
@@ -1040,22 +1040,22 @@
     <t xml:space="preserve">11.5050926208496</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4040250778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5556287765503</t>
+    <t xml:space="preserve">11.4040231704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.555627822876</t>
   </si>
   <si>
     <t xml:space="preserve">11.6819648742676</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7493438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9177932739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.884105682373</t>
+    <t xml:space="preserve">11.7493448257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9177942276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8841047286987</t>
   </si>
   <si>
     <t xml:space="preserve">11.943060874939</t>
@@ -1064,13 +1064,13 @@
     <t xml:space="preserve">12.0525531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0946655273438</t>
+    <t xml:space="preserve">12.0946664810181</t>
   </si>
   <si>
     <t xml:space="preserve">12.1536245346069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0357093811035</t>
+    <t xml:space="preserve">12.0357084274292</t>
   </si>
   <si>
     <t xml:space="preserve">12.0778207778931</t>
@@ -1079,22 +1079,22 @@
     <t xml:space="preserve">12.0441312789917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1788902282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1704683303833</t>
+    <t xml:space="preserve">12.1788911819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1704692840576</t>
   </si>
   <si>
     <t xml:space="preserve">12.3136510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3220739364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3726081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2041568756104</t>
+    <t xml:space="preserve">12.3220729827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3726062774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2041578292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.2883825302124</t>
@@ -1109,19 +1109,19 @@
     <t xml:space="preserve">11.7325000762939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8167247772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.010440826416</t>
+    <t xml:space="preserve">11.8167238235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0104417800903</t>
   </si>
   <si>
     <t xml:space="preserve">12.0020189285278</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9683294296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9262161254883</t>
+    <t xml:space="preserve">11.9683303833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.926215171814</t>
   </si>
   <si>
     <t xml:space="preserve">11.3113765716553</t>
@@ -1133,34 +1133,34 @@
     <t xml:space="preserve">10.6965360641479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8986759185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8228740692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0165901184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9407873153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7723369598389</t>
+    <t xml:space="preserve">10.8986749649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8228721618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0165891647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.940788269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7723388671875</t>
   </si>
   <si>
     <t xml:space="preserve">10.7976055145264</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7302265167236</t>
+    <t xml:space="preserve">10.7302255630493</t>
   </si>
   <si>
     <t xml:space="preserve">10.7218036651611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6628465652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6123113632202</t>
+    <t xml:space="preserve">10.6628475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6123123168945</t>
   </si>
   <si>
     <t xml:space="preserve">10.8060283660889</t>
@@ -1169,3298 +1169,3298 @@
     <t xml:space="preserve">10.6881141662598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8312959671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6712675094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4691286087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.48597240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0923910140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1597719192505</t>
+    <t xml:space="preserve">10.8312940597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6712684631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4691295623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4859733581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0923929214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1597709655762</t>
   </si>
   <si>
     <t xml:space="preserve">11.134503364563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1429271697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.218729019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4545583724976</t>
+    <t xml:space="preserve">11.1429281234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2187299728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4545593261719</t>
   </si>
   <si>
     <t xml:space="preserve">11.345067024231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4270172119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3175249099731</t>
+    <t xml:space="preserve">10.4270162582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3175239562988</t>
   </si>
   <si>
     <t xml:space="preserve">10.2417230606079</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2838344573975</t>
+    <t xml:space="preserve">10.2838335037231</t>
   </si>
   <si>
     <t xml:space="preserve">10.1911869049072</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1574974060059</t>
+    <t xml:space="preserve">10.1574964523315</t>
   </si>
   <si>
     <t xml:space="preserve">10.2248783111572</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1659212112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1069622039795</t>
+    <t xml:space="preserve">10.165919303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1069631576538</t>
   </si>
   <si>
     <t xml:space="preserve">10.0985412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93008995056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98904991149902</t>
+    <t xml:space="preserve">9.93009185791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98904800415039</t>
   </si>
   <si>
     <t xml:space="preserve">10.0058937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7195291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68583869934082</t>
+    <t xml:space="preserve">9.71953010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68584156036377</t>
   </si>
   <si>
     <t xml:space="preserve">9.4837007522583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37420749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.115385055542</t>
+    <t xml:space="preserve">9.37420845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1153869628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3091011047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5954647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7133808135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6038885116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.359637260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3006811141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4522848129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4017496109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5617771148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5449314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3427925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438619613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4101724624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4185934066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4354391098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2585668563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2333002090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.29225730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1490755081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0418586730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5365104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2754135131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2080316543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0648517608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93851375579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0500860214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.384801864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3075609207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.771014213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.676607131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5993661880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2303190231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.470627784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5049571990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6422758102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6851902008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.659441947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9340829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6508598327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452669143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5307054519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3933868408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3504724502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1444940567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.135910987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92135047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.075834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0586700439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89560222625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94709587097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74111843109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76686382293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85268878936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87843704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99001026153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2560663223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2903957366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.273229598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135402679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.48779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4362983703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3333082199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.084415435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1273288726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0157556533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0329217910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84410572052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0415029525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2389011383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78402900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.706787109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77544593811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68103885650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56088542938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59521389007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.689621925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47506046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.483642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62954521179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.912766456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88701915740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75828266143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56946754455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.578049659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73253440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61237907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71536922454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82694149017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1874074935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.221736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99859142303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96426200866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86985397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69820308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86127185821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52655410766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21758651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23475074768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69405555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52669429779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44087028503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12332057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43228912353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52240467071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41083240509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29926013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16623115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23060131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08469772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35504627227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22630977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48378372192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39366722106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57819080352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49236679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44945240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23489189147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11473655700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02032852172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79289245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72852563858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77143573760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83151483535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00316333770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02891063690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00745582580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25205707550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28638648986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61681270599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60823059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54815196990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75413131713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48807430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46232795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.161940574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19197845458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98170804977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0889892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33788204193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81435060501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.698486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99887418746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81864023208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86584568023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58691358566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63411712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68990278244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65986442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96454334259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93879652023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73696613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82279014587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47949123382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.385085105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40224838256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45374488830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.367919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49665641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50094795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46661758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59964847564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85712146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56960868835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56531715393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55673313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53957080841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50523948669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50953102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24776458740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15335750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39795780181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58248043060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77129650115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65972518920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09743022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96869373321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02018737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28624629974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31199264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08026504516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13176155090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32057476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94294548034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.814208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78846073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79704475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74554920196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72838497161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90861701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14034366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42356586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26049709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18325519561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00302314758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96011161804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76271343231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6511402130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.685471534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67689037322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87428569793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51797199249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44072914123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41498279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64670944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0672512054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.195987701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80977725982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62096118927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50938987731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86570358276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95152854919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83995532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75851821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77167415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74097442626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42080783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53483963012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57869815826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58746910095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47343730926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55238246917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42957973480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18397331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37694931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56992626190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67957305908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66202926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8944787979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75413227081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72781753540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72342967987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9383373260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82430458068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0611400604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00851058959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85062026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71465873718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88570785522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0523681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28043174743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32428932189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23657512664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92956447601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80676174163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78921890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49536800384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45589542388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48221015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62255668640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92079448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07868385314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0172815322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17958641052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1313419342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17081451416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96029567718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77170419692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61819982528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64890050888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63135719299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38574981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29803371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39013624191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22347450256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20593166351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28048992156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27171802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51293897628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39890813827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26733207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19277381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44276666641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45153856277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32873344421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53048324584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79363298416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98661088943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0611686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2234468460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28923225402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35063552856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21905899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19274520874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30239105224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87257766723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72346019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60942935943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74100255966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83310651779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84187746047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67521572113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50855445861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4032940864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45592451095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44715166091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31557655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47346782684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85064935684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85942029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00854015350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04362678527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80679082870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91643714904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18835830688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25414657592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29361915588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36379241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65325736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37256336212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43835163116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9646520614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12254238128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14885711669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37691974639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56112575531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75410270690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70147323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47340965270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35060501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49095344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24534606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42078018188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31551933288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48218154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64884185791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72778797149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80673122406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77164745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85936260223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81550407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86813449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9207649230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9997091293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8769063949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84181976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89444828033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9821662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0698823928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96462154388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67515850067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71901607513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79796123504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29797458648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52603912353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63129997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71024513244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68392944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69270133972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76287460327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73655891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57866859436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30674743652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21025848388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33306312561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20148658752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02605438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26289081573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13131332397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0874547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43832206726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42955017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21903038024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25411701202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15762996673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09622669219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39449214935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33747673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34186267852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1050271987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92959403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49978256225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6006555557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42960929870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11821365356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18400144577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57875728607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64892959594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5568265914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14017248153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38577938079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8770227432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9735107421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55244064331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11382818222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72784519195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82436275482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02172565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47349548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31560564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83316421508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9603533744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85070705413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61387252807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18406009674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47352504730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54369831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89895105361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82439184188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64895820617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69720268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92965221405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06122779846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0085973739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0568413734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40332221984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59191370010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83752107620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69717359542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86822175979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81120586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72348928451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48665380477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4822678565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36385107040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22789001464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77176237106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82000637054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26297521591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23227596282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21911716461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39454984664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59629964828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16207218170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51732444763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37259340286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33312034606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41645050048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79801988601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68398666381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55679750442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10067176818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35504961013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35066413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21031618118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23224639892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17522954940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10505723953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20154571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24540281295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21470355987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17084455490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40767908096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25856065750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36820650100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32434940338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14891481399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24978876113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4383807182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16645812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70155954360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61384296417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69278764724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75418996810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68401718139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71033191680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83313465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06119823455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1401424407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05681276321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04804039001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00856781005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94716739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07435655593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08751344680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09628486633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01734018325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35943555831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29364824295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49101114273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60504198074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9734525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57434034347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41206550598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88576459884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99102544784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0392689704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06997013092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31119155883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48223972320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86380624771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92082214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99976682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73661804199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68837308883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61381387710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62697172164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57872772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77608919143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240488052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96906757354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99099540710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15327167510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54799652099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56995630264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82433366775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66644525527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71907424926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78486156463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86819267272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22780323028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17517280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39446353912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83304691314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58744144439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40323638916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36814880371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35937690734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53481101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46463680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50849628448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41200733184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38569164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61375617980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49972438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03482532501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74533271789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90322113037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0961980819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1225128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93830871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66638660430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88567733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45586490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51726722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44709396362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82427501678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56989765167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94710826873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16640090942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28920364379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27165985107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34183406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19271659851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18394374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90324974060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06991100311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84184741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9997386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97342395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18857192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.198073387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1890983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43138885498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5749683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7275218963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79931163787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81725978851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94289207458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98776054382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79033756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74547004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68265438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70060157775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52112674713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51215362548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35062599182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53009986877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63778495788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61086463928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69162750244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5031795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58394336700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60188961029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55702114105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54804801940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35960006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76341724395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64675903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29678344726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33267784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38652038574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39549541473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7723913192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8890495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3915786743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5800266265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.651816368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6877117156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7415542602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8582134246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9389762878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9838438034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0556344985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1005029678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0915288925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1274242401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.019739151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9300022125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312902450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0107669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9748706817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8761596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.912055015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0466604232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9210271835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8941068649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9030799865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8043699264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.75950050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7864236831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8402643203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4274730682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2569732666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90699768066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96083927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1223659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1313400268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1403150558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0954446792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87110137939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80828666687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56599521636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47625827789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67368030548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70957469940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75444316864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84418106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85315418243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82623291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86212825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0236549377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96981239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1672353744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492881774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2031297683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1851825714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2838935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3377361297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4454212188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5172109603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3467092514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3018417358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4184999465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4364461898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7774496078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8492393493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6966857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7684745788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5620784759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0864715576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2479991912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4902896881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5979738235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8671855926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1453704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9658975601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9569234848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.082555770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1094779968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1722927093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2440814971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2261352539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1902408599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4594526290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6299524307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8004531860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0068492889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6568746566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8453226089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2171611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2081880569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3248462677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2620306015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1363983154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8223171234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3287630081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.373631477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.544132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7056589126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6159229278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4095258712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7146329879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6248960494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4005517959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6069469451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44933700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81668853759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01354026794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0225133895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15712070465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48914909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20198822021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34556865692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53850364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67759609222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09038734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96924209594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01859664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1083345413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18012523651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13525676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98270320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79874134063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90642642974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34165287017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25191497802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08141326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97373008728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.036545753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83014965057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43979263305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26480484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36351490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27377796173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30967330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35005474090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36800193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51606941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94232177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70900440216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57439804077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45773887634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46671485900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61478042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4936351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30069828033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18404102325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25134372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12571144104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88399124145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65573215484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6856861114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58440971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63044357299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87903022766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0539617538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2104806900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95268630981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98030757904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0355491638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89744472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0631704330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1184110641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1552381515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63965129852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40027046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22533893585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4463062286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87087249755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95833873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98596000671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02278614044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03199481964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66832065582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62228488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67292404174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77419853210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73737239837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53482055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52561283111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30464744567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35988807678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80642414093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08263206481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85706233978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88928604125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82023429870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60847568511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90309619903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00437259674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06882190704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10564994812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14247703552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99976921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71895790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86166572570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17470169067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47392654418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59361553192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64885711669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77775478363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72251319885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55678844451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7593412399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171901702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66727161407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37265014648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53837394714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21613311767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84325122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00897598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92611312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59466457366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56244087219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57164764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44275093078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38750839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45195770263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14352512359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12511157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23559474945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23099040985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42433643341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76959609985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75578689575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7926139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51640510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31385326385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33226776123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2171802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09749126434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01923179626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77985143661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88112878799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83049011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82588720321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49443769454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82128238677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9731969833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31845664978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2217845916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34147548675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30924987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29543972015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68213176727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47037124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61307811737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66371631622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73276805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90770053863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91690826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97214889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79721736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19311428070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54758167266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8237886428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79616832733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74092674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80537509918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0723752975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.219687461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8641719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7260675430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6892404556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444820404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5143089294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2381019592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3393774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841348648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3209638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1368255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1828594207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3485841751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.192066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0815830230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90665149688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85140991210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94347953796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86061763763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75013446807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65806484222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60282325744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48313331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62123680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8329963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.146032333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1276168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2473077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4866886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5327215194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.772102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6800336837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4038257598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7352743148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5695505142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6616191864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9286203384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9654483795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3889665603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7940721511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1163129806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2912454605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3372802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1623487472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9874172210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0886926651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8585195541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.318865776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3649015426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2820377349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2083826065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2636241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6779365539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8620748519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7275257110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7367324829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4789390563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1290760040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5950736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8252477645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896951675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5582466125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6963500976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6134872436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0058307647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9137601852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.171555519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0518655776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2267961502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2175903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3280735015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9966239929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9321756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4293489456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7700042724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2728319168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5674524307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.503005027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4661769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4845905303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3096580505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.024245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1991758346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2544174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.650315284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0738344192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2855939865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2579717636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1751108169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2119388580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1659030914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3040065765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2947998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3417444229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1821327209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9849634170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3041896820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2854108810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3323554992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3511343002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5389137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6891374588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5013580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4450235366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4168567657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4544124603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4919691085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6140260696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9895839691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9614181518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7548599243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8299722671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5952472686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5201358795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.703293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3840675354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3652906417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2150678634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3183460235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5061254501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6000146865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7502393722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6469602584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6281824111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5249042510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5342931747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4404029846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2526226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4028472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3277349472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1493434906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2901792526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2244567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2620124816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5155143737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4310131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1211767196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0836219787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4122362136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0930109024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2338447570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0272874832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9803428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9333972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0178985595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1305665969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0648441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.205677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9991207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8488969802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9240083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7268390655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9146194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9897317886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0554542541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0460653305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0742321014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9709539413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8770637512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7737846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3512811660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4827260971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6047830581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5578384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5484495162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6329507827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.510892868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.670506477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4076137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3606700897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3231143951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9006090164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9381647109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.994499206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0414447784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9851102828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8254976272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7785530090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6001615524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7034406661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4123821258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7503852844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7222185134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6471071243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.31849193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1588792800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1025457382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98048877716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81148719787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66126346588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68004131317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68943119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71759796142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53920650482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48287391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4077615737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52981758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51103973388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80209827423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96171092987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90537738800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69882011413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86782169342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94293308258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85843181610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1776580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93354415893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.018045425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0649900436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89598751068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78332042694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88659858703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99926662445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2527694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1307134628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2809362411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1964349746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3560485839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5062713623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4029932022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2246036529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97109985351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.487494468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4405498504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3654375076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5907726287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6658849716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5719957351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4499387741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4217710494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4687156677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.327880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3936042785645</t>
   </si>
   <si>
     <t xml:space="preserve">10.309103012085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5954656600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7133817672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.603889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.359637260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3006792068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4522848129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4017496109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5617771148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5449304580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.342791557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4101715087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4185943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4354391098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.25856590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2333011627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.29225730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1490755081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0418586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5365104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2754125595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2080335617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0648517608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93851375579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0500860214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3848028182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3075609207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7710151672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6766080856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5993661880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.230318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.470627784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.504958152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6422786712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6851892471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6594429016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9340829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6508598327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452669143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5307064056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.393385887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.350471496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.144492149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1359119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92134952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.075834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.058669090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89560222625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.947096824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74111652374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76686477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85268783569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87843608856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99000930786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2560653686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2903966903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2732315063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135402679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4877939224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4362983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3333082199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0844163894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1273288726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0157556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0329217910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84410667419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.04150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2389011383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78402900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.706787109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77544689178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68103885650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56088638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68962287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47505950927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.483642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62954521179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.912766456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88701915740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75828170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56946659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57804870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73253440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61237907409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71537017822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82694244384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.187406539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2217359542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99859142303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96426200866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86985397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69820404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86127185821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52655601501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21758556365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23474979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69405460357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52669620513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4408712387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12332057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43228816986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52240371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41083240509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29926013946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16623115539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23059940338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08469772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35504627227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22630786895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48378372192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39366626739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57819080352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49236679077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44945335388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23489189147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11473560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02032947540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79289150238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72852516174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77143669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83151483535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00316429138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02891063690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00745582580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25205707550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28638648986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61681175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60822868347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54815101623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75413036346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48807430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.462327003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16193962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19197940826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98170757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0889892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33788108825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81435012817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69848680496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99887323379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8186411857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86584424972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58691358566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.634117603302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68990278244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65986490249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96454429626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.938796043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73696613311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82279109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47949123382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38508415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40224933624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45374393463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.367919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49665641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50094795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46661853790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59964656829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85712146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56960964202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56531715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55673408508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53956985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50523853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50953102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24776458740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15335655212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39795780181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58248138427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77129650115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65972423553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09743022918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96869277954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02018737792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28624439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31199264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08026599884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13175964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32057476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94294548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.814208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78846073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.797043800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74554920196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72838497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.908616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14034366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42356586456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.260498046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18325614929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00302314758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96011161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76271343231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65114116668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.685471534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67688846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87428569793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51797294616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44073009490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41498279571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64670944213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0672512054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1959896087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80977630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62096118927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50938987731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86570262908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95152854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83995532989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75851726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77167510986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74097347259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42080783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53484058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57869815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58746910095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47343730926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55238342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42957973480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18397331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37695026397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56992626190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67957210540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66202831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89447975158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75413131713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72781753540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72343158721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9383373260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82430458068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06114101409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00851058959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85062026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71465873718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88570785522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0523681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28043174743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32429027557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23657417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9295654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80676174163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78921890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49536800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45589447021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48221111297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62255668640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92079448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07868385314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0172815322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17958641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13134288787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17081546783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96029615402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77170419692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61819982528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6488995552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63135766983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38574934005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29803466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39013624191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22347354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20593118667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28048992156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27171754837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.512939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39890718460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26733255386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19277286529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4427661895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4515380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32873344421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53048276901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79363298416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98661041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06116962432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22344589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28923225402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35063552856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21905994415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19274425506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30239009857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87257862091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72345972061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60942840576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74100208282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83310604095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84187746047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67521572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50855398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40329360961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45592451095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44715213775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31557703018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4734673500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85064935684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85942029953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00854015350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.043625831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80679035186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91643667221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18835926055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25414752960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29361915588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36379051208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65325736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3725643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43835067749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9646520614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12254333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1488561630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37692070007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56112480163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75410175323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70147323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47340869903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35060501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49095249176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24534511566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42078018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31551933288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48218154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64884281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72778701782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80673313140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77164649963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85936164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81550407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86813354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92076301574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9997091293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87690734863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84182071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89445018768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9821662902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0698823928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96462345123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67515754699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71901607513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79796028137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29797458648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52603816986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63129997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71024417877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68392944335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69270038604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76287364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73655891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57866954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30674743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2102575302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33306217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20148754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02605533599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26288986206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13131523132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0874547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43832302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42955017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21903038024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25411796569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15762996673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09622764587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39449214935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33747673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34186267852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1050271987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92959308624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49978303909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60065603256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42960929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11821413040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18400192260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57875633239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64892959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5568265914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14017200469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3857798576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87702226638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9735107421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55244064331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1138277053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72784566879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82436275482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02172565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47349548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31560516357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83316373825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96035289764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85070705413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61387252807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18406009674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47352504730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54369831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89895105361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82439279556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64895868301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69720268249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92965173721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06122732162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0085973739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0568413734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40332269668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59191370010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83752107620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69717407226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86822128295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81120586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72348880767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48665332794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4822678565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36385059356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22788953781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77176237106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82000637054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26297569274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23227548599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21911716461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39455080032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59629964828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16207218170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51732444763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37259340286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33312034606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41645097732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79801988601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68398666381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55679893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10067176818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35504913330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35066413879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21031665802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23224544525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17523002624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10505676269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20154523849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24540328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21470308303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17084407806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40767955780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25856065750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3682074546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32434940338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14891481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24978923797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43838024139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16645812988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70156002044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61384248733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69278717041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75418949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68401718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71033143997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83313465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06119775772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1401424407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05681276321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04804039001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00856876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94716644287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0743556022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08751344680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09628486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0173397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35943555831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29364824295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4910101890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60504245758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97345304489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57434177398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41206550598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88576459884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9910249710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03926944732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06997013092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31119155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48223924636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8638072013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92082262039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9997673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73661708831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68837404251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61381387710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62697124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57872676849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77609014511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80240631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96906614303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99099540710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15327072143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54799842834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56995534896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82433414459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66644334793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71907377243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78486204147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86819267272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22780227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17517185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39446353912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83304691314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58744049072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40323543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36814975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35937786102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53481101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46463680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50849628448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41200637817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38569164276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61375713348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49972438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03482532501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74533176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90322208404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0961971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1225128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.938307762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6663875579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88567638397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45586490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51726722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44709300994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82427597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56989765167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94710826873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16640090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28920459747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27166080474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34183406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19271564483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18394470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9032506942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06991291046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8418493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9997386932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97342300415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18857192993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19807243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1890983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43138980865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57496929168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72752285003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79931259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81725883483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94289207458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98776149749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79033756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74546909332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68265342712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70060157775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52112674713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51215267181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35062599182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53010082244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63778495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61086368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69162750244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50317859649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58394336700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60188961029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55702114105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5480489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35960102081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76341724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64675903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29678249359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33267784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38652038574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39549446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77239227294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88905048370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3915786743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5800256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.651816368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6877107620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7415542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8582124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9389743804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9838447570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0556344985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1005029678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0915298461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.127423286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.019739151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9300022125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0107660293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9748697280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8761587142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.912055015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0466604232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.921028137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8941078186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9030818939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8043699264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7595014572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7864217758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8402643203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.427472114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2569732666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90699768066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96083927154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1223659515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1313409805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1403141021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0954456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87110137939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8082857131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56599617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47625923156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67367935180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70957469940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75444412231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84418106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85315418243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82623386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86212730407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0236549377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96981239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1672344207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492881774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2031297683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1851835250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2838945388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3377370834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4454212188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5172100067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3467102050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3018407821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4184989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.436448097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7774486541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8492393493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6966857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7684745788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5620794296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0864715576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2479991912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4902896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5979738235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8671855926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1453704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9658975601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9569234848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.082555770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1094770431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1722936630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2440824508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2261352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1902408599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4594526290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6299533843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8004541397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0068492889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6568746566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8453226089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2171611785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2081880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3248462677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2620315551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1363973617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8223180770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3287620544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5351581573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3736305236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.544132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7056589126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6159219741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4095258712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7146329879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6248960494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4005527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6069478988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44933605194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81668853759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01354026794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0225133895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15712070465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48914813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20198822021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34556865692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5385046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6775951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09038734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96924209594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01859855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1083345413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18012428283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13525676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98270416259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79874134063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34165287017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25191497802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08141422271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97372913360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03654479980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83014965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43979167938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26480484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36351585388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27377796173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30967330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35005569458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36800193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51606845855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94232082366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70900440216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57439804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45773983001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46671390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61478042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4936351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30069923400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18404102325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25134372711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12571239471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88399124145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65573215484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6856861114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58440971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63044357299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87903118133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0539627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2104797363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95268630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98030757904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.035548210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89744472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0631694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1184101104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1552391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63965034484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40027141571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22533988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4463062286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87087249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95833778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98595905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02278709411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03199481964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66831970214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62228584289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67292404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77419948577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73737144470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53481960296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52561283111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30464744567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35988807678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80642318725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08263206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85706233978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88928699493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82023429870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60847568511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90309619903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00437259674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06882190704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1056489944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14247798919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99976921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71895885467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86166477203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17470073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47392559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5936164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64885711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77775478363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72251415252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55678844451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75934028625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66727161407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37265014648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53837394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21613311767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84325122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00897598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92611408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59466361999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56244087219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57164859771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44274997711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38750839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45195770263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14352607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1251106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23559474945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23099040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42433643341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76959609985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75578594207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7926139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51640605926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31385326385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33226680755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2171802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09749126434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01923179626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77985143661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88112878799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83049058914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82588672637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4944372177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82128286361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97319746017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31845664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2217845916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34147453308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30924987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29544067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68213081359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47037124633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61307907104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66371726989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73276805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90770053863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91690731048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97214889526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79721736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.193115234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54758071899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82378959655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79616928100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74092674255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80537509918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0723752975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2196865081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8641710281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7260675430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6892395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444820404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5143089294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2381019592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3393774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841348648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3209629058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1368246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1828603744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3485841751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.192066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0815839767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90665149688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85140895843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94347953796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86061668395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7501335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65806484222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60282421112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48313236236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62123680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8329963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.146032333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1276168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2473087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4866876602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5327224731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.772102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6800336837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4038257598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7352752685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5695495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6616201400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9286203384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9654474258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3889665603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7940711975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1163139343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2912454605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3372802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1623477935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9874172210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0886926651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8585195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.318865776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3649005889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2820377349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2083835601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2636241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6779365539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8620748519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7275257110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7367324829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4789390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1290760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5950736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8252468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8896951675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5582466125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6963500976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6134881973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0058298110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9137601852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1715545654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0518655776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2267961502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2175903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3280735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9966230392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9321756362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4293489456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7700061798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2728309631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5674524307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.503005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4661769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4845914840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3096590042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.024245262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1991767883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2544183731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6503143310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0738344192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2855939865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2579717636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1751098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2119379043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1659030914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3040065765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2947998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3417453765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1821327209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9849634170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3041896820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2854108810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3323564529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3511343002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5389137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6891374588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5013580322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4450235366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4168567657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4544134140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4919681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6140260696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9895849227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9614171981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7548599243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8299722671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5952472686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5201349258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.703293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3840684890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3652906417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2150678634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3183460235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5061254501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6000156402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7502393722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6469612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6281814575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5249032974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5342931747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4404029846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2526226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4028463363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3277349472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1493434906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2901792526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2244567871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2620124816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5155143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4310140609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1211767196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0836210250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4122352600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0930099487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2338447570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0272874832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9803428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9333972930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0178985595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1305665969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0648441314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2056789398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9991207122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8488969802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9240083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7268400192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9146194458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9897317886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0554552078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0460653305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0742321014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9709529876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8770627975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7737846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3512811660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4827260971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6047830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5578384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5484495162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6329507827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4545593261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5108938217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.670506477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4076147079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3606700897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3231143951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9006090164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9381647109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.994499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0414447784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9851102828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8254976272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7785520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6001625061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7034406661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4123821258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7503852844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7222194671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6471061706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.31849193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1588792800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1025457382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98048877716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81148719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66126346588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68004131317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68943023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71759796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53920650482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48287391662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4077615737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52981758117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51103973388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80209827423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96171092987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90537738800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69882011413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86782169342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94293308258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85843276977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1776580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93354415893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.018045425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0649909973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89598751068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78332042694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88659858703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99926662445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2527694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1307125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2809371948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1964349746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3560485839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.506272315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4029932022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2246036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97109985351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4874935150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4405498504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3654375076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5907726287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6658849716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5719947814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4499387741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4217710494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4687156677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.327880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3936042785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2621583938599</t>
+    <t xml:space="preserve">10.2621593475342</t>
   </si>
   <si>
     <t xml:space="preserve">10.1870470046997</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">10.1401023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058248519897</t>
+    <t xml:space="preserve">10.2058238983154</t>
   </si>
   <si>
     <t xml:space="preserve">10.6095514297485</t>
@@ -4490,10 +4490,10 @@
     <t xml:space="preserve">10.7409963607788</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9099979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7316083908081</t>
+    <t xml:space="preserve">10.9099988937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7316074371338</t>
   </si>
   <si>
     <t xml:space="preserve">10.8912210464478</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">10.7128295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7879409790039</t>
+    <t xml:space="preserve">10.7879419326782</t>
   </si>
   <si>
     <t xml:space="preserve">10.9287767410278</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">11.0602216720581</t>
   </si>
   <si>
-    <t xml:space="preserve">11.003888130188</t>
+    <t xml:space="preserve">11.0038890838623</t>
   </si>
   <si>
     <t xml:space="preserve">10.8818321228027</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">11.1728897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2949466705322</t>
+    <t xml:space="preserve">11.2949457168579</t>
   </si>
   <si>
     <t xml:space="preserve">11.1447229385376</t>
@@ -4571,7 +4571,7 @@
     <t xml:space="preserve">11.0508337020874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2480020523071</t>
+    <t xml:space="preserve">11.2480010986328</t>
   </si>
   <si>
     <t xml:space="preserve">11.3982257843018</t>
@@ -4583,16 +4583,16 @@
     <t xml:space="preserve">11.3418912887573</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1259450912476</t>
+    <t xml:space="preserve">11.1259460449219</t>
   </si>
   <si>
     <t xml:space="preserve">11.2386131286621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292232513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9757213592529</t>
+    <t xml:space="preserve">11.2292242050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9757204055786</t>
   </si>
   <si>
     <t xml:space="preserve">11.6104164123535</t>
@@ -4613,10 +4613,10 @@
     <t xml:space="preserve">11.4094924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3249921798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1090450286865</t>
+    <t xml:space="preserve">11.3249912261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1090440750122</t>
   </si>
   <si>
     <t xml:space="preserve">10.4705944061279</t>
@@ -4628,7 +4628,7 @@
     <t xml:space="preserve">10.4536933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3691921234131</t>
+    <t xml:space="preserve">10.3691930770874</t>
   </si>
   <si>
     <t xml:space="preserve">10.4799823760986</t>
@@ -5619,6 +5619,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.02499961853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35499954223633</t>
   </si>
 </sst>
 </file>
@@ -57013,7 +57016,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1964" t="s">
-        <v>1414</v>
+        <v>394</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -57039,7 +57042,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1965" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -57065,7 +57068,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1966" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -57091,7 +57094,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -57117,7 +57120,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1968" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -57143,7 +57146,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1969" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -57169,7 +57172,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G1970" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -57195,7 +57198,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1971" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -57221,7 +57224,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1972" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -57247,7 +57250,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1973" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -57273,7 +57276,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1974" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -57299,7 +57302,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G1975" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -57325,7 +57328,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1976" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -57351,7 +57354,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1977" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -57377,7 +57380,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1978" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -57403,7 +57406,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1979" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -57429,7 +57432,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1980" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -57455,7 +57458,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1981" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -57481,7 +57484,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1982" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -57507,7 +57510,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G1983" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -57533,7 +57536,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1984" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -57559,7 +57562,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1985" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -57585,7 +57588,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G1986" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -57611,7 +57614,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1987" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -57637,7 +57640,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G1988" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -57663,7 +57666,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G1989" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -57689,7 +57692,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1990" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -57715,7 +57718,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G1991" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -57741,7 +57744,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1992" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -57767,7 +57770,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1993" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -57793,7 +57796,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1994" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -57819,7 +57822,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1995" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -57845,7 +57848,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G1996" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -57871,7 +57874,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1997" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -57897,7 +57900,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G1998" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -57923,7 +57926,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -57949,7 +57952,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G2000" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -57975,7 +57978,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G2001" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -58001,7 +58004,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G2002" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -58027,7 +58030,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2003" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -58053,7 +58056,7 @@
         <v>10.5</v>
       </c>
       <c r="G2004" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -58079,7 +58082,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G2005" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -58105,7 +58108,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2006" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -58131,7 +58134,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2007" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -58157,7 +58160,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G2008" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -58183,7 +58186,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2009" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -58209,7 +58212,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2010" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -58235,7 +58238,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2011" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -58261,7 +58264,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2012" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -58287,7 +58290,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G2013" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -58313,7 +58316,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G2014" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -58339,7 +58342,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G2015" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -58365,7 +58368,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2016" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -58391,7 +58394,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G2017" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -58417,7 +58420,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G2018" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -58443,7 +58446,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2019" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -58469,7 +58472,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G2020" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -58495,7 +58498,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2021" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -58521,7 +58524,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2022" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -58547,7 +58550,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G2023" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -58573,7 +58576,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G2024" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -58599,7 +58602,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2025" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -58625,7 +58628,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2026" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -58651,7 +58654,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G2027" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -58677,7 +58680,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G2028" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -58703,7 +58706,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2029" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -58729,7 +58732,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G2030" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -58755,7 +58758,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G2031" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -58781,7 +58784,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2032" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -58807,7 +58810,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2033" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -58833,7 +58836,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2034" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -58859,7 +58862,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G2035" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -58885,7 +58888,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2036" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58911,7 +58914,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2037" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58937,7 +58940,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2038" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58963,7 +58966,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G2039" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -58989,7 +58992,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2040" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -59015,7 +59018,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G2041" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -59041,7 +59044,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2042" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -59067,7 +59070,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G2043" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -59093,7 +59096,7 @@
         <v>11</v>
       </c>
       <c r="G2044" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -59119,7 +59122,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G2045" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -59145,7 +59148,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G2046" t="s">
-        <v>414</v>
+        <v>1481</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -59171,7 +59174,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G2047" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -59483,7 +59486,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G2059" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -59613,7 +59616,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2064" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -59925,7 +59928,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G2076" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59951,7 +59954,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G2077" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -60185,7 +60188,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G2086" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -60315,7 +60318,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2091" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -61017,7 +61020,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2118" t="s">
-        <v>1414</v>
+        <v>394</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -70749,7 +70752,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6494907407</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>685655</v>
@@ -70770,6 +70773,32 @@
         <v>1868</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6496643518</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>967853</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>9.38000011444092</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>8.94499969482422</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>9.02499961853027</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>9.35499954223633</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="1873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="1874">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16937780380249</t>
+    <t xml:space="preserve">7.16937732696533</t>
   </si>
   <si>
     <t xml:space="preserve">BRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13994884490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92740154266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52519750595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54154682159424</t>
+    <t xml:space="preserve">7.13994836807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92740201950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52519702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54154634475708</t>
   </si>
   <si>
     <t xml:space="preserve">6.42873334884644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60040712356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78188848495483</t>
+    <t xml:space="preserve">6.60040616989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78188800811768</t>
   </si>
   <si>
     <t xml:space="preserve">6.55135679244995</t>
@@ -86,16 +86,16 @@
     <t xml:space="preserve">6.24888610839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30610990524292</t>
+    <t xml:space="preserve">6.30610942840576</t>
   </si>
   <si>
     <t xml:space="preserve">6.31919002532959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38785886764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23090076446533</t>
+    <t xml:space="preserve">6.38785934448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23090028762817</t>
   </si>
   <si>
     <t xml:space="preserve">6.16713666915894</t>
@@ -104,31 +104,31 @@
     <t xml:space="preserve">6.05922794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99219465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86466503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70443820953369</t>
+    <t xml:space="preserve">5.99219417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86466598510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70443773269653</t>
   </si>
   <si>
     <t xml:space="preserve">5.35945844650269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5164155960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72242259979248</t>
+    <t xml:space="preserve">5.51641511917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72242307662964</t>
   </si>
   <si>
     <t xml:space="preserve">5.67500829696655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73223400115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03960847854614</t>
+    <t xml:space="preserve">5.73223257064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03960800170898</t>
   </si>
   <si>
     <t xml:space="preserve">5.97420978546143</t>
@@ -137,37 +137,37 @@
     <t xml:space="preserve">6.11972236633301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14097738265991</t>
+    <t xml:space="preserve">6.1409764289856</t>
   </si>
   <si>
     <t xml:space="preserve">6.10010290145874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23744058609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11154794692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9758448600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07394313812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12953329086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21945667266846</t>
+    <t xml:space="preserve">6.23744106292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11154747009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97584533691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07394409179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12953281402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2194561958313</t>
   </si>
   <si>
     <t xml:space="preserve">6.35188961029053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32409620285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04675531387329</t>
+    <t xml:space="preserve">6.32409572601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04675579071045</t>
   </si>
   <si>
     <t xml:space="preserve">7.08272457122803</t>
@@ -179,31 +179,31 @@
     <t xml:space="preserve">7.07945442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12032985687256</t>
+    <t xml:space="preserve">7.12032842636108</t>
   </si>
   <si>
     <t xml:space="preserve">7.07127952575684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06637477874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16120386123657</t>
+    <t xml:space="preserve">7.06637525558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16120433807373</t>
   </si>
   <si>
     <t xml:space="preserve">7.14321899414062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2494912147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14158487319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22987127304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07618427276611</t>
+    <t xml:space="preserve">7.24949264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14158344268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22987174987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0761833190918</t>
   </si>
   <si>
     <t xml:space="preserve">7.2691125869751</t>
@@ -212,124 +212,124 @@
     <t xml:space="preserve">7.15302801132202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1513934135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31489086151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43097543716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40318059921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35576486587524</t>
+    <t xml:space="preserve">7.15139436721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31489133834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43097496032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40317964553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35576629638672</t>
   </si>
   <si>
     <t xml:space="preserve">7.1448540687561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18899917602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16283798217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27401733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998611450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35740041732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40644979476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42279863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39337110519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43914890289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47184944152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51108837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76778030395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71546030044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63534736633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68276119232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74162101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66968297958374</t>
+    <t xml:space="preserve">7.18899822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16283845901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2740159034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998754501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3574013710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40644931793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42279958724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39336967468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43914985656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47185039520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51108932495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76777935028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71546220779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63534688949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68276166915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74162006378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66968202590942</t>
   </si>
   <si>
     <t xml:space="preserve">7.72200012207031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63044261932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7105565071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85607004165649</t>
+    <t xml:space="preserve">7.63044214248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71055698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85606908798218</t>
   </si>
   <si>
     <t xml:space="preserve">8.47735977172852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50188732147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51006126403809</t>
+    <t xml:space="preserve">8.50188636779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51005935668945</t>
   </si>
   <si>
     <t xml:space="preserve">8.55093574523926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42831230163574</t>
+    <t xml:space="preserve">8.42831134796143</t>
   </si>
   <si>
     <t xml:space="preserve">8.36291217803955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35473728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41196155548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5199146270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45348262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51161098480225</t>
+    <t xml:space="preserve">8.354736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41196250915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51991558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45348167419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51161193847656</t>
   </si>
   <si>
     <t xml:space="preserve">8.46178531646729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47008991241455</t>
+    <t xml:space="preserve">8.47009086608887</t>
   </si>
   <si>
     <t xml:space="preserve">8.6112585067749</t>
@@ -338,13 +338,13 @@
     <t xml:space="preserve">8.63617134094238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72751331329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96002674102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86868190765381</t>
+    <t xml:space="preserve">8.72751522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9600248336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86868286132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.86037826538086</t>
@@ -359,40 +359,40 @@
     <t xml:space="preserve">8.10969638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30400943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3123140335083</t>
+    <t xml:space="preserve">8.30400848388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">8.60295391082764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61956310272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56973743438721</t>
+    <t xml:space="preserve">8.61956214904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56973934173584</t>
   </si>
   <si>
     <t xml:space="preserve">8.71921157836914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25916957855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64135026931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25418472290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0598726272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20602130889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23757648468018</t>
+    <t xml:space="preserve">8.25916767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64134931564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25418663024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05987167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20602226257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23757743835449</t>
   </si>
   <si>
     <t xml:space="preserve">7.84728908538818</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">7.67954874038696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67788791656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95524024963379</t>
+    <t xml:space="preserve">7.67788696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95524120330811</t>
   </si>
   <si>
     <t xml:space="preserve">8.02831649780273</t>
@@ -413,25 +413,25 @@
     <t xml:space="preserve">8.05488872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97849178314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14457130432129</t>
+    <t xml:space="preserve">7.97849273681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14457225799561</t>
   </si>
   <si>
     <t xml:space="preserve">8.11301708221436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23425769805908</t>
+    <t xml:space="preserve">8.23425674438477</t>
   </si>
   <si>
     <t xml:space="preserve">8.10471439361572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21100521087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16782283782959</t>
+    <t xml:space="preserve">8.21100425720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16782474517822</t>
   </si>
   <si>
     <t xml:space="preserve">8.32061862945557</t>
@@ -440,28 +440,31 @@
     <t xml:space="preserve">8.37044239044189</t>
   </si>
   <si>
+    <t xml:space="preserve">8.41196346282959</t>
+  </si>
+  <si>
     <t xml:space="preserve">8.50330543518066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36213684082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67768955230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76903438568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53652191162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55312824249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64447498321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73581695556641</t>
+    <t xml:space="preserve">8.36213779449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67769050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76903533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53652286529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55313014984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64447402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73581886291504</t>
   </si>
   <si>
     <t xml:space="preserve">8.68599414825439</t>
@@ -470,16 +473,16 @@
     <t xml:space="preserve">8.74412250518799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6693868637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48669719696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44517803192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47839450836182</t>
+    <t xml:space="preserve">8.66938781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48669624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4451789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47839546203613</t>
   </si>
   <si>
     <t xml:space="preserve">8.40365695953369</t>
@@ -494,43 +497,43 @@
     <t xml:space="preserve">8.69429874420166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71090507507324</t>
+    <t xml:space="preserve">8.71090602874756</t>
   </si>
   <si>
     <t xml:space="preserve">8.89359474182129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84377002716064</t>
+    <t xml:space="preserve">8.84377098083496</t>
   </si>
   <si>
     <t xml:space="preserve">8.88529109954834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78564262390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80225086212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81885719299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90189743041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05137157440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81055545806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6278657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70260143280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82716083526611</t>
+    <t xml:space="preserve">8.78564357757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80224895477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81885814666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90189838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05137062072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81055450439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62786674499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70260238647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82716178894043</t>
   </si>
   <si>
     <t xml:space="preserve">8.75242614746094</t>
@@ -548,16 +551,16 @@
     <t xml:space="preserve">9.35031604766846</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35861873626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15102005004883</t>
+    <t xml:space="preserve">9.35861968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15101909637451</t>
   </si>
   <si>
     <t xml:space="preserve">8.93511486053467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7773380279541</t>
+    <t xml:space="preserve">8.77733707427979</t>
   </si>
   <si>
     <t xml:space="preserve">9.19254016876221</t>
@@ -566,10 +569,10 @@
     <t xml:space="preserve">9.44996356964111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17593002319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00154685974121</t>
+    <t xml:space="preserve">9.17593097686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00154590606689</t>
   </si>
   <si>
     <t xml:space="preserve">9.1344108581543</t>
@@ -581,13 +584,13 @@
     <t xml:space="preserve">8.9268102645874</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00985050201416</t>
+    <t xml:space="preserve">9.00985145568848</t>
   </si>
   <si>
     <t xml:space="preserve">8.98493766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7607307434082</t>
+    <t xml:space="preserve">8.76072978973389</t>
   </si>
   <si>
     <t xml:space="preserve">9.11780261993408</t>
@@ -596,7 +599,7 @@
     <t xml:space="preserve">9.22575569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95172119140625</t>
+    <t xml:space="preserve">8.95172214508057</t>
   </si>
   <si>
     <t xml:space="preserve">9.06797885894775</t>
@@ -608,49 +611,49 @@
     <t xml:space="preserve">9.20084381103516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31710052490234</t>
+    <t xml:space="preserve">9.31709957122803</t>
   </si>
   <si>
     <t xml:space="preserve">9.36692428588867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49148464202881</t>
+    <t xml:space="preserve">9.49148273468018</t>
   </si>
   <si>
     <t xml:space="preserve">9.54961204528809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96481323242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0229415893555</t>
+    <t xml:space="preserve">9.96481132507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0229396820068</t>
   </si>
   <si>
     <t xml:space="preserve">9.82364368438721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93990135192871</t>
+    <t xml:space="preserve">9.93990039825439</t>
   </si>
   <si>
     <t xml:space="preserve">9.98141956329346</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0063323974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0561561584473</t>
+    <t xml:space="preserve">10.0063314437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0561571121216</t>
   </si>
   <si>
     <t xml:space="preserve">10.2056283950806</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2305402755737</t>
+    <t xml:space="preserve">10.230541229248</t>
   </si>
   <si>
     <t xml:space="preserve">10.2139339447021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.197322845459</t>
+    <t xml:space="preserve">10.1973237991333</t>
   </si>
   <si>
     <t xml:space="preserve">10.1558046340942</t>
@@ -659,34 +662,34 @@
     <t xml:space="preserve">10.1225881576538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1807174682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.147500038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2222356796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1308927536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.097677230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84855651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3135814666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0810689926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0727643966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5294857025146</t>
+    <t xml:space="preserve">10.1807155609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1475009918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2222347259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1308917999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0976753234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84855461120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3135805130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0810680389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0727634429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.529483795166</t>
   </si>
   <si>
     <t xml:space="preserve">10.4464435577393</t>
@@ -701,19 +704,19 @@
     <t xml:space="preserve">10.4713554382324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6872606277466</t>
+    <t xml:space="preserve">10.6872615814209</t>
   </si>
   <si>
     <t xml:space="preserve">10.720477104187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6540451049805</t>
+    <t xml:space="preserve">10.6540441513062</t>
   </si>
   <si>
     <t xml:space="preserve">10.4049253463745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6457405090332</t>
+    <t xml:space="preserve">10.6457414627075</t>
   </si>
   <si>
     <t xml:space="preserve">10.7952127456665</t>
@@ -722,22 +725,22 @@
     <t xml:space="preserve">10.9612941741943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9280767440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7703008651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7786045074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8699502944946</t>
+    <t xml:space="preserve">10.9280776977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7703018188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7786064147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8699493408203</t>
   </si>
   <si>
     <t xml:space="preserve">10.7869091033936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0360298156738</t>
+    <t xml:space="preserve">11.0360288619995</t>
   </si>
   <si>
     <t xml:space="preserve">10.8948621749878</t>
@@ -746,13 +749,13 @@
     <t xml:space="preserve">11.0443334579468</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2519330978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1771974563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2270212173462</t>
+    <t xml:space="preserve">11.2519340515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1771984100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2270202636719</t>
   </si>
   <si>
     <t xml:space="preserve">11.2602376937866</t>
@@ -767,28 +770,28 @@
     <t xml:space="preserve">11.393102645874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4512310028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5093574523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5010538101196</t>
+    <t xml:space="preserve">11.4512300491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5093584060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5010528564453</t>
   </si>
   <si>
     <t xml:space="preserve">11.5176620483398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.741870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7584791183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6920480728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6837406158447</t>
+    <t xml:space="preserve">11.7418689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7584781646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.692045211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.683741569519</t>
   </si>
   <si>
     <t xml:space="preserve">11.7252626419067</t>
@@ -797,25 +800,25 @@
     <t xml:space="preserve">11.7667818069458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7169580459595</t>
+    <t xml:space="preserve">11.7169570922852</t>
   </si>
   <si>
     <t xml:space="preserve">11.5923976898193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7003507614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5425748825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9577741622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0574216842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9162549972534</t>
+    <t xml:space="preserve">11.7003488540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5425729751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9577751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0574207305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9162540435791</t>
   </si>
   <si>
     <t xml:space="preserve">11.9909915924072</t>
@@ -836,37 +839,37 @@
     <t xml:space="preserve">12.3895816802979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.314847946167</t>
+    <t xml:space="preserve">12.3148469924927</t>
   </si>
   <si>
     <t xml:space="preserve">12.5058403015137</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5390558242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2733287811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1902875900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1985912322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0823345184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.64222240448</t>
+    <t xml:space="preserve">12.5390548706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2733278274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1902866363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1985921859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0823354721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6422214508057</t>
   </si>
   <si>
     <t xml:space="preserve">11.550877571106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8083009719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9346389770508</t>
+    <t xml:space="preserve">11.8083019256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9346399307251</t>
   </si>
   <si>
     <t xml:space="preserve">11.9514837265015</t>
@@ -875,25 +878,22 @@
     <t xml:space="preserve">12.0609760284424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1620454788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7830352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6566982269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8083019256592</t>
+    <t xml:space="preserve">12.1620445251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.783034324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6566972732544</t>
   </si>
   <si>
     <t xml:space="preserve">11.7577667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5977401733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5640506744385</t>
+    <t xml:space="preserve">11.5977411270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5640497207642</t>
   </si>
   <si>
     <t xml:space="preserve">11.3029546737671</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">10.9576320648193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2355737686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4208669662476</t>
+    <t xml:space="preserve">11.2355728149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4208688735962</t>
   </si>
   <si>
     <t xml:space="preserve">11.2271518707275</t>
@@ -926,22 +926,22 @@
     <t xml:space="preserve">11.1681938171387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.923942565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0250129699707</t>
+    <t xml:space="preserve">10.9239416122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0250120162964</t>
   </si>
   <si>
     <t xml:space="preserve">10.763916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9492101669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5786209106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7891826629639</t>
+    <t xml:space="preserve">10.9492092132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5786218643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7891836166382</t>
   </si>
   <si>
     <t xml:space="preserve">10.7386493682861</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">11.5219383239746</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2945318222046</t>
+    <t xml:space="preserve">11.2945308685303</t>
   </si>
   <si>
     <t xml:space="preserve">11.6398525238037</t>
@@ -971,16 +971,16 @@
     <t xml:space="preserve">11.4124450683594</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3619117736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3197984695435</t>
+    <t xml:space="preserve">11.361909866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3197975158691</t>
   </si>
   <si>
     <t xml:space="preserve">11.2103071212769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9997444152832</t>
+    <t xml:space="preserve">10.9997453689575</t>
   </si>
   <si>
     <t xml:space="preserve">10.9913234710693</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">10.8734073638916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8818292617798</t>
+    <t xml:space="preserve">10.8818302154541</t>
   </si>
   <si>
     <t xml:space="preserve">10.6796913146973</t>
@@ -1013,46 +1013,46 @@
     <t xml:space="preserve">10.7049589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9155206680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2608404159546</t>
+    <t xml:space="preserve">10.9155216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2608413696289</t>
   </si>
   <si>
     <t xml:space="preserve">11.151349067688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0839691162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0502805709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2524185180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3282203674316</t>
+    <t xml:space="preserve">11.0839700698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0502786636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2524194717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.328221321106</t>
   </si>
   <si>
     <t xml:space="preserve">11.3787565231323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.395601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5050935745239</t>
+    <t xml:space="preserve">11.3956003189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5050945281982</t>
   </si>
   <si>
     <t xml:space="preserve">11.4040241241455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.555627822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6819648742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7493457794189</t>
+    <t xml:space="preserve">11.5556268692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6819658279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7493438720703</t>
   </si>
   <si>
     <t xml:space="preserve">11.9177932739258</t>
@@ -1061,37 +1061,37 @@
     <t xml:space="preserve">11.8841037750244</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9430618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0525541305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0946674346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1536235809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0357074737549</t>
+    <t xml:space="preserve">11.9430627822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0525531768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0946664810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1536226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0357093811035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0778207778931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0441303253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1788911819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1704683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3136501312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3220739364624</t>
+    <t xml:space="preserve">12.0441312789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1788892745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.170467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3136510848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3220729827881</t>
   </si>
   <si>
     <t xml:space="preserve">12.3726072311401</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">11.7325010299683</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8167247772217</t>
+    <t xml:space="preserve">11.8167238235474</t>
   </si>
   <si>
     <t xml:space="preserve">12.010440826416</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">11.311375617981</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8144512176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6965370178223</t>
+    <t xml:space="preserve">10.8144502639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6965351104736</t>
   </si>
   <si>
     <t xml:space="preserve">10.8986759185791</t>
@@ -1142,19 +1142,19 @@
     <t xml:space="preserve">10.8228731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0165901184082</t>
+    <t xml:space="preserve">11.0165910720825</t>
   </si>
   <si>
     <t xml:space="preserve">10.9407873153687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7723388671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7976045608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7302255630493</t>
+    <t xml:space="preserve">10.7723379135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7976055145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.730224609375</t>
   </si>
   <si>
     <t xml:space="preserve">10.7218017578125</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">10.6123104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8060274124146</t>
+    <t xml:space="preserve">10.8060283660889</t>
   </si>
   <si>
     <t xml:space="preserve">10.6881141662598</t>
@@ -1175,19 +1175,19 @@
     <t xml:space="preserve">10.8312950134277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6712684631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4691286087036</t>
+    <t xml:space="preserve">10.6712694168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4691295623779</t>
   </si>
   <si>
     <t xml:space="preserve">10.4859733581543</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0923910140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1597719192505</t>
+    <t xml:space="preserve">11.0923919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1597709655762</t>
   </si>
   <si>
     <t xml:space="preserve">11.1345043182373</t>
@@ -1211,22 +1211,22 @@
     <t xml:space="preserve">10.3175249099731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2417230606079</t>
+    <t xml:space="preserve">10.2417221069336</t>
   </si>
   <si>
     <t xml:space="preserve">10.2838344573975</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1911869049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1574983596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2248773574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.165922164917</t>
+    <t xml:space="preserve">10.1911878585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1574974060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2248764038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1659212112427</t>
   </si>
   <si>
     <t xml:space="preserve">10.1069622039795</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">10.0985412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93009090423584</t>
+    <t xml:space="preserve">9.93008995056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.98904895782471</t>
@@ -1244,16 +1244,16 @@
     <t xml:space="preserve">10.0058927536011</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71953010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68583965301514</t>
+    <t xml:space="preserve">9.71952819824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68584060668945</t>
   </si>
   <si>
     <t xml:space="preserve">9.4837007522583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37420749664307</t>
+    <t xml:space="preserve">9.3742094039917</t>
   </si>
   <si>
     <t xml:space="preserve">10.115385055542</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">10.5954656600952</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7133798599243</t>
+    <t xml:space="preserve">10.7133808135986</t>
   </si>
   <si>
     <t xml:space="preserve">10.603889465332</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">10.359637260437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3006801605225</t>
+    <t xml:space="preserve">10.3006811141968</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522838592529</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">10.4017505645752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5617761611938</t>
+    <t xml:space="preserve">10.5617771148682</t>
   </si>
   <si>
     <t xml:space="preserve">10.5449314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3427906036377</t>
+    <t xml:space="preserve">10.342791557312</t>
   </si>
   <si>
     <t xml:space="preserve">10.4438610076904</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">10.4185934066772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4354400634766</t>
+    <t xml:space="preserve">10.4354391098022</t>
   </si>
   <si>
     <t xml:space="preserve">10.2585668563843</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2333002090454</t>
+    <t xml:space="preserve">10.2333011627197</t>
   </si>
   <si>
     <t xml:space="preserve">10.29225730896</t>
@@ -1322,28 +1322,28 @@
     <t xml:space="preserve">10.536509513855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2754125595093</t>
+    <t xml:space="preserve">10.2754135131836</t>
   </si>
   <si>
     <t xml:space="preserve">10.2080326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0648517608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93851470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0500869750977</t>
+    <t xml:space="preserve">10.0648508071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93851375579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0500860214233</t>
   </si>
   <si>
     <t xml:space="preserve">10.3848028182983</t>
   </si>
   <si>
-    <t xml:space="preserve">10.307559967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7710132598877</t>
+    <t xml:space="preserve">10.3075609207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.771014213562</t>
   </si>
   <si>
     <t xml:space="preserve">10.6766080856323</t>
@@ -1355,25 +1355,25 @@
     <t xml:space="preserve">10.2303190231323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.470627784729</t>
+    <t xml:space="preserve">10.4706287384033</t>
   </si>
   <si>
     <t xml:space="preserve">10.5049571990967</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6422777175903</t>
+    <t xml:space="preserve">10.642276763916</t>
   </si>
   <si>
     <t xml:space="preserve">10.6851892471313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6594429016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7109384536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.93408203125</t>
+    <t xml:space="preserve">10.659441947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9340810775757</t>
   </si>
   <si>
     <t xml:space="preserve">10.6508598327637</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">10.5307054519653</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3933849334717</t>
+    <t xml:space="preserve">10.393385887146</t>
   </si>
   <si>
     <t xml:space="preserve">10.3504724502563</t>
@@ -1400,49 +1400,49 @@
     <t xml:space="preserve">9.92135047912598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0758333206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0586681365967</t>
+    <t xml:space="preserve">10.075834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.058669090271</t>
   </si>
   <si>
     <t xml:space="preserve">9.89560127258301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94709587097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74111747741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76686382293701</t>
+    <t xml:space="preserve">9.947096824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74111652374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76686477661133</t>
   </si>
   <si>
     <t xml:space="preserve">9.85268878936768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87843608856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99000835418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2560663223267</t>
+    <t xml:space="preserve">9.8784351348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99000930786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2560653686523</t>
   </si>
   <si>
     <t xml:space="preserve">10.2903966903687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2732305526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135412216187</t>
+    <t xml:space="preserve">10.2732315063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135402679443</t>
   </si>
   <si>
     <t xml:space="preserve">10.48779296875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4362964630127</t>
+    <t xml:space="preserve">10.436297416687</t>
   </si>
   <si>
     <t xml:space="preserve">10.333309173584</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">10.1273288726807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0157556533813</t>
+    <t xml:space="preserve">10.015754699707</t>
   </si>
   <si>
     <t xml:space="preserve">10.0329217910767</t>
@@ -1463,40 +1463,40 @@
     <t xml:space="preserve">9.84410667419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0415029525757</t>
+    <t xml:space="preserve">10.04150390625</t>
   </si>
   <si>
     <t xml:space="preserve">10.2389011383057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78402996063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70678615570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77544689178467</t>
+    <t xml:space="preserve">9.78402900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.706787109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77544593811035</t>
   </si>
   <si>
     <t xml:space="preserve">9.68103885650635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56088638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68962383270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47505950927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48364067077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62954425811768</t>
+    <t xml:space="preserve">9.56088542938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59521579742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68962287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47505855560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.483642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62954521179199</t>
   </si>
   <si>
     <t xml:space="preserve">9.912766456604</t>
@@ -1505,31 +1505,31 @@
     <t xml:space="preserve">9.88701915740967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75828266143799</t>
+    <t xml:space="preserve">9.7582836151123</t>
   </si>
   <si>
     <t xml:space="preserve">9.56946659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.578049659729</t>
+    <t xml:space="preserve">9.57804870605469</t>
   </si>
   <si>
     <t xml:space="preserve">9.73253440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.612380027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71536922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82694053649902</t>
+    <t xml:space="preserve">9.61237907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71537017822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82694149017334</t>
   </si>
   <si>
     <t xml:space="preserve">10.187406539917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2217359542847</t>
+    <t xml:space="preserve">10.2217350006104</t>
   </si>
   <si>
     <t xml:space="preserve">9.99859237670898</t>
@@ -1544,16 +1544,16 @@
     <t xml:space="preserve">9.69820404052734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8612699508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52655506134033</t>
+    <t xml:space="preserve">9.86127185821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52655601501465</t>
   </si>
   <si>
     <t xml:space="preserve">9.21758651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23475074768066</t>
+    <t xml:space="preserve">9.23475170135498</t>
   </si>
   <si>
     <t xml:space="preserve">8.69405460357666</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">8.52669525146484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4408712387085</t>
+    <t xml:space="preserve">8.44087028503418</t>
   </si>
   <si>
     <t xml:space="preserve">8.12331962585449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43228816986084</t>
+    <t xml:space="preserve">8.43228912353516</t>
   </si>
   <si>
     <t xml:space="preserve">8.5224027633667</t>
@@ -1577,13 +1577,13 @@
     <t xml:space="preserve">8.41083240509033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29925918579102</t>
+    <t xml:space="preserve">8.29926109313965</t>
   </si>
   <si>
     <t xml:space="preserve">8.16623020172119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23059940338135</t>
+    <t xml:space="preserve">8.23060035705566</t>
   </si>
   <si>
     <t xml:space="preserve">8.08469772338867</t>
@@ -1595,46 +1595,46 @@
     <t xml:space="preserve">8.22630882263184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48378467559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39366722106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57819080352783</t>
+    <t xml:space="preserve">8.48378372192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39366817474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57818984985352</t>
   </si>
   <si>
     <t xml:space="preserve">8.49236679077148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44945430755615</t>
+    <t xml:space="preserve">8.44945335388184</t>
   </si>
   <si>
     <t xml:space="preserve">8.23489189147949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11473655700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02033042907715</t>
+    <t xml:space="preserve">8.11473751068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02032947540283</t>
   </si>
   <si>
     <t xml:space="preserve">7.79289293289185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72852468490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77143716812134</t>
+    <t xml:space="preserve">7.72852373123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77143621444702</t>
   </si>
   <si>
     <t xml:space="preserve">7.83151435852051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00316333770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02891063690186</t>
+    <t xml:space="preserve">8.00316429138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02891159057617</t>
   </si>
   <si>
     <t xml:space="preserve">8.00745487213135</t>
@@ -1643,322 +1643,322 @@
     <t xml:space="preserve">8.25205707550049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28638744354248</t>
+    <t xml:space="preserve">8.28638648986816</t>
   </si>
   <si>
     <t xml:space="preserve">8.61681175231934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.608229637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54815101623535</t>
+    <t xml:space="preserve">8.60823059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54815006256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75413131713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48807430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46232795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.161940574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19197845458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98170804977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08898830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33788013458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81435108184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.698486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81863975524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86584377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58691263198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63411712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68990278244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6598653793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96454477310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93879556655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73696517944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82279109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47949314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38508415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40225028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45374393463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.367919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49665832519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50094795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46661758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59964847564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85712146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56960678100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56531810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55673313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53956890106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50523948669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50953006744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24776458740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15335750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39795780181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58248043060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77129650115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65972423553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0974292755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96869373321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.020188331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28624439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31199359893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08026599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.131760597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32057476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94294548034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.814208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78846073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79704475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74554824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72838401794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.908616065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14034366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42356586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26049709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18325519561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00302410125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96011161804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76271343231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65114116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.685471534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67689037322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87428665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51797199249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44073009490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41498279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64670944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0672521591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.195987701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80977630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62096214294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50938987731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86570262908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95152854919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83995628356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75851726531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77167415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74097442626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42080783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53483963012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57869911193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58747005462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47343826293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55238342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42957878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1839714050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37695026397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56992530822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67957305908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66202831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89447975158691</t>
   </si>
   <si>
     <t xml:space="preserve">8.75413227081299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48807430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.462327003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16193962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19197940826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98170709609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08899021148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33788108825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81435108184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69848680496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99887371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81863975524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8658447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58691310882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63411664962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68990325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65986585617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96454381942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93879556655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73696613311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82279109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38508415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40225028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45374393463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36791896820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.496657371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50094795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46661949157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59964847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85712146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56960773468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56531810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55673313140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53956985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50523948669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50953102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24776554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15335845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39795780181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58248138427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77129650115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65972423553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09743022918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96869277954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.020188331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28624439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31199264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08026504516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.131760597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3205738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94294548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81420803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78846073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79704570770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74554824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72838497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90861511230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14034271240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4235668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26049709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18325519561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00302314758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96011161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76271438598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65114212036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.685471534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67688846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87428569793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51797199249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44073009490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41498184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64670944213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0672521591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.195987701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80977725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62096309661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50938987731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86570358276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95152854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83995628356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75851821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77167510986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74097442626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42080783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53484058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57869815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58747005462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47343730926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55238342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42957973480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18397235870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37694931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56992626190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67957305908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66202831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89447975158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7541332244873</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.72781753540039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72343158721924</t>
+    <t xml:space="preserve">8.72343063354492</t>
   </si>
   <si>
     <t xml:space="preserve">8.93833637237549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82430553436279</t>
+    <t xml:space="preserve">8.82430648803711</t>
   </si>
   <si>
     <t xml:space="preserve">9.06113910675049</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">8.85062026977539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71465873718262</t>
+    <t xml:space="preserve">8.71465969085693</t>
   </si>
   <si>
     <t xml:space="preserve">8.88570785522461</t>
@@ -1985,10 +1985,10 @@
     <t xml:space="preserve">9.28043270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3242883682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23657321929932</t>
+    <t xml:space="preserve">9.32428932189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23657512664795</t>
   </si>
   <si>
     <t xml:space="preserve">8.9295654296875</t>
@@ -2006,28 +2006,28 @@
     <t xml:space="preserve">8.45589542388916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48220920562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62255764007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92079448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07868480682373</t>
+    <t xml:space="preserve">8.48221015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62255668640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9207935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07868385314941</t>
   </si>
   <si>
     <t xml:space="preserve">9.0172815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17958641052246</t>
+    <t xml:space="preserve">8.17958736419678</t>
   </si>
   <si>
     <t xml:space="preserve">8.13134288787842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17081546783447</t>
+    <t xml:space="preserve">8.17081451416016</t>
   </si>
   <si>
     <t xml:space="preserve">7.96029567718506</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">7.77170372009277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61819982528687</t>
+    <t xml:space="preserve">7.61819887161255</t>
   </si>
   <si>
     <t xml:space="preserve">7.64890050888062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63135671615601</t>
+    <t xml:space="preserve">7.63135766983032</t>
   </si>
   <si>
     <t xml:space="preserve">7.38574981689453</t>
@@ -2057,31 +2057,31 @@
     <t xml:space="preserve">7.22347354888916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20593118667603</t>
+    <t xml:space="preserve">7.20593166351318</t>
   </si>
   <si>
     <t xml:space="preserve">7.28048992156982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27171754837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.512939453125</t>
+    <t xml:space="preserve">7.27171802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51293897628784</t>
   </si>
   <si>
     <t xml:space="preserve">7.39890766143799</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26733303070068</t>
+    <t xml:space="preserve">7.26733255386353</t>
   </si>
   <si>
     <t xml:space="preserve">7.19277334213257</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4427661895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4515380859375</t>
+    <t xml:space="preserve">7.44276571273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45153903961182</t>
   </si>
   <si>
     <t xml:space="preserve">7.32873439788818</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">7.79363346099854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98661136627197</t>
+    <t xml:space="preserve">7.98661041259766</t>
   </si>
   <si>
     <t xml:space="preserve">8.0611686706543</t>
@@ -2102,10 +2102,10 @@
     <t xml:space="preserve">8.22344589233398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28923225402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35063457489014</t>
+    <t xml:space="preserve">8.28923320770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35063552856445</t>
   </si>
   <si>
     <t xml:space="preserve">8.21905899047852</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">7.72346019744873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60942888259888</t>
+    <t xml:space="preserve">7.60942840576172</t>
   </si>
   <si>
     <t xml:space="preserve">7.74100255966187</t>
@@ -2141,10 +2141,10 @@
     <t xml:space="preserve">7.50855445861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40329360961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45592451095581</t>
+    <t xml:space="preserve">7.40329456329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45592403411865</t>
   </si>
   <si>
     <t xml:space="preserve">7.44715213775635</t>
@@ -2153,10 +2153,10 @@
     <t xml:space="preserve">7.31557655334473</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47346782684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85064888000488</t>
+    <t xml:space="preserve">7.4734673500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85064935684204</t>
   </si>
   <si>
     <t xml:space="preserve">7.85942029953003</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">8.00854015350342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04362678527832</t>
+    <t xml:space="preserve">8.04362773895264</t>
   </si>
   <si>
     <t xml:space="preserve">7.80679035186768</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">7.91643714904785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18835926055908</t>
+    <t xml:space="preserve">8.1883602142334</t>
   </si>
   <si>
     <t xml:space="preserve">8.25414657592773</t>
@@ -2183,13 +2183,13 @@
     <t xml:space="preserve">8.29361820220947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36379146575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65325832366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3725643157959</t>
+    <t xml:space="preserve">8.36379241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65325736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37256336212158</t>
   </si>
   <si>
     <t xml:space="preserve">8.43835067749023</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">9.37692070007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56112480163574</t>
+    <t xml:space="preserve">9.56112575531006</t>
   </si>
   <si>
     <t xml:space="preserve">9.75410175323486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70147323608398</t>
+    <t xml:space="preserve">9.70147228240967</t>
   </si>
   <si>
     <t xml:space="preserve">9.47340869903564</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">9.24534606933594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42077922821045</t>
+    <t xml:space="preserve">9.42078018188477</t>
   </si>
   <si>
     <t xml:space="preserve">9.31551933288574</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">9.85936260223389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.815505027771</t>
+    <t xml:space="preserve">9.81550407409668</t>
   </si>
   <si>
     <t xml:space="preserve">9.86813449859619</t>
@@ -2270,10 +2270,10 @@
     <t xml:space="preserve">9.84181976318359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89444923400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98216533660889</t>
+    <t xml:space="preserve">9.89445018768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9821662902832</t>
   </si>
   <si>
     <t xml:space="preserve">10.0698833465576</t>
@@ -2294,16 +2294,16 @@
     <t xml:space="preserve">9.29797554016113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52603816986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63129997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71024417877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68392944335938</t>
+    <t xml:space="preserve">9.52603912353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63129901885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71024513244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68392848968506</t>
   </si>
   <si>
     <t xml:space="preserve">9.69270038604736</t>
@@ -2315,22 +2315,22 @@
     <t xml:space="preserve">9.73655986785889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57867050170898</t>
+    <t xml:space="preserve">9.57866859436035</t>
   </si>
   <si>
     <t xml:space="preserve">9.30674743652344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21026039123535</t>
+    <t xml:space="preserve">9.21025943756104</t>
   </si>
   <si>
     <t xml:space="preserve">9.33306217193604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20148658752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02605533599854</t>
+    <t xml:space="preserve">9.20148754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02605438232422</t>
   </si>
   <si>
     <t xml:space="preserve">9.26288890838623</t>
@@ -2378,19 +2378,19 @@
     <t xml:space="preserve">7.4997820854187</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60065603256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42960929870605</t>
+    <t xml:space="preserve">7.60065698623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42960834503174</t>
   </si>
   <si>
     <t xml:space="preserve">7.11821413040161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18400192260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57875633239746</t>
+    <t xml:space="preserve">7.18400239944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57875680923462</t>
   </si>
   <si>
     <t xml:space="preserve">6.64892959594727</t>
@@ -2399,13 +2399,13 @@
     <t xml:space="preserve">6.55682611465454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14017248153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38577938079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87702226638794</t>
+    <t xml:space="preserve">6.14017200469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3857798576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87702178955078</t>
   </si>
   <si>
     <t xml:space="preserve">5.97351026535034</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">6.55244112014771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1138277053833</t>
+    <t xml:space="preserve">7.11382818222046</t>
   </si>
   <si>
     <t xml:space="preserve">7.72784471511841</t>
@@ -2426,25 +2426,25 @@
     <t xml:space="preserve">7.02172565460205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47349548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31560659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83316373825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9603533744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85070705413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61387205123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18405961990356</t>
+    <t xml:space="preserve">6.4734959602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31560564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83316421508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96035289764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85070753097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61387252807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18406009674072</t>
   </si>
   <si>
     <t xml:space="preserve">5.47352504730225</t>
@@ -2456,16 +2456,16 @@
     <t xml:space="preserve">5.89895105361938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82439231872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64895868301392</t>
+    <t xml:space="preserve">5.82439279556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64895820617676</t>
   </si>
   <si>
     <t xml:space="preserve">5.69720315933228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92965221405029</t>
+    <t xml:space="preserve">5.92965173721313</t>
   </si>
   <si>
     <t xml:space="preserve">6.06122779846191</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">6.0085973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0568413734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40332221984863</t>
+    <t xml:space="preserve">6.05684185028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40332317352295</t>
   </si>
   <si>
     <t xml:space="preserve">6.59191370010376</t>
@@ -2486,13 +2486,13 @@
     <t xml:space="preserve">6.83752155303955</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69717311859131</t>
+    <t xml:space="preserve">6.69717359542847</t>
   </si>
   <si>
     <t xml:space="preserve">6.86822175979614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81120586395264</t>
+    <t xml:space="preserve">6.81120538711548</t>
   </si>
   <si>
     <t xml:space="preserve">6.72348928451538</t>
@@ -2507,22 +2507,22 @@
     <t xml:space="preserve">6.36385059356689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22788953781128</t>
+    <t xml:space="preserve">6.22788906097412</t>
   </si>
   <si>
     <t xml:space="preserve">5.77176237106323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82000637054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26297521591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23227548599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21911716461182</t>
+    <t xml:space="preserve">5.82000684738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26297569274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23227596282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21911764144897</t>
   </si>
   <si>
     <t xml:space="preserve">6.39455080032349</t>
@@ -2531,19 +2531,19 @@
     <t xml:space="preserve">6.59629964828491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16207265853882</t>
+    <t xml:space="preserve">7.16207218170166</t>
   </si>
   <si>
     <t xml:space="preserve">7.51732540130615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37259340286255</t>
+    <t xml:space="preserve">7.37259292602539</t>
   </si>
   <si>
     <t xml:space="preserve">7.33312034606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41645097732544</t>
+    <t xml:space="preserve">7.4164514541626</t>
   </si>
   <si>
     <t xml:space="preserve">7.79801988601685</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">7.35066413879395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21031713485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23224639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17522954940796</t>
+    <t xml:space="preserve">7.21031665802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23224592208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17523002624512</t>
   </si>
   <si>
     <t xml:space="preserve">7.10505676269531</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">7.24540328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21470260620117</t>
+    <t xml:space="preserve">7.21470308303833</t>
   </si>
   <si>
     <t xml:space="preserve">7.17084407806396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40767955780029</t>
+    <t xml:space="preserve">7.40767908096313</t>
   </si>
   <si>
     <t xml:space="preserve">7.25856113433838</t>
@@ -2597,16 +2597,16 @@
     <t xml:space="preserve">7.36820697784424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32434892654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14891529083252</t>
+    <t xml:space="preserve">7.32434844970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14891481399536</t>
   </si>
   <si>
     <t xml:space="preserve">7.24978923797607</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43838024139404</t>
+    <t xml:space="preserve">7.4383807182312</t>
   </si>
   <si>
     <t xml:space="preserve">7.16645860671997</t>
@@ -2624,16 +2624,16 @@
     <t xml:space="preserve">6.75419044494629</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68401622772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71033191680908</t>
+    <t xml:space="preserve">6.68401718139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71033143997192</t>
   </si>
   <si>
     <t xml:space="preserve">6.83313465118408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06119775772095</t>
+    <t xml:space="preserve">7.06119823455811</t>
   </si>
   <si>
     <t xml:space="preserve">7.1401424407959</t>
@@ -2642,10 +2642,10 @@
     <t xml:space="preserve">7.05681276321411</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04804134368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00856828689575</t>
+    <t xml:space="preserve">7.04804086685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00856781005859</t>
   </si>
   <si>
     <t xml:space="preserve">6.94716691970825</t>
@@ -2657,70 +2657,70 @@
     <t xml:space="preserve">7.0875129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09628486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01734018325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35943555831909</t>
+    <t xml:space="preserve">7.09628534317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0173397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35943508148193</t>
   </si>
   <si>
     <t xml:space="preserve">7.29364824295044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49101066589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60504245758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97345352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57434129714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41206502914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88576507568359</t>
+    <t xml:space="preserve">7.49100971221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60504198074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9734525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57434034347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41206550598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88576459884644</t>
   </si>
   <si>
     <t xml:space="preserve">6.9910249710083</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03926944732666</t>
+    <t xml:space="preserve">7.0392689704895</t>
   </si>
   <si>
     <t xml:space="preserve">7.06997013092041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31119155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48223924636841</t>
+    <t xml:space="preserve">7.31119108200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48223972320557</t>
   </si>
   <si>
     <t xml:space="preserve">7.86380672454834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92082166671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9997673034668</t>
+    <t xml:space="preserve">7.92082262039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99976634979248</t>
   </si>
   <si>
     <t xml:space="preserve">7.73661756515503</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68837308883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61381387710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62697172164917</t>
+    <t xml:space="preserve">7.68837356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61381483078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62697219848633</t>
   </si>
   <si>
     <t xml:space="preserve">7.57872772216797</t>
@@ -2729,13 +2729,13 @@
     <t xml:space="preserve">7.77609014511108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80240440368652</t>
+    <t xml:space="preserve">7.80240535736084</t>
   </si>
   <si>
     <t xml:space="preserve">7.96906614303589</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99099493026733</t>
+    <t xml:space="preserve">7.99099588394165</t>
   </si>
   <si>
     <t xml:space="preserve">8.15327167510986</t>
@@ -2744,16 +2744,16 @@
     <t xml:space="preserve">8.54799747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56995487213135</t>
+    <t xml:space="preserve">7.56995534896851</t>
   </si>
   <si>
     <t xml:space="preserve">7.82433366775513</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66644477844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71907329559326</t>
+    <t xml:space="preserve">7.66644382476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71907424926758</t>
   </si>
   <si>
     <t xml:space="preserve">7.78486204147339</t>
@@ -2762,22 +2762,22 @@
     <t xml:space="preserve">7.86819267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22780227661133</t>
+    <t xml:space="preserve">9.22780132293701</t>
   </si>
   <si>
     <t xml:space="preserve">9.17517280578613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39446449279785</t>
+    <t xml:space="preserve">9.39446353912354</t>
   </si>
   <si>
     <t xml:space="preserve">9.83304786682129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58744049072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40323638916016</t>
+    <t xml:space="preserve">9.58744144439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40323543548584</t>
   </si>
   <si>
     <t xml:space="preserve">9.36814880371094</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">9.35937786102295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53481197357178</t>
+    <t xml:space="preserve">9.53481101989746</t>
   </si>
   <si>
     <t xml:space="preserve">9.46463775634766</t>
@@ -2798,22 +2798,22 @@
     <t xml:space="preserve">9.41200733184814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38569164276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61375713348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49972534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03482437133789</t>
+    <t xml:space="preserve">9.38569259643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61375617980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49972438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03482532501221</t>
   </si>
   <si>
     <t xml:space="preserve">9.74533176422119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90322303771973</t>
+    <t xml:space="preserve">9.90322208404541</t>
   </si>
   <si>
     <t xml:space="preserve">10.0961980819702</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">9.44709491729736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82427597045898</t>
+    <t xml:space="preserve">9.82427501678467</t>
   </si>
   <si>
     <t xml:space="preserve">9.56989765167236</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">9.27166080474854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34183406829834</t>
+    <t xml:space="preserve">9.34183502197266</t>
   </si>
   <si>
     <t xml:space="preserve">9.19271469116211</t>
@@ -2870,16 +2870,16 @@
     <t xml:space="preserve">8.90324878692627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06991100311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84184837341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99973773956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97342300415039</t>
+    <t xml:space="preserve">9.06991195678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84184741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9997386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97342395782471</t>
   </si>
   <si>
     <t xml:space="preserve">9.18857192993164</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">9.19807243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1890983581543</t>
+    <t xml:space="preserve">9.18909931182861</t>
   </si>
   <si>
     <t xml:space="preserve">9.43138980865479</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">9.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68265438079834</t>
+    <t xml:space="preserve">9.68265342712402</t>
   </si>
   <si>
     <t xml:space="preserve">9.70060157775879</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">9.53010082244873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63778495788574</t>
+    <t xml:space="preserve">9.63778591156006</t>
   </si>
   <si>
     <t xml:space="preserve">9.61086463928223</t>
@@ -2951,19 +2951,19 @@
     <t xml:space="preserve">9.58394336700439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60189056396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55702114105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5480489730835</t>
+    <t xml:space="preserve">9.60188961029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55702209472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54804801940918</t>
   </si>
   <si>
     <t xml:space="preserve">9.35960006713867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76341724395752</t>
+    <t xml:space="preserve">9.76341819763184</t>
   </si>
   <si>
     <t xml:space="preserve">9.64675903320312</t>
@@ -2972,13 +2972,13 @@
     <t xml:space="preserve">9.29678344726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33267784118652</t>
+    <t xml:space="preserve">9.33267879486084</t>
   </si>
   <si>
     <t xml:space="preserve">9.3865213394165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39549446105957</t>
+    <t xml:space="preserve">9.39549541473389</t>
   </si>
   <si>
     <t xml:space="preserve">9.7723913192749</t>
@@ -2990,13 +2990,13 @@
     <t xml:space="preserve">10.3915786743164</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5800256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.651816368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6877107620239</t>
+    <t xml:space="preserve">10.5800266265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6518154144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6877117156982</t>
   </si>
   <si>
     <t xml:space="preserve">10.7415533065796</t>
@@ -3005,67 +3005,67 @@
     <t xml:space="preserve">10.8582124710083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9389743804932</t>
+    <t xml:space="preserve">10.9389753341675</t>
   </si>
   <si>
     <t xml:space="preserve">10.9838438034058</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0556335449219</t>
+    <t xml:space="preserve">11.0556344985962</t>
   </si>
   <si>
     <t xml:space="preserve">11.1005020141602</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0915288925171</t>
+    <t xml:space="preserve">11.0915279388428</t>
   </si>
   <si>
     <t xml:space="preserve">11.127423286438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.019739151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9300012588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312902450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376863479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0107650756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9748697280884</t>
+    <t xml:space="preserve">11.0197381973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9300022125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0107660293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9748706817627</t>
   </si>
   <si>
     <t xml:space="preserve">10.8761587142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9120540618896</t>
+    <t xml:space="preserve">10.912055015564</t>
   </si>
   <si>
     <t xml:space="preserve">11.0466604232788</t>
   </si>
   <si>
-    <t xml:space="preserve">10.921028137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8941068649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9030809402466</t>
+    <t xml:space="preserve">10.9210271835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8941059112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9030799865723</t>
   </si>
   <si>
     <t xml:space="preserve">10.8043699264526</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7595014572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7864217758179</t>
+    <t xml:space="preserve">10.75950050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7864227294922</t>
   </si>
   <si>
     <t xml:space="preserve">10.8402643203735</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">10.2569723129272</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90699672698975</t>
+    <t xml:space="preserve">9.90699768066406</t>
   </si>
   <si>
     <t xml:space="preserve">9.96083927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1223669052124</t>
+    <t xml:space="preserve">10.1223659515381</t>
   </si>
   <si>
     <t xml:space="preserve">10.1313400268555</t>
@@ -3092,10 +3092,10 @@
     <t xml:space="preserve">10.1403141021729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0954456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87110233306885</t>
+    <t xml:space="preserve">10.0954446792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87110137939453</t>
   </si>
   <si>
     <t xml:space="preserve">9.80828666687012</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">10.0236558914185</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96981239318848</t>
+    <t xml:space="preserve">9.96981334686279</t>
   </si>
   <si>
     <t xml:space="preserve">10.1672353744507</t>
@@ -3143,19 +3143,19 @@
     <t xml:space="preserve">10.2031297683716</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1851835250854</t>
+    <t xml:space="preserve">10.1851825714111</t>
   </si>
   <si>
     <t xml:space="preserve">10.2838935852051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3377361297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4454212188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5172109603882</t>
+    <t xml:space="preserve">10.3377370834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4454202651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5172100067139</t>
   </si>
   <si>
     <t xml:space="preserve">10.3467092514038</t>
@@ -3176,37 +3176,37 @@
     <t xml:space="preserve">10.8492383956909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6966857910156</t>
+    <t xml:space="preserve">10.6966848373413</t>
   </si>
   <si>
     <t xml:space="preserve">10.7684745788574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5620784759521</t>
+    <t xml:space="preserve">10.5620794296265</t>
   </si>
   <si>
     <t xml:space="preserve">10.0864715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2479991912842</t>
+    <t xml:space="preserve">10.2479982376099</t>
   </si>
   <si>
     <t xml:space="preserve">10.490288734436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5979747772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8671855926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1453714370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9658975601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9569234848022</t>
+    <t xml:space="preserve">10.5979738235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8671846389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1453704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9658966064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9569225311279</t>
   </si>
   <si>
     <t xml:space="preserve">11.082555770874</t>
@@ -3215,22 +3215,22 @@
     <t xml:space="preserve">11.1094770431519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1722927093506</t>
+    <t xml:space="preserve">11.1722917556763</t>
   </si>
   <si>
     <t xml:space="preserve">11.2440814971924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2261352539062</t>
+    <t xml:space="preserve">11.2261343002319</t>
   </si>
   <si>
     <t xml:space="preserve">11.190239906311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.459451675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6299524307251</t>
+    <t xml:space="preserve">11.4594526290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6299533843994</t>
   </si>
   <si>
     <t xml:space="preserve">11.8004531860352</t>
@@ -3248,19 +3248,19 @@
     <t xml:space="preserve">11.2171611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2081880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3248453140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2620296478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1363964080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8223180770874</t>
+    <t xml:space="preserve">11.2081871032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3248462677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2620306015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1363983154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8223171234131</t>
   </si>
   <si>
     <t xml:space="preserve">10.3287620544434</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">10.5351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.373631477356</t>
+    <t xml:space="preserve">10.3736305236816</t>
   </si>
   <si>
     <t xml:space="preserve">10.5441312789917</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">10.7056589126587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6159210205078</t>
+    <t xml:space="preserve">10.6159219741821</t>
   </si>
   <si>
     <t xml:space="preserve">10.4095258712769</t>
@@ -3311,16 +3311,16 @@
     <t xml:space="preserve">8.15712070465088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48914813995361</t>
+    <t xml:space="preserve">8.48914909362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.20198917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34556865692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53850364685059</t>
+    <t xml:space="preserve">8.3455696105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53850269317627</t>
   </si>
   <si>
     <t xml:space="preserve">8.67759609222412</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">9.01859855651855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10833549499512</t>
+    <t xml:space="preserve">9.1083345413208</t>
   </si>
   <si>
     <t xml:space="preserve">9.18012523651123</t>
@@ -3344,16 +3344,16 @@
     <t xml:space="preserve">9.13525676727295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98270320892334</t>
+    <t xml:space="preserve">8.98270416259766</t>
   </si>
   <si>
     <t xml:space="preserve">8.79874229431152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90642738342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34165191650391</t>
+    <t xml:space="preserve">8.90642642974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34165287017822</t>
   </si>
   <si>
     <t xml:space="preserve">9.25191497802734</t>
@@ -3362,19 +3362,19 @@
     <t xml:space="preserve">9.08141422271729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97373008728027</t>
+    <t xml:space="preserve">8.97372913360596</t>
   </si>
   <si>
     <t xml:space="preserve">9.036545753479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83015060424805</t>
+    <t xml:space="preserve">8.83014965057373</t>
   </si>
   <si>
     <t xml:space="preserve">8.43979167938232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26480484008789</t>
+    <t xml:space="preserve">8.26480579376221</t>
   </si>
   <si>
     <t xml:space="preserve">8.36351585388184</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">8.30967330932617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35005569458008</t>
+    <t xml:space="preserve">8.35005474090576</t>
   </si>
   <si>
     <t xml:space="preserve">8.36800193786621</t>
@@ -3395,13 +3395,13 @@
     <t xml:space="preserve">8.51606941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94232082366943</t>
+    <t xml:space="preserve">8.94232177734375</t>
   </si>
   <si>
     <t xml:space="preserve">8.70900440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5743989944458</t>
+    <t xml:space="preserve">8.57439804077148</t>
   </si>
   <si>
     <t xml:space="preserve">8.45773983001709</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">8.61478042602539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4936351776123</t>
+    <t xml:space="preserve">8.49363422393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.30070018768311</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">8.25134372711182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12571239471436</t>
+    <t xml:space="preserve">8.12571144104004</t>
   </si>
   <si>
     <t xml:space="preserve">8.88399124145508</t>
@@ -3437,13 +3437,13 @@
     <t xml:space="preserve">9.6856861114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5844087600708</t>
+    <t xml:space="preserve">9.58440971374512</t>
   </si>
   <si>
     <t xml:space="preserve">9.63044357299805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87903022766113</t>
+    <t xml:space="preserve">9.87902927398682</t>
   </si>
   <si>
     <t xml:space="preserve">10.0539627075195</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">10.2104806900024</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95268630981445</t>
+    <t xml:space="preserve">9.95268726348877</t>
   </si>
   <si>
     <t xml:space="preserve">9.98030662536621</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">10.035548210144</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89744472503662</t>
+    <t xml:space="preserve">9.89744567871094</t>
   </si>
   <si>
     <t xml:space="preserve">10.0631694793701</t>
@@ -3470,13 +3470,13 @@
     <t xml:space="preserve">10.1184110641479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1552381515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63965034484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40027141571045</t>
+    <t xml:space="preserve">10.1552391052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63965129852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40027046203613</t>
   </si>
   <si>
     <t xml:space="preserve">9.22533893585205</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">9.44630527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87087345123291</t>
+    <t xml:space="preserve">8.87087249755859</t>
   </si>
   <si>
     <t xml:space="preserve">8.95833778381348</t>
@@ -3542,10 +3542,10 @@
     <t xml:space="preserve">8.82023525238037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60847663879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90309619903564</t>
+    <t xml:space="preserve">8.60847568511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90309715270996</t>
   </si>
   <si>
     <t xml:space="preserve">9.00437259674072</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">9.06882190704346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1056489944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14247798919678</t>
+    <t xml:space="preserve">9.10564994812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14247703552246</t>
   </si>
   <si>
     <t xml:space="preserve">8.99976921081543</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">8.86166572570801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17470073699951</t>
+    <t xml:space="preserve">9.17470169067383</t>
   </si>
   <si>
     <t xml:space="preserve">9.47392654418945</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">9.75934028625488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73171997070312</t>
+    <t xml:space="preserve">9.73171901702881</t>
   </si>
   <si>
     <t xml:space="preserve">9.66727161407471</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">8.92611408233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59466361999512</t>
+    <t xml:space="preserve">8.59466457366943</t>
   </si>
   <si>
     <t xml:space="preserve">8.56244087219238</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">8.57164764404297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44274997711182</t>
+    <t xml:space="preserve">8.44275093078613</t>
   </si>
   <si>
     <t xml:space="preserve">8.38750839233398</t>
@@ -3635,10 +3635,10 @@
     <t xml:space="preserve">8.45195770263672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14352607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1251106262207</t>
+    <t xml:space="preserve">8.14352512359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12511157989502</t>
   </si>
   <si>
     <t xml:space="preserve">8.23559474945068</t>
@@ -3656,19 +3656,19 @@
     <t xml:space="preserve">8.75578594207764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79261302947998</t>
+    <t xml:space="preserve">8.7926139831543</t>
   </si>
   <si>
     <t xml:space="preserve">8.51640605926514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31385326385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33226680755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21718120574951</t>
+    <t xml:space="preserve">8.3138542175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33226776123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2171802520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.09749126434326</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">7.4944372177124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8212833404541</t>
+    <t xml:space="preserve">7.82128238677979</t>
   </si>
   <si>
     <t xml:space="preserve">7.97319746017456</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31845664978027</t>
+    <t xml:space="preserve">8.31845760345459</t>
   </si>
   <si>
     <t xml:space="preserve">8.2217845916748</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">8.30924987792969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29544067382812</t>
+    <t xml:space="preserve">8.29543972015381</t>
   </si>
   <si>
     <t xml:space="preserve">8.68213081359863</t>
@@ -3719,19 +3719,19 @@
     <t xml:space="preserve">8.47037124633789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61307907104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66371726989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73276901245117</t>
+    <t xml:space="preserve">8.61307811737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66371631622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73276805877686</t>
   </si>
   <si>
     <t xml:space="preserve">8.90769958496094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91690635681152</t>
+    <t xml:space="preserve">8.91690731048584</t>
   </si>
   <si>
     <t xml:space="preserve">8.97214889526367</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">8.79721736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.193115234375</t>
+    <t xml:space="preserve">9.19311428070068</t>
   </si>
   <si>
     <t xml:space="preserve">9.54758071899414</t>
@@ -3767,13 +3767,13 @@
     <t xml:space="preserve">10.8641719818115</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7260675430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6892395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444820404053</t>
+    <t xml:space="preserve">10.7260665893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6892404556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444829940796</t>
   </si>
   <si>
     <t xml:space="preserve">10.5143089294434</t>
@@ -3782,16 +3782,16 @@
     <t xml:space="preserve">10.2381010055542</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3393774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841348648071</t>
+    <t xml:space="preserve">10.339376449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841358184814</t>
   </si>
   <si>
     <t xml:space="preserve">10.3209638595581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1368255615234</t>
+    <t xml:space="preserve">10.1368246078491</t>
   </si>
   <si>
     <t xml:space="preserve">10.1828603744507</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">10.3485841751099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.192066192627</t>
+    <t xml:space="preserve">10.1920652389526</t>
   </si>
   <si>
     <t xml:space="preserve">10.0815830230713</t>
@@ -3821,10 +3821,10 @@
     <t xml:space="preserve">9.7501335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65806484222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60282421112061</t>
+    <t xml:space="preserve">9.6580638885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60282325744629</t>
   </si>
   <si>
     <t xml:space="preserve">9.48313331604004</t>
@@ -3842,10 +3842,10 @@
     <t xml:space="preserve">10.1276178359985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2473087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4866876602173</t>
+    <t xml:space="preserve">10.2473077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4866886138916</t>
   </si>
   <si>
     <t xml:space="preserve">10.5327224731445</t>
@@ -3869,22 +3869,22 @@
     <t xml:space="preserve">10.6616201400757</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9286203384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9654474258423</t>
+    <t xml:space="preserve">10.9286193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9654483795166</t>
   </si>
   <si>
     <t xml:space="preserve">11.3889665603638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7940711975098</t>
+    <t xml:space="preserve">11.7940721511841</t>
   </si>
   <si>
     <t xml:space="preserve">12.1163129806519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2912464141846</t>
+    <t xml:space="preserve">12.2912454605103</t>
   </si>
   <si>
     <t xml:space="preserve">12.3372793197632</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">12.6779365539551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8620738983154</t>
+    <t xml:space="preserve">12.8620748519897</t>
   </si>
   <si>
     <t xml:space="preserve">13.7275247573853</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">12.5950736999512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8252477645874</t>
+    <t xml:space="preserve">12.8252468109131</t>
   </si>
   <si>
     <t xml:space="preserve">12.8896961212158</t>
@@ -3968,13 +3968,13 @@
     <t xml:space="preserve">12.2267961502075</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2175893783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3280725479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9966230392456</t>
+    <t xml:space="preserve">12.2175903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3280735015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9966239929199</t>
   </si>
   <si>
     <t xml:space="preserve">11.9321756362915</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">12.7700052261353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2728309631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5674533843994</t>
+    <t xml:space="preserve">12.2728319168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5674524307251</t>
   </si>
   <si>
     <t xml:space="preserve">12.503005027771</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">12.4845905303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3096590042114</t>
+    <t xml:space="preserve">12.3096580505371</t>
   </si>
   <si>
     <t xml:space="preserve">12.024245262146</t>
@@ -4019,7 +4019,7 @@
     <t xml:space="preserve">13.0738334655762</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2855939865112</t>
+    <t xml:space="preserve">13.2855930328369</t>
   </si>
   <si>
     <t xml:space="preserve">13.2579717636108</t>
@@ -4034,7 +4034,7 @@
     <t xml:space="preserve">13.1659030914307</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3040075302124</t>
+    <t xml:space="preserve">13.3040065765381</t>
   </si>
   <si>
     <t xml:space="preserve">13.2947998046875</t>
@@ -5631,6 +5631,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.34000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21500015258789</t>
   </si>
 </sst>
 </file>
@@ -9757,7 +9760,7 @@
         <v>10.1195363998413</v>
       </c>
       <c r="G146" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -9783,7 +9786,7 @@
         <v>10.2294216156006</v>
       </c>
       <c r="G147" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -9809,7 +9812,7 @@
         <v>10.0595979690552</v>
       </c>
       <c r="G148" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -9835,7 +9838,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G149" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -9861,7 +9864,7 @@
         <v>10.5490922927856</v>
       </c>
       <c r="G150" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -9913,7 +9916,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G152" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -9939,7 +9942,7 @@
         <v>10.2893600463867</v>
       </c>
       <c r="G153" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -9965,7 +9968,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G154" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9991,7 +9994,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G155" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -10017,7 +10020,7 @@
         <v>10.5091333389282</v>
       </c>
       <c r="G156" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -10043,7 +10046,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G157" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -10069,7 +10072,7 @@
         <v>10.5191230773926</v>
       </c>
       <c r="G158" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -10095,7 +10098,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G159" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -10147,7 +10150,7 @@
         <v>10.2094430923462</v>
       </c>
       <c r="G161" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -10173,7 +10176,7 @@
         <v>10.1594953536987</v>
       </c>
       <c r="G162" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -10199,7 +10202,7 @@
         <v>10.1994533538818</v>
       </c>
       <c r="G163" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -10225,7 +10228,7 @@
         <v>10.1095457077026</v>
       </c>
       <c r="G164" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -10251,7 +10254,7 @@
         <v>10.1395149230957</v>
       </c>
       <c r="G165" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -10277,7 +10280,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G166" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -10303,7 +10306,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G167" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -10329,7 +10332,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G168" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -10381,7 +10384,7 @@
         <v>10.4092359542847</v>
       </c>
       <c r="G170" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -10407,7 +10410,7 @@
         <v>10.4591846466064</v>
       </c>
       <c r="G171" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -10433,7 +10436,7 @@
         <v>10.4591846466064</v>
       </c>
       <c r="G172" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -10459,7 +10462,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G173" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -10485,7 +10488,7 @@
         <v>10.4791641235352</v>
       </c>
       <c r="G174" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -10537,7 +10540,7 @@
         <v>10.6989374160767</v>
       </c>
       <c r="G176" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -10563,7 +10566,7 @@
         <v>10.6389989852905</v>
       </c>
       <c r="G177" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -10667,7 +10670,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G181" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -10745,7 +10748,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G184" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -10823,7 +10826,7 @@
         <v>10.688946723938</v>
       </c>
       <c r="G187" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -10849,7 +10852,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G188" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -10875,7 +10878,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G189" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -10901,7 +10904,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G190" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -10953,7 +10956,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G192" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -10979,7 +10982,7 @@
         <v>10.6090297698975</v>
       </c>
       <c r="G193" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -11005,7 +11008,7 @@
         <v>10.7089262008667</v>
       </c>
       <c r="G194" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -11031,7 +11034,7 @@
         <v>10.8887405395508</v>
       </c>
       <c r="G195" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -11057,7 +11060,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G196" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -11083,7 +11086,7 @@
         <v>10.5990400314331</v>
       </c>
       <c r="G197" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -11109,7 +11112,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G198" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -11135,7 +11138,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G199" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -11161,7 +11164,7 @@
         <v>10.3792667388916</v>
       </c>
       <c r="G200" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -11239,7 +11242,7 @@
         <v>10.4691743850708</v>
       </c>
       <c r="G203" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -11265,7 +11268,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G204" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -11291,7 +11294,7 @@
         <v>10.5091333389282</v>
       </c>
       <c r="G205" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -11317,7 +11320,7 @@
         <v>10.6090297698975</v>
       </c>
       <c r="G206" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -11343,7 +11346,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G207" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -11369,7 +11372,7 @@
         <v>10.5291118621826</v>
       </c>
       <c r="G208" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -11395,7 +11398,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G209" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -11447,7 +11450,7 @@
         <v>10.8787508010864</v>
       </c>
       <c r="G211" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -11473,7 +11476,7 @@
         <v>10.9986267089844</v>
       </c>
       <c r="G212" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -11499,7 +11502,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G213" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -11525,7 +11528,7 @@
         <v>11.2483692169189</v>
       </c>
       <c r="G214" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -11551,7 +11554,7 @@
         <v>11.258358001709</v>
       </c>
       <c r="G215" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -11577,7 +11580,7 @@
         <v>11.008617401123</v>
       </c>
       <c r="G216" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -11603,7 +11606,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G217" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -11629,7 +11632,7 @@
         <v>10.5590810775757</v>
       </c>
       <c r="G218" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -11655,7 +11658,7 @@
         <v>11.0585651397705</v>
       </c>
       <c r="G219" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -11681,7 +11684,7 @@
         <v>11.3682451248169</v>
       </c>
       <c r="G220" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -11707,7 +11710,7 @@
         <v>11.0385856628418</v>
       </c>
       <c r="G221" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -11733,7 +11736,7 @@
         <v>10.828803062439</v>
       </c>
       <c r="G222" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -11759,7 +11762,7 @@
         <v>10.98863697052</v>
       </c>
       <c r="G223" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -11785,7 +11788,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G224" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -11811,7 +11814,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G225" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -11837,7 +11840,7 @@
         <v>10.7289056777954</v>
       </c>
       <c r="G226" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11863,7 +11866,7 @@
         <v>10.6389989852905</v>
       </c>
       <c r="G227" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -11889,7 +11892,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G228" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -11941,7 +11944,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G230" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -11967,7 +11970,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G231" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11993,7 +11996,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G232" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -12019,7 +12022,7 @@
         <v>10.838791847229</v>
       </c>
       <c r="G233" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -12071,7 +12074,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G235" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -12097,7 +12100,7 @@
         <v>10.8088226318359</v>
       </c>
       <c r="G236" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -12123,7 +12126,7 @@
         <v>10.7089262008667</v>
       </c>
       <c r="G237" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -12149,7 +12152,7 @@
         <v>10.539101600647</v>
       </c>
       <c r="G238" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -12175,7 +12178,7 @@
         <v>10.5590810775757</v>
       </c>
       <c r="G239" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -12227,7 +12230,7 @@
         <v>10.9686584472656</v>
       </c>
       <c r="G241" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -12253,7 +12256,7 @@
         <v>11.0985240936279</v>
       </c>
       <c r="G242" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -12279,7 +12282,7 @@
         <v>10.9686584472656</v>
       </c>
       <c r="G243" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -12305,7 +12308,7 @@
         <v>10.828803062439</v>
       </c>
       <c r="G244" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -12331,7 +12334,7 @@
         <v>11.008617401123</v>
       </c>
       <c r="G245" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -12357,7 +12360,7 @@
         <v>10.8887405395508</v>
       </c>
       <c r="G246" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -12383,7 +12386,7 @@
         <v>10.98863697052</v>
       </c>
       <c r="G247" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -12409,7 +12412,7 @@
         <v>10.8088226318359</v>
       </c>
       <c r="G248" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -12435,7 +12438,7 @@
         <v>10.7289056777954</v>
       </c>
       <c r="G249" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -12461,7 +12464,7 @@
         <v>10.7688636779785</v>
       </c>
       <c r="G250" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -12487,7 +12490,7 @@
         <v>10.9087200164795</v>
       </c>
       <c r="G251" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -12513,7 +12516,7 @@
         <v>10.9187097549438</v>
       </c>
       <c r="G252" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -12539,7 +12542,7 @@
         <v>11.0685548782349</v>
       </c>
       <c r="G253" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -12565,7 +12568,7 @@
         <v>11.2084102630615</v>
       </c>
       <c r="G254" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -12591,7 +12594,7 @@
         <v>11.2683477401733</v>
       </c>
       <c r="G255" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -12617,7 +12620,7 @@
         <v>11.4181928634644</v>
       </c>
       <c r="G256" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -12643,7 +12646,7 @@
         <v>11.4881210327148</v>
       </c>
       <c r="G257" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -12669,7 +12672,7 @@
         <v>11.9876041412354</v>
       </c>
       <c r="G258" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -12695,7 +12698,7 @@
         <v>12.0575323104858</v>
       </c>
       <c r="G259" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -12721,7 +12724,7 @@
         <v>11.8177795410156</v>
       </c>
       <c r="G260" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -12747,7 +12750,7 @@
         <v>11.9576349258423</v>
       </c>
       <c r="G261" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -12773,7 +12776,7 @@
         <v>12.0075836181641</v>
       </c>
       <c r="G262" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -12799,7 +12802,7 @@
         <v>12.0375528335571</v>
       </c>
       <c r="G263" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -12825,7 +12828,7 @@
         <v>12.0974912643433</v>
       </c>
       <c r="G264" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -12851,7 +12854,7 @@
         <v>12.277304649353</v>
       </c>
       <c r="G265" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12877,7 +12880,7 @@
         <v>12.0575323104858</v>
       </c>
       <c r="G266" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -12903,7 +12906,7 @@
         <v>12.3072738647461</v>
       </c>
       <c r="G267" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -12929,7 +12932,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G268" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -12955,7 +12958,7 @@
         <v>12.2673149108887</v>
       </c>
       <c r="G269" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -12981,7 +12984,7 @@
         <v>12.2173671722412</v>
       </c>
       <c r="G270" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -13007,7 +13010,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G271" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -13033,7 +13036,7 @@
         <v>12.1774082183838</v>
       </c>
       <c r="G272" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -13059,7 +13062,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G273" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -13085,7 +13088,7 @@
         <v>12.2073774337769</v>
       </c>
       <c r="G274" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -13111,7 +13114,7 @@
         <v>12.2972841262817</v>
       </c>
       <c r="G275" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -13137,7 +13140,7 @@
         <v>12.1873979568481</v>
       </c>
       <c r="G276" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -13163,7 +13166,7 @@
         <v>12.1474390029907</v>
       </c>
       <c r="G277" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -13189,7 +13192,7 @@
         <v>11.9876041412354</v>
       </c>
       <c r="G278" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -13215,7 +13218,7 @@
         <v>11.8477487564087</v>
       </c>
       <c r="G279" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -13241,7 +13244,7 @@
         <v>12.2173671722412</v>
       </c>
       <c r="G280" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -13267,7 +13270,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G281" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -13293,7 +13296,7 @@
         <v>12.4071702957153</v>
       </c>
       <c r="G282" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -13319,7 +13322,7 @@
         <v>12.127459526062</v>
       </c>
       <c r="G283" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -13345,7 +13348,7 @@
         <v>12.1174697875977</v>
       </c>
       <c r="G284" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -13371,7 +13374,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G285" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -13397,7 +13400,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G286" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -13423,7 +13426,7 @@
         <v>12.4071702957153</v>
       </c>
       <c r="G287" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -13449,7 +13452,7 @@
         <v>12.6669015884399</v>
       </c>
       <c r="G288" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -13475,7 +13478,7 @@
         <v>12.5670051574707</v>
       </c>
       <c r="G289" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -13501,7 +13504,7 @@
         <v>12.6569118499756</v>
       </c>
       <c r="G290" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -13527,7 +13530,7 @@
         <v>12.5670051574707</v>
       </c>
       <c r="G291" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -13553,7 +13556,7 @@
         <v>12.4970779418945</v>
       </c>
       <c r="G292" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -13579,7 +13582,7 @@
         <v>12.5969743728638</v>
       </c>
       <c r="G293" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -13605,7 +13608,7 @@
         <v>12.8567056655884</v>
       </c>
       <c r="G294" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -13631,7 +13634,7 @@
         <v>12.8966636657715</v>
       </c>
       <c r="G295" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -13657,7 +13660,7 @@
         <v>12.816746711731</v>
       </c>
       <c r="G296" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -13683,7 +13686,7 @@
         <v>12.5170574188232</v>
       </c>
       <c r="G297" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -13709,7 +13712,7 @@
         <v>12.8067569732666</v>
       </c>
       <c r="G298" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -13735,7 +13738,7 @@
         <v>12.6669015884399</v>
       </c>
       <c r="G299" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -13761,7 +13764,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G300" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -13787,7 +13790,7 @@
         <v>13.1863651275635</v>
       </c>
       <c r="G301" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13813,7 +13816,7 @@
         <v>13.1464061737061</v>
       </c>
       <c r="G302" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -13839,7 +13842,7 @@
         <v>12.9566020965576</v>
       </c>
       <c r="G303" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13865,7 +13868,7 @@
         <v>12.966591835022</v>
       </c>
       <c r="G304" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -13891,7 +13894,7 @@
         <v>13.0764780044556</v>
       </c>
       <c r="G305" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -13917,7 +13920,7 @@
         <v>12.9765815734863</v>
       </c>
       <c r="G306" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -13943,7 +13946,7 @@
         <v>12.9765815734863</v>
       </c>
       <c r="G307" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -13969,7 +13972,7 @@
         <v>13.1863651275635</v>
       </c>
       <c r="G308" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -13995,7 +13998,7 @@
         <v>13.2762718200684</v>
       </c>
       <c r="G309" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -14021,7 +14024,7 @@
         <v>13.1064472198486</v>
       </c>
       <c r="G310" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -14047,7 +14050,7 @@
         <v>13.2862615585327</v>
       </c>
       <c r="G311" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -14073,7 +14076,7 @@
         <v>13.536003112793</v>
       </c>
       <c r="G312" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -14099,7 +14102,7 @@
         <v>13.4460964202881</v>
       </c>
       <c r="G313" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -14125,7 +14128,7 @@
         <v>13.5060338973999</v>
       </c>
       <c r="G314" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -14151,7 +14154,7 @@
         <v>13.5459928512573</v>
       </c>
       <c r="G315" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -14177,7 +14180,7 @@
         <v>13.5759620666504</v>
       </c>
       <c r="G316" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -14203,7 +14206,7 @@
         <v>13.6458902359009</v>
       </c>
       <c r="G317" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -14229,7 +14232,7 @@
         <v>13.7058277130127</v>
       </c>
       <c r="G318" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -14255,7 +14258,7 @@
         <v>13.7757549285889</v>
       </c>
       <c r="G319" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -14281,7 +14284,7 @@
         <v>13.8456830978394</v>
       </c>
       <c r="G320" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -14307,7 +14310,7 @@
         <v>13.835693359375</v>
       </c>
       <c r="G321" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -14333,7 +14336,7 @@
         <v>13.8556728363037</v>
       </c>
       <c r="G322" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -14359,7 +14362,7 @@
         <v>14.1253938674927</v>
       </c>
       <c r="G323" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -14385,7 +14388,7 @@
         <v>14.1453733444214</v>
       </c>
       <c r="G324" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -14411,7 +14414,7 @@
         <v>14.1253938674927</v>
       </c>
       <c r="G325" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -14437,7 +14440,7 @@
         <v>14.1253938674927</v>
       </c>
       <c r="G326" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -14463,7 +14466,7 @@
         <v>14.0654563903809</v>
       </c>
       <c r="G327" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -14489,7 +14492,7 @@
         <v>14.0554656982422</v>
       </c>
       <c r="G328" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -14515,7 +14518,7 @@
         <v>14.1054153442383</v>
       </c>
       <c r="G329" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -14541,7 +14544,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G330" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -14567,7 +14570,7 @@
         <v>14.0954246520996</v>
       </c>
       <c r="G331" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -14593,7 +14596,7 @@
         <v>13.7757549285889</v>
       </c>
       <c r="G332" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -14619,7 +14622,7 @@
         <v>13.9455795288086</v>
       </c>
       <c r="G333" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -14645,7 +14648,7 @@
         <v>14.0754451751709</v>
       </c>
       <c r="G334" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -14671,7 +14674,7 @@
         <v>13.8856420516968</v>
       </c>
       <c r="G335" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -14697,7 +14700,7 @@
         <v>14.3851251602173</v>
       </c>
       <c r="G336" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -14723,7 +14726,7 @@
         <v>14.5050010681152</v>
       </c>
       <c r="G337" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -14749,7 +14752,7 @@
         <v>14.3351774215698</v>
       </c>
       <c r="G338" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -14775,7 +14778,7 @@
         <v>14.4250841140747</v>
       </c>
       <c r="G339" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -14801,7 +14804,7 @@
         <v>14.4150943756104</v>
       </c>
       <c r="G340" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -14827,7 +14830,7 @@
         <v>14.6148881912231</v>
       </c>
       <c r="G341" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -14853,7 +14856,7 @@
         <v>14.4950122833252</v>
       </c>
       <c r="G342" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -14879,7 +14882,7 @@
         <v>14.7847118377686</v>
       </c>
       <c r="G343" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -14905,7 +14908,7 @@
         <v>14.9045877456665</v>
       </c>
       <c r="G344" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -14931,7 +14934,7 @@
         <v>14.8146810531616</v>
       </c>
       <c r="G345" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -14957,7 +14960,7 @@
         <v>15.0444440841675</v>
       </c>
       <c r="G346" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -14983,7 +14986,7 @@
         <v>15.0844020843506</v>
       </c>
       <c r="G347" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -15009,7 +15012,7 @@
         <v>14.7647333145142</v>
       </c>
       <c r="G348" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -15035,7 +15038,7 @@
         <v>14.6648359298706</v>
       </c>
       <c r="G349" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -15061,7 +15064,7 @@
         <v>14.674825668335</v>
       </c>
       <c r="G350" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -15087,7 +15090,7 @@
         <v>14.5349702835083</v>
       </c>
       <c r="G351" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -15113,7 +15116,7 @@
         <v>14.0055179595947</v>
       </c>
       <c r="G352" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -15139,7 +15142,7 @@
         <v>13.8956308364868</v>
       </c>
       <c r="G353" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -15165,7 +15168,7 @@
         <v>14.2053108215332</v>
       </c>
       <c r="G354" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -15191,7 +15194,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G355" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -15217,7 +15220,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G356" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -15243,7 +15246,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G357" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -15269,7 +15272,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G358" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -15295,7 +15298,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G359" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -15321,7 +15324,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G360" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -15347,7 +15350,7 @@
         <v>14.4250841140747</v>
       </c>
       <c r="G361" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -15373,7 +15376,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G362" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -15399,7 +15402,7 @@
         <v>13.9755487442017</v>
       </c>
       <c r="G363" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -15425,7 +15428,7 @@
         <v>13.8257036209106</v>
       </c>
       <c r="G364" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -15451,7 +15454,7 @@
         <v>14.0055179595947</v>
       </c>
       <c r="G365" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -17401,7 +17404,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G440" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -17609,7 +17612,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G448" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -17635,7 +17638,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G449" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -17687,7 +17690,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G451" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -18077,7 +18080,7 @@
         <v>13.8257036209106</v>
       </c>
       <c r="G466" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -70865,7 +70868,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.649537037</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>440014</v>
@@ -70886,6 +70889,32 @@
         <v>1872</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6912152778</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>237813</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>9.35999965667725</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>9.21500015258789</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>9.31999969482422</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>9.21500015258789</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1873</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16937780380249</t>
+    <t xml:space="preserve">7.16937923431396</t>
   </si>
   <si>
     <t xml:space="preserve">BRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13994932174683</t>
+    <t xml:space="preserve">7.13994789123535</t>
   </si>
   <si>
     <t xml:space="preserve">6.92740154266357</t>
@@ -53,28 +53,28 @@
     <t xml:space="preserve">6.52519702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5415472984314</t>
+    <t xml:space="preserve">6.54154682159424</t>
   </si>
   <si>
     <t xml:space="preserve">6.42873382568359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60040712356567</t>
+    <t xml:space="preserve">6.60040664672852</t>
   </si>
   <si>
     <t xml:space="preserve">6.78188753128052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55135774612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21291542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19820117950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27504539489746</t>
+    <t xml:space="preserve">6.55135679244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21291637420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19820213317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2750449180603</t>
   </si>
   <si>
     <t xml:space="preserve">5.94641542434692</t>
@@ -83,25 +83,25 @@
     <t xml:space="preserve">6.20310640335083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24888610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30610990524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31919002532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38785934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23090028762817</t>
+    <t xml:space="preserve">6.24888563156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30610942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31918907165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38785886764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23090124130249</t>
   </si>
   <si>
     <t xml:space="preserve">6.16713666915894</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05922842025757</t>
+    <t xml:space="preserve">6.05922746658325</t>
   </si>
   <si>
     <t xml:space="preserve">5.99219417572021</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">5.5164155960083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72242212295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67500877380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73223352432251</t>
+    <t xml:space="preserve">5.72242259979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67500829696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73223257064819</t>
   </si>
   <si>
     <t xml:space="preserve">6.03960847854614</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">5.97420978546143</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11972284317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1409764289856</t>
+    <t xml:space="preserve">6.11972236633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14097738265991</t>
   </si>
   <si>
     <t xml:space="preserve">6.10010290145874</t>
@@ -146,160 +146,160 @@
     <t xml:space="preserve">6.23744058609009</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11154747009277</t>
+    <t xml:space="preserve">6.11154699325562</t>
   </si>
   <si>
     <t xml:space="preserve">5.9758448600769</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07394361495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12953329086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21945571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35189056396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32409572601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04675531387329</t>
+    <t xml:space="preserve">6.07394409179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12953233718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21945667266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35188961029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32409524917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04675579071045</t>
   </si>
   <si>
     <t xml:space="preserve">7.08272457122803</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11705827713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07945489883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1203293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07127904891968</t>
+    <t xml:space="preserve">7.1170597076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07945394515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12032842636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07128000259399</t>
   </si>
   <si>
     <t xml:space="preserve">7.06637477874756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16120386123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14321851730347</t>
+    <t xml:space="preserve">7.16120338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14321947097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.24949216842651</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14158391952515</t>
+    <t xml:space="preserve">7.14158487319946</t>
   </si>
   <si>
     <t xml:space="preserve">7.22987222671509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0761833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2691125869751</t>
+    <t xml:space="preserve">7.07618379592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26911211013794</t>
   </si>
   <si>
     <t xml:space="preserve">7.15302801132202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15139293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31489133834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43097496032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40318059921265</t>
+    <t xml:space="preserve">7.15139245986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31489038467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43097543716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40318012237549</t>
   </si>
   <si>
     <t xml:space="preserve">7.3557653427124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14485359191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18899822235107</t>
+    <t xml:space="preserve">7.1448540687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18899917602539</t>
   </si>
   <si>
     <t xml:space="preserve">7.16283845901489</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27401638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998659133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35740041732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40644979476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42280054092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39337110519409</t>
+    <t xml:space="preserve">7.27401685714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998754501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35740089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40645027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42280006408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39337062835693</t>
   </si>
   <si>
     <t xml:space="preserve">7.43915033340454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.471848487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5110878944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76778078079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71546030044556</t>
+    <t xml:space="preserve">7.47185039520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51108837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76778030395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71546125411987</t>
   </si>
   <si>
     <t xml:space="preserve">7.63534688949585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68276214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74162149429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66968154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72200155258179</t>
+    <t xml:space="preserve">7.68276262283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74162101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66968107223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72200012207031</t>
   </si>
   <si>
     <t xml:space="preserve">7.63044214248657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71055746078491</t>
+    <t xml:space="preserve">7.71055698394775</t>
   </si>
   <si>
     <t xml:space="preserve">7.85606908798218</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4773588180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50188541412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51006126403809</t>
+    <t xml:space="preserve">8.47736167907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50188732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51006031036377</t>
   </si>
   <si>
     <t xml:space="preserve">8.55093479156494</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">8.42831134796143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36291217803955</t>
+    <t xml:space="preserve">8.36291313171387</t>
   </si>
   <si>
     <t xml:space="preserve">8.35473728179932</t>
@@ -320,25 +320,25 @@
     <t xml:space="preserve">8.5199146270752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45348167419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51161193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46178531646729</t>
+    <t xml:space="preserve">8.45348262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51161003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4617862701416</t>
   </si>
   <si>
     <t xml:space="preserve">8.47008991241455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61125755310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63617038726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72751426696777</t>
+    <t xml:space="preserve">8.6112585067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63617134094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72751522064209</t>
   </si>
   <si>
     <t xml:space="preserve">8.96002674102783</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">8.10969638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30400848388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3123140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60295391082764</t>
+    <t xml:space="preserve">8.30401039123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31231498718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60295295715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.61956214904785</t>
@@ -374,46 +374,46 @@
     <t xml:space="preserve">8.56973838806152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71921062469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25916957855225</t>
+    <t xml:space="preserve">8.71921157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25916767120361</t>
   </si>
   <si>
     <t xml:space="preserve">7.64134931564331</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25418663024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0598726272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20602226257324</t>
+    <t xml:space="preserve">8.25418567657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05987167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20602130889893</t>
   </si>
   <si>
     <t xml:space="preserve">8.23757648468018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84729051589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6795482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67788743972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95524120330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02831649780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05488967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97849225997925</t>
+    <t xml:space="preserve">7.84728813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67954874038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67788696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95524215698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02831745147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05488872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97849178314209</t>
   </si>
   <si>
     <t xml:space="preserve">8.14457225799561</t>
@@ -428,67 +428,70 @@
     <t xml:space="preserve">8.10471439361572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21100425720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16782379150391</t>
+    <t xml:space="preserve">8.21100521087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16782474517822</t>
   </si>
   <si>
     <t xml:space="preserve">8.32061862945557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37044143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50330638885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36213874816895</t>
+    <t xml:space="preserve">8.37044239044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41196155548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50330543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36213779449463</t>
   </si>
   <si>
     <t xml:space="preserve">8.67768955230713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76903343200684</t>
+    <t xml:space="preserve">8.76903533935547</t>
   </si>
   <si>
     <t xml:space="preserve">8.53652191162109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55313014984131</t>
+    <t xml:space="preserve">8.55313110351562</t>
   </si>
   <si>
     <t xml:space="preserve">8.64447498321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73581790924072</t>
+    <t xml:space="preserve">8.73581981658936</t>
   </si>
   <si>
     <t xml:space="preserve">8.68599414825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74412155151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66938781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48669815063477</t>
+    <t xml:space="preserve">8.74412250518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66938591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48669719696045</t>
   </si>
   <si>
     <t xml:space="preserve">8.4451789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4783935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40365695953369</t>
+    <t xml:space="preserve">8.47839546203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40365791320801</t>
   </si>
   <si>
     <t xml:space="preserve">8.42856979370117</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65277862548828</t>
+    <t xml:space="preserve">8.65277767181396</t>
   </si>
   <si>
     <t xml:space="preserve">8.69429874420166</t>
@@ -506,76 +509,76 @@
     <t xml:space="preserve">8.88529109954834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78564167022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80224990844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8188591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90189838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05137157440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81055450439453</t>
+    <t xml:space="preserve">8.78564357757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80225086212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81885814666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90189933776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05137062072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81055545806885</t>
   </si>
   <si>
     <t xml:space="preserve">8.6278657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70260238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82716178894043</t>
+    <t xml:space="preserve">8.70260334014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82716274261475</t>
   </si>
   <si>
     <t xml:space="preserve">8.75242614746094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04306602478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14271450042725</t>
+    <t xml:space="preserve">9.04306697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14271545410156</t>
   </si>
   <si>
     <t xml:space="preserve">9.28388404846191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35031604766846</t>
+    <t xml:space="preserve">9.35031509399414</t>
   </si>
   <si>
     <t xml:space="preserve">9.35861873626709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15101909637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93511390686035</t>
+    <t xml:space="preserve">9.1510181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93511486053467</t>
   </si>
   <si>
     <t xml:space="preserve">8.7773380279541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19253921508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44996356964111</t>
+    <t xml:space="preserve">9.19254016876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44996452331543</t>
   </si>
   <si>
     <t xml:space="preserve">9.17593193054199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00154685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13441181182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91850757598877</t>
+    <t xml:space="preserve">9.00154590606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13441276550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91850471496582</t>
   </si>
   <si>
     <t xml:space="preserve">8.9268102645874</t>
@@ -587,40 +590,40 @@
     <t xml:space="preserve">8.984938621521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7607307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1178035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22575569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95172309875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06797885894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0762825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20084285736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31710052490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36692333221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49148273468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54961109161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96481227874756</t>
+    <t xml:space="preserve">8.76072978973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11780548095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.225754737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95172214508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06797790527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07628345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20084381103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31709861755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36692428588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49148368835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54961204528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96481132507324</t>
   </si>
   <si>
     <t xml:space="preserve">10.0229406356812</t>
@@ -629,52 +632,52 @@
     <t xml:space="preserve">9.82364273071289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93989944458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98141956329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0063304901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0561571121216</t>
+    <t xml:space="preserve">9.93990039825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98142051696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0063323974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0561561584473</t>
   </si>
   <si>
     <t xml:space="preserve">10.2056283950806</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2305402755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2139339447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1973247528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1558046340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1225891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1807174682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.147500038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2222366333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1308917999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.097674369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84855556488037</t>
+    <t xml:space="preserve">10.230541229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2139329910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.197322845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1558036804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1225881576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1807155609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1475009918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2222356796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1308927536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0976762771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84855651855469</t>
   </si>
   <si>
     <t xml:space="preserve">10.3135814666748</t>
@@ -683,55 +686,55 @@
     <t xml:space="preserve">10.0810680389404</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0727634429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5294857025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4464445114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5211811065674</t>
+    <t xml:space="preserve">10.0727624893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5294828414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4464435577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5211801528931</t>
   </si>
   <si>
     <t xml:space="preserve">10.3883171081543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4713573455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6872606277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7204761505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540441513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4049263000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6457405090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7952127456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9612922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9280776977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7703008651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7786054611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8699502944946</t>
+    <t xml:space="preserve">10.4713554382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6872625350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.720477104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4049243927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6457424163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7952136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9612941741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9280757904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7703018188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7786045074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8699493408203</t>
   </si>
   <si>
     <t xml:space="preserve">10.7869091033936</t>
@@ -740,10 +743,10 @@
     <t xml:space="preserve">11.0360298156738</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8948602676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0443334579468</t>
+    <t xml:space="preserve">10.8948612213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0443344116211</t>
   </si>
   <si>
     <t xml:space="preserve">11.2519330978394</t>
@@ -755,19 +758,19 @@
     <t xml:space="preserve">11.2270212173462</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2602376937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2851505279541</t>
+    <t xml:space="preserve">11.2602367401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2851495742798</t>
   </si>
   <si>
     <t xml:space="preserve">11.3432779312134</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3931016921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4512300491333</t>
+    <t xml:space="preserve">11.393102645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4512310028076</t>
   </si>
   <si>
     <t xml:space="preserve">11.5093584060669</t>
@@ -779,13 +782,13 @@
     <t xml:space="preserve">11.5176620483398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7418689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7584781646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6920461654663</t>
+    <t xml:space="preserve">11.7418699264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7584791183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.692045211792</t>
   </si>
   <si>
     <t xml:space="preserve">11.683741569519</t>
@@ -794,10 +797,10 @@
     <t xml:space="preserve">11.7252626419067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7667837142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7169570922852</t>
+    <t xml:space="preserve">11.7667808532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7169580459595</t>
   </si>
   <si>
     <t xml:space="preserve">11.5923976898193</t>
@@ -806,10 +809,10 @@
     <t xml:space="preserve">11.7003507614136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5425748825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9577751159668</t>
+    <t xml:space="preserve">11.542573928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9577741622925</t>
   </si>
   <si>
     <t xml:space="preserve">12.0574216842651</t>
@@ -818,34 +821,34 @@
     <t xml:space="preserve">11.9162549972534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9909906387329</t>
+    <t xml:space="preserve">11.9909915924072</t>
   </si>
   <si>
     <t xml:space="preserve">11.98268699646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1487674713135</t>
+    <t xml:space="preserve">12.1487665176392</t>
   </si>
   <si>
     <t xml:space="preserve">12.0491189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2899341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3895845413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3148460388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5058393478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5390558242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2733268737793</t>
+    <t xml:space="preserve">12.2899351119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3895826339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3148469924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.505838394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5390548706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2733278274536</t>
   </si>
   <si>
     <t xml:space="preserve">12.1902866363525</t>
@@ -854,16 +857,16 @@
     <t xml:space="preserve">12.1985912322998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0823354721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6422233581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5508766174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8083009719849</t>
+    <t xml:space="preserve">12.0823335647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6422214508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.550877571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8083019256592</t>
   </si>
   <si>
     <t xml:space="preserve">11.9346399307251</t>
@@ -872,19 +875,16 @@
     <t xml:space="preserve">11.9514837265015</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0609760284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1620464324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.783034324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6566972732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8083028793335</t>
+    <t xml:space="preserve">12.0609769821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1620454788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7830352783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6566982269287</t>
   </si>
   <si>
     <t xml:space="preserve">11.7577676773071</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">11.5977401733398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5640506744385</t>
+    <t xml:space="preserve">11.5640497207642</t>
   </si>
   <si>
     <t xml:space="preserve">11.3029546737671</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">11.0334339141846</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9576330184937</t>
+    <t xml:space="preserve">10.9576320648193</t>
   </si>
   <si>
     <t xml:space="preserve">11.2355737686157</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">11.4208679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2271518707275</t>
+    <t xml:space="preserve">11.2271509170532</t>
   </si>
   <si>
     <t xml:space="preserve">11.2861089706421</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">10.923942565918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.025013923645</t>
+    <t xml:space="preserve">11.0250120162964</t>
   </si>
   <si>
     <t xml:space="preserve">10.763916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9492111206055</t>
+    <t xml:space="preserve">10.9492092132568</t>
   </si>
   <si>
     <t xml:space="preserve">10.5786209106445</t>
@@ -947,40 +947,40 @@
     <t xml:space="preserve">10.7386493682861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6544237136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7554931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4292917251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.521936416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2945318222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6398544311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4629802703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4124460220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.361909866333</t>
+    <t xml:space="preserve">10.6544246673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7554941177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4292907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5219383239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2945308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6398525238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4629812240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4124441146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3619108200073</t>
   </si>
   <si>
     <t xml:space="preserve">11.3197984695435</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2103071212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9997444152832</t>
+    <t xml:space="preserve">11.2103061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9997453689575</t>
   </si>
   <si>
     <t xml:space="preserve">10.9913234710693</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">11.0081672668457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8902540206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9323654174805</t>
+    <t xml:space="preserve">10.8902530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9323663711548</t>
   </si>
   <si>
     <t xml:space="preserve">10.8734073638916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8818311691284</t>
+    <t xml:space="preserve">10.8818302154541</t>
   </si>
   <si>
     <t xml:space="preserve">10.6796922683716</t>
@@ -1007,31 +1007,31 @@
     <t xml:space="preserve">10.7807607650757</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8649854660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7049589157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9155197143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2608404159546</t>
+    <t xml:space="preserve">10.8649864196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7049579620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9155216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2608423233032</t>
   </si>
   <si>
     <t xml:space="preserve">11.151349067688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0839710235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0502796173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2524185180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3282203674316</t>
+    <t xml:space="preserve">11.0839691162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0502786636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.252420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.328221321106</t>
   </si>
   <si>
     <t xml:space="preserve">11.378755569458</t>
@@ -1046,49 +1046,49 @@
     <t xml:space="preserve">11.4040241241455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.555627822876</t>
+    <t xml:space="preserve">11.5556268692017</t>
   </si>
   <si>
     <t xml:space="preserve">11.6819648742676</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7493448257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9177942276001</t>
+    <t xml:space="preserve">11.7493438720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9177932739258</t>
   </si>
   <si>
     <t xml:space="preserve">11.8841037750244</t>
   </si>
   <si>
-    <t xml:space="preserve">11.943060874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0525541305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0946674346924</t>
+    <t xml:space="preserve">11.9430618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0525531768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0946664810181</t>
   </si>
   <si>
     <t xml:space="preserve">12.1536235809326</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0357074737549</t>
+    <t xml:space="preserve">12.0357084274292</t>
   </si>
   <si>
     <t xml:space="preserve">12.0778207778931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.044132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1788911819458</t>
+    <t xml:space="preserve">12.0441312789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1788902282715</t>
   </si>
   <si>
     <t xml:space="preserve">12.170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3136520385742</t>
+    <t xml:space="preserve">12.3136501312256</t>
   </si>
   <si>
     <t xml:space="preserve">12.3220729827881</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">12.3726081848145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2041578292847</t>
+    <t xml:space="preserve">12.2041568756104</t>
   </si>
   <si>
     <t xml:space="preserve">12.2883825302124</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">11.7324991226196</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8167238235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.010440826416</t>
+    <t xml:space="preserve">11.816722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0104398727417</t>
   </si>
   <si>
     <t xml:space="preserve">12.0020189285278</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">11.3113746643066</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8144521713257</t>
+    <t xml:space="preserve">10.8144493103027</t>
   </si>
   <si>
     <t xml:space="preserve">10.6965351104736</t>
@@ -1151,34 +1151,34 @@
     <t xml:space="preserve">10.7723379135132</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7976055145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7302265167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7218036651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6628456115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6123113632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8060274124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6881141662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312950134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6712684631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4691295623779</t>
+    <t xml:space="preserve">10.7976045608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7302255630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7218027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6628465652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6123123168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8060283660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6881132125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312959671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6712694168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4691286087036</t>
   </si>
   <si>
     <t xml:space="preserve">10.4859733581543</t>
@@ -1187,16 +1187,16 @@
     <t xml:space="preserve">11.0923919677734</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1597719192505</t>
+    <t xml:space="preserve">11.1597709655762</t>
   </si>
   <si>
     <t xml:space="preserve">11.1345043182373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1429281234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2187299728394</t>
+    <t xml:space="preserve">11.1429271697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.218729019165</t>
   </si>
   <si>
     <t xml:space="preserve">11.4545583724976</t>
@@ -1205,73 +1205,73 @@
     <t xml:space="preserve">11.3450660705566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4270172119141</t>
+    <t xml:space="preserve">10.4270181655884</t>
   </si>
   <si>
     <t xml:space="preserve">10.3175249099731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2417211532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2838344573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1911859512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1574964523315</t>
+    <t xml:space="preserve">10.2417221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2838354110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1911869049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1574983596802</t>
   </si>
   <si>
     <t xml:space="preserve">10.2248773574829</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1659212112427</t>
+    <t xml:space="preserve">10.1659202575684</t>
   </si>
   <si>
     <t xml:space="preserve">10.1069631576538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0985412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93009090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98904895782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0058946609497</t>
+    <t xml:space="preserve">10.0985403060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93008995056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98904800415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0058927536011</t>
   </si>
   <si>
     <t xml:space="preserve">9.7195291519165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68583869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4837007522583</t>
+    <t xml:space="preserve">9.68583965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48370170593262</t>
   </si>
   <si>
     <t xml:space="preserve">9.37420845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1153869628906</t>
+    <t xml:space="preserve">10.115385055542</t>
   </si>
   <si>
     <t xml:space="preserve">10.3091020584106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5954666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7133798599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.603889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3596382141113</t>
+    <t xml:space="preserve">10.5954656600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7133808135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6038885116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3596363067627</t>
   </si>
   <si>
     <t xml:space="preserve">10.3006801605225</t>
@@ -1280,61 +1280,61 @@
     <t xml:space="preserve">10.4522838592529</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4017486572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5617752075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5449323654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3427925109863</t>
+    <t xml:space="preserve">10.4017496109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5617771148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5449314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.342791557312</t>
   </si>
   <si>
     <t xml:space="preserve">10.4438610076904</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4101734161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4185943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4354391098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2585678100586</t>
+    <t xml:space="preserve">10.4101724624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4185953140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4354381561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2585668563843</t>
   </si>
   <si>
     <t xml:space="preserve">10.2333002090454</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2922563552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1490745544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0418577194214</t>
+    <t xml:space="preserve">10.29225730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1490755081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0418586730957</t>
   </si>
   <si>
     <t xml:space="preserve">10.536509513855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2754135131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2080335617065</t>
+    <t xml:space="preserve">10.2754125595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2080326080322</t>
   </si>
   <si>
     <t xml:space="preserve">10.0648517608643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93851470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0500869750977</t>
+    <t xml:space="preserve">9.93851375579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0500860214233</t>
   </si>
   <si>
     <t xml:space="preserve">10.384801864624</t>
@@ -1343,10 +1343,10 @@
     <t xml:space="preserve">10.3075609207153</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7710151672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.676607131958</t>
+    <t xml:space="preserve">10.771014213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6766080856323</t>
   </si>
   <si>
     <t xml:space="preserve">10.5993642807007</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">10.230318069458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4706268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.504958152771</t>
+    <t xml:space="preserve">10.470627784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5049571990967</t>
   </si>
   <si>
     <t xml:space="preserve">10.642276763916</t>
@@ -1367,28 +1367,28 @@
     <t xml:space="preserve">10.6851892471313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6594429016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7109365463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9340829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.650860786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452669143677</t>
+    <t xml:space="preserve">10.6594438552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.93408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6508598327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.745267868042</t>
   </si>
   <si>
     <t xml:space="preserve">10.5307054519653</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3933868408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3504724502563</t>
+    <t xml:space="preserve">10.393385887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3504734039307</t>
   </si>
   <si>
     <t xml:space="preserve">10.1444940567017</t>
@@ -1400,43 +1400,43 @@
     <t xml:space="preserve">9.92135047912598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0758352279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0586700439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89560222625732</t>
+    <t xml:space="preserve">10.075834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.058669090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89560127258301</t>
   </si>
   <si>
     <t xml:space="preserve">9.947096824646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74111557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76686477661133</t>
+    <t xml:space="preserve">9.74111747741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76686382293701</t>
   </si>
   <si>
     <t xml:space="preserve">9.85268878936768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87843704223633</t>
+    <t xml:space="preserve">9.87843608856201</t>
   </si>
   <si>
     <t xml:space="preserve">9.99000930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2560653686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2903966903687</t>
+    <t xml:space="preserve">10.2560663223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2903957366943</t>
   </si>
   <si>
     <t xml:space="preserve">10.2732305526733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.51353931427</t>
+    <t xml:space="preserve">10.5135402679443</t>
   </si>
   <si>
     <t xml:space="preserve">10.48779296875</t>
@@ -1445,43 +1445,43 @@
     <t xml:space="preserve">10.436297416687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3333082199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.084415435791</t>
+    <t xml:space="preserve">10.333309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0844163894653</t>
   </si>
   <si>
     <t xml:space="preserve">10.1273288726807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0157556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.032922744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84410667419434</t>
+    <t xml:space="preserve">10.0157566070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0329217910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84410572052002</t>
   </si>
   <si>
     <t xml:space="preserve">10.04150390625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2389001846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78402900695801</t>
+    <t xml:space="preserve">10.2389011383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78402996063232</t>
   </si>
   <si>
     <t xml:space="preserve">9.706787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77544498443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68103981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56088542938232</t>
+    <t xml:space="preserve">9.77544689178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68103885650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56088638305664</t>
   </si>
   <si>
     <t xml:space="preserve">9.59521579742432</t>
@@ -1496,58 +1496,58 @@
     <t xml:space="preserve">9.483642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62954616546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.912766456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88701820373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75828170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56946754455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.578049659729</t>
+    <t xml:space="preserve">9.62954425811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91276550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88701915740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75828266143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56946659088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57804870605469</t>
   </si>
   <si>
     <t xml:space="preserve">9.73253345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61237907409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71536922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82694149017334</t>
+    <t xml:space="preserve">9.612380027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71536827087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82694053649902</t>
   </si>
   <si>
     <t xml:space="preserve">10.187406539917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2217350006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99859142303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96426200866699</t>
+    <t xml:space="preserve">10.2217359542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99859237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96426105499268</t>
   </si>
   <si>
     <t xml:space="preserve">9.86985397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69820499420166</t>
+    <t xml:space="preserve">9.69820404052734</t>
   </si>
   <si>
     <t xml:space="preserve">9.86127090454102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52655506134033</t>
+    <t xml:space="preserve">9.52655601501465</t>
   </si>
   <si>
     <t xml:space="preserve">9.21758651733398</t>
@@ -1559,52 +1559,52 @@
     <t xml:space="preserve">8.69405460357666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52669620513916</t>
+    <t xml:space="preserve">8.52669525146484</t>
   </si>
   <si>
     <t xml:space="preserve">8.4408712387085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12331867218018</t>
+    <t xml:space="preserve">8.12331962585449</t>
   </si>
   <si>
     <t xml:space="preserve">8.43228912353516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52240371704102</t>
+    <t xml:space="preserve">8.5224027633667</t>
   </si>
   <si>
     <t xml:space="preserve">8.41083240509033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29925918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16623115539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23060131072998</t>
+    <t xml:space="preserve">8.29926013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16623020172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23060035705566</t>
   </si>
   <si>
     <t xml:space="preserve">8.08469772338867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35504722595215</t>
+    <t xml:space="preserve">8.35504627227783</t>
   </si>
   <si>
     <t xml:space="preserve">8.22630882263184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48378467559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39366722106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57818984985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49236679077148</t>
+    <t xml:space="preserve">8.48378372192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39366626739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57819080352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49236583709717</t>
   </si>
   <si>
     <t xml:space="preserve">8.44945335388184</t>
@@ -1613,46 +1613,46 @@
     <t xml:space="preserve">8.23489189147949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11473560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02033042907715</t>
+    <t xml:space="preserve">8.11473751068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02032947540283</t>
   </si>
   <si>
     <t xml:space="preserve">7.79289293289185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72852373123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77143669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83151435852051</t>
+    <t xml:space="preserve">7.72852468490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77143621444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83151340484619</t>
   </si>
   <si>
     <t xml:space="preserve">8.00316429138184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02891159057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00745391845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25205612182617</t>
+    <t xml:space="preserve">8.02891063690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00745487213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25205707550049</t>
   </si>
   <si>
     <t xml:space="preserve">8.28638744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61681079864502</t>
+    <t xml:space="preserve">8.61681175231934</t>
   </si>
   <si>
     <t xml:space="preserve">8.608229637146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54815006256104</t>
+    <t xml:space="preserve">8.54815101623535</t>
   </si>
   <si>
     <t xml:space="preserve">8.75413227081299</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">8.48807525634766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.462327003479</t>
+    <t xml:space="preserve">8.46232795715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.16193962097168</t>
@@ -1685,19 +1685,19 @@
     <t xml:space="preserve">7.69848680496216</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99887418746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81864070892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86584424972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58691310882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.634117603302</t>
+    <t xml:space="preserve">7.99887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81863975524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8658447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58691215515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63411712646484</t>
   </si>
   <si>
     <t xml:space="preserve">7.6899037361145</t>
@@ -1706,40 +1706,40 @@
     <t xml:space="preserve">7.65986633300781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96454334259033</t>
+    <t xml:space="preserve">7.96454381942749</t>
   </si>
   <si>
     <t xml:space="preserve">7.93879556655884</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73696708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82279109954834</t>
+    <t xml:space="preserve">8.73696517944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82279205322266</t>
   </si>
   <si>
     <t xml:space="preserve">8.4794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38508319854736</t>
+    <t xml:space="preserve">8.38508415222168</t>
   </si>
   <si>
     <t xml:space="preserve">8.40225028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45374298095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36791896820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49665641784668</t>
+    <t xml:space="preserve">8.45374393463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.367919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.496657371521</t>
   </si>
   <si>
     <t xml:space="preserve">8.50094795227051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46661853790283</t>
+    <t xml:space="preserve">8.46661949157715</t>
   </si>
   <si>
     <t xml:space="preserve">8.59964847564697</t>
@@ -1751,13 +1751,13 @@
     <t xml:space="preserve">8.56960773468018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56531715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55673503875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53956985473633</t>
+    <t xml:space="preserve">8.56531810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55673408508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53956890106201</t>
   </si>
   <si>
     <t xml:space="preserve">8.50523948669434</t>
@@ -1772,13 +1772,13 @@
     <t xml:space="preserve">8.15335845947266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39795970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58248138427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77129650115967</t>
+    <t xml:space="preserve">8.39795875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58248043060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77129554748535</t>
   </si>
   <si>
     <t xml:space="preserve">8.65972423553467</t>
@@ -1787,58 +1787,58 @@
     <t xml:space="preserve">9.09743022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96869373321533</t>
+    <t xml:space="preserve">8.96869277954102</t>
   </si>
   <si>
     <t xml:space="preserve">9.020188331604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2862434387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31199264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08026504516602</t>
+    <t xml:space="preserve">9.28624439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31199169158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08026599884033</t>
   </si>
   <si>
     <t xml:space="preserve">9.131760597229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32057476043701</t>
+    <t xml:space="preserve">9.3205738067627</t>
   </si>
   <si>
     <t xml:space="preserve">8.94294548034668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81420803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78845977783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.797043800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74554824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72838592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.908616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14034461975098</t>
+    <t xml:space="preserve">8.814208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78846073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79704475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74554920196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72838401794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90861511230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14034271240234</t>
   </si>
   <si>
     <t xml:space="preserve">9.42356586456299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26049709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18325710296631</t>
+    <t xml:space="preserve">9.260498046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18325519561768</t>
   </si>
   <si>
     <t xml:space="preserve">9.00302314758301</t>
@@ -1859,52 +1859,49 @@
     <t xml:space="preserve">8.67688941955566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8742847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51797199249268</t>
+    <t xml:space="preserve">8.87428569793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51797103881836</t>
   </si>
   <si>
     <t xml:space="preserve">9.44073009490967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41498184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64670944213867</t>
+    <t xml:space="preserve">9.41498279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64670753479004</t>
   </si>
   <si>
     <t xml:space="preserve">10.0672512054443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93851375579834</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.195987701416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80977630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62096214294434</t>
+    <t xml:space="preserve">9.80977725982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62096309661865</t>
   </si>
   <si>
     <t xml:space="preserve">9.50938987731934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86570262908936</t>
+    <t xml:space="preserve">8.86570453643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.95152854919434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83995628356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75851726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77167415618896</t>
+    <t xml:space="preserve">8.83995532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75851821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77167510986328</t>
   </si>
   <si>
     <t xml:space="preserve">8.74097442626953</t>
@@ -1913,7 +1910,7 @@
     <t xml:space="preserve">8.42080783843994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53483963012695</t>
+    <t xml:space="preserve">8.53484058380127</t>
   </si>
   <si>
     <t xml:space="preserve">8.57869815826416</t>
@@ -1925,19 +1922,19 @@
     <t xml:space="preserve">8.47343730926514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55238246917725</t>
+    <t xml:space="preserve">8.55238342285156</t>
   </si>
   <si>
     <t xml:space="preserve">8.42957973480225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1839714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37695026397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56992530822754</t>
+    <t xml:space="preserve">8.18397235870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37694931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56992626190186</t>
   </si>
   <si>
     <t xml:space="preserve">8.67957305908203</t>
@@ -1946,19 +1943,22 @@
     <t xml:space="preserve">8.66202831268311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8944787979126</t>
+    <t xml:space="preserve">8.89447975158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7541332244873</t>
   </si>
   <si>
     <t xml:space="preserve">8.72781753540039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72343063354492</t>
+    <t xml:space="preserve">8.72343158721924</t>
   </si>
   <si>
     <t xml:space="preserve">8.93833637237549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82430458068848</t>
+    <t xml:space="preserve">8.82430553436279</t>
   </si>
   <si>
     <t xml:space="preserve">9.06113910675049</t>
@@ -1970,31 +1970,31 @@
     <t xml:space="preserve">8.85062026977539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71465969085693</t>
+    <t xml:space="preserve">8.71465873718262</t>
   </si>
   <si>
     <t xml:space="preserve">8.88570785522461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11376953125</t>
+    <t xml:space="preserve">9.11377048492432</t>
   </si>
   <si>
     <t xml:space="preserve">9.05236911773682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28043174743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32428932189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23657417297363</t>
+    <t xml:space="preserve">9.28043270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3242883682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23657321929932</t>
   </si>
   <si>
     <t xml:space="preserve">8.9295654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80676078796387</t>
+    <t xml:space="preserve">8.80676174163818</t>
   </si>
   <si>
     <t xml:space="preserve">8.78921985626221</t>
@@ -2003,46 +2003,46 @@
     <t xml:space="preserve">8.49536800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45589637756348</t>
+    <t xml:space="preserve">8.45589542388916</t>
   </si>
   <si>
     <t xml:space="preserve">8.48220920562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62255668640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92079544067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07868385314941</t>
+    <t xml:space="preserve">8.62255764007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92079448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07868480682373</t>
   </si>
   <si>
     <t xml:space="preserve">9.0172815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17958736419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1313419342041</t>
+    <t xml:space="preserve">8.17958641052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13134288787842</t>
   </si>
   <si>
     <t xml:space="preserve">8.17081546783447</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96029663085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77170419692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61819887161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64890003204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63135766983032</t>
+    <t xml:space="preserve">7.96029567718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77170372009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61819982528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64890050888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63135671615601</t>
   </si>
   <si>
     <t xml:space="preserve">7.38574981689453</t>
@@ -2051,31 +2051,31 @@
     <t xml:space="preserve">7.29803371429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39013624191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22347402572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20593166351318</t>
+    <t xml:space="preserve">7.39013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22347354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20593118667603</t>
   </si>
   <si>
     <t xml:space="preserve">7.28048992156982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27171802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51293897628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39890813827515</t>
+    <t xml:space="preserve">7.27171754837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.512939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39890766143799</t>
   </si>
   <si>
     <t xml:space="preserve">7.26733303070068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19277381896973</t>
+    <t xml:space="preserve">7.19277334213257</t>
   </si>
   <si>
     <t xml:space="preserve">7.4427661895752</t>
@@ -2087,13 +2087,13 @@
     <t xml:space="preserve">7.32873439788818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53048276901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79363393783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98661041259766</t>
+    <t xml:space="preserve">7.53048372268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79363346099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98661136627197</t>
   </si>
   <si>
     <t xml:space="preserve">8.0611686706543</t>
@@ -2102,67 +2102,67 @@
     <t xml:space="preserve">8.22344589233398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28923320770264</t>
+    <t xml:space="preserve">8.28923225402832</t>
   </si>
   <si>
     <t xml:space="preserve">8.35063457489014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21905994415283</t>
+    <t xml:space="preserve">8.21905899047852</t>
   </si>
   <si>
     <t xml:space="preserve">8.19274425506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30239009857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87257862091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72346067428589</t>
+    <t xml:space="preserve">8.30239105224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87257814407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72346019744873</t>
   </si>
   <si>
     <t xml:space="preserve">7.60942888259888</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74100303649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83310604095459</t>
+    <t xml:space="preserve">7.74100255966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83310556411743</t>
   </si>
   <si>
     <t xml:space="preserve">7.84187793731689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67521524429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50855350494385</t>
+    <t xml:space="preserve">7.67521572113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50855445861816</t>
   </si>
   <si>
     <t xml:space="preserve">7.40329360961914</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45592403411865</t>
+    <t xml:space="preserve">7.45592451095581</t>
   </si>
   <si>
     <t xml:space="preserve">7.44715213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31557703018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47346687316895</t>
+    <t xml:space="preserve">7.31557655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47346782684326</t>
   </si>
   <si>
     <t xml:space="preserve">7.85064888000488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85942077636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0085391998291</t>
+    <t xml:space="preserve">7.85942029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00854015350342</t>
   </si>
   <si>
     <t xml:space="preserve">8.04362678527832</t>
@@ -2183,22 +2183,22 @@
     <t xml:space="preserve">8.29361820220947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36379241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65325736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37256336212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43835163116455</t>
+    <t xml:space="preserve">8.36379146575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65325832366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3725643157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43835067749023</t>
   </si>
   <si>
     <t xml:space="preserve">8.9646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12254333496094</t>
+    <t xml:space="preserve">9.12254238128662</t>
   </si>
   <si>
     <t xml:space="preserve">9.14885711669922</t>
@@ -2207,34 +2207,34 @@
     <t xml:space="preserve">9.37692070007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56112575531006</t>
+    <t xml:space="preserve">9.56112480163574</t>
   </si>
   <si>
     <t xml:space="preserve">9.75410175323486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70147228240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47340965270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35060596466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49095058441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24534511566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42078018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31551837921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48218059539795</t>
+    <t xml:space="preserve">9.70147323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47340869903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35060501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49095153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24534606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42077922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31551933288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48218154907227</t>
   </si>
   <si>
     <t xml:space="preserve">9.64884281158447</t>
@@ -2243,46 +2243,46 @@
     <t xml:space="preserve">9.72778701782227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80673408508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77164649963379</t>
+    <t xml:space="preserve">9.80673313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77164745330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.85936260223389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81550407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86813354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9207649230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9997091293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87690830230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84182071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89445018768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9821662902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0698823928833</t>
+    <t xml:space="preserve">9.815505027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86813449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92076396942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99971008300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87690734863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84181976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89444923400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98216533660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0698833465576</t>
   </si>
   <si>
     <t xml:space="preserve">9.96462249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67515850067139</t>
+    <t xml:space="preserve">9.67515754699707</t>
   </si>
   <si>
     <t xml:space="preserve">9.71901607513428</t>
@@ -2300,28 +2300,28 @@
     <t xml:space="preserve">9.63129997253418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71024513244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68392848968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69270133972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76287460327148</t>
+    <t xml:space="preserve">9.71024417877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68392944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69270038604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76287364959717</t>
   </si>
   <si>
     <t xml:space="preserve">9.73655986785889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57866859436035</t>
+    <t xml:space="preserve">9.57867050170898</t>
   </si>
   <si>
     <t xml:space="preserve">9.30674743652344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21025943756104</t>
+    <t xml:space="preserve">9.21026039123535</t>
   </si>
   <si>
     <t xml:space="preserve">9.33306217193604</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">9.20148658752441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0260534286499</t>
+    <t xml:space="preserve">9.02605533599854</t>
   </si>
   <si>
     <t xml:space="preserve">9.26288890838623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13131427764893</t>
+    <t xml:space="preserve">9.13131332397461</t>
   </si>
   <si>
     <t xml:space="preserve">9.0874547958374</t>
@@ -2345,13 +2345,13 @@
     <t xml:space="preserve">9.43832302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42955112457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21903038024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25411796569824</t>
+    <t xml:space="preserve">9.42955017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21902942657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25411701202393</t>
   </si>
   <si>
     <t xml:space="preserve">9.15762901306152</t>
@@ -2369,22 +2369,22 @@
     <t xml:space="preserve">8.34186267852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10502815246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92959356307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49978256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60065650939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4296088218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11821460723877</t>
+    <t xml:space="preserve">8.10502910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92959403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4997820854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60065603256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42960929870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11821413040161</t>
   </si>
   <si>
     <t xml:space="preserve">7.18400192260742</t>
@@ -2396,13 +2396,13 @@
     <t xml:space="preserve">6.64892959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5568265914917</t>
+    <t xml:space="preserve">6.55682611465454</t>
   </si>
   <si>
     <t xml:space="preserve">6.14017248153687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3857798576355</t>
+    <t xml:space="preserve">6.38577938079834</t>
   </si>
   <si>
     <t xml:space="preserve">5.87702226638794</t>
@@ -2417,46 +2417,46 @@
     <t xml:space="preserve">7.1138277053833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72784376144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82436323165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02172517776489</t>
+    <t xml:space="preserve">7.72784471511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82436275482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02172565460205</t>
   </si>
   <si>
     <t xml:space="preserve">6.47349548339844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31560611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83316421508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96035289764404</t>
+    <t xml:space="preserve">6.31560659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83316373825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9603533744812</t>
   </si>
   <si>
     <t xml:space="preserve">5.85070705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61387252807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18406009674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47352457046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54369831085205</t>
+    <t xml:space="preserve">5.61387205123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18405961990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47352504730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54369783401489</t>
   </si>
   <si>
     <t xml:space="preserve">5.89895105361938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82439279556274</t>
+    <t xml:space="preserve">5.82439231872559</t>
   </si>
   <si>
     <t xml:space="preserve">5.64895868301392</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">5.69720315933228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92965269088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06122732162476</t>
+    <t xml:space="preserve">5.92965221405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06122779846191</t>
   </si>
   <si>
     <t xml:space="preserve">6.0085973739624</t>
@@ -2477,46 +2477,46 @@
     <t xml:space="preserve">6.0568413734436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40332269668579</t>
+    <t xml:space="preserve">6.40332221984863</t>
   </si>
   <si>
     <t xml:space="preserve">6.59191370010376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83752107620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69717359542847</t>
+    <t xml:space="preserve">6.83752155303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69717311859131</t>
   </si>
   <si>
     <t xml:space="preserve">6.86822175979614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81120538711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72348880767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48665332794189</t>
+    <t xml:space="preserve">6.81120586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72348928451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48665380477905</t>
   </si>
   <si>
     <t xml:space="preserve">6.48226737976074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36385107040405</t>
+    <t xml:space="preserve">6.36385059356689</t>
   </si>
   <si>
     <t xml:space="preserve">6.22788953781128</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77176189422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82000684738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26297569274902</t>
+    <t xml:space="preserve">5.77176237106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82000637054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26297521591187</t>
   </si>
   <si>
     <t xml:space="preserve">6.23227548599243</t>
@@ -2546,28 +2546,28 @@
     <t xml:space="preserve">7.41645097732544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.798020362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68398714065552</t>
+    <t xml:space="preserve">7.79801988601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68398761749268</t>
   </si>
   <si>
     <t xml:space="preserve">7.55679845809937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10067224502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35504961013794</t>
+    <t xml:space="preserve">7.10067176818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35504913330078</t>
   </si>
   <si>
     <t xml:space="preserve">7.35066413879395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21031665802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23224544525146</t>
+    <t xml:space="preserve">7.21031713485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23224639892578</t>
   </si>
   <si>
     <t xml:space="preserve">7.17522954940796</t>
@@ -2588,67 +2588,67 @@
     <t xml:space="preserve">7.17084407806396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40767860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25856065750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3682074546814</t>
+    <t xml:space="preserve">7.40767955780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25856113433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36820697784424</t>
   </si>
   <si>
     <t xml:space="preserve">7.32434892654419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14891481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24978876113892</t>
+    <t xml:space="preserve">7.14891529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24978923797607</t>
   </si>
   <si>
     <t xml:space="preserve">7.43838024139404</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16645812988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70155954360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61384296417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69278764724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75418996810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68401670455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71033096313477</t>
+    <t xml:space="preserve">7.16645860671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70156002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61384248733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69278812408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75419044494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68401622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71033191680908</t>
   </si>
   <si>
     <t xml:space="preserve">6.83313465118408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06119823455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14014291763306</t>
+    <t xml:space="preserve">7.06119775772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1401424407959</t>
   </si>
   <si>
     <t xml:space="preserve">7.05681276321411</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04804086685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00856781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94716644287109</t>
+    <t xml:space="preserve">7.04804134368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00856828689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94716691970825</t>
   </si>
   <si>
     <t xml:space="preserve">7.07435607910156</t>
@@ -2657,40 +2657,40 @@
     <t xml:space="preserve">7.0875129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09628534317017</t>
+    <t xml:space="preserve">7.09628486633301</t>
   </si>
   <si>
     <t xml:space="preserve">7.01734018325806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35943508148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29364776611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49100971221924</t>
+    <t xml:space="preserve">7.35943555831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29364824295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49101066589355</t>
   </si>
   <si>
     <t xml:space="preserve">7.60504245758057</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97345304489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57434034347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41206550598145</t>
+    <t xml:space="preserve">7.97345352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57434129714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41206502914429</t>
   </si>
   <si>
     <t xml:space="preserve">6.88576507568359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99102544784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0392689704895</t>
+    <t xml:space="preserve">6.9910249710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03926944732666</t>
   </si>
   <si>
     <t xml:space="preserve">7.06997013092041</t>
@@ -2702,40 +2702,40 @@
     <t xml:space="preserve">7.48223924636841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8638072013855</t>
+    <t xml:space="preserve">7.86380672454834</t>
   </si>
   <si>
     <t xml:space="preserve">7.92082166671753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99976778030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73661804199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68837356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61381483078003</t>
+    <t xml:space="preserve">7.9997673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73661756515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68837308883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61381387710571</t>
   </si>
   <si>
     <t xml:space="preserve">7.62697172164917</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57872819900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77608966827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80240488052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96906566619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99099588394165</t>
+    <t xml:space="preserve">7.57872772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77609014511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240440368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96906614303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99099493026733</t>
   </si>
   <si>
     <t xml:space="preserve">8.15327167510986</t>
@@ -2744,28 +2744,28 @@
     <t xml:space="preserve">8.54799747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56995534896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82433414459229</t>
+    <t xml:space="preserve">7.56995487213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82433366775513</t>
   </si>
   <si>
     <t xml:space="preserve">7.66644477844238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71907377243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78486156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86819314956665</t>
+    <t xml:space="preserve">7.71907329559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78486204147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86819267272949</t>
   </si>
   <si>
     <t xml:space="preserve">9.22780227661133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17517185211182</t>
+    <t xml:space="preserve">9.17517280578613</t>
   </si>
   <si>
     <t xml:space="preserve">9.39446449279785</t>
@@ -2774,91 +2774,91 @@
     <t xml:space="preserve">9.83304786682129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58744144439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40323543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36814975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35937690734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53481006622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46463680267334</t>
+    <t xml:space="preserve">9.58744049072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40323638916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36814880371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35937786102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53481197357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46463775634766</t>
   </si>
   <si>
     <t xml:space="preserve">9.50849628448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41200828552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38569355010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61375617980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49972438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03482532501221</t>
+    <t xml:space="preserve">9.41200733184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38569164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61375713348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49972534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03482437133789</t>
   </si>
   <si>
     <t xml:space="preserve">9.74533176422119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90322208404541</t>
+    <t xml:space="preserve">9.90322303771973</t>
   </si>
   <si>
     <t xml:space="preserve">10.0961980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1225118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.938307762146</t>
+    <t xml:space="preserve">10.1225128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93830871582031</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638660430908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88567733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45586490631104</t>
+    <t xml:space="preserve">9.88567638397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45586395263672</t>
   </si>
   <si>
     <t xml:space="preserve">9.51726722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44709396362305</t>
+    <t xml:space="preserve">9.44709491729736</t>
   </si>
   <si>
     <t xml:space="preserve">9.82427597045898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56989669799805</t>
+    <t xml:space="preserve">9.56989765167236</t>
   </si>
   <si>
     <t xml:space="preserve">8.94710922241211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16640090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28920459747314</t>
+    <t xml:space="preserve">9.16639995574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28920364379883</t>
   </si>
   <si>
     <t xml:space="preserve">9.27166080474854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34183502197266</t>
+    <t xml:space="preserve">9.34183406829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.19271469116211</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">9.18394470214844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90324974060059</t>
+    <t xml:space="preserve">8.90324878692627</t>
   </si>
   <si>
     <t xml:space="preserve">9.06991100311279</t>
@@ -2876,19 +2876,19 @@
     <t xml:space="preserve">8.84184837341309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9997386932373</t>
+    <t xml:space="preserve">8.99973773956299</t>
   </si>
   <si>
     <t xml:space="preserve">8.97342300415039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18857097625732</t>
+    <t xml:space="preserve">9.18857192993164</t>
   </si>
   <si>
     <t xml:space="preserve">9.19807243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18909931182861</t>
+    <t xml:space="preserve">9.1890983581543</t>
   </si>
   <si>
     <t xml:space="preserve">9.43138980865479</t>
@@ -2909,13 +2909,13 @@
     <t xml:space="preserve">9.94289207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98776149749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79033756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74546909332275</t>
+    <t xml:space="preserve">9.98776054382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79033851623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74547004699707</t>
   </si>
   <si>
     <t xml:space="preserve">9.68265438079834</t>
@@ -2939,28 +2939,28 @@
     <t xml:space="preserve">9.63778495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61086368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69162750244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50317859649658</t>
+    <t xml:space="preserve">9.61086463928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69162845611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5031795501709</t>
   </si>
   <si>
     <t xml:space="preserve">9.58394336700439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60188961029053</t>
+    <t xml:space="preserve">9.60189056396484</t>
   </si>
   <si>
     <t xml:space="preserve">9.55702114105225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54804801940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35960102081299</t>
+    <t xml:space="preserve">9.5480489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35960006713867</t>
   </si>
   <si>
     <t xml:space="preserve">9.76341724395752</t>
@@ -2969,25 +2969,25 @@
     <t xml:space="preserve">9.64675903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29678249359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33267688751221</t>
+    <t xml:space="preserve">9.29678344726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33267784118652</t>
   </si>
   <si>
     <t xml:space="preserve">9.3865213394165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39549541473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77239227294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88905143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3915777206421</t>
+    <t xml:space="preserve">9.39549446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7723913192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8890495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3915786743164</t>
   </si>
   <si>
     <t xml:space="preserve">10.5800256729126</t>
@@ -2999,43 +2999,43 @@
     <t xml:space="preserve">10.6877107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7415542602539</t>
+    <t xml:space="preserve">10.7415533065796</t>
   </si>
   <si>
     <t xml:space="preserve">10.8582124710083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9389753341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9838447570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0556344985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1005029678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0915298461914</t>
+    <t xml:space="preserve">10.9389743804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9838438034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0556335449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1005020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0915288925171</t>
   </si>
   <si>
     <t xml:space="preserve">11.127423286438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0197401046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9300031661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0107660293579</t>
+    <t xml:space="preserve">11.019739151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9300012588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312902450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376863479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0107650756836</t>
   </si>
   <si>
     <t xml:space="preserve">10.9748697280884</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">10.8761587142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.912055015564</t>
+    <t xml:space="preserve">10.9120540618896</t>
   </si>
   <si>
     <t xml:space="preserve">11.0466604232788</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">10.921028137207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8941078186035</t>
+    <t xml:space="preserve">10.8941068649292</t>
   </si>
   <si>
     <t xml:space="preserve">10.9030809402466</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">10.2569723129272</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90699768066406</t>
+    <t xml:space="preserve">9.90699672698975</t>
   </si>
   <si>
     <t xml:space="preserve">9.96083927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1223659515381</t>
+    <t xml:space="preserve">10.1223669052124</t>
   </si>
   <si>
     <t xml:space="preserve">10.1313400268555</t>
@@ -3092,10 +3092,10 @@
     <t xml:space="preserve">10.1403141021729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0954465866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87110137939453</t>
+    <t xml:space="preserve">10.0954456329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87110233306885</t>
   </si>
   <si>
     <t xml:space="preserve">9.80828666687012</t>
@@ -3107,13 +3107,13 @@
     <t xml:space="preserve">9.47625923156738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67367935180664</t>
+    <t xml:space="preserve">9.67368030548096</t>
   </si>
   <si>
     <t xml:space="preserve">9.70957469940186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75444316864014</t>
+    <t xml:space="preserve">9.75444412231445</t>
   </si>
   <si>
     <t xml:space="preserve">9.84418106079102</t>
@@ -3122,10 +3122,10 @@
     <t xml:space="preserve">9.85315418243408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82623291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86212730407715</t>
+    <t xml:space="preserve">9.82623386383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86212825775146</t>
   </si>
   <si>
     <t xml:space="preserve">10.0236558914185</t>
@@ -3134,16 +3134,16 @@
     <t xml:space="preserve">9.96981239318848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1672344207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492881774902</t>
+    <t xml:space="preserve">10.1672353744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492872238159</t>
   </si>
   <si>
     <t xml:space="preserve">10.2031297683716</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1851825714111</t>
+    <t xml:space="preserve">10.1851835250854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2838935852051</t>
@@ -3158,43 +3158,43 @@
     <t xml:space="preserve">10.5172109603882</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3467102050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3018417358398</t>
+    <t xml:space="preserve">10.3467092514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3018407821655</t>
   </si>
   <si>
     <t xml:space="preserve">10.4184989929199</t>
   </si>
   <si>
-    <t xml:space="preserve">10.436448097229</t>
+    <t xml:space="preserve">10.4364471435547</t>
   </si>
   <si>
     <t xml:space="preserve">10.7774486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8492393493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6966848373413</t>
+    <t xml:space="preserve">10.8492383956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6966857910156</t>
   </si>
   <si>
     <t xml:space="preserve">10.7684745788574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5620794296265</t>
+    <t xml:space="preserve">10.5620784759521</t>
   </si>
   <si>
     <t xml:space="preserve">10.0864715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2479982376099</t>
+    <t xml:space="preserve">10.2479991912842</t>
   </si>
   <si>
     <t xml:space="preserve">10.490288734436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5979738235474</t>
+    <t xml:space="preserve">10.5979747772217</t>
   </si>
   <si>
     <t xml:space="preserve">10.8671855926514</t>
@@ -3203,61 +3203,61 @@
     <t xml:space="preserve">11.1453714370728</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9658966064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9569225311279</t>
+    <t xml:space="preserve">10.9658975601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9569234848022</t>
   </si>
   <si>
     <t xml:space="preserve">11.082555770874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1094760894775</t>
+    <t xml:space="preserve">11.1094770431519</t>
   </si>
   <si>
     <t xml:space="preserve">11.1722927093506</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2440824508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2261362075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1902408599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4594526290894</t>
+    <t xml:space="preserve">11.2440814971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2261352539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.190239906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.459451675415</t>
   </si>
   <si>
     <t xml:space="preserve">11.6299524307251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8004541397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0068502426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6568746566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8453235626221</t>
+    <t xml:space="preserve">11.8004531860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0068492889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6568737030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8453216552734</t>
   </si>
   <si>
     <t xml:space="preserve">11.2171611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2081871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3248462677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2620315551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1363983154297</t>
+    <t xml:space="preserve">11.2081880569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3248453140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2620296478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1363964080811</t>
   </si>
   <si>
     <t xml:space="preserve">10.8223180770874</t>
@@ -3266,10 +3266,10 @@
     <t xml:space="preserve">10.3287620544434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5351581573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3736305236816</t>
+    <t xml:space="preserve">10.5351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.373631477356</t>
   </si>
   <si>
     <t xml:space="preserve">10.5441312789917</t>
@@ -3278,55 +3278,55 @@
     <t xml:space="preserve">10.7056589126587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6159219741821</t>
+    <t xml:space="preserve">10.6159210205078</t>
   </si>
   <si>
     <t xml:space="preserve">10.4095258712769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7146329879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6248960494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4005527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6069478988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44933605194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81668758392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01354026794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02251434326172</t>
+    <t xml:space="preserve">10.7146320343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6248950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4005517959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6069469451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44933700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81668853759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01354122161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0225133895874</t>
   </si>
   <si>
     <t xml:space="preserve">8.15712070465088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4891471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20198822021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3455696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5385046005249</t>
+    <t xml:space="preserve">8.48914813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20198917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34556865692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53850364685059</t>
   </si>
   <si>
     <t xml:space="preserve">8.67759609222412</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09038734436035</t>
+    <t xml:space="preserve">9.09038829803467</t>
   </si>
   <si>
     <t xml:space="preserve">8.96924209594727</t>
@@ -3335,22 +3335,22 @@
     <t xml:space="preserve">9.01859855651855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1083345413208</t>
+    <t xml:space="preserve">9.10833549499512</t>
   </si>
   <si>
     <t xml:space="preserve">9.18012523651123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13525581359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98270416259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79874134063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90642642974854</t>
+    <t xml:space="preserve">9.13525676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98270320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79874229431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90642738342285</t>
   </si>
   <si>
     <t xml:space="preserve">9.34165191650391</t>
@@ -3362,19 +3362,19 @@
     <t xml:space="preserve">9.08141422271729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97372913360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03654479980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83014965057373</t>
+    <t xml:space="preserve">8.97373008728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.036545753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83015060424805</t>
   </si>
   <si>
     <t xml:space="preserve">8.43979167938232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26480579376221</t>
+    <t xml:space="preserve">8.26480484008789</t>
   </si>
   <si>
     <t xml:space="preserve">8.36351585388184</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">8.35005569458008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36800289154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51606845855713</t>
+    <t xml:space="preserve">8.36800193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51606941223145</t>
   </si>
   <si>
     <t xml:space="preserve">8.94232082366943</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">8.4936351776123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30069828033447</t>
+    <t xml:space="preserve">8.30070018768311</t>
   </si>
   <si>
     <t xml:space="preserve">8.18404102325439</t>
@@ -3425,13 +3425,13 @@
     <t xml:space="preserve">8.25134372711182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12571334838867</t>
+    <t xml:space="preserve">8.12571239471436</t>
   </si>
   <si>
     <t xml:space="preserve">8.88399124145508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65573215484619</t>
+    <t xml:space="preserve">9.65573310852051</t>
   </si>
   <si>
     <t xml:space="preserve">9.6856861114502</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">9.5844087600708</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63044452667236</t>
+    <t xml:space="preserve">9.63044357299805</t>
   </si>
   <si>
     <t xml:space="preserve">9.87903022766113</t>
@@ -3449,13 +3449,13 @@
     <t xml:space="preserve">10.0539627075195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2104797363281</t>
+    <t xml:space="preserve">10.2104806900024</t>
   </si>
   <si>
     <t xml:space="preserve">9.95268630981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98030757904053</t>
+    <t xml:space="preserve">9.98030662536621</t>
   </si>
   <si>
     <t xml:space="preserve">10.035548210144</t>
@@ -3464,28 +3464,28 @@
     <t xml:space="preserve">9.89744472503662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0631704330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1184101104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1552391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63965129852295</t>
+    <t xml:space="preserve">10.0631694793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1184110641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1552381515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63965034484863</t>
   </si>
   <si>
     <t xml:space="preserve">9.40027141571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22533988952637</t>
+    <t xml:space="preserve">9.22533893585205</t>
   </si>
   <si>
     <t xml:space="preserve">9.44630527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87087249755859</t>
+    <t xml:space="preserve">8.87087345123291</t>
   </si>
   <si>
     <t xml:space="preserve">8.95833778381348</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">8.98595905303955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02278709411621</t>
+    <t xml:space="preserve">9.02278614044189</t>
   </si>
   <si>
     <t xml:space="preserve">9.03199481964111</t>
@@ -3503,67 +3503,67 @@
     <t xml:space="preserve">8.66832065582275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62228488922119</t>
+    <t xml:space="preserve">8.62228584289551</t>
   </si>
   <si>
     <t xml:space="preserve">8.67292404174805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77420043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73737144470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53481960296631</t>
+    <t xml:space="preserve">8.77419948577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73737239837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53482055664062</t>
   </si>
   <si>
     <t xml:space="preserve">8.52561283111572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30464649200439</t>
+    <t xml:space="preserve">8.30464744567871</t>
   </si>
   <si>
     <t xml:space="preserve">8.35988807678223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80642414093018</t>
+    <t xml:space="preserve">8.80642318725586</t>
   </si>
   <si>
     <t xml:space="preserve">9.08263206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85706233978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88928699493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82023429870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60847568511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90309715270996</t>
+    <t xml:space="preserve">8.8570613861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88928604125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82023525238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60847663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90309619903564</t>
   </si>
   <si>
     <t xml:space="preserve">9.00437259674072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06882095336914</t>
+    <t xml:space="preserve">9.06882190704346</t>
   </si>
   <si>
     <t xml:space="preserve">9.1056489944458</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14247703552246</t>
+    <t xml:space="preserve">9.14247798919678</t>
   </si>
   <si>
     <t xml:space="preserve">8.99976921081543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71895790100098</t>
+    <t xml:space="preserve">8.71895885467529</t>
   </si>
   <si>
     <t xml:space="preserve">8.86166572570801</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">9.17470073699951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47392559051514</t>
+    <t xml:space="preserve">9.47392654418945</t>
   </si>
   <si>
     <t xml:space="preserve">9.5936164855957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64885711669922</t>
+    <t xml:space="preserve">9.6488561630249</t>
   </si>
   <si>
     <t xml:space="preserve">9.77775478363037</t>
@@ -3590,22 +3590,22 @@
     <t xml:space="preserve">9.55678844451904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7593412399292</t>
+    <t xml:space="preserve">9.75934028625488</t>
   </si>
   <si>
     <t xml:space="preserve">9.73171997070312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66727066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37264919281006</t>
+    <t xml:space="preserve">9.66727161407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37265014648438</t>
   </si>
   <si>
     <t xml:space="preserve">9.53837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21613311767578</t>
+    <t xml:space="preserve">9.21613216400146</t>
   </si>
   <si>
     <t xml:space="preserve">8.84325122833252</t>
@@ -3617,16 +3617,16 @@
     <t xml:space="preserve">8.92611408233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59466457366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5624418258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57164859771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44275093078613</t>
+    <t xml:space="preserve">8.59466361999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56244087219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57164764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44274997711182</t>
   </si>
   <si>
     <t xml:space="preserve">8.38750839233398</t>
@@ -3638,46 +3638,46 @@
     <t xml:space="preserve">8.14352607727051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12511157989502</t>
+    <t xml:space="preserve">8.1251106262207</t>
   </si>
   <si>
     <t xml:space="preserve">8.23559474945068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23099136352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42433547973633</t>
+    <t xml:space="preserve">8.23099040985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42433643341064</t>
   </si>
   <si>
     <t xml:space="preserve">8.76959609985352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75578689575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7926139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51640510559082</t>
+    <t xml:space="preserve">8.75578594207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79261302947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51640605926514</t>
   </si>
   <si>
     <t xml:space="preserve">8.31385326385498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33226776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2171802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09749031066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01923274993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77985143661499</t>
+    <t xml:space="preserve">8.33226680755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21718120574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09749126434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01923179626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77985191345215</t>
   </si>
   <si>
     <t xml:space="preserve">7.88112878799438</t>
@@ -3686,13 +3686,13 @@
     <t xml:space="preserve">7.83049058914185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82588624954224</t>
+    <t xml:space="preserve">7.82588672637939</t>
   </si>
   <si>
     <t xml:space="preserve">7.4944372177124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82128286361694</t>
+    <t xml:space="preserve">7.8212833404541</t>
   </si>
   <si>
     <t xml:space="preserve">7.97319746017456</t>
@@ -3704,13 +3704,13 @@
     <t xml:space="preserve">8.2217845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34147453308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30924892425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29543972015381</t>
+    <t xml:space="preserve">8.34147548675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30924987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29544067382812</t>
   </si>
   <si>
     <t xml:space="preserve">8.68213081359863</t>
@@ -3719,37 +3719,37 @@
     <t xml:space="preserve">8.47037124633789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61307811737061</t>
+    <t xml:space="preserve">8.61307907104492</t>
   </si>
   <si>
     <t xml:space="preserve">8.66371726989746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73276805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90770053863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91690731048584</t>
+    <t xml:space="preserve">8.73276901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90769958496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91690635681152</t>
   </si>
   <si>
     <t xml:space="preserve">8.97214889526367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79721832275391</t>
+    <t xml:space="preserve">8.79721736907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.193115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54758167266846</t>
+    <t xml:space="preserve">9.54758071899414</t>
   </si>
   <si>
     <t xml:space="preserve">9.82378959655762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79616832733154</t>
+    <t xml:space="preserve">9.79616928100586</t>
   </si>
   <si>
     <t xml:space="preserve">9.74092674255371</t>
@@ -3758,13 +3758,13 @@
     <t xml:space="preserve">9.80537509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0723762512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2196865081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8641710281372</t>
+    <t xml:space="preserve">10.0723752975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.219687461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8641719818115</t>
   </si>
   <si>
     <t xml:space="preserve">10.7260675430298</t>
@@ -3776,25 +3776,25 @@
     <t xml:space="preserve">10.7444820404053</t>
   </si>
   <si>
-    <t xml:space="preserve">10.514307975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2381019592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.339376449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841358184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3209629058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1368246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1828594207764</t>
+    <t xml:space="preserve">10.5143089294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2381010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3393774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841348648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3209638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1368255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1828603744507</t>
   </si>
   <si>
     <t xml:space="preserve">10.3485841751099</t>
@@ -3821,13 +3821,13 @@
     <t xml:space="preserve">9.7501335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6580638885498</t>
+    <t xml:space="preserve">9.65806484222412</t>
   </si>
   <si>
     <t xml:space="preserve">9.60282421112061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48313236236572</t>
+    <t xml:space="preserve">9.48313331604004</t>
   </si>
   <si>
     <t xml:space="preserve">9.62123680114746</t>
@@ -3836,22 +3836,22 @@
     <t xml:space="preserve">9.8329963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1460332870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1276168823242</t>
+    <t xml:space="preserve">10.146032333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1276178359985</t>
   </si>
   <si>
     <t xml:space="preserve">10.2473087310791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4866886138916</t>
+    <t xml:space="preserve">10.4866876602173</t>
   </si>
   <si>
     <t xml:space="preserve">10.5327224731445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.772102355957</t>
+    <t xml:space="preserve">10.7721033096313</t>
   </si>
   <si>
     <t xml:space="preserve">10.6800336837769</t>
@@ -3863,10 +3863,10 @@
     <t xml:space="preserve">10.7352743148804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5695505142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6616191864014</t>
+    <t xml:space="preserve">10.5695495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6616201400757</t>
   </si>
   <si>
     <t xml:space="preserve">10.9286203384399</t>
@@ -3881,10 +3881,10 @@
     <t xml:space="preserve">11.7940711975098</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1163139343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2912454605103</t>
+    <t xml:space="preserve">12.1163129806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2912464141846</t>
   </si>
   <si>
     <t xml:space="preserve">12.3372793197632</t>
@@ -3899,19 +3899,19 @@
     <t xml:space="preserve">12.0886926651001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8585205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3188667297363</t>
+    <t xml:space="preserve">11.8585195541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.318865776062</t>
   </si>
   <si>
     <t xml:space="preserve">12.3649015426636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2820386886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2083835601807</t>
+    <t xml:space="preserve">12.2820377349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2083826065063</t>
   </si>
   <si>
     <t xml:space="preserve">12.2636241912842</t>
@@ -3920,31 +3920,31 @@
     <t xml:space="preserve">12.6779365539551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8620748519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7275257110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7367324829102</t>
+    <t xml:space="preserve">12.8620738983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7275247573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7367334365845</t>
   </si>
   <si>
     <t xml:space="preserve">13.4789390563965</t>
   </si>
   <si>
-    <t xml:space="preserve">13.129075050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5950746536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8252468109131</t>
+    <t xml:space="preserve">13.1290760040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5950736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8252477645874</t>
   </si>
   <si>
     <t xml:space="preserve">12.8896961212158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5582456588745</t>
+    <t xml:space="preserve">12.5582466125488</t>
   </si>
   <si>
     <t xml:space="preserve">12.6963500976562</t>
@@ -3956,7 +3956,7 @@
     <t xml:space="preserve">12.0058298110962</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9137601852417</t>
+    <t xml:space="preserve">11.913761138916</t>
   </si>
   <si>
     <t xml:space="preserve">12.171555519104</t>
@@ -3968,16 +3968,16 @@
     <t xml:space="preserve">12.2267961502075</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2175903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3280735015869</t>
+    <t xml:space="preserve">12.2175893783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3280725479126</t>
   </si>
   <si>
     <t xml:space="preserve">11.9966230392456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9321746826172</t>
+    <t xml:space="preserve">11.9321756362915</t>
   </si>
   <si>
     <t xml:space="preserve">12.4293489456177</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">12.2728309631348</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5674514770508</t>
+    <t xml:space="preserve">12.5674533843994</t>
   </si>
   <si>
     <t xml:space="preserve">12.503005027771</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">12.4661769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4845914840698</t>
+    <t xml:space="preserve">12.4845905303955</t>
   </si>
   <si>
     <t xml:space="preserve">12.3096590042114</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">12.024245262146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1991767883301</t>
+    <t xml:space="preserve">12.1991758346558</t>
   </si>
   <si>
     <t xml:space="preserve">12.2544183731079</t>
@@ -4019,28 +4019,28 @@
     <t xml:space="preserve">13.0738334655762</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2855930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2579727172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1751108169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2119379043579</t>
+    <t xml:space="preserve">13.2855939865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2579717636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1751098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2119388580322</t>
   </si>
   <si>
     <t xml:space="preserve">13.1659030914307</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3040065765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2947988510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3417444229126</t>
+    <t xml:space="preserve">13.3040075302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2947998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3417453765869</t>
   </si>
   <si>
     <t xml:space="preserve">13.1821327209473</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">13.2854108810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3323554992676</t>
+    <t xml:space="preserve">13.3323564529419</t>
   </si>
   <si>
     <t xml:space="preserve">13.3511343002319</t>
@@ -4076,19 +4076,19 @@
     <t xml:space="preserve">13.4168567657471</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4544124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4919691085815</t>
+    <t xml:space="preserve">13.4544134140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4919681549072</t>
   </si>
   <si>
     <t xml:space="preserve">13.6140260696411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9895839691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9614181518555</t>
+    <t xml:space="preserve">13.9895849227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9614171981812</t>
   </si>
   <si>
     <t xml:space="preserve">13.7548599243164</t>
@@ -4100,13 +4100,13 @@
     <t xml:space="preserve">13.5952472686768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5201358795166</t>
+    <t xml:space="preserve">13.5201349258423</t>
   </si>
   <si>
     <t xml:space="preserve">12.703293800354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3840675354004</t>
+    <t xml:space="preserve">12.3840684890747</t>
   </si>
   <si>
     <t xml:space="preserve">12.3652906417847</t>
@@ -4121,19 +4121,19 @@
     <t xml:space="preserve">12.5061254501343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6000146865845</t>
+    <t xml:space="preserve">12.6000156402588</t>
   </si>
   <si>
     <t xml:space="preserve">12.7502393722534</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6469602584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6281824111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5249042510986</t>
+    <t xml:space="preserve">12.6469612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6281814575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5249032974243</t>
   </si>
   <si>
     <t xml:space="preserve">12.5342931747437</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">12.2526226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4028472900391</t>
+    <t xml:space="preserve">12.4028463363647</t>
   </si>
   <si>
     <t xml:space="preserve">12.3277349472046</t>
@@ -4166,19 +4166,19 @@
     <t xml:space="preserve">12.5155143737793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4310131072998</t>
+    <t xml:space="preserve">12.4310140609741</t>
   </si>
   <si>
     <t xml:space="preserve">12.1211767196655</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0836219787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4122362136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0930109024048</t>
+    <t xml:space="preserve">12.0836210250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4122352600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0930099487305</t>
   </si>
   <si>
     <t xml:space="preserve">12.2338447570801</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">12.0648441314697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.205677986145</t>
+    <t xml:space="preserve">12.2056789398193</t>
   </si>
   <si>
     <t xml:space="preserve">11.9991207122803</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">11.9240083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7268390655518</t>
+    <t xml:space="preserve">11.7268400192261</t>
   </si>
   <si>
     <t xml:space="preserve">11.9146194458008</t>
@@ -4223,7 +4223,7 @@
     <t xml:space="preserve">11.9897317886353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554542541504</t>
+    <t xml:space="preserve">12.0554552078247</t>
   </si>
   <si>
     <t xml:space="preserve">12.0460653305054</t>
@@ -4232,10 +4232,10 @@
     <t xml:space="preserve">12.0742321014404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9709539413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8770637512207</t>
+    <t xml:space="preserve">11.9709529876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8770627975464</t>
   </si>
   <si>
     <t xml:space="preserve">11.7737846374512</t>
@@ -4262,13 +4262,13 @@
     <t xml:space="preserve">11.4545593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.510892868042</t>
+    <t xml:space="preserve">11.5108938217163</t>
   </si>
   <si>
     <t xml:space="preserve">11.670506477356</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4076137542725</t>
+    <t xml:space="preserve">11.4076147079468</t>
   </si>
   <si>
     <t xml:space="preserve">11.3606700897217</t>
@@ -4295,10 +4295,10 @@
     <t xml:space="preserve">10.8254976272583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7785530090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6001615524292</t>
+    <t xml:space="preserve">10.7785520553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6001625061035</t>
   </si>
   <si>
     <t xml:space="preserve">10.7034406661987</t>
@@ -4310,10 +4310,10 @@
     <t xml:space="preserve">10.7503852844238</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7222185134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6471071243286</t>
+    <t xml:space="preserve">10.7222194671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6471061706543</t>
   </si>
   <si>
     <t xml:space="preserve">10.31849193573</t>
@@ -4337,7 +4337,7 @@
     <t xml:space="preserve">9.68004131317139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68943119049072</t>
+    <t xml:space="preserve">9.68943023681641</t>
   </si>
   <si>
     <t xml:space="preserve">9.71759796142578</t>
@@ -4376,7 +4376,7 @@
     <t xml:space="preserve">9.94293308258057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85843181610107</t>
+    <t xml:space="preserve">9.85843276977539</t>
   </si>
   <si>
     <t xml:space="preserve">10.1776580810547</t>
@@ -4388,7 +4388,7 @@
     <t xml:space="preserve">10.018045425415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0649900436401</t>
+    <t xml:space="preserve">10.0649909973145</t>
   </si>
   <si>
     <t xml:space="preserve">9.89598751068115</t>
@@ -4406,10 +4406,10 @@
     <t xml:space="preserve">10.2527694702148</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1307134628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2809362411499</t>
+    <t xml:space="preserve">10.1307125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2809371948242</t>
   </si>
   <si>
     <t xml:space="preserve">10.1964349746704</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">10.3560485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5062713623047</t>
+    <t xml:space="preserve">10.506272315979</t>
   </si>
   <si>
     <t xml:space="preserve">10.4029932022095</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">9.97109985351562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.487494468689</t>
+    <t xml:space="preserve">10.4874935150146</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405498504639</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">10.6658849716187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5719957351685</t>
+    <t xml:space="preserve">10.5719947814941</t>
   </si>
   <si>
     <t xml:space="preserve">10.4499387741089</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">10.309103012085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2621593475342</t>
+    <t xml:space="preserve">10.2621583938599</t>
   </si>
   <si>
     <t xml:space="preserve">10.1870470046997</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">10.1401023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058238983154</t>
+    <t xml:space="preserve">10.2058248519897</t>
   </si>
   <si>
     <t xml:space="preserve">10.6095514297485</t>
@@ -4496,10 +4496,10 @@
     <t xml:space="preserve">10.7409963607788</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9099988937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7316074371338</t>
+    <t xml:space="preserve">10.9099979400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7316083908081</t>
   </si>
   <si>
     <t xml:space="preserve">10.8912210464478</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">10.7128295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7879419326782</t>
+    <t xml:space="preserve">10.7879409790039</t>
   </si>
   <si>
     <t xml:space="preserve">10.9287767410278</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">11.0602216720581</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0038890838623</t>
+    <t xml:space="preserve">11.003888130188</t>
   </si>
   <si>
     <t xml:space="preserve">10.8818321228027</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">11.1728897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2949457168579</t>
+    <t xml:space="preserve">11.2949466705322</t>
   </si>
   <si>
     <t xml:space="preserve">11.1447229385376</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">11.0508337020874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2480010986328</t>
+    <t xml:space="preserve">11.2480020523071</t>
   </si>
   <si>
     <t xml:space="preserve">11.3982257843018</t>
@@ -4589,16 +4589,16 @@
     <t xml:space="preserve">11.3418912887573</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1259460449219</t>
+    <t xml:space="preserve">11.1259450912476</t>
   </si>
   <si>
     <t xml:space="preserve">11.2386131286621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9757204055786</t>
+    <t xml:space="preserve">11.2292232513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9757213592529</t>
   </si>
   <si>
     <t xml:space="preserve">11.6104164123535</t>
@@ -4619,10 +4619,10 @@
     <t xml:space="preserve">11.4094924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3249912261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1090440750122</t>
+    <t xml:space="preserve">11.3249921798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1090450286865</t>
   </si>
   <si>
     <t xml:space="preserve">10.4705944061279</t>
@@ -4634,7 +4634,7 @@
     <t xml:space="preserve">10.4536933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3691930770874</t>
+    <t xml:space="preserve">10.3691921234131</t>
   </si>
   <si>
     <t xml:space="preserve">10.4799823760986</t>
@@ -9796,7 +9796,7 @@
         <v>10.1195363998413</v>
       </c>
       <c r="G146" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -9822,7 +9822,7 @@
         <v>10.2294216156006</v>
       </c>
       <c r="G147" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -9848,7 +9848,7 @@
         <v>10.0595979690552</v>
       </c>
       <c r="G148" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -9874,7 +9874,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G149" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -9900,7 +9900,7 @@
         <v>10.5490922927856</v>
       </c>
       <c r="G150" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -9952,7 +9952,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G152" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -9978,7 +9978,7 @@
         <v>10.2893600463867</v>
       </c>
       <c r="G153" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -10004,7 +10004,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G154" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -10030,7 +10030,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G155" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -10056,7 +10056,7 @@
         <v>10.5091333389282</v>
       </c>
       <c r="G156" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -10082,7 +10082,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G157" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -10108,7 +10108,7 @@
         <v>10.5191230773926</v>
       </c>
       <c r="G158" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -10134,7 +10134,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G159" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -10186,7 +10186,7 @@
         <v>10.2094430923462</v>
       </c>
       <c r="G161" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -10212,7 +10212,7 @@
         <v>10.1594953536987</v>
       </c>
       <c r="G162" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -10238,7 +10238,7 @@
         <v>10.1994533538818</v>
       </c>
       <c r="G163" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -10264,7 +10264,7 @@
         <v>10.1095457077026</v>
       </c>
       <c r="G164" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -10290,7 +10290,7 @@
         <v>10.1395149230957</v>
       </c>
       <c r="G165" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -10316,7 +10316,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G166" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -10342,7 +10342,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G167" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -10368,7 +10368,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G168" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -10420,7 +10420,7 @@
         <v>10.4092359542847</v>
       </c>
       <c r="G170" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -10446,7 +10446,7 @@
         <v>10.4591846466064</v>
       </c>
       <c r="G171" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -10472,7 +10472,7 @@
         <v>10.4591846466064</v>
       </c>
       <c r="G172" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -10498,7 +10498,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G173" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -10524,7 +10524,7 @@
         <v>10.4791641235352</v>
       </c>
       <c r="G174" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -10576,7 +10576,7 @@
         <v>10.6989374160767</v>
       </c>
       <c r="G176" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -10602,7 +10602,7 @@
         <v>10.6389989852905</v>
       </c>
       <c r="G177" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -10706,7 +10706,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G181" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -10784,7 +10784,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G184" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -10862,7 +10862,7 @@
         <v>10.688946723938</v>
       </c>
       <c r="G187" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -10888,7 +10888,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G188" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -10914,7 +10914,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G189" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -10940,7 +10940,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G190" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -10992,7 +10992,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G192" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -11018,7 +11018,7 @@
         <v>10.6090297698975</v>
       </c>
       <c r="G193" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -11044,7 +11044,7 @@
         <v>10.7089262008667</v>
       </c>
       <c r="G194" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -11070,7 +11070,7 @@
         <v>10.8887405395508</v>
       </c>
       <c r="G195" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -11096,7 +11096,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G196" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -11122,7 +11122,7 @@
         <v>10.5990400314331</v>
       </c>
       <c r="G197" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -11148,7 +11148,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G198" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -11174,7 +11174,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G199" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -11200,7 +11200,7 @@
         <v>10.3792667388916</v>
       </c>
       <c r="G200" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -11278,7 +11278,7 @@
         <v>10.4691743850708</v>
       </c>
       <c r="G203" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -11304,7 +11304,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G204" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -11330,7 +11330,7 @@
         <v>10.5091333389282</v>
       </c>
       <c r="G205" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -11356,7 +11356,7 @@
         <v>10.6090297698975</v>
       </c>
       <c r="G206" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -11382,7 +11382,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G207" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -11408,7 +11408,7 @@
         <v>10.5291118621826</v>
       </c>
       <c r="G208" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -11434,7 +11434,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G209" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -11486,7 +11486,7 @@
         <v>10.8787508010864</v>
       </c>
       <c r="G211" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -11512,7 +11512,7 @@
         <v>10.9986267089844</v>
       </c>
       <c r="G212" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -11538,7 +11538,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G213" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -11564,7 +11564,7 @@
         <v>11.2483692169189</v>
       </c>
       <c r="G214" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -11590,7 +11590,7 @@
         <v>11.258358001709</v>
       </c>
       <c r="G215" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -11616,7 +11616,7 @@
         <v>11.008617401123</v>
       </c>
       <c r="G216" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -11642,7 +11642,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G217" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -11668,7 +11668,7 @@
         <v>10.5590810775757</v>
       </c>
       <c r="G218" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -11694,7 +11694,7 @@
         <v>11.0585651397705</v>
       </c>
       <c r="G219" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -11720,7 +11720,7 @@
         <v>11.3682451248169</v>
       </c>
       <c r="G220" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -11746,7 +11746,7 @@
         <v>11.0385856628418</v>
       </c>
       <c r="G221" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -11772,7 +11772,7 @@
         <v>10.828803062439</v>
       </c>
       <c r="G222" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -11798,7 +11798,7 @@
         <v>10.98863697052</v>
       </c>
       <c r="G223" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -11824,7 +11824,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G224" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -11850,7 +11850,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G225" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -11876,7 +11876,7 @@
         <v>10.7289056777954</v>
       </c>
       <c r="G226" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11902,7 +11902,7 @@
         <v>10.6389989852905</v>
       </c>
       <c r="G227" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -11928,7 +11928,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G228" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -11980,7 +11980,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G230" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -12006,7 +12006,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G231" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -12032,7 +12032,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G232" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -12058,7 +12058,7 @@
         <v>10.838791847229</v>
       </c>
       <c r="G233" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -12110,7 +12110,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G235" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -12136,7 +12136,7 @@
         <v>10.8088226318359</v>
       </c>
       <c r="G236" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -12162,7 +12162,7 @@
         <v>10.7089262008667</v>
       </c>
       <c r="G237" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -12188,7 +12188,7 @@
         <v>10.539101600647</v>
       </c>
       <c r="G238" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -12214,7 +12214,7 @@
         <v>10.5590810775757</v>
       </c>
       <c r="G239" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -12266,7 +12266,7 @@
         <v>10.9686584472656</v>
       </c>
       <c r="G241" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -12292,7 +12292,7 @@
         <v>11.0985240936279</v>
       </c>
       <c r="G242" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -12318,7 +12318,7 @@
         <v>10.9686584472656</v>
       </c>
       <c r="G243" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -12344,7 +12344,7 @@
         <v>10.828803062439</v>
       </c>
       <c r="G244" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -12370,7 +12370,7 @@
         <v>11.008617401123</v>
       </c>
       <c r="G245" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -12396,7 +12396,7 @@
         <v>10.8887405395508</v>
       </c>
       <c r="G246" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -12422,7 +12422,7 @@
         <v>10.98863697052</v>
       </c>
       <c r="G247" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -12448,7 +12448,7 @@
         <v>10.8088226318359</v>
       </c>
       <c r="G248" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -12474,7 +12474,7 @@
         <v>10.7289056777954</v>
       </c>
       <c r="G249" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -12500,7 +12500,7 @@
         <v>10.7688636779785</v>
       </c>
       <c r="G250" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -12526,7 +12526,7 @@
         <v>10.9087200164795</v>
       </c>
       <c r="G251" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -12552,7 +12552,7 @@
         <v>10.9187097549438</v>
       </c>
       <c r="G252" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -12578,7 +12578,7 @@
         <v>11.0685548782349</v>
       </c>
       <c r="G253" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -12604,7 +12604,7 @@
         <v>11.2084102630615</v>
       </c>
       <c r="G254" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -12630,7 +12630,7 @@
         <v>11.2683477401733</v>
       </c>
       <c r="G255" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -12656,7 +12656,7 @@
         <v>11.4181928634644</v>
       </c>
       <c r="G256" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -12682,7 +12682,7 @@
         <v>11.4881210327148</v>
       </c>
       <c r="G257" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -12708,7 +12708,7 @@
         <v>11.9876041412354</v>
       </c>
       <c r="G258" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -12734,7 +12734,7 @@
         <v>12.0575323104858</v>
       </c>
       <c r="G259" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -12760,7 +12760,7 @@
         <v>11.8177795410156</v>
       </c>
       <c r="G260" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -12786,7 +12786,7 @@
         <v>11.9576349258423</v>
       </c>
       <c r="G261" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -12812,7 +12812,7 @@
         <v>12.0075836181641</v>
       </c>
       <c r="G262" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -12838,7 +12838,7 @@
         <v>12.0375528335571</v>
       </c>
       <c r="G263" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -12864,7 +12864,7 @@
         <v>12.0974912643433</v>
       </c>
       <c r="G264" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -12890,7 +12890,7 @@
         <v>12.277304649353</v>
       </c>
       <c r="G265" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12916,7 +12916,7 @@
         <v>12.0575323104858</v>
       </c>
       <c r="G266" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -12942,7 +12942,7 @@
         <v>12.3072738647461</v>
       </c>
       <c r="G267" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -12968,7 +12968,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G268" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -12994,7 +12994,7 @@
         <v>12.2673149108887</v>
       </c>
       <c r="G269" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -13020,7 +13020,7 @@
         <v>12.2173671722412</v>
       </c>
       <c r="G270" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -13046,7 +13046,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G271" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -13072,7 +13072,7 @@
         <v>12.1774082183838</v>
       </c>
       <c r="G272" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -13098,7 +13098,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G273" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -13124,7 +13124,7 @@
         <v>12.2073774337769</v>
       </c>
       <c r="G274" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -13150,7 +13150,7 @@
         <v>12.2972841262817</v>
       </c>
       <c r="G275" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -13176,7 +13176,7 @@
         <v>12.1873979568481</v>
       </c>
       <c r="G276" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -13202,7 +13202,7 @@
         <v>12.1474390029907</v>
       </c>
       <c r="G277" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -13228,7 +13228,7 @@
         <v>11.9876041412354</v>
       </c>
       <c r="G278" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -13254,7 +13254,7 @@
         <v>11.8477487564087</v>
       </c>
       <c r="G279" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -13280,7 +13280,7 @@
         <v>12.2173671722412</v>
       </c>
       <c r="G280" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -13306,7 +13306,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G281" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -13332,7 +13332,7 @@
         <v>12.4071702957153</v>
       </c>
       <c r="G282" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -13358,7 +13358,7 @@
         <v>12.127459526062</v>
       </c>
       <c r="G283" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -13384,7 +13384,7 @@
         <v>12.1174697875977</v>
       </c>
       <c r="G284" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -13410,7 +13410,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G285" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -13436,7 +13436,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G286" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -13462,7 +13462,7 @@
         <v>12.4071702957153</v>
       </c>
       <c r="G287" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -13488,7 +13488,7 @@
         <v>12.6669015884399</v>
       </c>
       <c r="G288" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -13514,7 +13514,7 @@
         <v>12.5670051574707</v>
       </c>
       <c r="G289" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -13540,7 +13540,7 @@
         <v>12.6569118499756</v>
       </c>
       <c r="G290" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -13566,7 +13566,7 @@
         <v>12.5670051574707</v>
       </c>
       <c r="G291" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -13592,7 +13592,7 @@
         <v>12.4970779418945</v>
       </c>
       <c r="G292" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -13618,7 +13618,7 @@
         <v>12.5969743728638</v>
       </c>
       <c r="G293" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -13644,7 +13644,7 @@
         <v>12.8567056655884</v>
       </c>
       <c r="G294" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -13670,7 +13670,7 @@
         <v>12.8966636657715</v>
       </c>
       <c r="G295" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -13696,7 +13696,7 @@
         <v>12.816746711731</v>
       </c>
       <c r="G296" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -13722,7 +13722,7 @@
         <v>12.5170574188232</v>
       </c>
       <c r="G297" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -13748,7 +13748,7 @@
         <v>12.8067569732666</v>
       </c>
       <c r="G298" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -13774,7 +13774,7 @@
         <v>12.6669015884399</v>
       </c>
       <c r="G299" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -13800,7 +13800,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G300" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -13826,7 +13826,7 @@
         <v>13.1863651275635</v>
       </c>
       <c r="G301" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13852,7 +13852,7 @@
         <v>13.1464061737061</v>
       </c>
       <c r="G302" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -13878,7 +13878,7 @@
         <v>12.9566020965576</v>
       </c>
       <c r="G303" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13904,7 +13904,7 @@
         <v>12.966591835022</v>
       </c>
       <c r="G304" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -13930,7 +13930,7 @@
         <v>13.0764780044556</v>
       </c>
       <c r="G305" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -13956,7 +13956,7 @@
         <v>12.9765815734863</v>
       </c>
       <c r="G306" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -13982,7 +13982,7 @@
         <v>12.9765815734863</v>
       </c>
       <c r="G307" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -14008,7 +14008,7 @@
         <v>13.1863651275635</v>
       </c>
       <c r="G308" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -14034,7 +14034,7 @@
         <v>13.2762718200684</v>
       </c>
       <c r="G309" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -14060,7 +14060,7 @@
         <v>13.1064472198486</v>
       </c>
       <c r="G310" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -14086,7 +14086,7 @@
         <v>13.2862615585327</v>
       </c>
       <c r="G311" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -14112,7 +14112,7 @@
         <v>13.536003112793</v>
       </c>
       <c r="G312" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -14138,7 +14138,7 @@
         <v>13.4460964202881</v>
       </c>
       <c r="G313" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -14164,7 +14164,7 @@
         <v>13.5060338973999</v>
       </c>
       <c r="G314" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -14190,7 +14190,7 @@
         <v>13.5459928512573</v>
       </c>
       <c r="G315" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -14216,7 +14216,7 @@
         <v>13.5759620666504</v>
       </c>
       <c r="G316" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -14242,7 +14242,7 @@
         <v>13.6458902359009</v>
       </c>
       <c r="G317" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -14268,7 +14268,7 @@
         <v>13.7058277130127</v>
       </c>
       <c r="G318" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -14294,7 +14294,7 @@
         <v>13.7757549285889</v>
       </c>
       <c r="G319" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -14320,7 +14320,7 @@
         <v>13.8456830978394</v>
       </c>
       <c r="G320" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -14346,7 +14346,7 @@
         <v>13.835693359375</v>
       </c>
       <c r="G321" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -14372,7 +14372,7 @@
         <v>13.8556728363037</v>
       </c>
       <c r="G322" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -14398,7 +14398,7 @@
         <v>14.1253938674927</v>
       </c>
       <c r="G323" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -14424,7 +14424,7 @@
         <v>14.1453733444214</v>
       </c>
       <c r="G324" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -14450,7 +14450,7 @@
         <v>14.1253938674927</v>
       </c>
       <c r="G325" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -14476,7 +14476,7 @@
         <v>14.1253938674927</v>
       </c>
       <c r="G326" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -14502,7 +14502,7 @@
         <v>14.0654563903809</v>
       </c>
       <c r="G327" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -14528,7 +14528,7 @@
         <v>14.0554656982422</v>
       </c>
       <c r="G328" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -14554,7 +14554,7 @@
         <v>14.1054153442383</v>
       </c>
       <c r="G329" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -14580,7 +14580,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G330" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -14606,7 +14606,7 @@
         <v>14.0954246520996</v>
       </c>
       <c r="G331" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -14632,7 +14632,7 @@
         <v>13.7757549285889</v>
       </c>
       <c r="G332" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -14658,7 +14658,7 @@
         <v>13.9455795288086</v>
       </c>
       <c r="G333" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -14684,7 +14684,7 @@
         <v>14.0754451751709</v>
       </c>
       <c r="G334" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -14710,7 +14710,7 @@
         <v>13.8856420516968</v>
       </c>
       <c r="G335" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -14736,7 +14736,7 @@
         <v>14.3851251602173</v>
       </c>
       <c r="G336" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -14762,7 +14762,7 @@
         <v>14.5050010681152</v>
       </c>
       <c r="G337" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -14788,7 +14788,7 @@
         <v>14.3351774215698</v>
       </c>
       <c r="G338" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -14814,7 +14814,7 @@
         <v>14.4250841140747</v>
       </c>
       <c r="G339" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -14840,7 +14840,7 @@
         <v>14.4150943756104</v>
       </c>
       <c r="G340" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -14866,7 +14866,7 @@
         <v>14.6148881912231</v>
       </c>
       <c r="G341" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -14892,7 +14892,7 @@
         <v>14.4950122833252</v>
       </c>
       <c r="G342" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -14918,7 +14918,7 @@
         <v>14.7847118377686</v>
       </c>
       <c r="G343" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -14944,7 +14944,7 @@
         <v>14.9045877456665</v>
       </c>
       <c r="G344" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -14970,7 +14970,7 @@
         <v>14.8146810531616</v>
       </c>
       <c r="G345" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -14996,7 +14996,7 @@
         <v>15.0444440841675</v>
       </c>
       <c r="G346" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -15022,7 +15022,7 @@
         <v>15.0844020843506</v>
       </c>
       <c r="G347" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -15048,7 +15048,7 @@
         <v>14.7647333145142</v>
       </c>
       <c r="G348" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -15074,7 +15074,7 @@
         <v>14.6648359298706</v>
       </c>
       <c r="G349" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -15100,7 +15100,7 @@
         <v>14.674825668335</v>
       </c>
       <c r="G350" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -15126,7 +15126,7 @@
         <v>14.5349702835083</v>
       </c>
       <c r="G351" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -15152,7 +15152,7 @@
         <v>14.0055179595947</v>
       </c>
       <c r="G352" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -15178,7 +15178,7 @@
         <v>13.8956308364868</v>
       </c>
       <c r="G353" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -15204,7 +15204,7 @@
         <v>14.2053108215332</v>
       </c>
       <c r="G354" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -15230,7 +15230,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G355" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -15256,7 +15256,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G356" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -15282,7 +15282,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G357" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -15308,7 +15308,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G358" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -15334,7 +15334,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G359" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -15360,7 +15360,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G360" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -15386,7 +15386,7 @@
         <v>14.4250841140747</v>
       </c>
       <c r="G361" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -15412,7 +15412,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G362" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -15438,7 +15438,7 @@
         <v>13.9755487442017</v>
       </c>
       <c r="G363" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -15464,7 +15464,7 @@
         <v>13.8257036209106</v>
       </c>
       <c r="G364" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -15490,7 +15490,7 @@
         <v>14.0055179595947</v>
       </c>
       <c r="G365" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -17440,7 +17440,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G440" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -17648,7 +17648,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G448" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -17674,7 +17674,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G449" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -17726,7 +17726,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G451" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -18116,7 +18116,7 @@
         <v>13.8257036209106</v>
       </c>
       <c r="G466" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -27814,7 +27814,7 @@
         <v>11.5680379867554</v>
       </c>
       <c r="G839" t="s">
-        <v>621</v>
+        <v>439</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -27866,7 +27866,7 @@
         <v>11.8677282333374</v>
       </c>
       <c r="G841" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -28048,7 +28048,7 @@
         <v>11.4181928634644</v>
       </c>
       <c r="G848" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -28100,7 +28100,7 @@
         <v>11.1984195709229</v>
       </c>
       <c r="G850" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -28152,7 +28152,7 @@
         <v>11.0685548782349</v>
       </c>
       <c r="G852" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -28230,7 +28230,7 @@
         <v>10.3193292617798</v>
       </c>
       <c r="G855" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -28256,7 +28256,7 @@
         <v>10.419225692749</v>
       </c>
       <c r="G856" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -28282,7 +28282,7 @@
         <v>10.2893600463867</v>
       </c>
       <c r="G857" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -28334,7 +28334,7 @@
         <v>9.97468566894531</v>
       </c>
       <c r="G859" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -28360,7 +28360,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G860" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -28386,7 +28386,7 @@
         <v>9.9547061920166</v>
       </c>
       <c r="G861" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28412,7 +28412,7 @@
         <v>9.59008312225342</v>
       </c>
       <c r="G862" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -28438,7 +28438,7 @@
         <v>9.71994876861572</v>
       </c>
       <c r="G863" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28464,7 +28464,7 @@
         <v>9.7698974609375</v>
       </c>
       <c r="G864" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28490,7 +28490,7 @@
         <v>9.77988719940186</v>
       </c>
       <c r="G865" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28516,7 +28516,7 @@
         <v>9.65002059936523</v>
       </c>
       <c r="G866" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28542,7 +28542,7 @@
         <v>9.73992824554443</v>
       </c>
       <c r="G867" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28568,7 +28568,7 @@
         <v>9.60007286071777</v>
       </c>
       <c r="G868" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28594,7 +28594,7 @@
         <v>9.32036209106445</v>
       </c>
       <c r="G869" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28620,7 +28620,7 @@
         <v>9.54013538360596</v>
       </c>
       <c r="G870" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28646,7 +28646,7 @@
         <v>9.75990772247314</v>
       </c>
       <c r="G871" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28672,7 +28672,7 @@
         <v>9.88477897644043</v>
       </c>
       <c r="G872" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28698,7 +28698,7 @@
         <v>9.8647985458374</v>
       </c>
       <c r="G873" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -28724,7 +28724,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G874" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28750,7 +28750,7 @@
         <v>10.1295261383057</v>
       </c>
       <c r="G875" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28776,7 +28776,7 @@
         <v>9.96969127655029</v>
       </c>
       <c r="G876" t="s">
-        <v>547</v>
+        <v>644</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -28854,7 +28854,7 @@
         <v>9.8647985458374</v>
       </c>
       <c r="G879" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -29036,7 +29036,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G886" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -29062,7 +29062,7 @@
         <v>9.97468566894531</v>
       </c>
       <c r="G887" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -29374,7 +29374,7 @@
         <v>9.96969127655029</v>
       </c>
       <c r="G899" t="s">
-        <v>547</v>
+        <v>644</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29400,7 +29400,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G900" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29634,7 +29634,7 @@
         <v>9.73992824554443</v>
       </c>
       <c r="G909" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -30492,7 +30492,7 @@
         <v>9.65002059936523</v>
       </c>
       <c r="G942" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -38110,7 +38110,7 @@
         <v>9.54013538360596</v>
       </c>
       <c r="G1235" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -71268,7 +71268,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.6910763889</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>213216</v>
@@ -71289,6 +71289,32 @@
         <v>1885</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.6912152778</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>492943</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>9.67000007629395</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>9.28499984741211</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>9.67000007629395</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>9.34500026702881</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>1833</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16937828063965</t>
+    <t xml:space="preserve">7.16937875747681</t>
   </si>
   <si>
     <t xml:space="preserve">BRE.MI</t>
@@ -47,34 +47,34 @@
     <t xml:space="preserve">7.13994884490967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92740106582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52519702911377</t>
+    <t xml:space="preserve">6.92740154266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52519798278809</t>
   </si>
   <si>
     <t xml:space="preserve">6.54154682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42873334884644</t>
+    <t xml:space="preserve">6.42873382568359</t>
   </si>
   <si>
     <t xml:space="preserve">6.60040712356567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78188848495483</t>
+    <t xml:space="preserve">6.78188800811768</t>
   </si>
   <si>
     <t xml:space="preserve">6.55135679244995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21291542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19820165634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27504587173462</t>
+    <t xml:space="preserve">6.21291589736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19820213317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27504539489746</t>
   </si>
   <si>
     <t xml:space="preserve">5.94641494750977</t>
@@ -89,22 +89,22 @@
     <t xml:space="preserve">6.30610942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31918907165527</t>
+    <t xml:space="preserve">6.31919002532959</t>
   </si>
   <si>
     <t xml:space="preserve">6.38785839080811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23090028762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16713714599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05922746658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99219465255737</t>
+    <t xml:space="preserve">6.23090076446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16713666915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05922842025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99219417572021</t>
   </si>
   <si>
     <t xml:space="preserve">5.86466598510742</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">5.35945796966553</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5164155960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72242259979248</t>
+    <t xml:space="preserve">5.51641511917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72242212295532</t>
   </si>
   <si>
     <t xml:space="preserve">5.67500877380371</t>
@@ -131,19 +131,19 @@
     <t xml:space="preserve">6.03960800170898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97420978546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11972284317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14097738265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10010290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23744010925293</t>
+    <t xml:space="preserve">5.97420930862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11972236633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14097690582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10010242462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23744058609009</t>
   </si>
   <si>
     <t xml:space="preserve">6.11154747009277</t>
@@ -152,19 +152,19 @@
     <t xml:space="preserve">5.9758448600769</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07394361495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12953329086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2194561958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35188961029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32409620285034</t>
+    <t xml:space="preserve">6.07394313812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12953281402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21945571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35189056396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32409524917603</t>
   </si>
   <si>
     <t xml:space="preserve">7.04675579071045</t>
@@ -173,25 +173,25 @@
     <t xml:space="preserve">7.08272504806519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11705923080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07945394515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1203293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07128000259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06637382507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16120338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14321947097778</t>
+    <t xml:space="preserve">7.11705875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07945489883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12032890319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07127952575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06637477874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16120386123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14321851730347</t>
   </si>
   <si>
     <t xml:space="preserve">7.24949216842651</t>
@@ -209,16 +209,16 @@
     <t xml:space="preserve">7.2691125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15302801132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15139389038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31489181518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43097448348999</t>
+    <t xml:space="preserve">7.15302753448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1513934135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31489229202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43097591400146</t>
   </si>
   <si>
     <t xml:space="preserve">7.40317964553833</t>
@@ -227,49 +227,49 @@
     <t xml:space="preserve">7.35576486587524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14485502243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18899822235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16283893585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27401733398438</t>
+    <t xml:space="preserve">7.1448540687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18899869918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16283941268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27401638031006</t>
   </si>
   <si>
     <t xml:space="preserve">7.30998611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35740089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4064507484436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4227991104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39337158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43915033340454</t>
+    <t xml:space="preserve">7.35740041732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40644979476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42280054092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39337062835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43914985656738</t>
   </si>
   <si>
     <t xml:space="preserve">7.47184896469116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51108837127686</t>
+    <t xml:space="preserve">7.51108932495117</t>
   </si>
   <si>
     <t xml:space="preserve">7.76778078079224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71546173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63534688949585</t>
+    <t xml:space="preserve">7.71546220779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63534593582153</t>
   </si>
   <si>
     <t xml:space="preserve">7.68276214599609</t>
@@ -281,22 +281,22 @@
     <t xml:space="preserve">7.66968250274658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7220025062561</t>
+    <t xml:space="preserve">7.72199869155884</t>
   </si>
   <si>
     <t xml:space="preserve">7.63044166564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71055698394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85606908798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47736072540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50188446044922</t>
+    <t xml:space="preserve">7.7105565071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85606813430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47736167907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50188541412354</t>
   </si>
   <si>
     <t xml:space="preserve">8.51006126403809</t>
@@ -305,16 +305,16 @@
     <t xml:space="preserve">8.55093479156494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42831134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36291122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.354736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41196346282959</t>
+    <t xml:space="preserve">8.42831039428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36291217803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35473823547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41196250915527</t>
   </si>
   <si>
     <t xml:space="preserve">8.5199146270752</t>
@@ -323,43 +323,43 @@
     <t xml:space="preserve">8.45348167419434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51161098480225</t>
+    <t xml:space="preserve">8.51161193847656</t>
   </si>
   <si>
     <t xml:space="preserve">8.4617862701416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47009086608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6112585067749</t>
+    <t xml:space="preserve">8.47008991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61125755310059</t>
   </si>
   <si>
     <t xml:space="preserve">8.63617038726807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72751426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96002769470215</t>
+    <t xml:space="preserve">8.72751331329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96002674102783</t>
   </si>
   <si>
     <t xml:space="preserve">8.86868286132812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86038017272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58634662628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27577590942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10969734191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30401039123535</t>
+    <t xml:space="preserve">8.86037921905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58634567260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27577495574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10969638824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3040075302124</t>
   </si>
   <si>
     <t xml:space="preserve">8.3123140335083</t>
@@ -368,22 +368,22 @@
     <t xml:space="preserve">8.60295391082764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61956119537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56973743438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71921062469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25916957855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64135122299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25418663024902</t>
+    <t xml:space="preserve">8.61956214904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56973838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71921157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25916862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64134931564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25418567657471</t>
   </si>
   <si>
     <t xml:space="preserve">8.0598726272583</t>
@@ -395,43 +395,43 @@
     <t xml:space="preserve">8.23757839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84728813171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6795482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67788791656494</t>
+    <t xml:space="preserve">7.84728956222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67954874038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67788743972778</t>
   </si>
   <si>
     <t xml:space="preserve">7.95524120330811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02831554412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05488872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97849416732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14457321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11301708221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23425579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10471248626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21100521087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16782379150391</t>
+    <t xml:space="preserve">8.02831745147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05488967895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97849225997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14457225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11301612854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23425674438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10471439361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21100425720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16782283782959</t>
   </si>
   <si>
     <t xml:space="preserve">8.32061958312988</t>
@@ -440,55 +440,55 @@
     <t xml:space="preserve">8.37044239044189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50330638885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36213684082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67769050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76903533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53652095794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55312919616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64447402954102</t>
+    <t xml:space="preserve">8.50330543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36213779449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67768955230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76903438568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53652191162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55313014984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64447498321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.73581886291504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68599319458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74412250518799</t>
+    <t xml:space="preserve">8.68599605560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7441234588623</t>
   </si>
   <si>
     <t xml:space="preserve">8.6693868637085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48669719696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44517993927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47839546203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40365886688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42856884002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65277767181396</t>
+    <t xml:space="preserve">8.48669815063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44517803192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4783935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40365791320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42856979370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6527795791626</t>
   </si>
   <si>
     <t xml:space="preserve">8.69429874420166</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">8.71090602874756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89359569549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84377098083496</t>
+    <t xml:space="preserve">8.89359378814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84377002716064</t>
   </si>
   <si>
     <t xml:space="preserve">8.88529109954834</t>
@@ -509,94 +509,94 @@
     <t xml:space="preserve">8.78564167022705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80224990844727</t>
+    <t xml:space="preserve">8.80225086212158</t>
   </si>
   <si>
     <t xml:space="preserve">8.8188591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90189838409424</t>
+    <t xml:space="preserve">8.90189743041992</t>
   </si>
   <si>
     <t xml:space="preserve">9.05137157440186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81055355072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6278657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70260334014893</t>
+    <t xml:space="preserve">8.81055450439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62786483764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70260143280029</t>
   </si>
   <si>
     <t xml:space="preserve">8.82716178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75242614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04306602478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14271450042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2838830947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35031604766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35861968994141</t>
+    <t xml:space="preserve">8.7524242401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04306697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14271640777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28388500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35031509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35861873626709</t>
   </si>
   <si>
     <t xml:space="preserve">9.15102005004883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93511390686035</t>
+    <t xml:space="preserve">8.93511295318604</t>
   </si>
   <si>
     <t xml:space="preserve">8.7773380279541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19254016876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4499626159668</t>
+    <t xml:space="preserve">9.19253921508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44996452331543</t>
   </si>
   <si>
     <t xml:space="preserve">9.17593097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00154685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1344108581543</t>
+    <t xml:space="preserve">9.00154781341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13441181182861</t>
   </si>
   <si>
     <t xml:space="preserve">8.91850757598877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92681121826172</t>
+    <t xml:space="preserve">8.9268102645874</t>
   </si>
   <si>
     <t xml:space="preserve">9.00985050201416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98493957519531</t>
+    <t xml:space="preserve">8.984938621521</t>
   </si>
   <si>
     <t xml:space="preserve">8.76072978973389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1178035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.225754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95172309875488</t>
+    <t xml:space="preserve">9.11780261993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22575569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95172214508057</t>
   </si>
   <si>
     <t xml:space="preserve">9.06797790527344</t>
@@ -605,28 +605,28 @@
     <t xml:space="preserve">9.0762825012207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20084285736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31709861755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36692333221436</t>
+    <t xml:space="preserve">9.20084381103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31709957122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36692428588867</t>
   </si>
   <si>
     <t xml:space="preserve">9.49148273468018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5496129989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96481132507324</t>
+    <t xml:space="preserve">9.54961204528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96481227874756</t>
   </si>
   <si>
     <t xml:space="preserve">10.0229396820068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82364559173584</t>
+    <t xml:space="preserve">9.82364273071289</t>
   </si>
   <si>
     <t xml:space="preserve">9.93989944458008</t>
@@ -638,19 +638,19 @@
     <t xml:space="preserve">10.0063314437866</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0561571121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2056283950806</t>
+    <t xml:space="preserve">10.0561561584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2056293487549</t>
   </si>
   <si>
     <t xml:space="preserve">10.2305402755737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2139320373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1973257064819</t>
+    <t xml:space="preserve">10.2139329910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1973237991333</t>
   </si>
   <si>
     <t xml:space="preserve">10.1558055877686</t>
@@ -662,13 +662,13 @@
     <t xml:space="preserve">10.1807174682617</t>
   </si>
   <si>
-    <t xml:space="preserve">10.147500038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2222375869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1308927536011</t>
+    <t xml:space="preserve">10.1475009918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2222366333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1308908462524</t>
   </si>
   <si>
     <t xml:space="preserve">10.0976762771606</t>
@@ -677,22 +677,22 @@
     <t xml:space="preserve">9.84855556488037</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3135795593262</t>
+    <t xml:space="preserve">10.3135805130005</t>
   </si>
   <si>
     <t xml:space="preserve">10.0810689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0727643966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.529483795166</t>
+    <t xml:space="preserve">10.0727634429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5294847488403</t>
   </si>
   <si>
     <t xml:space="preserve">10.4464445114136</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5211791992188</t>
+    <t xml:space="preserve">10.5211811065674</t>
   </si>
   <si>
     <t xml:space="preserve">10.3883171081543</t>
@@ -707,82 +707,82 @@
     <t xml:space="preserve">10.7204761505127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6540431976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4049253463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6457414627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7952117919922</t>
+    <t xml:space="preserve">10.6540441513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4049263000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6457405090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7952127456665</t>
   </si>
   <si>
     <t xml:space="preserve">10.96129322052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9280767440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7703008651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7786045074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8699502944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7869081497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0360307693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8948612213135</t>
+    <t xml:space="preserve">10.9280776977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.770299911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7786054611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8699493408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7869091033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0360298156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8948602676392</t>
   </si>
   <si>
     <t xml:space="preserve">11.0443344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2519340515137</t>
+    <t xml:space="preserve">11.2519330978394</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771974563599</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2270221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2602367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2851505279541</t>
+    <t xml:space="preserve">11.2270212173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2602376937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2851495742798</t>
   </si>
   <si>
     <t xml:space="preserve">11.3432779312134</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3931016921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4512300491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5093584060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5010547637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5176639556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7418699264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7584781646729</t>
+    <t xml:space="preserve">11.3931007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.451229095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5093574523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5010538101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5176620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7418689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7584791183472</t>
   </si>
   <si>
     <t xml:space="preserve">11.6920471191406</t>
@@ -791,25 +791,25 @@
     <t xml:space="preserve">11.6837406158447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7252616882324</t>
+    <t xml:space="preserve">11.7252635955811</t>
   </si>
   <si>
     <t xml:space="preserve">11.7667827606201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7169580459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.592396736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7003507614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5425748825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9577751159668</t>
+    <t xml:space="preserve">11.7169570922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5923976898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7003498077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.542573928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9577741622925</t>
   </si>
   <si>
     <t xml:space="preserve">12.0574216842651</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">11.9162549972534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9909915924072</t>
+    <t xml:space="preserve">11.9909906387329</t>
   </si>
   <si>
     <t xml:space="preserve">11.98268699646</t>
@@ -830,28 +830,28 @@
     <t xml:space="preserve">12.0491189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2899332046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3895826339722</t>
+    <t xml:space="preserve">12.2899351119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3895835876465</t>
   </si>
   <si>
     <t xml:space="preserve">12.3148469924927</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5058403015137</t>
+    <t xml:space="preserve">12.505838394165</t>
   </si>
   <si>
     <t xml:space="preserve">12.5390548706055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2733278274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1902875900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1985902786255</t>
+    <t xml:space="preserve">12.2733268737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1902866363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1985912322998</t>
   </si>
   <si>
     <t xml:space="preserve">12.0823354721069</t>
@@ -860,73 +860,73 @@
     <t xml:space="preserve">11.64222240448</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5508785247803</t>
+    <t xml:space="preserve">11.5508766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8083009719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9346389770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9514837265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0609760284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1620454788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7830352783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6566972732544</t>
   </si>
   <si>
     <t xml:space="preserve">11.8083019256592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9346389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9514827728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0609769821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1620464324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7830333709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6566972732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8083028793335</t>
-  </si>
-  <si>
     <t xml:space="preserve">11.7577667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5977411270142</t>
+    <t xml:space="preserve">11.5977401733398</t>
   </si>
   <si>
     <t xml:space="preserve">11.5640506744385</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3029546737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2018842697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1934623718262</t>
+    <t xml:space="preserve">11.3029537200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2018852233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1934614181519</t>
   </si>
   <si>
     <t xml:space="preserve">11.0334339141846</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9576330184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.23557472229</t>
+    <t xml:space="preserve">10.957631111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2355728149414</t>
   </si>
   <si>
     <t xml:space="preserve">11.4208679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2271528244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2861089706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1681938171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.923942565918</t>
+    <t xml:space="preserve">11.2271518707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2861080169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.168194770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9239416122437</t>
   </si>
   <si>
     <t xml:space="preserve">11.0250129699707</t>
@@ -935,37 +935,37 @@
     <t xml:space="preserve">10.763916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9492092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5786228179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7891845703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7386484146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6544246673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7554931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4292898178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5219373703003</t>
+    <t xml:space="preserve">10.9492111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5786209106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7891836166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7386493682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6544237136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7554941177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4292917251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.521936416626</t>
   </si>
   <si>
     <t xml:space="preserve">11.2945318222046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6398525238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4629793167114</t>
+    <t xml:space="preserve">11.639853477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4629802703857</t>
   </si>
   <si>
     <t xml:space="preserve">11.4124460220337</t>
@@ -974,25 +974,25 @@
     <t xml:space="preserve">11.361909866333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3197984695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2103061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9997453689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9913234710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0081663131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8902521133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9323644638062</t>
+    <t xml:space="preserve">11.3197994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2103071212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9997444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.991322517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0081672668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8902540206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9323654174805</t>
   </si>
   <si>
     <t xml:space="preserve">10.8734073638916</t>
@@ -1001,10 +1001,10 @@
     <t xml:space="preserve">10.8818302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6796894073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.78076171875</t>
+    <t xml:space="preserve">10.6796913146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7807607650757</t>
   </si>
   <si>
     <t xml:space="preserve">10.8649854660034</t>
@@ -1013,19 +1013,19 @@
     <t xml:space="preserve">10.7049589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9155216217041</t>
+    <t xml:space="preserve">10.9155197143555</t>
   </si>
   <si>
     <t xml:space="preserve">11.2608413696289</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1513500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0839700698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0502786636353</t>
+    <t xml:space="preserve">11.1513481140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0839710235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0502796173096</t>
   </si>
   <si>
     <t xml:space="preserve">11.2524185180664</t>
@@ -1034,37 +1034,37 @@
     <t xml:space="preserve">11.3282203674316</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3787565231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3955993652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5050926208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4040250778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.555627822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6819667816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7493438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9177932739258</t>
+    <t xml:space="preserve">11.378755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3956003189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5050945281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4040241241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5556268692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6819648742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7493448257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9177951812744</t>
   </si>
   <si>
     <t xml:space="preserve">11.8841037750244</t>
   </si>
   <si>
-    <t xml:space="preserve">11.943060874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0525531768799</t>
+    <t xml:space="preserve">11.9430618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0525541305542</t>
   </si>
   <si>
     <t xml:space="preserve">12.0946664810181</t>
@@ -1076,43 +1076,43 @@
     <t xml:space="preserve">12.0357093811035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0778207778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.044132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1788902282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1704692840576</t>
+    <t xml:space="preserve">12.0778198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0441312789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1788921356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.170467376709</t>
   </si>
   <si>
     <t xml:space="preserve">12.3136510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3220739364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3726072311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2041568756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2883825302124</t>
+    <t xml:space="preserve">12.3220729827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3726081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.204158782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2883834838867</t>
   </si>
   <si>
     <t xml:space="preserve">12.2968053817749</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7914562225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7325010299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.816722869873</t>
+    <t xml:space="preserve">11.7914543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7325000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8167238235474</t>
   </si>
   <si>
     <t xml:space="preserve">12.010440826416</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">10.6965351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8986749649048</t>
+    <t xml:space="preserve">10.8986759185791</t>
   </si>
   <si>
     <t xml:space="preserve">10.8228731155396</t>
@@ -1148,19 +1148,19 @@
     <t xml:space="preserve">10.9407873153687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7723379135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7976064682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7302265167236</t>
+    <t xml:space="preserve">10.7723369598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7976055145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7302255630493</t>
   </si>
   <si>
     <t xml:space="preserve">10.7218036651611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6628465652466</t>
+    <t xml:space="preserve">10.6628475189209</t>
   </si>
   <si>
     <t xml:space="preserve">10.6123113632202</t>
@@ -1169,25 +1169,25 @@
     <t xml:space="preserve">10.8060274124146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6881141662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312969207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6712675094604</t>
+    <t xml:space="preserve">10.6881132125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312940597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6712684631348</t>
   </si>
   <si>
     <t xml:space="preserve">10.4691295623779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.48597240448</t>
+    <t xml:space="preserve">10.4859733581543</t>
   </si>
   <si>
     <t xml:space="preserve">11.0923929214478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1597728729248</t>
+    <t xml:space="preserve">11.1597719192505</t>
   </si>
   <si>
     <t xml:space="preserve">11.1345043182373</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">11.4545593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3450660705566</t>
+    <t xml:space="preserve">11.345067024231</t>
   </si>
   <si>
     <t xml:space="preserve">10.4270162582397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3175249099731</t>
+    <t xml:space="preserve">10.3175239562988</t>
   </si>
   <si>
     <t xml:space="preserve">10.2417230606079</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">10.2838344573975</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1911878585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1574983596802</t>
+    <t xml:space="preserve">10.1911869049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1574974060059</t>
   </si>
   <si>
     <t xml:space="preserve">10.2248783111572</t>
@@ -1229,49 +1229,49 @@
     <t xml:space="preserve">10.1659202575684</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1069622039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0985403060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93008995056152</t>
+    <t xml:space="preserve">10.1069631576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0985422134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93009185791016</t>
   </si>
   <si>
     <t xml:space="preserve">9.98904895782471</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0058927536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71952819824219</t>
+    <t xml:space="preserve">10.0058937072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71953010559082</t>
   </si>
   <si>
     <t xml:space="preserve">9.68583965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4837007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37420845031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.115385055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3091020584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5954656600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7133808135986</t>
+    <t xml:space="preserve">9.48369979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3742094039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1153860092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3091011047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5954666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7133817672729</t>
   </si>
   <si>
     <t xml:space="preserve">10.603889465332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3596363067627</t>
+    <t xml:space="preserve">10.359637260437</t>
   </si>
   <si>
     <t xml:space="preserve">10.3006811141968</t>
@@ -1280,28 +1280,28 @@
     <t xml:space="preserve">10.4522838592529</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4017505645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5617771148682</t>
+    <t xml:space="preserve">10.4017486572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5617761611938</t>
   </si>
   <si>
     <t xml:space="preserve">10.5449314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3427925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438610076904</t>
+    <t xml:space="preserve">10.342791557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438629150391</t>
   </si>
   <si>
     <t xml:space="preserve">10.4101724624634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4185943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4354391098022</t>
+    <t xml:space="preserve">10.4185934066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4354400634766</t>
   </si>
   <si>
     <t xml:space="preserve">10.2585678100586</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">10.1490755081177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0418577194214</t>
+    <t xml:space="preserve">11.0418586730957</t>
   </si>
   <si>
     <t xml:space="preserve">10.536509513855</t>
@@ -1325,16 +1325,16 @@
     <t xml:space="preserve">10.2754125595093</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2080326080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0648517608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93851375579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0500860214233</t>
+    <t xml:space="preserve">10.2080335617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0648527145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93851280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0500869750977</t>
   </si>
   <si>
     <t xml:space="preserve">10.3848028182983</t>
@@ -1349,10 +1349,10 @@
     <t xml:space="preserve">10.676607131958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5993661880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2303171157837</t>
+    <t xml:space="preserve">10.599365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2303190231323</t>
   </si>
   <si>
     <t xml:space="preserve">10.470627784729</t>
@@ -1364,25 +1364,25 @@
     <t xml:space="preserve">10.642276763916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.685188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6594409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7109384536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9340829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6508598327637</t>
+    <t xml:space="preserve">10.6851892471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6594429016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7109365463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.93408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.650860786438</t>
   </si>
   <si>
     <t xml:space="preserve">10.7452669143677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5307054519653</t>
+    <t xml:space="preserve">10.530704498291</t>
   </si>
   <si>
     <t xml:space="preserve">10.393385887146</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">10.1444931030273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1359119415283</t>
+    <t xml:space="preserve">10.1359128952026</t>
   </si>
   <si>
     <t xml:space="preserve">9.92135047912598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.075834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0586681365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89560127258301</t>
+    <t xml:space="preserve">10.0758333206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0586700439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89560222625732</t>
   </si>
   <si>
     <t xml:space="preserve">9.947096824646</t>
@@ -1415,13 +1415,13 @@
     <t xml:space="preserve">9.74111652374268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76686382293701</t>
+    <t xml:space="preserve">9.76686477661133</t>
   </si>
   <si>
     <t xml:space="preserve">9.85268878936768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87843608856201</t>
+    <t xml:space="preserve">9.87843704223633</t>
   </si>
   <si>
     <t xml:space="preserve">9.99000930786133</t>
@@ -1430,13 +1430,13 @@
     <t xml:space="preserve">10.2560663223267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2903957366943</t>
+    <t xml:space="preserve">10.29039478302</t>
   </si>
   <si>
     <t xml:space="preserve">10.2732305526733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.51353931427</t>
+    <t xml:space="preserve">10.5135402679443</t>
   </si>
   <si>
     <t xml:space="preserve">10.48779296875</t>
@@ -1457,16 +1457,16 @@
     <t xml:space="preserve">10.0157556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.032922744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84410667419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.04150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.23890209198</t>
+    <t xml:space="preserve">10.0329217910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84410572052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0415029525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2389001846313</t>
   </si>
   <si>
     <t xml:space="preserve">9.78402900695801</t>
@@ -1475,22 +1475,22 @@
     <t xml:space="preserve">9.706787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77544498443604</t>
+    <t xml:space="preserve">9.77544689178467</t>
   </si>
   <si>
     <t xml:space="preserve">9.68103981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56088447570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59521389007568</t>
+    <t xml:space="preserve">9.56088638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59521484375</t>
   </si>
   <si>
     <t xml:space="preserve">9.68962287902832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47505950927734</t>
+    <t xml:space="preserve">9.47506046295166</t>
   </si>
   <si>
     <t xml:space="preserve">9.483642578125</t>
@@ -1502,46 +1502,46 @@
     <t xml:space="preserve">9.912766456604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88701915740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75828266143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56946754455566</t>
+    <t xml:space="preserve">9.88701820373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75828170776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56946659088135</t>
   </si>
   <si>
     <t xml:space="preserve">9.578049659729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73253345489502</t>
+    <t xml:space="preserve">9.73253536224365</t>
   </si>
   <si>
     <t xml:space="preserve">9.612380027771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71537017822266</t>
+    <t xml:space="preserve">9.71536922454834</t>
   </si>
   <si>
     <t xml:space="preserve">9.82694149017334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1874055862427</t>
+    <t xml:space="preserve">10.187406539917</t>
   </si>
   <si>
     <t xml:space="preserve">10.2217350006104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99859237670898</t>
+    <t xml:space="preserve">9.99859142303467</t>
   </si>
   <si>
     <t xml:space="preserve">9.96426200866699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86985492706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69820404052734</t>
+    <t xml:space="preserve">9.86985397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69820499420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.86127090454102</t>
@@ -1550,61 +1550,61 @@
     <t xml:space="preserve">9.52655506134033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2175874710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23474979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69405555725098</t>
+    <t xml:space="preserve">9.21758556365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23475074768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69405460357666</t>
   </si>
   <si>
     <t xml:space="preserve">8.52669525146484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44087028503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12332057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43228721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52240371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41083145141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29926109313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16623115539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23060131072998</t>
+    <t xml:space="preserve">8.4408712387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12331867218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43228912353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5224027633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41083240509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29925918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16623020172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23060035705566</t>
   </si>
   <si>
     <t xml:space="preserve">8.08469772338867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35504531860352</t>
+    <t xml:space="preserve">8.35504722595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.22630882263184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48378467559814</t>
+    <t xml:space="preserve">8.48378276824951</t>
   </si>
   <si>
     <t xml:space="preserve">8.39366722106934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57819175720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49236583709717</t>
+    <t xml:space="preserve">8.57819080352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49236679077148</t>
   </si>
   <si>
     <t xml:space="preserve">8.44945335388184</t>
@@ -1616,25 +1616,25 @@
     <t xml:space="preserve">8.11473655700684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02032947540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79289293289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72852516174316</t>
+    <t xml:space="preserve">8.02033042907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79289388656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72852468490601</t>
   </si>
   <si>
     <t xml:space="preserve">7.77143669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83151483535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00316333770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02891063690186</t>
+    <t xml:space="preserve">7.83151531219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00316429138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02891159057617</t>
   </si>
   <si>
     <t xml:space="preserve">8.00745582580566</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">8.25205707550049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28638744354248</t>
+    <t xml:space="preserve">8.28638648986816</t>
   </si>
   <si>
     <t xml:space="preserve">8.61681270599365</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">8.60822868347168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54815196990967</t>
+    <t xml:space="preserve">8.54815101623535</t>
   </si>
   <si>
     <t xml:space="preserve">8.75413227081299</t>
@@ -1664,31 +1664,31 @@
     <t xml:space="preserve">8.46232795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16194152832031</t>
+    <t xml:space="preserve">8.16193962097168</t>
   </si>
   <si>
     <t xml:space="preserve">8.19197845458984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98170757293701</t>
+    <t xml:space="preserve">7.98170804977417</t>
   </si>
   <si>
     <t xml:space="preserve">8.0889892578125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33788204193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81435060501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.698486328125</t>
+    <t xml:space="preserve">8.33788013458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81435012817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69848680496216</t>
   </si>
   <si>
     <t xml:space="preserve">7.99887323379517</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81863927841187</t>
+    <t xml:space="preserve">7.81864070892334</t>
   </si>
   <si>
     <t xml:space="preserve">7.86584424972534</t>
@@ -1697,22 +1697,22 @@
     <t xml:space="preserve">7.58691310882568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63411664962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68990230560303</t>
+    <t xml:space="preserve">7.634117603302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6899037361145</t>
   </si>
   <si>
     <t xml:space="preserve">7.65986633300781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96454334259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.938796043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73696613311768</t>
+    <t xml:space="preserve">7.96454429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93879652023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73696708679199</t>
   </si>
   <si>
     <t xml:space="preserve">8.82279014587402</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">8.38508415222168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40225028991699</t>
+    <t xml:space="preserve">8.40224933624268</t>
   </si>
   <si>
     <t xml:space="preserve">8.45374393463135</t>
@@ -1739,25 +1739,25 @@
     <t xml:space="preserve">8.50094795227051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46661758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59964752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85712051391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56960868835449</t>
+    <t xml:space="preserve">8.46661949157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59964847564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85712146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56960773468018</t>
   </si>
   <si>
     <t xml:space="preserve">8.56531715393066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55673313140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53956890106201</t>
+    <t xml:space="preserve">8.55673408508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53956985473633</t>
   </si>
   <si>
     <t xml:space="preserve">8.50523948669434</t>
@@ -1766,28 +1766,28 @@
     <t xml:space="preserve">8.50953102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24776554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15335750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39795684814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58248138427734</t>
+    <t xml:space="preserve">8.24776458740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15335845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39795875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58248233795166</t>
   </si>
   <si>
     <t xml:space="preserve">8.77129650115967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65972518920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09743118286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96869277954102</t>
+    <t xml:space="preserve">8.65972423553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09743022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9686918258667</t>
   </si>
   <si>
     <t xml:space="preserve">9.02018737792969</t>
@@ -1796,61 +1796,61 @@
     <t xml:space="preserve">9.28624534606934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31199169158936</t>
+    <t xml:space="preserve">9.31199264526367</t>
   </si>
   <si>
     <t xml:space="preserve">9.08026504516602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.131760597229</t>
+    <t xml:space="preserve">9.13176155090332</t>
   </si>
   <si>
     <t xml:space="preserve">9.32057476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94294548034668</t>
+    <t xml:space="preserve">8.94294452667236</t>
   </si>
   <si>
     <t xml:space="preserve">8.814208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78846168518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79704475402832</t>
+    <t xml:space="preserve">8.78846073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79704284667969</t>
   </si>
   <si>
     <t xml:space="preserve">8.74554920196533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72838592529297</t>
+    <t xml:space="preserve">8.72838497161865</t>
   </si>
   <si>
     <t xml:space="preserve">8.908616065979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14034366607666</t>
+    <t xml:space="preserve">9.14034461975098</t>
   </si>
   <si>
     <t xml:space="preserve">9.42356586456299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26049900054932</t>
+    <t xml:space="preserve">9.260498046875</t>
   </si>
   <si>
     <t xml:space="preserve">9.18325614929199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00302314758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96011161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76271533966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65114212036133</t>
+    <t xml:space="preserve">9.00302410125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96011257171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76271438598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65114116668701</t>
   </si>
   <si>
     <t xml:space="preserve">8.685471534729</t>
@@ -1859,13 +1859,13 @@
     <t xml:space="preserve">8.67688941955566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87428569793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51797199249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44073009490967</t>
+    <t xml:space="preserve">8.8742847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51797294616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44072818756104</t>
   </si>
   <si>
     <t xml:space="preserve">9.41498184204102</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">10.195987701416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80977630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62096214294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50939083099365</t>
+    <t xml:space="preserve">9.80977725982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62096118927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50938987731934</t>
   </si>
   <si>
     <t xml:space="preserve">8.86570358276367</t>
@@ -1898,31 +1898,31 @@
     <t xml:space="preserve">8.83995532989502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75851821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77167415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74097442626953</t>
+    <t xml:space="preserve">8.75851726531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77167510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74097347259521</t>
   </si>
   <si>
     <t xml:space="preserve">8.42080879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53483963012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57869911193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58747005462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47343730926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55238437652588</t>
+    <t xml:space="preserve">8.53483772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57869815826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58746910095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47343826293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55238342285156</t>
   </si>
   <si>
     <t xml:space="preserve">8.42957973480225</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">8.37695026397705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56992721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67957210540771</t>
+    <t xml:space="preserve">8.56992626190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67957305908203</t>
   </si>
   <si>
     <t xml:space="preserve">8.66202926635742</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">8.8944787979126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72781658172607</t>
+    <t xml:space="preserve">8.72781753540039</t>
   </si>
   <si>
     <t xml:space="preserve">8.72343063354492</t>
@@ -1955,25 +1955,25 @@
     <t xml:space="preserve">8.9383373260498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82430553436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06114101409912</t>
+    <t xml:space="preserve">8.82430458068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0611400604248</t>
   </si>
   <si>
     <t xml:space="preserve">9.00851058959961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85062122344971</t>
+    <t xml:space="preserve">8.85062026977539</t>
   </si>
   <si>
     <t xml:space="preserve">8.71465873718262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88570785522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11376953125</t>
+    <t xml:space="preserve">8.88570690155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11377048492432</t>
   </si>
   <si>
     <t xml:space="preserve">9.05236911773682</t>
@@ -1982,28 +1982,28 @@
     <t xml:space="preserve">9.28043174743652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32429027557373</t>
+    <t xml:space="preserve">9.32428932189941</t>
   </si>
   <si>
     <t xml:space="preserve">9.23657417297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92956447601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80676174163818</t>
+    <t xml:space="preserve">8.9295654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8067626953125</t>
   </si>
   <si>
     <t xml:space="preserve">8.78921985626221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49536800384521</t>
+    <t xml:space="preserve">8.4953670501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.45589447021484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48221111297607</t>
+    <t xml:space="preserve">8.48220920562744</t>
   </si>
   <si>
     <t xml:space="preserve">8.62255668640137</t>
@@ -2012,76 +2012,76 @@
     <t xml:space="preserve">8.92079448699951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07868480682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01728248596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17958641052246</t>
+    <t xml:space="preserve">9.07868385314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01728057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17958736419678</t>
   </si>
   <si>
     <t xml:space="preserve">8.1313419342041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17081451416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9602952003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77170467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61819982528687</t>
+    <t xml:space="preserve">8.17081546783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96029567718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77170419692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61820030212402</t>
   </si>
   <si>
     <t xml:space="preserve">7.6488995552063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63135766983032</t>
+    <t xml:space="preserve">7.63135719299316</t>
   </si>
   <si>
     <t xml:space="preserve">7.38574934005737</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29803419113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39013671875</t>
+    <t xml:space="preserve">7.29803371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39013624191284</t>
   </si>
   <si>
     <t xml:space="preserve">7.22347402572632</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20593166351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28048992156982</t>
+    <t xml:space="preserve">7.20593118667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28048944473267</t>
   </si>
   <si>
     <t xml:space="preserve">7.27171802520752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.512939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39890813827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26733207702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19277334213257</t>
+    <t xml:space="preserve">7.51293897628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39890766143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26733303070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19277286529541</t>
   </si>
   <si>
     <t xml:space="preserve">7.44276666641235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45153903961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32873344421387</t>
+    <t xml:space="preserve">7.45153760910034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32873439788818</t>
   </si>
   <si>
     <t xml:space="preserve">7.53048276901245</t>
@@ -2099,22 +2099,22 @@
     <t xml:space="preserve">8.22344589233398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.289231300354</t>
+    <t xml:space="preserve">8.28923320770264</t>
   </si>
   <si>
     <t xml:space="preserve">8.35063552856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21905899047852</t>
+    <t xml:space="preserve">8.21905994415283</t>
   </si>
   <si>
     <t xml:space="preserve">8.19274425506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30239200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87257671356201</t>
+    <t xml:space="preserve">8.30239009857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87257814407349</t>
   </si>
   <si>
     <t xml:space="preserve">7.72346067428589</t>
@@ -2123,67 +2123,67 @@
     <t xml:space="preserve">7.60942888259888</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74100303649902</t>
+    <t xml:space="preserve">7.74100255966187</t>
   </si>
   <si>
     <t xml:space="preserve">7.83310604095459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84187746047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67521476745605</t>
+    <t xml:space="preserve">7.84187793731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67521524429321</t>
   </si>
   <si>
     <t xml:space="preserve">7.50855493545532</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4032940864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45592403411865</t>
+    <t xml:space="preserve">7.40329360961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45592451095581</t>
   </si>
   <si>
     <t xml:space="preserve">7.44715166091919</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31557655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47346782684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85064840316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85942029953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00854015350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04362773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80679130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91643667221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18835926055908</t>
+    <t xml:space="preserve">7.31557750701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47346687316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8506498336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85942077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0085391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04362678527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80679035186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91643619537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18835830688477</t>
   </si>
   <si>
     <t xml:space="preserve">8.25414657592773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29362010955811</t>
+    <t xml:space="preserve">8.29361915588379</t>
   </si>
   <si>
     <t xml:space="preserve">8.36379241943359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65325736999512</t>
+    <t xml:space="preserve">8.65325832366943</t>
   </si>
   <si>
     <t xml:space="preserve">8.37256336212158</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">9.37692070007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56112670898438</t>
+    <t xml:space="preserve">9.56112575531006</t>
   </si>
   <si>
     <t xml:space="preserve">9.75410175323486</t>
@@ -2213,76 +2213,76 @@
     <t xml:space="preserve">9.70147323608398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47340965270996</t>
+    <t xml:space="preserve">9.47340774536133</t>
   </si>
   <si>
     <t xml:space="preserve">9.35060501098633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49095344543457</t>
+    <t xml:space="preserve">9.49095249176025</t>
   </si>
   <si>
     <t xml:space="preserve">9.24534511566162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42078018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31551933288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48218154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64884281158447</t>
+    <t xml:space="preserve">9.42077922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31552028656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48218059539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64884090423584</t>
   </si>
   <si>
     <t xml:space="preserve">9.72778797149658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80673122406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77164649963379</t>
+    <t xml:space="preserve">9.80673313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77164745330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.85936260223389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81550407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86813449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92076396942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99971008300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8769063949585</t>
+    <t xml:space="preserve">9.815505027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86813354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9207649230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9997091293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87690734863281</t>
   </si>
   <si>
     <t xml:space="preserve">9.84181976318359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89444923400879</t>
+    <t xml:space="preserve">9.89445018768311</t>
   </si>
   <si>
     <t xml:space="preserve">9.9821662902832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0698833465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96462249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67515754699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71901702880859</t>
+    <t xml:space="preserve">10.0698823928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96462154388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67515659332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71901607513428</t>
   </si>
   <si>
     <t xml:space="preserve">9.79796123504639</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">9.29797554016113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52603912353516</t>
+    <t xml:space="preserve">9.52603816986084</t>
   </si>
   <si>
     <t xml:space="preserve">9.63129997253418</t>
@@ -2300,16 +2300,16 @@
     <t xml:space="preserve">9.71024417877197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68392848968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69270038604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76287364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73655891418457</t>
+    <t xml:space="preserve">9.68392944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69270133972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76287460327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73655986785889</t>
   </si>
   <si>
     <t xml:space="preserve">9.57866859436035</t>
@@ -2318,79 +2318,79 @@
     <t xml:space="preserve">9.30674743652344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2102575302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33306217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20148658752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02605533599854</t>
+    <t xml:space="preserve">9.21025848388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33306312561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20148754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02605438232422</t>
   </si>
   <si>
     <t xml:space="preserve">9.26288986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13131332397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08745574951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43832206726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42955112457275</t>
+    <t xml:space="preserve">9.13131427764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0874547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43832302093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42955017089844</t>
   </si>
   <si>
     <t xml:space="preserve">9.21902942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25411701202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15762901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09622573852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39449214935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33747673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34186363220215</t>
+    <t xml:space="preserve">9.25411605834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15762996673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09622669219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39449310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.337477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34186267852783</t>
   </si>
   <si>
     <t xml:space="preserve">8.1050271987915</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92959403991699</t>
+    <t xml:space="preserve">7.92959356307983</t>
   </si>
   <si>
     <t xml:space="preserve">7.49978256225586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60065603256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42960977554321</t>
+    <t xml:space="preserve">7.60065650939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42960929870605</t>
   </si>
   <si>
     <t xml:space="preserve">7.11821365356445</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18400192260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57875633239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64892959594727</t>
+    <t xml:space="preserve">7.18400144577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57875680923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64892911911011</t>
   </si>
   <si>
     <t xml:space="preserve">6.5568265914917</t>
@@ -2399,22 +2399,22 @@
     <t xml:space="preserve">6.14017200469971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3857798576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87702226638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97351026535034</t>
+    <t xml:space="preserve">6.38578033447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8770227432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9735107421875</t>
   </si>
   <si>
     <t xml:space="preserve">6.55244064331055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11382818222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72784471511841</t>
+    <t xml:space="preserve">7.1138277053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72784519195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.82436275482178</t>
@@ -2423,43 +2423,43 @@
     <t xml:space="preserve">7.02172565460205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47349548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31560516357422</t>
+    <t xml:space="preserve">6.4734959602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31560564041138</t>
   </si>
   <si>
     <t xml:space="preserve">5.83316373825073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9603533744812</t>
+    <t xml:space="preserve">5.96035289764404</t>
   </si>
   <si>
     <t xml:space="preserve">5.85070705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61387205123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18406009674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4735255241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54369831085205</t>
+    <t xml:space="preserve">5.61387252807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18405961990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47352457046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54369783401489</t>
   </si>
   <si>
     <t xml:space="preserve">5.89895105361938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82439184188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64895820617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69720268249512</t>
+    <t xml:space="preserve">5.82439231872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64895868301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69720315933228</t>
   </si>
   <si>
     <t xml:space="preserve">5.92965269088745</t>
@@ -2468,16 +2468,16 @@
     <t xml:space="preserve">6.06122732162476</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0085973739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0568413734436</t>
+    <t xml:space="preserve">6.00859689712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05684185028076</t>
   </si>
   <si>
     <t xml:space="preserve">6.40332269668579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5919132232666</t>
+    <t xml:space="preserve">6.59191370010376</t>
   </si>
   <si>
     <t xml:space="preserve">6.83752107620239</t>
@@ -2486,40 +2486,40 @@
     <t xml:space="preserve">6.69717311859131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86822128295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81120491027832</t>
+    <t xml:space="preserve">6.8682222366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81120538711548</t>
   </si>
   <si>
     <t xml:space="preserve">6.72348928451538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48665380477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48226833343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36385059356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22789001464844</t>
+    <t xml:space="preserve">6.48665332794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4822678565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36385107040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22788953781128</t>
   </si>
   <si>
     <t xml:space="preserve">5.77176237106323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82000589370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26297616958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23227596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21911811828613</t>
+    <t xml:space="preserve">5.82000684738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26297521591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23227548599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21911764144897</t>
   </si>
   <si>
     <t xml:space="preserve">6.39455032348633</t>
@@ -2531,10 +2531,10 @@
     <t xml:space="preserve">7.16207265853882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51732397079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37259340286255</t>
+    <t xml:space="preserve">7.51732444763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37259387969971</t>
   </si>
   <si>
     <t xml:space="preserve">7.33312034606934</t>
@@ -2543,10 +2543,10 @@
     <t xml:space="preserve">7.4164514541626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79801988601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6839861869812</t>
+    <t xml:space="preserve">7.79801940917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68398761749268</t>
   </si>
   <si>
     <t xml:space="preserve">7.55679798126221</t>
@@ -2555,13 +2555,13 @@
     <t xml:space="preserve">7.10067129135132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35504913330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35066366195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21031665802002</t>
+    <t xml:space="preserve">7.35504961013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35066413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21031713485718</t>
   </si>
   <si>
     <t xml:space="preserve">7.23224592208862</t>
@@ -2573,25 +2573,25 @@
     <t xml:space="preserve">7.10505676269531</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20154523849487</t>
+    <t xml:space="preserve">7.20154476165771</t>
   </si>
   <si>
     <t xml:space="preserve">7.24540328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21470308303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17084503173828</t>
+    <t xml:space="preserve">7.21470260620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17084407806396</t>
   </si>
   <si>
     <t xml:space="preserve">7.40767908096313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25856018066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36820650100708</t>
+    <t xml:space="preserve">7.25856065750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36820697784424</t>
   </si>
   <si>
     <t xml:space="preserve">7.32434940338135</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">7.14891481399536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24978876113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43838119506836</t>
+    <t xml:space="preserve">7.24978923797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43838024139404</t>
   </si>
   <si>
     <t xml:space="preserve">7.16645765304565</t>
@@ -2612,16 +2612,16 @@
     <t xml:space="preserve">6.70156002044678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61384248733521</t>
+    <t xml:space="preserve">6.61384344100952</t>
   </si>
   <si>
     <t xml:space="preserve">6.69278764724731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75418949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68401718139648</t>
+    <t xml:space="preserve">6.75418996810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68401622772217</t>
   </si>
   <si>
     <t xml:space="preserve">6.71033143997192</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">6.83313465118408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06119823455811</t>
+    <t xml:space="preserve">7.06119871139526</t>
   </si>
   <si>
     <t xml:space="preserve">7.14014291763306</t>
@@ -2639,55 +2639,55 @@
     <t xml:space="preserve">7.05681276321411</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04804039001465</t>
+    <t xml:space="preserve">7.04804134368896</t>
   </si>
   <si>
     <t xml:space="preserve">7.00856781005859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94716691970825</t>
+    <t xml:space="preserve">6.94716644287109</t>
   </si>
   <si>
     <t xml:space="preserve">7.07435607910156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0875129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09628534317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01733922958374</t>
+    <t xml:space="preserve">7.08751344680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09628486633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01734018325806</t>
   </si>
   <si>
     <t xml:space="preserve">7.35943603515625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29364776611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4910101890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60504198074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97345304489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5743408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41206550598145</t>
+    <t xml:space="preserve">7.29364824295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49100971221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60504293441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97345209121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57434177398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41206502914429</t>
   </si>
   <si>
     <t xml:space="preserve">6.88576507568359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99102544784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0392689704895</t>
+    <t xml:space="preserve">6.9910249710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03926944732666</t>
   </si>
   <si>
     <t xml:space="preserve">7.06997013092041</t>
@@ -2699,55 +2699,55 @@
     <t xml:space="preserve">7.48223924636841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8638072013855</t>
+    <t xml:space="preserve">7.86380624771118</t>
   </si>
   <si>
     <t xml:space="preserve">7.92082166671753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9997673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73661804199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68837404251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61381340026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62697219848633</t>
+    <t xml:space="preserve">7.99976682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73661708831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68837261199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61381483078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62697124481201</t>
   </si>
   <si>
     <t xml:space="preserve">7.57872676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77609062194824</t>
+    <t xml:space="preserve">7.77608966827393</t>
   </si>
   <si>
     <t xml:space="preserve">7.80240488052368</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96906614303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99099445343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15327072143555</t>
+    <t xml:space="preserve">7.96906661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99099588394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15327167510986</t>
   </si>
   <si>
     <t xml:space="preserve">8.54799747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56995582580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82433319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66644477844238</t>
+    <t xml:space="preserve">7.56995534896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82433414459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66644334793091</t>
   </si>
   <si>
     <t xml:space="preserve">7.71907377243042</t>
@@ -2756,10 +2756,10 @@
     <t xml:space="preserve">7.78486156463623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86819267272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22780227661133</t>
+    <t xml:space="preserve">7.86819314956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22780323028564</t>
   </si>
   <si>
     <t xml:space="preserve">9.17517185211182</t>
@@ -2768,58 +2768,58 @@
     <t xml:space="preserve">9.39446449279785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83304786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58744049072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40323543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36814880371094</t>
+    <t xml:space="preserve">9.83304691314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58744144439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40323638916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36815071105957</t>
   </si>
   <si>
     <t xml:space="preserve">9.35937786102295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53481197357178</t>
+    <t xml:space="preserve">9.53481101989746</t>
   </si>
   <si>
     <t xml:space="preserve">9.46463775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50849533081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41200733184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38569164276123</t>
+    <t xml:space="preserve">9.50849628448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41200828552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38569259643555</t>
   </si>
   <si>
     <t xml:space="preserve">9.61375617980957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49972438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03482532501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74533081054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90322303771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0961971282959</t>
+    <t xml:space="preserve">9.49972343444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03482437133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74533176422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90322208404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0961980819702</t>
   </si>
   <si>
     <t xml:space="preserve">10.1225118637085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93830871582031</t>
+    <t xml:space="preserve">9.93830680847168</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638660430908</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">9.44709396362305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82427597045898</t>
+    <t xml:space="preserve">9.8242769241333</t>
   </si>
   <si>
     <t xml:space="preserve">9.56989765167236</t>
@@ -2846,28 +2846,28 @@
     <t xml:space="preserve">8.94710922241211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16639995574951</t>
+    <t xml:space="preserve">9.1663990020752</t>
   </si>
   <si>
     <t xml:space="preserve">9.28920364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2716588973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34183406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19271659851074</t>
+    <t xml:space="preserve">9.27166080474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34183502197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19271564483643</t>
   </si>
   <si>
     <t xml:space="preserve">9.18394374847412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90324974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06991195678711</t>
+    <t xml:space="preserve">8.90325164794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06991100311279</t>
   </si>
   <si>
     <t xml:space="preserve">8.84184837341309</t>
@@ -2879,22 +2879,22 @@
     <t xml:space="preserve">8.97342300415039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18857192993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.198073387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1890983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43138885498047</t>
+    <t xml:space="preserve">9.18857097625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19807243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18909931182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43138980865479</t>
   </si>
   <si>
     <t xml:space="preserve">9.5749683380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7275218963623</t>
+    <t xml:space="preserve">9.72752285003662</t>
   </si>
   <si>
     <t xml:space="preserve">9.79931163787842</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">9.79033756256104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74547004699707</t>
+    <t xml:space="preserve">9.74546909332275</t>
   </si>
   <si>
     <t xml:space="preserve">9.68265438079834</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">9.70060157775879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52112674713135</t>
+    <t xml:space="preserve">9.52112579345703</t>
   </si>
   <si>
     <t xml:space="preserve">9.51215362548828</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">9.35062599182129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53009986877441</t>
+    <t xml:space="preserve">9.53010082244873</t>
   </si>
   <si>
     <t xml:space="preserve">9.63778495788574</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">9.60188961029053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55702114105225</t>
+    <t xml:space="preserve">9.55702209472656</t>
   </si>
   <si>
     <t xml:space="preserve">9.54804801940918</t>
@@ -2960,19 +2960,19 @@
     <t xml:space="preserve">9.35960006713867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76341724395752</t>
+    <t xml:space="preserve">9.76341819763184</t>
   </si>
   <si>
     <t xml:space="preserve">9.64675903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29678344726562</t>
+    <t xml:space="preserve">9.29678249359131</t>
   </si>
   <si>
     <t xml:space="preserve">9.33267784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38652038574219</t>
+    <t xml:space="preserve">9.3865213394165</t>
   </si>
   <si>
     <t xml:space="preserve">9.39549541473389</t>
@@ -2981,10 +2981,10 @@
     <t xml:space="preserve">9.7723913192749</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8890495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3915786743164</t>
+    <t xml:space="preserve">9.88905048370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3915777206421</t>
   </si>
   <si>
     <t xml:space="preserve">10.5800266265869</t>
@@ -2999,49 +2999,49 @@
     <t xml:space="preserve">10.7415542602539</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8582134246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9389762878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9838438034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0556344985962</t>
+    <t xml:space="preserve">10.8582124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9389753341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9838447570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0556354522705</t>
   </si>
   <si>
     <t xml:space="preserve">11.1005029678345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0915288925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1274242401123</t>
+    <t xml:space="preserve">11.0915298461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.127423286438</t>
   </si>
   <si>
     <t xml:space="preserve">11.019739151001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9300022125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312902450562</t>
+    <t xml:space="preserve">10.9300031661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312911987305</t>
   </si>
   <si>
     <t xml:space="preserve">11.0376873016357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0107669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9748706817627</t>
+    <t xml:space="preserve">11.0107660293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9748697280884</t>
   </si>
   <si>
     <t xml:space="preserve">10.8761596679688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.912055015564</t>
+    <t xml:space="preserve">10.9120540618896</t>
   </si>
   <si>
     <t xml:space="preserve">11.0466604232788</t>
@@ -3050,49 +3050,49 @@
     <t xml:space="preserve">10.9210271835327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8941068649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9030799865723</t>
+    <t xml:space="preserve">10.8941078186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9030818939209</t>
   </si>
   <si>
     <t xml:space="preserve">10.8043699264526</t>
   </si>
   <si>
-    <t xml:space="preserve">10.75950050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7864236831665</t>
+    <t xml:space="preserve">10.7595014572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7864227294922</t>
   </si>
   <si>
     <t xml:space="preserve">10.8402643203735</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4274730682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2569732666016</t>
+    <t xml:space="preserve">10.4274740219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2569723129272</t>
   </si>
   <si>
     <t xml:space="preserve">9.90699768066406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96083927154541</t>
+    <t xml:space="preserve">9.96084022521973</t>
   </si>
   <si>
     <t xml:space="preserve">10.1223659515381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1313400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1403150558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0954446792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87110137939453</t>
+    <t xml:space="preserve">10.1313409805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1403141021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0954456329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87110233306885</t>
   </si>
   <si>
     <t xml:space="preserve">9.80828666687012</t>
@@ -3104,19 +3104,19 @@
     <t xml:space="preserve">9.47625827789307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67368030548096</t>
+    <t xml:space="preserve">9.67367839813232</t>
   </si>
   <si>
     <t xml:space="preserve">9.70957469940186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75444316864014</t>
+    <t xml:space="preserve">9.75444412231445</t>
   </si>
   <si>
     <t xml:space="preserve">9.84418106079102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85315418243408</t>
+    <t xml:space="preserve">9.8531551361084</t>
   </si>
   <si>
     <t xml:space="preserve">9.82623291015625</t>
@@ -3125,13 +3125,13 @@
     <t xml:space="preserve">9.86212825775146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0236549377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96981239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1672353744507</t>
+    <t xml:space="preserve">10.0236558914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96981334686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1672344207764</t>
   </si>
   <si>
     <t xml:space="preserve">10.1492881774902</t>
@@ -3143,13 +3143,13 @@
     <t xml:space="preserve">10.1851825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2838935852051</t>
+    <t xml:space="preserve">10.2838945388794</t>
   </si>
   <si>
     <t xml:space="preserve">10.3377361297607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4454212188721</t>
+    <t xml:space="preserve">10.4454202651978</t>
   </si>
   <si>
     <t xml:space="preserve">10.5172109603882</t>
@@ -3161,10 +3161,10 @@
     <t xml:space="preserve">10.3018417358398</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4184999465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4364461898804</t>
+    <t xml:space="preserve">10.4184989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.436448097229</t>
   </si>
   <si>
     <t xml:space="preserve">10.7774496078491</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">10.7684745788574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5620784759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0864715576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2479991912842</t>
+    <t xml:space="preserve">10.5620794296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0864706039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2479982376099</t>
   </si>
   <si>
     <t xml:space="preserve">10.4902896881104</t>
@@ -3197,28 +3197,28 @@
     <t xml:space="preserve">10.8671855926514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1453704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9658975601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9569234848022</t>
+    <t xml:space="preserve">11.1453714370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9658966064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9569225311279</t>
   </si>
   <si>
     <t xml:space="preserve">11.082555770874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1094779968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1722927093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2440814971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2261352539062</t>
+    <t xml:space="preserve">11.1094770431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1722917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2440824508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2261362075806</t>
   </si>
   <si>
     <t xml:space="preserve">11.1902408599854</t>
@@ -3230,10 +3230,10 @@
     <t xml:space="preserve">11.6299524307251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8004531860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0068492889404</t>
+    <t xml:space="preserve">11.8004541397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0068502426147</t>
   </si>
   <si>
     <t xml:space="preserve">11.6568746566772</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">11.3248462677002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2620306015015</t>
+    <t xml:space="preserve">11.2620315551758</t>
   </si>
   <si>
     <t xml:space="preserve">11.1363983154297</t>
@@ -3263,43 +3263,43 @@
     <t xml:space="preserve">10.3287630081177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.373631477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.544132232666</t>
+    <t xml:space="preserve">10.5351581573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3736305236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5441312789917</t>
   </si>
   <si>
     <t xml:space="preserve">10.7056589126587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6159229278564</t>
+    <t xml:space="preserve">10.6159210205078</t>
   </si>
   <si>
     <t xml:space="preserve">10.4095258712769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7146329879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6248960494995</t>
+    <t xml:space="preserve">10.7146320343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6248950958252</t>
   </si>
   <si>
     <t xml:space="preserve">10.4005517959595</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6069469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44933700561523</t>
+    <t xml:space="preserve">10.6069478988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44933605194092</t>
   </si>
   <si>
     <t xml:space="preserve">8.81668853759766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01354026794434</t>
+    <t xml:space="preserve">8.01354122161865</t>
   </si>
   <si>
     <t xml:space="preserve">8.0225133895874</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">8.15712070465088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48914909362793</t>
+    <t xml:space="preserve">8.4891471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.20198822021484</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">8.96924209594727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01859664916992</t>
+    <t xml:space="preserve">9.01859855651855</t>
   </si>
   <si>
     <t xml:space="preserve">9.1083345413208</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">9.13525676727295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98270320892334</t>
+    <t xml:space="preserve">8.98270416259766</t>
   </si>
   <si>
     <t xml:space="preserve">8.79874134063721</t>
@@ -3350,43 +3350,43 @@
     <t xml:space="preserve">8.90642642974854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34165287017822</t>
+    <t xml:space="preserve">9.34165191650391</t>
   </si>
   <si>
     <t xml:space="preserve">9.25191497802734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08141326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97373008728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.036545753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83014965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43979263305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26480484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36351490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27377796173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30967330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35005474090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36800193786621</t>
+    <t xml:space="preserve">9.08141422271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97372913360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03654479980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83015060424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43979072570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26480579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36351585388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27377891540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30967426300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35005569458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36800289154053</t>
   </si>
   <si>
     <t xml:space="preserve">8.51606941223145</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">8.70900440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57439804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45773887634277</t>
+    <t xml:space="preserve">8.5743989944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45773983001709</t>
   </si>
   <si>
     <t xml:space="preserve">8.46671485900879</t>
@@ -3422,22 +3422,22 @@
     <t xml:space="preserve">8.25134372711182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12571144104004</t>
+    <t xml:space="preserve">8.12571239471436</t>
   </si>
   <si>
     <t xml:space="preserve">8.88399124145508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65573215484619</t>
+    <t xml:space="preserve">9.65573310852051</t>
   </si>
   <si>
     <t xml:space="preserve">9.6856861114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58440971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63044357299805</t>
+    <t xml:space="preserve">9.5844087600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63044452667236</t>
   </si>
   <si>
     <t xml:space="preserve">9.87903022766113</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">9.98030757904053</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0355491638184</t>
+    <t xml:space="preserve">10.035548210144</t>
   </si>
   <si>
     <t xml:space="preserve">9.89744472503662</t>
@@ -3476,10 +3476,10 @@
     <t xml:space="preserve">9.40027046203613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22533893585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4463062286377</t>
+    <t xml:space="preserve">9.22533988952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44630527496338</t>
   </si>
   <si>
     <t xml:space="preserve">8.87087249755859</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">8.95833873748779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98596000671387</t>
+    <t xml:space="preserve">8.98595905303955</t>
   </si>
   <si>
     <t xml:space="preserve">9.02278614044189</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">8.67292404174805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77419853210449</t>
+    <t xml:space="preserve">8.77419948577881</t>
   </si>
   <si>
     <t xml:space="preserve">8.73737239837646</t>
@@ -3515,10 +3515,10 @@
     <t xml:space="preserve">8.53482055664062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52561283111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30464744567871</t>
+    <t xml:space="preserve">8.52561378479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30464649200439</t>
   </si>
   <si>
     <t xml:space="preserve">8.35988807678223</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">8.80642414093018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08263206481934</t>
+    <t xml:space="preserve">9.08263111114502</t>
   </si>
   <si>
     <t xml:space="preserve">8.85706233978271</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">8.60847568511963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90309619903564</t>
+    <t xml:space="preserve">8.90309715270996</t>
   </si>
   <si>
     <t xml:space="preserve">9.00437259674072</t>
@@ -3551,7 +3551,7 @@
     <t xml:space="preserve">9.06882190704346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10564994812012</t>
+    <t xml:space="preserve">9.1056489944458</t>
   </si>
   <si>
     <t xml:space="preserve">9.14247703552246</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">8.71895790100098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86166572570801</t>
+    <t xml:space="preserve">8.86166477203369</t>
   </si>
   <si>
     <t xml:space="preserve">9.17470169067383</t>
@@ -3572,10 +3572,10 @@
     <t xml:space="preserve">9.47392654418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59361553192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64885711669922</t>
+    <t xml:space="preserve">9.5936164855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64885807037354</t>
   </si>
   <si>
     <t xml:space="preserve">9.77775478363037</t>
@@ -3590,10 +3590,10 @@
     <t xml:space="preserve">9.7593412399292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73171901702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66727161407471</t>
+    <t xml:space="preserve">9.73171997070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66727066040039</t>
   </si>
   <si>
     <t xml:space="preserve">9.37265014648438</t>
@@ -3605,28 +3605,28 @@
     <t xml:space="preserve">9.21613311767578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84325122833252</t>
+    <t xml:space="preserve">8.84325218200684</t>
   </si>
   <si>
     <t xml:space="preserve">9.00897598266602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92611312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59466457366943</t>
+    <t xml:space="preserve">8.92611408233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59466552734375</t>
   </si>
   <si>
     <t xml:space="preserve">8.56244087219238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57164764404297</t>
+    <t xml:space="preserve">8.57164859771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.44275093078613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38750839233398</t>
+    <t xml:space="preserve">8.38750743865967</t>
   </si>
   <si>
     <t xml:space="preserve">8.45195770263672</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">8.12511157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23559474945068</t>
+    <t xml:space="preserve">8.23559379577637</t>
   </si>
   <si>
     <t xml:space="preserve">8.23099040985107</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">8.76959609985352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75578689575195</t>
+    <t xml:space="preserve">8.75578594207764</t>
   </si>
   <si>
     <t xml:space="preserve">8.7926139831543</t>
@@ -3662,10 +3662,10 @@
     <t xml:space="preserve">8.31385326385498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33226776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2171802520752</t>
+    <t xml:space="preserve">8.33226680755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21718120574951</t>
   </si>
   <si>
     <t xml:space="preserve">8.09749126434326</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">7.83049011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82588720321655</t>
+    <t xml:space="preserve">7.82588624954224</t>
   </si>
   <si>
     <t xml:space="preserve">7.49443769454956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82128238677979</t>
+    <t xml:space="preserve">7.8212833404541</t>
   </si>
   <si>
     <t xml:space="preserve">7.9731969833374</t>
@@ -3698,10 +3698,10 @@
     <t xml:space="preserve">8.31845664978027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2217845916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34147548675537</t>
+    <t xml:space="preserve">8.22178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34147453308105</t>
   </si>
   <si>
     <t xml:space="preserve">8.30924987792969</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">8.29543972015381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68213176727295</t>
+    <t xml:space="preserve">8.68213081359863</t>
   </si>
   <si>
     <t xml:space="preserve">8.47037124633789</t>
@@ -3728,13 +3728,13 @@
     <t xml:space="preserve">8.90770053863525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91690826416016</t>
+    <t xml:space="preserve">8.91690731048584</t>
   </si>
   <si>
     <t xml:space="preserve">8.97214889526367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79721736907959</t>
+    <t xml:space="preserve">8.79721832275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.19311428070068</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">9.74092674255371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80537509918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0723752975464</t>
+    <t xml:space="preserve">9.80537605285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0723762512207</t>
   </si>
   <si>
     <t xml:space="preserve">10.219687461853</t>
@@ -3767,34 +3767,34 @@
     <t xml:space="preserve">10.7260675430298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6892404556274</t>
+    <t xml:space="preserve">10.6892395019531</t>
   </si>
   <si>
     <t xml:space="preserve">10.7444820404053</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5143089294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2381019592285</t>
+    <t xml:space="preserve">10.514307975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2381010055542</t>
   </si>
   <si>
     <t xml:space="preserve">10.3393774032593</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2841348648071</t>
+    <t xml:space="preserve">10.2841358184814</t>
   </si>
   <si>
     <t xml:space="preserve">10.3209638595581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1368255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1828594207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3485841751099</t>
+    <t xml:space="preserve">10.1368246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1828584671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3485832214355</t>
   </si>
   <si>
     <t xml:space="preserve">10.192066192627</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">10.0815830230713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90665149688721</t>
+    <t xml:space="preserve">9.90665245056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.85140991210938</t>
@@ -3818,7 +3818,7 @@
     <t xml:space="preserve">9.75013446807861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65806484222412</t>
+    <t xml:space="preserve">9.6580638885498</t>
   </si>
   <si>
     <t xml:space="preserve">9.60282325744629</t>
@@ -3836,7 +3836,7 @@
     <t xml:space="preserve">10.146032333374</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1276168823242</t>
+    <t xml:space="preserve">10.1276178359985</t>
   </si>
   <si>
     <t xml:space="preserve">10.2473077774048</t>
@@ -3845,10 +3845,10 @@
     <t xml:space="preserve">10.4866886138916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5327215194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.772102355957</t>
+    <t xml:space="preserve">10.5327224731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7721014022827</t>
   </si>
   <si>
     <t xml:space="preserve">10.6800336837769</t>
@@ -3875,13 +3875,13 @@
     <t xml:space="preserve">11.3889665603638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7940721511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1163129806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2912454605103</t>
+    <t xml:space="preserve">11.7940711975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1163139343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2912464141846</t>
   </si>
   <si>
     <t xml:space="preserve">12.3372802734375</t>
@@ -3896,16 +3896,16 @@
     <t xml:space="preserve">12.0886926651001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8585195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.318865776062</t>
+    <t xml:space="preserve">11.8585205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3188667297363</t>
   </si>
   <si>
     <t xml:space="preserve">12.3649015426636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2820377349854</t>
+    <t xml:space="preserve">12.2820386886597</t>
   </si>
   <si>
     <t xml:space="preserve">12.2083826065063</t>
@@ -3929,10 +3929,10 @@
     <t xml:space="preserve">13.4789390563965</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1290760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5950736999512</t>
+    <t xml:space="preserve">13.129075050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5950746536255</t>
   </si>
   <si>
     <t xml:space="preserve">12.8252477645874</t>
@@ -3953,13 +3953,13 @@
     <t xml:space="preserve">12.0058307647705</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9137601852417</t>
+    <t xml:space="preserve">11.913761138916</t>
   </si>
   <si>
     <t xml:space="preserve">12.171555519104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0518655776978</t>
+    <t xml:space="preserve">12.0518646240234</t>
   </si>
   <si>
     <t xml:space="preserve">12.2267961502075</t>
@@ -3971,19 +3971,19 @@
     <t xml:space="preserve">12.3280735015869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9966239929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9321756362915</t>
+    <t xml:space="preserve">11.9966230392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9321746826172</t>
   </si>
   <si>
     <t xml:space="preserve">12.4293489456177</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7700042724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2728319168091</t>
+    <t xml:space="preserve">12.7700052261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2728309631348</t>
   </si>
   <si>
     <t xml:space="preserve">12.5674524307251</t>
@@ -4013,7 +4013,7 @@
     <t xml:space="preserve">12.650315284729</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0738344192505</t>
+    <t xml:space="preserve">13.0738334655762</t>
   </si>
   <si>
     <t xml:space="preserve">13.2855939865112</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">13.1751108169556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2119388580322</t>
+    <t xml:space="preserve">13.2119379043579</t>
   </si>
   <si>
     <t xml:space="preserve">13.1659030914307</t>
@@ -71899,7 +71899,7 @@
     </row>
     <row r="2534">
       <c r="A2534" s="1" t="n">
-        <v>46007.6912268518</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2534" t="n">
         <v>288733</v>
@@ -71920,6 +71920,32 @@
         <v>1896</v>
       </c>
       <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.69125</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>295099</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>9.15999984741211</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>9.23999977111816</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>9.21500015258789</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>1871</v>
+      </c>
+      <c r="H2535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="1899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1900" uniqueCount="1900">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16937828063965</t>
+    <t xml:space="preserve">7.16937780380249</t>
   </si>
   <si>
     <t xml:space="preserve">BRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13994932174683</t>
+    <t xml:space="preserve">7.13994884490967</t>
   </si>
   <si>
     <t xml:space="preserve">6.92740106582642</t>
@@ -53,37 +53,37 @@
     <t xml:space="preserve">6.52519750595093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54154586791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42873382568359</t>
+    <t xml:space="preserve">6.54154682159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42873334884644</t>
   </si>
   <si>
     <t xml:space="preserve">6.60040712356567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78188705444336</t>
+    <t xml:space="preserve">6.78188848495483</t>
   </si>
   <si>
     <t xml:space="preserve">6.55135679244995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21291589736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19820261001587</t>
+    <t xml:space="preserve">6.21291637420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19820117950439</t>
   </si>
   <si>
     <t xml:space="preserve">6.27504539489746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94641542434692</t>
+    <t xml:space="preserve">5.94641590118408</t>
   </si>
   <si>
     <t xml:space="preserve">6.20310688018799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24888563156128</t>
+    <t xml:space="preserve">6.24888610839844</t>
   </si>
   <si>
     <t xml:space="preserve">6.30610942840576</t>
@@ -92,76 +92,76 @@
     <t xml:space="preserve">6.31919002532959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38785839080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23090076446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16713619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05922794342041</t>
+    <t xml:space="preserve">6.38785934448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23090028762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16713714599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05922746658325</t>
   </si>
   <si>
     <t xml:space="preserve">5.99219417572021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86466503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70443868637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35945796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5164155960083</t>
+    <t xml:space="preserve">5.86466598510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70443725585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35945844650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51641511917114</t>
   </si>
   <si>
     <t xml:space="preserve">5.72242307662964</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67500877380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73223352432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03960847854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97420978546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11972236633301</t>
+    <t xml:space="preserve">5.67500925064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73223257064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0396089553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97420930862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11972284317017</t>
   </si>
   <si>
     <t xml:space="preserve">6.14097738265991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10010290145874</t>
+    <t xml:space="preserve">6.10010242462158</t>
   </si>
   <si>
     <t xml:space="preserve">6.23744058609009</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11154747009277</t>
+    <t xml:space="preserve">6.11154794692993</t>
   </si>
   <si>
     <t xml:space="preserve">5.97584438323975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07394361495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12953233718872</t>
+    <t xml:space="preserve">6.07394313812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12953281402588</t>
   </si>
   <si>
     <t xml:space="preserve">6.2194561958313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35188961029053</t>
+    <t xml:space="preserve">6.35189008712769</t>
   </si>
   <si>
     <t xml:space="preserve">6.32409477233887</t>
@@ -170,100 +170,100 @@
     <t xml:space="preserve">7.04675579071045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08272552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1170597076416</t>
+    <t xml:space="preserve">7.08272504806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11705923080444</t>
   </si>
   <si>
     <t xml:space="preserve">7.07945442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12032842636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07128000259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06637525558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16120338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14321994781494</t>
+    <t xml:space="preserve">7.1203293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07127952575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06637477874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1612024307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14321899414062</t>
   </si>
   <si>
     <t xml:space="preserve">7.24949216842651</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14158344268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22987127304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07618427276611</t>
+    <t xml:space="preserve">7.14158487319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22987174987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0761833190918</t>
   </si>
   <si>
     <t xml:space="preserve">7.26911163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15302848815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15139293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31489181518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43097591400146</t>
+    <t xml:space="preserve">7.15302753448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15139389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31489133834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43097496032715</t>
   </si>
   <si>
     <t xml:space="preserve">7.40318012237549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35576438903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14485359191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18899917602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16283845901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2740159034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998706817627</t>
+    <t xml:space="preserve">7.35576486587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1448540687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18899774551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16283893585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27401685714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998611450195</t>
   </si>
   <si>
     <t xml:space="preserve">7.35740089416504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40644979476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42279863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39337205886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43915128707886</t>
+    <t xml:space="preserve">7.40645027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42279958724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39337110519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43914985656738</t>
   </si>
   <si>
     <t xml:space="preserve">7.47184991836548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51108837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76778030395508</t>
+    <t xml:space="preserve">7.51108980178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76777982711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.71546125411987</t>
@@ -272,31 +272,31 @@
     <t xml:space="preserve">7.63534641265869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68276262283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74162101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66968154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.721999168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63044261932373</t>
+    <t xml:space="preserve">7.68276166915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74162149429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66968107223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72200059890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63044166564941</t>
   </si>
   <si>
     <t xml:space="preserve">7.71055603027344</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85606813430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47736167907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50188636779785</t>
+    <t xml:space="preserve">7.85606861114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47735977172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50188732147217</t>
   </si>
   <si>
     <t xml:space="preserve">8.51006031036377</t>
@@ -305,52 +305,52 @@
     <t xml:space="preserve">8.55093479156494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42831230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36291313171387</t>
+    <t xml:space="preserve">8.42831134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36291217803955</t>
   </si>
   <si>
     <t xml:space="preserve">8.35473728179932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41196250915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45348167419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51161003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46178531646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47008895874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61125946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63617134094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72751426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96002578735352</t>
+    <t xml:space="preserve">8.41196346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51991367340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45348262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51161193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4617862701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47008991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6112585067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6361722946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72751522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96002769470215</t>
   </si>
   <si>
     <t xml:space="preserve">8.86868381500244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86037826538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58634567260742</t>
+    <t xml:space="preserve">8.86037921905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58634662628174</t>
   </si>
   <si>
     <t xml:space="preserve">8.27577590942383</t>
@@ -359,16 +359,16 @@
     <t xml:space="preserve">8.10969638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30400943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3123140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60295295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61956310272217</t>
+    <t xml:space="preserve">8.30400848388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31231307983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60295391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61956214904785</t>
   </si>
   <si>
     <t xml:space="preserve">8.56973838806152</t>
@@ -377,43 +377,43 @@
     <t xml:space="preserve">8.71920967102051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25917053222656</t>
+    <t xml:space="preserve">8.25916767120361</t>
   </si>
   <si>
     <t xml:space="preserve">7.64134931564331</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25418567657471</t>
+    <t xml:space="preserve">8.25418472290039</t>
   </si>
   <si>
     <t xml:space="preserve">8.05987167358398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20602130889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23757553100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84728908538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6795482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67788696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95524024963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02831745147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05488967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97849178314209</t>
+    <t xml:space="preserve">8.20602226257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23757743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84728813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67954778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67788791656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95524263381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02831649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05488872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97849225997925</t>
   </si>
   <si>
     <t xml:space="preserve">8.14457321166992</t>
@@ -422,40 +422,40 @@
     <t xml:space="preserve">8.11301708221436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23425674438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10471439361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21100425720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16782379150391</t>
+    <t xml:space="preserve">8.23425579071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10471343994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21100521087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16782474517822</t>
   </si>
   <si>
     <t xml:space="preserve">8.32061862945557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37044143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50330543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36213684082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67768955230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76903533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53652191162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55313014984131</t>
+    <t xml:space="preserve">8.37044239044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50330448150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36213779449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67769145965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76903438568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53652095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55312919616699</t>
   </si>
   <si>
     <t xml:space="preserve">8.64447498321533</t>
@@ -464,31 +464,31 @@
     <t xml:space="preserve">8.73581790924072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68599510192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74412250518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66938781738281</t>
+    <t xml:space="preserve">8.68599414825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7441234588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66938591003418</t>
   </si>
   <si>
     <t xml:space="preserve">8.48669815063477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44517803192139</t>
+    <t xml:space="preserve">8.4451789855957</t>
   </si>
   <si>
     <t xml:space="preserve">8.4783935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40365695953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42856979370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65277767181396</t>
+    <t xml:space="preserve">8.40365791320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42856884002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65277862548828</t>
   </si>
   <si>
     <t xml:space="preserve">8.69429874420166</t>
@@ -506,16 +506,16 @@
     <t xml:space="preserve">8.88529014587402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78564357757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80224990844727</t>
+    <t xml:space="preserve">8.78564167022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8022518157959</t>
   </si>
   <si>
     <t xml:space="preserve">8.81885814666748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90190029144287</t>
+    <t xml:space="preserve">8.90189838409424</t>
   </si>
   <si>
     <t xml:space="preserve">9.05137062072754</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">8.81055450439453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62786483764648</t>
+    <t xml:space="preserve">8.6278657913208</t>
   </si>
   <si>
     <t xml:space="preserve">8.70260143280029</t>
@@ -539,85 +539,85 @@
     <t xml:space="preserve">9.04306697845459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14271354675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28388404846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35031414031982</t>
+    <t xml:space="preserve">9.14271545410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2838830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35031509399414</t>
   </si>
   <si>
     <t xml:space="preserve">9.35861968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15102005004883</t>
+    <t xml:space="preserve">9.15102100372314</t>
   </si>
   <si>
     <t xml:space="preserve">8.93511390686035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77733898162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19253826141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44996547698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17593193054199</t>
+    <t xml:space="preserve">8.7773380279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19254112243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44996356964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17593097686768</t>
   </si>
   <si>
     <t xml:space="preserve">9.00154685974121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13441181182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91850662231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92681217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00985145568848</t>
+    <t xml:space="preserve">9.1344108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91850757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92681121826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00985050201416</t>
   </si>
   <si>
     <t xml:space="preserve">8.984938621521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76072978973389</t>
+    <t xml:space="preserve">8.7607307434082</t>
   </si>
   <si>
     <t xml:space="preserve">9.1178035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.225754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95172309875488</t>
+    <t xml:space="preserve">9.22575569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95172119140625</t>
   </si>
   <si>
     <t xml:space="preserve">9.06797981262207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0762825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20084285736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31709861755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36692428588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49148368835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54961204528809</t>
+    <t xml:space="preserve">9.07628345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20084190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31709957122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36692237854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49148273468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54961109161377</t>
   </si>
   <si>
     <t xml:space="preserve">9.96481132507324</t>
@@ -626,97 +626,97 @@
     <t xml:space="preserve">10.0229396820068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82364368438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93989944458008</t>
+    <t xml:space="preserve">9.82364273071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93989849090576</t>
   </si>
   <si>
     <t xml:space="preserve">9.98141956329346</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0063323974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0561571121216</t>
+    <t xml:space="preserve">10.0063333511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0561561584473</t>
   </si>
   <si>
     <t xml:space="preserve">10.2056293487549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.230541229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2139320373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.197322845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1558036804199</t>
+    <t xml:space="preserve">10.2305402755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2139310836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1973237991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1558046340942</t>
   </si>
   <si>
     <t xml:space="preserve">10.1225891113281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.180718421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.147500038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2222356796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1308917999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0976753234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84855651855469</t>
+    <t xml:space="preserve">10.1807165145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1475009918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2222375869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1308927536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0976762771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84855556488037</t>
   </si>
   <si>
     <t xml:space="preserve">10.3135805130005</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0810680389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0727634429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5294847488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4464435577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5211820602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.38831615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4713563919067</t>
+    <t xml:space="preserve">10.0810689926147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0727624893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.529483795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4464445114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5211801528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3883180618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4713573455811</t>
   </si>
   <si>
     <t xml:space="preserve">10.6872615814209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.720477104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540441513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4049253463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6457424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7952117919922</t>
+    <t xml:space="preserve">10.7204761505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4049243927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6457395553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7952136993408</t>
   </si>
   <si>
     <t xml:space="preserve">10.96129322052</t>
@@ -725,76 +725,76 @@
     <t xml:space="preserve">10.9280776977539</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7703018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7786045074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8699474334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7869100570679</t>
+    <t xml:space="preserve">10.770299911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7786064147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8699493408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7869081497192</t>
   </si>
   <si>
     <t xml:space="preserve">11.0360288619995</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8948612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0443334579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2519330978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1771965026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2270212173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2602376937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2851514816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3432788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.393102645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.451229095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5093584060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5010538101196</t>
+    <t xml:space="preserve">10.8948621749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0443325042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2519340515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1771974563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2270202636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2602367401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2851495742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3432769775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3931016921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4512300491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5093564987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5010547637939</t>
   </si>
   <si>
     <t xml:space="preserve">11.5176630020142</t>
   </si>
   <si>
-    <t xml:space="preserve">11.741870880127</t>
+    <t xml:space="preserve">11.7418699264526</t>
   </si>
   <si>
     <t xml:space="preserve">11.7584781646729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6920471191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6837406158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7252635955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7667818069458</t>
+    <t xml:space="preserve">11.6920461654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6837425231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7252626419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7667827606201</t>
   </si>
   <si>
     <t xml:space="preserve">11.7169589996338</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">11.5923976898193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7003498077393</t>
+    <t xml:space="preserve">11.7003507614136</t>
   </si>
   <si>
     <t xml:space="preserve">11.542573928833</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">11.9577751159668</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0574216842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9162549972534</t>
+    <t xml:space="preserve">12.0574235916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9162559509277</t>
   </si>
   <si>
     <t xml:space="preserve">11.9909906387329</t>
@@ -827,79 +827,76 @@
     <t xml:space="preserve">12.1487674713135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0491189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2899351119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3895826339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3148469924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5058403015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5390548706055</t>
+    <t xml:space="preserve">12.0491180419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2899360656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3895816802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3148460388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5058393478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5390558242798</t>
   </si>
   <si>
     <t xml:space="preserve">12.2733278274536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1902875900269</t>
+    <t xml:space="preserve">12.1902856826782</t>
   </si>
   <si>
     <t xml:space="preserve">12.1985912322998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0823354721069</t>
+    <t xml:space="preserve">12.0823345184326</t>
   </si>
   <si>
     <t xml:space="preserve">11.6422214508057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5508766174316</t>
+    <t xml:space="preserve">11.5508785247803</t>
   </si>
   <si>
     <t xml:space="preserve">11.8083009719849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9346389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9514837265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0609769821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1620464324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.783034324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6566982269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8083019256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7577676773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5977401733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5640506744385</t>
+    <t xml:space="preserve">11.9346399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9514827728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0609760284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1620454788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7830333709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6566963195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7577667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5977411270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5640497207642</t>
   </si>
   <si>
     <t xml:space="preserve">11.3029546737671</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2018842697144</t>
+    <t xml:space="preserve">11.20188331604</t>
   </si>
   <si>
     <t xml:space="preserve">11.1934614181519</t>
@@ -911,22 +908,22 @@
     <t xml:space="preserve">10.9576330184937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2355737686157</t>
+    <t xml:space="preserve">11.2355728149414</t>
   </si>
   <si>
     <t xml:space="preserve">11.4208679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2271528244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2861080169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.168194770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9239435195923</t>
+    <t xml:space="preserve">11.2271518707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2861089706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1681938171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9239416122437</t>
   </si>
   <si>
     <t xml:space="preserve">11.0250120162964</t>
@@ -941,19 +938,19 @@
     <t xml:space="preserve">10.5786209106445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7891826629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7386493682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6544246673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7554941177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4292907714844</t>
+    <t xml:space="preserve">10.7891845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7386474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6544237136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7554922103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4292917251587</t>
   </si>
   <si>
     <t xml:space="preserve">11.5219383239746</t>
@@ -962,13 +959,13 @@
     <t xml:space="preserve">11.2945308685303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.639853477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4629812240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4124450683594</t>
+    <t xml:space="preserve">11.6398515701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4629802703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4124460220337</t>
   </si>
   <si>
     <t xml:space="preserve">11.3619108200073</t>
@@ -980,34 +977,34 @@
     <t xml:space="preserve">11.2103071212769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9997434616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9913215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0081663131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8902521133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9323654174805</t>
+    <t xml:space="preserve">10.9997444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.991322517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0081672668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8902530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9323663711548</t>
   </si>
   <si>
     <t xml:space="preserve">10.8734073638916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8818302154541</t>
+    <t xml:space="preserve">10.8818311691284</t>
   </si>
   <si>
     <t xml:space="preserve">10.6796903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7807607650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8649873733521</t>
+    <t xml:space="preserve">10.78076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8649854660034</t>
   </si>
   <si>
     <t xml:space="preserve">10.7049579620361</t>
@@ -1016,25 +1013,25 @@
     <t xml:space="preserve">10.9155216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2608413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1513500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0839681625366</t>
+    <t xml:space="preserve">11.2608404159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.151349067688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0839700698853</t>
   </si>
   <si>
     <t xml:space="preserve">11.0502805709839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2524194717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3282203674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.378755569458</t>
+    <t xml:space="preserve">11.252420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.328221321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3787565231323</t>
   </si>
   <si>
     <t xml:space="preserve">11.395601272583</t>
@@ -1043,109 +1040,109 @@
     <t xml:space="preserve">11.5050926208496</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4040241241455</t>
+    <t xml:space="preserve">11.4040231704712</t>
   </si>
   <si>
     <t xml:space="preserve">11.555627822876</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6819639205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7493448257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9177942276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8841037750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9430618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0525541305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0946664810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1536235809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0357084274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0778207778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0441312789917</t>
+    <t xml:space="preserve">11.6819658279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7493438720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9177951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8841047286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9430627822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0525531768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0946655273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1536245346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0357093811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0778198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.044132232666</t>
   </si>
   <si>
     <t xml:space="preserve">12.1788902282715</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1704683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3136501312256</t>
+    <t xml:space="preserve">12.1704692840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3136491775513</t>
   </si>
   <si>
     <t xml:space="preserve">12.3220729827881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3726072311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2041568756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2883815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2968053817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7914552688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7325010299683</t>
+    <t xml:space="preserve">12.3726081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2041578292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2883834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2968063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7914571762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7324991226196</t>
   </si>
   <si>
     <t xml:space="preserve">11.8167247772217</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0104417800903</t>
+    <t xml:space="preserve">12.010440826416</t>
   </si>
   <si>
     <t xml:space="preserve">12.0020189285278</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9683303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9262170791626</t>
+    <t xml:space="preserve">11.9683284759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9262161254883</t>
   </si>
   <si>
     <t xml:space="preserve">11.3113765716553</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8144512176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6965351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8986740112305</t>
+    <t xml:space="preserve">10.8144502639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6965360641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8986749649048</t>
   </si>
   <si>
     <t xml:space="preserve">10.8228731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0165901184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.940788269043</t>
+    <t xml:space="preserve">11.0165910720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9407863616943</t>
   </si>
   <si>
     <t xml:space="preserve">10.7723379135132</t>
@@ -1154,22 +1151,22 @@
     <t xml:space="preserve">10.7976045608521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7302255630493</t>
+    <t xml:space="preserve">10.7302265167236</t>
   </si>
   <si>
     <t xml:space="preserve">10.7218027114868</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6628465652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6123113632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8060274124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6881141662598</t>
+    <t xml:space="preserve">10.6628475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6123123168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8060283660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6881132125854</t>
   </si>
   <si>
     <t xml:space="preserve">10.8312959671021</t>
@@ -1187,7 +1184,7 @@
     <t xml:space="preserve">11.0923910140991</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1597728729248</t>
+    <t xml:space="preserve">11.1597719192505</t>
   </si>
   <si>
     <t xml:space="preserve">11.1345043182373</t>
@@ -1196,7 +1193,7 @@
     <t xml:space="preserve">11.1429271697998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187299728394</t>
+    <t xml:space="preserve">11.2187280654907</t>
   </si>
   <si>
     <t xml:space="preserve">11.4545583724976</t>
@@ -1205,7 +1202,7 @@
     <t xml:space="preserve">11.345067024231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4270172119141</t>
+    <t xml:space="preserve">10.4270181655884</t>
   </si>
   <si>
     <t xml:space="preserve">10.3175249099731</t>
@@ -1220,19 +1217,19 @@
     <t xml:space="preserve">10.1911869049072</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1574983596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2248773574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1659212112427</t>
+    <t xml:space="preserve">10.1574974060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2248783111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1659202575684</t>
   </si>
   <si>
     <t xml:space="preserve">10.1069622039795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0985403060913</t>
+    <t xml:space="preserve">10.0985412597656</t>
   </si>
   <si>
     <t xml:space="preserve">9.93009090423584</t>
@@ -1244,16 +1241,16 @@
     <t xml:space="preserve">10.0058937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71953010559082</t>
+    <t xml:space="preserve">9.7195291519165</t>
   </si>
   <si>
     <t xml:space="preserve">9.68583965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4837007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37420749664307</t>
+    <t xml:space="preserve">9.48369979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37420845031738</t>
   </si>
   <si>
     <t xml:space="preserve">10.115385055542</t>
@@ -1265,52 +1262,52 @@
     <t xml:space="preserve">10.5954666137695</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7133798599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6038885116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.359637260437</t>
+    <t xml:space="preserve">10.7133817672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.603889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3596363067627</t>
   </si>
   <si>
     <t xml:space="preserve">10.3006801605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4522848129272</t>
+    <t xml:space="preserve">10.4522829055786</t>
   </si>
   <si>
     <t xml:space="preserve">10.4017496109009</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5617780685425</t>
+    <t xml:space="preserve">10.5617771148682</t>
   </si>
   <si>
     <t xml:space="preserve">10.5449314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3427934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4101705551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4185934066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4354400634766</t>
+    <t xml:space="preserve">10.342791557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438629150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4101715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4185943603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4354391098022</t>
   </si>
   <si>
     <t xml:space="preserve">10.2585678100586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2333002090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.29225730896</t>
+    <t xml:space="preserve">10.2332983016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2922582626343</t>
   </si>
   <si>
     <t xml:space="preserve">10.149076461792</t>
@@ -1319,25 +1316,25 @@
     <t xml:space="preserve">11.0418586730957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.536509513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.275411605835</t>
+    <t xml:space="preserve">10.5365104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2754135131836</t>
   </si>
   <si>
     <t xml:space="preserve">10.2080326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0648517608643</t>
+    <t xml:space="preserve">10.0648498535156</t>
   </si>
   <si>
     <t xml:space="preserve">9.93851375579834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.050085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3848028182983</t>
+    <t xml:space="preserve">10.0500869750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.384801864624</t>
   </si>
   <si>
     <t xml:space="preserve">10.3075609207153</t>
@@ -1346,16 +1343,16 @@
     <t xml:space="preserve">10.771014213562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.676607131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5993642807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.230318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4706268310547</t>
+    <t xml:space="preserve">10.6766080856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.599365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2303190231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4706287384033</t>
   </si>
   <si>
     <t xml:space="preserve">10.504958152771</t>
@@ -1376,55 +1373,55 @@
     <t xml:space="preserve">10.93408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6508598327637</t>
+    <t xml:space="preserve">10.6508588790894</t>
   </si>
   <si>
     <t xml:space="preserve">10.7452669143677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5307054519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3933849334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3504724502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1444931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1359119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92134952545166</t>
+    <t xml:space="preserve">10.530704498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.393385887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.350471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1444940567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.135910987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92135047912598</t>
   </si>
   <si>
     <t xml:space="preserve">10.0758333206177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.058669090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89560222625732</t>
+    <t xml:space="preserve">10.0586700439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89560127258301</t>
   </si>
   <si>
     <t xml:space="preserve">9.947096824646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74111747741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76686573028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85268688201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8784351348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99000930786133</t>
+    <t xml:space="preserve">9.74111652374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76686477661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85268783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87843704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99001026153564</t>
   </si>
   <si>
     <t xml:space="preserve">10.2560653686523</t>
@@ -1439,10 +1436,10 @@
     <t xml:space="preserve">10.5135402679443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.48779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.436297416687</t>
+    <t xml:space="preserve">10.4877939224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4362983703613</t>
   </si>
   <si>
     <t xml:space="preserve">10.3333072662354</t>
@@ -1454,28 +1451,28 @@
     <t xml:space="preserve">10.1273288726807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0157556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0329208374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84410572052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0415029525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2389001846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78402900695801</t>
+    <t xml:space="preserve">10.0157566070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0329217910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84410762786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.04150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2389011383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78402805328369</t>
   </si>
   <si>
     <t xml:space="preserve">9.706787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77544689178467</t>
+    <t xml:space="preserve">9.77544593811035</t>
   </si>
   <si>
     <t xml:space="preserve">9.68103885650635</t>
@@ -1487,46 +1484,46 @@
     <t xml:space="preserve">9.59521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.689621925354</t>
+    <t xml:space="preserve">9.68962383270264</t>
   </si>
   <si>
     <t xml:space="preserve">9.47505950927734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48364162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62954425811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91276550292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88701915740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75828075408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56946754455566</t>
+    <t xml:space="preserve">9.483642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62954521179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91276454925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88701820373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75828170776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56946659088135</t>
   </si>
   <si>
     <t xml:space="preserve">9.578049659729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73253440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61237907409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71536922454834</t>
+    <t xml:space="preserve">9.73253536224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.612380027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71537017822266</t>
   </si>
   <si>
     <t xml:space="preserve">9.82694149017334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.187406539917</t>
+    <t xml:space="preserve">10.1874055862427</t>
   </si>
   <si>
     <t xml:space="preserve">10.2217359542847</t>
@@ -1544,10 +1541,10 @@
     <t xml:space="preserve">9.69820404052734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86127185821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52655601501465</t>
+    <t xml:space="preserve">9.86127281188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52655410766602</t>
   </si>
   <si>
     <t xml:space="preserve">9.21758556365967</t>
@@ -1562,16 +1559,16 @@
     <t xml:space="preserve">8.52669525146484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4408712387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12331962585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43228912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5224027633667</t>
+    <t xml:space="preserve">8.44087028503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12332057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43228816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52240467071533</t>
   </si>
   <si>
     <t xml:space="preserve">8.41083240509033</t>
@@ -1580,40 +1577,40 @@
     <t xml:space="preserve">8.29926109313965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16623115539551</t>
+    <t xml:space="preserve">8.16623210906982</t>
   </si>
   <si>
     <t xml:space="preserve">8.23060035705566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08469867706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35504627227783</t>
+    <t xml:space="preserve">8.08469676971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35504722595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.22630882263184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48378372192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39366626739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57819080352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49236679077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44945430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23489284515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11473751068115</t>
+    <t xml:space="preserve">8.48378467559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39366817474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57818984985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49236583709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44945335388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23489189147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11473655700684</t>
   </si>
   <si>
     <t xml:space="preserve">8.02033042907715</t>
@@ -1622,40 +1619,40 @@
     <t xml:space="preserve">7.79289293289185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72852563858032</t>
+    <t xml:space="preserve">7.72852516174316</t>
   </si>
   <si>
     <t xml:space="preserve">7.77143621444702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83151435852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00316429138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02891159057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00745487213135</t>
+    <t xml:space="preserve">7.83151340484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00316333770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02891063690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00745582580566</t>
   </si>
   <si>
     <t xml:space="preserve">8.25205612182617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28638648986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61681079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60822868347168</t>
+    <t xml:space="preserve">8.28638553619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61681175231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60823059082031</t>
   </si>
   <si>
     <t xml:space="preserve">8.54815101623535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75413036346436</t>
+    <t xml:space="preserve">8.75413131713867</t>
   </si>
   <si>
     <t xml:space="preserve">8.48807430267334</t>
@@ -1670,73 +1667,73 @@
     <t xml:space="preserve">8.19197845458984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98170709609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08899021148682</t>
+    <t xml:space="preserve">7.98170804977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08898830413818</t>
   </si>
   <si>
     <t xml:space="preserve">8.33788108825684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81435108184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69848728179932</t>
+    <t xml:space="preserve">7.81434917449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69848585128784</t>
   </si>
   <si>
     <t xml:space="preserve">7.99887371063232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81864070892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8658447265625</t>
+    <t xml:space="preserve">7.81864166259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86584424972534</t>
   </si>
   <si>
     <t xml:space="preserve">7.58691358566284</t>
   </si>
   <si>
-    <t xml:space="preserve">7.634117603302</t>
+    <t xml:space="preserve">7.63411808013916</t>
   </si>
   <si>
     <t xml:space="preserve">7.68990325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65986585617065</t>
+    <t xml:space="preserve">7.65986442565918</t>
   </si>
   <si>
     <t xml:space="preserve">7.96454381942749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93879652023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73696613311768</t>
+    <t xml:space="preserve">7.938796043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73696708679199</t>
   </si>
   <si>
     <t xml:space="preserve">8.82279014587402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.385085105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40224838256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45374488830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36791896820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49665641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50094890594482</t>
+    <t xml:space="preserve">8.47949314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38508415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40224933624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45374393463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.367919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.496657371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50094795227051</t>
   </si>
   <si>
     <t xml:space="preserve">8.46661853790283</t>
@@ -1745,7 +1742,7 @@
     <t xml:space="preserve">8.59964752197266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85712051391602</t>
+    <t xml:space="preserve">8.85712146759033</t>
   </si>
   <si>
     <t xml:space="preserve">8.56960868835449</t>
@@ -1754,7 +1751,7 @@
     <t xml:space="preserve">8.56531715393066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55673313140869</t>
+    <t xml:space="preserve">8.55673408508301</t>
   </si>
   <si>
     <t xml:space="preserve">8.53956985473633</t>
@@ -1778,22 +1775,22 @@
     <t xml:space="preserve">8.58248138427734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77129554748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65972423553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09743022918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96869277954102</t>
+    <t xml:space="preserve">8.77129650115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65972328186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09743118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96869373321533</t>
   </si>
   <si>
     <t xml:space="preserve">9.020188331604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28624534606934</t>
+    <t xml:space="preserve">9.28624439239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.31199264526367</t>
@@ -1802,13 +1799,13 @@
     <t xml:space="preserve">9.08026504516602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13175964355469</t>
+    <t xml:space="preserve">9.131760597229</t>
   </si>
   <si>
     <t xml:space="preserve">9.32057476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94294548034668</t>
+    <t xml:space="preserve">8.94294738769531</t>
   </si>
   <si>
     <t xml:space="preserve">8.814208984375</t>
@@ -1817,40 +1814,40 @@
     <t xml:space="preserve">8.78846073150635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79704475402832</t>
+    <t xml:space="preserve">8.79704570770264</t>
   </si>
   <si>
     <t xml:space="preserve">8.74554920196533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72838401794434</t>
+    <t xml:space="preserve">8.72838497161865</t>
   </si>
   <si>
     <t xml:space="preserve">8.908616065979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14034271240234</t>
+    <t xml:space="preserve">9.14034366607666</t>
   </si>
   <si>
     <t xml:space="preserve">9.42356586456299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26049709320068</t>
+    <t xml:space="preserve">9.260498046875</t>
   </si>
   <si>
     <t xml:space="preserve">9.18325519561768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00302314758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96011161804199</t>
+    <t xml:space="preserve">9.00302410125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96011066436768</t>
   </si>
   <si>
     <t xml:space="preserve">8.76271343231201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65114116668701</t>
+    <t xml:space="preserve">8.65114212036133</t>
   </si>
   <si>
     <t xml:space="preserve">8.685471534729</t>
@@ -1871,31 +1868,34 @@
     <t xml:space="preserve">9.41498279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64670944213867</t>
+    <t xml:space="preserve">9.64670848846436</t>
   </si>
   <si>
     <t xml:space="preserve">10.0672512054443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.195987701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80977725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62096118927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50938987731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86570453643799</t>
+    <t xml:space="preserve">9.93851470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1959886550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80977630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62096214294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50938892364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86570358276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.95152759552002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83995628356934</t>
+    <t xml:space="preserve">8.83995532989502</t>
   </si>
   <si>
     <t xml:space="preserve">8.75851726531982</t>
@@ -1907,10 +1907,10 @@
     <t xml:space="preserve">8.74097347259521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42080879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53483867645264</t>
+    <t xml:space="preserve">8.42080783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53484058380127</t>
   </si>
   <si>
     <t xml:space="preserve">8.57869911193848</t>
@@ -1919,22 +1919,22 @@
     <t xml:space="preserve">8.58746910095215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47343826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55238342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42957878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18397235870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37694931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56992721557617</t>
+    <t xml:space="preserve">8.47343635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55238246917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42957973480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18397331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37695026397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56992530822754</t>
   </si>
   <si>
     <t xml:space="preserve">8.67957305908203</t>
@@ -1943,22 +1943,22 @@
     <t xml:space="preserve">8.66202831268311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8944787979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75413131713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72781753540039</t>
+    <t xml:space="preserve">8.89447975158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75413227081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72781658172607</t>
   </si>
   <si>
     <t xml:space="preserve">8.72343063354492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93833637237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82430553436279</t>
+    <t xml:space="preserve">8.9383373260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82430458068848</t>
   </si>
   <si>
     <t xml:space="preserve">9.0611400604248</t>
@@ -1970,16 +1970,16 @@
     <t xml:space="preserve">8.85062026977539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71465873718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88570690155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11377048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05236911773682</t>
+    <t xml:space="preserve">8.71465969085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88570785522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0523681640625</t>
   </si>
   <si>
     <t xml:space="preserve">9.28043174743652</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">8.80676174163818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78921890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49536895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45589542388916</t>
+    <t xml:space="preserve">8.78921985626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49536800384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45589447021484</t>
   </si>
   <si>
     <t xml:space="preserve">8.48221015930176</t>
@@ -2015,10 +2015,10 @@
     <t xml:space="preserve">8.92079448699951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07868385314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01728248596191</t>
+    <t xml:space="preserve">9.0786828994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01728057861328</t>
   </si>
   <si>
     <t xml:space="preserve">8.17958641052246</t>
@@ -2027,19 +2027,19 @@
     <t xml:space="preserve">8.1313419342041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17081451416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96029567718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77170467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61819934844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64890050888062</t>
+    <t xml:space="preserve">8.17081642150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96029472351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77170419692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61819982528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64889907836914</t>
   </si>
   <si>
     <t xml:space="preserve">7.63135719299316</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">7.38574981689453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29803371429443</t>
+    <t xml:space="preserve">7.29803466796875</t>
   </si>
   <si>
     <t xml:space="preserve">7.39013624191284</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">7.20593118667603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28049039840698</t>
+    <t xml:space="preserve">7.28048992156982</t>
   </si>
   <si>
     <t xml:space="preserve">7.27171802520752</t>
@@ -2069,16 +2069,16 @@
     <t xml:space="preserve">7.512939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39890813827515</t>
+    <t xml:space="preserve">7.39890718460083</t>
   </si>
   <si>
     <t xml:space="preserve">7.26733207702637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19277334213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44276666641235</t>
+    <t xml:space="preserve">7.19277286529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44276571273804</t>
   </si>
   <si>
     <t xml:space="preserve">7.4515380859375</t>
@@ -2087,16 +2087,16 @@
     <t xml:space="preserve">7.32873392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53048372268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79363346099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98661136627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0611686706543</t>
+    <t xml:space="preserve">7.53048229217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79363393783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98660945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06116771697998</t>
   </si>
   <si>
     <t xml:space="preserve">8.22344589233398</t>
@@ -2108,13 +2108,13 @@
     <t xml:space="preserve">8.35063552856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21905994415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19274425506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30239009857178</t>
+    <t xml:space="preserve">8.21905899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1927433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30239105224609</t>
   </si>
   <si>
     <t xml:space="preserve">7.87257814407349</t>
@@ -2123,49 +2123,49 @@
     <t xml:space="preserve">7.72346019744873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60942840576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74100255966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83310556411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84187698364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67521524429321</t>
+    <t xml:space="preserve">7.60942888259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74100303649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83310604095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84187793731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67521476745605</t>
   </si>
   <si>
     <t xml:space="preserve">7.50855445861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40329456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45592403411865</t>
+    <t xml:space="preserve">7.40329313278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45592451095581</t>
   </si>
   <si>
     <t xml:space="preserve">7.44715213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31557607650757</t>
+    <t xml:space="preserve">7.31557703018188</t>
   </si>
   <si>
     <t xml:space="preserve">7.47346687316895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85064935684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85942029953003</t>
+    <t xml:space="preserve">7.85064888000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85942077636719</t>
   </si>
   <si>
     <t xml:space="preserve">8.00854015350342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04362678527832</t>
+    <t xml:space="preserve">8.043625831604</t>
   </si>
   <si>
     <t xml:space="preserve">7.80679035186768</t>
@@ -2177,52 +2177,52 @@
     <t xml:space="preserve">8.18835926055908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25414752960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29361915588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36379241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65325736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3725643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43835067749023</t>
+    <t xml:space="preserve">8.25414657592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29361820220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36379146575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65325832366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37256336212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43835163116455</t>
   </si>
   <si>
     <t xml:space="preserve">8.9646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12254238128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14885711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37691974639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56112670898438</t>
+    <t xml:space="preserve">9.12254333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1488561630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37692070007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56112575531006</t>
   </si>
   <si>
     <t xml:space="preserve">9.75410270690918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70147228240967</t>
+    <t xml:space="preserve">9.70147323608398</t>
   </si>
   <si>
     <t xml:space="preserve">9.47340965270996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35060405731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49095249176025</t>
+    <t xml:space="preserve">9.35060501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49095153808594</t>
   </si>
   <si>
     <t xml:space="preserve">9.24534511566162</t>
@@ -2240,13 +2240,13 @@
     <t xml:space="preserve">9.64884281158447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72778701782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80673217773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77164745330811</t>
+    <t xml:space="preserve">9.72778797149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80673313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77164649963379</t>
   </si>
   <si>
     <t xml:space="preserve">9.85936260223389</t>
@@ -2255,19 +2255,19 @@
     <t xml:space="preserve">9.815505027771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86813449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92076396942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99971008300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87690734863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84181976318359</t>
+    <t xml:space="preserve">9.86813354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9207649230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99970817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8769063949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84182071685791</t>
   </si>
   <si>
     <t xml:space="preserve">9.89444923400879</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">9.9821662902832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0698823928833</t>
+    <t xml:space="preserve">10.069881439209</t>
   </si>
   <si>
     <t xml:space="preserve">9.96462249755859</t>
@@ -2285,25 +2285,25 @@
     <t xml:space="preserve">9.67515754699707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71901702880859</t>
+    <t xml:space="preserve">9.71901512145996</t>
   </si>
   <si>
     <t xml:space="preserve">9.79796123504639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29797554016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52603912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63129901885986</t>
+    <t xml:space="preserve">9.29797649383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52603816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63129997253418</t>
   </si>
   <si>
     <t xml:space="preserve">9.71024513244629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68392848968506</t>
+    <t xml:space="preserve">9.68392944335938</t>
   </si>
   <si>
     <t xml:space="preserve">9.69270038604736</t>
@@ -2315,10 +2315,10 @@
     <t xml:space="preserve">9.73655891418457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57866859436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30674839019775</t>
+    <t xml:space="preserve">9.57866954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30674743652344</t>
   </si>
   <si>
     <t xml:space="preserve">9.21025848388672</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">9.02605438232422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26288986206055</t>
+    <t xml:space="preserve">9.26288890838623</t>
   </si>
   <si>
     <t xml:space="preserve">9.13131332397461</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">9.43832302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42955017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21902942657471</t>
+    <t xml:space="preserve">9.42955112457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21903038024902</t>
   </si>
   <si>
     <t xml:space="preserve">9.25411701202393</t>
@@ -2363,13 +2363,13 @@
     <t xml:space="preserve">8.39449214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33747673034668</t>
+    <t xml:space="preserve">8.33747577667236</t>
   </si>
   <si>
     <t xml:space="preserve">8.34186267852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10502815246582</t>
+    <t xml:space="preserve">8.1050271987915</t>
   </si>
   <si>
     <t xml:space="preserve">7.92959356307983</t>
@@ -2378,34 +2378,34 @@
     <t xml:space="preserve">7.49978256225586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6006555557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42961025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11821413040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18400239944458</t>
+    <t xml:space="preserve">7.60065603256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42960929870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11821460723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18400192260742</t>
   </si>
   <si>
     <t xml:space="preserve">6.57875680923462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64892959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5568265914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14017200469971</t>
+    <t xml:space="preserve">6.64893007278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55682706832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14017295837402</t>
   </si>
   <si>
     <t xml:space="preserve">6.3857798576355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87702226638794</t>
+    <t xml:space="preserve">5.8770227432251</t>
   </si>
   <si>
     <t xml:space="preserve">5.97351026535034</t>
@@ -2426,58 +2426,58 @@
     <t xml:space="preserve">7.02172565460205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4734959602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31560516357422</t>
+    <t xml:space="preserve">6.47349548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31560611724854</t>
   </si>
   <si>
     <t xml:space="preserve">5.83316421508789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9603533744812</t>
+    <t xml:space="preserve">5.96035289764404</t>
   </si>
   <si>
     <t xml:space="preserve">5.85070705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61387205123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18406009674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4735255241394</t>
+    <t xml:space="preserve">5.61387252807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18406057357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47352457046509</t>
   </si>
   <si>
     <t xml:space="preserve">5.54369783401489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89895057678223</t>
+    <t xml:space="preserve">5.89895153045654</t>
   </si>
   <si>
     <t xml:space="preserve">5.82439231872559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64895868301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69720315933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92965269088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06122779846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00859785079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05684185028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40332269668579</t>
+    <t xml:space="preserve">5.64895820617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69720268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92965221405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06122732162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0085973739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0568413734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40332317352295</t>
   </si>
   <si>
     <t xml:space="preserve">6.59191370010376</t>
@@ -2486,25 +2486,25 @@
     <t xml:space="preserve">6.83752107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69717311859131</t>
+    <t xml:space="preserve">6.69717407226562</t>
   </si>
   <si>
     <t xml:space="preserve">6.86822175979614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81120586395264</t>
+    <t xml:space="preserve">6.81120538711548</t>
   </si>
   <si>
     <t xml:space="preserve">6.72348880767822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48665380477905</t>
+    <t xml:space="preserve">6.48665332794189</t>
   </si>
   <si>
     <t xml:space="preserve">6.4822678565979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36385059356689</t>
+    <t xml:space="preserve">6.36385011672974</t>
   </si>
   <si>
     <t xml:space="preserve">6.22789001464844</t>
@@ -2513,19 +2513,19 @@
     <t xml:space="preserve">5.77176237106323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82000637054443</t>
+    <t xml:space="preserve">5.82000684738159</t>
   </si>
   <si>
     <t xml:space="preserve">6.26297569274902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23227596282959</t>
+    <t xml:space="preserve">6.23227500915527</t>
   </si>
   <si>
     <t xml:space="preserve">6.21911764144897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39455032348633</t>
+    <t xml:space="preserve">6.39455080032349</t>
   </si>
   <si>
     <t xml:space="preserve">6.59629964828491</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">7.16207218170166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51732444763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37259340286255</t>
+    <t xml:space="preserve">7.51732492446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37259387969971</t>
   </si>
   <si>
     <t xml:space="preserve">7.33312034606934</t>
@@ -2546,55 +2546,55 @@
     <t xml:space="preserve">7.41645097732544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79802083969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68398714065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55679798126221</t>
+    <t xml:space="preserve">7.79801940917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6839861869812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55679845809937</t>
   </si>
   <si>
     <t xml:space="preserve">7.10067176818848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35504961013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35066413879395</t>
+    <t xml:space="preserve">7.35504913330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3506646156311</t>
   </si>
   <si>
     <t xml:space="preserve">7.21031665802002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23224639892578</t>
+    <t xml:space="preserve">7.23224592208862</t>
   </si>
   <si>
     <t xml:space="preserve">7.17523002624512</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10505723953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20154571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24540328979492</t>
+    <t xml:space="preserve">7.10505676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20154428482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24540281295776</t>
   </si>
   <si>
     <t xml:space="preserve">7.21470308303833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17084455490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40767955780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25856065750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36820650100708</t>
+    <t xml:space="preserve">7.17084407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40768003463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25856113433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3682074546814</t>
   </si>
   <si>
     <t xml:space="preserve">7.32434940338135</t>
@@ -2606,85 +2606,85 @@
     <t xml:space="preserve">7.24978876113892</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43838119506836</t>
+    <t xml:space="preserve">7.43838024139404</t>
   </si>
   <si>
     <t xml:space="preserve">7.16645812988281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70156002044678</t>
+    <t xml:space="preserve">6.70155954360962</t>
   </si>
   <si>
     <t xml:space="preserve">6.61384248733521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69278812408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75418996810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68401718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71033239364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83313512802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06119823455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1401424407959</t>
+    <t xml:space="preserve">6.69278717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75418949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68401622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71033143997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83313465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06119775772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14014291763306</t>
   </si>
   <si>
     <t xml:space="preserve">7.05681324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04804086685181</t>
+    <t xml:space="preserve">7.04804134368896</t>
   </si>
   <si>
     <t xml:space="preserve">7.00856828689575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94716739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07435655593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0875129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09628486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01733922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35943603515625</t>
+    <t xml:space="preserve">6.94716644287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07435607910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08751344680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09628534317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0173397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35943555831909</t>
   </si>
   <si>
     <t xml:space="preserve">7.29364824295044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4910101890564</t>
+    <t xml:space="preserve">7.49101066589355</t>
   </si>
   <si>
     <t xml:space="preserve">7.60504198074341</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9734525680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57434034347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41206550598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88576507568359</t>
+    <t xml:space="preserve">7.97345304489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57434129714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41206502914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88576459884644</t>
   </si>
   <si>
     <t xml:space="preserve">6.99102544784546</t>
@@ -2693,85 +2693,85 @@
     <t xml:space="preserve">7.0392689704895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06996965408325</t>
+    <t xml:space="preserve">7.06997013092041</t>
   </si>
   <si>
     <t xml:space="preserve">7.31119203567505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48223924636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86380577087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92082166671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9997673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73661756515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68837356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61381387710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62697172164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57872676849365</t>
+    <t xml:space="preserve">7.48223972320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8638072013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92082262039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99976682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73661804199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68837404251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61381530761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62697076797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57872724533081</t>
   </si>
   <si>
     <t xml:space="preserve">7.77609014511108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80240440368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96906614303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99099493026733</t>
+    <t xml:space="preserve">7.802405834198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96906661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99099683761597</t>
   </si>
   <si>
     <t xml:space="preserve">8.15327167510986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54799747467041</t>
+    <t xml:space="preserve">8.54799652099609</t>
   </si>
   <si>
     <t xml:space="preserve">7.56995534896851</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82433366775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6664457321167</t>
+    <t xml:space="preserve">7.82433414459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66644430160522</t>
   </si>
   <si>
     <t xml:space="preserve">7.71907424926758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78486204147339</t>
+    <t xml:space="preserve">7.78486156463623</t>
   </si>
   <si>
     <t xml:space="preserve">7.86819267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22780132293701</t>
+    <t xml:space="preserve">9.22780227661133</t>
   </si>
   <si>
     <t xml:space="preserve">9.17517185211182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39446449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83304595947266</t>
+    <t xml:space="preserve">9.39446544647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83304786682129</t>
   </si>
   <si>
     <t xml:space="preserve">9.58744049072266</t>
@@ -2783,22 +2783,22 @@
     <t xml:space="preserve">9.36814975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35937690734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53481101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46463775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50849628448486</t>
+    <t xml:space="preserve">9.35937786102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53481197357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46463680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50849533081055</t>
   </si>
   <si>
     <t xml:space="preserve">9.41200733184814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38569164276123</t>
+    <t xml:space="preserve">9.38569259643555</t>
   </si>
   <si>
     <t xml:space="preserve">9.61375617980957</t>
@@ -2807,13 +2807,13 @@
     <t xml:space="preserve">9.49972438812256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482532501221</t>
+    <t xml:space="preserve">9.03482437133789</t>
   </si>
   <si>
     <t xml:space="preserve">9.74533176422119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90322208404541</t>
+    <t xml:space="preserve">9.90322303771973</t>
   </si>
   <si>
     <t xml:space="preserve">10.0961980819702</t>
@@ -2822,13 +2822,13 @@
     <t xml:space="preserve">10.1225128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.938307762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638660430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88567638397217</t>
+    <t xml:space="preserve">9.93830680847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6663875579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8856782913208</t>
   </si>
   <si>
     <t xml:space="preserve">9.45586490631104</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">9.51726722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44709300994873</t>
+    <t xml:space="preserve">9.44709396362305</t>
   </si>
   <si>
     <t xml:space="preserve">9.82427597045898</t>
@@ -2858,76 +2858,76 @@
     <t xml:space="preserve">9.27166080474854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34183406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19271564483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18394470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90324878692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06991291046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84184837341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9997386932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97342395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18857097625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.198073387146</t>
+    <t xml:space="preserve">9.34183502197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19271469116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18394374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90324974060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06991195678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8418493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99973773956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97342300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18857192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19807147979736</t>
   </si>
   <si>
     <t xml:space="preserve">9.1890983581543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43138885498047</t>
+    <t xml:space="preserve">9.43138980865479</t>
   </si>
   <si>
     <t xml:space="preserve">9.57496929168701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72752285003662</t>
+    <t xml:space="preserve">9.7275218963623</t>
   </si>
   <si>
     <t xml:space="preserve">9.79931259155273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81725978851318</t>
+    <t xml:space="preserve">9.81725883483887</t>
   </si>
   <si>
     <t xml:space="preserve">9.94289207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98776054382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79033851623535</t>
+    <t xml:space="preserve">9.98776149749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79033756256104</t>
   </si>
   <si>
     <t xml:space="preserve">9.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68265342712402</t>
+    <t xml:space="preserve">9.68265438079834</t>
   </si>
   <si>
     <t xml:space="preserve">9.70060157775879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52112674713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51215362548828</t>
+    <t xml:space="preserve">9.52112579345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51215267181396</t>
   </si>
   <si>
     <t xml:space="preserve">9.35062599182129</t>
@@ -2939,19 +2939,19 @@
     <t xml:space="preserve">9.63778495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61086463928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69162845611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5031795501709</t>
+    <t xml:space="preserve">9.61086368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69162750244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50317859649658</t>
   </si>
   <si>
     <t xml:space="preserve">9.58394336700439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60189056396484</t>
+    <t xml:space="preserve">9.60188961029053</t>
   </si>
   <si>
     <t xml:space="preserve">9.55702114105225</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">9.5480489730835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35960006713867</t>
+    <t xml:space="preserve">9.35960102081299</t>
   </si>
   <si>
     <t xml:space="preserve">9.76341724395752</t>
@@ -2969,73 +2969,73 @@
     <t xml:space="preserve">9.64675903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29678344726562</t>
+    <t xml:space="preserve">9.29678249359131</t>
   </si>
   <si>
     <t xml:space="preserve">9.33267784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3865213394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39549541473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7723913192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8890495300293</t>
+    <t xml:space="preserve">9.38652038574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39549446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77239227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88905048370361</t>
   </si>
   <si>
     <t xml:space="preserve">10.3915786743164</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5800256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6518154144287</t>
+    <t xml:space="preserve">10.5800266265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.651816368103</t>
   </si>
   <si>
     <t xml:space="preserve">10.6877107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7415542602539</t>
+    <t xml:space="preserve">10.7415533065796</t>
   </si>
   <si>
     <t xml:space="preserve">10.8582124710083</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9389753341675</t>
+    <t xml:space="preserve">10.9389743804932</t>
   </si>
   <si>
     <t xml:space="preserve">10.9838438034058</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0556335449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1005020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0915288925171</t>
+    <t xml:space="preserve">11.0556344985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1005029678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0915298461914</t>
   </si>
   <si>
     <t xml:space="preserve">11.127423286438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.019739151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9300012588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312902450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376863479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0107650756836</t>
+    <t xml:space="preserve">11.0197401046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9300022125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0107660293579</t>
   </si>
   <si>
     <t xml:space="preserve">10.9748697280884</t>
@@ -3044,34 +3044,34 @@
     <t xml:space="preserve">10.8761587142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9120540618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0466613769531</t>
+    <t xml:space="preserve">10.912055015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0466604232788</t>
   </si>
   <si>
     <t xml:space="preserve">10.921028137207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8941068649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9030799865723</t>
+    <t xml:space="preserve">10.8941078186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9030818939209</t>
   </si>
   <si>
     <t xml:space="preserve">10.8043699264526</t>
   </si>
   <si>
-    <t xml:space="preserve">10.75950050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7864217758179</t>
+    <t xml:space="preserve">10.7595014572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7864227294922</t>
   </si>
   <si>
     <t xml:space="preserve">10.8402643203735</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4274730682373</t>
+    <t xml:space="preserve">10.427472114563</t>
   </si>
   <si>
     <t xml:space="preserve">10.2569723129272</t>
@@ -3080,13 +3080,13 @@
     <t xml:space="preserve">9.90699672698975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96083927154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1223669052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1313400268555</t>
+    <t xml:space="preserve">9.96084022521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1223659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1313409805298</t>
   </si>
   <si>
     <t xml:space="preserve">10.1403141021729</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">9.87110233306885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80828666687012</t>
+    <t xml:space="preserve">9.8082857131958</t>
   </si>
   <si>
     <t xml:space="preserve">9.56599617004395</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">9.67368030548096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70957469940186</t>
+    <t xml:space="preserve">9.70957374572754</t>
   </si>
   <si>
     <t xml:space="preserve">9.75444412231445</t>
@@ -3122,34 +3122,34 @@
     <t xml:space="preserve">9.85315418243408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82623386383057</t>
+    <t xml:space="preserve">9.82623291015625</t>
   </si>
   <si>
     <t xml:space="preserve">9.86212825775146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0236558914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96981334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1672353744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492872238159</t>
+    <t xml:space="preserve">10.0236549377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96981239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1672344207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492881774902</t>
   </si>
   <si>
     <t xml:space="preserve">10.2031297683716</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1851825714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2838935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3377361297607</t>
+    <t xml:space="preserve">10.1851835250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2838945388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3377370834351</t>
   </si>
   <si>
     <t xml:space="preserve">10.4454212188721</t>
@@ -3167,16 +3167,16 @@
     <t xml:space="preserve">10.4184989929199</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4364461898804</t>
+    <t xml:space="preserve">10.436448097229</t>
   </si>
   <si>
     <t xml:space="preserve">10.7774486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8492374420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6966857910156</t>
+    <t xml:space="preserve">10.8492393493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6966867446899</t>
   </si>
   <si>
     <t xml:space="preserve">10.7684745788574</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">10.2479991912842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.490288734436</t>
+    <t xml:space="preserve">10.4902896881104</t>
   </si>
   <si>
     <t xml:space="preserve">10.5979747772217</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">10.9658975601196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9569225311279</t>
+    <t xml:space="preserve">10.9569234848022</t>
   </si>
   <si>
     <t xml:space="preserve">11.082555770874</t>
@@ -3221,16 +3221,16 @@
     <t xml:space="preserve">11.2440824508667</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2261343002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1902408599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4594526290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6299524307251</t>
+    <t xml:space="preserve">11.2261362075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.190239906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.459451675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6299533843994</t>
   </si>
   <si>
     <t xml:space="preserve">11.8004531860352</t>
@@ -3239,22 +3239,22 @@
     <t xml:space="preserve">12.0068492889404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6568737030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8453216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2171611785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2081871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3248453140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2620296478271</t>
+    <t xml:space="preserve">11.6568746566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8453226089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2171621322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2081890106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3248462677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2620306015015</t>
   </si>
   <si>
     <t xml:space="preserve">11.1363973617554</t>
@@ -3275,40 +3275,40 @@
     <t xml:space="preserve">10.5441312789917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7056579589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6159219741821</t>
+    <t xml:space="preserve">10.705659866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6159210205078</t>
   </si>
   <si>
     <t xml:space="preserve">10.4095258712769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7146320343018</t>
+    <t xml:space="preserve">10.7146329879761</t>
   </si>
   <si>
     <t xml:space="preserve">10.6248950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4005517959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6069469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44933795928955</t>
+    <t xml:space="preserve">10.4005527496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6069478988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44933605194092</t>
   </si>
   <si>
     <t xml:space="preserve">8.81668853759766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01354122161865</t>
+    <t xml:space="preserve">8.01354026794434</t>
   </si>
   <si>
     <t xml:space="preserve">8.0225133895874</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1571216583252</t>
+    <t xml:space="preserve">8.15711975097656</t>
   </si>
   <si>
     <t xml:space="preserve">8.48914813995361</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">8.34556865692139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53850269317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67759704589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09038829803467</t>
+    <t xml:space="preserve">8.5385046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6775951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09038734436035</t>
   </si>
   <si>
     <t xml:space="preserve">8.96924209594727</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">9.1083345413208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18012523651123</t>
+    <t xml:space="preserve">9.18012428283691</t>
   </si>
   <si>
     <t xml:space="preserve">9.13525676727295</t>
@@ -3347,25 +3347,25 @@
     <t xml:space="preserve">8.98270320892334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79874229431152</t>
+    <t xml:space="preserve">8.79874134063721</t>
   </si>
   <si>
     <t xml:space="preserve">8.90642642974854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34165287017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25191593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08141422271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97373008728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.036545753479</t>
+    <t xml:space="preserve">9.34165191650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25191497802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08141326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97372913360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03654479980469</t>
   </si>
   <si>
     <t xml:space="preserve">8.83015060424805</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">8.26480484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36351585388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27377891540527</t>
+    <t xml:space="preserve">8.36351490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27377796173096</t>
   </si>
   <si>
     <t xml:space="preserve">8.30967330932617</t>
@@ -3395,16 +3395,16 @@
     <t xml:space="preserve">8.51606941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94232177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70900344848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5743989944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45773887634277</t>
+    <t xml:space="preserve">8.94232082366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70900535583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57439804077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45773983001709</t>
   </si>
   <si>
     <t xml:space="preserve">8.46671390533447</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">8.4936351776123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30070018768311</t>
+    <t xml:space="preserve">8.30069923400879</t>
   </si>
   <si>
     <t xml:space="preserve">8.18404102325439</t>
@@ -3428,22 +3428,22 @@
     <t xml:space="preserve">8.12571239471436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88399124145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65573310852051</t>
+    <t xml:space="preserve">8.88399028778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65573215484619</t>
   </si>
   <si>
     <t xml:space="preserve">9.6856861114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58440971374512</t>
+    <t xml:space="preserve">9.5844087600708</t>
   </si>
   <si>
     <t xml:space="preserve">9.63044357299805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87902927398682</t>
+    <t xml:space="preserve">9.87903022766113</t>
   </si>
   <si>
     <t xml:space="preserve">10.0539627075195</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">10.2104806900024</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95268726348877</t>
+    <t xml:space="preserve">9.95268630981445</t>
   </si>
   <si>
     <t xml:space="preserve">9.98030662536621</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">10.035548210144</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89744567871094</t>
+    <t xml:space="preserve">9.89744472503662</t>
   </si>
   <si>
     <t xml:space="preserve">10.0631694793701</t>
@@ -3470,13 +3470,13 @@
     <t xml:space="preserve">10.1184110641479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1552391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63965129852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40027046203613</t>
+    <t xml:space="preserve">10.1552381515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63965034484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40027141571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.22533893585205</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">9.44630527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87087249755859</t>
+    <t xml:space="preserve">8.87087345123291</t>
   </si>
   <si>
     <t xml:space="preserve">8.95833778381348</t>
@@ -3542,10 +3542,10 @@
     <t xml:space="preserve">8.82023525238037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60847568511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90309715270996</t>
+    <t xml:space="preserve">8.60847663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90309619903564</t>
   </si>
   <si>
     <t xml:space="preserve">9.00437259674072</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">9.06882190704346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10564994812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14247703552246</t>
+    <t xml:space="preserve">9.1056489944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14247798919678</t>
   </si>
   <si>
     <t xml:space="preserve">8.99976921081543</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">8.86166572570801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17470169067383</t>
+    <t xml:space="preserve">9.17470073699951</t>
   </si>
   <si>
     <t xml:space="preserve">9.47392654418945</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">9.75934028625488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73171901702881</t>
+    <t xml:space="preserve">9.73171997070312</t>
   </si>
   <si>
     <t xml:space="preserve">9.66727161407471</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">8.92611408233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59466457366943</t>
+    <t xml:space="preserve">8.59466361999512</t>
   </si>
   <si>
     <t xml:space="preserve">8.56244087219238</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">8.57164764404297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44275093078613</t>
+    <t xml:space="preserve">8.44274997711182</t>
   </si>
   <si>
     <t xml:space="preserve">8.38750839233398</t>
@@ -3635,10 +3635,10 @@
     <t xml:space="preserve">8.45195770263672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14352512359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12511157989502</t>
+    <t xml:space="preserve">8.14352607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1251106262207</t>
   </si>
   <si>
     <t xml:space="preserve">8.23559474945068</t>
@@ -3656,19 +3656,19 @@
     <t xml:space="preserve">8.75578594207764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7926139831543</t>
+    <t xml:space="preserve">8.79261302947998</t>
   </si>
   <si>
     <t xml:space="preserve">8.51640605926514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3138542175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33226776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2171802520752</t>
+    <t xml:space="preserve">8.31385326385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33226680755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21718120574951</t>
   </si>
   <si>
     <t xml:space="preserve">8.09749126434326</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">7.4944372177124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82128238677979</t>
+    <t xml:space="preserve">7.8212833404541</t>
   </si>
   <si>
     <t xml:space="preserve">7.97319746017456</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31845760345459</t>
+    <t xml:space="preserve">8.31845664978027</t>
   </si>
   <si>
     <t xml:space="preserve">8.2217845916748</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">8.30924987792969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29543972015381</t>
+    <t xml:space="preserve">8.29544067382812</t>
   </si>
   <si>
     <t xml:space="preserve">8.68213081359863</t>
@@ -3719,19 +3719,19 @@
     <t xml:space="preserve">8.47037124633789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61307811737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66371631622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73276805877686</t>
+    <t xml:space="preserve">8.61307907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66371726989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73276901245117</t>
   </si>
   <si>
     <t xml:space="preserve">8.90769958496094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91690731048584</t>
+    <t xml:space="preserve">8.91690635681152</t>
   </si>
   <si>
     <t xml:space="preserve">8.97214889526367</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">8.79721736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19311428070068</t>
+    <t xml:space="preserve">9.193115234375</t>
   </si>
   <si>
     <t xml:space="preserve">9.54758071899414</t>
@@ -3767,13 +3767,13 @@
     <t xml:space="preserve">10.8641719818115</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7260665893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6892404556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444829940796</t>
+    <t xml:space="preserve">10.7260675430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6892395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444820404053</t>
   </si>
   <si>
     <t xml:space="preserve">10.5143089294434</t>
@@ -3782,16 +3782,16 @@
     <t xml:space="preserve">10.2381010055542</t>
   </si>
   <si>
-    <t xml:space="preserve">10.339376449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841358184814</t>
+    <t xml:space="preserve">10.3393774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841348648071</t>
   </si>
   <si>
     <t xml:space="preserve">10.3209638595581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1368246078491</t>
+    <t xml:space="preserve">10.1368255615234</t>
   </si>
   <si>
     <t xml:space="preserve">10.1828603744507</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">10.3485841751099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1920652389526</t>
+    <t xml:space="preserve">10.192066192627</t>
   </si>
   <si>
     <t xml:space="preserve">10.0815830230713</t>
@@ -3821,10 +3821,10 @@
     <t xml:space="preserve">9.7501335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6580638885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60282325744629</t>
+    <t xml:space="preserve">9.65806484222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60282421112061</t>
   </si>
   <si>
     <t xml:space="preserve">9.48313331604004</t>
@@ -3842,10 +3842,10 @@
     <t xml:space="preserve">10.1276178359985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2473077774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4866886138916</t>
+    <t xml:space="preserve">10.2473087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4866876602173</t>
   </si>
   <si>
     <t xml:space="preserve">10.5327224731445</t>
@@ -3869,22 +3869,22 @@
     <t xml:space="preserve">10.6616201400757</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9286193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9654483795166</t>
+    <t xml:space="preserve">10.9286203384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9654474258423</t>
   </si>
   <si>
     <t xml:space="preserve">11.3889665603638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7940721511841</t>
+    <t xml:space="preserve">11.7940711975098</t>
   </si>
   <si>
     <t xml:space="preserve">12.1163129806519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2912454605103</t>
+    <t xml:space="preserve">12.2912464141846</t>
   </si>
   <si>
     <t xml:space="preserve">12.3372793197632</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">12.6779365539551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8620748519897</t>
+    <t xml:space="preserve">12.8620738983154</t>
   </si>
   <si>
     <t xml:space="preserve">13.7275247573853</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">12.5950736999512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8252468109131</t>
+    <t xml:space="preserve">12.8252477645874</t>
   </si>
   <si>
     <t xml:space="preserve">12.8896961212158</t>
@@ -3968,13 +3968,13 @@
     <t xml:space="preserve">12.2267961502075</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2175903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3280735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9966239929199</t>
+    <t xml:space="preserve">12.2175893783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3280725479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9966230392456</t>
   </si>
   <si>
     <t xml:space="preserve">11.9321756362915</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">12.7700052261353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2728319168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5674524307251</t>
+    <t xml:space="preserve">12.2728309631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5674533843994</t>
   </si>
   <si>
     <t xml:space="preserve">12.503005027771</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">12.4845905303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3096580505371</t>
+    <t xml:space="preserve">12.3096590042114</t>
   </si>
   <si>
     <t xml:space="preserve">12.024245262146</t>
@@ -4019,7 +4019,7 @@
     <t xml:space="preserve">13.0738334655762</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2855930328369</t>
+    <t xml:space="preserve">13.2855939865112</t>
   </si>
   <si>
     <t xml:space="preserve">13.2579717636108</t>
@@ -4034,7 +4034,7 @@
     <t xml:space="preserve">13.1659030914307</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3040065765381</t>
+    <t xml:space="preserve">13.3040075302124</t>
   </si>
   <si>
     <t xml:space="preserve">13.2947998046875</t>
@@ -5709,6 +5709,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44499969482422</t>
   </si>
 </sst>
 </file>
@@ -15529,7 +15532,7 @@
         <v>14.0055179595947</v>
       </c>
       <c r="G365" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -15555,7 +15558,7 @@
         <v>13.9455795288086</v>
       </c>
       <c r="G366" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -15581,7 +15584,7 @@
         <v>13.7557764053345</v>
       </c>
       <c r="G367" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -15607,7 +15610,7 @@
         <v>13.7158174514771</v>
       </c>
       <c r="G368" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -15633,7 +15636,7 @@
         <v>13.406138420105</v>
       </c>
       <c r="G369" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -15659,7 +15662,7 @@
         <v>13.2862615585327</v>
       </c>
       <c r="G370" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -15685,7 +15688,7 @@
         <v>13.2762718200684</v>
       </c>
       <c r="G371" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -15711,7 +15714,7 @@
         <v>13.0864677429199</v>
       </c>
       <c r="G372" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -15737,7 +15740,7 @@
         <v>12.996561050415</v>
       </c>
       <c r="G373" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -15763,7 +15766,7 @@
         <v>13.3262195587158</v>
       </c>
       <c r="G374" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -15789,7 +15792,7 @@
         <v>13.5459928512573</v>
       </c>
       <c r="G375" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -15815,7 +15818,7 @@
         <v>13.3162307739258</v>
       </c>
       <c r="G376" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15841,7 +15844,7 @@
         <v>13.386157989502</v>
       </c>
       <c r="G377" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -15867,7 +15870,7 @@
         <v>13.2463026046753</v>
       </c>
       <c r="G378" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -15893,7 +15896,7 @@
         <v>12.9566020965576</v>
       </c>
       <c r="G379" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -15919,7 +15922,7 @@
         <v>13.0764780044556</v>
       </c>
       <c r="G380" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -15945,7 +15948,7 @@
         <v>12.7667989730835</v>
       </c>
       <c r="G381" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -15971,7 +15974,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G382" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -15997,7 +16000,7 @@
         <v>12.547025680542</v>
       </c>
       <c r="G383" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -16023,7 +16026,7 @@
         <v>12.7967681884766</v>
       </c>
       <c r="G384" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -16049,7 +16052,7 @@
         <v>12.7368297576904</v>
       </c>
       <c r="G385" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -16075,7 +16078,7 @@
         <v>12.6369333267212</v>
       </c>
       <c r="G386" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -16101,7 +16104,7 @@
         <v>12.7568092346191</v>
       </c>
       <c r="G387" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -16127,7 +16130,7 @@
         <v>13.3262195587158</v>
       </c>
       <c r="G388" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -16153,7 +16156,7 @@
         <v>13.5559825897217</v>
       </c>
       <c r="G389" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -16179,7 +16182,7 @@
         <v>13.6658687591553</v>
       </c>
       <c r="G390" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -16205,7 +16208,7 @@
         <v>13.3961477279663</v>
       </c>
       <c r="G391" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -16231,7 +16234,7 @@
         <v>13.8057241439819</v>
       </c>
       <c r="G392" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -16257,7 +16260,7 @@
         <v>13.7557764053345</v>
       </c>
       <c r="G393" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -16283,7 +16286,7 @@
         <v>13.5459928512573</v>
       </c>
       <c r="G394" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -16309,7 +16312,7 @@
         <v>13.5959405899048</v>
       </c>
       <c r="G395" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -16335,7 +16338,7 @@
         <v>13.536003112793</v>
       </c>
       <c r="G396" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -16361,7 +16364,7 @@
         <v>13.4760646820068</v>
       </c>
       <c r="G397" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -16387,7 +16390,7 @@
         <v>13.5559825897217</v>
       </c>
       <c r="G398" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -16413,7 +16416,7 @@
         <v>13.2463026046753</v>
       </c>
       <c r="G399" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -16439,7 +16442,7 @@
         <v>13.4261169433594</v>
       </c>
       <c r="G400" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -16465,7 +16468,7 @@
         <v>13.2962512969971</v>
       </c>
       <c r="G401" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -16491,7 +16494,7 @@
         <v>13.2862615585327</v>
       </c>
       <c r="G402" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -16517,7 +16520,7 @@
         <v>13.2463026046753</v>
       </c>
       <c r="G403" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -16543,7 +16546,7 @@
         <v>13.0465087890625</v>
       </c>
       <c r="G404" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -16569,7 +16572,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G405" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -16595,7 +16598,7 @@
         <v>13.0365200042725</v>
       </c>
       <c r="G406" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -16621,7 +16624,7 @@
         <v>13.0564985275269</v>
       </c>
       <c r="G407" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -16647,7 +16650,7 @@
         <v>12.9166440963745</v>
       </c>
       <c r="G408" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -16673,7 +16676,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G409" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -16699,7 +16702,7 @@
         <v>12.966591835022</v>
       </c>
       <c r="G410" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -16725,7 +16728,7 @@
         <v>12.8966636657715</v>
       </c>
       <c r="G411" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -16751,7 +16754,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G412" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -16777,7 +16780,7 @@
         <v>12.9066543579102</v>
       </c>
       <c r="G413" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -16803,7 +16806,7 @@
         <v>12.6669015884399</v>
       </c>
       <c r="G414" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -16829,7 +16832,7 @@
         <v>12.7867784500122</v>
       </c>
       <c r="G415" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -16855,7 +16858,7 @@
         <v>12.8866748809814</v>
       </c>
       <c r="G416" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -16881,7 +16884,7 @@
         <v>12.7568092346191</v>
       </c>
       <c r="G417" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -16907,7 +16910,7 @@
         <v>12.7368297576904</v>
       </c>
       <c r="G418" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -16933,7 +16936,7 @@
         <v>12.696870803833</v>
       </c>
       <c r="G419" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -16959,7 +16962,7 @@
         <v>12.7667989730835</v>
       </c>
       <c r="G420" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -16985,7 +16988,7 @@
         <v>12.9466133117676</v>
       </c>
       <c r="G421" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -17011,7 +17014,7 @@
         <v>13.3561887741089</v>
       </c>
       <c r="G422" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -17037,7 +17040,7 @@
         <v>13.2263231277466</v>
       </c>
       <c r="G423" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -17063,7 +17066,7 @@
         <v>13.1464061737061</v>
       </c>
       <c r="G424" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -17089,7 +17092,7 @@
         <v>12.8966636657715</v>
       </c>
       <c r="G425" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -17115,7 +17118,7 @@
         <v>13.1064472198486</v>
       </c>
       <c r="G426" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -17141,7 +17144,7 @@
         <v>13.0864677429199</v>
       </c>
       <c r="G427" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -17167,7 +17170,7 @@
         <v>13.3461999893188</v>
       </c>
       <c r="G428" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -17193,7 +17196,7 @@
         <v>13.2862615585327</v>
       </c>
       <c r="G429" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -17219,7 +17222,7 @@
         <v>13.4361066818237</v>
       </c>
       <c r="G430" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -17245,7 +17248,7 @@
         <v>13.4960451126099</v>
       </c>
       <c r="G431" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -17271,7 +17274,7 @@
         <v>13.5160236358643</v>
       </c>
       <c r="G432" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -17297,7 +17300,7 @@
         <v>13.3961477279663</v>
       </c>
       <c r="G433" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -17323,7 +17326,7 @@
         <v>13.6458902359009</v>
       </c>
       <c r="G434" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -17349,7 +17352,7 @@
         <v>13.5160236358643</v>
       </c>
       <c r="G435" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -17375,7 +17378,7 @@
         <v>13.5260143280029</v>
       </c>
       <c r="G436" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -17401,7 +17404,7 @@
         <v>13.6658687591553</v>
       </c>
       <c r="G437" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -17427,7 +17430,7 @@
         <v>13.7058277130127</v>
       </c>
       <c r="G438" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -17453,7 +17456,7 @@
         <v>13.8556728363037</v>
       </c>
       <c r="G439" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -17505,7 +17508,7 @@
         <v>13.9355897903442</v>
       </c>
       <c r="G441" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -17531,7 +17534,7 @@
         <v>14.135383605957</v>
       </c>
       <c r="G442" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -17557,7 +17560,7 @@
         <v>14.135383605957</v>
       </c>
       <c r="G443" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -17583,7 +17586,7 @@
         <v>14.0954246520996</v>
       </c>
       <c r="G444" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -17609,7 +17612,7 @@
         <v>14.135383605957</v>
       </c>
       <c r="G445" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -17635,7 +17638,7 @@
         <v>14.1653528213501</v>
       </c>
       <c r="G446" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -17661,7 +17664,7 @@
         <v>14.2952184677124</v>
       </c>
       <c r="G447" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -17739,7 +17742,7 @@
         <v>14.3451671600342</v>
       </c>
       <c r="G450" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -17791,7 +17794,7 @@
         <v>14.4150943756104</v>
       </c>
       <c r="G452" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -17817,7 +17820,7 @@
         <v>14.2752389907837</v>
       </c>
       <c r="G453" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -17843,7 +17846,7 @@
         <v>14.3251867294312</v>
       </c>
       <c r="G454" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -17869,7 +17872,7 @@
         <v>14.285228729248</v>
       </c>
       <c r="G455" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -17895,7 +17898,7 @@
         <v>14.4450626373291</v>
       </c>
       <c r="G456" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -17921,7 +17924,7 @@
         <v>14.4350738525391</v>
       </c>
       <c r="G457" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -17947,7 +17950,7 @@
         <v>14.4450626373291</v>
       </c>
       <c r="G458" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -17973,7 +17976,7 @@
         <v>14.6048984527588</v>
       </c>
       <c r="G459" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -17999,7 +18002,7 @@
         <v>14.6148881912231</v>
       </c>
       <c r="G460" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -18025,7 +18028,7 @@
         <v>14.674825668335</v>
       </c>
       <c r="G461" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -18051,7 +18054,7 @@
         <v>14.4750318527222</v>
       </c>
       <c r="G462" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -18077,7 +18080,7 @@
         <v>14.5749292373657</v>
       </c>
       <c r="G463" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -18103,7 +18106,7 @@
         <v>14.5849189758301</v>
       </c>
       <c r="G464" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -18129,7 +18132,7 @@
         <v>13.9855375289917</v>
       </c>
       <c r="G465" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -18181,7 +18184,7 @@
         <v>13.9156112670898</v>
       </c>
       <c r="G467" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -18207,7 +18210,7 @@
         <v>13.9855375289917</v>
       </c>
       <c r="G468" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -18233,7 +18236,7 @@
         <v>14.0155067443848</v>
       </c>
       <c r="G469" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -18259,7 +18262,7 @@
         <v>14.1653528213501</v>
       </c>
       <c r="G470" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -18285,7 +18288,7 @@
         <v>14.2452697753906</v>
       </c>
       <c r="G471" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -18311,7 +18314,7 @@
         <v>14.2352800369263</v>
       </c>
       <c r="G472" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -18337,7 +18340,7 @@
         <v>14.1953220367432</v>
       </c>
       <c r="G473" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -18363,7 +18366,7 @@
         <v>14.1453733444214</v>
       </c>
       <c r="G474" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -18389,7 +18392,7 @@
         <v>14.0155067443848</v>
       </c>
       <c r="G475" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -18415,7 +18418,7 @@
         <v>13.6458902359009</v>
       </c>
       <c r="G476" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -18441,7 +18444,7 @@
         <v>13.416127204895</v>
       </c>
       <c r="G477" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -18467,7 +18470,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G478" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -18493,7 +18496,7 @@
         <v>12.7867784500122</v>
       </c>
       <c r="G479" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -18519,7 +18522,7 @@
         <v>12.8267374038696</v>
       </c>
       <c r="G480" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -18545,7 +18548,7 @@
         <v>12.6868810653687</v>
       </c>
       <c r="G481" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -18571,7 +18574,7 @@
         <v>12.9266328811646</v>
       </c>
       <c r="G482" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -18597,7 +18600,7 @@
         <v>12.7967681884766</v>
       </c>
       <c r="G483" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -18623,7 +18626,7 @@
         <v>12.7368297576904</v>
       </c>
       <c r="G484" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -18649,7 +18652,7 @@
         <v>13.0564985275269</v>
       </c>
       <c r="G485" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -18675,7 +18678,7 @@
         <v>12.9166440963745</v>
       </c>
       <c r="G486" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -18701,7 +18704,7 @@
         <v>13.0465087890625</v>
       </c>
       <c r="G487" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -18727,7 +18730,7 @@
         <v>12.8966636657715</v>
       </c>
       <c r="G488" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -18753,7 +18756,7 @@
         <v>12.8367261886597</v>
       </c>
       <c r="G489" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -18779,7 +18782,7 @@
         <v>13.0664892196655</v>
       </c>
       <c r="G490" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -18805,7 +18808,7 @@
         <v>13.0564985275269</v>
       </c>
       <c r="G491" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -18831,7 +18834,7 @@
         <v>12.9765815734863</v>
       </c>
       <c r="G492" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -18857,7 +18860,7 @@
         <v>12.7767877578735</v>
       </c>
       <c r="G493" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -18883,7 +18886,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G494" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -18909,7 +18912,7 @@
         <v>12.8067569732666</v>
       </c>
       <c r="G495" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -18935,7 +18938,7 @@
         <v>12.7268400192261</v>
       </c>
       <c r="G496" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -18961,7 +18964,7 @@
         <v>12.7168502807617</v>
       </c>
       <c r="G497" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -18987,7 +18990,7 @@
         <v>12.7268400192261</v>
       </c>
       <c r="G498" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -19013,7 +19016,7 @@
         <v>12.696870803833</v>
       </c>
       <c r="G499" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -19039,7 +19042,7 @@
         <v>12.6469230651855</v>
       </c>
       <c r="G500" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -19065,7 +19068,7 @@
         <v>12.6469230651855</v>
       </c>
       <c r="G501" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -19091,7 +19094,7 @@
         <v>12.6369333267212</v>
       </c>
       <c r="G502" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -19117,7 +19120,7 @@
         <v>12.5869846343994</v>
       </c>
       <c r="G503" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -19143,7 +19146,7 @@
         <v>12.816746711731</v>
       </c>
       <c r="G504" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -19169,7 +19172,7 @@
         <v>12.6768922805786</v>
       </c>
       <c r="G505" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -19195,7 +19198,7 @@
         <v>12.7867784500122</v>
       </c>
       <c r="G506" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -19221,7 +19224,7 @@
         <v>12.8067569732666</v>
       </c>
       <c r="G507" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -19247,7 +19250,7 @@
         <v>12.7268400192261</v>
       </c>
       <c r="G508" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -19273,7 +19276,7 @@
         <v>12.846715927124</v>
       </c>
       <c r="G509" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -19299,7 +19302,7 @@
         <v>12.846715927124</v>
       </c>
       <c r="G510" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -19325,7 +19328,7 @@
         <v>12.6569118499756</v>
       </c>
       <c r="G511" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -19351,7 +19354,7 @@
         <v>12.4171600341797</v>
       </c>
       <c r="G512" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -19377,7 +19380,7 @@
         <v>12.4371385574341</v>
       </c>
       <c r="G513" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -19403,7 +19406,7 @@
         <v>12.8267374038696</v>
       </c>
       <c r="G514" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -19429,7 +19432,7 @@
         <v>13.1563959121704</v>
       </c>
       <c r="G515" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -19455,7 +19458,7 @@
         <v>13.2363128662109</v>
       </c>
       <c r="G516" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -19481,7 +19484,7 @@
         <v>13.2463026046753</v>
       </c>
       <c r="G517" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -19507,7 +19510,7 @@
         <v>13.2063436508179</v>
       </c>
       <c r="G518" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -19533,7 +19536,7 @@
         <v>13.2163343429565</v>
       </c>
       <c r="G519" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -19559,7 +19562,7 @@
         <v>13.3262195587158</v>
       </c>
       <c r="G520" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -19585,7 +19588,7 @@
         <v>13.3561887741089</v>
       </c>
       <c r="G521" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -19611,7 +19614,7 @@
         <v>13.3062410354614</v>
       </c>
       <c r="G522" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -19637,7 +19640,7 @@
         <v>13.2163343429565</v>
       </c>
       <c r="G523" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -19663,7 +19666,7 @@
         <v>13.2862615585327</v>
       </c>
       <c r="G524" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -19689,7 +19692,7 @@
         <v>13.536003112793</v>
       </c>
       <c r="G525" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -19715,7 +19718,7 @@
         <v>13.5859518051147</v>
       </c>
       <c r="G526" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -19741,7 +19744,7 @@
         <v>13.5459928512573</v>
       </c>
       <c r="G527" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -19767,7 +19770,7 @@
         <v>13.3262195587158</v>
       </c>
       <c r="G528" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -19793,7 +19796,7 @@
         <v>13.2762718200684</v>
       </c>
       <c r="G529" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -19819,7 +19822,7 @@
         <v>13.3062410354614</v>
       </c>
       <c r="G530" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -19845,7 +19848,7 @@
         <v>13.4560861587524</v>
       </c>
       <c r="G531" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -19871,7 +19874,7 @@
         <v>13.2163343429565</v>
       </c>
       <c r="G532" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -19897,7 +19900,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G533" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -19923,7 +19926,7 @@
         <v>12.816746711731</v>
       </c>
       <c r="G534" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -19949,7 +19952,7 @@
         <v>12.6469230651855</v>
       </c>
       <c r="G535" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -19975,7 +19978,7 @@
         <v>12.696870803833</v>
       </c>
       <c r="G536" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -20001,7 +20004,7 @@
         <v>12.3672122955322</v>
       </c>
       <c r="G537" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -20027,7 +20030,7 @@
         <v>12.7368297576904</v>
       </c>
       <c r="G538" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -20053,7 +20056,7 @@
         <v>12.2373456954956</v>
       </c>
       <c r="G539" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -20079,7 +20082,7 @@
         <v>12.1474390029907</v>
       </c>
       <c r="G540" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -20105,7 +20108,7 @@
         <v>12.1973867416382</v>
       </c>
       <c r="G541" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -20131,7 +20134,7 @@
         <v>12.0875005722046</v>
       </c>
       <c r="G542" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -20157,7 +20160,7 @@
         <v>12.0475416183472</v>
       </c>
       <c r="G543" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -20183,7 +20186,7 @@
         <v>12.127459526062</v>
       </c>
       <c r="G544" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -20209,7 +20212,7 @@
         <v>12.0875005722046</v>
       </c>
       <c r="G545" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -20235,7 +20238,7 @@
         <v>12.0575323104858</v>
       </c>
       <c r="G546" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -20261,7 +20264,7 @@
         <v>11.9876041412354</v>
       </c>
       <c r="G547" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -20287,7 +20290,7 @@
         <v>11.9776153564453</v>
       </c>
       <c r="G548" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -20313,7 +20316,7 @@
         <v>11.7778205871582</v>
       </c>
       <c r="G549" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -20339,7 +20342,7 @@
         <v>11.8477487564087</v>
       </c>
       <c r="G550" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -20365,7 +20368,7 @@
         <v>11.8677282333374</v>
       </c>
       <c r="G551" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -20391,7 +20394,7 @@
         <v>11.5280790328979</v>
       </c>
       <c r="G552" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -20417,7 +20420,7 @@
         <v>11.4881210327148</v>
       </c>
       <c r="G553" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -20443,7 +20446,7 @@
         <v>11.2483692169189</v>
       </c>
       <c r="G554" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -20469,7 +20472,7 @@
         <v>11.1185026168823</v>
       </c>
       <c r="G555" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -20495,7 +20498,7 @@
         <v>11.9975938796997</v>
       </c>
       <c r="G556" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -20521,7 +20524,7 @@
         <v>12.2273559570312</v>
       </c>
       <c r="G557" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -20547,7 +20550,7 @@
         <v>12.5670051574707</v>
       </c>
       <c r="G558" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -20573,7 +20576,7 @@
         <v>12.8866748809814</v>
       </c>
       <c r="G559" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -20599,7 +20602,7 @@
         <v>12.8267374038696</v>
       </c>
       <c r="G560" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -20625,7 +20628,7 @@
         <v>12.7767877578735</v>
       </c>
       <c r="G561" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -20651,7 +20654,7 @@
         <v>12.8267374038696</v>
       </c>
       <c r="G562" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -20677,7 +20680,7 @@
         <v>12.6569118499756</v>
       </c>
       <c r="G563" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -20703,7 +20706,7 @@
         <v>12.9066543579102</v>
       </c>
       <c r="G564" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -20729,7 +20732,7 @@
         <v>12.846715927124</v>
       </c>
       <c r="G565" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -20755,7 +20758,7 @@
         <v>12.7068605422974</v>
       </c>
       <c r="G566" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -20781,7 +20784,7 @@
         <v>12.7967681884766</v>
       </c>
       <c r="G567" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -20807,7 +20810,7 @@
         <v>12.7268400192261</v>
       </c>
       <c r="G568" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -20833,7 +20836,7 @@
         <v>12.5769948959351</v>
       </c>
       <c r="G569" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -20859,7 +20862,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G570" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -20885,7 +20888,7 @@
         <v>12.2173671722412</v>
       </c>
       <c r="G571" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -20911,7 +20914,7 @@
         <v>12.397180557251</v>
       </c>
       <c r="G572" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -20937,7 +20940,7 @@
         <v>12.3372430801392</v>
       </c>
       <c r="G573" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -20963,7 +20966,7 @@
         <v>12.5270471572876</v>
       </c>
       <c r="G574" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -20989,7 +20992,7 @@
         <v>12.5070667266846</v>
       </c>
       <c r="G575" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -21015,7 +21018,7 @@
         <v>12.2673149108887</v>
       </c>
       <c r="G576" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -21041,7 +21044,7 @@
         <v>12.3871908187866</v>
       </c>
       <c r="G577" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -21067,7 +21070,7 @@
         <v>12.3472318649292</v>
       </c>
       <c r="G578" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -21093,7 +21096,7 @@
         <v>12.3572216033936</v>
       </c>
       <c r="G579" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -21119,7 +21122,7 @@
         <v>12.3772010803223</v>
       </c>
       <c r="G580" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -21145,7 +21148,7 @@
         <v>12.1973867416382</v>
       </c>
       <c r="G581" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -21171,7 +21174,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G582" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -21197,7 +21200,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G583" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -21223,7 +21226,7 @@
         <v>12.2673149108887</v>
       </c>
       <c r="G584" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -21249,7 +21252,7 @@
         <v>12.397180557251</v>
       </c>
       <c r="G585" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -21275,7 +21278,7 @@
         <v>12.1674175262451</v>
       </c>
       <c r="G586" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -21301,7 +21304,7 @@
         <v>12.1374492645264</v>
       </c>
       <c r="G587" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -21327,7 +21330,7 @@
         <v>12.1674175262451</v>
       </c>
       <c r="G588" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -21353,7 +21356,7 @@
         <v>12.127459526062</v>
       </c>
       <c r="G589" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -21379,7 +21382,7 @@
         <v>12.2073774337769</v>
       </c>
       <c r="G590" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -21405,7 +21408,7 @@
         <v>12.0375528335571</v>
       </c>
       <c r="G591" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -21431,7 +21434,7 @@
         <v>12.2373456954956</v>
       </c>
       <c r="G592" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -21457,7 +21460,7 @@
         <v>12.127459526062</v>
       </c>
       <c r="G593" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -21483,7 +21486,7 @@
         <v>12.2373456954956</v>
       </c>
       <c r="G594" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -21509,7 +21512,7 @@
         <v>12.9266328811646</v>
       </c>
       <c r="G595" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -21535,7 +21538,7 @@
         <v>12.8067569732666</v>
       </c>
       <c r="G596" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -21561,7 +21564,7 @@
         <v>12.966591835022</v>
       </c>
       <c r="G597" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -21587,7 +21590,7 @@
         <v>13.0964584350586</v>
       </c>
       <c r="G598" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -21613,7 +21616,7 @@
         <v>12.6369333267212</v>
       </c>
       <c r="G599" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -21639,7 +21642,7 @@
         <v>12.4970779418945</v>
       </c>
       <c r="G600" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -21665,7 +21668,7 @@
         <v>12.2173671722412</v>
       </c>
       <c r="G601" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -21691,7 +21694,7 @@
         <v>12.1674175262451</v>
       </c>
       <c r="G602" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -21717,7 +21720,7 @@
         <v>12.1873979568481</v>
       </c>
       <c r="G603" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -21743,7 +21746,7 @@
         <v>12.1074800491333</v>
       </c>
       <c r="G604" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -21769,7 +21772,7 @@
         <v>11.9776153564453</v>
       </c>
       <c r="G605" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -21795,7 +21798,7 @@
         <v>11.9376564025879</v>
       </c>
       <c r="G606" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -21821,7 +21824,7 @@
         <v>11.7878112792969</v>
       </c>
       <c r="G607" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -21847,7 +21850,7 @@
         <v>11.6979036331177</v>
       </c>
       <c r="G608" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -21873,7 +21876,7 @@
         <v>12.0875005722046</v>
       </c>
       <c r="G609" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -21899,7 +21902,7 @@
         <v>11.9975938796997</v>
       </c>
       <c r="G610" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -21925,7 +21928,7 @@
         <v>12.5370359420776</v>
       </c>
       <c r="G611" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -21951,7 +21954,7 @@
         <v>12.427149772644</v>
       </c>
       <c r="G612" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -21977,7 +21980,7 @@
         <v>12.3372430801392</v>
       </c>
       <c r="G613" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -22003,7 +22006,7 @@
         <v>11.9076871871948</v>
       </c>
       <c r="G614" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -22029,7 +22032,7 @@
         <v>12.1873979568481</v>
       </c>
       <c r="G615" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -22055,7 +22058,7 @@
         <v>12.2273559570312</v>
       </c>
       <c r="G616" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -22081,7 +22084,7 @@
         <v>12.3871908187866</v>
       </c>
       <c r="G617" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -22107,7 +22110,7 @@
         <v>12.4371385574341</v>
       </c>
       <c r="G618" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -22133,7 +22136,7 @@
         <v>12.4071702957153</v>
       </c>
       <c r="G619" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -22159,7 +22162,7 @@
         <v>12.4671087265015</v>
       </c>
       <c r="G620" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -22185,7 +22188,7 @@
         <v>12.7268400192261</v>
       </c>
       <c r="G621" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -22211,7 +22214,7 @@
         <v>12.397180557251</v>
       </c>
       <c r="G622" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -22237,7 +22240,7 @@
         <v>12.427149772644</v>
       </c>
       <c r="G623" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -22263,7 +22266,7 @@
         <v>12.5070667266846</v>
       </c>
       <c r="G624" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -22289,7 +22292,7 @@
         <v>12.397180557251</v>
       </c>
       <c r="G625" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -22315,7 +22318,7 @@
         <v>12.5070667266846</v>
       </c>
       <c r="G626" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -22341,7 +22344,7 @@
         <v>12.2573251724243</v>
       </c>
       <c r="G627" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -22367,7 +22370,7 @@
         <v>12.2273559570312</v>
       </c>
       <c r="G628" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -22393,7 +22396,7 @@
         <v>12.0974912643433</v>
       </c>
       <c r="G629" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -22419,7 +22422,7 @@
         <v>12.0475416183472</v>
       </c>
       <c r="G630" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -22445,7 +22448,7 @@
         <v>11.8077898025513</v>
       </c>
       <c r="G631" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -22471,7 +22474,7 @@
         <v>11.7978010177612</v>
       </c>
       <c r="G632" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -22497,7 +22500,7 @@
         <v>11.548059463501</v>
       </c>
       <c r="G633" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -22523,7 +22526,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G634" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -22549,7 +22552,7 @@
         <v>11.7078943252563</v>
       </c>
       <c r="G635" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -22575,7 +22578,7 @@
         <v>11.5180902481079</v>
       </c>
       <c r="G636" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -22601,7 +22604,7 @@
         <v>11.5780277252197</v>
       </c>
       <c r="G637" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -22627,7 +22630,7 @@
         <v>11.3382759094238</v>
       </c>
       <c r="G638" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -22653,7 +22656,7 @@
         <v>11.3682451248169</v>
       </c>
       <c r="G639" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -22679,7 +22682,7 @@
         <v>11.3682451248169</v>
       </c>
       <c r="G640" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -22705,7 +22708,7 @@
         <v>11.4681406021118</v>
       </c>
       <c r="G641" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -22731,7 +22734,7 @@
         <v>11.4981098175049</v>
       </c>
       <c r="G642" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -22757,7 +22760,7 @@
         <v>11.6279764175415</v>
       </c>
       <c r="G643" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -22783,7 +22786,7 @@
         <v>11.9376564025879</v>
       </c>
       <c r="G644" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -22809,7 +22812,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G645" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -22835,7 +22838,7 @@
         <v>11.9776153564453</v>
       </c>
       <c r="G646" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -22861,7 +22864,7 @@
         <v>11.9576349258423</v>
       </c>
       <c r="G647" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -22887,7 +22890,7 @@
         <v>11.9076871871948</v>
       </c>
       <c r="G648" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -22913,7 +22916,7 @@
         <v>12.2373456954956</v>
       </c>
       <c r="G649" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -22939,7 +22942,7 @@
         <v>12.2073774337769</v>
       </c>
       <c r="G650" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -22965,7 +22968,7 @@
         <v>12.2073774337769</v>
       </c>
       <c r="G651" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -22991,7 +22994,7 @@
         <v>12.1474390029907</v>
       </c>
       <c r="G652" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -23017,7 +23020,7 @@
         <v>12.0974912643433</v>
       </c>
       <c r="G653" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -23043,7 +23046,7 @@
         <v>12.2273559570312</v>
       </c>
       <c r="G654" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -23069,7 +23072,7 @@
         <v>12.0275630950928</v>
       </c>
       <c r="G655" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -23095,7 +23098,7 @@
         <v>11.7378625869751</v>
       </c>
       <c r="G656" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -23121,7 +23124,7 @@
         <v>11.7878112792969</v>
       </c>
       <c r="G657" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -23147,7 +23150,7 @@
         <v>11.6579446792603</v>
       </c>
       <c r="G658" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -23173,7 +23176,7 @@
         <v>11.7078943252563</v>
       </c>
       <c r="G659" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -23199,7 +23202,7 @@
         <v>11.6779251098633</v>
       </c>
       <c r="G660" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -23225,7 +23228,7 @@
         <v>11.4581518173218</v>
       </c>
       <c r="G661" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -23251,7 +23254,7 @@
         <v>11.6879138946533</v>
       </c>
       <c r="G662" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -23277,7 +23280,7 @@
         <v>11.7378625869751</v>
       </c>
       <c r="G663" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -23303,7 +23306,7 @@
         <v>11.9176769256592</v>
       </c>
       <c r="G664" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -23329,7 +23332,7 @@
         <v>11.8077898025513</v>
       </c>
       <c r="G665" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -23355,7 +23358,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G666" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -23381,7 +23384,7 @@
         <v>11.3882236480713</v>
       </c>
       <c r="G667" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -23407,7 +23410,7 @@
         <v>11.2983169555664</v>
       </c>
       <c r="G668" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -23433,7 +23436,7 @@
         <v>11.3782339096069</v>
       </c>
       <c r="G669" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -23459,7 +23462,7 @@
         <v>11.2683477401733</v>
       </c>
       <c r="G670" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -23485,7 +23488,7 @@
         <v>11.128493309021</v>
       </c>
       <c r="G671" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -23511,7 +23514,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G672" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -23537,7 +23540,7 @@
         <v>11.278338432312</v>
       </c>
       <c r="G673" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -23563,7 +23566,7 @@
         <v>11.0285959243774</v>
       </c>
       <c r="G674" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -23589,7 +23592,7 @@
         <v>11.0385856628418</v>
       </c>
       <c r="G675" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -23615,7 +23618,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G676" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -23641,7 +23644,7 @@
         <v>11.2084102630615</v>
       </c>
       <c r="G677" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -23667,7 +23670,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G678" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -23693,7 +23696,7 @@
         <v>11.5380687713623</v>
       </c>
       <c r="G679" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -23719,7 +23722,7 @@
         <v>11.7978010177612</v>
       </c>
       <c r="G680" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -23745,7 +23748,7 @@
         <v>11.5080995559692</v>
       </c>
       <c r="G681" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -23771,7 +23774,7 @@
         <v>11.4981098175049</v>
       </c>
       <c r="G682" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -23797,7 +23800,7 @@
         <v>11.3582553863525</v>
       </c>
       <c r="G683" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23823,7 +23826,7 @@
         <v>11.138482093811</v>
       </c>
       <c r="G684" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -23849,7 +23852,7 @@
         <v>11.1484718322754</v>
       </c>
       <c r="G685" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -23875,7 +23878,7 @@
         <v>11.138482093811</v>
       </c>
       <c r="G686" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -23901,7 +23904,7 @@
         <v>11.3282861709595</v>
       </c>
       <c r="G687" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -23927,7 +23930,7 @@
         <v>11.1884307861328</v>
       </c>
       <c r="G688" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -23953,7 +23956,7 @@
         <v>11.278338432312</v>
       </c>
       <c r="G689" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -23979,7 +23982,7 @@
         <v>11.3083066940308</v>
       </c>
       <c r="G690" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -24005,7 +24008,7 @@
         <v>11.4381723403931</v>
       </c>
       <c r="G691" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -24031,7 +24034,7 @@
         <v>11.6279764175415</v>
       </c>
       <c r="G692" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -24057,7 +24060,7 @@
         <v>11.6879138946533</v>
       </c>
       <c r="G693" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -24083,7 +24086,7 @@
         <v>11.8577394485474</v>
       </c>
       <c r="G694" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -24109,7 +24112,7 @@
         <v>11.9376564025879</v>
       </c>
       <c r="G695" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -24135,7 +24138,7 @@
         <v>11.8976974487305</v>
       </c>
       <c r="G696" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -24161,7 +24164,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G697" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -24187,7 +24190,7 @@
         <v>11.6379661560059</v>
       </c>
       <c r="G698" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -24213,7 +24216,7 @@
         <v>11.6379661560059</v>
       </c>
       <c r="G699" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -24239,7 +24242,7 @@
         <v>11.5980072021484</v>
       </c>
       <c r="G700" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -24265,7 +24268,7 @@
         <v>11.2683477401733</v>
       </c>
       <c r="G701" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -24291,7 +24294,7 @@
         <v>11.4881210327148</v>
       </c>
       <c r="G702" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -24317,7 +24320,7 @@
         <v>11.2883272171021</v>
       </c>
       <c r="G703" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -24343,7 +24346,7 @@
         <v>11.4781312942505</v>
       </c>
       <c r="G704" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -24369,7 +24372,7 @@
         <v>11.0885343551636</v>
       </c>
       <c r="G705" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -24395,7 +24398,7 @@
         <v>11.1484718322754</v>
       </c>
       <c r="G706" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -24421,7 +24424,7 @@
         <v>10.7289056777954</v>
       </c>
       <c r="G707" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -24447,7 +24450,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G708" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -24473,7 +24476,7 @@
         <v>10.1195363998413</v>
       </c>
       <c r="G709" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -24499,7 +24502,7 @@
         <v>9.92473697662354</v>
       </c>
       <c r="G710" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -24525,7 +24528,7 @@
         <v>9.8248405456543</v>
       </c>
       <c r="G711" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -24551,7 +24554,7 @@
         <v>9.45522308349609</v>
       </c>
       <c r="G712" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -24577,7 +24580,7 @@
         <v>9.81485080718994</v>
       </c>
       <c r="G713" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -24603,7 +24606,7 @@
         <v>9.9197416305542</v>
       </c>
       <c r="G714" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -24629,7 +24632,7 @@
         <v>9.78987693786621</v>
       </c>
       <c r="G715" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -24655,7 +24658,7 @@
         <v>9.66001129150391</v>
       </c>
       <c r="G716" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -24681,7 +24684,7 @@
         <v>9.50517082214355</v>
       </c>
       <c r="G717" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -24707,7 +24710,7 @@
         <v>9.58009433746338</v>
       </c>
       <c r="G718" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -24733,7 +24736,7 @@
         <v>9.41026878356934</v>
       </c>
       <c r="G719" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -24759,7 +24762,7 @@
         <v>9.72494411468506</v>
       </c>
       <c r="G720" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -24785,7 +24788,7 @@
         <v>9.57509899139404</v>
       </c>
       <c r="G721" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -24811,7 +24814,7 @@
         <v>9.87478923797607</v>
       </c>
       <c r="G722" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -24837,7 +24840,7 @@
         <v>9.8248405456543</v>
       </c>
       <c r="G723" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -24863,7 +24866,7 @@
         <v>9.7698974609375</v>
       </c>
       <c r="G724" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -24889,7 +24892,7 @@
         <v>9.98467540740967</v>
       </c>
       <c r="G725" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -24915,7 +24918,7 @@
         <v>10.1195363998413</v>
       </c>
       <c r="G726" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -24941,7 +24944,7 @@
         <v>9.88477897644043</v>
       </c>
       <c r="G727" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -24967,7 +24970,7 @@
         <v>9.83483028411865</v>
       </c>
       <c r="G728" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -24993,7 +24996,7 @@
         <v>9.5850887298584</v>
       </c>
       <c r="G729" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -25019,7 +25022,7 @@
         <v>9.44523334503174</v>
       </c>
       <c r="G730" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -25045,7 +25048,7 @@
         <v>9.33534717559814</v>
       </c>
       <c r="G731" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -25071,7 +25074,7 @@
         <v>9.07061958312988</v>
       </c>
       <c r="G732" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -25097,7 +25100,7 @@
         <v>8.99569797515869</v>
       </c>
       <c r="G733" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -25123,7 +25126,7 @@
         <v>9.04564571380615</v>
       </c>
       <c r="G734" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -25149,7 +25152,7 @@
         <v>9.11557388305664</v>
       </c>
       <c r="G735" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -25175,7 +25178,7 @@
         <v>9.31536674499512</v>
       </c>
       <c r="G736" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -25201,7 +25204,7 @@
         <v>9.34533596038818</v>
       </c>
       <c r="G737" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -25227,7 +25230,7 @@
         <v>9.32036209106445</v>
       </c>
       <c r="G738" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -25253,7 +25256,7 @@
         <v>9.60506820678711</v>
       </c>
       <c r="G739" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -25279,7 +25282,7 @@
         <v>9.64502716064453</v>
       </c>
       <c r="G740" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -25305,7 +25308,7 @@
         <v>9.7698974609375</v>
       </c>
       <c r="G741" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -25331,7 +25334,7 @@
         <v>10.0296287536621</v>
       </c>
       <c r="G742" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -25357,7 +25360,7 @@
         <v>10.0196390151978</v>
       </c>
       <c r="G743" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -25383,7 +25386,7 @@
         <v>9.92473697662354</v>
       </c>
       <c r="G744" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -25409,7 +25412,7 @@
         <v>9.94971084594727</v>
       </c>
       <c r="G745" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -25435,7 +25438,7 @@
         <v>9.83483028411865</v>
       </c>
       <c r="G746" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -25461,7 +25464,7 @@
         <v>10.1894636154175</v>
       </c>
       <c r="G747" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -25487,7 +25490,7 @@
         <v>9.87978363037109</v>
       </c>
       <c r="G748" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -25513,7 +25516,7 @@
         <v>9.84981536865234</v>
       </c>
       <c r="G749" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -25539,7 +25542,7 @@
         <v>9.50017642974854</v>
       </c>
       <c r="G750" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -25565,7 +25568,7 @@
         <v>9.53514003753662</v>
       </c>
       <c r="G751" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -25591,7 +25594,7 @@
         <v>9.29039287567139</v>
       </c>
       <c r="G752" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -25617,7 +25620,7 @@
         <v>9.41526412963867</v>
       </c>
       <c r="G753" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -25643,7 +25646,7 @@
         <v>9.70496463775635</v>
       </c>
       <c r="G754" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -25669,7 +25672,7 @@
         <v>9.66001129150391</v>
       </c>
       <c r="G755" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -25695,7 +25698,7 @@
         <v>9.44523334503174</v>
       </c>
       <c r="G756" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -25721,7 +25724,7 @@
         <v>9.09559535980225</v>
       </c>
       <c r="G757" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -25747,7 +25750,7 @@
         <v>8.96073436737061</v>
       </c>
       <c r="G758" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -25773,7 +25776,7 @@
         <v>9.31037330627441</v>
       </c>
       <c r="G759" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -25799,7 +25802,7 @@
         <v>9.10058879852295</v>
       </c>
       <c r="G760" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -25825,7 +25828,7 @@
         <v>9.15553283691406</v>
       </c>
       <c r="G761" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -25851,7 +25854,7 @@
         <v>8.83086776733398</v>
       </c>
       <c r="G762" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -25877,7 +25880,7 @@
         <v>8.8858118057251</v>
       </c>
       <c r="G763" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -25903,7 +25906,7 @@
         <v>8.95074367523193</v>
       </c>
       <c r="G764" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -25929,7 +25932,7 @@
         <v>8.91578102111816</v>
       </c>
       <c r="G765" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -25955,7 +25958,7 @@
         <v>9.27041435241699</v>
       </c>
       <c r="G766" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -25981,7 +25984,7 @@
         <v>9.24044513702393</v>
       </c>
       <c r="G767" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -26007,7 +26010,7 @@
         <v>9.5850887298584</v>
       </c>
       <c r="G768" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -26033,7 +26036,7 @@
         <v>10.1694841384888</v>
       </c>
       <c r="G769" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -26059,7 +26062,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G770" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -26085,7 +26088,7 @@
         <v>9.86979389190674</v>
       </c>
       <c r="G771" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -26111,7 +26114,7 @@
         <v>9.75990772247314</v>
       </c>
       <c r="G772" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -26137,7 +26140,7 @@
         <v>9.77988719940186</v>
       </c>
       <c r="G773" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -26163,7 +26166,7 @@
         <v>9.83982467651367</v>
       </c>
       <c r="G774" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -26189,7 +26192,7 @@
         <v>9.73992824554443</v>
       </c>
       <c r="G775" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -26215,7 +26218,7 @@
         <v>9.88977336883545</v>
       </c>
       <c r="G776" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -26241,7 +26244,7 @@
         <v>9.9197416305542</v>
       </c>
       <c r="G777" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -26267,7 +26270,7 @@
         <v>9.89476776123047</v>
       </c>
       <c r="G778" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -26293,7 +26296,7 @@
         <v>9.85480976104736</v>
       </c>
       <c r="G779" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -26319,7 +26322,7 @@
         <v>10.0096502304077</v>
       </c>
       <c r="G780" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -26345,7 +26348,7 @@
         <v>10.3093395233154</v>
       </c>
       <c r="G781" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -26371,7 +26374,7 @@
         <v>10.1195363998413</v>
       </c>
       <c r="G782" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -26397,7 +26400,7 @@
         <v>9.97468566894531</v>
       </c>
       <c r="G783" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -26423,7 +26426,7 @@
         <v>9.96969127655029</v>
       </c>
       <c r="G784" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -26449,7 +26452,7 @@
         <v>9.95970058441162</v>
       </c>
       <c r="G785" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -26475,7 +26478,7 @@
         <v>9.93972206115723</v>
       </c>
       <c r="G786" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -26501,7 +26504,7 @@
         <v>9.8997631072998</v>
       </c>
       <c r="G787" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -26527,7 +26530,7 @@
         <v>9.90475845336914</v>
       </c>
       <c r="G788" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -26553,7 +26556,7 @@
         <v>9.87478923797607</v>
       </c>
       <c r="G789" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -26579,7 +26582,7 @@
         <v>9.60007286071777</v>
       </c>
       <c r="G790" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -26605,7 +26608,7 @@
         <v>9.31037330627441</v>
       </c>
       <c r="G791" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -26631,7 +26634,7 @@
         <v>9.49018669128418</v>
       </c>
       <c r="G792" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -26657,7 +26660,7 @@
         <v>9.77489185333252</v>
       </c>
       <c r="G793" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -26683,7 +26686,7 @@
         <v>10.0196390151978</v>
       </c>
       <c r="G794" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -26709,7 +26712,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G795" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -26735,7 +26738,7 @@
         <v>10.2094430923462</v>
       </c>
       <c r="G796" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -26761,7 +26764,7 @@
         <v>10.0795774459839</v>
       </c>
       <c r="G797" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -26787,7 +26790,7 @@
         <v>10.0795774459839</v>
       </c>
       <c r="G798" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -26813,7 +26816,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G799" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -26839,7 +26842,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G800" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -26865,7 +26868,7 @@
         <v>10.4991426467896</v>
       </c>
       <c r="G801" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -26891,7 +26894,7 @@
         <v>10.8088226318359</v>
       </c>
       <c r="G802" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -26917,7 +26920,7 @@
         <v>10.838791847229</v>
       </c>
       <c r="G803" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -26943,7 +26946,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G804" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26969,7 +26972,7 @@
         <v>10.6290092468262</v>
       </c>
       <c r="G805" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26995,7 +26998,7 @@
         <v>10.8487815856934</v>
       </c>
       <c r="G806" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -27021,7 +27024,7 @@
         <v>10.4092359542847</v>
       </c>
       <c r="G807" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -27047,7 +27050,7 @@
         <v>10.2593908309937</v>
       </c>
       <c r="G808" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -27073,7 +27076,7 @@
         <v>10.2294216156006</v>
       </c>
       <c r="G809" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -27099,7 +27102,7 @@
         <v>10.2394123077393</v>
       </c>
       <c r="G810" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -27125,7 +27128,7 @@
         <v>10.1794738769531</v>
       </c>
       <c r="G811" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -27151,7 +27154,7 @@
         <v>10.2094430923462</v>
       </c>
       <c r="G812" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -27177,7 +27180,7 @@
         <v>10.1594953536987</v>
       </c>
       <c r="G813" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -27203,7 +27206,7 @@
         <v>10.3692779541016</v>
       </c>
       <c r="G814" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -27229,7 +27232,7 @@
         <v>10.6389989852905</v>
       </c>
       <c r="G815" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -27255,7 +27258,7 @@
         <v>10.9686584472656</v>
       </c>
       <c r="G816" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -27281,7 +27284,7 @@
         <v>10.7788543701172</v>
       </c>
       <c r="G817" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -27307,7 +27310,7 @@
         <v>10.688946723938</v>
       </c>
       <c r="G818" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -27333,7 +27336,7 @@
         <v>10.4791641235352</v>
       </c>
       <c r="G819" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -27359,7 +27362,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G820" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -27385,7 +27388,7 @@
         <v>10.1994533538818</v>
       </c>
       <c r="G821" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -27411,7 +27414,7 @@
         <v>10.0695877075195</v>
       </c>
       <c r="G822" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -27437,7 +27440,7 @@
         <v>10.1095457077026</v>
       </c>
       <c r="G823" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -27463,7 +27466,7 @@
         <v>10.0995569229126</v>
       </c>
       <c r="G824" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -27489,7 +27492,7 @@
         <v>10.0296287536621</v>
       </c>
       <c r="G825" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -27515,7 +27518,7 @@
         <v>10.0995569229126</v>
       </c>
       <c r="G826" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -27541,7 +27544,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G827" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -27567,7 +27570,7 @@
         <v>10.3293190002441</v>
       </c>
       <c r="G828" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -27593,7 +27596,7 @@
         <v>11.0785436630249</v>
       </c>
       <c r="G829" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -27619,7 +27622,7 @@
         <v>11.0385856628418</v>
       </c>
       <c r="G830" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -27645,7 +27648,7 @@
         <v>11.138482093811</v>
       </c>
       <c r="G831" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -27671,7 +27674,7 @@
         <v>10.98863697052</v>
       </c>
       <c r="G832" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -27697,7 +27700,7 @@
         <v>10.958667755127</v>
       </c>
       <c r="G833" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -27723,7 +27726,7 @@
         <v>11.0385856628418</v>
       </c>
       <c r="G834" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -27749,7 +27752,7 @@
         <v>10.8487815856934</v>
       </c>
       <c r="G835" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -27775,7 +27778,7 @@
         <v>11.2283887863159</v>
       </c>
       <c r="G836" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -27801,7 +27804,7 @@
         <v>11.6379661560059</v>
       </c>
       <c r="G837" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -27827,7 +27830,7 @@
         <v>11.7178831100464</v>
       </c>
       <c r="G838" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -27853,7 +27856,7 @@
         <v>11.5680379867554</v>
       </c>
       <c r="G839" t="s">
-        <v>439</v>
+        <v>620</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -27879,7 +27882,7 @@
         <v>11.7878112792969</v>
       </c>
       <c r="G840" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -27931,7 +27934,7 @@
         <v>11.6579446792603</v>
       </c>
       <c r="G842" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -27957,7 +27960,7 @@
         <v>11.6379661560059</v>
       </c>
       <c r="G843" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27983,7 +27986,7 @@
         <v>11.6979036331177</v>
       </c>
       <c r="G844" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -28009,7 +28012,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G845" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -28035,7 +28038,7 @@
         <v>11.6879138946533</v>
       </c>
       <c r="G846" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -28061,7 +28064,7 @@
         <v>11.5380687713623</v>
       </c>
       <c r="G847" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -28113,7 +28116,7 @@
         <v>11.0885343551636</v>
       </c>
       <c r="G849" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -28165,7 +28168,7 @@
         <v>11.3782339096069</v>
       </c>
       <c r="G851" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -28217,7 +28220,7 @@
         <v>10.8487815856934</v>
       </c>
       <c r="G853" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -28243,7 +28246,7 @@
         <v>10.2593908309937</v>
       </c>
       <c r="G854" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -28347,7 +28350,7 @@
         <v>10.1894636154175</v>
       </c>
       <c r="G858" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -59235,7 +59238,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G2046" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -72056,6 +72059,32 @@
         <v>1843</v>
       </c>
       <c r="H2539" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" s="1" t="n">
+        <v>46020.6910532407</v>
+      </c>
+      <c r="B2540" t="n">
+        <v>217264</v>
+      </c>
+      <c r="C2540" t="n">
+        <v>9.46500015258789</v>
+      </c>
+      <c r="D2540" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E2540" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="F2540" t="n">
+        <v>9.44499969482422</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>1899</v>
+      </c>
+      <c r="H2540" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="1905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="1906">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">BRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13994884490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92740154266357</t>
+    <t xml:space="preserve">7.13994979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92740106582642</t>
   </si>
   <si>
     <t xml:space="preserve">6.52519702911377</t>
@@ -56,25 +56,25 @@
     <t xml:space="preserve">6.54154682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42873382568359</t>
+    <t xml:space="preserve">6.42873334884644</t>
   </si>
   <si>
     <t xml:space="preserve">6.60040664672852</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78188800811768</t>
+    <t xml:space="preserve">6.78188848495483</t>
   </si>
   <si>
     <t xml:space="preserve">6.55135679244995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21291589736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19820213317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27504539489746</t>
+    <t xml:space="preserve">6.21291637420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19820165634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2750449180603</t>
   </si>
   <si>
     <t xml:space="preserve">5.94641447067261</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">6.20310688018799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24888610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30610990524292</t>
+    <t xml:space="preserve">6.24888563156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30610942840576</t>
   </si>
   <si>
     <t xml:space="preserve">6.31919002532959</t>
@@ -95,16 +95,16 @@
     <t xml:space="preserve">6.38785886764526</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23090171813965</t>
+    <t xml:space="preserve">6.23090076446533</t>
   </si>
   <si>
     <t xml:space="preserve">6.16713666915894</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05922746658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99219417572021</t>
+    <t xml:space="preserve">6.05922794342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99219465255737</t>
   </si>
   <si>
     <t xml:space="preserve">5.86466598510742</t>
@@ -113,25 +113,25 @@
     <t xml:space="preserve">5.70443868637085</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35945796966553</t>
+    <t xml:space="preserve">5.35945749282837</t>
   </si>
   <si>
     <t xml:space="preserve">5.51641511917114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72242307662964</t>
+    <t xml:space="preserve">5.72242212295532</t>
   </si>
   <si>
     <t xml:space="preserve">5.67500877380371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73223304748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03960800170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97420978546143</t>
+    <t xml:space="preserve">5.73223352432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03960847854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97420883178711</t>
   </si>
   <si>
     <t xml:space="preserve">6.11972236633301</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">6.14097738265991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10010242462158</t>
+    <t xml:space="preserve">6.1001033782959</t>
   </si>
   <si>
     <t xml:space="preserve">6.23744106292725</t>
@@ -149,22 +149,22 @@
     <t xml:space="preserve">6.11154747009277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9758448600769</t>
+    <t xml:space="preserve">5.97584438323975</t>
   </si>
   <si>
     <t xml:space="preserve">6.07394361495972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12953186035156</t>
+    <t xml:space="preserve">6.12953233718872</t>
   </si>
   <si>
     <t xml:space="preserve">6.2194561958313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35189008712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32409572601318</t>
+    <t xml:space="preserve">6.35188961029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32409477233887</t>
   </si>
   <si>
     <t xml:space="preserve">7.04675626754761</t>
@@ -173,130 +173,130 @@
     <t xml:space="preserve">7.08272504806519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1170597076416</t>
+    <t xml:space="preserve">7.11705875396729</t>
   </si>
   <si>
     <t xml:space="preserve">7.07945489883423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12032890319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07128000259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06637382507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16120338439941</t>
+    <t xml:space="preserve">7.1203293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07127952575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06637477874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16120386123657</t>
   </si>
   <si>
     <t xml:space="preserve">7.14321899414062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24949264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14158391952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22987127304077</t>
+    <t xml:space="preserve">7.24949216842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14158535003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22987222671509</t>
   </si>
   <si>
     <t xml:space="preserve">7.07618379592896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2691125869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15302801132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15139389038086</t>
+    <t xml:space="preserve">7.26911306381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15302896499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1513934135437</t>
   </si>
   <si>
     <t xml:space="preserve">7.31489181518555</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43097400665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40318059921265</t>
+    <t xml:space="preserve">7.43097591400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4031810760498</t>
   </si>
   <si>
     <t xml:space="preserve">7.35576486587524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1448540687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18899965286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16283845901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27401733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998754501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35739994049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40645027160645</t>
+    <t xml:space="preserve">7.14485359191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18899869918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16283798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27401685714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998706817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35740089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40644931793213</t>
   </si>
   <si>
     <t xml:space="preserve">7.4227991104126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39337015151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4391508102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47184944152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5110878944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76777935028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71546125411987</t>
+    <t xml:space="preserve">7.39337062835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43915033340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47184991836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51108884811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76777982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71546173095703</t>
   </si>
   <si>
     <t xml:space="preserve">7.63534736633301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68276214599609</t>
+    <t xml:space="preserve">7.68276166915894</t>
   </si>
   <si>
     <t xml:space="preserve">7.74162197113037</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6696834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72200107574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6304407119751</t>
+    <t xml:space="preserve">7.66968250274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72200155258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63044261932373</t>
   </si>
   <si>
     <t xml:space="preserve">7.7105565071106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85606908798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47735977172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50188636779785</t>
+    <t xml:space="preserve">7.85606956481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47736263275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50188541412354</t>
   </si>
   <si>
     <t xml:space="preserve">8.51006031036377</t>
@@ -308,58 +308,58 @@
     <t xml:space="preserve">8.42831039428711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36291217803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.354736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41196250915527</t>
+    <t xml:space="preserve">8.36291313171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35473728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41196346282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.5199146270752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45348358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51161098480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46178531646729</t>
+    <t xml:space="preserve">8.45348167419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51161193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4617862701416</t>
   </si>
   <si>
     <t xml:space="preserve">8.47008991241455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61125946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63616943359375</t>
+    <t xml:space="preserve">8.61125755310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63617134094238</t>
   </si>
   <si>
     <t xml:space="preserve">8.72751426696777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96002674102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86868286132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86037826538086</t>
+    <t xml:space="preserve">8.96002769470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86868381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86037921905518</t>
   </si>
   <si>
     <t xml:space="preserve">8.58634567260742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27577590942383</t>
+    <t xml:space="preserve">8.27577495574951</t>
   </si>
   <si>
     <t xml:space="preserve">8.10969638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30401039123535</t>
+    <t xml:space="preserve">8.30400943756104</t>
   </si>
   <si>
     <t xml:space="preserve">8.31231498718262</t>
@@ -371,145 +371,142 @@
     <t xml:space="preserve">8.61956310272217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56973838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71920967102051</t>
+    <t xml:space="preserve">8.56973934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71921062469482</t>
   </si>
   <si>
     <t xml:space="preserve">8.25916862487793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64135026931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25418472290039</t>
+    <t xml:space="preserve">7.64134979248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25418567657471</t>
   </si>
   <si>
     <t xml:space="preserve">8.05987167358398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20602321624756</t>
+    <t xml:space="preserve">8.20602226257324</t>
   </si>
   <si>
     <t xml:space="preserve">8.23757839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84728908538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67954874038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67788791656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95524120330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02831554412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05488777160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97849273681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14457321166992</t>
+    <t xml:space="preserve">7.8472900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6795482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67788743972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95524168014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02831649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05488872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97849321365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14457225799561</t>
   </si>
   <si>
     <t xml:space="preserve">8.11301803588867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23425579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10471439361572</t>
+    <t xml:space="preserve">8.23425674438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10471248626709</t>
   </si>
   <si>
     <t xml:space="preserve">8.21100521087646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16782283782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32061958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37044143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41196441650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50330448150635</t>
+    <t xml:space="preserve">8.16782569885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32061862945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37044239044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50330543518066</t>
   </si>
   <si>
     <t xml:space="preserve">8.36213684082031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67769145965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76903533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53652191162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55313014984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64447593688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73581790924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68599510192871</t>
+    <t xml:space="preserve">8.67769050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76903629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53652381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55312919616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64447498321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73581886291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68599414825439</t>
   </si>
   <si>
     <t xml:space="preserve">8.7441234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6693868637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48669719696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44517803192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47839450836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40365695953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42856884002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65277862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69429779052734</t>
+    <t xml:space="preserve">8.66938781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48669815063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4451789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4783935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40365791320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42856979370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65277767181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69429874420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.71090507507324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89359474182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84377193450928</t>
+    <t xml:space="preserve">8.89359569549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84377002716064</t>
   </si>
   <si>
     <t xml:space="preserve">8.88529014587402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78564262390137</t>
+    <t xml:space="preserve">8.78564167022705</t>
   </si>
   <si>
     <t xml:space="preserve">8.80224990844727</t>
@@ -518,49 +515,49 @@
     <t xml:space="preserve">8.8188591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90189933776855</t>
+    <t xml:space="preserve">8.90189838409424</t>
   </si>
   <si>
     <t xml:space="preserve">9.05137062072754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81055545806885</t>
+    <t xml:space="preserve">8.81055355072021</t>
   </si>
   <si>
     <t xml:space="preserve">8.6278657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70260238647461</t>
+    <t xml:space="preserve">8.70260047912598</t>
   </si>
   <si>
     <t xml:space="preserve">8.82716178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75242614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04306697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14271450042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28388214111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35031604766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35861778259277</t>
+    <t xml:space="preserve">8.75242519378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04306602478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14271354675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2838830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35031700134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35861968994141</t>
   </si>
   <si>
     <t xml:space="preserve">9.15102005004883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93511486053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7773380279541</t>
+    <t xml:space="preserve">8.93511390686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77733898162842</t>
   </si>
   <si>
     <t xml:space="preserve">9.19254016876221</t>
@@ -569,55 +566,55 @@
     <t xml:space="preserve">9.44996452331543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17593097686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00154685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13440990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91850757598877</t>
+    <t xml:space="preserve">9.17593002319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00154781341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1344108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91850662231445</t>
   </si>
   <si>
     <t xml:space="preserve">8.9268102645874</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00985050201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98493957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76073169708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11780452728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22575569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95172214508057</t>
+    <t xml:space="preserve">9.00985145568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98493671417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7607307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1178035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22575664520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95172023773193</t>
   </si>
   <si>
     <t xml:space="preserve">9.06797885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07628345489502</t>
+    <t xml:space="preserve">9.0762825012207</t>
   </si>
   <si>
     <t xml:space="preserve">9.20084381103516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31709957122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36692333221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49148464202881</t>
+    <t xml:space="preserve">9.31710052490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36692237854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49148273468018</t>
   </si>
   <si>
     <t xml:space="preserve">9.54961204528809</t>
@@ -626,13 +623,13 @@
     <t xml:space="preserve">9.96481132507324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0229396820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82364368438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93989944458008</t>
+    <t xml:space="preserve">10.0229406356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82364273071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93990039825439</t>
   </si>
   <si>
     <t xml:space="preserve">9.98142051696777</t>
@@ -641,7 +638,7 @@
     <t xml:space="preserve">10.0063323974609</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0561571121216</t>
+    <t xml:space="preserve">10.0561561584473</t>
   </si>
   <si>
     <t xml:space="preserve">10.2056283950806</t>
@@ -650,25 +647,25 @@
     <t xml:space="preserve">10.230541229248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2139329910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.197322845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1558036804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1225881576538</t>
+    <t xml:space="preserve">10.2139320373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1973237991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1558046340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1225900650024</t>
   </si>
   <si>
     <t xml:space="preserve">10.1807165145874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.147500038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2222375869751</t>
+    <t xml:space="preserve">10.1475009918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2222356796265</t>
   </si>
   <si>
     <t xml:space="preserve">10.1308927536011</t>
@@ -677,13 +674,13 @@
     <t xml:space="preserve">10.0976762771606</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84855556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3135795593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0810670852661</t>
+    <t xml:space="preserve">9.84855651855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3135805130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0810680389404</t>
   </si>
   <si>
     <t xml:space="preserve">10.0727643966675</t>
@@ -692,40 +689,40 @@
     <t xml:space="preserve">10.5294847488403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4464435577393</t>
+    <t xml:space="preserve">10.4464445114136</t>
   </si>
   <si>
     <t xml:space="preserve">10.5211811065674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3883171081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4713573455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6872615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.720477104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540451049805</t>
+    <t xml:space="preserve">10.38831615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4713563919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6872606277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7204761505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540460586548</t>
   </si>
   <si>
     <t xml:space="preserve">10.4049253463745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6457405090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7952117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9612941741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9280767440796</t>
+    <t xml:space="preserve">10.6457386016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7952127456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.96129322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9280776977539</t>
   </si>
   <si>
     <t xml:space="preserve">10.7703008651733</t>
@@ -734,7 +731,7 @@
     <t xml:space="preserve">10.7786045074463</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8699493408203</t>
+    <t xml:space="preserve">10.869948387146</t>
   </si>
   <si>
     <t xml:space="preserve">10.7869081497192</t>
@@ -743,16 +740,16 @@
     <t xml:space="preserve">11.0360288619995</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8948612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0443334579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2519330978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1771974563599</t>
+    <t xml:space="preserve">10.8948602676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0443344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2519340515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1771984100342</t>
   </si>
   <si>
     <t xml:space="preserve">11.2270212173462</t>
@@ -764,13 +761,13 @@
     <t xml:space="preserve">11.2851495742798</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3432769775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.393102645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4512281417847</t>
+    <t xml:space="preserve">11.3432779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3931016921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4512300491333</t>
   </si>
   <si>
     <t xml:space="preserve">11.5093584060669</t>
@@ -779,10 +776,10 @@
     <t xml:space="preserve">11.5010538101196</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5176620483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.741870880127</t>
+    <t xml:space="preserve">11.5176610946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7418699264526</t>
   </si>
   <si>
     <t xml:space="preserve">11.7584781646729</t>
@@ -791,37 +788,37 @@
     <t xml:space="preserve">11.6920461654663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6837406158447</t>
+    <t xml:space="preserve">11.6837425231934</t>
   </si>
   <si>
     <t xml:space="preserve">11.7252626419067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7667818069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7169589996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5923986434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7003507614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5425758361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9577732086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0574216842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9162540435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9909915924072</t>
+    <t xml:space="preserve">11.7667827606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7169570922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5923976898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7003498077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5425748825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9577751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0574226379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9162549972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9909906387329</t>
   </si>
   <si>
     <t xml:space="preserve">11.98268699646</t>
@@ -830,61 +827,64 @@
     <t xml:space="preserve">12.1487674713135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0491199493408</t>
+    <t xml:space="preserve">12.0491189956665</t>
   </si>
   <si>
     <t xml:space="preserve">12.2899351119995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3895816802979</t>
+    <t xml:space="preserve">12.3895835876465</t>
   </si>
   <si>
     <t xml:space="preserve">12.3148469924927</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5058403015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5390558242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2733278274536</t>
+    <t xml:space="preserve">12.505838394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5390539169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2733268737793</t>
   </si>
   <si>
     <t xml:space="preserve">12.1902866363525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1985912322998</t>
+    <t xml:space="preserve">12.1985902786255</t>
   </si>
   <si>
     <t xml:space="preserve">12.0823345184326</t>
   </si>
   <si>
-    <t xml:space="preserve">11.64222240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5508785247803</t>
+    <t xml:space="preserve">11.6422233581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.550877571106</t>
   </si>
   <si>
     <t xml:space="preserve">11.8083019256592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9346389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9514827728271</t>
+    <t xml:space="preserve">11.9346399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9514837265015</t>
   </si>
   <si>
     <t xml:space="preserve">12.0609769821167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1620464324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7830333709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6566972732544</t>
+    <t xml:space="preserve">12.1620454788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.783034324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6566982269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8083028793335</t>
   </si>
   <si>
     <t xml:space="preserve">11.7577667236328</t>
@@ -893,34 +893,34 @@
     <t xml:space="preserve">11.5977411270142</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5640497207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3029546737671</t>
+    <t xml:space="preserve">11.5640506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3029556274414</t>
   </si>
   <si>
     <t xml:space="preserve">11.2018852233887</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1934604644775</t>
+    <t xml:space="preserve">11.1934614181519</t>
   </si>
   <si>
     <t xml:space="preserve">11.0334339141846</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9576320648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.23557472229</t>
+    <t xml:space="preserve">10.9576330184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2355737686157</t>
   </si>
   <si>
     <t xml:space="preserve">11.4208679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2271528244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2861089706421</t>
+    <t xml:space="preserve">11.2271509170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2861080169678</t>
   </si>
   <si>
     <t xml:space="preserve">11.1681938171387</t>
@@ -935,19 +935,19 @@
     <t xml:space="preserve">10.763916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9492092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5786199569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7891845703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7386484146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6544237136841</t>
+    <t xml:space="preserve">10.9492101669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5786218643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7891836166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7386493682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6544227600098</t>
   </si>
   <si>
     <t xml:space="preserve">10.7554931640625</t>
@@ -956,37 +956,37 @@
     <t xml:space="preserve">11.4292907714844</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5219373703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2945318222046</t>
+    <t xml:space="preserve">11.5219383239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2945308685303</t>
   </si>
   <si>
     <t xml:space="preserve">11.6398525238037</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4629812240601</t>
+    <t xml:space="preserve">11.4629802703857</t>
   </si>
   <si>
     <t xml:space="preserve">11.4124460220337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.361909866333</t>
+    <t xml:space="preserve">11.3619108200073</t>
   </si>
   <si>
     <t xml:space="preserve">11.3197984695435</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2103061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9997444152832</t>
+    <t xml:space="preserve">11.2103071212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9997434616089</t>
   </si>
   <si>
     <t xml:space="preserve">10.991322517395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0081672668457</t>
+    <t xml:space="preserve">11.00816822052</t>
   </si>
   <si>
     <t xml:space="preserve">10.8902530670166</t>
@@ -995,13 +995,13 @@
     <t xml:space="preserve">10.9323644638062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8734083175659</t>
+    <t xml:space="preserve">10.8734073638916</t>
   </si>
   <si>
     <t xml:space="preserve">10.8818302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6796913146973</t>
+    <t xml:space="preserve">10.6796903610229</t>
   </si>
   <si>
     <t xml:space="preserve">10.78076171875</t>
@@ -1010,22 +1010,22 @@
     <t xml:space="preserve">10.8649854660034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7049598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9155197143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2608404159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1513481140137</t>
+    <t xml:space="preserve">10.7049579620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9155206680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2608413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1513500213623</t>
   </si>
   <si>
     <t xml:space="preserve">11.0839700698853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0502796173096</t>
+    <t xml:space="preserve">11.0502786636353</t>
   </si>
   <si>
     <t xml:space="preserve">11.2524194717407</t>
@@ -1037,16 +1037,16 @@
     <t xml:space="preserve">11.3787574768066</t>
   </si>
   <si>
-    <t xml:space="preserve">11.395601272583</t>
+    <t xml:space="preserve">11.3955993652344</t>
   </si>
   <si>
     <t xml:space="preserve">11.5050935745239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4040241241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5556287765503</t>
+    <t xml:space="preserve">11.4040250778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.555627822876</t>
   </si>
   <si>
     <t xml:space="preserve">11.6819648742676</t>
@@ -1058,19 +1058,19 @@
     <t xml:space="preserve">11.9177932739258</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8841037750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9430627822876</t>
+    <t xml:space="preserve">11.8841028213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9430618286133</t>
   </si>
   <si>
     <t xml:space="preserve">12.0525541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0946664810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1536226272583</t>
+    <t xml:space="preserve">12.0946674346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1536235809326</t>
   </si>
   <si>
     <t xml:space="preserve">12.0357084274292</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">12.0441312789917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1788911819458</t>
+    <t xml:space="preserve">12.1788902282715</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704683303833</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">12.3136510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3220739364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3726062774658</t>
+    <t xml:space="preserve">12.3220729827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3726072311401</t>
   </si>
   <si>
     <t xml:space="preserve">12.2041578292847</t>
@@ -1103,19 +1103,19 @@
     <t xml:space="preserve">12.2883825302124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2968053817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7914571762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7325000762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8167247772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0104417800903</t>
+    <t xml:space="preserve">12.2968063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7914552688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7325010299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.816722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.010440826416</t>
   </si>
   <si>
     <t xml:space="preserve">12.0020179748535</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">10.6965351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8986759185791</t>
+    <t xml:space="preserve">10.8986749649048</t>
   </si>
   <si>
     <t xml:space="preserve">10.8228731155396</t>
@@ -1145,16 +1145,16 @@
     <t xml:space="preserve">11.0165910720825</t>
   </si>
   <si>
-    <t xml:space="preserve">10.940788269043</t>
+    <t xml:space="preserve">10.9407873153687</t>
   </si>
   <si>
     <t xml:space="preserve">10.7723379135132</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7976055145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7302255630493</t>
+    <t xml:space="preserve">10.7976036071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7302265167236</t>
   </si>
   <si>
     <t xml:space="preserve">10.7218036651611</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">10.6628475189209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6123104095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8060274124146</t>
+    <t xml:space="preserve">10.6123123168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8060293197632</t>
   </si>
   <si>
     <t xml:space="preserve">10.6881132125854</t>
@@ -1175,46 +1175,46 @@
     <t xml:space="preserve">10.8312950134277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6712675094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4691295623779</t>
+    <t xml:space="preserve">10.6712694168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4691286087036</t>
   </si>
   <si>
     <t xml:space="preserve">10.4859733581543</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0923919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1597728729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1345052719116</t>
+    <t xml:space="preserve">11.0923910140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1597709655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1345043182373</t>
   </si>
   <si>
     <t xml:space="preserve">11.1429271697998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187299728394</t>
+    <t xml:space="preserve">11.218729019165</t>
   </si>
   <si>
     <t xml:space="preserve">11.4545583724976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3450660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4270181655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3175239562988</t>
+    <t xml:space="preserve">11.3450651168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4270172119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3175258636475</t>
   </si>
   <si>
     <t xml:space="preserve">10.2417221069336</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2838354110718</t>
+    <t xml:space="preserve">10.2838344573975</t>
   </si>
   <si>
     <t xml:space="preserve">10.1911869049072</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">10.1574974060059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2248764038086</t>
+    <t xml:space="preserve">10.2248773574829</t>
   </si>
   <si>
     <t xml:space="preserve">10.1659202575684</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1069612503052</t>
+    <t xml:space="preserve">10.1069631576538</t>
   </si>
   <si>
     <t xml:space="preserve">10.0985403060913</t>
@@ -1238,40 +1238,40 @@
     <t xml:space="preserve">9.93009090423584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98904705047607</t>
+    <t xml:space="preserve">9.98904895782471</t>
   </si>
   <si>
     <t xml:space="preserve">10.0058927536011</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7195291519165</t>
+    <t xml:space="preserve">9.71953010559082</t>
   </si>
   <si>
     <t xml:space="preserve">9.68583965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48370170593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37420749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1153860092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3091020584106</t>
+    <t xml:space="preserve">9.48370265960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37420845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.115385055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3091011047363</t>
   </si>
   <si>
     <t xml:space="preserve">10.5954656600952</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7133808135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6038875579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3596363067627</t>
+    <t xml:space="preserve">10.7133817672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6038885116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.359637260437</t>
   </si>
   <si>
     <t xml:space="preserve">10.3006801605225</t>
@@ -1280,19 +1280,19 @@
     <t xml:space="preserve">10.4522838592529</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4017505645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5617780685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5449323654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3427906036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438619613647</t>
+    <t xml:space="preserve">10.4017486572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5617761611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5449314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.342791557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438610076904</t>
   </si>
   <si>
     <t xml:space="preserve">10.4101715087891</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">10.5365085601807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2754125595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2080335617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0648517608643</t>
+    <t xml:space="preserve">10.2754135131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2080326080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0648508071899</t>
   </si>
   <si>
     <t xml:space="preserve">9.93851375579834</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">10.0500860214233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.384801864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3075609207153</t>
+    <t xml:space="preserve">10.3848028182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.307559967041</t>
   </si>
   <si>
     <t xml:space="preserve">10.771014213562</t>
@@ -1358,82 +1358,82 @@
     <t xml:space="preserve">10.470627784729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5049571990967</t>
+    <t xml:space="preserve">10.5049562454224</t>
   </si>
   <si>
     <t xml:space="preserve">10.642276763916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6851892471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.659441947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7109384536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.93408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6508598327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.745267868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.530704498291</t>
+    <t xml:space="preserve">10.685188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6594429016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9340829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6508588790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452669143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5307054519653</t>
   </si>
   <si>
     <t xml:space="preserve">10.393385887146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3504724502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1444940567017</t>
+    <t xml:space="preserve">10.3504734039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1444931030273</t>
   </si>
   <si>
     <t xml:space="preserve">10.1359119415283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92134952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0758333206177</t>
+    <t xml:space="preserve">9.92134857177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.075834274292</t>
   </si>
   <si>
     <t xml:space="preserve">10.058669090271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89560127258301</t>
+    <t xml:space="preserve">9.89560222625732</t>
   </si>
   <si>
     <t xml:space="preserve">9.94709587097168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74111843109131</t>
+    <t xml:space="preserve">9.74111652374268</t>
   </si>
   <si>
     <t xml:space="preserve">9.76686477661133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85268783569336</t>
+    <t xml:space="preserve">9.85268878936768</t>
   </si>
   <si>
     <t xml:space="preserve">9.87843704223633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99000930786133</t>
+    <t xml:space="preserve">9.99001026153564</t>
   </si>
   <si>
     <t xml:space="preserve">10.2560663223267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2903966903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.273229598999</t>
+    <t xml:space="preserve">10.2903957366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2732305526733</t>
   </si>
   <si>
     <t xml:space="preserve">10.5135402679443</t>
@@ -1445,34 +1445,34 @@
     <t xml:space="preserve">10.436297416687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.333309173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0844163894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1273279190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.015754699707</t>
+    <t xml:space="preserve">10.3333082199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.084415435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1273288726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0157566070557</t>
   </si>
   <si>
     <t xml:space="preserve">10.0329217910767</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84410667419434</t>
+    <t xml:space="preserve">9.84410762786865</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415029525757</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2389001846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78402900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.706787109375</t>
+    <t xml:space="preserve">10.23890209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78402996063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70678615570068</t>
   </si>
   <si>
     <t xml:space="preserve">9.77544593811035</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">9.68103885650635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56088638305664</t>
+    <t xml:space="preserve">9.56088447570801</t>
   </si>
   <si>
     <t xml:space="preserve">9.59521389007568</t>
@@ -1496,13 +1496,13 @@
     <t xml:space="preserve">9.48364162445068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62954425811768</t>
+    <t xml:space="preserve">9.62954521179199</t>
   </si>
   <si>
     <t xml:space="preserve">9.912766456604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88702011108398</t>
+    <t xml:space="preserve">9.88701915740967</t>
   </si>
   <si>
     <t xml:space="preserve">9.75828266143799</t>
@@ -1511,13 +1511,13 @@
     <t xml:space="preserve">9.56946659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57805061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73253536224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61237907409668</t>
+    <t xml:space="preserve">9.57804775238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73253440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.612380027771</t>
   </si>
   <si>
     <t xml:space="preserve">9.71536922454834</t>
@@ -1535,22 +1535,22 @@
     <t xml:space="preserve">9.99859237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96426296234131</t>
+    <t xml:space="preserve">9.96426105499268</t>
   </si>
   <si>
     <t xml:space="preserve">9.86985397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69820404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86127090454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52655410766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21758651733398</t>
+    <t xml:space="preserve">9.69820499420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86127185821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52655601501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21758460998535</t>
   </si>
   <si>
     <t xml:space="preserve">9.23475074768066</t>
@@ -1559,16 +1559,16 @@
     <t xml:space="preserve">8.69405555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52669525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4408712387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12332057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43228816986084</t>
+    <t xml:space="preserve">8.52669620513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44087028503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12331962585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43228912353516</t>
   </si>
   <si>
     <t xml:space="preserve">8.52240371704102</t>
@@ -1580,25 +1580,25 @@
     <t xml:space="preserve">8.29926013946533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16623020172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23060131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08469867706299</t>
+    <t xml:space="preserve">8.16623210906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23060035705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08469676971436</t>
   </si>
   <si>
     <t xml:space="preserve">8.35504627227783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22630882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48378467559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39366817474365</t>
+    <t xml:space="preserve">8.22630977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48378372192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39366722106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.57819080352783</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">8.02032947540283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79289388656616</t>
+    <t xml:space="preserve">7.79289245605469</t>
   </si>
   <si>
     <t xml:space="preserve">7.72852468490601</t>
@@ -1628,130 +1628,130 @@
     <t xml:space="preserve">7.77143621444702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83151435852051</t>
+    <t xml:space="preserve">7.83151388168335</t>
   </si>
   <si>
     <t xml:space="preserve">8.00316333770752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02891063690186</t>
+    <t xml:space="preserve">8.02891159057617</t>
   </si>
   <si>
     <t xml:space="preserve">8.00745487213135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25205612182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28638648986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61681270599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.608229637146</t>
+    <t xml:space="preserve">8.25205516815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28638744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61681175231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60822868347168</t>
   </si>
   <si>
     <t xml:space="preserve">8.54815101623535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75413227081299</t>
+    <t xml:space="preserve">8.75413036346436</t>
   </si>
   <si>
     <t xml:space="preserve">8.48807430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46232891082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16193962097168</t>
+    <t xml:space="preserve">8.462327003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.161940574646</t>
   </si>
   <si>
     <t xml:space="preserve">8.19197845458984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98170709609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0889892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33788013458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81435012817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69848680496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99887466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81863975524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86584568023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5869140625</t>
+    <t xml:space="preserve">7.98170852661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08898830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33788108825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81434965133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69848728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81864070892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8658447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58691263198853</t>
   </si>
   <si>
     <t xml:space="preserve">7.634117603302</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68990325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65986585617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96454286575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93879652023315</t>
+    <t xml:space="preserve">7.6899037361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6598653793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96454381942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93879556655884</t>
   </si>
   <si>
     <t xml:space="preserve">8.73696613311768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82279109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47949123382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38508415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40224933624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45374488830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36791896820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49665641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50094890594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46661949157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59964847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85712146759033</t>
+    <t xml:space="preserve">8.82279205322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.385085105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40225028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45374393463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.367919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.496657371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50094795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46661758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59964752197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85712242126465</t>
   </si>
   <si>
     <t xml:space="preserve">8.56960773468018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56531620025635</t>
+    <t xml:space="preserve">8.56531810760498</t>
   </si>
   <si>
     <t xml:space="preserve">8.55673313140869</t>
@@ -1760,85 +1760,85 @@
     <t xml:space="preserve">8.53956985473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50523948669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50953006744385</t>
+    <t xml:space="preserve">8.50524044036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50953102111816</t>
   </si>
   <si>
     <t xml:space="preserve">8.24776458740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15335750579834</t>
+    <t xml:space="preserve">8.15335845947266</t>
   </si>
   <si>
     <t xml:space="preserve">8.39795780181885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58248043060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77129650115967</t>
+    <t xml:space="preserve">8.58248138427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77129554748535</t>
   </si>
   <si>
     <t xml:space="preserve">8.65972423553467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09743022918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96869277954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.020188331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28624534606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31199169158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0802640914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13176155090332</t>
+    <t xml:space="preserve">9.09743118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96869373321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02018737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28624439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31199359893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08026599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.131760597229</t>
   </si>
   <si>
     <t xml:space="preserve">9.32057476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94294548034668</t>
+    <t xml:space="preserve">8.942946434021</t>
   </si>
   <si>
     <t xml:space="preserve">8.81420803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78845977783203</t>
+    <t xml:space="preserve">8.78846073150635</t>
   </si>
   <si>
     <t xml:space="preserve">8.79704475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74554824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72838401794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.908616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14034366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42356586456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26049709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18325519561768</t>
+    <t xml:space="preserve">8.74554920196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72838497161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90861701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14034271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4235668182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26049900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18325614929199</t>
   </si>
   <si>
     <t xml:space="preserve">9.00302314758301</t>
@@ -1853,55 +1853,55 @@
     <t xml:space="preserve">8.65114116668701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68547248840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67688941955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87428665161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51797199249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44073009490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41498184204102</t>
+    <t xml:space="preserve">8.685471534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67689037322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87428569793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51797103881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44073104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41498279571533</t>
   </si>
   <si>
     <t xml:space="preserve">9.64670944213867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0672512054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93851470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.195987701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80977725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62096309661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50939083099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86570453643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95152854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83995723724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75851821899414</t>
+    <t xml:space="preserve">10.06725025177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93851280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1959886550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80977535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62096214294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50938987731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86570358276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95152950286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83995532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75851726531982</t>
   </si>
   <si>
     <t xml:space="preserve">8.77167415618896</t>
@@ -1919,31 +1919,31 @@
     <t xml:space="preserve">8.57869911193848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58746910095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47343826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55238342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42957878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18397235870361</t>
+    <t xml:space="preserve">8.58747100830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47343730926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55238246917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42957973480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1839714050293</t>
   </si>
   <si>
     <t xml:space="preserve">8.37695026397705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56992626190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67957305908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66202926635742</t>
+    <t xml:space="preserve">8.56992530822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67957210540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66202831268311</t>
   </si>
   <si>
     <t xml:space="preserve">8.8944787979126</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">8.75413131713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72781753540039</t>
+    <t xml:space="preserve">8.72781848907471</t>
   </si>
   <si>
     <t xml:space="preserve">8.72343063354492</t>
@@ -1964,10 +1964,10 @@
     <t xml:space="preserve">8.82430553436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0611400604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00850963592529</t>
+    <t xml:space="preserve">9.06113910675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00851058959961</t>
   </si>
   <si>
     <t xml:space="preserve">8.85062026977539</t>
@@ -1976,13 +1976,13 @@
     <t xml:space="preserve">8.71465873718262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88570880889893</t>
+    <t xml:space="preserve">8.88570785522461</t>
   </si>
   <si>
     <t xml:space="preserve">9.11377048492432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05236911773682</t>
+    <t xml:space="preserve">9.0523681640625</t>
   </si>
   <si>
     <t xml:space="preserve">9.28043174743652</t>
@@ -1991,16 +1991,16 @@
     <t xml:space="preserve">9.32429027557373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23657512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9295654296875</t>
+    <t xml:space="preserve">9.23657417297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92956447601318</t>
   </si>
   <si>
     <t xml:space="preserve">8.80676174163818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78921985626221</t>
+    <t xml:space="preserve">8.78921890258789</t>
   </si>
   <si>
     <t xml:space="preserve">8.49536800384521</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">8.45589542388916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48221015930176</t>
+    <t xml:space="preserve">8.48220920562744</t>
   </si>
   <si>
     <t xml:space="preserve">8.62255668640137</t>
@@ -2021,25 +2021,25 @@
     <t xml:space="preserve">9.07868385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0172815322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17958641052246</t>
+    <t xml:space="preserve">9.01728248596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17958736419678</t>
   </si>
   <si>
     <t xml:space="preserve">8.1313419342041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17081451416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96029567718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77170372009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61819982528687</t>
+    <t xml:space="preserve">8.17081546783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96029663085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77170467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61819887161255</t>
   </si>
   <si>
     <t xml:space="preserve">7.64890050888062</t>
@@ -2048,13 +2048,13 @@
     <t xml:space="preserve">7.63135766983032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38574981689453</t>
+    <t xml:space="preserve">7.38575029373169</t>
   </si>
   <si>
     <t xml:space="preserve">7.29803371429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39013671875</t>
+    <t xml:space="preserve">7.39013624191284</t>
   </si>
   <si>
     <t xml:space="preserve">7.22347354888916</t>
@@ -2072,115 +2072,115 @@
     <t xml:space="preserve">7.51293897628784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39890766143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26733207702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19277334213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44276666641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45153903961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32873344421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53048372268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79363346099854</t>
+    <t xml:space="preserve">7.39890813827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26733255386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19277429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44276571273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4515380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32873439788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53048324584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79363441467285</t>
   </si>
   <si>
     <t xml:space="preserve">7.98661041259766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06116771697998</t>
+    <t xml:space="preserve">8.0611686706543</t>
   </si>
   <si>
     <t xml:space="preserve">8.22344589233398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28923320770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35063648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21905899047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19274520874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30239200592041</t>
+    <t xml:space="preserve">8.28923225402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35063362121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21905994415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19274425506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30239105224609</t>
   </si>
   <si>
     <t xml:space="preserve">7.87257814407349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72346019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60942935943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74100255966187</t>
+    <t xml:space="preserve">7.72346067428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60942840576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74100303649902</t>
   </si>
   <si>
     <t xml:space="preserve">7.83310556411743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84187793731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67521572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50855445861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40329456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45592403411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44715118408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31557607650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4734673500061</t>
+    <t xml:space="preserve">7.84187746047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67521524429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50855350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4032940864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45592355728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44715213775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31557703018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47346687316895</t>
   </si>
   <si>
     <t xml:space="preserve">7.85064935684204</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85942029953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00854015350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04362773895264</t>
+    <t xml:space="preserve">7.85941934585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0085391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04362678527832</t>
   </si>
   <si>
     <t xml:space="preserve">7.80679035186768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91643714904785</t>
+    <t xml:space="preserve">7.91643619537354</t>
   </si>
   <si>
     <t xml:space="preserve">8.18835926055908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25414657592773</t>
+    <t xml:space="preserve">8.25414752960205</t>
   </si>
   <si>
     <t xml:space="preserve">8.29361820220947</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">8.37256336212158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43835163116455</t>
+    <t xml:space="preserve">8.43835258483887</t>
   </si>
   <si>
     <t xml:space="preserve">8.9646520614624</t>
@@ -2204,34 +2204,34 @@
     <t xml:space="preserve">9.12254238128662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14885711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37691974639893</t>
+    <t xml:space="preserve">9.14885807037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37692070007324</t>
   </si>
   <si>
     <t xml:space="preserve">9.56112575531006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75410270690918</t>
+    <t xml:space="preserve">9.75410175323486</t>
   </si>
   <si>
     <t xml:space="preserve">9.70147228240967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47340869903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35060405731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49095249176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24534606933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42078018188477</t>
+    <t xml:space="preserve">9.47340965270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35060501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49095058441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24534511566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42077922821045</t>
   </si>
   <si>
     <t xml:space="preserve">9.31551933288574</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">9.64884281158447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72778701782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80673217773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77164745330811</t>
+    <t xml:space="preserve">9.72778797149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80673313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77164649963379</t>
   </si>
   <si>
     <t xml:space="preserve">9.85936260223389</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">9.86813449859619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9207649230957</t>
+    <t xml:space="preserve">9.92076396942139</t>
   </si>
   <si>
     <t xml:space="preserve">9.9997091293335</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">9.84181976318359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89444923400879</t>
+    <t xml:space="preserve">9.89445018768311</t>
   </si>
   <si>
     <t xml:space="preserve">9.9821662902832</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">10.0698823928833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96462154388428</t>
+    <t xml:space="preserve">9.96462249755859</t>
   </si>
   <si>
     <t xml:space="preserve">9.67515754699707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71901702880859</t>
+    <t xml:space="preserve">9.71901607513428</t>
   </si>
   <si>
     <t xml:space="preserve">9.79796123504639</t>
@@ -2300,25 +2300,25 @@
     <t xml:space="preserve">9.52603912353516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63129901885986</t>
+    <t xml:space="preserve">9.63129997253418</t>
   </si>
   <si>
     <t xml:space="preserve">9.71024513244629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68392944335938</t>
+    <t xml:space="preserve">9.68392848968506</t>
   </si>
   <si>
     <t xml:space="preserve">9.69270038604736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76287364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73655891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57866859436035</t>
+    <t xml:space="preserve">9.76287460327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73655986785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57867050170898</t>
   </si>
   <si>
     <t xml:space="preserve">9.30674743652344</t>
@@ -2327,19 +2327,19 @@
     <t xml:space="preserve">9.21025848388672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33306312561035</t>
+    <t xml:space="preserve">9.33306217193604</t>
   </si>
   <si>
     <t xml:space="preserve">9.20148658752441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02605438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26288986206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13131332397461</t>
+    <t xml:space="preserve">9.02605533599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26288890838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13131427764893</t>
   </si>
   <si>
     <t xml:space="preserve">9.0874547958374</t>
@@ -2351,16 +2351,16 @@
     <t xml:space="preserve">9.42955017089844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21902942657471</t>
+    <t xml:space="preserve">9.21903038024902</t>
   </si>
   <si>
     <t xml:space="preserve">9.25411701202393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15762901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09622764587402</t>
+    <t xml:space="preserve">9.15763092041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09622669219971</t>
   </si>
   <si>
     <t xml:space="preserve">8.39449310302734</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">8.10502910614014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92959403991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49978303909302</t>
+    <t xml:space="preserve">7.92959356307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49978256225586</t>
   </si>
   <si>
     <t xml:space="preserve">7.60065603256226</t>
@@ -2387,25 +2387,25 @@
     <t xml:space="preserve">7.42960929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11821365356445</t>
+    <t xml:space="preserve">7.11821460723877</t>
   </si>
   <si>
     <t xml:space="preserve">7.18400192260742</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57875728607178</t>
+    <t xml:space="preserve">6.57875633239746</t>
   </si>
   <si>
     <t xml:space="preserve">6.64892959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55682611465454</t>
+    <t xml:space="preserve">6.5568265914917</t>
   </si>
   <si>
     <t xml:space="preserve">6.14017248153687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3857798576355</t>
+    <t xml:space="preserve">6.38577938079834</t>
   </si>
   <si>
     <t xml:space="preserve">5.87702226638794</t>
@@ -2414,19 +2414,19 @@
     <t xml:space="preserve">5.97351026535034</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55244112014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11382818222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72784471511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82436275482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02172613143921</t>
+    <t xml:space="preserve">6.55244064331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1138277053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72784423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82436323165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02172517776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.47349548339844</t>
@@ -2441,25 +2441,25 @@
     <t xml:space="preserve">5.96035289764404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85070753097534</t>
+    <t xml:space="preserve">5.85070705413818</t>
   </si>
   <si>
     <t xml:space="preserve">5.61387252807617</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18406009674072</t>
+    <t xml:space="preserve">5.18406057357788</t>
   </si>
   <si>
     <t xml:space="preserve">5.47352504730225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54369783401489</t>
+    <t xml:space="preserve">5.54369831085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.89895105361938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82439231872559</t>
+    <t xml:space="preserve">5.82439279556274</t>
   </si>
   <si>
     <t xml:space="preserve">5.64895820617676</t>
@@ -2468,25 +2468,25 @@
     <t xml:space="preserve">5.69720315933228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92965221405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06122779846191</t>
+    <t xml:space="preserve">5.92965269088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06122732162476</t>
   </si>
   <si>
     <t xml:space="preserve">6.0085973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05684185028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40332317352295</t>
+    <t xml:space="preserve">6.0568413734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40332221984863</t>
   </si>
   <si>
     <t xml:space="preserve">6.59191370010376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83752107620239</t>
+    <t xml:space="preserve">6.83752059936523</t>
   </si>
   <si>
     <t xml:space="preserve">6.69717311859131</t>
@@ -2501,13 +2501,13 @@
     <t xml:space="preserve">6.72348928451538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48665380477905</t>
+    <t xml:space="preserve">6.48665332794189</t>
   </si>
   <si>
     <t xml:space="preserve">6.48226737976074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36385059356689</t>
+    <t xml:space="preserve">6.36385107040405</t>
   </si>
   <si>
     <t xml:space="preserve">6.22788953781128</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">5.77176237106323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82000637054443</t>
+    <t xml:space="preserve">5.82000684738159</t>
   </si>
   <si>
     <t xml:space="preserve">6.26297569274902</t>
@@ -2525,70 +2525,70 @@
     <t xml:space="preserve">6.23227596282959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21911764144897</t>
+    <t xml:space="preserve">6.21911716461182</t>
   </si>
   <si>
     <t xml:space="preserve">6.39455032348633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59629964828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16207218170166</t>
+    <t xml:space="preserve">6.59629917144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16207265853882</t>
   </si>
   <si>
     <t xml:space="preserve">7.51732492446899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37259387969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33312034606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41645050048828</t>
+    <t xml:space="preserve">7.37259292602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33311986923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41645097732544</t>
   </si>
   <si>
     <t xml:space="preserve">7.79801988601685</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68398666381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55679750442505</t>
+    <t xml:space="preserve">7.68398809432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55679845809937</t>
   </si>
   <si>
     <t xml:space="preserve">7.10067176818848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35504913330078</t>
+    <t xml:space="preserve">7.35504961013794</t>
   </si>
   <si>
     <t xml:space="preserve">7.35066413879395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21031618118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23224639892578</t>
+    <t xml:space="preserve">7.21031713485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23224544525146</t>
   </si>
   <si>
     <t xml:space="preserve">7.17523002624512</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10505723953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20154571533203</t>
+    <t xml:space="preserve">7.10505676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20154523849487</t>
   </si>
   <si>
     <t xml:space="preserve">7.24540328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21470308303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17084455490112</t>
+    <t xml:space="preserve">7.21470260620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17084407806396</t>
   </si>
   <si>
     <t xml:space="preserve">7.40767908096313</t>
@@ -2600,61 +2600,61 @@
     <t xml:space="preserve">7.36820650100708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32434940338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14891481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24978923797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4383807182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16645812988281</t>
+    <t xml:space="preserve">7.32434892654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1489143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24978876113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43838024139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16645765304565</t>
   </si>
   <si>
     <t xml:space="preserve">6.70155954360962</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61384248733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69278812408447</t>
+    <t xml:space="preserve">6.61384201049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69278764724731</t>
   </si>
   <si>
     <t xml:space="preserve">6.75419044494629</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68401718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71033191680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83313465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06119823455811</t>
+    <t xml:space="preserve">6.68401670455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71033143997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83313512802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06119775772095</t>
   </si>
   <si>
     <t xml:space="preserve">7.1401424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05681276321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04804039001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00856781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94716691970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07435655593872</t>
+    <t xml:space="preserve">7.05681228637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04804086685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00856828689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94716644287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07435607910156</t>
   </si>
   <si>
     <t xml:space="preserve">7.0875129699707</t>
@@ -2663,34 +2663,34 @@
     <t xml:space="preserve">7.09628486633301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0173397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35943603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29364824295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49101066589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60504198074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97345161437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57434034347534</t>
+    <t xml:space="preserve">7.01734018325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35943460464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29364776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49100971221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60504245758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97345352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5743408203125</t>
   </si>
   <si>
     <t xml:space="preserve">7.41206550598145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88576507568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99102544784546</t>
+    <t xml:space="preserve">6.88576459884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99102449417114</t>
   </si>
   <si>
     <t xml:space="preserve">7.0392689704895</t>
@@ -2699,31 +2699,31 @@
     <t xml:space="preserve">7.06997013092041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31119155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48223972320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86380672454834</t>
+    <t xml:space="preserve">7.31119108200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48223924636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8638072013855</t>
   </si>
   <si>
     <t xml:space="preserve">7.92082262039185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99976634979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73661851882935</t>
+    <t xml:space="preserve">7.99976682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73661756515503</t>
   </si>
   <si>
     <t xml:space="preserve">7.68837356567383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61381387710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62697219848633</t>
+    <t xml:space="preserve">7.61381483078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62697124481201</t>
   </si>
   <si>
     <t xml:space="preserve">7.57872772216797</t>
@@ -2732,13 +2732,13 @@
     <t xml:space="preserve">7.77609014511108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80240535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96906614303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99099493026733</t>
+    <t xml:space="preserve">7.80240440368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96906566619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99099588394165</t>
   </si>
   <si>
     <t xml:space="preserve">8.15327167510986</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">8.54799747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56995630264282</t>
+    <t xml:space="preserve">7.56995582580566</t>
   </si>
   <si>
     <t xml:space="preserve">7.82433366775513</t>
@@ -2759,10 +2759,10 @@
     <t xml:space="preserve">7.71907424926758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78486204147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86819267272949</t>
+    <t xml:space="preserve">7.78486156463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86819314956665</t>
   </si>
   <si>
     <t xml:space="preserve">9.22780227661133</t>
@@ -2771,22 +2771,22 @@
     <t xml:space="preserve">9.17517280578613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39446353912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83304786682129</t>
+    <t xml:space="preserve">9.39446449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83304691314697</t>
   </si>
   <si>
     <t xml:space="preserve">9.58744144439697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40323638916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36814880371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35937786102295</t>
+    <t xml:space="preserve">9.40323543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36814975738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35937690734863</t>
   </si>
   <si>
     <t xml:space="preserve">9.53481101989746</t>
@@ -2801,70 +2801,70 @@
     <t xml:space="preserve">9.41200733184814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38569164276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61375617980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49972438812256</t>
+    <t xml:space="preserve">9.38569259643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61375713348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49972343444824</t>
   </si>
   <si>
     <t xml:space="preserve">9.03482532501221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74533176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90322113037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0961990356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1225128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93830871582031</t>
+    <t xml:space="preserve">9.74533271789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90322208404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0961980819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1225118637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.938307762146</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638660430908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88567638397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45586395263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51726627349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44709396362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82427501678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56989860534668</t>
+    <t xml:space="preserve">9.88567733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45586490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51726722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44709491729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82427597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56989669799805</t>
   </si>
   <si>
     <t xml:space="preserve">8.94710922241211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16639995574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28920269012451</t>
+    <t xml:space="preserve">9.16640090942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28920364379883</t>
   </si>
   <si>
     <t xml:space="preserve">9.27165985107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34183502197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19271564483643</t>
+    <t xml:space="preserve">9.34183406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19271469116211</t>
   </si>
   <si>
     <t xml:space="preserve">9.18394470214844</t>
@@ -2873,10 +2873,10 @@
     <t xml:space="preserve">8.90324878692627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06991195678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84184741973877</t>
+    <t xml:space="preserve">9.06991100311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84184837341309</t>
   </si>
   <si>
     <t xml:space="preserve">8.9997386932373</t>
@@ -2885,19 +2885,19 @@
     <t xml:space="preserve">8.97342395782471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18857192993164</t>
+    <t xml:space="preserve">9.18857097625732</t>
   </si>
   <si>
     <t xml:space="preserve">9.19807243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18909931182861</t>
+    <t xml:space="preserve">9.1890983581543</t>
   </si>
   <si>
     <t xml:space="preserve">9.43138980865479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57496929168701</t>
+    <t xml:space="preserve">9.5749683380127</t>
   </si>
   <si>
     <t xml:space="preserve">9.72752285003662</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">9.79931259155273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81725978851318</t>
+    <t xml:space="preserve">9.81725883483887</t>
   </si>
   <si>
     <t xml:space="preserve">9.94289207458496</t>
@@ -2942,25 +2942,25 @@
     <t xml:space="preserve">9.63778591156006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61086463928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69162845611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5031795501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58394336700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60188961029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55702209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54804801940918</t>
+    <t xml:space="preserve">9.61086368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69162750244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50317859649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58394241333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60189056396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55702114105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54804706573486</t>
   </si>
   <si>
     <t xml:space="preserve">9.35960006713867</t>
@@ -2972,10 +2972,10 @@
     <t xml:space="preserve">9.64675903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29678344726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33267879486084</t>
+    <t xml:space="preserve">9.29678249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33267784118652</t>
   </si>
   <si>
     <t xml:space="preserve">9.3865213394165</t>
@@ -2984,10 +2984,10 @@
     <t xml:space="preserve">9.39549541473389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7723913192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8890495300293</t>
+    <t xml:space="preserve">9.77239227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88905048370361</t>
   </si>
   <si>
     <t xml:space="preserve">10.3915786743164</t>
@@ -2996,13 +2996,13 @@
     <t xml:space="preserve">10.5800266265869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6518154144287</t>
+    <t xml:space="preserve">10.651816368103</t>
   </si>
   <si>
     <t xml:space="preserve">10.6877117156982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7415533065796</t>
+    <t xml:space="preserve">10.7415542602539</t>
   </si>
   <si>
     <t xml:space="preserve">10.8582124710083</t>
@@ -3011,22 +3011,22 @@
     <t xml:space="preserve">10.9389753341675</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9838438034058</t>
+    <t xml:space="preserve">10.9838447570801</t>
   </si>
   <si>
     <t xml:space="preserve">11.0556344985962</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1005020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0915279388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.127423286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0197381973267</t>
+    <t xml:space="preserve">11.1005029678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0915298461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1274242401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0197401046753</t>
   </si>
   <si>
     <t xml:space="preserve">10.9300022125244</t>
@@ -3035,19 +3035,19 @@
     <t xml:space="preserve">10.8312911987305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0376873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0107660293579</t>
+    <t xml:space="preserve">11.0376863479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0107669830322</t>
   </si>
   <si>
     <t xml:space="preserve">10.9748706817627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8761587142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.912055015564</t>
+    <t xml:space="preserve">10.8761596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9120540618896</t>
   </si>
   <si>
     <t xml:space="preserve">11.0466604232788</t>
@@ -3056,16 +3056,16 @@
     <t xml:space="preserve">10.9210271835327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8941059112549</t>
+    <t xml:space="preserve">10.8941078186035</t>
   </si>
   <si>
     <t xml:space="preserve">10.9030799865723</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8043699264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.75950050354</t>
+    <t xml:space="preserve">10.804370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7595024108887</t>
   </si>
   <si>
     <t xml:space="preserve">10.7864227294922</t>
@@ -3074,13 +3074,13 @@
     <t xml:space="preserve">10.8402643203735</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4274730682373</t>
+    <t xml:space="preserve">10.4274740219116</t>
   </si>
   <si>
     <t xml:space="preserve">10.2569723129272</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90699768066406</t>
+    <t xml:space="preserve">9.90699672698975</t>
   </si>
   <si>
     <t xml:space="preserve">9.96083927154541</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">10.1403141021729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0954446792603</t>
+    <t xml:space="preserve">10.0954456329346</t>
   </si>
   <si>
     <t xml:space="preserve">9.87110137939453</t>
@@ -3104,10 +3104,10 @@
     <t xml:space="preserve">9.80828666687012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56599617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47625923156738</t>
+    <t xml:space="preserve">9.56599521636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47625827789307</t>
   </si>
   <si>
     <t xml:space="preserve">9.67368030548096</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">9.70957469940186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75444412231445</t>
+    <t xml:space="preserve">9.75444316864014</t>
   </si>
   <si>
     <t xml:space="preserve">9.84418106079102</t>
@@ -3125,43 +3125,43 @@
     <t xml:space="preserve">9.85315418243408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82623386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86212825775146</t>
+    <t xml:space="preserve">9.82623195648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86212730407715</t>
   </si>
   <si>
     <t xml:space="preserve">10.0236558914185</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96981334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1672353744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492872238159</t>
+    <t xml:space="preserve">9.96981239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1672344207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492881774902</t>
   </si>
   <si>
     <t xml:space="preserve">10.2031297683716</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1851825714111</t>
+    <t xml:space="preserve">10.1851835250854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2838935852051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3377370834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4454202651978</t>
+    <t xml:space="preserve">10.3377361297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4454212188721</t>
   </si>
   <si>
     <t xml:space="preserve">10.5172100067139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3467092514038</t>
+    <t xml:space="preserve">10.3467102050781</t>
   </si>
   <si>
     <t xml:space="preserve">10.3018407821655</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">10.4184989929199</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4364471435547</t>
+    <t xml:space="preserve">10.436448097229</t>
   </si>
   <si>
     <t xml:space="preserve">10.7774486541748</t>
@@ -3179,10 +3179,10 @@
     <t xml:space="preserve">10.8492383956909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6966848373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7684745788574</t>
+    <t xml:space="preserve">10.6966857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7684755325317</t>
   </si>
   <si>
     <t xml:space="preserve">10.5620794296265</t>
@@ -3194,16 +3194,16 @@
     <t xml:space="preserve">10.2479982376099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.490288734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5979738235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8671846389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1453704833984</t>
+    <t xml:space="preserve">10.4902896881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5979747772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8671855926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1453723907471</t>
   </si>
   <si>
     <t xml:space="preserve">10.9658966064453</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">11.1094770431519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1722917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2440814971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2261343002319</t>
+    <t xml:space="preserve">11.1722927093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2440824508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2261352539062</t>
   </si>
   <si>
     <t xml:space="preserve">11.190239906311</t>
@@ -3233,19 +3233,19 @@
     <t xml:space="preserve">11.4594526290894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6299533843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8004531860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0068492889404</t>
+    <t xml:space="preserve">11.6299524307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8004541397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0068502426147</t>
   </si>
   <si>
     <t xml:space="preserve">11.6568737030029</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8453216552734</t>
+    <t xml:space="preserve">11.8453226089478</t>
   </si>
   <si>
     <t xml:space="preserve">11.2171611785889</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">11.2081871032715</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3248462677002</t>
+    <t xml:space="preserve">11.3248453140259</t>
   </si>
   <si>
     <t xml:space="preserve">11.2620306015015</t>
@@ -3263,10 +3263,10 @@
     <t xml:space="preserve">11.1363983154297</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8223171234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3287620544434</t>
+    <t xml:space="preserve">10.8223180770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3287630081177</t>
   </si>
   <si>
     <t xml:space="preserve">10.5351572036743</t>
@@ -3290,13 +3290,13 @@
     <t xml:space="preserve">10.7146320343018</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6248950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4005517959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6069469451904</t>
+    <t xml:space="preserve">10.6248960494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4005527496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6069478988647</t>
   </si>
   <si>
     <t xml:space="preserve">9.44933700561523</t>
@@ -3308,25 +3308,25 @@
     <t xml:space="preserve">8.01354122161865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0225133895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15712070465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48914909362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20198917388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3455696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53850269317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67759609222412</t>
+    <t xml:space="preserve">8.02251434326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15711975097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4891471862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20198822021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34556865692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5385046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67759704589844</t>
   </si>
   <si>
     <t xml:space="preserve">9.09038829803467</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">9.01859855651855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1083345413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18012523651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13525676727295</t>
+    <t xml:space="preserve">9.10833549499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18012428283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13525581359863</t>
   </si>
   <si>
     <t xml:space="preserve">8.98270416259766</t>
@@ -3353,10 +3353,10 @@
     <t xml:space="preserve">8.79874229431152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34165287017822</t>
+    <t xml:space="preserve">8.90642738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34165191650391</t>
   </si>
   <si>
     <t xml:space="preserve">9.25191497802734</t>
@@ -3365,10 +3365,10 @@
     <t xml:space="preserve">9.08141422271729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97372913360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.036545753479</t>
+    <t xml:space="preserve">8.97373008728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03654479980469</t>
   </si>
   <si>
     <t xml:space="preserve">8.83014965057373</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">8.43979167938232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26480579376221</t>
+    <t xml:space="preserve">8.26480484008789</t>
   </si>
   <si>
     <t xml:space="preserve">8.36351585388184</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">8.27377891540527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30967330932617</t>
+    <t xml:space="preserve">8.30967426300049</t>
   </si>
   <si>
     <t xml:space="preserve">8.35005474090576</t>
@@ -3395,19 +3395,19 @@
     <t xml:space="preserve">8.36800193786621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51606941223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94232177734375</t>
+    <t xml:space="preserve">8.51606845855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94232082366943</t>
   </si>
   <si>
     <t xml:space="preserve">8.70900440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57439804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45773983001709</t>
+    <t xml:space="preserve">8.57439994812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45774078369141</t>
   </si>
   <si>
     <t xml:space="preserve">8.46671390533447</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">8.61478042602539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49363422393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30070018768311</t>
+    <t xml:space="preserve">8.4936351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30069923400879</t>
   </si>
   <si>
     <t xml:space="preserve">8.18404102325439</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">8.25134372711182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12571144104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88399124145508</t>
+    <t xml:space="preserve">8.12571239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88399028778076</t>
   </si>
   <si>
     <t xml:space="preserve">9.65573310852051</t>
@@ -3440,37 +3440,37 @@
     <t xml:space="preserve">9.6856861114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58440971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63044357299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87902927398682</t>
+    <t xml:space="preserve">9.5844087600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63044452667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87903022766113</t>
   </si>
   <si>
     <t xml:space="preserve">10.0539627075195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2104806900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95268726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98030662536621</t>
+    <t xml:space="preserve">10.2104797363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95268630981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98030757904053</t>
   </si>
   <si>
     <t xml:space="preserve">10.035548210144</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89744567871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0631694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1184110641479</t>
+    <t xml:space="preserve">9.89744472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0631704330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1184101104736</t>
   </si>
   <si>
     <t xml:space="preserve">10.1552391052246</t>
@@ -3479,10 +3479,10 @@
     <t xml:space="preserve">9.63965129852295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40027046203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22533893585205</t>
+    <t xml:space="preserve">9.40027141571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22533988952637</t>
   </si>
   <si>
     <t xml:space="preserve">9.44630527496338</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">8.98595905303955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02278614044189</t>
+    <t xml:space="preserve">9.02278709411621</t>
   </si>
   <si>
     <t xml:space="preserve">9.03199481964111</t>
@@ -3506,43 +3506,43 @@
     <t xml:space="preserve">8.66832065582275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62228584289551</t>
+    <t xml:space="preserve">8.62228488922119</t>
   </si>
   <si>
     <t xml:space="preserve">8.67292404174805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77419948577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73737239837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53482055664062</t>
+    <t xml:space="preserve">8.77420043945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73737144470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53481960296631</t>
   </si>
   <si>
     <t xml:space="preserve">8.52561283111572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30464744567871</t>
+    <t xml:space="preserve">8.30464649200439</t>
   </si>
   <si>
     <t xml:space="preserve">8.35988807678223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80642318725586</t>
+    <t xml:space="preserve">8.80642414093018</t>
   </si>
   <si>
     <t xml:space="preserve">9.08263206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8570613861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88928604125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82023525238037</t>
+    <t xml:space="preserve">8.85706233978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88928699493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82023429870605</t>
   </si>
   <si>
     <t xml:space="preserve">8.60847568511963</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">9.00437259674072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06882190704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10564994812012</t>
+    <t xml:space="preserve">9.06882095336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1056489944458</t>
   </si>
   <si>
     <t xml:space="preserve">9.14247703552246</t>
@@ -3566,22 +3566,22 @@
     <t xml:space="preserve">8.99976921081543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71895885467529</t>
+    <t xml:space="preserve">8.71895790100098</t>
   </si>
   <si>
     <t xml:space="preserve">8.86166572570801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17470169067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47392654418945</t>
+    <t xml:space="preserve">9.17470073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47392559051514</t>
   </si>
   <si>
     <t xml:space="preserve">9.5936164855957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6488561630249</t>
+    <t xml:space="preserve">9.64885711669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.77775478363037</t>
@@ -3593,22 +3593,22 @@
     <t xml:space="preserve">9.55678844451904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75934028625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171901702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66727161407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37265014648438</t>
+    <t xml:space="preserve">9.7593412399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171997070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66727066040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37264919281006</t>
   </si>
   <si>
     <t xml:space="preserve">9.53837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21613216400146</t>
+    <t xml:space="preserve">9.21613311767578</t>
   </si>
   <si>
     <t xml:space="preserve">8.84325122833252</t>
@@ -3623,10 +3623,10 @@
     <t xml:space="preserve">8.59466457366943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56244087219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57164764404297</t>
+    <t xml:space="preserve">8.5624418258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57164859771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.44275093078613</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">8.45195770263672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14352512359619</t>
+    <t xml:space="preserve">8.14352607727051</t>
   </si>
   <si>
     <t xml:space="preserve">8.12511157989502</t>
@@ -3647,25 +3647,25 @@
     <t xml:space="preserve">8.23559474945068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23099040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42433643341064</t>
+    <t xml:space="preserve">8.23099136352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42433547973633</t>
   </si>
   <si>
     <t xml:space="preserve">8.76959609985352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75578594207764</t>
+    <t xml:space="preserve">8.75578689575195</t>
   </si>
   <si>
     <t xml:space="preserve">8.7926139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51640605926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3138542175293</t>
+    <t xml:space="preserve">8.51640510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31385326385498</t>
   </si>
   <si>
     <t xml:space="preserve">8.33226776123047</t>
@@ -3674,13 +3674,13 @@
     <t xml:space="preserve">8.2171802520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09749126434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01923179626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77985191345215</t>
+    <t xml:space="preserve">8.09749031066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01923274993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77985143661499</t>
   </si>
   <si>
     <t xml:space="preserve">7.88112878799438</t>
@@ -3689,28 +3689,28 @@
     <t xml:space="preserve">7.83049058914185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82588672637939</t>
+    <t xml:space="preserve">7.82588624954224</t>
   </si>
   <si>
     <t xml:space="preserve">7.4944372177124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82128238677979</t>
+    <t xml:space="preserve">7.82128286361694</t>
   </si>
   <si>
     <t xml:space="preserve">7.97319746017456</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31845760345459</t>
+    <t xml:space="preserve">8.31845664978027</t>
   </si>
   <si>
     <t xml:space="preserve">8.2217845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34147548675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30924987792969</t>
+    <t xml:space="preserve">8.34147453308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30924892425537</t>
   </si>
   <si>
     <t xml:space="preserve">8.29543972015381</t>
@@ -3725,13 +3725,13 @@
     <t xml:space="preserve">8.61307811737061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66371631622314</t>
+    <t xml:space="preserve">8.66371726989746</t>
   </si>
   <si>
     <t xml:space="preserve">8.73276805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90769958496094</t>
+    <t xml:space="preserve">8.90770053863525</t>
   </si>
   <si>
     <t xml:space="preserve">8.91690731048584</t>
@@ -3740,19 +3740,19 @@
     <t xml:space="preserve">8.97214889526367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79721736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19311428070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54758071899414</t>
+    <t xml:space="preserve">8.79721832275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.193115234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54758167266846</t>
   </si>
   <si>
     <t xml:space="preserve">9.82378959655762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79616928100586</t>
+    <t xml:space="preserve">9.79616832733154</t>
   </si>
   <si>
     <t xml:space="preserve">9.74092674255371</t>
@@ -3761,28 +3761,28 @@
     <t xml:space="preserve">9.80537509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0723752975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.219687461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8641719818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7260665893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6892404556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444829940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5143089294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2381010055542</t>
+    <t xml:space="preserve">10.0723762512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2196865081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8641710281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7260675430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6892395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444820404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.514307975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2381019592285</t>
   </si>
   <si>
     <t xml:space="preserve">10.339376449585</t>
@@ -3791,19 +3791,19 @@
     <t xml:space="preserve">10.2841358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3209638595581</t>
+    <t xml:space="preserve">10.3209629058838</t>
   </si>
   <si>
     <t xml:space="preserve">10.1368246078491</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1828603744507</t>
+    <t xml:space="preserve">10.1828594207764</t>
   </si>
   <si>
     <t xml:space="preserve">10.3485841751099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1920652389526</t>
+    <t xml:space="preserve">10.192066192627</t>
   </si>
   <si>
     <t xml:space="preserve">10.0815830230713</t>
@@ -3827,10 +3827,10 @@
     <t xml:space="preserve">9.6580638885498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60282325744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48313331604004</t>
+    <t xml:space="preserve">9.60282421112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48313236236572</t>
   </si>
   <si>
     <t xml:space="preserve">9.62123680114746</t>
@@ -3839,13 +3839,13 @@
     <t xml:space="preserve">9.8329963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">10.146032333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1276178359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2473077774048</t>
+    <t xml:space="preserve">10.1460332870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1276168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2473087310791</t>
   </si>
   <si>
     <t xml:space="preserve">10.4866886138916</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">10.5327224731445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7721033096313</t>
+    <t xml:space="preserve">10.772102355957</t>
   </si>
   <si>
     <t xml:space="preserve">10.6800336837769</t>
@@ -3866,25 +3866,25 @@
     <t xml:space="preserve">10.7352743148804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5695495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6616201400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9286193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9654483795166</t>
+    <t xml:space="preserve">10.5695505142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6616191864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9286203384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9654474258423</t>
   </si>
   <si>
     <t xml:space="preserve">11.3889665603638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7940721511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1163129806519</t>
+    <t xml:space="preserve">11.7940711975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1163139343262</t>
   </si>
   <si>
     <t xml:space="preserve">12.2912454605103</t>
@@ -3902,19 +3902,19 @@
     <t xml:space="preserve">12.0886926651001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8585195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.318865776062</t>
+    <t xml:space="preserve">11.8585205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3188667297363</t>
   </si>
   <si>
     <t xml:space="preserve">12.3649015426636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2820377349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2083826065063</t>
+    <t xml:space="preserve">12.2820386886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2083835601807</t>
   </si>
   <si>
     <t xml:space="preserve">12.2636241912842</t>
@@ -3926,19 +3926,19 @@
     <t xml:space="preserve">12.8620748519897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7275247573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7367334365845</t>
+    <t xml:space="preserve">13.7275257110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7367324829102</t>
   </si>
   <si>
     <t xml:space="preserve">13.4789390563965</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1290760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5950736999512</t>
+    <t xml:space="preserve">13.129075050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5950746536255</t>
   </si>
   <si>
     <t xml:space="preserve">12.8252468109131</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">12.8896961212158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5582466125488</t>
+    <t xml:space="preserve">12.5582456588745</t>
   </si>
   <si>
     <t xml:space="preserve">12.6963500976562</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">12.0058298110962</t>
   </si>
   <si>
-    <t xml:space="preserve">11.913761138916</t>
+    <t xml:space="preserve">11.9137601852417</t>
   </si>
   <si>
     <t xml:space="preserve">12.171555519104</t>
@@ -3977,10 +3977,10 @@
     <t xml:space="preserve">12.3280735015869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9966239929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9321756362915</t>
+    <t xml:space="preserve">11.9966230392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9321746826172</t>
   </si>
   <si>
     <t xml:space="preserve">12.4293489456177</t>
@@ -3989,10 +3989,10 @@
     <t xml:space="preserve">12.7700052261353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2728319168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5674524307251</t>
+    <t xml:space="preserve">12.2728309631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5674514770508</t>
   </si>
   <si>
     <t xml:space="preserve">12.503005027771</t>
@@ -4001,16 +4001,16 @@
     <t xml:space="preserve">12.4661769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4845905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3096580505371</t>
+    <t xml:space="preserve">12.4845914840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3096590042114</t>
   </si>
   <si>
     <t xml:space="preserve">12.024245262146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1991758346558</t>
+    <t xml:space="preserve">12.1991767883301</t>
   </si>
   <si>
     <t xml:space="preserve">12.2544183731079</t>
@@ -4025,13 +4025,13 @@
     <t xml:space="preserve">13.2855930328369</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2579717636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1751098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2119388580322</t>
+    <t xml:space="preserve">13.2579727172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1751108169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2119379043579</t>
   </si>
   <si>
     <t xml:space="preserve">13.1659030914307</t>
@@ -4040,10 +4040,10 @@
     <t xml:space="preserve">13.3040065765381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2947998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3417453765869</t>
+    <t xml:space="preserve">13.2947988510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3417444229126</t>
   </si>
   <si>
     <t xml:space="preserve">13.1821327209473</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">13.2854108810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3323564529419</t>
+    <t xml:space="preserve">13.3323554992676</t>
   </si>
   <si>
     <t xml:space="preserve">13.3511343002319</t>
@@ -4079,19 +4079,19 @@
     <t xml:space="preserve">13.4168567657471</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4544134140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4919681549072</t>
+    <t xml:space="preserve">13.4544124603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4919691085815</t>
   </si>
   <si>
     <t xml:space="preserve">13.6140260696411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9895849227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9614171981812</t>
+    <t xml:space="preserve">13.9895839691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9614181518555</t>
   </si>
   <si>
     <t xml:space="preserve">13.7548599243164</t>
@@ -4103,13 +4103,13 @@
     <t xml:space="preserve">13.5952472686768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5201349258423</t>
+    <t xml:space="preserve">13.5201358795166</t>
   </si>
   <si>
     <t xml:space="preserve">12.703293800354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3840684890747</t>
+    <t xml:space="preserve">12.3840675354004</t>
   </si>
   <si>
     <t xml:space="preserve">12.3652906417847</t>
@@ -4124,19 +4124,19 @@
     <t xml:space="preserve">12.5061254501343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6000156402588</t>
+    <t xml:space="preserve">12.6000146865845</t>
   </si>
   <si>
     <t xml:space="preserve">12.7502393722534</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6469612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6281814575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5249032974243</t>
+    <t xml:space="preserve">12.6469602584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6281824111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5249042510986</t>
   </si>
   <si>
     <t xml:space="preserve">12.5342931747437</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">12.2526226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4028463363647</t>
+    <t xml:space="preserve">12.4028472900391</t>
   </si>
   <si>
     <t xml:space="preserve">12.3277349472046</t>
@@ -4169,19 +4169,19 @@
     <t xml:space="preserve">12.5155143737793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4310140609741</t>
+    <t xml:space="preserve">12.4310131072998</t>
   </si>
   <si>
     <t xml:space="preserve">12.1211767196655</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0836210250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4122352600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0930099487305</t>
+    <t xml:space="preserve">12.0836219787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4122362136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0930109024048</t>
   </si>
   <si>
     <t xml:space="preserve">12.2338447570801</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">12.0648441314697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2056789398193</t>
+    <t xml:space="preserve">12.205677986145</t>
   </si>
   <si>
     <t xml:space="preserve">11.9991207122803</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">11.9240083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7268400192261</t>
+    <t xml:space="preserve">11.7268390655518</t>
   </si>
   <si>
     <t xml:space="preserve">11.9146194458008</t>
@@ -4226,7 +4226,7 @@
     <t xml:space="preserve">11.9897317886353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554552078247</t>
+    <t xml:space="preserve">12.0554542541504</t>
   </si>
   <si>
     <t xml:space="preserve">12.0460653305054</t>
@@ -4235,10 +4235,10 @@
     <t xml:space="preserve">12.0742321014404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9709529876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8770627975464</t>
+    <t xml:space="preserve">11.9709539413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8770637512207</t>
   </si>
   <si>
     <t xml:space="preserve">11.7737846374512</t>
@@ -4265,13 +4265,13 @@
     <t xml:space="preserve">11.4545593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5108938217163</t>
+    <t xml:space="preserve">11.510892868042</t>
   </si>
   <si>
     <t xml:space="preserve">11.670506477356</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4076147079468</t>
+    <t xml:space="preserve">11.4076137542725</t>
   </si>
   <si>
     <t xml:space="preserve">11.3606700897217</t>
@@ -4298,10 +4298,10 @@
     <t xml:space="preserve">10.8254976272583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7785520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6001625061035</t>
+    <t xml:space="preserve">10.7785530090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6001615524292</t>
   </si>
   <si>
     <t xml:space="preserve">10.7034406661987</t>
@@ -4313,10 +4313,10 @@
     <t xml:space="preserve">10.7503852844238</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7222194671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6471061706543</t>
+    <t xml:space="preserve">10.7222185134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6471071243286</t>
   </si>
   <si>
     <t xml:space="preserve">10.31849193573</t>
@@ -4340,7 +4340,7 @@
     <t xml:space="preserve">9.68004131317139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68943023681641</t>
+    <t xml:space="preserve">9.68943119049072</t>
   </si>
   <si>
     <t xml:space="preserve">9.71759796142578</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">9.94293308258057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85843276977539</t>
+    <t xml:space="preserve">9.85843181610107</t>
   </si>
   <si>
     <t xml:space="preserve">10.1776580810547</t>
@@ -4391,7 +4391,7 @@
     <t xml:space="preserve">10.018045425415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0649909973145</t>
+    <t xml:space="preserve">10.0649900436401</t>
   </si>
   <si>
     <t xml:space="preserve">9.89598751068115</t>
@@ -4409,10 +4409,10 @@
     <t xml:space="preserve">10.2527694702148</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1307125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2809371948242</t>
+    <t xml:space="preserve">10.1307134628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2809362411499</t>
   </si>
   <si>
     <t xml:space="preserve">10.1964349746704</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">10.3560485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">10.506272315979</t>
+    <t xml:space="preserve">10.5062713623047</t>
   </si>
   <si>
     <t xml:space="preserve">10.4029932022095</t>
@@ -4433,7 +4433,7 @@
     <t xml:space="preserve">9.97109985351562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4874935150146</t>
+    <t xml:space="preserve">10.487494468689</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405498504639</t>
@@ -4448,7 +4448,7 @@
     <t xml:space="preserve">10.6658849716187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5719947814941</t>
+    <t xml:space="preserve">10.5719957351685</t>
   </si>
   <si>
     <t xml:space="preserve">10.4499387741089</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">10.309103012085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2621583938599</t>
+    <t xml:space="preserve">10.2621593475342</t>
   </si>
   <si>
     <t xml:space="preserve">10.1870470046997</t>
@@ -4481,7 +4481,7 @@
     <t xml:space="preserve">10.1401023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058248519897</t>
+    <t xml:space="preserve">10.2058238983154</t>
   </si>
   <si>
     <t xml:space="preserve">10.6095514297485</t>
@@ -4499,10 +4499,10 @@
     <t xml:space="preserve">10.7409963607788</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9099979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7316083908081</t>
+    <t xml:space="preserve">10.9099988937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7316074371338</t>
   </si>
   <si>
     <t xml:space="preserve">10.8912210464478</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">10.7128295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7879409790039</t>
+    <t xml:space="preserve">10.7879419326782</t>
   </si>
   <si>
     <t xml:space="preserve">10.9287767410278</t>
@@ -4544,7 +4544,7 @@
     <t xml:space="preserve">11.0602216720581</t>
   </si>
   <si>
-    <t xml:space="preserve">11.003888130188</t>
+    <t xml:space="preserve">11.0038890838623</t>
   </si>
   <si>
     <t xml:space="preserve">10.8818321228027</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">11.1728897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2949466705322</t>
+    <t xml:space="preserve">11.2949457168579</t>
   </si>
   <si>
     <t xml:space="preserve">11.1447229385376</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">11.0508337020874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2480020523071</t>
+    <t xml:space="preserve">11.2480010986328</t>
   </si>
   <si>
     <t xml:space="preserve">11.3982257843018</t>
@@ -4592,16 +4592,16 @@
     <t xml:space="preserve">11.3418912887573</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1259450912476</t>
+    <t xml:space="preserve">11.1259460449219</t>
   </si>
   <si>
     <t xml:space="preserve">11.2386131286621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292232513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9757213592529</t>
+    <t xml:space="preserve">11.2292242050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9757204055786</t>
   </si>
   <si>
     <t xml:space="preserve">11.6104164123535</t>
@@ -4622,10 +4622,10 @@
     <t xml:space="preserve">11.4094924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3249921798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1090450286865</t>
+    <t xml:space="preserve">11.3249912261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1090440750122</t>
   </si>
   <si>
     <t xml:space="preserve">10.4705944061279</t>
@@ -4637,7 +4637,7 @@
     <t xml:space="preserve">10.4536933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3691921234131</t>
+    <t xml:space="preserve">10.3691930770874</t>
   </si>
   <si>
     <t xml:space="preserve">10.4799823760986</t>
@@ -5727,6 +5727,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.64999961853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84000015258789</t>
   </si>
 </sst>
 </file>
@@ -9853,7 +9856,7 @@
         <v>10.1195363998413</v>
       </c>
       <c r="G146" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -9879,7 +9882,7 @@
         <v>10.2294216156006</v>
       </c>
       <c r="G147" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -9905,7 +9908,7 @@
         <v>10.0595979690552</v>
       </c>
       <c r="G148" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -9931,7 +9934,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G149" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -9957,7 +9960,7 @@
         <v>10.5490922927856</v>
       </c>
       <c r="G150" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -10009,7 +10012,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G152" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -10035,7 +10038,7 @@
         <v>10.2893600463867</v>
       </c>
       <c r="G153" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -10061,7 +10064,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G154" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -10087,7 +10090,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G155" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -10113,7 +10116,7 @@
         <v>10.5091333389282</v>
       </c>
       <c r="G156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -10139,7 +10142,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G157" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -10165,7 +10168,7 @@
         <v>10.5191230773926</v>
       </c>
       <c r="G158" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -10191,7 +10194,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G159" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -10243,7 +10246,7 @@
         <v>10.2094430923462</v>
       </c>
       <c r="G161" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -10269,7 +10272,7 @@
         <v>10.1594953536987</v>
       </c>
       <c r="G162" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -10295,7 +10298,7 @@
         <v>10.1994533538818</v>
       </c>
       <c r="G163" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -10321,7 +10324,7 @@
         <v>10.1095457077026</v>
       </c>
       <c r="G164" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -10347,7 +10350,7 @@
         <v>10.1395149230957</v>
       </c>
       <c r="G165" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -10373,7 +10376,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G166" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -10399,7 +10402,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G167" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -10425,7 +10428,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G168" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -10477,7 +10480,7 @@
         <v>10.4092359542847</v>
       </c>
       <c r="G170" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -10503,7 +10506,7 @@
         <v>10.4591846466064</v>
       </c>
       <c r="G171" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -10529,7 +10532,7 @@
         <v>10.4591846466064</v>
       </c>
       <c r="G172" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -10555,7 +10558,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G173" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -10581,7 +10584,7 @@
         <v>10.4791641235352</v>
       </c>
       <c r="G174" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -10633,7 +10636,7 @@
         <v>10.6989374160767</v>
       </c>
       <c r="G176" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -10659,7 +10662,7 @@
         <v>10.6389989852905</v>
       </c>
       <c r="G177" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -10763,7 +10766,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G181" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -10841,7 +10844,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G184" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -10919,7 +10922,7 @@
         <v>10.688946723938</v>
       </c>
       <c r="G187" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -10945,7 +10948,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G188" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -10971,7 +10974,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G189" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -10997,7 +11000,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G190" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -11049,7 +11052,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G192" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -11075,7 +11078,7 @@
         <v>10.6090297698975</v>
       </c>
       <c r="G193" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -11101,7 +11104,7 @@
         <v>10.7089262008667</v>
       </c>
       <c r="G194" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -11127,7 +11130,7 @@
         <v>10.8887405395508</v>
       </c>
       <c r="G195" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -11153,7 +11156,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G196" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -11179,7 +11182,7 @@
         <v>10.5990400314331</v>
       </c>
       <c r="G197" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -11205,7 +11208,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G198" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -11231,7 +11234,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G199" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -11257,7 +11260,7 @@
         <v>10.3792667388916</v>
       </c>
       <c r="G200" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -11335,7 +11338,7 @@
         <v>10.4691743850708</v>
       </c>
       <c r="G203" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -11361,7 +11364,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G204" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -11387,7 +11390,7 @@
         <v>10.5091333389282</v>
       </c>
       <c r="G205" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -11413,7 +11416,7 @@
         <v>10.6090297698975</v>
       </c>
       <c r="G206" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -11439,7 +11442,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G207" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -11465,7 +11468,7 @@
         <v>10.5291118621826</v>
       </c>
       <c r="G208" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -11491,7 +11494,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G209" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -11543,7 +11546,7 @@
         <v>10.8787508010864</v>
       </c>
       <c r="G211" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -11569,7 +11572,7 @@
         <v>10.9986267089844</v>
       </c>
       <c r="G212" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -11595,7 +11598,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G213" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -11621,7 +11624,7 @@
         <v>11.2483692169189</v>
       </c>
       <c r="G214" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -11647,7 +11650,7 @@
         <v>11.258358001709</v>
       </c>
       <c r="G215" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -11673,7 +11676,7 @@
         <v>11.008617401123</v>
       </c>
       <c r="G216" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -11699,7 +11702,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G217" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -11725,7 +11728,7 @@
         <v>10.5590810775757</v>
       </c>
       <c r="G218" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -11751,7 +11754,7 @@
         <v>11.0585651397705</v>
       </c>
       <c r="G219" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -11777,7 +11780,7 @@
         <v>11.3682451248169</v>
       </c>
       <c r="G220" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -11803,7 +11806,7 @@
         <v>11.0385856628418</v>
       </c>
       <c r="G221" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -11829,7 +11832,7 @@
         <v>10.828803062439</v>
       </c>
       <c r="G222" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -11855,7 +11858,7 @@
         <v>10.98863697052</v>
       </c>
       <c r="G223" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -11881,7 +11884,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G224" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -11907,7 +11910,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G225" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -11933,7 +11936,7 @@
         <v>10.7289056777954</v>
       </c>
       <c r="G226" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11959,7 +11962,7 @@
         <v>10.6389989852905</v>
       </c>
       <c r="G227" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -11985,7 +11988,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G228" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -12037,7 +12040,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G230" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -12063,7 +12066,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G231" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -12089,7 +12092,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G232" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -12115,7 +12118,7 @@
         <v>10.838791847229</v>
       </c>
       <c r="G233" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -12167,7 +12170,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G235" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -12193,7 +12196,7 @@
         <v>10.8088226318359</v>
       </c>
       <c r="G236" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -12219,7 +12222,7 @@
         <v>10.7089262008667</v>
       </c>
       <c r="G237" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -12245,7 +12248,7 @@
         <v>10.539101600647</v>
       </c>
       <c r="G238" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -12271,7 +12274,7 @@
         <v>10.5590810775757</v>
       </c>
       <c r="G239" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -12323,7 +12326,7 @@
         <v>10.9686584472656</v>
       </c>
       <c r="G241" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -12349,7 +12352,7 @@
         <v>11.0985240936279</v>
       </c>
       <c r="G242" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -12375,7 +12378,7 @@
         <v>10.9686584472656</v>
       </c>
       <c r="G243" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -12401,7 +12404,7 @@
         <v>10.828803062439</v>
       </c>
       <c r="G244" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -12427,7 +12430,7 @@
         <v>11.008617401123</v>
       </c>
       <c r="G245" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -12453,7 +12456,7 @@
         <v>10.8887405395508</v>
       </c>
       <c r="G246" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -12479,7 +12482,7 @@
         <v>10.98863697052</v>
       </c>
       <c r="G247" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -12505,7 +12508,7 @@
         <v>10.8088226318359</v>
       </c>
       <c r="G248" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -12531,7 +12534,7 @@
         <v>10.7289056777954</v>
       </c>
       <c r="G249" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -12557,7 +12560,7 @@
         <v>10.7688636779785</v>
       </c>
       <c r="G250" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -12583,7 +12586,7 @@
         <v>10.9087200164795</v>
       </c>
       <c r="G251" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -12609,7 +12612,7 @@
         <v>10.9187097549438</v>
       </c>
       <c r="G252" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -12635,7 +12638,7 @@
         <v>11.0685548782349</v>
       </c>
       <c r="G253" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -12661,7 +12664,7 @@
         <v>11.2084102630615</v>
       </c>
       <c r="G254" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -12687,7 +12690,7 @@
         <v>11.2683477401733</v>
       </c>
       <c r="G255" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -12713,7 +12716,7 @@
         <v>11.4181928634644</v>
       </c>
       <c r="G256" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -12739,7 +12742,7 @@
         <v>11.4881210327148</v>
       </c>
       <c r="G257" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -12765,7 +12768,7 @@
         <v>11.9876041412354</v>
       </c>
       <c r="G258" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -12791,7 +12794,7 @@
         <v>12.0575323104858</v>
       </c>
       <c r="G259" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -12817,7 +12820,7 @@
         <v>11.8177795410156</v>
       </c>
       <c r="G260" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -12843,7 +12846,7 @@
         <v>11.9576349258423</v>
       </c>
       <c r="G261" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -12869,7 +12872,7 @@
         <v>12.0075836181641</v>
       </c>
       <c r="G262" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -12895,7 +12898,7 @@
         <v>12.0375528335571</v>
       </c>
       <c r="G263" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -12921,7 +12924,7 @@
         <v>12.0974912643433</v>
       </c>
       <c r="G264" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -12947,7 +12950,7 @@
         <v>12.277304649353</v>
       </c>
       <c r="G265" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12973,7 +12976,7 @@
         <v>12.0575323104858</v>
       </c>
       <c r="G266" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -12999,7 +13002,7 @@
         <v>12.3072738647461</v>
       </c>
       <c r="G267" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -13025,7 +13028,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G268" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -13051,7 +13054,7 @@
         <v>12.2673149108887</v>
       </c>
       <c r="G269" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -13077,7 +13080,7 @@
         <v>12.2173671722412</v>
       </c>
       <c r="G270" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -13103,7 +13106,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G271" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -13129,7 +13132,7 @@
         <v>12.1774082183838</v>
       </c>
       <c r="G272" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -13155,7 +13158,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G273" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -13181,7 +13184,7 @@
         <v>12.2073774337769</v>
       </c>
       <c r="G274" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -13207,7 +13210,7 @@
         <v>12.2972841262817</v>
       </c>
       <c r="G275" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -13233,7 +13236,7 @@
         <v>12.1873979568481</v>
       </c>
       <c r="G276" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -13259,7 +13262,7 @@
         <v>12.1474390029907</v>
       </c>
       <c r="G277" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -13285,7 +13288,7 @@
         <v>11.9876041412354</v>
       </c>
       <c r="G278" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -13311,7 +13314,7 @@
         <v>11.8477487564087</v>
       </c>
       <c r="G279" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -13337,7 +13340,7 @@
         <v>12.2173671722412</v>
       </c>
       <c r="G280" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -13363,7 +13366,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G281" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -13389,7 +13392,7 @@
         <v>12.4071702957153</v>
       </c>
       <c r="G282" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -13415,7 +13418,7 @@
         <v>12.127459526062</v>
       </c>
       <c r="G283" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -13441,7 +13444,7 @@
         <v>12.1174697875977</v>
       </c>
       <c r="G284" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -13467,7 +13470,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G285" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -13493,7 +13496,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G286" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -13519,7 +13522,7 @@
         <v>12.4071702957153</v>
       </c>
       <c r="G287" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -13545,7 +13548,7 @@
         <v>12.6669015884399</v>
       </c>
       <c r="G288" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -13571,7 +13574,7 @@
         <v>12.5670051574707</v>
       </c>
       <c r="G289" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -13597,7 +13600,7 @@
         <v>12.6569118499756</v>
       </c>
       <c r="G290" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -13623,7 +13626,7 @@
         <v>12.5670051574707</v>
       </c>
       <c r="G291" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -13649,7 +13652,7 @@
         <v>12.4970779418945</v>
       </c>
       <c r="G292" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -13675,7 +13678,7 @@
         <v>12.5969743728638</v>
       </c>
       <c r="G293" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -13701,7 +13704,7 @@
         <v>12.8567056655884</v>
       </c>
       <c r="G294" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -13727,7 +13730,7 @@
         <v>12.8966636657715</v>
       </c>
       <c r="G295" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -13753,7 +13756,7 @@
         <v>12.816746711731</v>
       </c>
       <c r="G296" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -13779,7 +13782,7 @@
         <v>12.5170574188232</v>
       </c>
       <c r="G297" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -13805,7 +13808,7 @@
         <v>12.8067569732666</v>
       </c>
       <c r="G298" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -13831,7 +13834,7 @@
         <v>12.6669015884399</v>
       </c>
       <c r="G299" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -13857,7 +13860,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G300" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -13883,7 +13886,7 @@
         <v>13.1863651275635</v>
       </c>
       <c r="G301" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13909,7 +13912,7 @@
         <v>13.1464061737061</v>
       </c>
       <c r="G302" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -13935,7 +13938,7 @@
         <v>12.9566020965576</v>
       </c>
       <c r="G303" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13961,7 +13964,7 @@
         <v>12.966591835022</v>
       </c>
       <c r="G304" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -13987,7 +13990,7 @@
         <v>13.0764780044556</v>
       </c>
       <c r="G305" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -14013,7 +14016,7 @@
         <v>12.9765815734863</v>
       </c>
       <c r="G306" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -14039,7 +14042,7 @@
         <v>12.9765815734863</v>
       </c>
       <c r="G307" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -14065,7 +14068,7 @@
         <v>13.1863651275635</v>
       </c>
       <c r="G308" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -14091,7 +14094,7 @@
         <v>13.2762718200684</v>
       </c>
       <c r="G309" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -14117,7 +14120,7 @@
         <v>13.1064472198486</v>
       </c>
       <c r="G310" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -14143,7 +14146,7 @@
         <v>13.2862615585327</v>
       </c>
       <c r="G311" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -14169,7 +14172,7 @@
         <v>13.536003112793</v>
       </c>
       <c r="G312" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -14195,7 +14198,7 @@
         <v>13.4460964202881</v>
       </c>
       <c r="G313" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -14221,7 +14224,7 @@
         <v>13.5060338973999</v>
       </c>
       <c r="G314" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -14247,7 +14250,7 @@
         <v>13.5459928512573</v>
       </c>
       <c r="G315" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -14273,7 +14276,7 @@
         <v>13.5759620666504</v>
       </c>
       <c r="G316" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -14299,7 +14302,7 @@
         <v>13.6458902359009</v>
       </c>
       <c r="G317" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -14325,7 +14328,7 @@
         <v>13.7058277130127</v>
       </c>
       <c r="G318" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -14351,7 +14354,7 @@
         <v>13.7757549285889</v>
       </c>
       <c r="G319" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -14377,7 +14380,7 @@
         <v>13.8456830978394</v>
       </c>
       <c r="G320" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -14403,7 +14406,7 @@
         <v>13.835693359375</v>
       </c>
       <c r="G321" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -14429,7 +14432,7 @@
         <v>13.8556728363037</v>
       </c>
       <c r="G322" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -14455,7 +14458,7 @@
         <v>14.1253938674927</v>
       </c>
       <c r="G323" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -14481,7 +14484,7 @@
         <v>14.1453733444214</v>
       </c>
       <c r="G324" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -14507,7 +14510,7 @@
         <v>14.1253938674927</v>
       </c>
       <c r="G325" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -14533,7 +14536,7 @@
         <v>14.1253938674927</v>
       </c>
       <c r="G326" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -14559,7 +14562,7 @@
         <v>14.0654563903809</v>
       </c>
       <c r="G327" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -14585,7 +14588,7 @@
         <v>14.0554656982422</v>
       </c>
       <c r="G328" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -14611,7 +14614,7 @@
         <v>14.1054153442383</v>
       </c>
       <c r="G329" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -14637,7 +14640,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G330" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -14663,7 +14666,7 @@
         <v>14.0954246520996</v>
       </c>
       <c r="G331" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -14689,7 +14692,7 @@
         <v>13.7757549285889</v>
       </c>
       <c r="G332" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -14715,7 +14718,7 @@
         <v>13.9455795288086</v>
       </c>
       <c r="G333" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -14741,7 +14744,7 @@
         <v>14.0754451751709</v>
       </c>
       <c r="G334" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -14767,7 +14770,7 @@
         <v>13.8856420516968</v>
       </c>
       <c r="G335" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -14793,7 +14796,7 @@
         <v>14.3851251602173</v>
       </c>
       <c r="G336" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -14819,7 +14822,7 @@
         <v>14.5050010681152</v>
       </c>
       <c r="G337" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -14845,7 +14848,7 @@
         <v>14.3351774215698</v>
       </c>
       <c r="G338" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -14871,7 +14874,7 @@
         <v>14.4250841140747</v>
       </c>
       <c r="G339" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -14897,7 +14900,7 @@
         <v>14.4150943756104</v>
       </c>
       <c r="G340" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -14923,7 +14926,7 @@
         <v>14.6148881912231</v>
       </c>
       <c r="G341" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -14949,7 +14952,7 @@
         <v>14.4950122833252</v>
       </c>
       <c r="G342" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -14975,7 +14978,7 @@
         <v>14.7847118377686</v>
       </c>
       <c r="G343" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -15001,7 +15004,7 @@
         <v>14.9045877456665</v>
       </c>
       <c r="G344" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -15027,7 +15030,7 @@
         <v>14.8146810531616</v>
       </c>
       <c r="G345" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -15053,7 +15056,7 @@
         <v>15.0444440841675</v>
       </c>
       <c r="G346" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -15079,7 +15082,7 @@
         <v>15.0844020843506</v>
       </c>
       <c r="G347" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -15105,7 +15108,7 @@
         <v>14.7647333145142</v>
       </c>
       <c r="G348" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -15131,7 +15134,7 @@
         <v>14.6648359298706</v>
       </c>
       <c r="G349" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -15157,7 +15160,7 @@
         <v>14.674825668335</v>
       </c>
       <c r="G350" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -15183,7 +15186,7 @@
         <v>14.5349702835083</v>
       </c>
       <c r="G351" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -15209,7 +15212,7 @@
         <v>14.0055179595947</v>
       </c>
       <c r="G352" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -15235,7 +15238,7 @@
         <v>13.8956308364868</v>
       </c>
       <c r="G353" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -15261,7 +15264,7 @@
         <v>14.2053108215332</v>
       </c>
       <c r="G354" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -15287,7 +15290,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G355" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -15313,7 +15316,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G356" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -15339,7 +15342,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G357" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -15365,7 +15368,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G358" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -15391,7 +15394,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G359" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -15417,7 +15420,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G360" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -15443,7 +15446,7 @@
         <v>14.4250841140747</v>
       </c>
       <c r="G361" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -15469,7 +15472,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G362" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -15495,7 +15498,7 @@
         <v>13.9755487442017</v>
       </c>
       <c r="G363" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -15521,7 +15524,7 @@
         <v>13.8257036209106</v>
       </c>
       <c r="G364" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -15547,7 +15550,7 @@
         <v>14.0055179595947</v>
       </c>
       <c r="G365" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -17497,7 +17500,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G440" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -17705,7 +17708,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G448" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -17731,7 +17734,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G449" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -17783,7 +17786,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G451" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -18173,7 +18176,7 @@
         <v>13.8257036209106</v>
       </c>
       <c r="G466" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -72157,7 +72160,7 @@
     </row>
     <row r="2543">
       <c r="A2543" s="1" t="n">
-        <v>46027.6910763889</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B2543" t="n">
         <v>268321</v>
@@ -72178,6 +72181,32 @@
         <v>1904</v>
       </c>
       <c r="H2543" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" s="1" t="n">
+        <v>46028.6874537037</v>
+      </c>
+      <c r="B2544" t="n">
+        <v>231357</v>
+      </c>
+      <c r="C2544" t="n">
+        <v>9.84000015258789</v>
+      </c>
+      <c r="D2544" t="n">
+        <v>9.61999988555908</v>
+      </c>
+      <c r="E2544" t="n">
+        <v>9.61999988555908</v>
+      </c>
+      <c r="F2544" t="n">
+        <v>9.84000015258789</v>
+      </c>
+      <c r="G2544" t="s">
+        <v>1905</v>
+      </c>
+      <c r="H2544" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1917" uniqueCount="1917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="1918">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,73 +44,73 @@
     <t xml:space="preserve">BRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13994932174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92740106582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52519750595093</t>
+    <t xml:space="preserve">7.13994884490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92740201950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52519702911377</t>
   </si>
   <si>
     <t xml:space="preserve">6.54154682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42873334884644</t>
+    <t xml:space="preserve">6.42873287200928</t>
   </si>
   <si>
     <t xml:space="preserve">6.60040664672852</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78188800811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55135822296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21291589736938</t>
+    <t xml:space="preserve">6.78188848495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55135679244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21291542053223</t>
   </si>
   <si>
     <t xml:space="preserve">6.19820165634155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27504539489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94641494750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20310640335083</t>
+    <t xml:space="preserve">6.27504444122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94641542434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20310688018799</t>
   </si>
   <si>
     <t xml:space="preserve">6.24888563156128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30610942840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31919002532959</t>
+    <t xml:space="preserve">6.30610990524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31918954849243</t>
   </si>
   <si>
     <t xml:space="preserve">6.38785934448242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23090124130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16713619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05922889709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99219417572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86466503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70443820953369</t>
+    <t xml:space="preserve">6.23090171813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16713714599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05922794342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99219465255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86466550827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70443773269653</t>
   </si>
   <si>
     <t xml:space="preserve">5.35945796966553</t>
@@ -119,19 +119,19 @@
     <t xml:space="preserve">5.51641511917114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72242259979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67500829696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73223352432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03960943222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97420978546143</t>
+    <t xml:space="preserve">5.72242212295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67500877380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73223304748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03960847854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97420883178711</t>
   </si>
   <si>
     <t xml:space="preserve">6.11972284317017</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">6.14097738265991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10010290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23744058609009</t>
+    <t xml:space="preserve">6.10010194778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23744106292725</t>
   </si>
   <si>
     <t xml:space="preserve">6.11154794692993</t>
@@ -152,31 +152,31 @@
     <t xml:space="preserve">5.97584533691406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07394313812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12953281402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21945667266846</t>
+    <t xml:space="preserve">6.07394409179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12953233718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21945571899414</t>
   </si>
   <si>
     <t xml:space="preserve">6.35188961029053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32409477233887</t>
+    <t xml:space="preserve">6.32409429550171</t>
   </si>
   <si>
     <t xml:space="preserve">7.04675579071045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08272409439087</t>
+    <t xml:space="preserve">7.08272504806519</t>
   </si>
   <si>
     <t xml:space="preserve">7.11705923080444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07945394515991</t>
+    <t xml:space="preserve">7.07945489883423</t>
   </si>
   <si>
     <t xml:space="preserve">7.1203293800354</t>
@@ -185,16 +185,16 @@
     <t xml:space="preserve">7.07128000259399</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0663743019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16120290756226</t>
+    <t xml:space="preserve">7.06637525558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16120338439941</t>
   </si>
   <si>
     <t xml:space="preserve">7.14321947097778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24949264526367</t>
+    <t xml:space="preserve">7.24949169158936</t>
   </si>
   <si>
     <t xml:space="preserve">7.1415843963623</t>
@@ -203,91 +203,91 @@
     <t xml:space="preserve">7.22987222671509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07618379592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26911306381226</t>
+    <t xml:space="preserve">7.07618474960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2691125869751</t>
   </si>
   <si>
     <t xml:space="preserve">7.15302801132202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15139389038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31489038467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43097400665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40318012237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35576629638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14485359191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18899822235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16283893585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27401638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998706817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35740041732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40644979476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42279958724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39337110519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43914985656738</t>
+    <t xml:space="preserve">7.1513934135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31489133834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43097543716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40318059921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35576581954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14485454559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18899869918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16283941268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27401733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998611450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35739994049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40645027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42279863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39337062835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4391508102417</t>
   </si>
   <si>
     <t xml:space="preserve">7.47184991836548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51108837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7677788734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71546077728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63534593582153</t>
+    <t xml:space="preserve">7.51108884811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76777982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71546125411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63534688949585</t>
   </si>
   <si>
     <t xml:space="preserve">7.68276214599609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74162101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66968202590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72200012207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63044309616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71055698394775</t>
+    <t xml:space="preserve">7.7416205406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66968250274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72200155258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63044214248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71055603027344</t>
   </si>
   <si>
     <t xml:space="preserve">7.85606908798218</t>
@@ -302,10 +302,10 @@
     <t xml:space="preserve">8.51006126403809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55093574523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42831039428711</t>
+    <t xml:space="preserve">8.55093383789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42831134796143</t>
   </si>
   <si>
     <t xml:space="preserve">8.36291313171387</t>
@@ -317,22 +317,22 @@
     <t xml:space="preserve">8.41196155548096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51991558074951</t>
+    <t xml:space="preserve">8.51991367340088</t>
   </si>
   <si>
     <t xml:space="preserve">8.45348167419434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51161003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46178531646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47008895874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61125946044922</t>
+    <t xml:space="preserve">8.51161098480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4617862701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47008991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6112585067749</t>
   </si>
   <si>
     <t xml:space="preserve">8.63617038726807</t>
@@ -341,19 +341,19 @@
     <t xml:space="preserve">8.72751426696777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96002674102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86868381500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86037731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58634567260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27577590942383</t>
+    <t xml:space="preserve">8.96002769470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86868286132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86038112640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58634662628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27577495574951</t>
   </si>
   <si>
     <t xml:space="preserve">8.10969638824463</t>
@@ -362,76 +362,76 @@
     <t xml:space="preserve">8.30400943756104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3123140335083</t>
+    <t xml:space="preserve">8.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">8.60295391082764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61956214904785</t>
+    <t xml:space="preserve">8.61956405639648</t>
   </si>
   <si>
     <t xml:space="preserve">8.56973838806152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71921062469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25916862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64134979248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25418472290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0598726272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20602130889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23757934570312</t>
+    <t xml:space="preserve">8.71920967102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25916767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64135074615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25418567657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05987167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20602226257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23757743835449</t>
   </si>
   <si>
     <t xml:space="preserve">7.84728956222534</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67954921722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67788743972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95524024963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02831745147705</t>
+    <t xml:space="preserve">7.67954874038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67788600921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95524120330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02831649780273</t>
   </si>
   <si>
     <t xml:space="preserve">8.05488967895508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97849321365356</t>
+    <t xml:space="preserve">7.97849273681641</t>
   </si>
   <si>
     <t xml:space="preserve">8.14457321166992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11301708221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23425769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10471343994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21100521087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16782379150391</t>
+    <t xml:space="preserve">8.11301898956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23425674438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10471248626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21100425720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16782569885254</t>
   </si>
   <si>
     <t xml:space="preserve">8.32061862945557</t>
@@ -440,16 +440,13 @@
     <t xml:space="preserve">8.37044239044189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41196250915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50330638885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36213779449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67769050598145</t>
+    <t xml:space="preserve">8.50330543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36213874816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67768955230713</t>
   </si>
   <si>
     <t xml:space="preserve">8.76903438568115</t>
@@ -461,7 +458,7 @@
     <t xml:space="preserve">8.55313014984131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64447498321533</t>
+    <t xml:space="preserve">8.64447593688965</t>
   </si>
   <si>
     <t xml:space="preserve">8.73581886291504</t>
@@ -473,7 +470,7 @@
     <t xml:space="preserve">8.74412250518799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6693868637085</t>
+    <t xml:space="preserve">8.66938781738281</t>
   </si>
   <si>
     <t xml:space="preserve">8.48669815063477</t>
@@ -488,28 +485,28 @@
     <t xml:space="preserve">8.40365886688232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42856979370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65277767181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69429779052734</t>
+    <t xml:space="preserve">8.42857074737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65277671813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69429969787598</t>
   </si>
   <si>
     <t xml:space="preserve">8.71090698242188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89359474182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84377098083496</t>
+    <t xml:space="preserve">8.89359569549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84377193450928</t>
   </si>
   <si>
     <t xml:space="preserve">8.88529109954834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78564262390137</t>
+    <t xml:space="preserve">8.78564167022705</t>
   </si>
   <si>
     <t xml:space="preserve">8.80225086212158</t>
@@ -518,10 +515,10 @@
     <t xml:space="preserve">8.81885814666748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90189743041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05137062072754</t>
+    <t xml:space="preserve">8.90189838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05136966705322</t>
   </si>
   <si>
     <t xml:space="preserve">8.81055545806885</t>
@@ -530,37 +527,37 @@
     <t xml:space="preserve">8.6278657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70260334014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82716369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75242519378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04306602478027</t>
+    <t xml:space="preserve">8.70260238647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82716274261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75242614746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04306793212891</t>
   </si>
   <si>
     <t xml:space="preserve">9.14271545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28388214111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35031604766846</t>
+    <t xml:space="preserve">9.28388404846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35031700134277</t>
   </si>
   <si>
     <t xml:space="preserve">9.35861873626709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15101909637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93511486053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7773380279541</t>
+    <t xml:space="preserve">9.15102005004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93511390686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77733898162842</t>
   </si>
   <si>
     <t xml:space="preserve">9.19253921508789</t>
@@ -572,19 +569,19 @@
     <t xml:space="preserve">9.17593097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00154685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13441181182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91850662231445</t>
+    <t xml:space="preserve">9.00154590606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13440990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91850566864014</t>
   </si>
   <si>
     <t xml:space="preserve">8.92681121826172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00985145568848</t>
+    <t xml:space="preserve">9.00985050201416</t>
   </si>
   <si>
     <t xml:space="preserve">8.984938621521</t>
@@ -596,97 +593,97 @@
     <t xml:space="preserve">9.1178035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.225754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95172214508057</t>
+    <t xml:space="preserve">9.22575569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95172309875488</t>
   </si>
   <si>
     <t xml:space="preserve">9.06797885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0762825012207</t>
+    <t xml:space="preserve">9.07628345489502</t>
   </si>
   <si>
     <t xml:space="preserve">9.20084285736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31709957122803</t>
+    <t xml:space="preserve">9.31709861755371</t>
   </si>
   <si>
     <t xml:space="preserve">9.36692237854004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49148368835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54961109161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96481037139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0229396820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82364463806152</t>
+    <t xml:space="preserve">9.49148273468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54961204528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96481132507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0229406356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82364273071289</t>
   </si>
   <si>
     <t xml:space="preserve">9.93989944458008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98142051696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0063323974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0561571121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2056303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2305402755737</t>
+    <t xml:space="preserve">9.98141956329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0063314437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0561561584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2056274414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2305421829224</t>
   </si>
   <si>
     <t xml:space="preserve">10.2139329910278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1973247528076</t>
+    <t xml:space="preserve">10.1973237991333</t>
   </si>
   <si>
     <t xml:space="preserve">10.1558046340942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1225881576538</t>
+    <t xml:space="preserve">10.1225891113281</t>
   </si>
   <si>
     <t xml:space="preserve">10.1807165145874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.147500038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2222366333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1308908462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.097677230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84855556488037</t>
+    <t xml:space="preserve">10.1474990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2222356796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1308927536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0976762771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84855651855469</t>
   </si>
   <si>
     <t xml:space="preserve">10.3135805130005</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0810689926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0727634429932</t>
+    <t xml:space="preserve">10.0810680389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0727643966675</t>
   </si>
   <si>
     <t xml:space="preserve">10.5294847488403</t>
@@ -698,7 +695,7 @@
     <t xml:space="preserve">10.5211801528931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3883171081543</t>
+    <t xml:space="preserve">10.38831615448</t>
   </si>
   <si>
     <t xml:space="preserve">10.4713563919067</t>
@@ -707,16 +704,16 @@
     <t xml:space="preserve">10.6872615814209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.720477104187</t>
+    <t xml:space="preserve">10.7204761505127</t>
   </si>
   <si>
     <t xml:space="preserve">10.6540441513062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4049263000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6457395553589</t>
+    <t xml:space="preserve">10.4049253463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6457414627075</t>
   </si>
   <si>
     <t xml:space="preserve">10.7952136993408</t>
@@ -725,7 +722,7 @@
     <t xml:space="preserve">10.96129322052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9280757904053</t>
+    <t xml:space="preserve">10.9280786514282</t>
   </si>
   <si>
     <t xml:space="preserve">10.7703008651733</t>
@@ -734,7 +731,7 @@
     <t xml:space="preserve">10.7786054611206</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8699502944946</t>
+    <t xml:space="preserve">10.8699493408203</t>
   </si>
   <si>
     <t xml:space="preserve">10.7869091033936</t>
@@ -749,49 +746,49 @@
     <t xml:space="preserve">11.0443334579468</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2519330978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1771984100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2270202636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2602376937866</t>
+    <t xml:space="preserve">11.2519340515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1771974563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2270212173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2602396011353</t>
   </si>
   <si>
     <t xml:space="preserve">11.2851495742798</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3432779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3931007385254</t>
+    <t xml:space="preserve">11.3432788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.393102645874</t>
   </si>
   <si>
     <t xml:space="preserve">11.451229095459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5093574523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5010547637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5176620483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7418699264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7584791183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6920461654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6837425231934</t>
+    <t xml:space="preserve">11.5093584060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5010538101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5176630020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7418689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7584772109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6920471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.683741569519</t>
   </si>
   <si>
     <t xml:space="preserve">11.7252626419067</t>
@@ -800,7 +797,7 @@
     <t xml:space="preserve">11.7667827606201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7169570922852</t>
+    <t xml:space="preserve">11.7169589996338</t>
   </si>
   <si>
     <t xml:space="preserve">11.5923976898193</t>
@@ -809,37 +806,37 @@
     <t xml:space="preserve">11.7003507614136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.542573928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9577741622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0574226379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9162540435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9909925460815</t>
+    <t xml:space="preserve">11.5425748825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9577732086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0574216842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9162559509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9909896850586</t>
   </si>
   <si>
     <t xml:space="preserve">11.98268699646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1487674713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0491189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2899351119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3895835876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3148469924927</t>
+    <t xml:space="preserve">12.1487665176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0491199493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2899341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3895826339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.314847946167</t>
   </si>
   <si>
     <t xml:space="preserve">12.505838394165</t>
@@ -848,7 +845,7 @@
     <t xml:space="preserve">12.5390548706055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2733287811279</t>
+    <t xml:space="preserve">12.2733268737793</t>
   </si>
   <si>
     <t xml:space="preserve">12.1902866363525</t>
@@ -872,7 +869,7 @@
     <t xml:space="preserve">11.9346389770508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9514837265015</t>
+    <t xml:space="preserve">11.9514846801758</t>
   </si>
   <si>
     <t xml:space="preserve">12.0609760284424</t>
@@ -887,7 +884,10 @@
     <t xml:space="preserve">11.6566972732544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7577667236328</t>
+    <t xml:space="preserve">11.8083019256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7577676773071</t>
   </si>
   <si>
     <t xml:space="preserve">11.5977401733398</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">11.5640506744385</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3029556274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2018842697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1934623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0334358215332</t>
+    <t xml:space="preserve">11.3029546737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2018852233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1934614181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0334348678589</t>
   </si>
   <si>
     <t xml:space="preserve">10.957631111145</t>
@@ -914,16 +914,16 @@
     <t xml:space="preserve">11.2355737686157</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208679199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2271509170532</t>
+    <t xml:space="preserve">11.4208698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2271518707275</t>
   </si>
   <si>
     <t xml:space="preserve">11.2861080169678</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1681938171387</t>
+    <t xml:space="preserve">11.168194770813</t>
   </si>
   <si>
     <t xml:space="preserve">10.923942565918</t>
@@ -932,19 +932,19 @@
     <t xml:space="preserve">11.0250120162964</t>
   </si>
   <si>
-    <t xml:space="preserve">10.763916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9492111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5786218643188</t>
+    <t xml:space="preserve">10.7639169692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9492101669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5786209106445</t>
   </si>
   <si>
     <t xml:space="preserve">10.7891836166382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7386493682861</t>
+    <t xml:space="preserve">10.7386484146118</t>
   </si>
   <si>
     <t xml:space="preserve">10.6544246673584</t>
@@ -956,124 +956,124 @@
     <t xml:space="preserve">11.4292907714844</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5219373703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2945318222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.639853477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4629802703857</t>
+    <t xml:space="preserve">11.5219383239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2945308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6398525238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4629812240601</t>
   </si>
   <si>
     <t xml:space="preserve">11.4124460220337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3619108200073</t>
+    <t xml:space="preserve">11.361909866333</t>
   </si>
   <si>
     <t xml:space="preserve">11.3197994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2103071212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9997444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.991322517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.00816822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8902540206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9323644638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8734064102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8818302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6796913146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7807607650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8649854660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7049589157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9155206680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2608413696289</t>
+    <t xml:space="preserve">11.2103061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9997453689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9913215637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0081672668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8902530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9323654174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8734073638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8818311691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6796903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.78076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8649864196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7049579620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9155216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2608404159546</t>
   </si>
   <si>
     <t xml:space="preserve">11.1513500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0839691162109</t>
+    <t xml:space="preserve">11.0839700698853</t>
   </si>
   <si>
     <t xml:space="preserve">11.0502796173096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2524185180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.328221321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3787574768066</t>
+    <t xml:space="preserve">11.2524194717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3282222747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3787565231323</t>
   </si>
   <si>
     <t xml:space="preserve">11.3956003189087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5050945281982</t>
+    <t xml:space="preserve">11.5050935745239</t>
   </si>
   <si>
     <t xml:space="preserve">11.4040241241455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5556268692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6819648742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7493457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9177951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8841037750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9430627822876</t>
+    <t xml:space="preserve">11.5556287765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6819658279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7493448257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9177942276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8841047286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.943060874939</t>
   </si>
   <si>
     <t xml:space="preserve">12.0525531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0946674346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1536235809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0357093811035</t>
+    <t xml:space="preserve">12.0946655273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1536226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0357074737549</t>
   </si>
   <si>
     <t xml:space="preserve">12.0778198242188</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">12.0441312789917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1788911819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1704683303833</t>
+    <t xml:space="preserve">12.1788902282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1704692840576</t>
   </si>
   <si>
     <t xml:space="preserve">12.3136510848999</t>
@@ -1097,10 +1097,10 @@
     <t xml:space="preserve">12.3726072311401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.204158782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2883834838867</t>
+    <t xml:space="preserve">12.2041578292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.288384437561</t>
   </si>
   <si>
     <t xml:space="preserve">12.2968044281006</t>
@@ -1109,31 +1109,31 @@
     <t xml:space="preserve">11.7914562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7325000762939</t>
+    <t xml:space="preserve">11.7325010299683</t>
   </si>
   <si>
     <t xml:space="preserve">11.8167238235474</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0104417800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0020189285278</t>
+    <t xml:space="preserve">12.0104398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0020198822021</t>
   </si>
   <si>
     <t xml:space="preserve">11.9683294296265</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9262170791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.311375617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8144502639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6965351104736</t>
+    <t xml:space="preserve">11.926215171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3113765716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8144521713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6965360641479</t>
   </si>
   <si>
     <t xml:space="preserve">10.8986749649048</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">10.7723379135132</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7976055145264</t>
+    <t xml:space="preserve">10.7976064682007</t>
   </si>
   <si>
     <t xml:space="preserve">10.7302265167236</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">10.7218027114868</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6628475189209</t>
+    <t xml:space="preserve">10.6628465652466</t>
   </si>
   <si>
     <t xml:space="preserve">10.6123113632202</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">10.8060274124146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6881132125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312959671021</t>
+    <t xml:space="preserve">10.6881141662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312950134277</t>
   </si>
   <si>
     <t xml:space="preserve">10.6712684631348</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">11.1597709655762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.134503364563</t>
+    <t xml:space="preserve">11.1345062255859</t>
   </si>
   <si>
     <t xml:space="preserve">11.1429271697998</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">11.4545583724976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.345067024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4270162582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3175239562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2417230606079</t>
+    <t xml:space="preserve">11.3450660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4270172119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3175230026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2417240142822</t>
   </si>
   <si>
     <t xml:space="preserve">10.2838344573975</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">10.1911878585815</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1574964523315</t>
+    <t xml:space="preserve">10.1574974060059</t>
   </si>
   <si>
     <t xml:space="preserve">10.2248773574829</t>
@@ -1232,28 +1232,28 @@
     <t xml:space="preserve">10.1069631576538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0985412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93009185791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98904705047607</t>
+    <t xml:space="preserve">10.0985403060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93009090423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98904800415039</t>
   </si>
   <si>
     <t xml:space="preserve">10.0058937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71952819824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68583965301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4837007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37420845031738</t>
+    <t xml:space="preserve">9.7195291519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68584060668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48370170593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3742094039917</t>
   </si>
   <si>
     <t xml:space="preserve">10.1153860092163</t>
@@ -1262,79 +1262,79 @@
     <t xml:space="preserve">10.3091020584106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5954666137695</t>
+    <t xml:space="preserve">10.5954675674438</t>
   </si>
   <si>
     <t xml:space="preserve">10.7133808135986</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6038885116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3596363067627</t>
+    <t xml:space="preserve">10.603889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3596382141113</t>
   </si>
   <si>
     <t xml:space="preserve">10.3006801605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4522829055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4017486572266</t>
+    <t xml:space="preserve">10.4522838592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4017496109009</t>
   </si>
   <si>
     <t xml:space="preserve">10.5617771148682</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5449304580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.342791557312</t>
+    <t xml:space="preserve">10.5449314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3427925109863</t>
   </si>
   <si>
     <t xml:space="preserve">10.4438619613647</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4101724624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4185953140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4354400634766</t>
+    <t xml:space="preserve">10.4101715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4185934066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4354391098022</t>
   </si>
   <si>
     <t xml:space="preserve">10.2585668563843</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2333011627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2922582626343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.149076461792</t>
+    <t xml:space="preserve">10.2333002090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.29225730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1490745544434</t>
   </si>
   <si>
     <t xml:space="preserve">11.0418577194214</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5365085601807</t>
+    <t xml:space="preserve">10.5365076065063</t>
   </si>
   <si>
     <t xml:space="preserve">10.2754125595093</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2080335617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0648517608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93851470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.050085067749</t>
+    <t xml:space="preserve">10.2080316543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0648508071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93851375579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0500869750977</t>
   </si>
   <si>
     <t xml:space="preserve">10.3848028182983</t>
@@ -1355,40 +1355,40 @@
     <t xml:space="preserve">10.230318069458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4706287384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.504958152771</t>
+    <t xml:space="preserve">10.470627784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5049562454224</t>
   </si>
   <si>
     <t xml:space="preserve">10.642276763916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6851892471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.659441947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9340810775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6508588790894</t>
+    <t xml:space="preserve">10.6851902008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6594429016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7109384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.93408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6508598327637</t>
   </si>
   <si>
     <t xml:space="preserve">10.7452669143677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.530704498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3933849334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3504734039307</t>
+    <t xml:space="preserve">10.5307054519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.393385887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3504724502563</t>
   </si>
   <si>
     <t xml:space="preserve">10.1444940567017</t>
@@ -1397,16 +1397,16 @@
     <t xml:space="preserve">10.135910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92135143280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.075834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0586700439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89560127258301</t>
+    <t xml:space="preserve">9.92135047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0758333206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.058669090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89560317993164</t>
   </si>
   <si>
     <t xml:space="preserve">9.94709587097168</t>
@@ -1415,16 +1415,16 @@
     <t xml:space="preserve">9.74111747741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76686382293701</t>
+    <t xml:space="preserve">9.76686477661133</t>
   </si>
   <si>
     <t xml:space="preserve">9.85268878936768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87843704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99000930786133</t>
+    <t xml:space="preserve">9.87843608856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99001026153564</t>
   </si>
   <si>
     <t xml:space="preserve">10.2560663223267</t>
@@ -1436,43 +1436,43 @@
     <t xml:space="preserve">10.2732305526733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.51353931427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4877939224243</t>
+    <t xml:space="preserve">10.5135402679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.48779296875</t>
   </si>
   <si>
     <t xml:space="preserve">10.4362983703613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3333072662354</t>
+    <t xml:space="preserve">10.333309173584</t>
   </si>
   <si>
     <t xml:space="preserve">10.0844163894653</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1273288726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0157556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.032922744751</t>
+    <t xml:space="preserve">10.127329826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0157566070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0329217910767</t>
   </si>
   <si>
     <t xml:space="preserve">9.84410667419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0415029525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2389001846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78402900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70678520202637</t>
+    <t xml:space="preserve">10.0415019989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2389011383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78402805328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.706787109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.77544593811035</t>
@@ -1481,19 +1481,19 @@
     <t xml:space="preserve">9.68103885650635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56088542938232</t>
+    <t xml:space="preserve">9.56088447570801</t>
   </si>
   <si>
     <t xml:space="preserve">9.59521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68962287902832</t>
+    <t xml:space="preserve">9.689621925354</t>
   </si>
   <si>
     <t xml:space="preserve">9.47506046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48364162445068</t>
+    <t xml:space="preserve">9.483642578125</t>
   </si>
   <si>
     <t xml:space="preserve">9.62954521179199</t>
@@ -1502,25 +1502,25 @@
     <t xml:space="preserve">9.91276550292969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88701820373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75828170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56946659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.578049659729</t>
+    <t xml:space="preserve">9.88701915740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7582836151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56946754455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57804870605469</t>
   </si>
   <si>
     <t xml:space="preserve">9.73253536224365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61237907409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71537017822266</t>
+    <t xml:space="preserve">9.612380027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71536827087402</t>
   </si>
   <si>
     <t xml:space="preserve">9.82694149017334</t>
@@ -1529,34 +1529,34 @@
     <t xml:space="preserve">10.187406539917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2217359542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99859142303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96426200866699</t>
+    <t xml:space="preserve">10.221736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99859237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96426010131836</t>
   </si>
   <si>
     <t xml:space="preserve">9.86985492706299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69820499420166</t>
+    <t xml:space="preserve">9.69820404052734</t>
   </si>
   <si>
     <t xml:space="preserve">9.86127281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52655410766602</t>
+    <t xml:space="preserve">9.52655601501465</t>
   </si>
   <si>
     <t xml:space="preserve">9.21758556365967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23474979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69405460357666</t>
+    <t xml:space="preserve">9.23475074768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69405555725098</t>
   </si>
   <si>
     <t xml:space="preserve">8.52669525146484</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">8.44087028503418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12331867218018</t>
+    <t xml:space="preserve">8.12332057952881</t>
   </si>
   <si>
     <t xml:space="preserve">8.43228721618652</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">8.52240371704102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41083240509033</t>
+    <t xml:space="preserve">8.41083145141602</t>
   </si>
   <si>
     <t xml:space="preserve">8.29926013946533</t>
@@ -1586,10 +1586,10 @@
     <t xml:space="preserve">8.23060131072998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08469867706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35504722595215</t>
+    <t xml:space="preserve">8.08469772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35504627227783</t>
   </si>
   <si>
     <t xml:space="preserve">8.22630882263184</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">8.48378372192383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39366722106934</t>
+    <t xml:space="preserve">8.39366626739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.57819080352783</t>
@@ -1607,28 +1607,28 @@
     <t xml:space="preserve">8.49236583709717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44945240020752</t>
+    <t xml:space="preserve">8.44945335388184</t>
   </si>
   <si>
     <t xml:space="preserve">8.23489189147949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11473655700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02033042907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79289197921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72852420806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77143669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83151435852051</t>
+    <t xml:space="preserve">8.11473560333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02032852172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79289245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72852468490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77143716812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83151388168335</t>
   </si>
   <si>
     <t xml:space="preserve">8.00316333770752</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">8.02891159057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00745487213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25205612182617</t>
+    <t xml:space="preserve">8.00745391845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25205707550049</t>
   </si>
   <si>
     <t xml:space="preserve">8.28638744354248</t>
@@ -1652,58 +1652,58 @@
     <t xml:space="preserve">8.60822868347168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54815101623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75413131713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48807525634766</t>
+    <t xml:space="preserve">8.54815196990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75413227081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48807430267334</t>
   </si>
   <si>
     <t xml:space="preserve">8.46232795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16193962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19197940826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98170804977417</t>
+    <t xml:space="preserve">8.161940574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19197845458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98170709609985</t>
   </si>
   <si>
     <t xml:space="preserve">8.0889892578125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33788013458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81435108184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.698486328125</t>
+    <t xml:space="preserve">8.33788108825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81435060501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69848680496216</t>
   </si>
   <si>
     <t xml:space="preserve">7.99887323379517</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81864023208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86584329605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58691263198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.634117603302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68990325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65986490249634</t>
+    <t xml:space="preserve">7.81863927841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8658447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63411808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68990230560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65986633300781</t>
   </si>
   <si>
     <t xml:space="preserve">7.96454429626465</t>
@@ -1712,16 +1712,16 @@
     <t xml:space="preserve">7.93879556655884</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73696708679199</t>
+    <t xml:space="preserve">8.73696613311768</t>
   </si>
   <si>
     <t xml:space="preserve">8.82279109954834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47949123382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38508319854736</t>
+    <t xml:space="preserve">8.4794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.385085105896</t>
   </si>
   <si>
     <t xml:space="preserve">8.40224933624268</t>
@@ -1733,28 +1733,28 @@
     <t xml:space="preserve">8.367919921875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49665641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50094795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46661949157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59964847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85712051391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56960868835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56531715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55673503875732</t>
+    <t xml:space="preserve">8.496657371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50094699859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46661758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59964752197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8571195602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56960773468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56531810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55673313140869</t>
   </si>
   <si>
     <t xml:space="preserve">8.53956890106201</t>
@@ -1769,16 +1769,16 @@
     <t xml:space="preserve">8.24776458740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15335750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39795780181885</t>
+    <t xml:space="preserve">8.15335845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39795875549316</t>
   </si>
   <si>
     <t xml:space="preserve">8.58248138427734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77129650115967</t>
+    <t xml:space="preserve">8.77129745483398</t>
   </si>
   <si>
     <t xml:space="preserve">8.65972518920898</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">9.02018737792969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28624439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31199359893799</t>
+    <t xml:space="preserve">9.28624534606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31199264526367</t>
   </si>
   <si>
     <t xml:space="preserve">9.08026504516602</t>
@@ -1805,34 +1805,34 @@
     <t xml:space="preserve">9.131760597229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32057571411133</t>
+    <t xml:space="preserve">9.32057476043701</t>
   </si>
   <si>
     <t xml:space="preserve">8.942946434021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81420803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78845977783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79704475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74554824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72838401794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.908616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14034271240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42356491088867</t>
+    <t xml:space="preserve">8.81420993804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78846073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.797043800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74554920196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72838306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90861701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14034366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42356586456299</t>
   </si>
   <si>
     <t xml:space="preserve">9.260498046875</t>
@@ -1847,28 +1847,28 @@
     <t xml:space="preserve">8.96011161804199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76271438598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65114212036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68547058105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67688846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87428569793701</t>
+    <t xml:space="preserve">8.76271343231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65114116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.685471534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67689037322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87428665161133</t>
   </si>
   <si>
     <t xml:space="preserve">9.51797199249268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44073009490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4149808883667</t>
+    <t xml:space="preserve">9.44072914123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41498279571533</t>
   </si>
   <si>
     <t xml:space="preserve">9.64670944213867</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">10.1959886550903</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80977725982666</t>
+    <t xml:space="preserve">9.80977630615234</t>
   </si>
   <si>
     <t xml:space="preserve">9.62096118927002</t>
@@ -1889,52 +1889,52 @@
     <t xml:space="preserve">9.50939083099365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86570358276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9515266418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83995628356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75851821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77167415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7409725189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42080783843994</t>
+    <t xml:space="preserve">8.86570262908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95152854919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83995532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75851726531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77167510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74097347259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42080879211426</t>
   </si>
   <si>
     <t xml:space="preserve">8.53484058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57869815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58746910095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47343730926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55238342285156</t>
+    <t xml:space="preserve">8.57869720458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58747005462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47343826293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55238151550293</t>
   </si>
   <si>
     <t xml:space="preserve">8.42957973480225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18397235870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37694931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56992530822754</t>
+    <t xml:space="preserve">8.1839714050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37695026397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56992626190186</t>
   </si>
   <si>
     <t xml:space="preserve">8.67957210540771</t>
@@ -1943,61 +1943,61 @@
     <t xml:space="preserve">8.66202831268311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89447975158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75413227081299</t>
+    <t xml:space="preserve">8.8944787979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7541332244873</t>
   </si>
   <si>
     <t xml:space="preserve">8.72781658172607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72343063354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93833637237549</t>
+    <t xml:space="preserve">8.72343158721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9383373260498</t>
   </si>
   <si>
     <t xml:space="preserve">8.82430553436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0611400604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00850963592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85062122344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71465873718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88570785522461</t>
+    <t xml:space="preserve">9.06113910675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00851058959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85062026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71465969085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88570690155029</t>
   </si>
   <si>
     <t xml:space="preserve">9.11376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0523681640625</t>
+    <t xml:space="preserve">9.05236721038818</t>
   </si>
   <si>
     <t xml:space="preserve">9.28043174743652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32429027557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23657512664795</t>
+    <t xml:space="preserve">9.32428932189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23657417297363</t>
   </si>
   <si>
     <t xml:space="preserve">8.9295654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80676174163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78921985626221</t>
+    <t xml:space="preserve">8.80676078796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78921890258789</t>
   </si>
   <si>
     <t xml:space="preserve">8.49536800384521</t>
@@ -2006,52 +2006,52 @@
     <t xml:space="preserve">8.45589447021484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48221015930176</t>
+    <t xml:space="preserve">8.48221111297607</t>
   </si>
   <si>
     <t xml:space="preserve">8.62255668640137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9207935333252</t>
+    <t xml:space="preserve">8.92079448699951</t>
   </si>
   <si>
     <t xml:space="preserve">9.07868385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0172815322876</t>
+    <t xml:space="preserve">9.01728248596191</t>
   </si>
   <si>
     <t xml:space="preserve">8.17958641052246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13134288787842</t>
+    <t xml:space="preserve">8.1313419342041</t>
   </si>
   <si>
     <t xml:space="preserve">8.17081546783447</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9602952003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77170419692993</t>
+    <t xml:space="preserve">7.96029567718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77170467376709</t>
   </si>
   <si>
     <t xml:space="preserve">7.61819982528687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64890050888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63135814666748</t>
+    <t xml:space="preserve">7.64890003204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63135719299316</t>
   </si>
   <si>
     <t xml:space="preserve">7.38574934005737</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29803466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39013671875</t>
+    <t xml:space="preserve">7.29803419113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39013576507568</t>
   </si>
   <si>
     <t xml:space="preserve">7.22347402572632</t>
@@ -2060,28 +2060,28 @@
     <t xml:space="preserve">7.20593118667603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28048944473267</t>
+    <t xml:space="preserve">7.28049039840698</t>
   </si>
   <si>
     <t xml:space="preserve">7.27171802520752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.512939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39890718460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26733255386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19277334213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44276666641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45153903961182</t>
+    <t xml:space="preserve">7.51293992996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39890813827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26733303070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19277286529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4427661895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45153856277466</t>
   </si>
   <si>
     <t xml:space="preserve">7.32873344421387</t>
@@ -2090,58 +2090,58 @@
     <t xml:space="preserve">7.53048276901245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79363393783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98661136627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06116962432861</t>
+    <t xml:space="preserve">7.79363298416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98661088943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0611686706543</t>
   </si>
   <si>
     <t xml:space="preserve">8.22344589233398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28923225402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35063552856445</t>
+    <t xml:space="preserve">8.28923320770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35063362121582</t>
   </si>
   <si>
     <t xml:space="preserve">8.21905994415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19274425506592</t>
+    <t xml:space="preserve">8.1927433013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.30239009857178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87257766723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72345972061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6094274520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74100255966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83310508728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84187841415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67521524429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50855398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40329360961914</t>
+    <t xml:space="preserve">7.87257862091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72346067428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60942888259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74100303649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83310556411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84187746047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67521619796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50855350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4032940864563</t>
   </si>
   <si>
     <t xml:space="preserve">7.45592451095581</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">7.44715261459351</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31557703018188</t>
+    <t xml:space="preserve">7.31557655334473</t>
   </si>
   <si>
     <t xml:space="preserve">7.4734673500061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85064935684204</t>
+    <t xml:space="preserve">7.85064840316772</t>
   </si>
   <si>
     <t xml:space="preserve">7.85942029953003</t>
@@ -2165,31 +2165,31 @@
     <t xml:space="preserve">8.00854015350342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04362487792969</t>
+    <t xml:space="preserve">8.04362678527832</t>
   </si>
   <si>
     <t xml:space="preserve">7.80679082870483</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91643762588501</t>
+    <t xml:space="preserve">7.91643619537354</t>
   </si>
   <si>
     <t xml:space="preserve">8.18835926055908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25414657592773</t>
+    <t xml:space="preserve">8.25414752960205</t>
   </si>
   <si>
     <t xml:space="preserve">8.29361915588379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36379146575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65325832366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3725643157959</t>
+    <t xml:space="preserve">8.36379241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65325736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37256336212158</t>
   </si>
   <si>
     <t xml:space="preserve">8.43835067749023</t>
@@ -2201,7 +2201,7 @@
     <t xml:space="preserve">9.12254238128662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14885520935059</t>
+    <t xml:space="preserve">9.14885711669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.37692070007324</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">9.56112480163574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75410175323486</t>
+    <t xml:space="preserve">9.75410270690918</t>
   </si>
   <si>
     <t xml:space="preserve">9.70147323608398</t>
@@ -2219,25 +2219,25 @@
     <t xml:space="preserve">9.47340965270996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35060501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49095153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24534511566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42077922821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31551933288574</t>
+    <t xml:space="preserve">9.35060596466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49095249176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24534606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42077827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31551837921143</t>
   </si>
   <si>
     <t xml:space="preserve">9.48218154907227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64884281158447</t>
+    <t xml:space="preserve">9.64884185791016</t>
   </si>
   <si>
     <t xml:space="preserve">9.72778701782227</t>
@@ -2252,13 +2252,13 @@
     <t xml:space="preserve">9.85936260223389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.815505027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86813449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92076301574707</t>
+    <t xml:space="preserve">9.81550407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86813354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9207649230957</t>
   </si>
   <si>
     <t xml:space="preserve">9.9997091293335</t>
@@ -2267,13 +2267,13 @@
     <t xml:space="preserve">9.8769063949585</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84181976318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89444923400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98216533660889</t>
+    <t xml:space="preserve">9.84181880950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89444828033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98216724395752</t>
   </si>
   <si>
     <t xml:space="preserve">10.0698823928833</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">9.96462345123291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67515850067139</t>
+    <t xml:space="preserve">9.67515659332275</t>
   </si>
   <si>
     <t xml:space="preserve">9.71901702880859</t>
@@ -2291,40 +2291,40 @@
     <t xml:space="preserve">9.79796123504639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29797458648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52603912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63129901885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71024417877197</t>
+    <t xml:space="preserve">9.29797554016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52604007720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63129997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71024513244629</t>
   </si>
   <si>
     <t xml:space="preserve">9.68392944335938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69270038604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76287460327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73655891418457</t>
+    <t xml:space="preserve">9.69270133972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76287364959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7365608215332</t>
   </si>
   <si>
     <t xml:space="preserve">9.57866954803467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30674839019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2102575302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33306217193604</t>
+    <t xml:space="preserve">9.30674648284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21025943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33306121826172</t>
   </si>
   <si>
     <t xml:space="preserve">9.20148754119873</t>
@@ -2336,19 +2336,19 @@
     <t xml:space="preserve">9.26288986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13131427764893</t>
+    <t xml:space="preserve">9.13131523132324</t>
   </si>
   <si>
     <t xml:space="preserve">9.0874547958374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43832206726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42955112457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21902942657471</t>
+    <t xml:space="preserve">9.43832302093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42955017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21903038024902</t>
   </si>
   <si>
     <t xml:space="preserve">9.25411701202393</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">8.39449310302734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33747673034668</t>
+    <t xml:space="preserve">8.33747577667236</t>
   </si>
   <si>
     <t xml:space="preserve">8.34186267852783</t>
@@ -2375,16 +2375,16 @@
     <t xml:space="preserve">7.92959403991699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49978303909302</t>
+    <t xml:space="preserve">7.49978256225586</t>
   </si>
   <si>
     <t xml:space="preserve">7.60065650939941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42960929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11821413040161</t>
+    <t xml:space="preserve">7.4296088218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11821460723877</t>
   </si>
   <si>
     <t xml:space="preserve">7.18400144577026</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">6.57875633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64892959594727</t>
+    <t xml:space="preserve">6.64892911911011</t>
   </si>
   <si>
     <t xml:space="preserve">6.5568265914917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14017248153687</t>
+    <t xml:space="preserve">6.14017200469971</t>
   </si>
   <si>
     <t xml:space="preserve">6.38577938079834</t>
@@ -2408,16 +2408,16 @@
     <t xml:space="preserve">5.87702226638794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9735107421875</t>
+    <t xml:space="preserve">5.97351026535034</t>
   </si>
   <si>
     <t xml:space="preserve">6.55244064331055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11382722854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72784566879272</t>
+    <t xml:space="preserve">7.11382818222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72784519195557</t>
   </si>
   <si>
     <t xml:space="preserve">6.82436275482178</t>
@@ -2429,25 +2429,25 @@
     <t xml:space="preserve">6.4734959602356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31560516357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83316373825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96035289764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85070753097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61387205123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18406009674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47352504730225</t>
+    <t xml:space="preserve">6.31560564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83316421508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9603533744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85070657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61387252807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18405961990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4735255241394</t>
   </si>
   <si>
     <t xml:space="preserve">5.54369783401489</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">5.64895820617676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69720268249512</t>
+    <t xml:space="preserve">5.69720315933228</t>
   </si>
   <si>
     <t xml:space="preserve">5.92965173721313</t>
@@ -2471,25 +2471,25 @@
     <t xml:space="preserve">6.06122732162476</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00859785079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05684185028076</t>
+    <t xml:space="preserve">6.0085973739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0568413734436</t>
   </si>
   <si>
     <t xml:space="preserve">6.40332269668579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59191370010376</t>
+    <t xml:space="preserve">6.5919132232666</t>
   </si>
   <si>
     <t xml:space="preserve">6.83752107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69717311859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86822128295898</t>
+    <t xml:space="preserve">6.69717359542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86822175979614</t>
   </si>
   <si>
     <t xml:space="preserve">6.81120586395264</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">6.72348880767822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48665285110474</t>
+    <t xml:space="preserve">6.48665428161621</t>
   </si>
   <si>
     <t xml:space="preserve">6.4822678565979</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">6.21911764144897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39455080032349</t>
+    <t xml:space="preserve">6.39455032348633</t>
   </si>
   <si>
     <t xml:space="preserve">6.59629964828491</t>
@@ -2534,25 +2534,25 @@
     <t xml:space="preserve">7.16207265853882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51732397079468</t>
+    <t xml:space="preserve">7.51732444763184</t>
   </si>
   <si>
     <t xml:space="preserve">7.37259340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33312082290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41645097732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79801893234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68398761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55679845809937</t>
+    <t xml:space="preserve">7.33312034606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4164514541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79801988601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68398714065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55679798126221</t>
   </si>
   <si>
     <t xml:space="preserve">7.10067176818848</t>
@@ -2567,55 +2567,55 @@
     <t xml:space="preserve">7.21031665802002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23224544525146</t>
+    <t xml:space="preserve">7.23224639892578</t>
   </si>
   <si>
     <t xml:space="preserve">7.17523002624512</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10505676269531</t>
+    <t xml:space="preserve">7.10505723953247</t>
   </si>
   <si>
     <t xml:space="preserve">7.20154523849487</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24540328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21470308303833</t>
+    <t xml:space="preserve">7.24540281295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21470260620117</t>
   </si>
   <si>
     <t xml:space="preserve">7.17084455490112</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40768051147461</t>
+    <t xml:space="preserve">7.40768003463745</t>
   </si>
   <si>
     <t xml:space="preserve">7.25856065750122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36820793151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32434892654419</t>
+    <t xml:space="preserve">7.36820697784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32434940338135</t>
   </si>
   <si>
     <t xml:space="preserve">7.14891481399536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24978923797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43838024139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16645812988281</t>
+    <t xml:space="preserve">7.24978828430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43837976455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16645765304565</t>
   </si>
   <si>
     <t xml:space="preserve">6.70155954360962</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61384248733521</t>
+    <t xml:space="preserve">6.61384296417236</t>
   </si>
   <si>
     <t xml:space="preserve">6.69278764724731</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">6.75418996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68401670455933</t>
+    <t xml:space="preserve">6.68401718139648</t>
   </si>
   <si>
     <t xml:space="preserve">6.71033191680908</t>
@@ -2633,16 +2633,16 @@
     <t xml:space="preserve">6.83313465118408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06119775772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14014291763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05681324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04804039001465</t>
+    <t xml:space="preserve">7.06119823455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1401424407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05681276321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04804134368896</t>
   </si>
   <si>
     <t xml:space="preserve">7.00856828689575</t>
@@ -2654,16 +2654,16 @@
     <t xml:space="preserve">7.07435607910156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0875129699707</t>
+    <t xml:space="preserve">7.08751344680786</t>
   </si>
   <si>
     <t xml:space="preserve">7.09628534317017</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01733922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35943555831909</t>
+    <t xml:space="preserve">7.0173397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35943603515625</t>
   </si>
   <si>
     <t xml:space="preserve">7.29364824295044</t>
@@ -2672,22 +2672,22 @@
     <t xml:space="preserve">7.49101066589355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60504150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97345304489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5743408203125</t>
+    <t xml:space="preserve">7.60504198074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9734525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57434129714966</t>
   </si>
   <si>
     <t xml:space="preserve">7.41206502914429</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88576507568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9910249710083</t>
+    <t xml:space="preserve">6.88576412200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99102544784546</t>
   </si>
   <si>
     <t xml:space="preserve">7.0392689704895</t>
@@ -2699,40 +2699,40 @@
     <t xml:space="preserve">7.31119155883789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48223972320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8638072013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92082262039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9997673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73661756515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68837451934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61381435394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62697124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57872724533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77609014511108</t>
+    <t xml:space="preserve">7.48223829269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86380624771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92082214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99976682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73661708831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68837356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61381387710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62697172164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57872676849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77608919143677</t>
   </si>
   <si>
     <t xml:space="preserve">7.80240488052368</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96906518936157</t>
+    <t xml:space="preserve">7.96906661987305</t>
   </si>
   <si>
     <t xml:space="preserve">7.99099540710449</t>
@@ -2741,31 +2741,31 @@
     <t xml:space="preserve">8.15327072143555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54799842834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56995487213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82433462142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66644382476807</t>
+    <t xml:space="preserve">8.54799747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56995534896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82433366775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66644525527954</t>
   </si>
   <si>
     <t xml:space="preserve">7.71907424926758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78486156463623</t>
+    <t xml:space="preserve">7.78486108779907</t>
   </si>
   <si>
     <t xml:space="preserve">7.86819267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22780132293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17517280578613</t>
+    <t xml:space="preserve">9.22780227661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17517185211182</t>
   </si>
   <si>
     <t xml:space="preserve">9.39446353912354</t>
@@ -2783,16 +2783,16 @@
     <t xml:space="preserve">9.36814975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35937690734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53481197357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46463775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50849533081055</t>
+    <t xml:space="preserve">9.35937881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53481101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46463871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50849628448486</t>
   </si>
   <si>
     <t xml:space="preserve">9.41200733184814</t>
@@ -2801,22 +2801,22 @@
     <t xml:space="preserve">9.38569259643555</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61375713348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49972438812256</t>
+    <t xml:space="preserve">9.61375617980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49972534179688</t>
   </si>
   <si>
     <t xml:space="preserve">9.03482532501221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74533176422119</t>
+    <t xml:space="preserve">9.74533271789551</t>
   </si>
   <si>
     <t xml:space="preserve">9.90322208404541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0961980819702</t>
+    <t xml:space="preserve">10.0961971282959</t>
   </si>
   <si>
     <t xml:space="preserve">10.1225118637085</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">9.938307762146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6663875579834</t>
+    <t xml:space="preserve">9.66638660430908</t>
   </si>
   <si>
     <t xml:space="preserve">9.88567733764648</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">9.45586490631104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51726818084717</t>
+    <t xml:space="preserve">9.51726722717285</t>
   </si>
   <si>
     <t xml:space="preserve">9.44709396362305</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">8.94710826873779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16639995574951</t>
+    <t xml:space="preserve">9.1663990020752</t>
   </si>
   <si>
     <t xml:space="preserve">9.28920364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27165985107422</t>
+    <t xml:space="preserve">9.27166080474854</t>
   </si>
   <si>
     <t xml:space="preserve">9.34183311462402</t>
@@ -2864,19 +2864,19 @@
     <t xml:space="preserve">9.19271564483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18394470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9032506942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06991195678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8418493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9997386932373</t>
+    <t xml:space="preserve">9.18394374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90324974060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06991100311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84184837341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99973964691162</t>
   </si>
   <si>
     <t xml:space="preserve">8.97342395782471</t>
@@ -2888,22 +2888,22 @@
     <t xml:space="preserve">9.19807243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1890983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43138885498047</t>
+    <t xml:space="preserve">9.18909931182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43138980865479</t>
   </si>
   <si>
     <t xml:space="preserve">9.57496929168701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72752285003662</t>
+    <t xml:space="preserve">9.7275218963623</t>
   </si>
   <si>
     <t xml:space="preserve">9.79931259155273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81725883483887</t>
+    <t xml:space="preserve">9.81725978851318</t>
   </si>
   <si>
     <t xml:space="preserve">9.94289207458496</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">9.70060157775879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52112674713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51215267181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35062503814697</t>
+    <t xml:space="preserve">9.52112579345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51215362548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35062599182129</t>
   </si>
   <si>
     <t xml:space="preserve">9.53010082244873</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">9.61086368560791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69162654876709</t>
+    <t xml:space="preserve">9.69162750244141</t>
   </si>
   <si>
     <t xml:space="preserve">9.5031795501709</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">9.55702018737793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54804801940918</t>
+    <t xml:space="preserve">9.5480489730835</t>
   </si>
   <si>
     <t xml:space="preserve">9.35960006713867</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">9.76341724395752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64675903320312</t>
+    <t xml:space="preserve">9.64675807952881</t>
   </si>
   <si>
     <t xml:space="preserve">9.29678249359131</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">9.33267784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3865213394165</t>
+    <t xml:space="preserve">9.38652038574219</t>
   </si>
   <si>
     <t xml:space="preserve">9.39549446105957</t>
@@ -2993,10 +2993,10 @@
     <t xml:space="preserve">10.5800266265869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.651816368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6877117156982</t>
+    <t xml:space="preserve">10.6518154144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6877107620239</t>
   </si>
   <si>
     <t xml:space="preserve">10.7415542602539</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">10.8582134246826</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9389753341675</t>
+    <t xml:space="preserve">10.9389762878418</t>
   </si>
   <si>
     <t xml:space="preserve">10.9838447570801</t>
@@ -3017,16 +3017,16 @@
     <t xml:space="preserve">11.1005029678345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0915279388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1274242401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0197401046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9300012588501</t>
+    <t xml:space="preserve">11.0915298461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.127423286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.019739151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9300031661987</t>
   </si>
   <si>
     <t xml:space="preserve">10.8312902450562</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">11.0376863479614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0107660293579</t>
+    <t xml:space="preserve">11.0107669830322</t>
   </si>
   <si>
     <t xml:space="preserve">10.9748697280884</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">10.9120540618896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0466604232788</t>
+    <t xml:space="preserve">11.0466613769531</t>
   </si>
   <si>
     <t xml:space="preserve">10.921028137207</t>
@@ -3062,22 +3062,22 @@
     <t xml:space="preserve">10.8043699264526</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7595014572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7864227294922</t>
+    <t xml:space="preserve">10.75950050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7864236831665</t>
   </si>
   <si>
     <t xml:space="preserve">10.8402643203735</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4274730682373</t>
+    <t xml:space="preserve">10.427472114563</t>
   </si>
   <si>
     <t xml:space="preserve">10.2569723129272</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90699768066406</t>
+    <t xml:space="preserve">9.90699672698975</t>
   </si>
   <si>
     <t xml:space="preserve">9.96083927154541</t>
@@ -3086,13 +3086,13 @@
     <t xml:space="preserve">10.1223659515381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1313400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1403141021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0954446792603</t>
+    <t xml:space="preserve">10.1313390731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1403150558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0954456329346</t>
   </si>
   <si>
     <t xml:space="preserve">9.87110137939453</t>
@@ -3101,10 +3101,10 @@
     <t xml:space="preserve">9.80828666687012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56599521636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47625827789307</t>
+    <t xml:space="preserve">9.56599426269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47625732421875</t>
   </si>
   <si>
     <t xml:space="preserve">9.67368030548096</t>
@@ -3113,121 +3113,121 @@
     <t xml:space="preserve">9.70957469940186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75444316864014</t>
+    <t xml:space="preserve">9.75444412231445</t>
   </si>
   <si>
     <t xml:space="preserve">9.84418106079102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85315322875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82623386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86212825775146</t>
+    <t xml:space="preserve">9.8531551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82623291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86212730407715</t>
   </si>
   <si>
     <t xml:space="preserve">10.0236549377441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96981143951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1672353744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492872238159</t>
+    <t xml:space="preserve">9.96981239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1672344207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492881774902</t>
   </si>
   <si>
     <t xml:space="preserve">10.2031307220459</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1851835250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2838945388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3377370834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4454221725464</t>
+    <t xml:space="preserve">10.1851825714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2838935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3377361297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4454212188721</t>
   </si>
   <si>
     <t xml:space="preserve">10.5172100067139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3467102050781</t>
+    <t xml:space="preserve">10.3467082977295</t>
   </si>
   <si>
     <t xml:space="preserve">10.3018407821655</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4184989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4364471435547</t>
+    <t xml:space="preserve">10.4184999465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4364461898804</t>
   </si>
   <si>
     <t xml:space="preserve">10.7774486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8492383956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6966857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7684745788574</t>
+    <t xml:space="preserve">10.8492393493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6966848373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7684755325317</t>
   </si>
   <si>
     <t xml:space="preserve">10.5620794296265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0864715576172</t>
+    <t xml:space="preserve">10.0864706039429</t>
   </si>
   <si>
     <t xml:space="preserve">10.2479991912842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4902896881104</t>
+    <t xml:space="preserve">10.490288734436</t>
   </si>
   <si>
     <t xml:space="preserve">10.5979747772217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8671865463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1453723907471</t>
+    <t xml:space="preserve">10.8671855926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1453714370728</t>
   </si>
   <si>
     <t xml:space="preserve">10.9658975601196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9569234848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.082555770874</t>
+    <t xml:space="preserve">10.9569225311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0825548171997</t>
   </si>
   <si>
     <t xml:space="preserve">11.1094770431519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1722917556763</t>
+    <t xml:space="preserve">11.1722927093506</t>
   </si>
   <si>
     <t xml:space="preserve">11.2440824508667</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2261362075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.190239906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.459451675415</t>
+    <t xml:space="preserve">11.2261352539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1902408599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4594526290894</t>
   </si>
   <si>
     <t xml:space="preserve">11.6299524307251</t>
@@ -3239,13 +3239,13 @@
     <t xml:space="preserve">12.0068492889404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6568737030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8453226089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2171611785889</t>
+    <t xml:space="preserve">11.6568746566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8453216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2171602249146</t>
   </si>
   <si>
     <t xml:space="preserve">11.2081880569458</t>
@@ -3254,22 +3254,22 @@
     <t xml:space="preserve">11.3248462677002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2620306015015</t>
+    <t xml:space="preserve">11.2620296478271</t>
   </si>
   <si>
     <t xml:space="preserve">11.1363973617554</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8223180770874</t>
+    <t xml:space="preserve">10.8223171234131</t>
   </si>
   <si>
     <t xml:space="preserve">10.3287630081177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3736305236816</t>
+    <t xml:space="preserve">10.5351581573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.373631477356</t>
   </si>
   <si>
     <t xml:space="preserve">10.544132232666</t>
@@ -3293,22 +3293,22 @@
     <t xml:space="preserve">10.4005527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6069488525391</t>
+    <t xml:space="preserve">10.6069469451904</t>
   </si>
   <si>
     <t xml:space="preserve">9.44933700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81668853759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01354026794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0225133895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15711975097656</t>
+    <t xml:space="preserve">8.81668949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01354122161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02251243591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15712070465088</t>
   </si>
   <si>
     <t xml:space="preserve">8.48914813995361</t>
@@ -3317,19 +3317,19 @@
     <t xml:space="preserve">8.20198822021484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34556865692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5385046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67759609222412</t>
+    <t xml:space="preserve">8.34556770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53850269317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6775951385498</t>
   </si>
   <si>
     <t xml:space="preserve">9.09038734436035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96924304962158</t>
+    <t xml:space="preserve">8.96924209594727</t>
   </si>
   <si>
     <t xml:space="preserve">9.01859760284424</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">9.10833549499512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18012428283691</t>
+    <t xml:space="preserve">9.18012523651123</t>
   </si>
   <si>
     <t xml:space="preserve">9.13525676727295</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">8.98270320892334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79874229431152</t>
+    <t xml:space="preserve">8.79874134063721</t>
   </si>
   <si>
     <t xml:space="preserve">8.90642642974854</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">9.25191497802734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08141422271729</t>
+    <t xml:space="preserve">9.08141326904297</t>
   </si>
   <si>
     <t xml:space="preserve">8.97372913360596</t>
@@ -3371,19 +3371,19 @@
     <t xml:space="preserve">8.83014965057373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43979263305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26480484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36351490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27377796173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30967330932617</t>
+    <t xml:space="preserve">8.43979167938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26480388641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36351585388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27377891540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30967426300049</t>
   </si>
   <si>
     <t xml:space="preserve">8.35005474090576</t>
@@ -3395,40 +3395,40 @@
     <t xml:space="preserve">8.51606845855713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94232082366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70900535583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57439804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45774078369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46671390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61477947235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49363422393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30070018768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18404197692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25134372711182</t>
+    <t xml:space="preserve">8.94232177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70900440216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5743989944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45773887634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46671485900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61478042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4936351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30069923400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18404102325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25134468078613</t>
   </si>
   <si>
     <t xml:space="preserve">8.12571239471436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88399124145508</t>
+    <t xml:space="preserve">8.88399219512939</t>
   </si>
   <si>
     <t xml:space="preserve">9.65573310852051</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">9.6856861114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58440971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63044357299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87903118133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0539627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2104797363281</t>
+    <t xml:space="preserve">9.5844087600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63044452667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87903022766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0539617538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2104806900024</t>
   </si>
   <si>
     <t xml:space="preserve">9.95268630981445</t>
@@ -3464,46 +3464,46 @@
     <t xml:space="preserve">9.89744472503662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0631694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1184101104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1552391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63965034484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40027141571045</t>
+    <t xml:space="preserve">10.0631704330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1184110641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1552381515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63965129852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40027046203613</t>
   </si>
   <si>
     <t xml:space="preserve">9.22533988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4463062286377</t>
+    <t xml:space="preserve">9.44630527496338</t>
   </si>
   <si>
     <t xml:space="preserve">8.87087249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95833778381348</t>
+    <t xml:space="preserve">8.95833873748779</t>
   </si>
   <si>
     <t xml:space="preserve">8.98595905303955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02278709411621</t>
+    <t xml:space="preserve">9.02278614044189</t>
   </si>
   <si>
     <t xml:space="preserve">9.03199481964111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66831970214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62228584289551</t>
+    <t xml:space="preserve">8.66832065582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62228488922119</t>
   </si>
   <si>
     <t xml:space="preserve">8.67292404174805</t>
@@ -3512,31 +3512,31 @@
     <t xml:space="preserve">8.77419948577881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73737144470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53481960296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52561283111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30464744567871</t>
+    <t xml:space="preserve">8.73737239837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53482055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52561378479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30464649200439</t>
   </si>
   <si>
     <t xml:space="preserve">8.35988807678223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80642318725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08263206481934</t>
+    <t xml:space="preserve">8.80642414093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08263111114502</t>
   </si>
   <si>
     <t xml:space="preserve">8.85706233978271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88928699493408</t>
+    <t xml:space="preserve">8.88928604125977</t>
   </si>
   <si>
     <t xml:space="preserve">8.82023429870605</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">8.60847568511963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90309619903564</t>
+    <t xml:space="preserve">8.90309715270996</t>
   </si>
   <si>
     <t xml:space="preserve">9.00437259674072</t>
@@ -3557,46 +3557,46 @@
     <t xml:space="preserve">9.1056489944458</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14247798919678</t>
+    <t xml:space="preserve">9.14247703552246</t>
   </si>
   <si>
     <t xml:space="preserve">8.99976921081543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71895885467529</t>
+    <t xml:space="preserve">8.71895790100098</t>
   </si>
   <si>
     <t xml:space="preserve">8.86166477203369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17470073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47392559051514</t>
+    <t xml:space="preserve">9.17470169067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47392654418945</t>
   </si>
   <si>
     <t xml:space="preserve">9.5936164855957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64885711669922</t>
+    <t xml:space="preserve">9.64885807037354</t>
   </si>
   <si>
     <t xml:space="preserve">9.77775478363037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72251415252686</t>
+    <t xml:space="preserve">9.72251319885254</t>
   </si>
   <si>
     <t xml:space="preserve">9.55678844451904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75934028625488</t>
+    <t xml:space="preserve">9.7593412399292</t>
   </si>
   <si>
     <t xml:space="preserve">9.73171997070312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66727161407471</t>
+    <t xml:space="preserve">9.66727066040039</t>
   </si>
   <si>
     <t xml:space="preserve">9.37265014648438</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">9.21613311767578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84325122833252</t>
+    <t xml:space="preserve">8.84325218200684</t>
   </si>
   <si>
     <t xml:space="preserve">9.00897598266602</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">8.92611408233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59466361999512</t>
+    <t xml:space="preserve">8.59466552734375</t>
   </si>
   <si>
     <t xml:space="preserve">8.56244087219238</t>
@@ -3626,22 +3626,22 @@
     <t xml:space="preserve">8.57164859771729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44274997711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38750839233398</t>
+    <t xml:space="preserve">8.44275093078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38750743865967</t>
   </si>
   <si>
     <t xml:space="preserve">8.45195770263672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14352607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1251106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23559474945068</t>
+    <t xml:space="preserve">8.14352512359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12511157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23559379577637</t>
   </si>
   <si>
     <t xml:space="preserve">8.23099040985107</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">8.7926139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51640605926514</t>
+    <t xml:space="preserve">8.51640510559082</t>
   </si>
   <si>
     <t xml:space="preserve">8.31385326385498</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">8.33226680755615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2171802520752</t>
+    <t xml:space="preserve">8.21718120574951</t>
   </si>
   <si>
     <t xml:space="preserve">8.09749126434326</t>
@@ -3683,25 +3683,25 @@
     <t xml:space="preserve">7.88112878799438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83049058914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82588672637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4944372177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82128286361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97319746017456</t>
+    <t xml:space="preserve">7.83049011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82588624954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49443769454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8212833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9731969833374</t>
   </si>
   <si>
     <t xml:space="preserve">8.31845664978027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2217845916748</t>
+    <t xml:space="preserve">8.22178554534912</t>
   </si>
   <si>
     <t xml:space="preserve">8.34147453308105</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">8.30924987792969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29544067382812</t>
+    <t xml:space="preserve">8.29543972015381</t>
   </si>
   <si>
     <t xml:space="preserve">8.68213081359863</t>
@@ -3719,10 +3719,10 @@
     <t xml:space="preserve">8.47037124633789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61307907104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66371726989746</t>
+    <t xml:space="preserve">8.61307811737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66371631622314</t>
   </si>
   <si>
     <t xml:space="preserve">8.73276805877686</t>
@@ -3737,34 +3737,34 @@
     <t xml:space="preserve">8.97214889526367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79721736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.193115234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54758071899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82378959655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79616928100586</t>
+    <t xml:space="preserve">8.79721832275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19311428070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54758167266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8237886428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79616832733154</t>
   </si>
   <si>
     <t xml:space="preserve">9.74092674255371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80537509918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0723752975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2196865081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8641710281372</t>
+    <t xml:space="preserve">9.80537605285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0723762512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.219687461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8641719818115</t>
   </si>
   <si>
     <t xml:space="preserve">10.7260675430298</t>
@@ -3776,58 +3776,58 @@
     <t xml:space="preserve">10.7444820404053</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5143089294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2381019592285</t>
+    <t xml:space="preserve">10.514307975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2381010055542</t>
   </si>
   <si>
     <t xml:space="preserve">10.3393774032593</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2841348648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3209629058838</t>
+    <t xml:space="preserve">10.2841358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3209638595581</t>
   </si>
   <si>
     <t xml:space="preserve">10.1368246078491</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1828603744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3485841751099</t>
+    <t xml:space="preserve">10.1828584671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3485832214355</t>
   </si>
   <si>
     <t xml:space="preserve">10.192066192627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0815839767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90665149688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85140895843506</t>
+    <t xml:space="preserve">10.0815830230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90665245056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85140991210938</t>
   </si>
   <si>
     <t xml:space="preserve">9.94347953796387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86061668395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7501335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65806484222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60282421112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48313236236572</t>
+    <t xml:space="preserve">9.86061763763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75013446807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6580638885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60282325744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48313331604004</t>
   </si>
   <si>
     <t xml:space="preserve">9.62123680114746</t>
@@ -3839,19 +3839,19 @@
     <t xml:space="preserve">10.146032333374</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1276168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2473087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4866876602173</t>
+    <t xml:space="preserve">10.1276178359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2473077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4866886138916</t>
   </si>
   <si>
     <t xml:space="preserve">10.5327224731445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.772102355957</t>
+    <t xml:space="preserve">10.7721014022827</t>
   </si>
   <si>
     <t xml:space="preserve">10.6800336837769</t>
@@ -3860,19 +3860,19 @@
     <t xml:space="preserve">10.4038257598877</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7352752685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5695495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6616201400757</t>
+    <t xml:space="preserve">10.7352743148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5695505142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6616191864014</t>
   </si>
   <si>
     <t xml:space="preserve">10.9286203384399</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9654474258423</t>
+    <t xml:space="preserve">10.9654483795166</t>
   </si>
   <si>
     <t xml:space="preserve">11.3889665603638</t>
@@ -3884,13 +3884,13 @@
     <t xml:space="preserve">12.1163139343262</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2912454605103</t>
+    <t xml:space="preserve">12.2912464141846</t>
   </si>
   <si>
     <t xml:space="preserve">12.3372802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1623477935791</t>
+    <t xml:space="preserve">12.1623487472534</t>
   </si>
   <si>
     <t xml:space="preserve">11.9874172210693</t>
@@ -3899,19 +3899,19 @@
     <t xml:space="preserve">12.0886926651001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8585195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.318865776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3649005889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2820377349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2083835601807</t>
+    <t xml:space="preserve">11.8585205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3188667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3649015426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2820386886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2083826065063</t>
   </si>
   <si>
     <t xml:space="preserve">12.2636241912842</t>
@@ -3932,13 +3932,13 @@
     <t xml:space="preserve">13.4789390563965</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1290760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5950736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8252468109131</t>
+    <t xml:space="preserve">13.129075050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5950746536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8252477645874</t>
   </si>
   <si>
     <t xml:space="preserve">12.8896951675415</t>
@@ -3950,19 +3950,19 @@
     <t xml:space="preserve">12.6963500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6134881973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0058298110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9137601852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1715545654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0518655776978</t>
+    <t xml:space="preserve">12.6134872436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0058307647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.913761138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.171555519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0518646240234</t>
   </si>
   <si>
     <t xml:space="preserve">12.2267961502075</t>
@@ -3977,13 +3977,13 @@
     <t xml:space="preserve">11.9966230392456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9321756362915</t>
+    <t xml:space="preserve">11.9321746826172</t>
   </si>
   <si>
     <t xml:space="preserve">12.4293489456177</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7700061798096</t>
+    <t xml:space="preserve">12.7700052261353</t>
   </si>
   <si>
     <t xml:space="preserve">12.2728309631348</t>
@@ -3998,25 +3998,25 @@
     <t xml:space="preserve">12.4661769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4845914840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3096590042114</t>
+    <t xml:space="preserve">12.4845905303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3096580505371</t>
   </si>
   <si>
     <t xml:space="preserve">12.024245262146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1991767883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2544183731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6503143310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0738344192505</t>
+    <t xml:space="preserve">12.1991758346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2544174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.650315284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0738334655762</t>
   </si>
   <si>
     <t xml:space="preserve">13.2855939865112</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">13.2579717636108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1751098632812</t>
+    <t xml:space="preserve">13.1751108169556</t>
   </si>
   <si>
     <t xml:space="preserve">13.2119379043579</t>
@@ -4040,7 +4040,7 @@
     <t xml:space="preserve">13.2947998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3417453765869</t>
+    <t xml:space="preserve">13.3417444229126</t>
   </si>
   <si>
     <t xml:space="preserve">13.1821327209473</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">13.2854108810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3323564529419</t>
+    <t xml:space="preserve">13.3323554992676</t>
   </si>
   <si>
     <t xml:space="preserve">13.3511343002319</t>
@@ -4076,19 +4076,19 @@
     <t xml:space="preserve">13.4168567657471</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4544134140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4919681549072</t>
+    <t xml:space="preserve">13.4544124603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4919691085815</t>
   </si>
   <si>
     <t xml:space="preserve">13.6140260696411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9895849227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9614171981812</t>
+    <t xml:space="preserve">13.9895839691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9614181518555</t>
   </si>
   <si>
     <t xml:space="preserve">13.7548599243164</t>
@@ -4100,13 +4100,13 @@
     <t xml:space="preserve">13.5952472686768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5201349258423</t>
+    <t xml:space="preserve">13.5201358795166</t>
   </si>
   <si>
     <t xml:space="preserve">12.703293800354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3840684890747</t>
+    <t xml:space="preserve">12.3840675354004</t>
   </si>
   <si>
     <t xml:space="preserve">12.3652906417847</t>
@@ -4121,19 +4121,19 @@
     <t xml:space="preserve">12.5061254501343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6000156402588</t>
+    <t xml:space="preserve">12.6000146865845</t>
   </si>
   <si>
     <t xml:space="preserve">12.7502393722534</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6469612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6281814575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5249032974243</t>
+    <t xml:space="preserve">12.6469602584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6281824111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5249042510986</t>
   </si>
   <si>
     <t xml:space="preserve">12.5342931747437</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">12.2526226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4028463363647</t>
+    <t xml:space="preserve">12.4028472900391</t>
   </si>
   <si>
     <t xml:space="preserve">12.3277349472046</t>
@@ -4166,19 +4166,19 @@
     <t xml:space="preserve">12.5155143737793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4310140609741</t>
+    <t xml:space="preserve">12.4310131072998</t>
   </si>
   <si>
     <t xml:space="preserve">12.1211767196655</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0836210250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4122352600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0930099487305</t>
+    <t xml:space="preserve">12.0836219787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4122362136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0930109024048</t>
   </si>
   <si>
     <t xml:space="preserve">12.2338447570801</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">12.0648441314697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2056789398193</t>
+    <t xml:space="preserve">12.205677986145</t>
   </si>
   <si>
     <t xml:space="preserve">11.9991207122803</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">11.9240083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7268400192261</t>
+    <t xml:space="preserve">11.7268390655518</t>
   </si>
   <si>
     <t xml:space="preserve">11.9146194458008</t>
@@ -4223,7 +4223,7 @@
     <t xml:space="preserve">11.9897317886353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554552078247</t>
+    <t xml:space="preserve">12.0554542541504</t>
   </si>
   <si>
     <t xml:space="preserve">12.0460653305054</t>
@@ -4232,10 +4232,10 @@
     <t xml:space="preserve">12.0742321014404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9709529876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8770627975464</t>
+    <t xml:space="preserve">11.9709539413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8770637512207</t>
   </si>
   <si>
     <t xml:space="preserve">11.7737846374512</t>
@@ -4262,13 +4262,13 @@
     <t xml:space="preserve">11.4545593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5108938217163</t>
+    <t xml:space="preserve">11.510892868042</t>
   </si>
   <si>
     <t xml:space="preserve">11.670506477356</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4076147079468</t>
+    <t xml:space="preserve">11.4076137542725</t>
   </si>
   <si>
     <t xml:space="preserve">11.3606700897217</t>
@@ -4295,10 +4295,10 @@
     <t xml:space="preserve">10.8254976272583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7785520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6001625061035</t>
+    <t xml:space="preserve">10.7785530090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6001615524292</t>
   </si>
   <si>
     <t xml:space="preserve">10.7034406661987</t>
@@ -4310,10 +4310,10 @@
     <t xml:space="preserve">10.7503852844238</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7222194671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6471061706543</t>
+    <t xml:space="preserve">10.7222185134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6471071243286</t>
   </si>
   <si>
     <t xml:space="preserve">10.31849193573</t>
@@ -4337,7 +4337,7 @@
     <t xml:space="preserve">9.68004131317139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68943023681641</t>
+    <t xml:space="preserve">9.68943119049072</t>
   </si>
   <si>
     <t xml:space="preserve">9.71759796142578</t>
@@ -4376,7 +4376,7 @@
     <t xml:space="preserve">9.94293308258057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85843276977539</t>
+    <t xml:space="preserve">9.85843181610107</t>
   </si>
   <si>
     <t xml:space="preserve">10.1776580810547</t>
@@ -4388,7 +4388,7 @@
     <t xml:space="preserve">10.018045425415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0649909973145</t>
+    <t xml:space="preserve">10.0649900436401</t>
   </si>
   <si>
     <t xml:space="preserve">9.89598751068115</t>
@@ -4406,10 +4406,10 @@
     <t xml:space="preserve">10.2527694702148</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1307125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2809371948242</t>
+    <t xml:space="preserve">10.1307134628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2809362411499</t>
   </si>
   <si>
     <t xml:space="preserve">10.1964349746704</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">10.3560485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">10.506272315979</t>
+    <t xml:space="preserve">10.5062713623047</t>
   </si>
   <si>
     <t xml:space="preserve">10.4029932022095</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">9.97109985351562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4874935150146</t>
+    <t xml:space="preserve">10.487494468689</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405498504639</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">10.6658849716187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5719947814941</t>
+    <t xml:space="preserve">10.5719957351685</t>
   </si>
   <si>
     <t xml:space="preserve">10.4499387741089</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">10.309103012085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2621583938599</t>
+    <t xml:space="preserve">10.2621593475342</t>
   </si>
   <si>
     <t xml:space="preserve">10.1870470046997</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">10.1401023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058248519897</t>
+    <t xml:space="preserve">10.2058238983154</t>
   </si>
   <si>
     <t xml:space="preserve">10.6095514297485</t>
@@ -4496,10 +4496,10 @@
     <t xml:space="preserve">10.7409963607788</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9099979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7316083908081</t>
+    <t xml:space="preserve">10.9099988937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7316074371338</t>
   </si>
   <si>
     <t xml:space="preserve">10.8912210464478</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">10.7128295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7879409790039</t>
+    <t xml:space="preserve">10.7879419326782</t>
   </si>
   <si>
     <t xml:space="preserve">10.9287767410278</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">11.0602216720581</t>
   </si>
   <si>
-    <t xml:space="preserve">11.003888130188</t>
+    <t xml:space="preserve">11.0038890838623</t>
   </si>
   <si>
     <t xml:space="preserve">10.8818321228027</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">11.1728897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2949466705322</t>
+    <t xml:space="preserve">11.2949457168579</t>
   </si>
   <si>
     <t xml:space="preserve">11.1447229385376</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">11.0508337020874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2480020523071</t>
+    <t xml:space="preserve">11.2480010986328</t>
   </si>
   <si>
     <t xml:space="preserve">11.3982257843018</t>
@@ -4589,16 +4589,16 @@
     <t xml:space="preserve">11.3418912887573</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1259450912476</t>
+    <t xml:space="preserve">11.1259460449219</t>
   </si>
   <si>
     <t xml:space="preserve">11.2386131286621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292232513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9757213592529</t>
+    <t xml:space="preserve">11.2292242050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9757204055786</t>
   </si>
   <si>
     <t xml:space="preserve">11.6104164123535</t>
@@ -4619,10 +4619,10 @@
     <t xml:space="preserve">11.4094924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3249921798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1090450286865</t>
+    <t xml:space="preserve">11.3249912261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1090440750122</t>
   </si>
   <si>
     <t xml:space="preserve">10.4705944061279</t>
@@ -4634,7 +4634,7 @@
     <t xml:space="preserve">10.4536933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3691921234131</t>
+    <t xml:space="preserve">10.3691930770874</t>
   </si>
   <si>
     <t xml:space="preserve">10.4799823760986</t>
@@ -5763,6 +5763,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.94499969482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77000045776367</t>
   </si>
 </sst>
 </file>
@@ -9889,7 +9892,7 @@
         <v>10.1195363998413</v>
       </c>
       <c r="G146" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -9915,7 +9918,7 @@
         <v>10.2294216156006</v>
       </c>
       <c r="G147" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -9941,7 +9944,7 @@
         <v>10.0595979690552</v>
       </c>
       <c r="G148" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -9967,7 +9970,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G149" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -9993,7 +9996,7 @@
         <v>10.5490922927856</v>
       </c>
       <c r="G150" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -10045,7 +10048,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G152" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -10071,7 +10074,7 @@
         <v>10.2893600463867</v>
       </c>
       <c r="G153" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -10097,7 +10100,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G154" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -10123,7 +10126,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G155" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -10149,7 +10152,7 @@
         <v>10.5091333389282</v>
       </c>
       <c r="G156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -10175,7 +10178,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G157" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -10201,7 +10204,7 @@
         <v>10.5191230773926</v>
       </c>
       <c r="G158" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -10227,7 +10230,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G159" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -10279,7 +10282,7 @@
         <v>10.2094430923462</v>
       </c>
       <c r="G161" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -10305,7 +10308,7 @@
         <v>10.1594953536987</v>
       </c>
       <c r="G162" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -10331,7 +10334,7 @@
         <v>10.1994533538818</v>
       </c>
       <c r="G163" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -10357,7 +10360,7 @@
         <v>10.1095457077026</v>
       </c>
       <c r="G164" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -10383,7 +10386,7 @@
         <v>10.1395149230957</v>
       </c>
       <c r="G165" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -10409,7 +10412,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G166" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -10435,7 +10438,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G167" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -10461,7 +10464,7 @@
         <v>10.3992471694946</v>
       </c>
       <c r="G168" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -10513,7 +10516,7 @@
         <v>10.4092359542847</v>
       </c>
       <c r="G170" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -10539,7 +10542,7 @@
         <v>10.4591846466064</v>
       </c>
       <c r="G171" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -10565,7 +10568,7 @@
         <v>10.4591846466064</v>
       </c>
       <c r="G172" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -10591,7 +10594,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G173" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -10617,7 +10620,7 @@
         <v>10.4791641235352</v>
       </c>
       <c r="G174" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -10669,7 +10672,7 @@
         <v>10.6989374160767</v>
       </c>
       <c r="G176" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -10695,7 +10698,7 @@
         <v>10.6389989852905</v>
       </c>
       <c r="G177" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -10799,7 +10802,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G181" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -10877,7 +10880,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G184" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -10955,7 +10958,7 @@
         <v>10.688946723938</v>
       </c>
       <c r="G187" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -10981,7 +10984,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G188" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -11007,7 +11010,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G189" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -11033,7 +11036,7 @@
         <v>10.4491949081421</v>
       </c>
       <c r="G190" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -11085,7 +11088,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G192" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -11111,7 +11114,7 @@
         <v>10.6090297698975</v>
       </c>
       <c r="G193" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -11137,7 +11140,7 @@
         <v>10.7089262008667</v>
       </c>
       <c r="G194" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -11163,7 +11166,7 @@
         <v>10.8887405395508</v>
       </c>
       <c r="G195" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -11189,7 +11192,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G196" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -11215,7 +11218,7 @@
         <v>10.5990400314331</v>
       </c>
       <c r="G197" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -11241,7 +11244,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G198" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -11267,7 +11270,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G199" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -11293,7 +11296,7 @@
         <v>10.3792667388916</v>
       </c>
       <c r="G200" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -11371,7 +11374,7 @@
         <v>10.4691743850708</v>
       </c>
       <c r="G203" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -11397,7 +11400,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G204" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -11423,7 +11426,7 @@
         <v>10.5091333389282</v>
       </c>
       <c r="G205" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -11449,7 +11452,7 @@
         <v>10.6090297698975</v>
       </c>
       <c r="G206" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -11475,7 +11478,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G207" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -11501,7 +11504,7 @@
         <v>10.5291118621826</v>
       </c>
       <c r="G208" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -11527,7 +11530,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G209" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -11579,7 +11582,7 @@
         <v>10.8787508010864</v>
       </c>
       <c r="G211" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -11605,7 +11608,7 @@
         <v>10.9986267089844</v>
       </c>
       <c r="G212" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -11631,7 +11634,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G213" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -11657,7 +11660,7 @@
         <v>11.2483692169189</v>
       </c>
       <c r="G214" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -11683,7 +11686,7 @@
         <v>11.258358001709</v>
       </c>
       <c r="G215" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -11709,7 +11712,7 @@
         <v>11.008617401123</v>
       </c>
       <c r="G216" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -11735,7 +11738,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G217" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -11761,7 +11764,7 @@
         <v>10.5590810775757</v>
       </c>
       <c r="G218" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -11787,7 +11790,7 @@
         <v>11.0585651397705</v>
       </c>
       <c r="G219" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -11813,7 +11816,7 @@
         <v>11.3682451248169</v>
       </c>
       <c r="G220" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -11839,7 +11842,7 @@
         <v>11.0385856628418</v>
       </c>
       <c r="G221" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -11865,7 +11868,7 @@
         <v>10.828803062439</v>
       </c>
       <c r="G222" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -11891,7 +11894,7 @@
         <v>10.98863697052</v>
       </c>
       <c r="G223" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -11917,7 +11920,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G224" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -11943,7 +11946,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G225" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -11969,7 +11972,7 @@
         <v>10.7289056777954</v>
       </c>
       <c r="G226" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11995,7 +11998,7 @@
         <v>10.6389989852905</v>
       </c>
       <c r="G227" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -12021,7 +12024,7 @@
         <v>10.6190185546875</v>
       </c>
       <c r="G228" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -12073,7 +12076,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G230" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -12099,7 +12102,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G231" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -12125,7 +12128,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G232" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -12151,7 +12154,7 @@
         <v>10.838791847229</v>
       </c>
       <c r="G233" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -12203,7 +12206,7 @@
         <v>10.7388954162598</v>
       </c>
       <c r="G235" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -12229,7 +12232,7 @@
         <v>10.8088226318359</v>
       </c>
       <c r="G236" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -12255,7 +12258,7 @@
         <v>10.7089262008667</v>
       </c>
       <c r="G237" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -12281,7 +12284,7 @@
         <v>10.539101600647</v>
       </c>
       <c r="G238" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -12307,7 +12310,7 @@
         <v>10.5590810775757</v>
       </c>
       <c r="G239" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -12359,7 +12362,7 @@
         <v>10.9686584472656</v>
       </c>
       <c r="G241" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -12385,7 +12388,7 @@
         <v>11.0985240936279</v>
       </c>
       <c r="G242" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -12411,7 +12414,7 @@
         <v>10.9686584472656</v>
       </c>
       <c r="G243" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -12437,7 +12440,7 @@
         <v>10.828803062439</v>
       </c>
       <c r="G244" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -12463,7 +12466,7 @@
         <v>11.008617401123</v>
       </c>
       <c r="G245" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -12489,7 +12492,7 @@
         <v>10.8887405395508</v>
       </c>
       <c r="G246" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -12515,7 +12518,7 @@
         <v>10.98863697052</v>
       </c>
       <c r="G247" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -12541,7 +12544,7 @@
         <v>10.8088226318359</v>
       </c>
       <c r="G248" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -12567,7 +12570,7 @@
         <v>10.7289056777954</v>
       </c>
       <c r="G249" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -12593,7 +12596,7 @@
         <v>10.7688636779785</v>
       </c>
       <c r="G250" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -12619,7 +12622,7 @@
         <v>10.9087200164795</v>
       </c>
       <c r="G251" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -12645,7 +12648,7 @@
         <v>10.9187097549438</v>
       </c>
       <c r="G252" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -12671,7 +12674,7 @@
         <v>11.0685548782349</v>
       </c>
       <c r="G253" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -12697,7 +12700,7 @@
         <v>11.2084102630615</v>
       </c>
       <c r="G254" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -12723,7 +12726,7 @@
         <v>11.2683477401733</v>
       </c>
       <c r="G255" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -12749,7 +12752,7 @@
         <v>11.4181928634644</v>
       </c>
       <c r="G256" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -12775,7 +12778,7 @@
         <v>11.4881210327148</v>
       </c>
       <c r="G257" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -12801,7 +12804,7 @@
         <v>11.9876041412354</v>
       </c>
       <c r="G258" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -12827,7 +12830,7 @@
         <v>12.0575323104858</v>
       </c>
       <c r="G259" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -12853,7 +12856,7 @@
         <v>11.8177795410156</v>
       </c>
       <c r="G260" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -12879,7 +12882,7 @@
         <v>11.9576349258423</v>
       </c>
       <c r="G261" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -12905,7 +12908,7 @@
         <v>12.0075836181641</v>
       </c>
       <c r="G262" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -12931,7 +12934,7 @@
         <v>12.0375528335571</v>
       </c>
       <c r="G263" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -12957,7 +12960,7 @@
         <v>12.0974912643433</v>
       </c>
       <c r="G264" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -12983,7 +12986,7 @@
         <v>12.277304649353</v>
       </c>
       <c r="G265" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -13009,7 +13012,7 @@
         <v>12.0575323104858</v>
       </c>
       <c r="G266" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -13035,7 +13038,7 @@
         <v>12.3072738647461</v>
       </c>
       <c r="G267" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -13061,7 +13064,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G268" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -13087,7 +13090,7 @@
         <v>12.2673149108887</v>
       </c>
       <c r="G269" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -13113,7 +13116,7 @@
         <v>12.2173671722412</v>
       </c>
       <c r="G270" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -13139,7 +13142,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G271" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -13165,7 +13168,7 @@
         <v>12.1774082183838</v>
       </c>
       <c r="G272" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -13191,7 +13194,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G273" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -13217,7 +13220,7 @@
         <v>12.2073774337769</v>
       </c>
       <c r="G274" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -13243,7 +13246,7 @@
         <v>12.2972841262817</v>
       </c>
       <c r="G275" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -13269,7 +13272,7 @@
         <v>12.1873979568481</v>
       </c>
       <c r="G276" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -13295,7 +13298,7 @@
         <v>12.1474390029907</v>
       </c>
       <c r="G277" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -13321,7 +13324,7 @@
         <v>11.9876041412354</v>
       </c>
       <c r="G278" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -13347,7 +13350,7 @@
         <v>11.8477487564087</v>
       </c>
       <c r="G279" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -13373,7 +13376,7 @@
         <v>12.2173671722412</v>
       </c>
       <c r="G280" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -13399,7 +13402,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G281" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -13425,7 +13428,7 @@
         <v>12.4071702957153</v>
       </c>
       <c r="G282" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -13451,7 +13454,7 @@
         <v>12.127459526062</v>
       </c>
       <c r="G283" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -13477,7 +13480,7 @@
         <v>12.1174697875977</v>
       </c>
       <c r="G284" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -13503,7 +13506,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G285" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -13529,7 +13532,7 @@
         <v>12.2473363876343</v>
       </c>
       <c r="G286" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -13555,7 +13558,7 @@
         <v>12.4071702957153</v>
       </c>
       <c r="G287" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -13581,7 +13584,7 @@
         <v>12.6669015884399</v>
       </c>
       <c r="G288" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -13607,7 +13610,7 @@
         <v>12.5670051574707</v>
       </c>
       <c r="G289" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -13633,7 +13636,7 @@
         <v>12.6569118499756</v>
       </c>
       <c r="G290" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -13659,7 +13662,7 @@
         <v>12.5670051574707</v>
       </c>
       <c r="G291" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -13685,7 +13688,7 @@
         <v>12.4970779418945</v>
       </c>
       <c r="G292" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -13711,7 +13714,7 @@
         <v>12.5969743728638</v>
       </c>
       <c r="G293" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -13737,7 +13740,7 @@
         <v>12.8567056655884</v>
       </c>
       <c r="G294" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -13763,7 +13766,7 @@
         <v>12.8966636657715</v>
       </c>
       <c r="G295" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -13789,7 +13792,7 @@
         <v>12.816746711731</v>
       </c>
       <c r="G296" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -13815,7 +13818,7 @@
         <v>12.5170574188232</v>
       </c>
       <c r="G297" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -13841,7 +13844,7 @@
         <v>12.8067569732666</v>
       </c>
       <c r="G298" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -13867,7 +13870,7 @@
         <v>12.6669015884399</v>
       </c>
       <c r="G299" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -13893,7 +13896,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G300" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -13919,7 +13922,7 @@
         <v>13.1863651275635</v>
       </c>
       <c r="G301" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13945,7 +13948,7 @@
         <v>13.1464061737061</v>
       </c>
       <c r="G302" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -13971,7 +13974,7 @@
         <v>12.9566020965576</v>
       </c>
       <c r="G303" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13997,7 +14000,7 @@
         <v>12.966591835022</v>
       </c>
       <c r="G304" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -14023,7 +14026,7 @@
         <v>13.0764780044556</v>
       </c>
       <c r="G305" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -14049,7 +14052,7 @@
         <v>12.9765815734863</v>
       </c>
       <c r="G306" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -14075,7 +14078,7 @@
         <v>12.9765815734863</v>
       </c>
       <c r="G307" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -14101,7 +14104,7 @@
         <v>13.1863651275635</v>
       </c>
       <c r="G308" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -14127,7 +14130,7 @@
         <v>13.2762718200684</v>
       </c>
       <c r="G309" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -14153,7 +14156,7 @@
         <v>13.1064472198486</v>
       </c>
       <c r="G310" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -14179,7 +14182,7 @@
         <v>13.2862615585327</v>
       </c>
       <c r="G311" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -14205,7 +14208,7 @@
         <v>13.536003112793</v>
       </c>
       <c r="G312" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -14231,7 +14234,7 @@
         <v>13.4460964202881</v>
       </c>
       <c r="G313" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -14257,7 +14260,7 @@
         <v>13.5060338973999</v>
       </c>
       <c r="G314" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -14283,7 +14286,7 @@
         <v>13.5459928512573</v>
       </c>
       <c r="G315" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -14309,7 +14312,7 @@
         <v>13.5759620666504</v>
       </c>
       <c r="G316" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -14335,7 +14338,7 @@
         <v>13.6458902359009</v>
       </c>
       <c r="G317" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -14361,7 +14364,7 @@
         <v>13.7058277130127</v>
       </c>
       <c r="G318" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -14387,7 +14390,7 @@
         <v>13.7757549285889</v>
       </c>
       <c r="G319" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -14413,7 +14416,7 @@
         <v>13.8456830978394</v>
       </c>
       <c r="G320" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -14439,7 +14442,7 @@
         <v>13.835693359375</v>
       </c>
       <c r="G321" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -14465,7 +14468,7 @@
         <v>13.8556728363037</v>
       </c>
       <c r="G322" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -14491,7 +14494,7 @@
         <v>14.1253938674927</v>
       </c>
       <c r="G323" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -14517,7 +14520,7 @@
         <v>14.1453733444214</v>
       </c>
       <c r="G324" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -14543,7 +14546,7 @@
         <v>14.1253938674927</v>
       </c>
       <c r="G325" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -14569,7 +14572,7 @@
         <v>14.1253938674927</v>
       </c>
       <c r="G326" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -14595,7 +14598,7 @@
         <v>14.0654563903809</v>
       </c>
       <c r="G327" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -14621,7 +14624,7 @@
         <v>14.0554656982422</v>
       </c>
       <c r="G328" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -14647,7 +14650,7 @@
         <v>14.1054153442383</v>
       </c>
       <c r="G329" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -14673,7 +14676,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G330" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -14699,7 +14702,7 @@
         <v>14.0954246520996</v>
       </c>
       <c r="G331" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -14725,7 +14728,7 @@
         <v>13.7757549285889</v>
       </c>
       <c r="G332" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -14751,7 +14754,7 @@
         <v>13.9455795288086</v>
       </c>
       <c r="G333" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -14777,7 +14780,7 @@
         <v>14.0754451751709</v>
       </c>
       <c r="G334" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -14803,7 +14806,7 @@
         <v>13.8856420516968</v>
       </c>
       <c r="G335" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -14829,7 +14832,7 @@
         <v>14.3851251602173</v>
       </c>
       <c r="G336" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -14855,7 +14858,7 @@
         <v>14.5050010681152</v>
       </c>
       <c r="G337" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -14881,7 +14884,7 @@
         <v>14.3351774215698</v>
       </c>
       <c r="G338" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -14907,7 +14910,7 @@
         <v>14.4250841140747</v>
       </c>
       <c r="G339" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -14933,7 +14936,7 @@
         <v>14.4150943756104</v>
       </c>
       <c r="G340" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -14959,7 +14962,7 @@
         <v>14.6148881912231</v>
       </c>
       <c r="G341" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -14985,7 +14988,7 @@
         <v>14.4950122833252</v>
       </c>
       <c r="G342" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -15011,7 +15014,7 @@
         <v>14.7847118377686</v>
       </c>
       <c r="G343" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -15037,7 +15040,7 @@
         <v>14.9045877456665</v>
       </c>
       <c r="G344" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -15063,7 +15066,7 @@
         <v>14.8146810531616</v>
       </c>
       <c r="G345" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -15089,7 +15092,7 @@
         <v>15.0444440841675</v>
       </c>
       <c r="G346" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -15115,7 +15118,7 @@
         <v>15.0844020843506</v>
       </c>
       <c r="G347" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -15141,7 +15144,7 @@
         <v>14.7647333145142</v>
       </c>
       <c r="G348" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -15167,7 +15170,7 @@
         <v>14.6648359298706</v>
       </c>
       <c r="G349" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -15193,7 +15196,7 @@
         <v>14.674825668335</v>
       </c>
       <c r="G350" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -15219,7 +15222,7 @@
         <v>14.5349702835083</v>
       </c>
       <c r="G351" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -15245,7 +15248,7 @@
         <v>14.0055179595947</v>
       </c>
       <c r="G352" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -15271,7 +15274,7 @@
         <v>13.8956308364868</v>
       </c>
       <c r="G353" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -15297,7 +15300,7 @@
         <v>14.2053108215332</v>
       </c>
       <c r="G354" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -15323,7 +15326,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G355" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -15349,7 +15352,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G356" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -15375,7 +15378,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G357" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -15401,7 +15404,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G358" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -15427,7 +15430,7 @@
         <v>14.1753416061401</v>
       </c>
       <c r="G359" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -15453,7 +15456,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G360" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -15479,7 +15482,7 @@
         <v>14.4250841140747</v>
       </c>
       <c r="G361" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -15505,7 +15508,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G362" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -15531,7 +15534,7 @@
         <v>13.9755487442017</v>
       </c>
       <c r="G363" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -15557,7 +15560,7 @@
         <v>13.8257036209106</v>
       </c>
       <c r="G364" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -15583,7 +15586,7 @@
         <v>14.0055179595947</v>
       </c>
       <c r="G365" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -17533,7 +17536,7 @@
         <v>14.1553630828857</v>
       </c>
       <c r="G440" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -17741,7 +17744,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G448" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -17767,7 +17770,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G449" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -17819,7 +17822,7 @@
         <v>14.3052082061768</v>
       </c>
       <c r="G451" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -18209,7 +18212,7 @@
         <v>13.8257036209106</v>
       </c>
       <c r="G466" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -72609,7 +72612,7 @@
     </row>
     <row r="2559">
       <c r="A2559" s="1" t="n">
-        <v>46049.6910416667</v>
+        <v>46049.3333333333</v>
       </c>
       <c r="B2559" t="n">
         <v>229232</v>
@@ -72630,6 +72633,32 @@
         <v>1916</v>
       </c>
       <c r="H2559" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" s="1" t="n">
+        <v>46050.6909953704</v>
+      </c>
+      <c r="B2560" t="n">
+        <v>304204</v>
+      </c>
+      <c r="C2560" t="n">
+        <v>9.94999980926514</v>
+      </c>
+      <c r="D2560" t="n">
+        <v>9.77000045776367</v>
+      </c>
+      <c r="E2560" t="n">
+        <v>9.89000034332275</v>
+      </c>
+      <c r="F2560" t="n">
+        <v>9.77000045776367</v>
+      </c>
+      <c r="G2560" t="s">
+        <v>1917</v>
+      </c>
+      <c r="H2560" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="1937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1938" uniqueCount="1938">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16937875747681</t>
+    <t xml:space="preserve">7.16937828063965</t>
   </si>
   <si>
     <t xml:space="preserve">BRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13994932174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92740201950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52519702911377</t>
+    <t xml:space="preserve">7.13994979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92740058898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52519798278809</t>
   </si>
   <si>
     <t xml:space="preserve">6.54154682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42873287200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60040664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78188800811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55135679244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21291589736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19820213317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2750449180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94641447067261</t>
+    <t xml:space="preserve">6.42873382568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60040712356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78188896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55135726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21291542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19820117950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27504539489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94641494750977</t>
   </si>
   <si>
     <t xml:space="preserve">6.20310735702515</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24888563156128</t>
+    <t xml:space="preserve">6.24888610839844</t>
   </si>
   <si>
     <t xml:space="preserve">6.30610942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31919002532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38785886764526</t>
+    <t xml:space="preserve">6.31919050216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38785934448242</t>
   </si>
   <si>
     <t xml:space="preserve">6.23090124130249</t>
@@ -101,25 +101,25 @@
     <t xml:space="preserve">6.16713762283325</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05922794342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99219369888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86466503143311</t>
+    <t xml:space="preserve">6.05922746658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99219417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86466598510742</t>
   </si>
   <si>
     <t xml:space="preserve">5.70443773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35945796966553</t>
+    <t xml:space="preserve">5.35945844650269</t>
   </si>
   <si>
     <t xml:space="preserve">5.51641511917114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72242212295532</t>
+    <t xml:space="preserve">5.72242259979248</t>
   </si>
   <si>
     <t xml:space="preserve">5.67500877380371</t>
@@ -134,172 +134,172 @@
     <t xml:space="preserve">5.97420978546143</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11972284317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14097690582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10010242462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23744010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11154747009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97584438323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07394409179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12953281402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21945667266846</t>
+    <t xml:space="preserve">6.11972236633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14097738265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1001033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23744106292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11154794692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97584533691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07394361495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12953329086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2194561958313</t>
   </si>
   <si>
     <t xml:space="preserve">6.35188961029053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32409429550171</t>
+    <t xml:space="preserve">6.32409524917603</t>
   </si>
   <si>
     <t xml:space="preserve">7.04675579071045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08272504806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1170597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07945537567139</t>
+    <t xml:space="preserve">7.08272457122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11705875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07945394515991</t>
   </si>
   <si>
     <t xml:space="preserve">7.1203293800354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07127904891968</t>
+    <t xml:space="preserve">7.07127952575684</t>
   </si>
   <si>
     <t xml:space="preserve">7.06637525558472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16120290756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14321899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24949216842651</t>
+    <t xml:space="preserve">7.16120338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14321994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24949169158936</t>
   </si>
   <si>
     <t xml:space="preserve">7.14158391952515</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22987174987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07618379592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26911306381226</t>
+    <t xml:space="preserve">7.22987222671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07618284225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2691125869751</t>
   </si>
   <si>
     <t xml:space="preserve">7.15302801132202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15139389038086</t>
+    <t xml:space="preserve">7.15139436721802</t>
   </si>
   <si>
     <t xml:space="preserve">7.31489229202271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43097496032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40318059921265</t>
+    <t xml:space="preserve">7.43097448348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40318012237549</t>
   </si>
   <si>
     <t xml:space="preserve">7.3557653427124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1448540687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18899917602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16283845901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2740159034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998611450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35739994049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40644931793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42279958724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39337062835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43915033340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47185039520264</t>
+    <t xml:space="preserve">7.14485454559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18899822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16283798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27401733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998659133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35740089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40644979476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4227991104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39337205886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43914985656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47184896469116</t>
   </si>
   <si>
     <t xml:space="preserve">7.51108837127686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76777982711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71546125411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63534688949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68276166915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74162149429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66968107223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72200012207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63044309616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71055698394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8560676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47736072540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50188541412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5100622177124</t>
+    <t xml:space="preserve">7.76778173446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71546220779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63534736633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68276119232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74162101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66968202590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.721999168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63044214248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71055603027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85606956481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47735977172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50188636779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51006031036377</t>
   </si>
   <si>
     <t xml:space="preserve">8.55093479156494</t>
@@ -308,235 +308,235 @@
     <t xml:space="preserve">8.42831039428711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36291122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.354736328125</t>
+    <t xml:space="preserve">8.36291217803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35473728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41196155548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5199146270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45348072052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51161098480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4617862701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47008991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6112585067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63617134094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72751522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96002864837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86868381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86037731170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58634567260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27577686309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10969638824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30400943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31231307983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60295391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61956214904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56973934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71921062469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25916957855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64135026931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25418663024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05987167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20602321624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23757743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8472900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67954921722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67788648605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95524263381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02831554412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05488872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97849416732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11301708221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23425674438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10471439361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21100616455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16782665252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32061958312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37044239044189</t>
   </si>
   <si>
     <t xml:space="preserve">8.41196250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45348358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51161098480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46178531646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47008800506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6112585067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63617134094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72751426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96002674102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86868286132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86038017272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58634662628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27577495574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10969638824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30401039123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3123140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60295295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61956310272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56973743438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71920967102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25916862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64134979248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25418567657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0598726272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20602321624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23757743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84728908538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67954874038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67788791656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95524072647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02831649780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05488872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97849321365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14457321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11301708221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23425579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10471439361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21100521087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16782474517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32061958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37044143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41196346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5033073425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36213684082031</t>
+    <t xml:space="preserve">8.50330638885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36213779449463</t>
   </si>
   <si>
     <t xml:space="preserve">8.67769050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76903533935547</t>
+    <t xml:space="preserve">8.76903438568115</t>
   </si>
   <si>
     <t xml:space="preserve">8.53652191162109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55313110351562</t>
+    <t xml:space="preserve">8.55313014984131</t>
   </si>
   <si>
     <t xml:space="preserve">8.64447498321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73581886291504</t>
+    <t xml:space="preserve">8.73581790924072</t>
   </si>
   <si>
     <t xml:space="preserve">8.68599510192871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7441234588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66938495635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48669719696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4451789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47839450836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40365791320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42856979370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65277767181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69429779052734</t>
+    <t xml:space="preserve">8.74412250518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6693868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48669815063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44517993927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4783935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40365695953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42856884002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65277862548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69429874420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.71090602874756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89359474182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84377002716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88529014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78564167022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80224990844727</t>
+    <t xml:space="preserve">8.89359569549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84377098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88529205322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78564262390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8022518157959</t>
   </si>
   <si>
     <t xml:space="preserve">8.81885814666748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90189838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05137062072754</t>
+    <t xml:space="preserve">8.90189743041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05137157440186</t>
   </si>
   <si>
     <t xml:space="preserve">8.81055450439453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6278657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70260238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82716274261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75242710113525</t>
+    <t xml:space="preserve">8.62786483764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70260143280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82716178894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75242614746094</t>
   </si>
   <si>
     <t xml:space="preserve">9.04306602478027</t>
@@ -554,13 +554,13 @@
     <t xml:space="preserve">9.35861873626709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15102100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93511390686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7773380279541</t>
+    <t xml:space="preserve">9.15102005004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93511486053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77733898162842</t>
   </si>
   <si>
     <t xml:space="preserve">9.19253921508789</t>
@@ -569,19 +569,19 @@
     <t xml:space="preserve">9.44996356964111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17593193054199</t>
+    <t xml:space="preserve">9.17593002319336</t>
   </si>
   <si>
     <t xml:space="preserve">9.00154685974121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13440990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91850662231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92681121826172</t>
+    <t xml:space="preserve">9.13441181182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91850757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92680931091309</t>
   </si>
   <si>
     <t xml:space="preserve">9.00985145568848</t>
@@ -593,22 +593,22 @@
     <t xml:space="preserve">8.7607307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11780261993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22575664520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95172214508057</t>
+    <t xml:space="preserve">9.11780452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22575569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95172119140625</t>
   </si>
   <si>
     <t xml:space="preserve">9.06797790527344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0762825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20084285736084</t>
+    <t xml:space="preserve">9.07628345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20084381103516</t>
   </si>
   <si>
     <t xml:space="preserve">9.31709861755371</t>
@@ -620,31 +620,31 @@
     <t xml:space="preserve">9.49148273468018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54961204528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96481227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0229406356812</t>
+    <t xml:space="preserve">9.54961013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96481323242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0229387283325</t>
   </si>
   <si>
     <t xml:space="preserve">9.82364368438721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93989944458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98141956329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0063314437866</t>
+    <t xml:space="preserve">9.93990039825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98142051696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0063323974609</t>
   </si>
   <si>
     <t xml:space="preserve">10.0561561584473</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2056293487549</t>
+    <t xml:space="preserve">10.2056274414062</t>
   </si>
   <si>
     <t xml:space="preserve">10.2305402755737</t>
@@ -653,70 +653,70 @@
     <t xml:space="preserve">10.2139329910278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1973247528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1558046340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1225881576538</t>
+    <t xml:space="preserve">10.1973237991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1558055877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1225891113281</t>
   </si>
   <si>
     <t xml:space="preserve">10.1807165145874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.147500038147</t>
+    <t xml:space="preserve">10.1475009918213</t>
   </si>
   <si>
     <t xml:space="preserve">10.2222366333008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1308927536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0976762771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84855556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3135805130005</t>
+    <t xml:space="preserve">10.1308917999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0976753234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84855651855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3135814666748</t>
   </si>
   <si>
     <t xml:space="preserve">10.0810689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0727643966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5294857025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4464454650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5211801528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3883171081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4713563919067</t>
+    <t xml:space="preserve">10.0727634429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5294847488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4464435577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5211791992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3883180618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4713573455811</t>
   </si>
   <si>
     <t xml:space="preserve">10.6872606277466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7204761505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540441513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4049253463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6457414627075</t>
+    <t xml:space="preserve">10.720477104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4049263000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6457405090332</t>
   </si>
   <si>
     <t xml:space="preserve">10.7952127456665</t>
@@ -734,22 +734,22 @@
     <t xml:space="preserve">10.7786045074463</t>
   </si>
   <si>
-    <t xml:space="preserve">10.869948387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7869091033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0360298156738</t>
+    <t xml:space="preserve">10.8699493408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7869100570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0360288619995</t>
   </si>
   <si>
     <t xml:space="preserve">10.8948612213135</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0443353652954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2519330978394</t>
+    <t xml:space="preserve">11.0443334579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2519340515137</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771984100342</t>
@@ -758,73 +758,73 @@
     <t xml:space="preserve">11.2270212173462</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2602386474609</t>
+    <t xml:space="preserve">11.2602367401123</t>
   </si>
   <si>
     <t xml:space="preserve">11.2851495742798</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3432779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.393102645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.451229095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5093593597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5010538101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5176610946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.741870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7584781646729</t>
+    <t xml:space="preserve">11.3432769775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3931016921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4512300491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5093574523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5010528564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5176620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7418699264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7584791183472</t>
   </si>
   <si>
     <t xml:space="preserve">11.6920471191406</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6837425231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7252616882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7667827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7169589996338</t>
+    <t xml:space="preserve">11.683741569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7252626419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7667818069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7169580459595</t>
   </si>
   <si>
     <t xml:space="preserve">11.5923976898193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7003488540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.542573928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9577741622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0574226379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9162559509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9909896850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.98268699646</t>
+    <t xml:space="preserve">11.7003507614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5425748825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9577751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0574216842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9162549972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9909906387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9826860427856</t>
   </si>
   <si>
     <t xml:space="preserve">12.1487665176392</t>
@@ -833,13 +833,13 @@
     <t xml:space="preserve">12.0491189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2899351119995</t>
+    <t xml:space="preserve">12.2899341583252</t>
   </si>
   <si>
     <t xml:space="preserve">12.3895826339722</t>
   </si>
   <si>
-    <t xml:space="preserve">12.314847946167</t>
+    <t xml:space="preserve">12.3148460388184</t>
   </si>
   <si>
     <t xml:space="preserve">12.5058393478394</t>
@@ -848,73 +848,76 @@
     <t xml:space="preserve">12.5390558242798</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2733268737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1902866363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1985912322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0823345184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6422233581543</t>
+    <t xml:space="preserve">12.2733278274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1902875900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1985902786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0823335647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.64222240448</t>
   </si>
   <si>
     <t xml:space="preserve">11.5508785247803</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8083028793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9346399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9514827728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0609769821167</t>
+    <t xml:space="preserve">11.8083009719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9346389770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9514837265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0609760284424</t>
   </si>
   <si>
     <t xml:space="preserve">12.1620454788208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.783034324646</t>
+    <t xml:space="preserve">11.7830352783203</t>
   </si>
   <si>
     <t xml:space="preserve">11.6566982269287</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7577676773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5977411270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5640516281128</t>
+    <t xml:space="preserve">11.8083019256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7577667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5977401733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5640506744385</t>
   </si>
   <si>
     <t xml:space="preserve">11.3029556274414</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2018852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1934623718262</t>
+    <t xml:space="preserve">11.2018842697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1934614181519</t>
   </si>
   <si>
     <t xml:space="preserve">11.0334348678589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9576330184937</t>
+    <t xml:space="preserve">10.9576320648193</t>
   </si>
   <si>
     <t xml:space="preserve">11.2355728149414</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208688735962</t>
+    <t xml:space="preserve">11.4208679199219</t>
   </si>
   <si>
     <t xml:space="preserve">11.2271509170532</t>
@@ -923,52 +926,52 @@
     <t xml:space="preserve">11.2861089706421</t>
   </si>
   <si>
-    <t xml:space="preserve">11.168194770813</t>
+    <t xml:space="preserve">11.1681928634644</t>
   </si>
   <si>
     <t xml:space="preserve">10.9239435195923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0250110626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7639150619507</t>
+    <t xml:space="preserve">11.0250120162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.763916015625</t>
   </si>
   <si>
     <t xml:space="preserve">10.9492101669312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5786218643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7891826629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7386493682861</t>
+    <t xml:space="preserve">10.5786209106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7891836166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7386474609375</t>
   </si>
   <si>
     <t xml:space="preserve">10.6544227600098</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7554931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4292907714844</t>
+    <t xml:space="preserve">10.7554941177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4292917251587</t>
   </si>
   <si>
     <t xml:space="preserve">11.5219383239746</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2945318222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.639853477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4629793167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.412446975708</t>
+    <t xml:space="preserve">11.2945308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6398525238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4629802703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4124460220337</t>
   </si>
   <si>
     <t xml:space="preserve">11.361909866333</t>
@@ -977,25 +980,25 @@
     <t xml:space="preserve">11.3197984695435</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2103061676025</t>
+    <t xml:space="preserve">11.2103071212769</t>
   </si>
   <si>
     <t xml:space="preserve">10.9997434616089</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9913215637207</t>
+    <t xml:space="preserve">10.991322517395</t>
   </si>
   <si>
     <t xml:space="preserve">11.0081672668457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.890251159668</t>
+    <t xml:space="preserve">10.8902530670166</t>
   </si>
   <si>
     <t xml:space="preserve">10.9323644638062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8734073638916</t>
+    <t xml:space="preserve">10.8734083175659</t>
   </si>
   <si>
     <t xml:space="preserve">10.8818302154541</t>
@@ -1004,22 +1007,22 @@
     <t xml:space="preserve">10.6796913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7807607650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8649845123291</t>
+    <t xml:space="preserve">10.78076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8649854660034</t>
   </si>
   <si>
     <t xml:space="preserve">10.7049589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9155216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2608394622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1513500213623</t>
+    <t xml:space="preserve">10.9155206680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2608413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.151349067688</t>
   </si>
   <si>
     <t xml:space="preserve">11.0839700698853</t>
@@ -1028,10 +1031,10 @@
     <t xml:space="preserve">11.0502796173096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2524194717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3282203674316</t>
+    <t xml:space="preserve">11.2524185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.328221321106</t>
   </si>
   <si>
     <t xml:space="preserve">11.3787565231323</t>
@@ -1040,58 +1043,58 @@
     <t xml:space="preserve">11.3956003189087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5050935745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4040260314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5556268692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6819639205933</t>
+    <t xml:space="preserve">11.5050926208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4040250778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.555627822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6819648742676</t>
   </si>
   <si>
     <t xml:space="preserve">11.7493448257446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9177942276001</t>
+    <t xml:space="preserve">11.9177932739258</t>
   </si>
   <si>
     <t xml:space="preserve">11.8841037750244</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9430618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0525541305542</t>
+    <t xml:space="preserve">11.943060874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0525550842285</t>
   </si>
   <si>
     <t xml:space="preserve">12.0946664810181</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1536235809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0357084274292</t>
+    <t xml:space="preserve">12.1536226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0357093811035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0778207778931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0441312789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1788902282715</t>
+    <t xml:space="preserve">12.0441303253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1788892745972</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3136501312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3220729827881</t>
+    <t xml:space="preserve">12.3136510848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3220720291138</t>
   </si>
   <si>
     <t xml:space="preserve">12.3726072311401</t>
@@ -1103,7 +1106,7 @@
     <t xml:space="preserve">12.2883834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2968063354492</t>
+    <t xml:space="preserve">12.2968044281006</t>
   </si>
   <si>
     <t xml:space="preserve">11.7914562225342</t>
@@ -1115,7 +1118,7 @@
     <t xml:space="preserve">11.816722869873</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0104417800903</t>
+    <t xml:space="preserve">12.010440826416</t>
   </si>
   <si>
     <t xml:space="preserve">12.0020189285278</t>
@@ -1124,58 +1127,58 @@
     <t xml:space="preserve">11.9683294296265</t>
   </si>
   <si>
-    <t xml:space="preserve">11.926215171814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3113775253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8144521713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6965351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8986740112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8228740692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0165901184082</t>
+    <t xml:space="preserve">11.9262170791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.311375617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8144512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6965360641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8986759185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8228731155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0165910720825</t>
   </si>
   <si>
     <t xml:space="preserve">10.940788269043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7723369598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7976045608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7302265167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7218036651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6628465652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6123123168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8060293197632</t>
+    <t xml:space="preserve">10.7723379135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7976055145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7302274703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7218027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6628456115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6123113632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8060283660889</t>
   </si>
   <si>
     <t xml:space="preserve">10.6881141662598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8312959671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6712684631348</t>
+    <t xml:space="preserve">10.8312950134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6712675094604</t>
   </si>
   <si>
     <t xml:space="preserve">10.4691286087036</t>
@@ -1184,19 +1187,19 @@
     <t xml:space="preserve">10.4859733581543</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0923910140991</t>
+    <t xml:space="preserve">11.0923919677734</t>
   </si>
   <si>
     <t xml:space="preserve">11.1597719192505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.134503364563</t>
+    <t xml:space="preserve">11.1345043182373</t>
   </si>
   <si>
     <t xml:space="preserve">11.1429271697998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187299728394</t>
+    <t xml:space="preserve">11.218729019165</t>
   </si>
   <si>
     <t xml:space="preserve">11.4545583724976</t>
@@ -1205,13 +1208,13 @@
     <t xml:space="preserve">11.3450660705566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4270162582397</t>
+    <t xml:space="preserve">10.4270172119141</t>
   </si>
   <si>
     <t xml:space="preserve">10.3175258636475</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2417230606079</t>
+    <t xml:space="preserve">10.2417221069336</t>
   </si>
   <si>
     <t xml:space="preserve">10.2838344573975</t>
@@ -1220,22 +1223,22 @@
     <t xml:space="preserve">10.1911869049072</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1574964523315</t>
+    <t xml:space="preserve">10.1574974060059</t>
   </si>
   <si>
     <t xml:space="preserve">10.2248783111572</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1659202575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1069631576538</t>
+    <t xml:space="preserve">10.165919303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1069641113281</t>
   </si>
   <si>
     <t xml:space="preserve">10.0985403060913</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93009090423584</t>
+    <t xml:space="preserve">9.93008995056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.98904895782471</t>
@@ -1244,52 +1247,52 @@
     <t xml:space="preserve">10.0058927536011</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71953010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68583965301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48370265960693</t>
+    <t xml:space="preserve">9.7195291519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68583869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4837007522583</t>
   </si>
   <si>
     <t xml:space="preserve">9.37420845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1153860092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3091020584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5954666137695</t>
+    <t xml:space="preserve">10.115385055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3091011047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5954656600952</t>
   </si>
   <si>
     <t xml:space="preserve">10.7133817672729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6038885116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.359637260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3006792068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4522838592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4017486572266</t>
+    <t xml:space="preserve">10.603889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3596382141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3006811141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4522848129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4017496109009</t>
   </si>
   <si>
     <t xml:space="preserve">10.5617771148682</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5449304580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3427925109863</t>
+    <t xml:space="preserve">10.5449314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.342791557312</t>
   </si>
   <si>
     <t xml:space="preserve">10.4438619613647</t>
@@ -1301,13 +1304,13 @@
     <t xml:space="preserve">10.4185934066772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4354391098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2585668563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2333002090454</t>
+    <t xml:space="preserve">10.4354381561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.25856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2333011627197</t>
   </si>
   <si>
     <t xml:space="preserve">10.2922582626343</t>
@@ -1319,31 +1322,31 @@
     <t xml:space="preserve">11.0418577194214</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5365085601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2754135131836</t>
+    <t xml:space="preserve">10.5365104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2754125595093</t>
   </si>
   <si>
     <t xml:space="preserve">10.2080326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0648508071899</t>
+    <t xml:space="preserve">10.0648517608643</t>
   </si>
   <si>
     <t xml:space="preserve">9.93851375579834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.050085067749</t>
+    <t xml:space="preserve">10.0500860214233</t>
   </si>
   <si>
     <t xml:space="preserve">10.3848028182983</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3075609207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7710151672363</t>
+    <t xml:space="preserve">10.307559967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.771014213562</t>
   </si>
   <si>
     <t xml:space="preserve">10.676607131958</t>
@@ -1352,13 +1355,13 @@
     <t xml:space="preserve">10.599365234375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2303190231323</t>
+    <t xml:space="preserve">10.230318069458</t>
   </si>
   <si>
     <t xml:space="preserve">10.470627784729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5049571990967</t>
+    <t xml:space="preserve">10.5049562454224</t>
   </si>
   <si>
     <t xml:space="preserve">10.6422777175903</t>
@@ -1376,10 +1379,10 @@
     <t xml:space="preserve">10.9340829849243</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6508588790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452659606934</t>
+    <t xml:space="preserve">10.6508598327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452669143677</t>
   </si>
   <si>
     <t xml:space="preserve">10.5307054519653</t>
@@ -1391,37 +1394,37 @@
     <t xml:space="preserve">10.3504724502563</t>
   </si>
   <si>
-    <t xml:space="preserve">10.144492149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1359119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92134857177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0758333206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0586700439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89560317993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94709587097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74111652374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76686477661133</t>
+    <t xml:space="preserve">10.1444931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.135910987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92134952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0758352279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.058669090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89560127258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.947096824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74111557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76686382293701</t>
   </si>
   <si>
     <t xml:space="preserve">9.85268878936768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87843608856201</t>
+    <t xml:space="preserve">9.87843704223633</t>
   </si>
   <si>
     <t xml:space="preserve">9.99001026153564</t>
@@ -1433,7 +1436,7 @@
     <t xml:space="preserve">10.2903957366943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.273229598999</t>
+    <t xml:space="preserve">10.2732315063477</t>
   </si>
   <si>
     <t xml:space="preserve">10.5135402679443</t>
@@ -1442,7 +1445,7 @@
     <t xml:space="preserve">10.48779296875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4362983703613</t>
+    <t xml:space="preserve">10.436297416687</t>
   </si>
   <si>
     <t xml:space="preserve">10.3333082199097</t>
@@ -1460,13 +1463,13 @@
     <t xml:space="preserve">10.0329217910767</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84410667419434</t>
+    <t xml:space="preserve">9.84410762786865</t>
   </si>
   <si>
     <t xml:space="preserve">10.04150390625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2389011383057</t>
+    <t xml:space="preserve">10.23890209198</t>
   </si>
   <si>
     <t xml:space="preserve">9.78402996063232</t>
@@ -1481,19 +1484,19 @@
     <t xml:space="preserve">9.68103981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56088447570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59521389007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.689621925354</t>
+    <t xml:space="preserve">9.56088542938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68962287902832</t>
   </si>
   <si>
     <t xml:space="preserve">9.47505950927734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.483642578125</t>
+    <t xml:space="preserve">9.48364162445068</t>
   </si>
   <si>
     <t xml:space="preserve">9.62954521179199</t>
@@ -1502,10 +1505,10 @@
     <t xml:space="preserve">9.912766456604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88701915740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75828170776367</t>
+    <t xml:space="preserve">9.88701820373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75828266143799</t>
   </si>
   <si>
     <t xml:space="preserve">9.56946659088135</t>
@@ -1532,49 +1535,49 @@
     <t xml:space="preserve">10.2217359542847</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99859142303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96426105499268</t>
+    <t xml:space="preserve">9.99859237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96426010131836</t>
   </si>
   <si>
     <t xml:space="preserve">9.86985397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69820404052734</t>
+    <t xml:space="preserve">9.69820499420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.86127185821533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52655601501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21758460998535</t>
+    <t xml:space="preserve">9.52655506134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21758556365967</t>
   </si>
   <si>
     <t xml:space="preserve">9.23475074768066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69405555725098</t>
+    <t xml:space="preserve">8.69405460357666</t>
   </si>
   <si>
     <t xml:space="preserve">8.52669525146484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4408712387085</t>
+    <t xml:space="preserve">8.44087028503418</t>
   </si>
   <si>
     <t xml:space="preserve">8.12331962585449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43228912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52240371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41083145141602</t>
+    <t xml:space="preserve">8.43228816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5224027633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41083240509033</t>
   </si>
   <si>
     <t xml:space="preserve">8.29926013946533</t>
@@ -1595,22 +1598,22 @@
     <t xml:space="preserve">8.22630977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48378372192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39366722106934</t>
+    <t xml:space="preserve">8.48378467559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39366626739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.57819080352783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49236583709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44945430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23488998413086</t>
+    <t xml:space="preserve">8.49236679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44945335388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23489093780518</t>
   </si>
   <si>
     <t xml:space="preserve">8.11473655700684</t>
@@ -1631,19 +1634,19 @@
     <t xml:space="preserve">7.83151483535767</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0031623840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02891063690186</t>
+    <t xml:space="preserve">8.00316429138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02891159057617</t>
   </si>
   <si>
     <t xml:space="preserve">8.00745487213135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25205516815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28638553619385</t>
+    <t xml:space="preserve">8.25205612182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28638648986816</t>
   </si>
   <si>
     <t xml:space="preserve">8.61681175231934</t>
@@ -1652,13 +1655,13 @@
     <t xml:space="preserve">8.60822868347168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54815101623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75413036346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48807525634766</t>
+    <t xml:space="preserve">8.54815196990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75413131713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48807430267334</t>
   </si>
   <si>
     <t xml:space="preserve">8.462327003479</t>
@@ -1667,16 +1670,16 @@
     <t xml:space="preserve">8.161940574646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19197940826416</t>
+    <t xml:space="preserve">8.19197845458984</t>
   </si>
   <si>
     <t xml:space="preserve">7.98170852661133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0889892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33788299560547</t>
+    <t xml:space="preserve">8.08898830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33788108825684</t>
   </si>
   <si>
     <t xml:space="preserve">7.81435060501099</t>
@@ -1691,28 +1694,28 @@
     <t xml:space="preserve">7.81864070892334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86584568023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58691358566284</t>
+    <t xml:space="preserve">7.86584377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58691310882568</t>
   </si>
   <si>
     <t xml:space="preserve">7.634117603302</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6899037361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65986442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96454286575317</t>
+    <t xml:space="preserve">7.68990278244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65986633300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96454381942749</t>
   </si>
   <si>
     <t xml:space="preserve">7.93879556655884</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73696613311768</t>
+    <t xml:space="preserve">8.73696517944336</t>
   </si>
   <si>
     <t xml:space="preserve">8.82279109954834</t>
@@ -1730,13 +1733,13 @@
     <t xml:space="preserve">8.45374393463135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.367919921875</t>
+    <t xml:space="preserve">8.36791896820068</t>
   </si>
   <si>
     <t xml:space="preserve">8.496657371521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50094795227051</t>
+    <t xml:space="preserve">8.50094699859619</t>
   </si>
   <si>
     <t xml:space="preserve">8.46661853790283</t>
@@ -1763,25 +1766,25 @@
     <t xml:space="preserve">8.50524044036865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50953006744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24776363372803</t>
+    <t xml:space="preserve">8.50953102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24776458740234</t>
   </si>
   <si>
     <t xml:space="preserve">8.15335750579834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39795684814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58248233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77129459381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65972328186035</t>
+    <t xml:space="preserve">8.39795875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58248138427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77129554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65972423553467</t>
   </si>
   <si>
     <t xml:space="preserve">9.09743118286133</t>
@@ -1790,10 +1793,10 @@
     <t xml:space="preserve">8.96869373321533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02018642425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28624534606934</t>
+    <t xml:space="preserve">9.020188331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28624439239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.31199359893799</t>
@@ -1808,7 +1811,7 @@
     <t xml:space="preserve">9.32057476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94294548034668</t>
+    <t xml:space="preserve">8.942946434021</t>
   </si>
   <si>
     <t xml:space="preserve">8.81420803070068</t>
@@ -1817,7 +1820,7 @@
     <t xml:space="preserve">8.78846168518066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.797043800354</t>
+    <t xml:space="preserve">8.79704475402832</t>
   </si>
   <si>
     <t xml:space="preserve">8.74554920196533</t>
@@ -1826,22 +1829,22 @@
     <t xml:space="preserve">8.72838592529297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90861701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14034271240234</t>
+    <t xml:space="preserve">8.908616065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14034366607666</t>
   </si>
   <si>
     <t xml:space="preserve">9.4235668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.260498046875</t>
+    <t xml:space="preserve">9.26049900054932</t>
   </si>
   <si>
     <t xml:space="preserve">9.18325614929199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00302314758301</t>
+    <t xml:space="preserve">9.00302219390869</t>
   </si>
   <si>
     <t xml:space="preserve">8.96011161804199</t>
@@ -1853,25 +1856,25 @@
     <t xml:space="preserve">8.65114116668701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.685471534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67689037322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87428569793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51797199249268</t>
+    <t xml:space="preserve">8.68547058105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67688941955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87428665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51797103881836</t>
   </si>
   <si>
     <t xml:space="preserve">9.44073104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41498279571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64670944213867</t>
+    <t xml:space="preserve">9.41498184204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64670848846436</t>
   </si>
   <si>
     <t xml:space="preserve">10.06725025177</t>
@@ -1886,10 +1889,10 @@
     <t xml:space="preserve">9.80977630615234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62096118927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50938987731934</t>
+    <t xml:space="preserve">9.62096214294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50939083099365</t>
   </si>
   <si>
     <t xml:space="preserve">8.86570358276367</t>
@@ -1898,25 +1901,25 @@
     <t xml:space="preserve">8.95152950286865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83995628356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75851726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77167510986328</t>
+    <t xml:space="preserve">8.83995532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75851821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77167415618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.74097442626953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42080879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53483867645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57869911193848</t>
+    <t xml:space="preserve">8.42080783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53484058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57869815826416</t>
   </si>
   <si>
     <t xml:space="preserve">8.58747100830078</t>
@@ -1925,49 +1928,46 @@
     <t xml:space="preserve">8.47343730926514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55238342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42957878112793</t>
+    <t xml:space="preserve">8.55238246917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42957973480225</t>
   </si>
   <si>
     <t xml:space="preserve">8.18397235870361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37695026397705</t>
+    <t xml:space="preserve">8.37694931030273</t>
   </si>
   <si>
     <t xml:space="preserve">8.56992626190186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67957210540771</t>
+    <t xml:space="preserve">8.67957305908203</t>
   </si>
   <si>
     <t xml:space="preserve">8.66202926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8944787979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75413131713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72781848907471</t>
+    <t xml:space="preserve">8.89447975158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72781753540039</t>
   </si>
   <si>
     <t xml:space="preserve">8.72343063354492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93833637237549</t>
+    <t xml:space="preserve">8.9383373260498</t>
   </si>
   <si>
     <t xml:space="preserve">8.82430553436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0611400604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00851154327393</t>
+    <t xml:space="preserve">9.06113910675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00851058959961</t>
   </si>
   <si>
     <t xml:space="preserve">8.85062026977539</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">8.71465873718262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88570690155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11377048492432</t>
+    <t xml:space="preserve">8.88570785522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11376953125</t>
   </si>
   <si>
     <t xml:space="preserve">9.0523681640625</t>
@@ -1994,10 +1994,10 @@
     <t xml:space="preserve">9.23657417297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92956447601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8067626953125</t>
+    <t xml:space="preserve">8.92956352233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80676174163818</t>
   </si>
   <si>
     <t xml:space="preserve">8.78921890258789</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">8.62255668640137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9207935333252</t>
+    <t xml:space="preserve">8.92079448699951</t>
   </si>
   <si>
     <t xml:space="preserve">9.07868385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0172815322876</t>
+    <t xml:space="preserve">9.01728248596191</t>
   </si>
   <si>
     <t xml:space="preserve">8.17958736419678</t>
@@ -2039,16 +2039,16 @@
     <t xml:space="preserve">7.77170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61819982528687</t>
+    <t xml:space="preserve">7.61819887161255</t>
   </si>
   <si>
     <t xml:space="preserve">7.64890050888062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63135766983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38574981689453</t>
+    <t xml:space="preserve">7.63135719299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38575029373169</t>
   </si>
   <si>
     <t xml:space="preserve">7.29803371429443</t>
@@ -2063,37 +2063,37 @@
     <t xml:space="preserve">7.20593118667603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28048992156982</t>
+    <t xml:space="preserve">7.28049039840698</t>
   </si>
   <si>
     <t xml:space="preserve">7.27171802520752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51293897628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39890813827515</t>
+    <t xml:space="preserve">7.512939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3989086151123</t>
   </si>
   <si>
     <t xml:space="preserve">7.26733255386353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19277334213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44276666641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45153713226318</t>
+    <t xml:space="preserve">7.19277381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4427661895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4515380859375</t>
   </si>
   <si>
     <t xml:space="preserve">7.32873439788818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53048324584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79363441467285</t>
+    <t xml:space="preserve">7.53048276901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79363346099854</t>
   </si>
   <si>
     <t xml:space="preserve">7.98661041259766</t>
@@ -2108,10 +2108,10 @@
     <t xml:space="preserve">8.28923225402832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35063457489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21905994415283</t>
+    <t xml:space="preserve">8.35063362121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21905899047852</t>
   </si>
   <si>
     <t xml:space="preserve">8.19274425506592</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">7.60942840576172</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74100303649902</t>
+    <t xml:space="preserve">7.74100255966187</t>
   </si>
   <si>
     <t xml:space="preserve">7.83310556411743</t>
@@ -2144,25 +2144,25 @@
     <t xml:space="preserve">7.50855445861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4032940864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45592451095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44715118408203</t>
+    <t xml:space="preserve">7.40329456329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45592355728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44715213775635</t>
   </si>
   <si>
     <t xml:space="preserve">7.31557750701904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47346687316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85064935684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85942029953003</t>
+    <t xml:space="preserve">7.4734673500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85064840316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85941934585571</t>
   </si>
   <si>
     <t xml:space="preserve">8.0085391998291</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">7.91643619537354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18835830688477</t>
+    <t xml:space="preserve">8.18835926055908</t>
   </si>
   <si>
     <t xml:space="preserve">8.25414657592773</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">8.29361915588379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36379241943359</t>
+    <t xml:space="preserve">8.36379146575928</t>
   </si>
   <si>
     <t xml:space="preserve">8.65325832366943</t>
@@ -2195,19 +2195,19 @@
     <t xml:space="preserve">8.37256336212158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43835258483887</t>
+    <t xml:space="preserve">8.43835163116455</t>
   </si>
   <si>
     <t xml:space="preserve">8.9646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1225414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14885711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37692070007324</t>
+    <t xml:space="preserve">9.12254333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14885807037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37691974639893</t>
   </si>
   <si>
     <t xml:space="preserve">9.56112575531006</t>
@@ -2219,34 +2219,34 @@
     <t xml:space="preserve">9.70147228240967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47340869903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35060405731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49095153808594</t>
+    <t xml:space="preserve">9.47341060638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35060501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49095058441162</t>
   </si>
   <si>
     <t xml:space="preserve">9.24534511566162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42077827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31552028656006</t>
+    <t xml:space="preserve">9.42077922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31551933288574</t>
   </si>
   <si>
     <t xml:space="preserve">9.48218154907227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64884185791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72778797149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80673217773438</t>
+    <t xml:space="preserve">9.64884281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72778701782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80673313140869</t>
   </si>
   <si>
     <t xml:space="preserve">9.77164745330811</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">9.85936260223389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.815505027771</t>
+    <t xml:space="preserve">9.81550407409668</t>
   </si>
   <si>
     <t xml:space="preserve">9.86813449859619</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">9.9997091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8769063949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84181880950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89445018768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9821662902832</t>
+    <t xml:space="preserve">9.87690734863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84181976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89444923400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98216533660889</t>
   </si>
   <si>
     <t xml:space="preserve">10.0698823928833</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">9.96462249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67515659332275</t>
+    <t xml:space="preserve">9.67515850067139</t>
   </si>
   <si>
     <t xml:space="preserve">9.71901702880859</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">9.79796123504639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29797554016113</t>
+    <t xml:space="preserve">9.29797649383545</t>
   </si>
   <si>
     <t xml:space="preserve">9.52603912353516</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">9.71024417877197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68392944335938</t>
+    <t xml:space="preserve">9.68392848968506</t>
   </si>
   <si>
     <t xml:space="preserve">9.69270038604736</t>
@@ -2327,19 +2327,19 @@
     <t xml:space="preserve">9.21025848388672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33306312561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20148658752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02605533599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26288986206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13131427764893</t>
+    <t xml:space="preserve">9.33306217193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2014856338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02605438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26288890838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13131332397461</t>
   </si>
   <si>
     <t xml:space="preserve">9.0874547958374</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">9.42955017089844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21902942657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25411605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15763092041016</t>
+    <t xml:space="preserve">9.21903038024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25411701202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15762996673584</t>
   </si>
   <si>
     <t xml:space="preserve">9.09622764587402</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">8.39449310302734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.337477684021</t>
+    <t xml:space="preserve">8.33747673034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.34186267852783</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">7.49978256225586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60065603256226</t>
+    <t xml:space="preserve">7.60065698623657</t>
   </si>
   <si>
     <t xml:space="preserve">7.42960929870605</t>
@@ -2408,34 +2408,34 @@
     <t xml:space="preserve">6.38577938079834</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87702226638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9735107421875</t>
+    <t xml:space="preserve">5.87702178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97351026535034</t>
   </si>
   <si>
     <t xml:space="preserve">6.55244064331055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1138277053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72784519195557</t>
+    <t xml:space="preserve">7.11382818222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72784423828125</t>
   </si>
   <si>
     <t xml:space="preserve">6.82436323165894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02172565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4734959602356</t>
+    <t xml:space="preserve">7.02172517776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47349548339844</t>
   </si>
   <si>
     <t xml:space="preserve">6.31560516357422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83316373825073</t>
+    <t xml:space="preserve">5.83316421508789</t>
   </si>
   <si>
     <t xml:space="preserve">5.96035289764404</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">5.61387252807617</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18406009674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47352504730225</t>
+    <t xml:space="preserve">5.18406057357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4735255241394</t>
   </si>
   <si>
     <t xml:space="preserve">5.54369831085205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89895105361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82439231872559</t>
+    <t xml:space="preserve">5.89895153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82439279556274</t>
   </si>
   <si>
     <t xml:space="preserve">5.64895820617676</t>
@@ -2468,16 +2468,16 @@
     <t xml:space="preserve">5.69720315933228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92965316772461</t>
+    <t xml:space="preserve">5.92965269088745</t>
   </si>
   <si>
     <t xml:space="preserve">6.06122732162476</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0085973739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05684185028076</t>
+    <t xml:space="preserve">6.00859785079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0568413734436</t>
   </si>
   <si>
     <t xml:space="preserve">6.40332221984863</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">6.59191370010376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83752059936523</t>
+    <t xml:space="preserve">6.83752107620239</t>
   </si>
   <si>
     <t xml:space="preserve">6.69717311859131</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">6.86822175979614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81120538711548</t>
+    <t xml:space="preserve">6.81120586395264</t>
   </si>
   <si>
     <t xml:space="preserve">6.72348928451538</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">6.48665332794189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4822678565979</t>
+    <t xml:space="preserve">6.48226737976074</t>
   </si>
   <si>
     <t xml:space="preserve">6.36385107040405</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">6.23227596282959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21911764144897</t>
+    <t xml:space="preserve">6.21911716461182</t>
   </si>
   <si>
     <t xml:space="preserve">6.39455032348633</t>
@@ -2537,37 +2537,37 @@
     <t xml:space="preserve">7.16207265853882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51732397079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37259340286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33312034606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4164514541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79801893234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68398809432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55679750442505</t>
+    <t xml:space="preserve">7.51732492446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37259244918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33311986923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41645097732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79801988601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68398714065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55679845809937</t>
   </si>
   <si>
     <t xml:space="preserve">7.10067129135132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35504961013794</t>
+    <t xml:space="preserve">7.35504913330078</t>
   </si>
   <si>
     <t xml:space="preserve">7.35066413879395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21031713485718</t>
+    <t xml:space="preserve">7.21031665802002</t>
   </si>
   <si>
     <t xml:space="preserve">7.23224544525146</t>
@@ -2582,10 +2582,10 @@
     <t xml:space="preserve">7.20154523849487</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24540328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21470260620117</t>
+    <t xml:space="preserve">7.24540281295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21470308303833</t>
   </si>
   <si>
     <t xml:space="preserve">7.17084407806396</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">7.40767908096313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25856065750122</t>
+    <t xml:space="preserve">7.25856113433838</t>
   </si>
   <si>
     <t xml:space="preserve">7.36820650100708</t>
@@ -2603,16 +2603,16 @@
     <t xml:space="preserve">7.32434940338135</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1489143371582</t>
+    <t xml:space="preserve">7.14891481399536</t>
   </si>
   <si>
     <t xml:space="preserve">7.24978923797607</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43838024139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16645765304565</t>
+    <t xml:space="preserve">7.43837976455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16645812988281</t>
   </si>
   <si>
     <t xml:space="preserve">6.70156002044678</t>
@@ -2624,22 +2624,22 @@
     <t xml:space="preserve">6.69278764724731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75419044494629</t>
+    <t xml:space="preserve">6.75418996810913</t>
   </si>
   <si>
     <t xml:space="preserve">6.68401670455933</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71033191680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83313465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06119823455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1401424407959</t>
+    <t xml:space="preserve">6.71033143997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83313512802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06119775772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14014291763306</t>
   </si>
   <si>
     <t xml:space="preserve">7.05681276321411</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">7.04804134368896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00856828689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94716644287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0743556022644</t>
+    <t xml:space="preserve">7.00856781005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94716691970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07435607910156</t>
   </si>
   <si>
     <t xml:space="preserve">7.0875129699707</t>
@@ -2663,25 +2663,25 @@
     <t xml:space="preserve">7.09628486633301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01734018325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35943555831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29364824295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49100971221924</t>
+    <t xml:space="preserve">7.0173397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35943508148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29364776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49101066589355</t>
   </si>
   <si>
     <t xml:space="preserve">7.60504245758057</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9734525680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57434177398682</t>
+    <t xml:space="preserve">7.97345352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57434034347534</t>
   </si>
   <si>
     <t xml:space="preserve">7.41206502914429</t>
@@ -2699,10 +2699,10 @@
     <t xml:space="preserve">7.06997013092041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31119155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48223924636841</t>
+    <t xml:space="preserve">7.31119060516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48223876953125</t>
   </si>
   <si>
     <t xml:space="preserve">7.86380624771118</t>
@@ -2711,22 +2711,22 @@
     <t xml:space="preserve">7.92082262039185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99976587295532</t>
+    <t xml:space="preserve">7.99976682662964</t>
   </si>
   <si>
     <t xml:space="preserve">7.73661756515503</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68837261199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61381483078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62697124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57872724533081</t>
+    <t xml:space="preserve">7.68837356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61381435394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62697172164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57872772216797</t>
   </si>
   <si>
     <t xml:space="preserve">7.77609014511108</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">7.80240535736084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96906661987305</t>
+    <t xml:space="preserve">7.96906566619873</t>
   </si>
   <si>
     <t xml:space="preserve">7.99099588394165</t>
@@ -2747,25 +2747,25 @@
     <t xml:space="preserve">8.54799747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56995582580566</t>
+    <t xml:space="preserve">7.56995534896851</t>
   </si>
   <si>
     <t xml:space="preserve">7.82433366775513</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66644382476807</t>
+    <t xml:space="preserve">7.66644477844238</t>
   </si>
   <si>
     <t xml:space="preserve">7.71907424926758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78486156463623</t>
+    <t xml:space="preserve">7.78486251831055</t>
   </si>
   <si>
     <t xml:space="preserve">7.86819314956665</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22780323028564</t>
+    <t xml:space="preserve">9.22780227661133</t>
   </si>
   <si>
     <t xml:space="preserve">9.17517280578613</t>
@@ -2780,19 +2780,19 @@
     <t xml:space="preserve">9.58744144439697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40323543548584</t>
+    <t xml:space="preserve">9.40323448181152</t>
   </si>
   <si>
     <t xml:space="preserve">9.36814975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35937786102295</t>
+    <t xml:space="preserve">9.35937595367432</t>
   </si>
   <si>
     <t xml:space="preserve">9.53481101989746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46463871002197</t>
+    <t xml:space="preserve">9.46463775634766</t>
   </si>
   <si>
     <t xml:space="preserve">9.50849628448486</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">9.41200733184814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38569164276123</t>
+    <t xml:space="preserve">9.38569259643555</t>
   </si>
   <si>
     <t xml:space="preserve">9.61375713348389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49972343444824</t>
+    <t xml:space="preserve">9.49972438812256</t>
   </si>
   <si>
     <t xml:space="preserve">9.03482532501221</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">10.0961980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1225118637085</t>
+    <t xml:space="preserve">10.1225128173828</t>
   </si>
   <si>
     <t xml:space="preserve">9.938307762146</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">9.45586490631104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51726722717285</t>
+    <t xml:space="preserve">9.51726818084717</t>
   </si>
   <si>
     <t xml:space="preserve">9.44709491729736</t>
@@ -2852,13 +2852,13 @@
     <t xml:space="preserve">8.94710922241211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16639995574951</t>
+    <t xml:space="preserve">9.16640090942383</t>
   </si>
   <si>
     <t xml:space="preserve">9.28920364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27165985107422</t>
+    <t xml:space="preserve">9.27166080474854</t>
   </si>
   <si>
     <t xml:space="preserve">9.34183406829834</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">9.18394470214844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90324974060059</t>
+    <t xml:space="preserve">8.90324878692627</t>
   </si>
   <si>
     <t xml:space="preserve">9.06991100311279</t>
@@ -2885,10 +2885,10 @@
     <t xml:space="preserve">8.97342395782471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18857097625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19807243347168</t>
+    <t xml:space="preserve">9.18857192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19807147979736</t>
   </si>
   <si>
     <t xml:space="preserve">9.1890983581543</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">9.43138980865479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5749683380127</t>
+    <t xml:space="preserve">9.57496929168701</t>
   </si>
   <si>
     <t xml:space="preserve">9.72752285003662</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">9.98776054382324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79033851623535</t>
+    <t xml:space="preserve">9.79033946990967</t>
   </si>
   <si>
     <t xml:space="preserve">9.74547004699707</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">9.70060157775879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52112674713135</t>
+    <t xml:space="preserve">9.52112579345703</t>
   </si>
   <si>
     <t xml:space="preserve">9.51215362548828</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">9.53010082244873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63778591156006</t>
+    <t xml:space="preserve">9.63778495788574</t>
   </si>
   <si>
     <t xml:space="preserve">9.61086368560791</t>
@@ -2954,19 +2954,19 @@
     <t xml:space="preserve">9.58394241333008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60189056396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55702114105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54804706573486</t>
+    <t xml:space="preserve">9.60188961029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55702018737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54804801940918</t>
   </si>
   <si>
     <t xml:space="preserve">9.35960006713867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76341819763184</t>
+    <t xml:space="preserve">9.76341724395752</t>
   </si>
   <si>
     <t xml:space="preserve">9.64675903320312</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">9.29678249359131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33267784118652</t>
+    <t xml:space="preserve">9.33267879486084</t>
   </si>
   <si>
     <t xml:space="preserve">9.3865213394165</t>
@@ -2987,22 +2987,22 @@
     <t xml:space="preserve">9.77239227294922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88905048370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3915786743164</t>
+    <t xml:space="preserve">9.8890495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3915777206421</t>
   </si>
   <si>
     <t xml:space="preserve">10.5800266265869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.651816368103</t>
+    <t xml:space="preserve">10.6518154144287</t>
   </si>
   <si>
     <t xml:space="preserve">10.6877117156982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7415542602539</t>
+    <t xml:space="preserve">10.7415552139282</t>
   </si>
   <si>
     <t xml:space="preserve">10.8582124710083</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">10.9838447570801</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0556344985962</t>
+    <t xml:space="preserve">11.0556335449219</t>
   </si>
   <si>
     <t xml:space="preserve">11.1005029678345</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">11.1274242401123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0197401046753</t>
+    <t xml:space="preserve">11.019739151001</t>
   </si>
   <si>
     <t xml:space="preserve">10.9300022125244</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">11.0107669830322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9748706817627</t>
+    <t xml:space="preserve">10.9748697280884</t>
   </si>
   <si>
     <t xml:space="preserve">10.8761596679688</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">10.9120540618896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0466604232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9210271835327</t>
+    <t xml:space="preserve">11.0466613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.921028137207</t>
   </si>
   <si>
     <t xml:space="preserve">10.8941078186035</t>
@@ -3062,19 +3062,19 @@
     <t xml:space="preserve">10.9030799865723</t>
   </si>
   <si>
-    <t xml:space="preserve">10.804370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7595024108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7864227294922</t>
+    <t xml:space="preserve">10.8043699264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7595014572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7864236831665</t>
   </si>
   <si>
     <t xml:space="preserve">10.8402643203735</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4274740219116</t>
+    <t xml:space="preserve">10.4274730682373</t>
   </si>
   <si>
     <t xml:space="preserve">10.2569723129272</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">9.96083927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1223659515381</t>
+    <t xml:space="preserve">10.1223669052124</t>
   </si>
   <si>
     <t xml:space="preserve">10.1313400268555</t>
@@ -3104,10 +3104,10 @@
     <t xml:space="preserve">9.80828666687012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56599521636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47625827789307</t>
+    <t xml:space="preserve">9.56599426269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47625732421875</t>
   </si>
   <si>
     <t xml:space="preserve">9.67368030548096</t>
@@ -3116,10 +3116,10 @@
     <t xml:space="preserve">9.70957469940186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75444316864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84418106079102</t>
+    <t xml:space="preserve">9.75444412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8441801071167</t>
   </si>
   <si>
     <t xml:space="preserve">9.85315418243408</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">9.86212730407715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0236558914185</t>
+    <t xml:space="preserve">10.0236549377441</t>
   </si>
   <si>
     <t xml:space="preserve">9.96981239318848</t>
@@ -3140,37 +3140,37 @@
     <t xml:space="preserve">10.1672344207764</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1492881774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2031297683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1851835250854</t>
+    <t xml:space="preserve">10.1492872238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2031307220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1851825714111</t>
   </si>
   <si>
     <t xml:space="preserve">10.2838935852051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3377361297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4454212188721</t>
+    <t xml:space="preserve">10.3377370834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4454221725464</t>
   </si>
   <si>
     <t xml:space="preserve">10.5172100067139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3467102050781</t>
+    <t xml:space="preserve">10.3467092514038</t>
   </si>
   <si>
     <t xml:space="preserve">10.3018407821655</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4184989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.436448097229</t>
+    <t xml:space="preserve">10.4184999465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4364471435547</t>
   </si>
   <si>
     <t xml:space="preserve">10.7774486541748</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">10.8492383956909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6966857910156</t>
+    <t xml:space="preserve">10.6966848373413</t>
   </si>
   <si>
     <t xml:space="preserve">10.7684755325317</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">11.1453723907471</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9658966064453</t>
+    <t xml:space="preserve">10.9658975601196</t>
   </si>
   <si>
     <t xml:space="preserve">10.9569225311279</t>
@@ -3239,16 +3239,16 @@
     <t xml:space="preserve">11.8004541397095</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0068502426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6568737030029</t>
+    <t xml:space="preserve">12.0068492889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6568746566772</t>
   </si>
   <si>
     <t xml:space="preserve">11.8453226089478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2171611785889</t>
+    <t xml:space="preserve">11.2171602249146</t>
   </si>
   <si>
     <t xml:space="preserve">11.2081871032715</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">11.3248453140259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2620306015015</t>
+    <t xml:space="preserve">11.2620296478271</t>
   </si>
   <si>
     <t xml:space="preserve">11.1363983154297</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">10.5351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3736305236816</t>
+    <t xml:space="preserve">10.373631477356</t>
   </si>
   <si>
     <t xml:space="preserve">10.5441312789917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7056589126587</t>
+    <t xml:space="preserve">10.705659866333</t>
   </si>
   <si>
     <t xml:space="preserve">10.6159219741821</t>
@@ -3302,16 +3302,16 @@
     <t xml:space="preserve">9.44933700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81668853759766</t>
+    <t xml:space="preserve">8.81668949127197</t>
   </si>
   <si>
     <t xml:space="preserve">8.01354122161865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02251434326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15711975097656</t>
+    <t xml:space="preserve">8.0225133895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15712070465088</t>
   </si>
   <si>
     <t xml:space="preserve">8.4891471862793</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">8.20198822021484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34556865692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5385046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67759704589844</t>
+    <t xml:space="preserve">8.34556770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53850364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67759609222412</t>
   </si>
   <si>
     <t xml:space="preserve">9.09038829803467</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">8.96924209594727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01859855651855</t>
+    <t xml:space="preserve">9.01859760284424</t>
   </si>
   <si>
     <t xml:space="preserve">9.10833549499512</t>
@@ -3344,28 +3344,28 @@
     <t xml:space="preserve">9.18012428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13525581359863</t>
+    <t xml:space="preserve">9.13525676727295</t>
   </si>
   <si>
     <t xml:space="preserve">8.98270416259766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79874229431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90642738342285</t>
+    <t xml:space="preserve">8.79874134063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90642642974854</t>
   </si>
   <si>
     <t xml:space="preserve">9.34165191650391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25191497802734</t>
+    <t xml:space="preserve">9.25191593170166</t>
   </si>
   <si>
     <t xml:space="preserve">9.08141422271729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97373008728027</t>
+    <t xml:space="preserve">8.97372913360596</t>
   </si>
   <si>
     <t xml:space="preserve">9.03654479980469</t>
@@ -3374,10 +3374,10 @@
     <t xml:space="preserve">8.83014965057373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43979167938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26480484008789</t>
+    <t xml:space="preserve">8.43979263305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26480388641357</t>
   </si>
   <si>
     <t xml:space="preserve">8.36351585388184</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">8.57439994812012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45774078369141</t>
+    <t xml:space="preserve">8.45773983001709</t>
   </si>
   <si>
     <t xml:space="preserve">8.46671390533447</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">8.4936351776123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30069923400879</t>
+    <t xml:space="preserve">8.30070018768311</t>
   </si>
   <si>
     <t xml:space="preserve">8.18404102325439</t>
@@ -3431,10 +3431,10 @@
     <t xml:space="preserve">8.12571239471436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88399028778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65573310852051</t>
+    <t xml:space="preserve">8.88399124145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65573406219482</t>
   </si>
   <si>
     <t xml:space="preserve">9.6856861114502</t>
@@ -5823,6 +5823,9 @@
   </si>
   <si>
     <t xml:space="preserve">10.3999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.460000038147</t>
   </si>
 </sst>
 </file>
@@ -15643,7 +15646,7 @@
         <v>14.0055179595947</v>
       </c>
       <c r="G365" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -15669,7 +15672,7 @@
         <v>13.9455795288086</v>
       </c>
       <c r="G366" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -15695,7 +15698,7 @@
         <v>13.7557764053345</v>
       </c>
       <c r="G367" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -15721,7 +15724,7 @@
         <v>13.7158174514771</v>
       </c>
       <c r="G368" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -15747,7 +15750,7 @@
         <v>13.406138420105</v>
       </c>
       <c r="G369" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -15773,7 +15776,7 @@
         <v>13.2862615585327</v>
       </c>
       <c r="G370" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -15799,7 +15802,7 @@
         <v>13.2762718200684</v>
       </c>
       <c r="G371" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -15825,7 +15828,7 @@
         <v>13.0864677429199</v>
       </c>
       <c r="G372" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -15851,7 +15854,7 @@
         <v>12.996561050415</v>
       </c>
       <c r="G373" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -15877,7 +15880,7 @@
         <v>13.3262195587158</v>
       </c>
       <c r="G374" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -15903,7 +15906,7 @@
         <v>13.5459928512573</v>
       </c>
       <c r="G375" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -15929,7 +15932,7 @@
         <v>13.3162307739258</v>
       </c>
       <c r="G376" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15955,7 +15958,7 @@
         <v>13.386157989502</v>
       </c>
       <c r="G377" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -15981,7 +15984,7 @@
         <v>13.2463026046753</v>
       </c>
       <c r="G378" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -16007,7 +16010,7 @@
         <v>12.9566020965576</v>
       </c>
       <c r="G379" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -16033,7 +16036,7 @@
         <v>13.0764780044556</v>
       </c>
       <c r="G380" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -16059,7 +16062,7 @@
         <v>12.7667989730835</v>
       </c>
       <c r="G381" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -16085,7 +16088,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G382" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -16111,7 +16114,7 @@
         <v>12.547025680542</v>
       </c>
       <c r="G383" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -16137,7 +16140,7 @@
         <v>12.7967681884766</v>
       </c>
       <c r="G384" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -16163,7 +16166,7 @@
         <v>12.7368297576904</v>
       </c>
       <c r="G385" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -16189,7 +16192,7 @@
         <v>12.6369333267212</v>
       </c>
       <c r="G386" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -16215,7 +16218,7 @@
         <v>12.7568092346191</v>
       </c>
       <c r="G387" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -16241,7 +16244,7 @@
         <v>13.3262195587158</v>
       </c>
       <c r="G388" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -16267,7 +16270,7 @@
         <v>13.5559825897217</v>
       </c>
       <c r="G389" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -16293,7 +16296,7 @@
         <v>13.6658687591553</v>
       </c>
       <c r="G390" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -16319,7 +16322,7 @@
         <v>13.3961477279663</v>
       </c>
       <c r="G391" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -16345,7 +16348,7 @@
         <v>13.8057241439819</v>
       </c>
       <c r="G392" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -16371,7 +16374,7 @@
         <v>13.7557764053345</v>
       </c>
       <c r="G393" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -16397,7 +16400,7 @@
         <v>13.5459928512573</v>
       </c>
       <c r="G394" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -16423,7 +16426,7 @@
         <v>13.5959405899048</v>
       </c>
       <c r="G395" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -16449,7 +16452,7 @@
         <v>13.536003112793</v>
       </c>
       <c r="G396" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -16475,7 +16478,7 @@
         <v>13.4760646820068</v>
       </c>
       <c r="G397" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -16501,7 +16504,7 @@
         <v>13.5559825897217</v>
       </c>
       <c r="G398" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -16527,7 +16530,7 @@
         <v>13.2463026046753</v>
       </c>
       <c r="G399" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -16553,7 +16556,7 @@
         <v>13.4261169433594</v>
       </c>
       <c r="G400" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -16579,7 +16582,7 @@
         <v>13.2962512969971</v>
       </c>
       <c r="G401" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -16605,7 +16608,7 @@
         <v>13.2862615585327</v>
       </c>
       <c r="G402" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -16631,7 +16634,7 @@
         <v>13.2463026046753</v>
       </c>
       <c r="G403" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -16657,7 +16660,7 @@
         <v>13.0465087890625</v>
       </c>
       <c r="G404" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -16683,7 +16686,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G405" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -16709,7 +16712,7 @@
         <v>13.0365200042725</v>
       </c>
       <c r="G406" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -16735,7 +16738,7 @@
         <v>13.0564985275269</v>
       </c>
       <c r="G407" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -16761,7 +16764,7 @@
         <v>12.9166440963745</v>
       </c>
       <c r="G408" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -16787,7 +16790,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G409" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -16813,7 +16816,7 @@
         <v>12.966591835022</v>
       </c>
       <c r="G410" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -16839,7 +16842,7 @@
         <v>12.8966636657715</v>
       </c>
       <c r="G411" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -16865,7 +16868,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G412" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -16891,7 +16894,7 @@
         <v>12.9066543579102</v>
       </c>
       <c r="G413" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -16917,7 +16920,7 @@
         <v>12.6669015884399</v>
       </c>
       <c r="G414" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -16943,7 +16946,7 @@
         <v>12.7867784500122</v>
       </c>
       <c r="G415" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -16969,7 +16972,7 @@
         <v>12.8866748809814</v>
       </c>
       <c r="G416" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -16995,7 +16998,7 @@
         <v>12.7568092346191</v>
       </c>
       <c r="G417" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -17021,7 +17024,7 @@
         <v>12.7368297576904</v>
       </c>
       <c r="G418" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -17047,7 +17050,7 @@
         <v>12.696870803833</v>
       </c>
       <c r="G419" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -17073,7 +17076,7 @@
         <v>12.7667989730835</v>
       </c>
       <c r="G420" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -17099,7 +17102,7 @@
         <v>12.9466133117676</v>
       </c>
       <c r="G421" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -17125,7 +17128,7 @@
         <v>13.3561887741089</v>
       </c>
       <c r="G422" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -17151,7 +17154,7 @@
         <v>13.2263231277466</v>
       </c>
       <c r="G423" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -17177,7 +17180,7 @@
         <v>13.1464061737061</v>
       </c>
       <c r="G424" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -17203,7 +17206,7 @@
         <v>12.8966636657715</v>
       </c>
       <c r="G425" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -17229,7 +17232,7 @@
         <v>13.1064472198486</v>
       </c>
       <c r="G426" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -17255,7 +17258,7 @@
         <v>13.0864677429199</v>
       </c>
       <c r="G427" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -17281,7 +17284,7 @@
         <v>13.3461999893188</v>
       </c>
       <c r="G428" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -17307,7 +17310,7 @@
         <v>13.2862615585327</v>
       </c>
       <c r="G429" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -17333,7 +17336,7 @@
         <v>13.4361066818237</v>
       </c>
       <c r="G430" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -17359,7 +17362,7 @@
         <v>13.4960451126099</v>
       </c>
       <c r="G431" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -17385,7 +17388,7 @@
         <v>13.5160236358643</v>
       </c>
       <c r="G432" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -17411,7 +17414,7 @@
         <v>13.3961477279663</v>
       </c>
       <c r="G433" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -17437,7 +17440,7 @@
         <v>13.6458902359009</v>
       </c>
       <c r="G434" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -17463,7 +17466,7 @@
         <v>13.5160236358643</v>
       </c>
       <c r="G435" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -17489,7 +17492,7 @@
         <v>13.5260143280029</v>
       </c>
       <c r="G436" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -17515,7 +17518,7 @@
         <v>13.6658687591553</v>
       </c>
       <c r="G437" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -17541,7 +17544,7 @@
         <v>13.7058277130127</v>
       </c>
       <c r="G438" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -17567,7 +17570,7 @@
         <v>13.8556728363037</v>
       </c>
       <c r="G439" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -17619,7 +17622,7 @@
         <v>13.9355897903442</v>
       </c>
       <c r="G441" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -17645,7 +17648,7 @@
         <v>14.135383605957</v>
       </c>
       <c r="G442" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -17671,7 +17674,7 @@
         <v>14.135383605957</v>
       </c>
       <c r="G443" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -17697,7 +17700,7 @@
         <v>14.0954246520996</v>
       </c>
       <c r="G444" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -17723,7 +17726,7 @@
         <v>14.135383605957</v>
       </c>
       <c r="G445" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -17749,7 +17752,7 @@
         <v>14.1653528213501</v>
       </c>
       <c r="G446" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -17775,7 +17778,7 @@
         <v>14.2952184677124</v>
       </c>
       <c r="G447" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -17853,7 +17856,7 @@
         <v>14.3451671600342</v>
       </c>
       <c r="G450" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -17905,7 +17908,7 @@
         <v>14.4150943756104</v>
       </c>
       <c r="G452" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -17931,7 +17934,7 @@
         <v>14.2752389907837</v>
       </c>
       <c r="G453" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -17957,7 +17960,7 @@
         <v>14.3251867294312</v>
       </c>
       <c r="G454" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -17983,7 +17986,7 @@
         <v>14.285228729248</v>
       </c>
       <c r="G455" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -18009,7 +18012,7 @@
         <v>14.4450626373291</v>
       </c>
       <c r="G456" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -18035,7 +18038,7 @@
         <v>14.4350738525391</v>
       </c>
       <c r="G457" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -18061,7 +18064,7 @@
         <v>14.4450626373291</v>
       </c>
       <c r="G458" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -18087,7 +18090,7 @@
         <v>14.6048984527588</v>
       </c>
       <c r="G459" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -18113,7 +18116,7 @@
         <v>14.6148881912231</v>
       </c>
       <c r="G460" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -18139,7 +18142,7 @@
         <v>14.674825668335</v>
       </c>
       <c r="G461" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -18165,7 +18168,7 @@
         <v>14.4750318527222</v>
       </c>
       <c r="G462" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -18191,7 +18194,7 @@
         <v>14.5749292373657</v>
       </c>
       <c r="G463" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -18217,7 +18220,7 @@
         <v>14.5849189758301</v>
       </c>
       <c r="G464" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -18243,7 +18246,7 @@
         <v>13.9855375289917</v>
       </c>
       <c r="G465" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -18295,7 +18298,7 @@
         <v>13.9156112670898</v>
       </c>
       <c r="G467" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -18321,7 +18324,7 @@
         <v>13.9855375289917</v>
       </c>
       <c r="G468" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -18347,7 +18350,7 @@
         <v>14.0155067443848</v>
       </c>
       <c r="G469" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -18373,7 +18376,7 @@
         <v>14.1653528213501</v>
       </c>
       <c r="G470" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -18399,7 +18402,7 @@
         <v>14.2452697753906</v>
       </c>
       <c r="G471" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -18425,7 +18428,7 @@
         <v>14.2352800369263</v>
       </c>
       <c r="G472" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -18451,7 +18454,7 @@
         <v>14.1953220367432</v>
       </c>
       <c r="G473" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -18477,7 +18480,7 @@
         <v>14.1453733444214</v>
       </c>
       <c r="G474" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -18503,7 +18506,7 @@
         <v>14.0155067443848</v>
       </c>
       <c r="G475" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -18529,7 +18532,7 @@
         <v>13.6458902359009</v>
       </c>
       <c r="G476" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -18555,7 +18558,7 @@
         <v>13.416127204895</v>
       </c>
       <c r="G477" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -18581,7 +18584,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G478" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -18607,7 +18610,7 @@
         <v>12.7867784500122</v>
       </c>
       <c r="G479" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -18633,7 +18636,7 @@
         <v>12.8267374038696</v>
       </c>
       <c r="G480" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -18659,7 +18662,7 @@
         <v>12.6868810653687</v>
       </c>
       <c r="G481" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -18685,7 +18688,7 @@
         <v>12.9266328811646</v>
       </c>
       <c r="G482" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -18711,7 +18714,7 @@
         <v>12.7967681884766</v>
       </c>
       <c r="G483" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -18737,7 +18740,7 @@
         <v>12.7368297576904</v>
       </c>
       <c r="G484" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -18763,7 +18766,7 @@
         <v>13.0564985275269</v>
       </c>
       <c r="G485" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -18789,7 +18792,7 @@
         <v>12.9166440963745</v>
       </c>
       <c r="G486" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -18815,7 +18818,7 @@
         <v>13.0465087890625</v>
       </c>
       <c r="G487" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -18841,7 +18844,7 @@
         <v>12.8966636657715</v>
       </c>
       <c r="G488" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -18867,7 +18870,7 @@
         <v>12.8367261886597</v>
       </c>
       <c r="G489" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -18893,7 +18896,7 @@
         <v>13.0664892196655</v>
       </c>
       <c r="G490" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -18919,7 +18922,7 @@
         <v>13.0564985275269</v>
       </c>
       <c r="G491" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -18945,7 +18948,7 @@
         <v>12.9765815734863</v>
       </c>
       <c r="G492" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -18971,7 +18974,7 @@
         <v>12.7767877578735</v>
       </c>
       <c r="G493" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -18997,7 +19000,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G494" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -19023,7 +19026,7 @@
         <v>12.8067569732666</v>
       </c>
       <c r="G495" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -19049,7 +19052,7 @@
         <v>12.7268400192261</v>
       </c>
       <c r="G496" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -19075,7 +19078,7 @@
         <v>12.7168502807617</v>
       </c>
       <c r="G497" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -19101,7 +19104,7 @@
         <v>12.7268400192261</v>
       </c>
       <c r="G498" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -19127,7 +19130,7 @@
         <v>12.696870803833</v>
       </c>
       <c r="G499" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -19153,7 +19156,7 @@
         <v>12.6469230651855</v>
       </c>
       <c r="G500" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -19179,7 +19182,7 @@
         <v>12.6469230651855</v>
       </c>
       <c r="G501" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -19205,7 +19208,7 @@
         <v>12.6369333267212</v>
       </c>
       <c r="G502" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -19231,7 +19234,7 @@
         <v>12.5869846343994</v>
       </c>
       <c r="G503" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -19257,7 +19260,7 @@
         <v>12.816746711731</v>
       </c>
       <c r="G504" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -19283,7 +19286,7 @@
         <v>12.6768922805786</v>
       </c>
       <c r="G505" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -19309,7 +19312,7 @@
         <v>12.7867784500122</v>
       </c>
       <c r="G506" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -19335,7 +19338,7 @@
         <v>12.8067569732666</v>
       </c>
       <c r="G507" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -19361,7 +19364,7 @@
         <v>12.7268400192261</v>
       </c>
       <c r="G508" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -19387,7 +19390,7 @@
         <v>12.846715927124</v>
       </c>
       <c r="G509" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -19413,7 +19416,7 @@
         <v>12.846715927124</v>
       </c>
       <c r="G510" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -19439,7 +19442,7 @@
         <v>12.6569118499756</v>
       </c>
       <c r="G511" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -19465,7 +19468,7 @@
         <v>12.4171600341797</v>
       </c>
       <c r="G512" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -19491,7 +19494,7 @@
         <v>12.4371385574341</v>
       </c>
       <c r="G513" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -19517,7 +19520,7 @@
         <v>12.8267374038696</v>
       </c>
       <c r="G514" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -19543,7 +19546,7 @@
         <v>13.1563959121704</v>
       </c>
       <c r="G515" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -19569,7 +19572,7 @@
         <v>13.2363128662109</v>
       </c>
       <c r="G516" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -19595,7 +19598,7 @@
         <v>13.2463026046753</v>
       </c>
       <c r="G517" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -19621,7 +19624,7 @@
         <v>13.2063436508179</v>
       </c>
       <c r="G518" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -19647,7 +19650,7 @@
         <v>13.2163343429565</v>
       </c>
       <c r="G519" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -19673,7 +19676,7 @@
         <v>13.3262195587158</v>
       </c>
       <c r="G520" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -19699,7 +19702,7 @@
         <v>13.3561887741089</v>
       </c>
       <c r="G521" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -19725,7 +19728,7 @@
         <v>13.3062410354614</v>
       </c>
       <c r="G522" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -19751,7 +19754,7 @@
         <v>13.2163343429565</v>
       </c>
       <c r="G523" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -19777,7 +19780,7 @@
         <v>13.2862615585327</v>
       </c>
       <c r="G524" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -19803,7 +19806,7 @@
         <v>13.536003112793</v>
       </c>
       <c r="G525" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -19829,7 +19832,7 @@
         <v>13.5859518051147</v>
       </c>
       <c r="G526" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -19855,7 +19858,7 @@
         <v>13.5459928512573</v>
       </c>
       <c r="G527" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -19881,7 +19884,7 @@
         <v>13.3262195587158</v>
       </c>
       <c r="G528" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -19907,7 +19910,7 @@
         <v>13.2762718200684</v>
       </c>
       <c r="G529" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -19933,7 +19936,7 @@
         <v>13.3062410354614</v>
       </c>
       <c r="G530" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -19959,7 +19962,7 @@
         <v>13.4560861587524</v>
       </c>
       <c r="G531" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -19985,7 +19988,7 @@
         <v>13.2163343429565</v>
       </c>
       <c r="G532" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -20011,7 +20014,7 @@
         <v>12.9865713119507</v>
       </c>
       <c r="G533" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -20037,7 +20040,7 @@
         <v>12.816746711731</v>
       </c>
       <c r="G534" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -20063,7 +20066,7 @@
         <v>12.6469230651855</v>
       </c>
       <c r="G535" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -20089,7 +20092,7 @@
         <v>12.696870803833</v>
       </c>
       <c r="G536" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -20115,7 +20118,7 @@
         <v>12.3672122955322</v>
       </c>
       <c r="G537" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -20141,7 +20144,7 @@
         <v>12.7368297576904</v>
       </c>
       <c r="G538" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -20167,7 +20170,7 @@
         <v>12.2373456954956</v>
       </c>
       <c r="G539" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -20193,7 +20196,7 @@
         <v>12.1474390029907</v>
       </c>
       <c r="G540" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -20219,7 +20222,7 @@
         <v>12.1973867416382</v>
       </c>
       <c r="G541" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -20245,7 +20248,7 @@
         <v>12.0875005722046</v>
       </c>
       <c r="G542" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -20271,7 +20274,7 @@
         <v>12.0475416183472</v>
       </c>
       <c r="G543" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -20297,7 +20300,7 @@
         <v>12.127459526062</v>
       </c>
       <c r="G544" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -20323,7 +20326,7 @@
         <v>12.0875005722046</v>
       </c>
       <c r="G545" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -20349,7 +20352,7 @@
         <v>12.0575323104858</v>
       </c>
       <c r="G546" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -20375,7 +20378,7 @@
         <v>11.9876041412354</v>
       </c>
       <c r="G547" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -20401,7 +20404,7 @@
         <v>11.9776153564453</v>
       </c>
       <c r="G548" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -20427,7 +20430,7 @@
         <v>11.7778205871582</v>
       </c>
       <c r="G549" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -20453,7 +20456,7 @@
         <v>11.8477487564087</v>
       </c>
       <c r="G550" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -20479,7 +20482,7 @@
         <v>11.8677282333374</v>
       </c>
       <c r="G551" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -20505,7 +20508,7 @@
         <v>11.5280790328979</v>
       </c>
       <c r="G552" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -20531,7 +20534,7 @@
         <v>11.4881210327148</v>
       </c>
       <c r="G553" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -20557,7 +20560,7 @@
         <v>11.2483692169189</v>
       </c>
       <c r="G554" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -20583,7 +20586,7 @@
         <v>11.1185026168823</v>
       </c>
       <c r="G555" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -20609,7 +20612,7 @@
         <v>11.9975938796997</v>
       </c>
       <c r="G556" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -20635,7 +20638,7 @@
         <v>12.2273559570312</v>
       </c>
       <c r="G557" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -20661,7 +20664,7 @@
         <v>12.5670051574707</v>
       </c>
       <c r="G558" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -20687,7 +20690,7 @@
         <v>12.8866748809814</v>
       </c>
       <c r="G559" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -20713,7 +20716,7 @@
         <v>12.8267374038696</v>
       </c>
       <c r="G560" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -20739,7 +20742,7 @@
         <v>12.7767877578735</v>
       </c>
       <c r="G561" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -20765,7 +20768,7 @@
         <v>12.8267374038696</v>
       </c>
       <c r="G562" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -20791,7 +20794,7 @@
         <v>12.6569118499756</v>
       </c>
       <c r="G563" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -20817,7 +20820,7 @@
         <v>12.9066543579102</v>
       </c>
       <c r="G564" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -20843,7 +20846,7 @@
         <v>12.846715927124</v>
       </c>
       <c r="G565" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -20869,7 +20872,7 @@
         <v>12.7068605422974</v>
       </c>
       <c r="G566" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -20895,7 +20898,7 @@
         <v>12.7967681884766</v>
       </c>
       <c r="G567" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -20921,7 +20924,7 @@
         <v>12.7268400192261</v>
       </c>
       <c r="G568" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -20947,7 +20950,7 @@
         <v>12.5769948959351</v>
       </c>
       <c r="G569" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -20973,7 +20976,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G570" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -20999,7 +21002,7 @@
         <v>12.2173671722412</v>
       </c>
       <c r="G571" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -21025,7 +21028,7 @@
         <v>12.397180557251</v>
       </c>
       <c r="G572" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -21051,7 +21054,7 @@
         <v>12.3372430801392</v>
       </c>
       <c r="G573" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -21077,7 +21080,7 @@
         <v>12.5270471572876</v>
       </c>
       <c r="G574" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -21103,7 +21106,7 @@
         <v>12.5070667266846</v>
       </c>
       <c r="G575" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -21129,7 +21132,7 @@
         <v>12.2673149108887</v>
       </c>
       <c r="G576" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -21155,7 +21158,7 @@
         <v>12.3871908187866</v>
       </c>
       <c r="G577" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -21181,7 +21184,7 @@
         <v>12.3472318649292</v>
       </c>
       <c r="G578" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -21207,7 +21210,7 @@
         <v>12.3572216033936</v>
       </c>
       <c r="G579" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -21233,7 +21236,7 @@
         <v>12.3772010803223</v>
       </c>
       <c r="G580" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -21259,7 +21262,7 @@
         <v>12.1973867416382</v>
       </c>
       <c r="G581" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -21285,7 +21288,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G582" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -21311,7 +21314,7 @@
         <v>12.2872943878174</v>
       </c>
       <c r="G583" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -21337,7 +21340,7 @@
         <v>12.2673149108887</v>
       </c>
       <c r="G584" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -21363,7 +21366,7 @@
         <v>12.397180557251</v>
       </c>
       <c r="G585" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -21389,7 +21392,7 @@
         <v>12.1674175262451</v>
       </c>
       <c r="G586" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -21415,7 +21418,7 @@
         <v>12.1374492645264</v>
       </c>
       <c r="G587" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -21441,7 +21444,7 @@
         <v>12.1674175262451</v>
       </c>
       <c r="G588" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -21467,7 +21470,7 @@
         <v>12.127459526062</v>
       </c>
       <c r="G589" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -21493,7 +21496,7 @@
         <v>12.2073774337769</v>
       </c>
       <c r="G590" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -21519,7 +21522,7 @@
         <v>12.0375528335571</v>
       </c>
       <c r="G591" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -21545,7 +21548,7 @@
         <v>12.2373456954956</v>
       </c>
       <c r="G592" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -21571,7 +21574,7 @@
         <v>12.127459526062</v>
       </c>
       <c r="G593" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -21597,7 +21600,7 @@
         <v>12.2373456954956</v>
       </c>
       <c r="G594" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -21623,7 +21626,7 @@
         <v>12.9266328811646</v>
       </c>
       <c r="G595" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -21649,7 +21652,7 @@
         <v>12.8067569732666</v>
       </c>
       <c r="G596" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -21675,7 +21678,7 @@
         <v>12.966591835022</v>
       </c>
       <c r="G597" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -21701,7 +21704,7 @@
         <v>13.0964584350586</v>
       </c>
       <c r="G598" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -21727,7 +21730,7 @@
         <v>12.6369333267212</v>
       </c>
       <c r="G599" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -21753,7 +21756,7 @@
         <v>12.4970779418945</v>
       </c>
       <c r="G600" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -21779,7 +21782,7 @@
         <v>12.2173671722412</v>
       </c>
       <c r="G601" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -21805,7 +21808,7 @@
         <v>12.1674175262451</v>
       </c>
       <c r="G602" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -21831,7 +21834,7 @@
         <v>12.1873979568481</v>
       </c>
       <c r="G603" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -21857,7 +21860,7 @@
         <v>12.1074800491333</v>
       </c>
       <c r="G604" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -21883,7 +21886,7 @@
         <v>11.9776153564453</v>
       </c>
       <c r="G605" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -21909,7 +21912,7 @@
         <v>11.9376564025879</v>
       </c>
       <c r="G606" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -21935,7 +21938,7 @@
         <v>11.7878112792969</v>
       </c>
       <c r="G607" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -21961,7 +21964,7 @@
         <v>11.6979036331177</v>
       </c>
       <c r="G608" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -21987,7 +21990,7 @@
         <v>12.0875005722046</v>
       </c>
       <c r="G609" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -22013,7 +22016,7 @@
         <v>11.9975938796997</v>
       </c>
       <c r="G610" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -22039,7 +22042,7 @@
         <v>12.5370359420776</v>
       </c>
       <c r="G611" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -22065,7 +22068,7 @@
         <v>12.427149772644</v>
       </c>
       <c r="G612" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -22091,7 +22094,7 @@
         <v>12.3372430801392</v>
       </c>
       <c r="G613" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -22117,7 +22120,7 @@
         <v>11.9076871871948</v>
       </c>
       <c r="G614" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -22143,7 +22146,7 @@
         <v>12.1873979568481</v>
       </c>
       <c r="G615" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -22169,7 +22172,7 @@
         <v>12.2273559570312</v>
       </c>
       <c r="G616" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -22195,7 +22198,7 @@
         <v>12.3871908187866</v>
       </c>
       <c r="G617" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -22221,7 +22224,7 @@
         <v>12.4371385574341</v>
       </c>
       <c r="G618" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -22247,7 +22250,7 @@
         <v>12.4071702957153</v>
       </c>
       <c r="G619" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -22273,7 +22276,7 @@
         <v>12.4671087265015</v>
       </c>
       <c r="G620" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -22299,7 +22302,7 @@
         <v>12.7268400192261</v>
       </c>
       <c r="G621" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -22325,7 +22328,7 @@
         <v>12.397180557251</v>
       </c>
       <c r="G622" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -22351,7 +22354,7 @@
         <v>12.427149772644</v>
       </c>
       <c r="G623" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -22377,7 +22380,7 @@
         <v>12.5070667266846</v>
       </c>
       <c r="G624" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -22403,7 +22406,7 @@
         <v>12.397180557251</v>
       </c>
       <c r="G625" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -22429,7 +22432,7 @@
         <v>12.5070667266846</v>
       </c>
       <c r="G626" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -22455,7 +22458,7 @@
         <v>12.2573251724243</v>
       </c>
       <c r="G627" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -22481,7 +22484,7 @@
         <v>12.2273559570312</v>
       </c>
       <c r="G628" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -22507,7 +22510,7 @@
         <v>12.0974912643433</v>
       </c>
       <c r="G629" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -22533,7 +22536,7 @@
         <v>12.0475416183472</v>
       </c>
       <c r="G630" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -22559,7 +22562,7 @@
         <v>11.8077898025513</v>
       </c>
       <c r="G631" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -22585,7 +22588,7 @@
         <v>11.7978010177612</v>
       </c>
       <c r="G632" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -22611,7 +22614,7 @@
         <v>11.548059463501</v>
       </c>
       <c r="G633" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -22637,7 +22640,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G634" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -22663,7 +22666,7 @@
         <v>11.7078943252563</v>
       </c>
       <c r="G635" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -22689,7 +22692,7 @@
         <v>11.5180902481079</v>
       </c>
       <c r="G636" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -22715,7 +22718,7 @@
         <v>11.5780277252197</v>
       </c>
       <c r="G637" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -22741,7 +22744,7 @@
         <v>11.3382759094238</v>
       </c>
       <c r="G638" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -22767,7 +22770,7 @@
         <v>11.3682451248169</v>
       </c>
       <c r="G639" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -22793,7 +22796,7 @@
         <v>11.3682451248169</v>
       </c>
       <c r="G640" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -22819,7 +22822,7 @@
         <v>11.4681406021118</v>
       </c>
       <c r="G641" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -22845,7 +22848,7 @@
         <v>11.4981098175049</v>
       </c>
       <c r="G642" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -22871,7 +22874,7 @@
         <v>11.6279764175415</v>
       </c>
       <c r="G643" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -22897,7 +22900,7 @@
         <v>11.9376564025879</v>
       </c>
       <c r="G644" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -22923,7 +22926,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G645" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -22949,7 +22952,7 @@
         <v>11.9776153564453</v>
       </c>
       <c r="G646" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -22975,7 +22978,7 @@
         <v>11.9576349258423</v>
       </c>
       <c r="G647" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -23001,7 +23004,7 @@
         <v>11.9076871871948</v>
       </c>
       <c r="G648" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -23027,7 +23030,7 @@
         <v>12.2373456954956</v>
       </c>
       <c r="G649" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -23053,7 +23056,7 @@
         <v>12.2073774337769</v>
       </c>
       <c r="G650" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -23079,7 +23082,7 @@
         <v>12.2073774337769</v>
       </c>
       <c r="G651" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -23105,7 +23108,7 @@
         <v>12.1474390029907</v>
       </c>
       <c r="G652" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -23131,7 +23134,7 @@
         <v>12.0974912643433</v>
       </c>
       <c r="G653" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -23157,7 +23160,7 @@
         <v>12.2273559570312</v>
       </c>
       <c r="G654" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -23183,7 +23186,7 @@
         <v>12.0275630950928</v>
       </c>
       <c r="G655" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -23209,7 +23212,7 @@
         <v>11.7378625869751</v>
       </c>
       <c r="G656" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -23235,7 +23238,7 @@
         <v>11.7878112792969</v>
       </c>
       <c r="G657" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -23261,7 +23264,7 @@
         <v>11.6579446792603</v>
       </c>
       <c r="G658" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -23287,7 +23290,7 @@
         <v>11.7078943252563</v>
       </c>
       <c r="G659" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -23313,7 +23316,7 @@
         <v>11.6779251098633</v>
       </c>
       <c r="G660" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -23339,7 +23342,7 @@
         <v>11.4581518173218</v>
       </c>
       <c r="G661" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -23365,7 +23368,7 @@
         <v>11.6879138946533</v>
       </c>
       <c r="G662" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -23391,7 +23394,7 @@
         <v>11.7378625869751</v>
       </c>
       <c r="G663" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -23417,7 +23420,7 @@
         <v>11.9176769256592</v>
       </c>
       <c r="G664" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -23443,7 +23446,7 @@
         <v>11.8077898025513</v>
       </c>
       <c r="G665" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -23469,7 +23472,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G666" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -23495,7 +23498,7 @@
         <v>11.3882236480713</v>
       </c>
       <c r="G667" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -23521,7 +23524,7 @@
         <v>11.2983169555664</v>
       </c>
       <c r="G668" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -23547,7 +23550,7 @@
         <v>11.3782339096069</v>
       </c>
       <c r="G669" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -23573,7 +23576,7 @@
         <v>11.2683477401733</v>
       </c>
       <c r="G670" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -23599,7 +23602,7 @@
         <v>11.128493309021</v>
       </c>
       <c r="G671" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -23625,7 +23628,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G672" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -23651,7 +23654,7 @@
         <v>11.278338432312</v>
       </c>
       <c r="G673" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -23677,7 +23680,7 @@
         <v>11.0285959243774</v>
       </c>
       <c r="G674" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -23703,7 +23706,7 @@
         <v>11.0385856628418</v>
       </c>
       <c r="G675" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -23729,7 +23732,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G676" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -23755,7 +23758,7 @@
         <v>11.2084102630615</v>
       </c>
       <c r="G677" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -23781,7 +23784,7 @@
         <v>11.1684513092041</v>
       </c>
       <c r="G678" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -23807,7 +23810,7 @@
         <v>11.5380687713623</v>
       </c>
       <c r="G679" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -23833,7 +23836,7 @@
         <v>11.7978010177612</v>
       </c>
       <c r="G680" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -23859,7 +23862,7 @@
         <v>11.5080995559692</v>
       </c>
       <c r="G681" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -23885,7 +23888,7 @@
         <v>11.4981098175049</v>
       </c>
       <c r="G682" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -23911,7 +23914,7 @@
         <v>11.3582553863525</v>
       </c>
       <c r="G683" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23937,7 +23940,7 @@
         <v>11.138482093811</v>
       </c>
       <c r="G684" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -23963,7 +23966,7 @@
         <v>11.1484718322754</v>
       </c>
       <c r="G685" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -23989,7 +23992,7 @@
         <v>11.138482093811</v>
       </c>
       <c r="G686" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -24015,7 +24018,7 @@
         <v>11.3282861709595</v>
       </c>
       <c r="G687" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -24041,7 +24044,7 @@
         <v>11.1884307861328</v>
       </c>
       <c r="G688" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -24067,7 +24070,7 @@
         <v>11.278338432312</v>
       </c>
       <c r="G689" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -24093,7 +24096,7 @@
         <v>11.3083066940308</v>
       </c>
       <c r="G690" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -24119,7 +24122,7 @@
         <v>11.4381723403931</v>
       </c>
       <c r="G691" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -24145,7 +24148,7 @@
         <v>11.6279764175415</v>
       </c>
       <c r="G692" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -24171,7 +24174,7 @@
         <v>11.6879138946533</v>
       </c>
       <c r="G693" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -24197,7 +24200,7 @@
         <v>11.8577394485474</v>
       </c>
       <c r="G694" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -24223,7 +24226,7 @@
         <v>11.9376564025879</v>
       </c>
       <c r="G695" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -24249,7 +24252,7 @@
         <v>11.8976974487305</v>
       </c>
       <c r="G696" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -24275,7 +24278,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G697" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -24301,7 +24304,7 @@
         <v>11.6379661560059</v>
       </c>
       <c r="G698" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -24327,7 +24330,7 @@
         <v>11.6379661560059</v>
       </c>
       <c r="G699" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -24353,7 +24356,7 @@
         <v>11.5980072021484</v>
       </c>
       <c r="G700" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -24379,7 +24382,7 @@
         <v>11.2683477401733</v>
       </c>
       <c r="G701" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -24405,7 +24408,7 @@
         <v>11.4881210327148</v>
       </c>
       <c r="G702" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -24431,7 +24434,7 @@
         <v>11.2883272171021</v>
       </c>
       <c r="G703" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -24457,7 +24460,7 @@
         <v>11.4781312942505</v>
       </c>
       <c r="G704" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -24483,7 +24486,7 @@
         <v>11.0885343551636</v>
       </c>
       <c r="G705" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -24509,7 +24512,7 @@
         <v>11.1484718322754</v>
       </c>
       <c r="G706" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -24535,7 +24538,7 @@
         <v>10.7289056777954</v>
       </c>
       <c r="G707" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -24561,7 +24564,7 @@
         <v>10.7488851547241</v>
       </c>
       <c r="G708" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -24587,7 +24590,7 @@
         <v>10.1195363998413</v>
       </c>
       <c r="G709" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -24613,7 +24616,7 @@
         <v>9.92473697662354</v>
       </c>
       <c r="G710" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -24639,7 +24642,7 @@
         <v>9.8248405456543</v>
       </c>
       <c r="G711" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -24665,7 +24668,7 @@
         <v>9.45522308349609</v>
       </c>
       <c r="G712" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -24691,7 +24694,7 @@
         <v>9.81485080718994</v>
       </c>
       <c r="G713" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -24717,7 +24720,7 @@
         <v>9.9197416305542</v>
       </c>
       <c r="G714" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -24743,7 +24746,7 @@
         <v>9.78987693786621</v>
       </c>
       <c r="G715" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -24769,7 +24772,7 @@
         <v>9.66001129150391</v>
       </c>
       <c r="G716" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -24795,7 +24798,7 @@
         <v>9.50517082214355</v>
       </c>
       <c r="G717" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -24821,7 +24824,7 @@
         <v>9.58009433746338</v>
       </c>
       <c r="G718" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -24847,7 +24850,7 @@
         <v>9.41026878356934</v>
       </c>
       <c r="G719" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -24873,7 +24876,7 @@
         <v>9.72494411468506</v>
       </c>
       <c r="G720" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -24899,7 +24902,7 @@
         <v>9.57509899139404</v>
       </c>
       <c r="G721" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -24925,7 +24928,7 @@
         <v>9.87478923797607</v>
       </c>
       <c r="G722" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -24951,7 +24954,7 @@
         <v>9.8248405456543</v>
       </c>
       <c r="G723" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -24977,7 +24980,7 @@
         <v>9.7698974609375</v>
       </c>
       <c r="G724" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -25003,7 +25006,7 @@
         <v>9.98467540740967</v>
       </c>
       <c r="G725" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -25029,7 +25032,7 @@
         <v>10.1195363998413</v>
       </c>
       <c r="G726" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -25055,7 +25058,7 @@
         <v>9.88477897644043</v>
       </c>
       <c r="G727" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -25081,7 +25084,7 @@
         <v>9.83483028411865</v>
       </c>
       <c r="G728" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -25107,7 +25110,7 @@
         <v>9.5850887298584</v>
       </c>
       <c r="G729" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -25133,7 +25136,7 @@
         <v>9.44523334503174</v>
       </c>
       <c r="G730" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -25159,7 +25162,7 @@
         <v>9.33534717559814</v>
       </c>
       <c r="G731" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -25185,7 +25188,7 @@
         <v>9.07061958312988</v>
       </c>
       <c r="G732" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -25211,7 +25214,7 @@
         <v>8.99569797515869</v>
       </c>
       <c r="G733" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -25237,7 +25240,7 @@
         <v>9.04564571380615</v>
       </c>
       <c r="G734" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -25263,7 +25266,7 @@
         <v>9.11557388305664</v>
       </c>
       <c r="G735" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -25289,7 +25292,7 @@
         <v>9.31536674499512</v>
       </c>
       <c r="G736" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -25315,7 +25318,7 @@
         <v>9.34533596038818</v>
       </c>
       <c r="G737" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -25341,7 +25344,7 @@
         <v>9.32036209106445</v>
       </c>
       <c r="G738" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -25367,7 +25370,7 @@
         <v>9.60506820678711</v>
       </c>
       <c r="G739" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -25393,7 +25396,7 @@
         <v>9.64502716064453</v>
       </c>
       <c r="G740" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -25419,7 +25422,7 @@
         <v>9.7698974609375</v>
       </c>
       <c r="G741" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -25445,7 +25448,7 @@
         <v>10.0296287536621</v>
       </c>
       <c r="G742" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -25471,7 +25474,7 @@
         <v>10.0196390151978</v>
       </c>
       <c r="G743" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -25497,7 +25500,7 @@
         <v>9.92473697662354</v>
       </c>
       <c r="G744" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -25523,7 +25526,7 @@
         <v>9.94971084594727</v>
       </c>
       <c r="G745" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -25549,7 +25552,7 @@
         <v>9.83483028411865</v>
       </c>
       <c r="G746" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -25575,7 +25578,7 @@
         <v>10.1894636154175</v>
       </c>
       <c r="G747" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -25601,7 +25604,7 @@
         <v>9.87978363037109</v>
       </c>
       <c r="G748" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -25627,7 +25630,7 @@
         <v>9.84981536865234</v>
       </c>
       <c r="G749" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -25653,7 +25656,7 @@
         <v>9.50017642974854</v>
       </c>
       <c r="G750" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -25679,7 +25682,7 @@
         <v>9.53514003753662</v>
       </c>
       <c r="G751" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -25705,7 +25708,7 @@
         <v>9.29039287567139</v>
       </c>
       <c r="G752" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -25731,7 +25734,7 @@
         <v>9.41526412963867</v>
       </c>
       <c r="G753" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -25757,7 +25760,7 @@
         <v>9.70496463775635</v>
       </c>
       <c r="G754" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -25783,7 +25786,7 @@
         <v>9.66001129150391</v>
       </c>
       <c r="G755" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -25809,7 +25812,7 @@
         <v>9.44523334503174</v>
       </c>
       <c r="G756" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -25835,7 +25838,7 @@
         <v>9.09559535980225</v>
       </c>
       <c r="G757" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -25861,7 +25864,7 @@
         <v>8.96073436737061</v>
       </c>
       <c r="G758" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -25887,7 +25890,7 @@
         <v>9.31037330627441</v>
       </c>
       <c r="G759" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -25913,7 +25916,7 @@
         <v>9.10058879852295</v>
       </c>
       <c r="G760" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -25939,7 +25942,7 @@
         <v>9.15553283691406</v>
       </c>
       <c r="G761" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -25965,7 +25968,7 @@
         <v>8.83086776733398</v>
       </c>
       <c r="G762" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -25991,7 +25994,7 @@
         <v>8.8858118057251</v>
       </c>
       <c r="G763" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -26017,7 +26020,7 @@
         <v>8.95074367523193</v>
       </c>
       <c r="G764" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -26043,7 +26046,7 @@
         <v>8.91578102111816</v>
       </c>
       <c r="G765" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -26069,7 +26072,7 @@
         <v>9.27041435241699</v>
       </c>
       <c r="G766" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -26095,7 +26098,7 @@
         <v>9.24044513702393</v>
       </c>
       <c r="G767" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -26121,7 +26124,7 @@
         <v>9.5850887298584</v>
       </c>
       <c r="G768" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -26147,7 +26150,7 @@
         <v>10.1694841384888</v>
       </c>
       <c r="G769" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -26173,7 +26176,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G770" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -26199,7 +26202,7 @@
         <v>9.86979389190674</v>
       </c>
       <c r="G771" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -26225,7 +26228,7 @@
         <v>9.75990772247314</v>
       </c>
       <c r="G772" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -26251,7 +26254,7 @@
         <v>9.77988719940186</v>
       </c>
       <c r="G773" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -26277,7 +26280,7 @@
         <v>9.83982467651367</v>
       </c>
       <c r="G774" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -26303,7 +26306,7 @@
         <v>9.73992824554443</v>
       </c>
       <c r="G775" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -26329,7 +26332,7 @@
         <v>9.88977336883545</v>
       </c>
       <c r="G776" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -26355,7 +26358,7 @@
         <v>9.9197416305542</v>
       </c>
       <c r="G777" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -26381,7 +26384,7 @@
         <v>9.89476776123047</v>
       </c>
       <c r="G778" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -26407,7 +26410,7 @@
         <v>9.85480976104736</v>
       </c>
       <c r="G779" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -26433,7 +26436,7 @@
         <v>10.0096502304077</v>
       </c>
       <c r="G780" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -26459,7 +26462,7 @@
         <v>10.3093395233154</v>
       </c>
       <c r="G781" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -26485,7 +26488,7 @@
         <v>10.1195363998413</v>
       </c>
       <c r="G782" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -26511,7 +26514,7 @@
         <v>9.97468566894531</v>
       </c>
       <c r="G783" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -26537,7 +26540,7 @@
         <v>9.96969127655029</v>
       </c>
       <c r="G784" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -26563,7 +26566,7 @@
         <v>9.95970058441162</v>
       </c>
       <c r="G785" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -26589,7 +26592,7 @@
         <v>9.93972206115723</v>
       </c>
       <c r="G786" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -26615,7 +26618,7 @@
         <v>9.8997631072998</v>
       </c>
       <c r="G787" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -26641,7 +26644,7 @@
         <v>9.90475845336914</v>
       </c>
       <c r="G788" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -26667,7 +26670,7 @@
         <v>9.87478923797607</v>
       </c>
       <c r="G789" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -26693,7 +26696,7 @@
         <v>9.60007286071777</v>
       </c>
       <c r="G790" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -26719,7 +26722,7 @@
         <v>9.31037330627441</v>
       </c>
       <c r="G791" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -26745,7 +26748,7 @@
         <v>9.49018669128418</v>
       </c>
       <c r="G792" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -26771,7 +26774,7 @@
         <v>9.77489185333252</v>
       </c>
       <c r="G793" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -26797,7 +26800,7 @@
         <v>10.0196390151978</v>
       </c>
       <c r="G794" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -26823,7 +26826,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G795" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -26849,7 +26852,7 @@
         <v>10.2094430923462</v>
       </c>
       <c r="G796" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -26875,7 +26878,7 @@
         <v>10.0795774459839</v>
       </c>
       <c r="G797" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -26901,7 +26904,7 @@
         <v>10.0795774459839</v>
       </c>
       <c r="G798" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -26927,7 +26930,7 @@
         <v>10.5890502929688</v>
       </c>
       <c r="G799" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -26953,7 +26956,7 @@
         <v>10.4392051696777</v>
       </c>
       <c r="G800" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -26979,7 +26982,7 @@
         <v>10.4991426467896</v>
       </c>
       <c r="G801" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -27005,7 +27008,7 @@
         <v>10.8088226318359</v>
       </c>
       <c r="G802" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -27031,7 +27034,7 @@
         <v>10.838791847229</v>
       </c>
       <c r="G803" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -27057,7 +27060,7 @@
         <v>10.56907081604</v>
       </c>
       <c r="G804" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -27083,7 +27086,7 @@
         <v>10.6290092468262</v>
       </c>
       <c r="G805" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -27109,7 +27112,7 @@
         <v>10.8487815856934</v>
       </c>
       <c r="G806" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -27135,7 +27138,7 @@
         <v>10.4092359542847</v>
       </c>
       <c r="G807" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -27161,7 +27164,7 @@
         <v>10.2593908309937</v>
       </c>
       <c r="G808" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -27187,7 +27190,7 @@
         <v>10.2294216156006</v>
       </c>
       <c r="G809" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -27213,7 +27216,7 @@
         <v>10.2394123077393</v>
       </c>
       <c r="G810" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -27239,7 +27242,7 @@
         <v>10.1794738769531</v>
       </c>
       <c r="G811" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -27265,7 +27268,7 @@
         <v>10.2094430923462</v>
       </c>
       <c r="G812" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -27291,7 +27294,7 @@
         <v>10.1594953536987</v>
       </c>
       <c r="G813" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -27317,7 +27320,7 @@
         <v>10.3692779541016</v>
       </c>
       <c r="G814" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -27343,7 +27346,7 @@
         <v>10.6389989852905</v>
       </c>
       <c r="G815" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -27369,7 +27372,7 @@
         <v>10.9686584472656</v>
       </c>
       <c r="G816" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -27395,7 +27398,7 @@
         <v>10.7788543701172</v>
       </c>
       <c r="G817" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -27421,7 +27424,7 @@
         <v>10.688946723938</v>
       </c>
       <c r="G818" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -27447,7 +27450,7 @@
         <v>10.4791641235352</v>
       </c>
       <c r="G819" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -27473,7 +27476,7 @@
         <v>10.4292163848877</v>
       </c>
       <c r="G820" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -27499,7 +27502,7 @@
         <v>10.1994533538818</v>
       </c>
       <c r="G821" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -27525,7 +27528,7 @@
         <v>10.0695877075195</v>
       </c>
       <c r="G822" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -27551,7 +27554,7 @@
         <v>10.1095457077026</v>
       </c>
       <c r="G823" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -27577,7 +27580,7 @@
         <v>10.0995569229126</v>
       </c>
       <c r="G824" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -27603,7 +27606,7 @@
         <v>10.0296287536621</v>
       </c>
       <c r="G825" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -27629,7 +27632,7 @@
         <v>10.0995569229126</v>
       </c>
       <c r="G826" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -27655,7 +27658,7 @@
         <v>10.269380569458</v>
       </c>
       <c r="G827" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -27681,7 +27684,7 @@
         <v>10.3293190002441</v>
       </c>
       <c r="G828" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -27707,7 +27710,7 @@
         <v>11.0785436630249</v>
       </c>
       <c r="G829" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -27733,7 +27736,7 @@
         <v>11.0385856628418</v>
       </c>
       <c r="G830" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -27759,7 +27762,7 @@
         <v>11.138482093811</v>
       </c>
       <c r="G831" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -27785,7 +27788,7 @@
         <v>10.98863697052</v>
       </c>
       <c r="G832" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -27811,7 +27814,7 @@
         <v>10.958667755127</v>
       </c>
       <c r="G833" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -27837,7 +27840,7 @@
         <v>11.0385856628418</v>
       </c>
       <c r="G834" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -27863,7 +27866,7 @@
         <v>10.8487815856934</v>
       </c>
       <c r="G835" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -27889,7 +27892,7 @@
         <v>11.2283887863159</v>
       </c>
       <c r="G836" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -27915,7 +27918,7 @@
         <v>11.6379661560059</v>
       </c>
       <c r="G837" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -27941,7 +27944,7 @@
         <v>11.7178831100464</v>
       </c>
       <c r="G838" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -27967,7 +27970,7 @@
         <v>11.5680379867554</v>
       </c>
       <c r="G839" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -27993,7 +27996,7 @@
         <v>11.7878112792969</v>
       </c>
       <c r="G840" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -28019,7 +28022,7 @@
         <v>11.8677282333374</v>
       </c>
       <c r="G841" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -28045,7 +28048,7 @@
         <v>11.6579446792603</v>
       </c>
       <c r="G842" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -28071,7 +28074,7 @@
         <v>11.6379661560059</v>
       </c>
       <c r="G843" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -28097,7 +28100,7 @@
         <v>11.6979036331177</v>
       </c>
       <c r="G844" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -28123,7 +28126,7 @@
         <v>11.7278728485107</v>
       </c>
       <c r="G845" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -28149,7 +28152,7 @@
         <v>11.6879138946533</v>
       </c>
       <c r="G846" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -28175,7 +28178,7 @@
         <v>11.5380687713623</v>
       </c>
       <c r="G847" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -28201,7 +28204,7 @@
         <v>11.4181928634644</v>
       </c>
       <c r="G848" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -28227,7 +28230,7 @@
         <v>11.0885343551636</v>
       </c>
       <c r="G849" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -28253,7 +28256,7 @@
         <v>11.1984195709229</v>
       </c>
       <c r="G850" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -28279,7 +28282,7 @@
         <v>11.3782339096069</v>
       </c>
       <c r="G851" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -28305,7 +28308,7 @@
         <v>11.0685548782349</v>
       </c>
       <c r="G852" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -28331,7 +28334,7 @@
         <v>10.8487815856934</v>
       </c>
       <c r="G853" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -28357,7 +28360,7 @@
         <v>10.2593908309937</v>
       </c>
       <c r="G854" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -28383,7 +28386,7 @@
         <v>10.3193292617798</v>
       </c>
       <c r="G855" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -28409,7 +28412,7 @@
         <v>10.419225692749</v>
       </c>
       <c r="G856" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -28435,7 +28438,7 @@
         <v>10.2893600463867</v>
       </c>
       <c r="G857" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -28461,7 +28464,7 @@
         <v>10.1894636154175</v>
       </c>
       <c r="G858" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28487,7 +28490,7 @@
         <v>9.97468566894531</v>
       </c>
       <c r="G859" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -28513,7 +28516,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G860" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -28539,7 +28542,7 @@
         <v>9.9547061920166</v>
       </c>
       <c r="G861" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28565,7 +28568,7 @@
         <v>9.59008312225342</v>
       </c>
       <c r="G862" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -28591,7 +28594,7 @@
         <v>9.71994876861572</v>
       </c>
       <c r="G863" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28617,7 +28620,7 @@
         <v>9.7698974609375</v>
       </c>
       <c r="G864" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28643,7 +28646,7 @@
         <v>9.77988719940186</v>
       </c>
       <c r="G865" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28669,7 +28672,7 @@
         <v>9.65002059936523</v>
       </c>
       <c r="G866" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28695,7 +28698,7 @@
         <v>9.73992824554443</v>
       </c>
       <c r="G867" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28721,7 +28724,7 @@
         <v>9.60007286071777</v>
       </c>
       <c r="G868" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28747,7 +28750,7 @@
         <v>9.32036209106445</v>
       </c>
       <c r="G869" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28773,7 +28776,7 @@
         <v>9.54013538360596</v>
       </c>
       <c r="G870" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28799,7 +28802,7 @@
         <v>9.75990772247314</v>
       </c>
       <c r="G871" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28825,7 +28828,7 @@
         <v>9.88477897644043</v>
       </c>
       <c r="G872" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28851,7 +28854,7 @@
         <v>9.8647985458374</v>
       </c>
       <c r="G873" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -28877,7 +28880,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G874" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28903,7 +28906,7 @@
         <v>10.1295261383057</v>
       </c>
       <c r="G875" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28929,7 +28932,7 @@
         <v>9.96969127655029</v>
       </c>
       <c r="G876" t="s">
-        <v>645</v>
+        <v>548</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -29007,7 +29010,7 @@
         <v>9.8647985458374</v>
       </c>
       <c r="G879" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -29189,7 +29192,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G886" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -29215,7 +29218,7 @@
         <v>9.97468566894531</v>
       </c>
       <c r="G887" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -29527,7 +29530,7 @@
         <v>9.96969127655029</v>
       </c>
       <c r="G899" t="s">
-        <v>645</v>
+        <v>548</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29553,7 +29556,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G900" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29787,7 +29790,7 @@
         <v>9.73992824554443</v>
       </c>
       <c r="G909" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -30645,7 +30648,7 @@
         <v>9.65002059936523</v>
       </c>
       <c r="G942" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -38263,7 +38266,7 @@
         <v>9.54013538360596</v>
       </c>
       <c r="G1235" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -73215,7 +73218,7 @@
     </row>
     <row r="2580">
       <c r="A2580" s="1" t="n">
-        <v>46078.6910648148</v>
+        <v>46078.3333333333</v>
       </c>
       <c r="B2580" t="n">
         <v>216953</v>
@@ -73236,6 +73239,32 @@
         <v>1936</v>
       </c>
       <c r="H2580" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2581">
+      <c r="A2581" s="1" t="n">
+        <v>46079.691099537</v>
+      </c>
+      <c r="B2581" t="n">
+        <v>258182</v>
+      </c>
+      <c r="C2581" t="n">
+        <v>10.4700002670288</v>
+      </c>
+      <c r="D2581" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="E2581" t="n">
+        <v>10.4099998474121</v>
+      </c>
+      <c r="F2581" t="n">
+        <v>10.460000038147</v>
+      </c>
+      <c r="G2581" t="s">
+        <v>1937</v>
+      </c>
+      <c r="H2581" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16937828063965</t>
+    <t xml:space="preserve">7.16937780380249</t>
   </si>
   <si>
     <t xml:space="preserve">BRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13994932174683</t>
+    <t xml:space="preserve">7.13994979858398</t>
   </si>
   <si>
     <t xml:space="preserve">6.92740154266357</t>
@@ -53,13 +53,13 @@
     <t xml:space="preserve">6.52519702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5415472984314</t>
+    <t xml:space="preserve">6.54154634475708</t>
   </si>
   <si>
     <t xml:space="preserve">6.42873334884644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60040664672852</t>
+    <t xml:space="preserve">6.60040616989136</t>
   </si>
   <si>
     <t xml:space="preserve">6.78188800811768</t>
@@ -71,19 +71,19 @@
     <t xml:space="preserve">6.21291542053223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19820213317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2750449180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94641494750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20310735702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2488865852356</t>
+    <t xml:space="preserve">6.19820165634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27504539489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94641447067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20310688018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24888563156128</t>
   </si>
   <si>
     <t xml:space="preserve">6.30610942840576</t>
@@ -92,28 +92,28 @@
     <t xml:space="preserve">6.31918954849243</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38785886764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23090076446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16713714599609</t>
+    <t xml:space="preserve">6.38785934448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23090028762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16713762283325</t>
   </si>
   <si>
     <t xml:space="preserve">6.05922794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99219512939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86466550827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70443868637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35945796966553</t>
+    <t xml:space="preserve">5.99219369888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86466503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70443820953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35945844650269</t>
   </si>
   <si>
     <t xml:space="preserve">5.5164155960083</t>
@@ -131,52 +131,52 @@
     <t xml:space="preserve">6.03960847854614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97420930862427</t>
+    <t xml:space="preserve">5.97420978546143</t>
   </si>
   <si>
     <t xml:space="preserve">6.11972236633301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14097690582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10010194778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23744058609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11154747009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9758448600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07394361495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12953281402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21945571899414</t>
+    <t xml:space="preserve">6.14097738265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10010290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23744106292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11154699325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97584438323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07394313812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12953233718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21945667266846</t>
   </si>
   <si>
     <t xml:space="preserve">6.35188961029053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32409477233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04675579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08272409439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1170597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07945442199707</t>
+    <t xml:space="preserve">6.32409524917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04675531387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08272457122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11705875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07945489883423</t>
   </si>
   <si>
     <t xml:space="preserve">7.12032985687256</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">7.07127952575684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06637525558472</t>
+    <t xml:space="preserve">7.0663743019104</t>
   </si>
   <si>
     <t xml:space="preserve">7.16120338439941</t>
@@ -194,55 +194,55 @@
     <t xml:space="preserve">7.14321947097778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24949216842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1415843963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22987270355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07618474960327</t>
+    <t xml:space="preserve">7.24949169158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14158391952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22987222671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07618284225464</t>
   </si>
   <si>
     <t xml:space="preserve">7.26911306381226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15302896499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1513934135437</t>
+    <t xml:space="preserve">7.15302753448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15139293670654</t>
   </si>
   <si>
     <t xml:space="preserve">7.31489133834839</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43097496032715</t>
+    <t xml:space="preserve">7.43097543716431</t>
   </si>
   <si>
     <t xml:space="preserve">7.40318059921265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35576581954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14485502243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18899822235107</t>
+    <t xml:space="preserve">7.35576486587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1448540687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18899726867676</t>
   </si>
   <si>
     <t xml:space="preserve">7.16283845901489</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27401685714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998706817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35740041732788</t>
+    <t xml:space="preserve">7.2740159034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998611450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35740184783936</t>
   </si>
   <si>
     <t xml:space="preserve">7.40644979476929</t>
@@ -251,136 +251,136 @@
     <t xml:space="preserve">7.42279863357544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39337015151978</t>
+    <t xml:space="preserve">7.39337205886841</t>
   </si>
   <si>
     <t xml:space="preserve">7.43915033340454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47184991836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51108741760254</t>
+    <t xml:space="preserve">7.47185039520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51108837127686</t>
   </si>
   <si>
     <t xml:space="preserve">7.76778030395508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71546125411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63534593582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68276119232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74162149429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66968250274658</t>
+    <t xml:space="preserve">7.71546173095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63534641265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68276166915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74162101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66968059539795</t>
   </si>
   <si>
     <t xml:space="preserve">7.72200059890747</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63044166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71055603027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85606908798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47735977172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50188636779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5100622177124</t>
+    <t xml:space="preserve">7.63044214248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71055698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85606861114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47736072540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50188732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51006031036377</t>
   </si>
   <si>
     <t xml:space="preserve">8.55093383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42831134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36291408538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.354736328125</t>
+    <t xml:space="preserve">8.42831039428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36291217803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35473728179932</t>
   </si>
   <si>
     <t xml:space="preserve">8.41196250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5199146270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45348262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51161098480225</t>
+    <t xml:space="preserve">8.51991367340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45348167419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51161003112793</t>
   </si>
   <si>
     <t xml:space="preserve">8.4617862701416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47008991241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61125946044922</t>
+    <t xml:space="preserve">8.47008895874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61125755310059</t>
   </si>
   <si>
     <t xml:space="preserve">8.63617038726807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72751426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96002864837646</t>
+    <t xml:space="preserve">8.72751331329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96002674102783</t>
   </si>
   <si>
     <t xml:space="preserve">8.86868381500244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86038017272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58634662628174</t>
+    <t xml:space="preserve">8.86037826538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58634567260742</t>
   </si>
   <si>
     <t xml:space="preserve">8.27577590942383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10969638824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30401039123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3123140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60295391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61956310272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56973743438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71921157836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25916767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64135122299194</t>
+    <t xml:space="preserve">8.10969543457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30400848388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31231307983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60295295715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61956214904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56973838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71921062469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25916957855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64134979248047</t>
   </si>
   <si>
     <t xml:space="preserve">8.25418567657471</t>
@@ -389,40 +389,40 @@
     <t xml:space="preserve">8.0598726272583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20602130889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23757743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84728956222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67954874038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67788791656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95524120330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02831745147705</t>
+    <t xml:space="preserve">8.20602226257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23757648468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84728813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6795482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67788743972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95524168014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02831840515137</t>
   </si>
   <si>
     <t xml:space="preserve">8.05488872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97849273681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14457225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11301803588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23425674438477</t>
+    <t xml:space="preserve">7.97849178314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11301612854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23425579071045</t>
   </si>
   <si>
     <t xml:space="preserve">8.10471343994141</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">8.21100425720215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16782569885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32061862945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37044239044189</t>
+    <t xml:space="preserve">8.16782379150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32061767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37044143676758</t>
   </si>
   <si>
     <t xml:space="preserve">8.50330543518066</t>
@@ -446,28 +446,28 @@
     <t xml:space="preserve">8.36213779449463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67768859863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76903533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53652191162109</t>
+    <t xml:space="preserve">8.67769050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76903629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53652286529541</t>
   </si>
   <si>
     <t xml:space="preserve">8.55313014984131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64447593688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73581886291504</t>
+    <t xml:space="preserve">8.64447402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73581790924072</t>
   </si>
   <si>
     <t xml:space="preserve">8.68599414825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7441234588623</t>
+    <t xml:space="preserve">8.74412250518799</t>
   </si>
   <si>
     <t xml:space="preserve">8.6693868637085</t>
@@ -485,13 +485,13 @@
     <t xml:space="preserve">8.40365791320801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42856884002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65277862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69429779052734</t>
+    <t xml:space="preserve">8.42856979370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6527795791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69429874420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.71090698242188</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">8.89359474182129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84377098083496</t>
+    <t xml:space="preserve">8.84377002716064</t>
   </si>
   <si>
     <t xml:space="preserve">8.88529109954834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78564167022705</t>
+    <t xml:space="preserve">8.78564262390137</t>
   </si>
   <si>
     <t xml:space="preserve">8.80225086212158</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">8.81885814666748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90189838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05136966705322</t>
+    <t xml:space="preserve">8.90189743041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05137062072754</t>
   </si>
   <si>
     <t xml:space="preserve">8.81055450439453</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">8.62786483764648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70260334014893</t>
+    <t xml:space="preserve">8.70260143280029</t>
   </si>
   <si>
     <t xml:space="preserve">8.82716178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75242710113525</t>
+    <t xml:space="preserve">8.75242614746094</t>
   </si>
   <si>
     <t xml:space="preserve">9.04306697845459</t>
@@ -542,22 +542,22 @@
     <t xml:space="preserve">9.14271450042725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28388500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35031700134277</t>
+    <t xml:space="preserve">9.2838830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35031604766846</t>
   </si>
   <si>
     <t xml:space="preserve">9.35861873626709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15101909637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93511486053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77733898162842</t>
+    <t xml:space="preserve">9.1510181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93511390686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7773380279541</t>
   </si>
   <si>
     <t xml:space="preserve">9.19253921508789</t>
@@ -569,43 +569,43 @@
     <t xml:space="preserve">9.17593097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00154685974121</t>
+    <t xml:space="preserve">9.00154781341553</t>
   </si>
   <si>
     <t xml:space="preserve">9.13440990447998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91850566864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9268102645874</t>
+    <t xml:space="preserve">8.91850662231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92681217193604</t>
   </si>
   <si>
     <t xml:space="preserve">9.00985050201416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.984938621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76072978973389</t>
+    <t xml:space="preserve">8.98493957519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7607307434082</t>
   </si>
   <si>
     <t xml:space="preserve">9.1178035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22575664520264</t>
+    <t xml:space="preserve">9.22575569152832</t>
   </si>
   <si>
     <t xml:space="preserve">8.95172119140625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06797885894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0762825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20084285736084</t>
+    <t xml:space="preserve">9.06797790527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07628345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20084381103516</t>
   </si>
   <si>
     <t xml:space="preserve">9.31709957122803</t>
@@ -614,121 +614,121 @@
     <t xml:space="preserve">9.36692237854004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49148273468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5496129989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96481132507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0229425430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82364273071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93989944458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98141860961914</t>
+    <t xml:space="preserve">9.49148368835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54961204528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96481227874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0229406356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82364463806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93990039825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98142051696777</t>
   </si>
   <si>
     <t xml:space="preserve">10.0063323974609</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0561580657959</t>
+    <t xml:space="preserve">10.0561571121216</t>
   </si>
   <si>
     <t xml:space="preserve">10.2056283950806</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2305402755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2139339447021</t>
+    <t xml:space="preserve">10.230541229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2139329910278</t>
   </si>
   <si>
     <t xml:space="preserve">10.1973237991333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1558055877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1225891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1807165145874</t>
+    <t xml:space="preserve">10.1558046340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1225872039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1807174682617</t>
   </si>
   <si>
     <t xml:space="preserve">10.147500038147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2222366333008</t>
+    <t xml:space="preserve">10.2222375869751</t>
   </si>
   <si>
     <t xml:space="preserve">10.1308917999268</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0976753234863</t>
+    <t xml:space="preserve">10.097677230835</t>
   </si>
   <si>
     <t xml:space="preserve">9.84855556488037</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3135814666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0810670852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0727634429932</t>
+    <t xml:space="preserve">10.3135805130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0810680389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0727643966675</t>
   </si>
   <si>
     <t xml:space="preserve">10.5294847488403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4464454650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5211801528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.38831615448</t>
+    <t xml:space="preserve">10.4464445114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5211811065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3883180618286</t>
   </si>
   <si>
     <t xml:space="preserve">10.4713573455811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6872615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7204780578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540441513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4049234390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6457395553589</t>
+    <t xml:space="preserve">10.6872606277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.720477104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4049263000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6457405090332</t>
   </si>
   <si>
     <t xml:space="preserve">10.7952136993408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.96129322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9280786514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7703008651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7786045074463</t>
+    <t xml:space="preserve">10.9612922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9280767440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7703018188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7786064147949</t>
   </si>
   <si>
     <t xml:space="preserve">10.869948387146</t>
@@ -737,73 +737,73 @@
     <t xml:space="preserve">10.7869091033936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0360298156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8948612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0443325042725</t>
+    <t xml:space="preserve">11.0360288619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8948621749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0443334579468</t>
   </si>
   <si>
     <t xml:space="preserve">11.2519340515137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771974563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2270212173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2602376937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2851495742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3432788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3931016921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4512300491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5093584060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5010538101196</t>
+    <t xml:space="preserve">11.1771965026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2270202636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2602386474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2851505279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3432779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3931007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4512281417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5093574523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5010547637939</t>
   </si>
   <si>
     <t xml:space="preserve">11.5176630020142</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7418699264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7584791183472</t>
+    <t xml:space="preserve">11.7418689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7584781646729</t>
   </si>
   <si>
     <t xml:space="preserve">11.6920461654663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.683741569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7252635955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7667827606201</t>
+    <t xml:space="preserve">11.6837406158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7252616882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7667837142944</t>
   </si>
   <si>
     <t xml:space="preserve">11.7169589996338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5923976898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7003498077393</t>
+    <t xml:space="preserve">11.5923986434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7003488540649</t>
   </si>
   <si>
     <t xml:space="preserve">11.542573928833</t>
@@ -815,28 +815,28 @@
     <t xml:space="preserve">12.0574216842651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9162549972534</t>
+    <t xml:space="preserve">11.9162540435791</t>
   </si>
   <si>
     <t xml:space="preserve">11.9909906387329</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9826879501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1487674713135</t>
+    <t xml:space="preserve">11.9826860427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1487665176392</t>
   </si>
   <si>
     <t xml:space="preserve">12.0491189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2899351119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3895835876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3148469924927</t>
+    <t xml:space="preserve">12.2899341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3895826339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.314847946167</t>
   </si>
   <si>
     <t xml:space="preserve">12.5058393478394</t>
@@ -848,25 +848,25 @@
     <t xml:space="preserve">12.2733278274536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1902875900269</t>
+    <t xml:space="preserve">12.1902866363525</t>
   </si>
   <si>
     <t xml:space="preserve">12.1985912322998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0823345184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.64222240448</t>
+    <t xml:space="preserve">12.0823354721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6422214508057</t>
   </si>
   <si>
     <t xml:space="preserve">11.5508766174316</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8083009719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9346389770508</t>
+    <t xml:space="preserve">11.8083028793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9346399307251</t>
   </si>
   <si>
     <t xml:space="preserve">11.9514837265015</t>
@@ -878,19 +878,19 @@
     <t xml:space="preserve">12.1620454788208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7830352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6566963195801</t>
+    <t xml:space="preserve">11.783034324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6566972732544</t>
   </si>
   <si>
     <t xml:space="preserve">11.8083019256592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7577667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5977411270142</t>
+    <t xml:space="preserve">11.7577676773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5977401733398</t>
   </si>
   <si>
     <t xml:space="preserve">11.5640506744385</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">11.3029546737671</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2018852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1934623718262</t>
+    <t xml:space="preserve">11.2018842697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1934614181519</t>
   </si>
   <si>
     <t xml:space="preserve">11.0334348678589</t>
@@ -911,22 +911,22 @@
     <t xml:space="preserve">10.9576320648193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2355728149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4208679199219</t>
+    <t xml:space="preserve">11.2355718612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4208688735962</t>
   </si>
   <si>
     <t xml:space="preserve">11.2271518707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2861080169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1681938171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.923942565918</t>
+    <t xml:space="preserve">11.2861089706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.168194770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9239435195923</t>
   </si>
   <si>
     <t xml:space="preserve">11.0250120162964</t>
@@ -935,13 +935,13 @@
     <t xml:space="preserve">10.763916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9492111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5786209106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7891845703125</t>
+    <t xml:space="preserve">10.9492101669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5786218643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7891836166382</t>
   </si>
   <si>
     <t xml:space="preserve">10.7386484146118</t>
@@ -953,31 +953,31 @@
     <t xml:space="preserve">10.7554941177368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4292917251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5219383239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2945318222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.639853477478</t>
+    <t xml:space="preserve">11.4292907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5219392776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2945308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6398525238037</t>
   </si>
   <si>
     <t xml:space="preserve">11.4629802703857</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4124460220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3619108200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3197994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2103080749512</t>
+    <t xml:space="preserve">11.412446975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.361909866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3197984695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2103071212769</t>
   </si>
   <si>
     <t xml:space="preserve">10.9997444152832</t>
@@ -986,55 +986,55 @@
     <t xml:space="preserve">10.991322517395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0081672668457</t>
+    <t xml:space="preserve">11.00816822052</t>
   </si>
   <si>
     <t xml:space="preserve">10.8902530670166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9323654174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8734092712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8818302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6796922683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.78076171875</t>
+    <t xml:space="preserve">10.9323663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8734073638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8818321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6796913146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7807607650757</t>
   </si>
   <si>
     <t xml:space="preserve">10.8649854660034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7049579620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9155197143555</t>
+    <t xml:space="preserve">10.7049589157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9155216217041</t>
   </si>
   <si>
     <t xml:space="preserve">11.2608404159546</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1513481140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0839700698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0502796173096</t>
+    <t xml:space="preserve">11.151349067688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0839691162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0502805709839</t>
   </si>
   <si>
     <t xml:space="preserve">11.2524185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3282222747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.378755569458</t>
+    <t xml:space="preserve">11.328221321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3787546157837</t>
   </si>
   <si>
     <t xml:space="preserve">11.3955993652344</t>
@@ -1046,37 +1046,37 @@
     <t xml:space="preserve">11.4040241241455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.555627822876</t>
+    <t xml:space="preserve">11.5556268692017</t>
   </si>
   <si>
     <t xml:space="preserve">11.6819658279419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7493448257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9177932739258</t>
+    <t xml:space="preserve">11.749342918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9177942276001</t>
   </si>
   <si>
     <t xml:space="preserve">11.8841047286987</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9430618286133</t>
+    <t xml:space="preserve">11.943060874939</t>
   </si>
   <si>
     <t xml:space="preserve">12.0525531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0946664810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1536235809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0357093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0778198242188</t>
+    <t xml:space="preserve">12.0946655273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1536226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0357084274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0778207778931</t>
   </si>
   <si>
     <t xml:space="preserve">12.0441312789917</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">12.1704683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3136510848999</t>
+    <t xml:space="preserve">12.3136501312256</t>
   </si>
   <si>
     <t xml:space="preserve">12.3220729827881</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">12.2883834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2968063354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7914562225342</t>
+    <t xml:space="preserve">12.2968053817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7914552688599</t>
   </si>
   <si>
     <t xml:space="preserve">11.7325000762939</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">11.816722869873</t>
   </si>
   <si>
-    <t xml:space="preserve">12.010440826416</t>
+    <t xml:space="preserve">12.0104417800903</t>
   </si>
   <si>
     <t xml:space="preserve">12.0020189285278</t>
@@ -1124,19 +1124,19 @@
     <t xml:space="preserve">11.9683294296265</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9262161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3113765716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8144512176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6965351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8986749649048</t>
+    <t xml:space="preserve">11.9262170791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.311375617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8144521713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6965370178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8986759185791</t>
   </si>
   <si>
     <t xml:space="preserve">10.8228731155396</t>
@@ -1148,34 +1148,34 @@
     <t xml:space="preserve">10.940788269043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7723379135132</t>
+    <t xml:space="preserve">10.7723388671875</t>
   </si>
   <si>
     <t xml:space="preserve">10.7976055145264</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7302255630493</t>
+    <t xml:space="preserve">10.7302265167236</t>
   </si>
   <si>
     <t xml:space="preserve">10.7218036651611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6628465652466</t>
+    <t xml:space="preserve">10.6628475189209</t>
   </si>
   <si>
     <t xml:space="preserve">10.6123113632202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8060274124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6881132125854</t>
+    <t xml:space="preserve">10.8060283660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6881151199341</t>
   </si>
   <si>
     <t xml:space="preserve">10.8312950134277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6712694168091</t>
+    <t xml:space="preserve">10.6712684631348</t>
   </si>
   <si>
     <t xml:space="preserve">10.4691295623779</t>
@@ -1184,3091 +1184,3094 @@
     <t xml:space="preserve">10.4859733581543</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0923938751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1597709655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.134503364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1429281234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2187309265137</t>
+    <t xml:space="preserve">11.0923919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1597719192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1345043182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1429262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.218729019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4545583724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3450651168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4270181655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3175249099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2417230606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2838344573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1911878585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1574964523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2248783111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1659212112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1069641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0985422134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93009090423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98904895782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0058937072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7195291519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68583965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48370170593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37420845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1153860092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3091020584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5954656600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7133808135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.603889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.359637260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3006792068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4522848129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4017505645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5617780685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5449304580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3427925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438629150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4101724624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4185943603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4354391098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2585668563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2333002090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.29225730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.149076461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0418577194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.536509513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2754125595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2080335617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0648498535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93851375579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0500860214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3848028182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3075609207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7710151672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.676607131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5993661880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.230318069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.470627784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5049571990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6422786712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6851892471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6594429016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9340829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.650860786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5307054519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.393385887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.350471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1444931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1359119415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92134952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.075834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0586700439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89560222625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.947096824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74111652374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76686573028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85268783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87843608856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99000930786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2560653686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.290397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2732305526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135402679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.48779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4362983703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3333082199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0844173431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1273288726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0157566070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.032922744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84410762786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0415048599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2389011383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78402900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.706787109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77544689178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68103885650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56088638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68962287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47505950927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.483642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62954425811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.912766456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88701915740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75828266143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56946659088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.578049659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73253440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61237907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71536922454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82694244384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.187406539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2217350006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99859142303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96426105499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86985397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69820308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86127185821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52655601501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21758556365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23474979400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69405460357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52669525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4408712387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12331962585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43228912353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52240371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41083240509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29926013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16623115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23059940338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08469772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35504531860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22630882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48378372192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39366626739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57819080352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49236679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44945430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23489189147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11473560333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02032947540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79289150238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72852516174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77143669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83151388168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00316333770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02891063690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00745582580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25205707550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28638648986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61681175231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60822868347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54815101623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75413036346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48807525634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46232795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.161940574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19197940826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98170852661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08898830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33788108825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81435012817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69848680496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99887323379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81864023208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86584424972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58691358566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.634117603302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68990278244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65986585617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96454429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93879699707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73696613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82279109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47949123382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38508319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40224933624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45374393463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36791896820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49665641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50094795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46661853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59964656829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85712146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56960868835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56531715393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55673313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53956985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50523948669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50953102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24776458740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15335750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39795684814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58248043060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77129650115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65972328186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09743118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96869373321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02018737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28624534606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31199264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08026599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13175964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32057571411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.942946434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.814208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78846073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.797043800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74554920196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72838592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.908616065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14034271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42356586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.260498046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18325519561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00302314758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96011161804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76271343231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65114116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.685471534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67688846588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87428569793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51797294616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44072914123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41498184204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64670944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0672512054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93851280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1959886550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80977630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62096214294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50939083099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86570262908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95152854919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83995628356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75851726531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77167510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74097347259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42080783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53484058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57869911193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58746910095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47343635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55238342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42957973480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18397331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37695026397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56992530822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67957305908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66202831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89447975158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75413131713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72781658172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72343063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9383373260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82430458068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06114101409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00850963592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85062026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71465969085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88570785522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0523681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28043174743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32429027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23657417297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9295654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80676174163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78921985626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49536800384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45589447021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48221111297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62255573272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9207935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0786828994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0172815322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17958641052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13134288787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17081546783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9602952003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77170419692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61819982528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6488995552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63135766983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38574934005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29803466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22347402572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20593118667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28048992156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27171802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.512939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39890718460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26733255386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19277286529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4427661895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4515380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32873392105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53048229217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79363393783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98660945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0611686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2234468460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28923225402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35063552856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21905899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19274425506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30239105224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87257862091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72345972061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60942840576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74100303649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83310604095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84187746047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67521476745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50855493545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40329313278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45592451095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44715213775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31557703018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47346687316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85064840316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85942029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00854015350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.043625831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80679035186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91643762588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18835926055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25414752960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29361915588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36379146575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65325736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37256336212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43835163116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96465301513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12254333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1488561630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37692070007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56112480163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75410175323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70147323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47340965270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35060501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49095249176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24534511566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42078018188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31551933288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48218154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64884376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72778797149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80673313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77164649963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85936164855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81550407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86813354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92076396942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9997091293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8769063949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84182071685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89444923400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9821662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0698823928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96462345123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67515850067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71901512145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79796028137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29797554016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52603816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63129997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71024513244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68392944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69270038604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76287460327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73655891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57866954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30674743652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2102575302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33306121826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20148754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02605533599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26288986206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13131427764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08745574951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43832302093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42955017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21903038024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25411701202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15762901306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09622669219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39449119567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33747577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34186267852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1050271987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92959403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49978256225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60065603256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4296088218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11821460723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18400239944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57875633239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64893007278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5568265914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14017248153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3857798576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87702226638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9735107421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55244064331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11382722854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72784471511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82436275482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02172565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4734959602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31560564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83316421508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96035289764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85070705413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61387252807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18406009674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47352457046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54369783401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89895105361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82439231872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64895820617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69720268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92965173721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06122732162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0085973739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0568413734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40332269668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59191370010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83752107620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69717407226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86822128295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81120538711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72348880767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48665332794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48226833343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36385011672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22789001464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77176237106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82000684738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26297569274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23227548599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21911764144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39455127716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59629964828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16207218170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51732444763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37259340286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33312034606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41645097732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79801988601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68398666381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55679845809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10067176818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35504913330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35066413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21031665802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23224592208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17523002624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10505676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20154476165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24540328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21470355987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17084407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40768003463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25856113433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36820697784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32434940338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14891481399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24978923797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43838024139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16645812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70156002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61384248733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69278717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75418949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68401670455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71033191680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83313465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06119775772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1401424407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05681324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04804086685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00856876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94716644287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0743556022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08751344680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09628534317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0173397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35943555831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29364824295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49101066589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60504198074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97345304489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57434129714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41206550598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88576459884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99102544784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03926944732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06997013092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31119203567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48223972320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8638072013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92082262039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9997673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73661804199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68837404251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61381483078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62697076797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57872676849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77609014511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240535736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96906709671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99099636077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15327072143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54799747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56995534896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82433414459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66644430160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71907472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78486156463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86819267272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22780227661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17517185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39446449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83304786682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58744144439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40323543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36814975738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35937786102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53481197357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46463680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50849533081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41200733184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38569164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61375713348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49972438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03482437133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74533176422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90322303771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0961980819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1225128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.938307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6663875579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88567733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45586490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51726722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44709396362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82427597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56989765167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94710826873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16640090942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28920364379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27165985107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34183406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19271564483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18394374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90324974060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06991291046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8418493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9997386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97342300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18857192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19807147979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1890983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43138980865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57496929168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7275218963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79931259155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81725883483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94289207458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98776149749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79033756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74547004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68265438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70060157775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52112579345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51215267181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35062599182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53010082244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63778495788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61086368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69162750244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50317859649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58394336700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60188961029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55702114105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5480489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35960102081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76341724395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64675903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29678249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33267784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38652038574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39549446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77239227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88905048370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3915786743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5800266265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.651816368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6877107620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7415533065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8582124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9389743804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9838438034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0556344985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1005029678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0915298461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.127423286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0197401046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9300022125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0107660293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9748697280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8761587142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.912055015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0466604232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.921028137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8941078186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9030818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8043699264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7595014572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7864227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8402643203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.427472114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2569723129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90699672698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96084022521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1223659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1313409805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1403141021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0954456329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87110233306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8082857131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56599617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47625923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67368030548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70957374572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75444412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84418106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85315418243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82623291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86212825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0236549377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96981239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1672344207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492881774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2031297683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1851835250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2838945388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3377370834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4454212188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5172109603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3467092514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3018407821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4184989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.436448097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7774486541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8492393493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6966867446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7684745788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5620784759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0864715576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2479991912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4902896881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5979747772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8671855926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1453714370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9658975601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9569234848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.082555770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1094770431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1722927093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2440824508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2261362075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.190239906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.459451675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6299533843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8004531860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0068492889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6568746566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8453226089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2171621322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2081890106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3248462677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2620306015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1363973617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8223180770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3287620544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.373631477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5441312789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.705659866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6159210205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4095258712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7146329879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6248950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4005527496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6069478988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44933605194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81668853759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01354026794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0225133895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15711975097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48914813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20198917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34556865692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5385046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6775951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09038734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96924209594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01859855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1083345413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18012428283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13525676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98270320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79874134063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90642642974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34165191650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25191497802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08141326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97372913360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03654479980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83015060424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43979167938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26480484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36351490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27377796173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30967330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35005569458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36800193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51606941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94232082366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70900535583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57439804077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45773983001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46671390533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61478042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4936351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30069923400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18404102325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25134372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12571239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88399028778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65573215484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6856861114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5844087600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63044357299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87903022766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0539627075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2104806900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95268630981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98030662536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.035548210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89744472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0631694793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1184110641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1552381515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63965034484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40027141571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22533893585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44630527496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87087345123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95833778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98595905303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02278614044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03199481964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66832065582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62228584289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67292404174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77419948577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73737239837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53482055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52561283111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30464744567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35988807678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80642318725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08263206481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8570613861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88928604125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82023525238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60847663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90309619903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00437259674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06882190704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1056489944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14247798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99976921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71895885467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86166572570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17470073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47392654418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5936164855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6488561630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77775478363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72251415252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55678844451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75934028625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171997070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66727161407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37265014648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53837394714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21613216400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84325122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00897598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92611408233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59466361999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56244087219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57164764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44274997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38750839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45195770263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14352607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1251106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23559474945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23099040985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42433643341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76959609985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75578594207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79261302947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51640605926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31385326385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33226680755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21718120574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09749126434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01923179626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77985191345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88112878799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83049058914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82588672637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4944372177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8212833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97319746017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31845664978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2217845916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34147548675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30924987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29544067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68213081359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47037124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61307907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66371726989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73276901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90769958496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91690635681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97214889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79721736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.193115234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54758071899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82378959655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79616928100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74092674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80537509918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0723752975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.219687461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8641719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7260675430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6892395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444820404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5143089294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2381010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3393774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841348648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3209638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1368255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1828603744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3485841751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.192066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0815830230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90665149688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85140991210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94347953796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86061668395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7501335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65806484222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60282421112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48313331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62123680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8329963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.146032333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1276178359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2473087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4866876602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5327224731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7721033096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6800336837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4038257598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7352743148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5695495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6616201400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9286203384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9654474258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3889665603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7940711975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1163129806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2912464141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3372793197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1623487472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9874172210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0886926651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8585195541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.318865776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3649015426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2820377349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2083826065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2636241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6779365539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8620738983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7275247573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7367334365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4789390563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1290760040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5950736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8252477645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896961212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5582466125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6963500976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6134872436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0058298110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.913761138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.171555519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0518655776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2267961502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2175893783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3280725479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9966230392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9321756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4293489456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7700052261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2728309631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5674533843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.503005027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4661769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4845905303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3096590042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.024245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1991758346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2544183731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6503143310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0738334655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2855939865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2579717636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1751098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2119388580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1659030914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3040075302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2947998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3417453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1821327209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9849634170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3041896820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2854108810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3323564529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3511343002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5389137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6891374588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5013580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4450235366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4168567657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4544134140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4919681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6140260696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9895849227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9614171981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7548599243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8299722671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5952472686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5201349258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.703293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3840684890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3652906417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2150678634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3183460235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5061254501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6000156402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7502393722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6469612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6281814575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5249032974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5342931747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4404029846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2526226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4028463363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3277349472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1493434906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2901792526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2244567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2620124816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5155143737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4310140609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1211767196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0836210250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4122352600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0930099487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2338447570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0272874832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9803428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9333972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0178985595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1305665969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0648441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2056789398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9991207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8488969802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9240083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7268400192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9146194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9897317886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0554552078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0460653305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0742321014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9709529876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8770627975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7737846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3512811660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4827260971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6047830581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5578384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5484495162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6329507827759</t>
   </si>
   <si>
     <t xml:space="preserve">11.4545593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3450660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4270162582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3175230026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2417230606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2838335037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1911869049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1574974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2248783111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1659212112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1069631576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0985412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93009185791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98904895782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0058946609497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7195291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68584156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4837007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37420749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1153860092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.309100151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5954666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7133798599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.603889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3596382141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3006801605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4522848129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4017505645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5617771148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5449314117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.342791557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4101724624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4185934066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4354391098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2585678100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2332992553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.29225730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1490755081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0418577194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5365085601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2754135131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2080316543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0648508071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93851470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0500860214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3848028182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3075609207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.771014213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.676607131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5993661880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2303190231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.470627784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5049562454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6422758102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6851892471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6594429016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7109384536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.93408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6508598327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452669143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5307054519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.393385887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3504734039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1444931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.135910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92134952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0758333206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.058669090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89560222625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94709587097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74111747741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76686477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85268878936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87843608856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99000930786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2560653686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2903966903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.273229598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.51353931427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.48779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4362983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3333082199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.084415435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.127329826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0157566070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0329217910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84410667419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0415029525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2389011383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78402900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.706787109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77544593811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68103885650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56088447570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68962287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47506046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.483642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62954425811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.912766456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88701820373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7582836151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56946659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.578049659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73253440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.612380027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71536827087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82694053649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1874074935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.221736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99859142303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96426105499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86985492706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69820404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86127281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52655601501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21758460998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23475074768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69405460357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52669525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44087028503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12331962585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43228816986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52240371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41083335876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29926109313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16623210906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23060131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08469772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35504627227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22630882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48378372192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39366626739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57818984985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49236583709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44945240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23489093780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11473655700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02032852172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79289245605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72852373123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7714376449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83151388168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00316333770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02891159057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00745391845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25205707550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28638744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61681175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60822868347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54815196990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75413131713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48807430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46232795715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.161940574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19197845458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98170804977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0889892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33788108825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81435060501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.698486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99887418746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81864023208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8658447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58691358566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63411712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68990278244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65986633300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96454334259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93879556655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73696708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82279109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.385085105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40224933624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45374393463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36791896820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49665641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50094699859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46661758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59964752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85712051391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56960773468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56531810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55673408508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53956985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50523948669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50953197479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24776458740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15335750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39795875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58248138427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77129650115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65972518920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09743118286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96869277954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02018737792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28624534606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31199264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08026504516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13175964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32057571411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94294548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.814208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78846073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79704475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74554920196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72838497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90861701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14034271240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42356586456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26049900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18325614929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00302410125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96011066436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76271343231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65114116668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.685471534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67689037322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87428569793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51797103881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44072914123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41498279571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64670944213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0672512054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93851375579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1959886550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80977630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62096118927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50939083099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86570262908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95152854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83995532989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75851726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77167510986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74097347259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42080879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53484058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57869720458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58747005462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47343826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55238151550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42957973480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1839714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37695026397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56992626190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67957210540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66202831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8944787979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7541332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72781658172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72343158721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9383373260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82430553436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06113910675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00851058959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85062026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71465969085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88570690155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05236721038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28043174743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32428932189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23657417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9295654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80676078796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78921890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49536800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45589447021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48221111297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62255668640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92079448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07868385314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01728248596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17958641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1313419342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17081546783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96029567718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77170467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61819982528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64890003204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63135719299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38574934005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29803419113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39013576507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22347402572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20593118667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28049039840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27171802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51293992996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39890813827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26733303070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19277286529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4427661895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45153856277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32873344421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53048276901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79363298416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98661088943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0611686706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22344589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28923320770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35063362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21905994415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1927433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30239009857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87257862091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72346067428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60942888259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74100303649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83310556411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84187746047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67521619796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50855350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4032940864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45592451095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44715261459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31557655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4734673500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85064840316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85942029953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00854015350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04362678527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80679082870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91643619537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18835926055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25414752960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29361915588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36379241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65325736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37256336212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43835067749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9646520614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12254238128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14885711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37692070007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56112480163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75410270690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70147323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47340965270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35060596466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49095249176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24534606933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42077827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31551837921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48218154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64884185791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72778701782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80673313140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77164649963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85936260223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81550407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86813354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9207649230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9997091293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8769063949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84181880950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89444828033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98216724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0698823928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96462345123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67515659332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71901702880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79796123504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29797554016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52604007720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63129997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71024513244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68392944335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69270133972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76287364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7365608215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57866954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30674648284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21025943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33306121826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20148754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02605533599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26288986206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13131523132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0874547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43832302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42955017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21903038024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25411701202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15762901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09622764587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39449310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33747577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34186267852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1050271987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92959403991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49978256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60065650939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4296088218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11821460723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18400144577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57875633239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64892911911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5568265914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14017200469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38577938079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87702226638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97351026535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55244064331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11382818222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72784519195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82436275482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02172565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4734959602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31560564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83316421508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9603533744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85070657730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61387252807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18405961990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4735255241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54369783401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89895105361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82439231872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64895820617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69720315933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92965173721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06122732162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0085973739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0568413734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40332269668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5919132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83752107620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69717359542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86822175979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81120586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72348880767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48665428161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4822678565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36385059356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22788953781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77176237106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82000637054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26297569274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23227548599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21911764144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39455032348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59629964828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16207265853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51732444763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37259340286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33312034606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4164514541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79801988601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68398714065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55679798126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10067176818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35504913330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35066366195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21031665802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23224639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17523002624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10505723953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20154523849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24540281295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21470260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17084455490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40768003463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25856065750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36820697784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32434940338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14891481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24978828430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43837976455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16645765304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70155954360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61384296417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69278764724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75418996810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68401718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71033191680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83313465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06119823455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1401424407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05681276321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04804134368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00856828689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94716644287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07435607910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08751344680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09628534317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0173397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35943603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29364824295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49101066589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60504198074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9734525680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57434129714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41206502914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88576412200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99102544784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0392689704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06996965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31119155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48223829269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86380624771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92082214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99976682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73661708831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68837356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61381387710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62697172164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57872676849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77608919143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80240488052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96906661987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99099540710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15327072143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54799747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56995534896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82433366775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66644525527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71907424926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78486108779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86819267272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22780227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17517185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39446353912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83304691314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58744049072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40323543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36814975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35937881469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53481101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46463871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50849628448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41200733184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38569259643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61375617980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49972534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03482532501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74533271789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90322208404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0961971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1225118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.938307762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638660430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88567733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45586490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51726722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44709396362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82427597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56989765167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94710826873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1663990020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28920364379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27166080474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34183311462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19271564483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18394374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90324974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06991100311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84184837341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99973964691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97342395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18857192993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19807243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18909931182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43138980865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57496929168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7275218963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79931259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81725978851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94289207458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98776149749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79033851623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74547004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68265342712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70060157775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52112579345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51215362548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35062599182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53010082244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63778495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61086368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69162750244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5031795501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58394336700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60188961029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55702018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5480489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35960006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76341724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64675807952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29678249359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33267784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38652038574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39549446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7723913192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8890495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3915777206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5800266265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6518154144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6877107620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7415542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8582134246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9389762878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9838447570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0556335449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1005029678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0915298461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.127423286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.019739151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9300031661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312902450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376863479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0107669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9748697280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8761596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9120540618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0466613769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.921028137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8941078186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9030809402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8043699264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.75950050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7864236831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8402643203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.427472114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2569723129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90699672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96083927154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1223659515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1313390731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1403150558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0954456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87110137939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80828666687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56599426269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47625732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67368030548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70957469940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75444412231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84418106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8531551361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82623291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86212730407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0236549377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96981239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1672344207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492881774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2031307220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1851825714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2838935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3377361297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4454212188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5172100067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3467082977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3018407821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4184999465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4364461898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7774486541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8492393493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6966848373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7684755325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5620794296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0864706039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2479991912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.490288734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5979747772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8671855926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1453714370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9658975601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9569225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0825548171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1094770431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1722927093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2440824508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2261352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1902408599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4594526290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6299524307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8004531860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0068492889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6568746566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8453216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2171602249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2081880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3248462677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2620296478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1363973617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8223171234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3287630081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5351581573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.373631477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.544132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.705659866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6159219741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4095258712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7146320343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6248960494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4005527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6069469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44933700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81668949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01354122161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02251243591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15712070465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48914813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20198822021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34556770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53850269317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6775951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09038734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96924209594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01859760284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10833549499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18012523651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13525676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98270320892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79874134063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34165191650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25191497802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08141326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97372913360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03654479980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83014965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43979167938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26480388641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36351585388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27377891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30967426300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35005474090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36800193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51606845855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94232177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70900440216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5743989944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45773887634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46671485900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61478042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4936351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30069923400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18404102325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25134468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12571239471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88399219512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65573310852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6856861114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5844087600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63044452667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87903022766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0539617538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2104806900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95268630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98030757904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.035548210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89744472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0631704330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1184110641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1552381515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63965129852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40027046203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22533988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44630527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87087249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95833873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98595905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02278614044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03199481964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66832065582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62228488922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67292404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77419948577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73737239837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53482055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52561378479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30464649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35988807678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80642414093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08263111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85706233978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88928604125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82023429870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60847568511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90309715270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00437259674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06882190704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1056489944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14247703552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99976921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71895790100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86166477203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17470169067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47392654418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5936164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64885807037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77775478363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72251319885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55678844451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7593412399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66727066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37265014648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53837394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21613311767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84325218200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00897598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92611408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59466552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56244087219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57164859771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44275093078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38750743865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45195770263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14352512359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12511157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23559379577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23099040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42433643341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76959609985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75578594207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7926139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51640510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31385326385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33226680755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21718120574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09749126434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01923179626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77985143661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88112878799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83049011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82588624954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49443769454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8212833404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9731969833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31845664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22178554534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34147453308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30924987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29543972015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68213081359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47037124633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61307811737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66371631622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73276805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90770053863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91690731048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97214889526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79721832275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19311428070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54758167266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8237886428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79616832733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74092674255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80537605285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0723762512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.219687461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8641719818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7260675430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6892395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444820404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.514307975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2381010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3393774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841358184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3209638595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1368246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1828584671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3485832214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.192066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0815830230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90665245056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85140991210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94347953796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86061763763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75013446807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6580638885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60282325744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48313331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62123680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8329963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.146032333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1276178359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2473077774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4866886138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5327224731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7721014022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6800336837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4038257598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7352743148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5695505142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6616191864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9286203384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9654483795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3889665603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7940711975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1163139343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2912464141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3372802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1623487472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9874172210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0886926651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8585205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3188667297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3649015426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2820386886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2083826065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2636241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6779365539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8620748519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7275257110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7367324829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4789390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.129075050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5950746536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8252477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8896951675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5582466125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6963500976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6134872436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0058307647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.913761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.171555519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0518646240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2267961502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2175903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3280735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9966230392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9321746826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4293489456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7700052261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2728309631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5674524307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.503005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4661769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4845905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3096580505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.024245262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1991758346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2544174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.650315284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0738334655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2855939865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2579717636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1751108169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2119379043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1659030914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3040065765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2947998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3417444229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1821327209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9849634170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3041896820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2854108810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3323554992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3511343002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5389137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6891374588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5013580322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4450235366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4168567657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4544124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4919691085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6140260696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9895839691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9614181518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7548599243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8299722671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5952472686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5201358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.703293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3840675354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3652906417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2150678634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3183460235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5061254501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6000146865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7502393722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6469602584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6281824111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5249042510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5342931747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4404029846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2526226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4028472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3277349472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1493434906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2901792526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2244567871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2620124816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5155143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4310131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1211767196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0836219787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4122362136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0930109024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2338447570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0272874832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9803428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9333972930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0178985595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1305665969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0648441314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.205677986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9991207122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8488969802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9240083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7268390655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9146194458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9897317886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0554542541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0460653305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0742321014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9709539413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8770637512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7737846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3512811660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4827260971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6047830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5578384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5484495162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6329507827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.510892868042</t>
+    <t xml:space="preserve">11.5108938217163</t>
   </si>
   <si>
     <t xml:space="preserve">11.670506477356</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4076137542725</t>
+    <t xml:space="preserve">11.4076147079468</t>
   </si>
   <si>
     <t xml:space="preserve">11.3606700897217</t>
@@ -4295,10 +4298,10 @@
     <t xml:space="preserve">10.8254976272583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7785530090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6001615524292</t>
+    <t xml:space="preserve">10.7785520553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6001625061035</t>
   </si>
   <si>
     <t xml:space="preserve">10.7034406661987</t>
@@ -4310,10 +4313,10 @@
     <t xml:space="preserve">10.7503852844238</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7222185134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6471071243286</t>
+    <t xml:space="preserve">10.7222194671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6471061706543</t>
   </si>
   <si>
     <t xml:space="preserve">10.31849193573</t>
@@ -4337,7 +4340,7 @@
     <t xml:space="preserve">9.68004131317139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68943119049072</t>
+    <t xml:space="preserve">9.68943023681641</t>
   </si>
   <si>
     <t xml:space="preserve">9.71759796142578</t>
@@ -4376,7 +4379,7 @@
     <t xml:space="preserve">9.94293308258057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85843181610107</t>
+    <t xml:space="preserve">9.85843276977539</t>
   </si>
   <si>
     <t xml:space="preserve">10.1776580810547</t>
@@ -4388,7 +4391,7 @@
     <t xml:space="preserve">10.018045425415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0649900436401</t>
+    <t xml:space="preserve">10.0649909973145</t>
   </si>
   <si>
     <t xml:space="preserve">9.89598751068115</t>
@@ -4406,10 +4409,10 @@
     <t xml:space="preserve">10.2527694702148</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1307134628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2809362411499</t>
+    <t xml:space="preserve">10.1307125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2809371948242</t>
   </si>
   <si>
     <t xml:space="preserve">10.1964349746704</t>
@@ -4418,7 +4421,7 @@
     <t xml:space="preserve">10.3560485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5062713623047</t>
+    <t xml:space="preserve">10.506272315979</t>
   </si>
   <si>
     <t xml:space="preserve">10.4029932022095</t>
@@ -4430,7 +4433,7 @@
     <t xml:space="preserve">9.97109985351562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.487494468689</t>
+    <t xml:space="preserve">10.4874935150146</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405498504639</t>
@@ -4445,7 +4448,7 @@
     <t xml:space="preserve">10.6658849716187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5719957351685</t>
+    <t xml:space="preserve">10.5719947814941</t>
   </si>
   <si>
     <t xml:space="preserve">10.4499387741089</t>
@@ -4466,7 +4469,7 @@
     <t xml:space="preserve">10.309103012085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2621593475342</t>
+    <t xml:space="preserve">10.2621583938599</t>
   </si>
   <si>
     <t xml:space="preserve">10.1870470046997</t>
@@ -4478,7 +4481,7 @@
     <t xml:space="preserve">10.1401023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058238983154</t>
+    <t xml:space="preserve">10.2058248519897</t>
   </si>
   <si>
     <t xml:space="preserve">10.6095514297485</t>
@@ -4496,10 +4499,10 @@
     <t xml:space="preserve">10.7409963607788</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9099988937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7316074371338</t>
+    <t xml:space="preserve">10.9099979400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7316083908081</t>
   </si>
   <si>
     <t xml:space="preserve">10.8912210464478</t>
@@ -4526,7 +4529,7 @@
     <t xml:space="preserve">10.7128295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7879419326782</t>
+    <t xml:space="preserve">10.7879409790039</t>
   </si>
   <si>
     <t xml:space="preserve">10.9287767410278</t>
@@ -4541,10 +4544,7 @@
     <t xml:space="preserve">11.0602216720581</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0038890838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8818321228027</t>
+    <t xml:space="preserve">11.003888130188</t>
   </si>
   <si>
     <t xml:space="preserve">10.6377172470093</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">11.1728897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2949457168579</t>
+    <t xml:space="preserve">11.2949466705322</t>
   </si>
   <si>
     <t xml:space="preserve">11.1447229385376</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">11.0508337020874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2480010986328</t>
+    <t xml:space="preserve">11.2480020523071</t>
   </si>
   <si>
     <t xml:space="preserve">11.3982257843018</t>
@@ -4589,16 +4589,16 @@
     <t xml:space="preserve">11.3418912887573</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1259460449219</t>
+    <t xml:space="preserve">11.1259450912476</t>
   </si>
   <si>
     <t xml:space="preserve">11.2386131286621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9757204055786</t>
+    <t xml:space="preserve">11.2292232513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9757213592529</t>
   </si>
   <si>
     <t xml:space="preserve">11.6104164123535</t>
@@ -4619,10 +4619,10 @@
     <t xml:space="preserve">11.4094924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3249912261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1090440750122</t>
+    <t xml:space="preserve">11.3249921798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1090450286865</t>
   </si>
   <si>
     <t xml:space="preserve">10.4705944061279</t>
@@ -4634,7 +4634,7 @@
     <t xml:space="preserve">10.4536933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3691930770874</t>
+    <t xml:space="preserve">10.3691921234131</t>
   </si>
   <si>
     <t xml:space="preserve">10.4799823760986</t>
@@ -57241,7 +57241,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1964" t="s">
-        <v>395</v>
+        <v>1416</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -57267,7 +57267,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1965" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -57293,7 +57293,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1966" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -57319,7 +57319,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -57345,7 +57345,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1968" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -57371,7 +57371,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1969" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -57397,7 +57397,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G1970" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -57423,7 +57423,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1971" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -57449,7 +57449,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1972" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -57475,7 +57475,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1973" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -57501,7 +57501,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1974" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -57527,7 +57527,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G1975" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -57553,7 +57553,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1976" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -57579,7 +57579,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1977" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -57605,7 +57605,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1978" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -57631,7 +57631,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1979" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -57657,7 +57657,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1980" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -57683,7 +57683,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1981" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -57709,7 +57709,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1982" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -57735,7 +57735,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G1983" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -57761,7 +57761,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1984" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -57787,7 +57787,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1985" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -57813,7 +57813,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G1986" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -57839,7 +57839,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1987" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -57865,7 +57865,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G1988" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -57891,7 +57891,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G1989" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -57917,7 +57917,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1990" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -57943,7 +57943,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G1991" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -57969,7 +57969,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1992" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -57995,7 +57995,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1993" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -58021,7 +58021,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1994" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -58047,7 +58047,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1995" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -58073,7 +58073,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G1996" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -58099,7 +58099,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1997" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -58125,7 +58125,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G1998" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -58151,7 +58151,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -58177,7 +58177,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G2000" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -58203,7 +58203,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G2001" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -58229,7 +58229,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G2002" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -58255,7 +58255,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2003" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -58281,7 +58281,7 @@
         <v>10.5</v>
       </c>
       <c r="G2004" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -58307,7 +58307,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G2005" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -58333,7 +58333,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2006" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -58359,7 +58359,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2007" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -58385,7 +58385,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G2008" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -58411,7 +58411,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2009" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -58437,7 +58437,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2010" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -58463,7 +58463,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2011" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -58489,7 +58489,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2012" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -58515,7 +58515,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G2013" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -58541,7 +58541,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G2014" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -58567,7 +58567,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G2015" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -58593,7 +58593,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2016" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -58619,7 +58619,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G2017" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -58645,7 +58645,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G2018" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -58671,7 +58671,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2019" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -58697,7 +58697,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G2020" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -58723,7 +58723,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2021" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -58749,7 +58749,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2022" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -58775,7 +58775,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G2023" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -58801,7 +58801,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G2024" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -58827,7 +58827,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2025" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -58853,7 +58853,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2026" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -58879,7 +58879,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G2027" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -58905,7 +58905,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G2028" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -58931,7 +58931,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2029" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -58957,7 +58957,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G2030" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -58983,7 +58983,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G2031" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -59009,7 +59009,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2032" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -59035,7 +59035,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2033" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -59061,7 +59061,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2034" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -59087,7 +59087,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G2035" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -59113,7 +59113,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2036" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -59139,7 +59139,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2037" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -59165,7 +59165,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2038" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -59191,7 +59191,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G2039" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -59217,7 +59217,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2040" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -59243,7 +59243,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G2041" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -59269,7 +59269,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2042" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -59295,7 +59295,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G2043" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -59321,7 +59321,7 @@
         <v>11</v>
       </c>
       <c r="G2044" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -59347,7 +59347,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G2045" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -59373,7 +59373,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G2046" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -59399,7 +59399,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G2047" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -59425,7 +59425,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G2048" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -59451,7 +59451,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G2049" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -59477,7 +59477,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G2050" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -59503,7 +59503,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2051" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -59529,7 +59529,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G2052" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -59555,7 +59555,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G2053" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -59581,7 +59581,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2054" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -59607,7 +59607,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G2055" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -59633,7 +59633,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G2056" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -59659,7 +59659,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G2057" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -59685,7 +59685,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2058" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -59711,7 +59711,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G2059" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -59737,7 +59737,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G2060" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -59763,7 +59763,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G2061" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -59789,7 +59789,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2062" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -59815,7 +59815,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G2063" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -59841,7 +59841,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2064" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -59867,7 +59867,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2065" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -59893,7 +59893,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G2066" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -59919,7 +59919,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2067" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -59945,7 +59945,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2068" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -59971,7 +59971,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G2069" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -59997,7 +59997,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G2070" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -60023,7 +60023,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G2071" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -60049,7 +60049,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G2072" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -60075,7 +60075,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G2073" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -60101,7 +60101,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G2074" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -60127,7 +60127,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G2075" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -60153,7 +60153,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G2076" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -60179,7 +60179,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G2077" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -60205,7 +60205,7 @@
         <v>11.5</v>
       </c>
       <c r="G2078" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -60231,7 +60231,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G2079" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -60257,7 +60257,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G2080" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -60283,7 +60283,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G2081" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -60309,7 +60309,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G2082" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -60335,7 +60335,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2083" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -60361,7 +60361,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G2084" t="s">
-        <v>1510</v>
+        <v>328</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -60413,7 +60413,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G2086" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -60439,7 +60439,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G2087" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -60465,7 +60465,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2088" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -60543,7 +60543,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2091" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -61063,7 +61063,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G2111" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -61245,7 +61245,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2118" t="s">
-        <v>395</v>
+        <v>1416</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -61479,7 +61479,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2127" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -73473,7 +73473,7 @@
     </row>
     <row r="2589">
       <c r="A2589" s="1" t="n">
-        <v>46091.6911689815</v>
+        <v>46091.3333333333</v>
       </c>
       <c r="B2589" t="n">
         <v>574122</v>
@@ -73494,6 +73494,32 @@
         <v>1944</v>
       </c>
       <c r="H2589" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2590">
+      <c r="A2590" s="1" t="n">
+        <v>46092.6911689815</v>
+      </c>
+      <c r="B2590" t="n">
+        <v>325042</v>
+      </c>
+      <c r="C2590" t="n">
+        <v>8.85499954223633</v>
+      </c>
+      <c r="D2590" t="n">
+        <v>8.69499969482422</v>
+      </c>
+      <c r="E2590" t="n">
+        <v>8.69999980926514</v>
+      </c>
+      <c r="F2590" t="n">
+        <v>8.82499980926514</v>
+      </c>
+      <c r="G2590" t="s">
+        <v>1826</v>
+      </c>
+      <c r="H2590" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="1945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="1946">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16937780380249</t>
+    <t xml:space="preserve">7.16937875747681</t>
   </si>
   <si>
     <t xml:space="preserve">BRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13994836807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92740201950073</t>
+    <t xml:space="preserve">7.13994884490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92740106582642</t>
   </si>
   <si>
     <t xml:space="preserve">6.52519750595093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5415472984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42873382568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60040712356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78188848495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55135774612427</t>
+    <t xml:space="preserve">6.54154634475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42873334884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60040664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78188753128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55135679244995</t>
   </si>
   <si>
     <t xml:space="preserve">6.21291589736938</t>
@@ -74,22 +74,22 @@
     <t xml:space="preserve">6.19820213317871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2750449180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94641590118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20310688018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24888610839844</t>
+    <t xml:space="preserve">6.27504539489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94641494750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20310735702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24888515472412</t>
   </si>
   <si>
     <t xml:space="preserve">6.30610942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31919002532959</t>
+    <t xml:space="preserve">6.31918954849243</t>
   </si>
   <si>
     <t xml:space="preserve">6.38785886764526</t>
@@ -98,82 +98,82 @@
     <t xml:space="preserve">6.23090076446533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16713714599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05922842025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99219465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86466598510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70443773269653</t>
+    <t xml:space="preserve">6.16713666915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05922794342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99219417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86466550827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70443820953369</t>
   </si>
   <si>
     <t xml:space="preserve">5.35945844650269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51641464233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72242259979248</t>
+    <t xml:space="preserve">5.5164155960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72242307662964</t>
   </si>
   <si>
     <t xml:space="preserve">5.67500829696655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73223257064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03960847854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97420978546143</t>
+    <t xml:space="preserve">5.73223304748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03960800170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97420930862427</t>
   </si>
   <si>
     <t xml:space="preserve">6.11972284317017</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14097738265991</t>
+    <t xml:space="preserve">6.1409764289856</t>
   </si>
   <si>
     <t xml:space="preserve">6.10010290145874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2374415397644</t>
+    <t xml:space="preserve">6.23744106292725</t>
   </si>
   <si>
     <t xml:space="preserve">6.11154747009277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97584438323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07394313812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12953281402588</t>
+    <t xml:space="preserve">5.97584533691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07394361495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12953233718872</t>
   </si>
   <si>
     <t xml:space="preserve">6.21945667266846</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35188961029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32409477233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04675579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08272504806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1170597076416</t>
+    <t xml:space="preserve">6.35189008712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32409524917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04675531387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08272457122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11705875396729</t>
   </si>
   <si>
     <t xml:space="preserve">7.07945442199707</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">7.12032890319824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07127904891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06637573242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16120433807373</t>
+    <t xml:space="preserve">7.07128000259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0663743019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16120338439941</t>
   </si>
   <si>
     <t xml:space="preserve">7.14321947097778</t>
@@ -203,103 +203,103 @@
     <t xml:space="preserve">7.22987222671509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07618427276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26911211013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15302848815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15139436721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31489133834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43097543716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4031810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3557653427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1448540687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18899822235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16283798217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27401685714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998611450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35740089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40644931793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42279863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39337158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43914890289307</t>
+    <t xml:space="preserve">7.07618474960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26911306381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15302801132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1513934135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31489229202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43097639083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40317964553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35576486587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14485359191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18899917602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16283845901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2740159034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998706817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3574013710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40644979476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42279958724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39337062835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43915033340454</t>
   </si>
   <si>
     <t xml:space="preserve">7.47184991836548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51108741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76778173446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71546173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63534688949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68276166915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74162006378174</t>
+    <t xml:space="preserve">7.51108932495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76777935028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71546316146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63534593582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68276262283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74162101745605</t>
   </si>
   <si>
     <t xml:space="preserve">7.66968202590942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72200155258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63044023513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71055746078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85606861114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47736167907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50188732147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51006126403809</t>
+    <t xml:space="preserve">7.721999168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63044214248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71055603027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85606908798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47736072540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50188541412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51006031036377</t>
   </si>
   <si>
     <t xml:space="preserve">8.55093479156494</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">8.41196250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5199146270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45348262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51161098480225</t>
+    <t xml:space="preserve">8.51991558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45348167419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51161003112793</t>
   </si>
   <si>
     <t xml:space="preserve">8.4617862701416</t>
@@ -335,121 +335,121 @@
     <t xml:space="preserve">8.6112585067749</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63617134094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72751331329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96002674102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86868476867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86037826538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58634662628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27577590942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10969638824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30400943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31231307983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60295295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61956310272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56973648071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71921062469482</t>
+    <t xml:space="preserve">8.63617038726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72751426696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96002578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86868190765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86037921905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58634567260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27577495574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.109694480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30400848388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31231498718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60295391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61956405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56973838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71920967102051</t>
   </si>
   <si>
     <t xml:space="preserve">8.25916767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64135026931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25418663024902</t>
+    <t xml:space="preserve">7.64135074615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25418567657471</t>
   </si>
   <si>
     <t xml:space="preserve">8.05987358093262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20602130889893</t>
+    <t xml:space="preserve">8.20602321624756</t>
   </si>
   <si>
     <t xml:space="preserve">8.23757743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84729051589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6795482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67788743972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95524120330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02831649780273</t>
+    <t xml:space="preserve">7.84728813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67954778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67788696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95524215698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02831840515137</t>
   </si>
   <si>
     <t xml:space="preserve">8.05488872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97849273681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14457225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11301803588867</t>
+    <t xml:space="preserve">7.97849130630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14457416534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11301708221436</t>
   </si>
   <si>
     <t xml:space="preserve">8.23425674438477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10471439361572</t>
+    <t xml:space="preserve">8.10471343994141</t>
   </si>
   <si>
     <t xml:space="preserve">8.21100521087646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16782474517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32061958312988</t>
+    <t xml:space="preserve">8.16782283782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32061672210693</t>
   </si>
   <si>
     <t xml:space="preserve">8.37044239044189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50330543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36213684082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67769050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76903438568115</t>
+    <t xml:space="preserve">8.50330448150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.362135887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67768859863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76903533935547</t>
   </si>
   <si>
     <t xml:space="preserve">8.53652286529541</t>
@@ -461,31 +461,31 @@
     <t xml:space="preserve">8.64447498321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73581790924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68599510192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74412155151367</t>
+    <t xml:space="preserve">8.73581886291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68599414825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7441234588623</t>
   </si>
   <si>
     <t xml:space="preserve">8.6693868637085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48669815063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44517993927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4783935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40365695953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42856979370117</t>
+    <t xml:space="preserve">8.48669719696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4451789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47839546203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40365791320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42857074737549</t>
   </si>
   <si>
     <t xml:space="preserve">8.65277862548828</t>
@@ -494,43 +494,43 @@
     <t xml:space="preserve">8.69429874420166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71090793609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89359569549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84377098083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88529109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78564167022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80225086212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8188591003418</t>
+    <t xml:space="preserve">8.71090698242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89359474182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84377193450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88529014587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78564262390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8022518157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81885814666748</t>
   </si>
   <si>
     <t xml:space="preserve">8.90189838409424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05137062072754</t>
+    <t xml:space="preserve">9.05137157440186</t>
   </si>
   <si>
     <t xml:space="preserve">8.81055450439453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62786674499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70260238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82716178894043</t>
+    <t xml:space="preserve">8.62786483764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70260334014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82716274261475</t>
   </si>
   <si>
     <t xml:space="preserve">8.75242519378662</t>
@@ -539,67 +539,67 @@
     <t xml:space="preserve">9.04306697845459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14271450042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2838830947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35031509399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35861778259277</t>
+    <t xml:space="preserve">9.14271354675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28388404846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35031604766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35861968994141</t>
   </si>
   <si>
     <t xml:space="preserve">9.15102005004883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93511390686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77733898162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19254016876221</t>
+    <t xml:space="preserve">8.93511581420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7773380279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19253921508789</t>
   </si>
   <si>
     <t xml:space="preserve">9.44996356964111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17593002319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00154685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1344108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91850662231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9268102645874</t>
+    <t xml:space="preserve">9.17593097686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00154590606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13440990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91850757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92681121826172</t>
   </si>
   <si>
     <t xml:space="preserve">9.00985145568848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.984938621521</t>
+    <t xml:space="preserve">8.98493766784668</t>
   </si>
   <si>
     <t xml:space="preserve">8.76072978973389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11780261993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22575664520264</t>
+    <t xml:space="preserve">9.11780452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.225754737854</t>
   </si>
   <si>
     <t xml:space="preserve">8.95172119140625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06797981262207</t>
+    <t xml:space="preserve">9.06797885894775</t>
   </si>
   <si>
     <t xml:space="preserve">9.0762825012207</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">9.31709957122803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36692333221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49148464202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54961109161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96481132507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0229396820068</t>
+    <t xml:space="preserve">9.36692428588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49148368835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54961204528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96481037139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0229406356812</t>
   </si>
   <si>
     <t xml:space="preserve">9.82364368438721</t>
@@ -632,112 +632,112 @@
     <t xml:space="preserve">9.93990039825439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98142051696777</t>
+    <t xml:space="preserve">9.98141956329346</t>
   </si>
   <si>
     <t xml:space="preserve">10.0063323974609</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0561571121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2056274414062</t>
+    <t xml:space="preserve">10.0561552047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2056283950806</t>
   </si>
   <si>
     <t xml:space="preserve">10.2305402755737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2139320373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1973247528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1558046340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1225881576538</t>
+    <t xml:space="preserve">10.2139329910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1973237991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1558036804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1225891113281</t>
   </si>
   <si>
     <t xml:space="preserve">10.1807165145874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475009918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2222356796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1308917999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0976762771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84855651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3135814666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0810680389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0727643966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5294857025146</t>
+    <t xml:space="preserve">10.147500038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2222366333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1308937072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0976753234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84855556488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3135805130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0810689926147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0727624893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5294847488403</t>
   </si>
   <si>
     <t xml:space="preserve">10.4464445114136</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5211801528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.38831615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4713563919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6872606277466</t>
+    <t xml:space="preserve">10.5211820602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3883171081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4713554382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6872625350952</t>
   </si>
   <si>
     <t xml:space="preserve">10.720477104187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6540451049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4049253463745</t>
+    <t xml:space="preserve">10.6540441513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4049243927002</t>
   </si>
   <si>
     <t xml:space="preserve">10.6457424163818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7952136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.96129322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9280767440796</t>
+    <t xml:space="preserve">10.7952127456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9612941741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9280757904053</t>
   </si>
   <si>
     <t xml:space="preserve">10.7703008651733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7786045074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.869948387146</t>
+    <t xml:space="preserve">10.7786054611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8699493408203</t>
   </si>
   <si>
     <t xml:space="preserve">10.7869091033936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0360298156738</t>
+    <t xml:space="preserve">11.0360288619995</t>
   </si>
   <si>
     <t xml:space="preserve">10.8948612213135</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">11.2602367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851495742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3432769775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.393102645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.451229095459</t>
+    <t xml:space="preserve">11.2851505279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3432788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3931016921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4512300491333</t>
   </si>
   <si>
     <t xml:space="preserve">11.5093584060669</t>
@@ -779,46 +779,46 @@
     <t xml:space="preserve">11.5176620483398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7418689727783</t>
+    <t xml:space="preserve">11.7418718338013</t>
   </si>
   <si>
     <t xml:space="preserve">11.7584781646729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6920471191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.683741569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7252626419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7667827606201</t>
+    <t xml:space="preserve">11.692045211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6837425231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7252635955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7667808532715</t>
   </si>
   <si>
     <t xml:space="preserve">11.7169580459595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.592396736145</t>
+    <t xml:space="preserve">11.5923986434937</t>
   </si>
   <si>
     <t xml:space="preserve">11.7003507614136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5425729751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9577741622925</t>
+    <t xml:space="preserve">11.5425748825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9577732086182</t>
   </si>
   <si>
     <t xml:space="preserve">12.0574216842651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9162559509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9909896850586</t>
+    <t xml:space="preserve">11.9162549972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9909915924072</t>
   </si>
   <si>
     <t xml:space="preserve">11.98268699646</t>
@@ -827,16 +827,16 @@
     <t xml:space="preserve">12.1487665176392</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0491199493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2899341583252</t>
+    <t xml:space="preserve">12.0491189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2899351119995</t>
   </si>
   <si>
     <t xml:space="preserve">12.3895826339722</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3148469924927</t>
+    <t xml:space="preserve">12.3148460388184</t>
   </si>
   <si>
     <t xml:space="preserve">12.5058403015137</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">12.1902866363525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1985902786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0823354721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6422233581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5508785247803</t>
+    <t xml:space="preserve">12.1985921859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0823345184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6422214508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.550877571106</t>
   </si>
   <si>
     <t xml:space="preserve">11.8083019256592</t>
@@ -869,43 +869,43 @@
     <t xml:space="preserve">11.9346389770508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9514837265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0609769821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1620445251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7830352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6566982269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8083028793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7577657699585</t>
+    <t xml:space="preserve">11.9514846801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0609760284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1620454788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.783034324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6566972732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8083009719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7577676773071</t>
   </si>
   <si>
     <t xml:space="preserve">11.5977401733398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5640506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3029546737671</t>
+    <t xml:space="preserve">11.5640497207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3029556274414</t>
   </si>
   <si>
     <t xml:space="preserve">11.2018842697144</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1934623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0334358215332</t>
+    <t xml:space="preserve">11.1934614181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0334348678589</t>
   </si>
   <si>
     <t xml:space="preserve">10.9576320648193</t>
@@ -917,13 +917,13 @@
     <t xml:space="preserve">11.4208679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2271528244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2861070632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1681938171387</t>
+    <t xml:space="preserve">11.2271518707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2861080169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.168194770813</t>
   </si>
   <si>
     <t xml:space="preserve">10.923942565918</t>
@@ -932,22 +932,22 @@
     <t xml:space="preserve">11.0250120162964</t>
   </si>
   <si>
-    <t xml:space="preserve">10.763916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9492111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5786228179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7891826629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7386484146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6544237136841</t>
+    <t xml:space="preserve">10.7639169692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9492092132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5786199569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7891836166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7386493682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6544246673584</t>
   </si>
   <si>
     <t xml:space="preserve">10.7554931640625</t>
@@ -959,46 +959,46 @@
     <t xml:space="preserve">11.5219383239746</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2945318222046</t>
+    <t xml:space="preserve">11.2945308685303</t>
   </si>
   <si>
     <t xml:space="preserve">11.6398515701294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4629812240601</t>
+    <t xml:space="preserve">11.4629802703857</t>
   </si>
   <si>
     <t xml:space="preserve">11.4124450683594</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3619108200073</t>
+    <t xml:space="preserve">11.361909866333</t>
   </si>
   <si>
     <t xml:space="preserve">11.3197975158691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2103071212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9997444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.991322517395</t>
+    <t xml:space="preserve">11.2103052139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9997453689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9913234710693</t>
   </si>
   <si>
     <t xml:space="preserve">11.0081672668457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8902521133423</t>
+    <t xml:space="preserve">10.8902530670166</t>
   </si>
   <si>
     <t xml:space="preserve">10.9323654174805</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8734073638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8818302154541</t>
+    <t xml:space="preserve">10.8734083175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8818311691284</t>
   </si>
   <si>
     <t xml:space="preserve">10.6796913146973</t>
@@ -1007,88 +1007,88 @@
     <t xml:space="preserve">10.78076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8649873733521</t>
+    <t xml:space="preserve">10.8649854660034</t>
   </si>
   <si>
     <t xml:space="preserve">10.7049579620361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9155206680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2608413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.151349067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0839700698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0502805709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2524185180664</t>
+    <t xml:space="preserve">10.9155216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2608423233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1513481140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0839681625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0502796173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.252420425415</t>
   </si>
   <si>
     <t xml:space="preserve">11.3282203674316</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3787565231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.395601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5050916671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4040241241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.555627822876</t>
+    <t xml:space="preserve">11.3787574768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3956022262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5050945281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4040231704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5556268692017</t>
   </si>
   <si>
     <t xml:space="preserve">11.6819658279419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7493457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9177951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8841047286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.943060874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0525541305542</t>
+    <t xml:space="preserve">11.7493438720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9177932739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8841037750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9430627822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0525531768799</t>
   </si>
   <si>
     <t xml:space="preserve">12.0946664810181</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1536235809326</t>
+    <t xml:space="preserve">12.1536226272583</t>
   </si>
   <si>
     <t xml:space="preserve">12.0357084274292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0778207778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0441312789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1788911819458</t>
+    <t xml:space="preserve">12.0778198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.044132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1788902282715</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3136510848999</t>
+    <t xml:space="preserve">12.3136501312256</t>
   </si>
   <si>
     <t xml:space="preserve">12.3220729827881</t>
@@ -1097,49 +1097,49 @@
     <t xml:space="preserve">12.3726081848145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2041578292847</t>
+    <t xml:space="preserve">12.2041568756104</t>
   </si>
   <si>
     <t xml:space="preserve">12.2883834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2968034744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7914552688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7325000762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8167238235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.010440826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0020198822021</t>
+    <t xml:space="preserve">12.2968063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7914562225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7324991226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8167247772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0104417800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0020179748535</t>
   </si>
   <si>
     <t xml:space="preserve">11.9683294296265</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9262161254883</t>
+    <t xml:space="preserve">11.926215171814</t>
   </si>
   <si>
     <t xml:space="preserve">11.311375617981</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8144512176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6965360641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8986749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8228721618652</t>
+    <t xml:space="preserve">10.8144493103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6965351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8986740112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8228731155396</t>
   </si>
   <si>
     <t xml:space="preserve">11.0165910720825</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">10.9407873153687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7723388671875</t>
+    <t xml:space="preserve">10.7723369598389</t>
   </si>
   <si>
     <t xml:space="preserve">10.7976064682007</t>
@@ -1160,25 +1160,25 @@
     <t xml:space="preserve">10.7218027114868</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6628475189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6123123168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8060283660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6881141662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312969207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6712675094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4691295623779</t>
+    <t xml:space="preserve">10.6628465652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6123104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8060274124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6881132125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312950134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6712694168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4691286087036</t>
   </si>
   <si>
     <t xml:space="preserve">10.4859733581543</t>
@@ -1187,3078 +1187,3081 @@
     <t xml:space="preserve">11.0923919677734</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1597709655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1345043182373</t>
+    <t xml:space="preserve">11.1597728729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.134503364563</t>
   </si>
   <si>
     <t xml:space="preserve">11.1429271697998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187280654907</t>
+    <t xml:space="preserve">11.218729019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4545583724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.345067024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4270162582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3175249099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2417221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2838354110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1911878585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1574974060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2248783111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1659212112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1069612503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0985412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93009090423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98904800415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0058927536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7195291519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68583965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48370170593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37420845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.115385055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.309103012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5954666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7133798599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.603889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3596363067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3006792068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4522829055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4017515182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5617771148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5449314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.342791557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438619613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4101724624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4185953140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4354391098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2585668563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2333002090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.29225730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.149076461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0418567657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.536509513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2754135131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2080326080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0648508071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93851375579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0500860214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3848028182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3075609207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7710132598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6766080856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5993661880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2303190231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4706287384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.504958152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6422777175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6851892471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6594429016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7109384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.93408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6508588790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.745267868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.530704498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3933849334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3504724502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1444940567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.135910987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92135047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.075834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0586681365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89560127258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.947096824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74111747741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76686382293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85268783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87843704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99001026153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2560653686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2903966903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2732305526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135402679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.48779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.436297416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3333082199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0844163894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1273288726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0157556533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0329217910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84410572052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0415029525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2389011383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78402900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.706787109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77544593811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68103981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56088638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.689621925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47506046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48364162445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62954425811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91276550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88701820373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7582836151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56946754455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.578049659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73253440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.612380027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71537017822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82694149017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.187406539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2217359542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99859237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96426010131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86985397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69820404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86127281188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52655506134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21758651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23475170135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69405460357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52669525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4408712387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12332057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43228816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5224027633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41083240509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29926109313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16623210906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23060131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08469772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35504627227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22630882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48378372192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39366722106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57818984985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49236679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44945430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23489093780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11473751068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02032947540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79289197921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72852563858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77143621444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83151435852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00316429138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02891159057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00745582580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25205707550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28638648986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61681270599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.608229637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54815101623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75413131713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48807430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46232795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16193962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19197845458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98170804977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0889892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33788108825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81434917449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69848680496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99887275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81864070892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8658447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58691310882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63411808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68990325927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65986490249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96454381942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93879556655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73696613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82279109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47949314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38508415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40224933624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45374393463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36791896820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.496657371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50094795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46661853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59964656829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85712146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56960773468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56531715393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55673408508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53956890106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50523948669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50953006744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24776363372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15335655212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39795875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58248043060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77129554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65972423553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09743118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9686918258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.020188331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28624439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31199264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08026504516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.131760597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3205738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.942946434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.814208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78846073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.797043800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74554920196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72838401794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90861701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14034366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4235668182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26049709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18325519561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00302410125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96011161804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76271438598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65114212036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.685471534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67688846588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87428665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51797199249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44072914123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41498279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64670848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0672512054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93851470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.195987701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80977725982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62096309661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50938987731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86570453643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95152854919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83995532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75851821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77167510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74097347259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42080783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53484058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57869911193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58746910095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47343730926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55238246917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42957878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18397235870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37694931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56992626190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67957305908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66202831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89447975158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72781753540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72343063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9383373260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82430553436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06114101409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00851058959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85062026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71465969085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88570690155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11377048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0523681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28043174743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32429027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23657512664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9295654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80676174163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78921794891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4953670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45589447021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48221015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62255573272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92079448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07868385314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0172815322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17958736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1313419342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17081546783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96029567718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77170372009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61819887161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6488995552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63135814666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38574981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29803419113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39013624191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22347402572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20593166351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28048992156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27171754837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.512939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39890766143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26733255386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19277286529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4427661895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4515380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32873392105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53048229217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79363346099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98661041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0611686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22344589233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28923225402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35063552856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21905899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19274425506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30239105224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87257719039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72346019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60942888259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74100255966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83310651779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84187698364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67521524429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50855445861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4032940864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45592451095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44715213775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31557655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47346639633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85064935684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85942029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00854015350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04362678527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80679035186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91643714904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18835830688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25414657592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29361915588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36379146575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65325736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37256336212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43835067749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9646520614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12254238128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14885711669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37691974639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56112670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75410270690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70147323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47340869903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35060501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49095153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24534511566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42077922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31551933288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48218154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64884281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72778701782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80673313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77164745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85936260223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.815505027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86813354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92076396942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9997091293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87690734863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84182071685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89445018768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9821662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0698823928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96462345123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67515754699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71901702880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79796123504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29797554016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52603816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63129997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71024417877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68393039703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69270038604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76287364959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73655891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57866954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30674839019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21025848388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33306217193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20148754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02605533599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26288890838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13131427764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0874547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43832302093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42955017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21902942657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25411701202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15762901306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09622669219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39449310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.337477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34186172485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10502815246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92959356307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49978351593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60065650939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42960929870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11821413040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18400192260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57875633239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64892959594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5568265914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14017295837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3857798576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87702226638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9735107421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55244112014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11382722854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72784471511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82436275482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02172565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47349548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31560611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83316373825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9603533744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85070705413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61387252807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18405961990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47352504730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54369783401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89895105361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82439231872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64895820617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69720268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92965221405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06122732162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00859785079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05684185028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40332269668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59191417694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83752155303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69717311859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86822175979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81120538711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72348880767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48665380477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4822678565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36385059356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22788953781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77176189422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82000684738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26297616958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23227548599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21911764144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39455032348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59629917144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16207265853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51732444763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37259387969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33312082290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41645097732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79801893234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68398714065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55679845809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10067176818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35504961013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35066413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21031665802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23224544525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17522954940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10505676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20154476165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24540281295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21470355987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17084407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40767955780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25856113433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36820793151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32434940338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14891481399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24978923797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43838024139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16645860671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70155954360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61384296417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69278764724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75419044494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68401670455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71033191680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83313465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06119775772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1401424407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05681276321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04804086685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00856828689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94716691970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07435655593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08751344680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09628486633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01734018325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35943555831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29364824295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49101066589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60504198074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97345352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57434034347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41206502914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88576507568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99102544784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03926944732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06996917724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31119251251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48223924636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86380672454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92082357406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9997673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73661756515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68837404251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61381483078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62697124481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57872772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77609014511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240535736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96906614303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99099683761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15327072143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54799747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56995534896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82433462142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66644477844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71907329559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78486108779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86819267272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22780227661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17517280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39446449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83304691314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58744049072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40323543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36814975738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35937690734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53481101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46463775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50849628448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41200637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38569259643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61375617980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49972438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03482437133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74533176422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90322113037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0961990356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1225128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.938307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66638660430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88567733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45586490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51726722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44709300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82427597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56989669799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94710826873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16639995574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28920364379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27166175842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34183502197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19271469116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18394470214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90324974060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06991195678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84184837341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99973773956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97342395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18857192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19807243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18909931182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43138980865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57496929168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72752285003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79931259155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81725883483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94289207458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98776054382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79033851623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74547004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68265438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70060157775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52112674713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51215267181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35062599182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53010082244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63778495788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61086368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69162750244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5031795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58394336700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60189056396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55702114105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5480489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35960006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76341819763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64675903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29678344726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33267784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3865213394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39549446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7723913192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8890495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3915777206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5800256729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.651816368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6877107620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7415533065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8582124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9389743804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9838438034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0556335449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1005020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0915279388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1274242401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.019739151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9300012588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312902450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376863479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0107660293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9748697280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8761587142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9120540618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0466604232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.921028137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8941068649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9030809402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8043699264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.75950050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7864227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8402643203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4274730682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2569723129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90699768066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96083927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1223669052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1313400268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1403141021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0954456329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87110137939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80828666687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56599617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47625923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67368030548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70957565307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75444316864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84418106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85315418243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82623386383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86212825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0236558914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96981239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1672353744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492872238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2031297683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1851835250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2838935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3377361297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4454212188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5172100067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3467092514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3018407821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4184989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4364471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7774486541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8492383956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6966848373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7684745788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5620794296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0864715576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2479991912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.490288734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5979747772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8671855926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1453714370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9658975601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9569234848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.082555770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1094760894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1722917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2440814971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2261352539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.190239906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.459451675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6299524307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8004531860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0068492889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6568727493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8453226089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2171611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2081880569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3248462677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2620306015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1363973617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8223171234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3287620544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3736305236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.544132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7056589126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6159210205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4095258712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7146320343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6248950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4005517959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6069478988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44933700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81668853759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01354026794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0225133895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15711975097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48914909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20198917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3455696105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53850364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67759609222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09038734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96924304962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01859855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10833549499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18012523651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13525676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98270320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79874229431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90642738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34165191650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25191497802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08141422271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97372913360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03654479980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83014965057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43979263305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26480484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36351585388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27377796173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30967330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35005474090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36800289154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51606941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94232082366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70900440216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57439804077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45773983001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46671390533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61478042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4936351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30070018768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18404197692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25134372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12571144104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88399219512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65573310852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6856861114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5844087600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63044357299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87903022766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0539627075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2104806900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95268630981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98030662536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.035548210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89744472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0631694793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1184110641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1552381515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63965034484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40027141571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22533893585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44630527496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87087345123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95833778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98595905303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02278614044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03199481964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66832065582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62228584289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67292404174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77419948577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73737239837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53482055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52561283111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30464744567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35988807678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80642318725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08263206481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8570613861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88928604125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82023525238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60847663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90309619903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00437259674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06882190704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1056489944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14247798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99976921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71895885467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86166572570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17470073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47392654418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5936164855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6488561630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77775478363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72251415252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55678844451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75934028625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171997070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66727161407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37265014648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53837394714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21613216400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84325122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00897598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92611408233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59466361999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56244087219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57164764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44274997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38750839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45195770263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14352607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1251106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23559474945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23099040985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42433643341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76959609985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75578594207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79261302947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51640605926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31385326385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33226680755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21718120574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09749126434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01923179626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77985191345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88112878799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83049058914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82588672637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4944372177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8212833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97319746017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31845664978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2217845916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34147548675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30924987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29544067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68213081359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47037124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61307907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66371726989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73276901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90769958496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91690635681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97214889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79721736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.193115234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54758071899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82378959655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79616928100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74092674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80537509918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0723752975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.219687461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8641719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7260675430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6892395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444820404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5143089294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2381010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3393774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841348648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3209638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1368255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1828603744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3485841751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.192066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0815830230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90665149688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85140991210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94347953796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86061668395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7501335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65806484222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60282421112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48313331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62123680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8329963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.146032333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1276178359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2473087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4866876602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5327224731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7721033096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6800336837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4038257598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7352743148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5695495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6616201400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9286203384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9654474258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3889665603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7940711975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1163129806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2912464141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3372793197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1623487472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9874172210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0886926651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8585195541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.318865776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3649015426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2820377349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2083826065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2636241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6779365539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8620738983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7275247573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7367334365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4789390563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1290760040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5950736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8252477645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896961212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5582466125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6963500976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6134872436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0058298110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.913761138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.171555519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0518655776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2267961502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2175893783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3280725479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9966230392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9321756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4293489456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7700052261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2728309631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5674533843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.503005027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4661769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4845905303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3096590042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.024245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1991758346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2544183731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6503143310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0738334655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2855939865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2579717636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1751098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2119388580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1659030914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3040075302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2947998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3417453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1821327209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9849634170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3041896820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2854108810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3323564529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3511343002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5389137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6891374588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5013580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4450235366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4168567657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4544134140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4919681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6140260696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9895849227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9614171981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7548599243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8299722671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5952472686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5201349258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.703293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3840684890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3652906417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2150678634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3183460235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5061254501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6000156402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7502393722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6469612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6281814575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5249032974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5342931747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4404029846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2526226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4028463363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3277349472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1493434906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2901792526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2244567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2620124816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5155143737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4310140609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1211767196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0836210250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4122352600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0930099487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2338447570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0272874832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9803428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9333972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0178985595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1305665969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0648441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2056789398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9991207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8488969802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9240083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7268400192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9146194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9897317886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0554552078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0460653305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0742321014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9709529876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8770627975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7737846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3512811660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4827260971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6047830581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5578384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5484495162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6329507827759</t>
   </si>
   <si>
     <t xml:space="preserve">11.4545593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3450660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4270181655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3175239562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2417230606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2838335037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1911869049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1574974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2248783111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1659202575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1069622039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0985403060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93008995056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98904895782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0058937072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71953010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68583965301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48369979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37420845031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1153860092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3091020584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5954666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7133808135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.603889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.359637260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3006792068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4522838592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4017496109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5617761611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5449314117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3427925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4101724624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4185943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4354391098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2585678100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2333002090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2922582626343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1490755081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0418577194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5365085601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.275411605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2080335617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0648508071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93851375579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0500869750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3848028182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3075618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.771014213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6766080856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.599365234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2303190231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.470627784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5049571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.642276763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6851902008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.659441947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7109384536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.93408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6508598327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.745267868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5307054519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.393385887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3504724502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.144492149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1359119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92135047912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.075834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.058669090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89560127258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.947096824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74111652374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76686477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85268878936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87843608856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99001026153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2560653686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2903957366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2732315063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135402679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4877939224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4362983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3333082199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0844144821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.127329826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0157556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0329217910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84410572052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.04150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.23890209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78402805328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.706787109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77544593811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68103981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56088542938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68962383270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47505855560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.483642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62954616546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.912766456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88702011108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75828266143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56946754455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57804870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73253440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.612380027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71537017822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82694244384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1874074935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.221734046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99859142303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96426105499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86985492706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69820404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86127090454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52655601501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21758556365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23475074768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69405460357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52669525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44087028503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12331867218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43228816986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5224027633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41083240509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29926013946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16623115539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23060131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08469676971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35504627227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22630882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48378372192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39366817474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57819080352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49236679077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44945335388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23489093780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11473655700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02032947540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79289293289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72852373123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77143621444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83151340484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00316429138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02891063690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00745582580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25205707550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28638648986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61681175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60823059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54815101623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75413227081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48807430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.462327003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16193962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19197845458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98170709609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08898830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33788108825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81435108184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.698486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99887466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81864070892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86584424972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58691310882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.634117603302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68990278244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6598653793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96454381942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93879508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73696613311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82279014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47949314117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38508319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40224933624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45374393463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36792087554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.496657371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50094795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46661758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59964752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85712146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56960678100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56531715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55673408508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53956985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50523948669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50953006744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24776554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15335750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39795875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58248043060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77129650115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65972328186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0974292755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96869373321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02018737792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28624439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31199359893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08026599884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.131760597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32057476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94294548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81420803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78846073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79704475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74554824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72838497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.908616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14034366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42356491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26049709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18325519561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00302410125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96011161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76271343231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65114116668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.685471534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67688941955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87428665161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51797199249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44073009490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41498279571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64670944213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0672521591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1959886550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80977630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62096118927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50938987731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86570358276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95152854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83995628356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75851726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77167415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74097442626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42080879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53483963012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57869815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58747005462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47343826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55238342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42958068847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18397235870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37695026397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56992626190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67957401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66202831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89447975158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7541332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72781753540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72343063354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9383373260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82430553436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06113910675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00850963592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85062026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71465969085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88570785522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0523681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28043270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32429027557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23657417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9295654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80676174163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78921985626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49536895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45589542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48221015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62255764007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92079448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07868385314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01728057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17958736419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1313419342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17081546783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96029567718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77170467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61819887161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64890050888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63135719299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38575029373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29803371429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39013624191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22347354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20593166351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28048992156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27171802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51293897628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39890813827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26733255386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19277334213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44276571273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45153856277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32873439788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53048372268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79363393783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98661136627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0611686706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22344589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28923225402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35063457489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21905899047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1927433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30239009857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87257814407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72346019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60942888259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74100351333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83310604095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84187793731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67521524429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50855445861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40329456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45592403411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44715213775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31557703018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4734673500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8506498336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85942077636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0085391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04362678527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80679035186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91643714904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18835926055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25414562225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29361820220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36379146575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65325736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37256336212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43835163116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9646520614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12254238128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1488561630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37692165374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56112575531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75410175323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70147323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47340869903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35060596466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49095153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24534511566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42078018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31552028656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48218154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64884281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72778701782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80673313140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77164745330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85936260223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81550407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86813449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92076396942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9997091293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87690734863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84182071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89445018768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98216533660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0698823928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96462249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67515754699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71901512145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79796123504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29797554016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52603912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63129997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71024513244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68392848968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69270133972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76287460327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73655986785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57866954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30674839019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21025848388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33306312561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20148754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0260534286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26288890838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13131332397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08745384216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43832302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42955112457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21902942657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25411701202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15762901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09622573852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39449310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33747577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34186267852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10502815246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92959451675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4997820854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60065698623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4296088218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11821460723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18400144577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57875633239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64892959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5568265914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14017200469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3857798576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87702226638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9735107421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55244064331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11382818222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72784519195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82436275482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02172565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4734959602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31560564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83316421508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96035289764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85070705413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61387252807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18406009674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47352457046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54369831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89895105361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82439231872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64895868301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69720268249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92965221405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06122779846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0085973739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05684185028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40332269668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59191370010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83752107620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69717359542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86822175979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81120538711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72348880767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48665332794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4822678565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36385059356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22788906097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77176237106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82000637054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26297521591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23227548599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21911716461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39455080032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59629964828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16207218170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51732540130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37259340286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33312082290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4164514541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.798020362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68398714065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55679845809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10067176818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35504961013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35066413879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21031665802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23224544525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17522954940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10505676269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20154476165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24540281295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21470260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17084407806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40767908096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25856065750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36820793151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32434892654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14891481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24978828430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4383807182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16645812988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70156002044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61384248733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69278764724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75418996810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68401670455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71033096313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83313465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06119823455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14014291763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05681228637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04804134368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00856781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94716691970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07435607910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08751344680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09628534317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01734018325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35943508148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29364776611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4910101890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60504245758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97345304489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57434034347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41206502914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88576507568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9910249710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0392689704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06997013092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31119155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48223924636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8638072013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92082262039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99976682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73661756515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68837261199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61381435394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62697172164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57872772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77609014511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.802405834198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96906566619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99099588394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15327167510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54799842834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56995487213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82433414459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66644430160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71907377243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78486204147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86819314956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22780132293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17517185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39446544647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83304786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58744144439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40323543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36814975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35937786102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53481101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46463680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50849628448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41200828552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38569355010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61375617980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49972438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03482437133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74533176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90322303771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0961971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1225118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.938307762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638660430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88567733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45586490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51726818084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44709491729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82427597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56989765167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94710922241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16639995574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28920459747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27165985107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34183502197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19271469116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18394374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90324974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06991195678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84184837341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9997386932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97342300415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18857097625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19807243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1890983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43138885498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57496929168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7275218963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79931259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81725883483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94289207458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98776054382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79033756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74547004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68265342712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70060253143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52112579345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51215267181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35062599182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53010082244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63778495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61086368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69162750244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50317859649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58394336700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60188961029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55702114105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5480489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35960006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76341724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64675998687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29678249359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33267784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38652038574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39549541473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77239227294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88905048370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3915786743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5800266265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6518154144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6877117156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7415542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8582124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9389753341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9838438034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0556344985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1005029678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0915298461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.127423286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0197401046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9300022125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0107660293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9748697280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8761587142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.912055015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0466613769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.921028137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8941078186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9030809402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8043699264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.75950050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7864227294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8402643203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.427472114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2569723129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90699672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96084022521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1223659515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1313400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1403141021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0954456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87110233306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8082857131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56599617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47625923156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67368030548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70957374572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75444412231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84418106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85315418243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82623291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86212825775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0236558914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96981334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1672353744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492881774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2031288146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1851825714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2838945388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3377370834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4454212188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5172109603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3467092514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3018407821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4184999465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4364471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7774486541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8492383956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6966867446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7684745788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5620784759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0864715576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2479991912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4902896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5979747772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8671855926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1453714370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9658975601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9569225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.082555770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1094770431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1722927093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.244083404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2261352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1902408599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4594526290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6299533843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8004531860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0068492889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6568746566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8453226089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2171621322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2081880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3248462677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2620306015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1363983154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8223180770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3287620544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.373631477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5441312789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7056589126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6159219741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4095258712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7146329879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6248950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4005517959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6069478988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44933700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81668853759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01354026794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0225133895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15712070465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48914813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20198917388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34556865692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53850364685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67759609222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09038734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96924209594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01859855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10833358764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18012428283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13525676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98270320892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79874134063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34165287017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25191593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08141326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97372913360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03654479980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83015060424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43979167938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26480484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36351490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27377796173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30967330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35005569458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36800193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51606941223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94232177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70900440216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57439804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45773887634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46671390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61478042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4936351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30069923400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18404102325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25134372711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12571239471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88399028778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65573215484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6856861114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58440971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63044357299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87902927398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0539627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2104806900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95268726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98030662536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.035548210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89744567871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0631694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1184110641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1552391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63965129852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40027046203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22533893585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44630527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87087249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95833778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98595905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02278614044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03199481964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66832065582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62228584289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67292404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77419948577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73737239837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53482055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52561283111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30464744567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35988807678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80642318725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08263206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8570613861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88928604125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82023525238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60847568511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90309715270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00437259674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06882190704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10564994812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14247703552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99976921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71895885467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86166572570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17470169067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47392654418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5936164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6488561630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77775478363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72251415252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55678844451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75934028625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171901702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66727161407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37265014648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53837394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21613216400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84325122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00897598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92611408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59466457366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56244087219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57164764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44275093078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38750839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45195770263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14352512359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12511157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23559474945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23099040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42433643341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76959609985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75578594207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7926139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51640605926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3138542175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33226776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2171802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09749126434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01923179626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77985191345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88112878799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83049058914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82588672637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4944372177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82128238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97319746017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31845760345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2217845916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34147548675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30924987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29543972015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68213081359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47037124633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61307811737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66371631622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73276805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90769958496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91690731048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97214889526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79721736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19311428070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54758071899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82378959655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79616928100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74092674255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80537509918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0723752975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.219687461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8641719818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7260665893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6892404556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444829940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5143089294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2381010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.339376449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841358184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3209638595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1368246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1828603744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3485841751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1920652389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0815830230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90665149688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85140991210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94347953796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86061668395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7501335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6580638885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60282325744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48313331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62123680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8329963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.146032333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1276178359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2473077774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4866886138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5327224731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7721033096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6800336837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4038257598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7352743148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5695495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6616201400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9286193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9654483795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3889665603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7940721511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1163129806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2912454605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3372793197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1623487472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9874172210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0886926651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8585195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.318865776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3649015426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2820377349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2083826065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2636241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6779365539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8620748519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7275247573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7367334365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4789390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1290760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5950736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8252468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8896961212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5582466125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6963500976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6134872436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0058298110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.913761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.171555519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0518655776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2267961502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2175903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3280735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9966239929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9321756362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4293489456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7700052261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2728319168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5674524307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.503005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4661769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4845905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3096580505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.024245262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1991758346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2544183731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6503143310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0738334655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2855930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2579717636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1751098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2119388580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1659030914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3040065765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2947998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3417453765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1821327209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9849634170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3041896820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2854108810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3323564529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3511343002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5389137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6891374588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5013580322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4450235366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4168567657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4544134140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4919681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6140260696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9895849227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9614171981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7548599243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8299722671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5952472686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5201349258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.703293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3840684890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3652906417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2150678634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3183460235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5061254501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6000156402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7502393722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6469612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6281814575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5249032974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5342931747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4404029846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2526226043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4028463363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3277349472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1493434906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2901792526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2244567871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2620124816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5155143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4310140609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1211767196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0836210250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4122352600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0930099487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2338447570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0272874832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9803428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9333972930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0178985595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1305665969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0648441314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2056789398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9991207122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8488969802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9240083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7268400192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9146194458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9897317886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0554552078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0460653305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0742321014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9709529876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8770627975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7737846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3512811660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4827260971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6047830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5578384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5484495162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6329507827759</t>
-  </si>
-  <si>
     <t xml:space="preserve">11.5108938217163</t>
   </si>
   <si>
@@ -4460,9 +4463,6 @@
     <t xml:space="preserve">10.3936042785645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.309103012085</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.2621583938599</t>
   </si>
   <si>
@@ -5847,6 +5847,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.72500038146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -27991,7 +27994,7 @@
         <v>11.5680379867554</v>
       </c>
       <c r="G839" t="s">
-        <v>439</v>
+        <v>621</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -28043,7 +28046,7 @@
         <v>11.8677282333374</v>
       </c>
       <c r="G841" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -28225,7 +28228,7 @@
         <v>11.4181928634644</v>
       </c>
       <c r="G848" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -28277,7 +28280,7 @@
         <v>11.1984195709229</v>
       </c>
       <c r="G850" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -28329,7 +28332,7 @@
         <v>11.0685548782349</v>
       </c>
       <c r="G852" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -28407,7 +28410,7 @@
         <v>10.3193292617798</v>
       </c>
       <c r="G855" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -28433,7 +28436,7 @@
         <v>10.419225692749</v>
       </c>
       <c r="G856" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -28459,7 +28462,7 @@
         <v>10.2893600463867</v>
       </c>
       <c r="G857" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -28511,7 +28514,7 @@
         <v>9.97468566894531</v>
       </c>
       <c r="G859" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -28537,7 +28540,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G860" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -28563,7 +28566,7 @@
         <v>9.9547061920166</v>
       </c>
       <c r="G861" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28589,7 +28592,7 @@
         <v>9.59008312225342</v>
       </c>
       <c r="G862" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -28615,7 +28618,7 @@
         <v>9.71994876861572</v>
       </c>
       <c r="G863" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28641,7 +28644,7 @@
         <v>9.7698974609375</v>
       </c>
       <c r="G864" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28667,7 +28670,7 @@
         <v>9.77988719940186</v>
       </c>
       <c r="G865" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28693,7 +28696,7 @@
         <v>9.65002059936523</v>
       </c>
       <c r="G866" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28719,7 +28722,7 @@
         <v>9.73992824554443</v>
       </c>
       <c r="G867" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28745,7 +28748,7 @@
         <v>9.60007286071777</v>
       </c>
       <c r="G868" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28771,7 +28774,7 @@
         <v>9.32036209106445</v>
       </c>
       <c r="G869" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28797,7 +28800,7 @@
         <v>9.54013538360596</v>
       </c>
       <c r="G870" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28823,7 +28826,7 @@
         <v>9.75990772247314</v>
       </c>
       <c r="G871" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28849,7 +28852,7 @@
         <v>9.88477897644043</v>
       </c>
       <c r="G872" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28875,7 +28878,7 @@
         <v>9.8647985458374</v>
       </c>
       <c r="G873" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -28901,7 +28904,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G874" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28927,7 +28930,7 @@
         <v>10.1295261383057</v>
       </c>
       <c r="G875" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28953,7 +28956,7 @@
         <v>9.96969127655029</v>
       </c>
       <c r="G876" t="s">
-        <v>644</v>
+        <v>547</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -29031,7 +29034,7 @@
         <v>9.8647985458374</v>
       </c>
       <c r="G879" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -29213,7 +29216,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G886" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -29239,7 +29242,7 @@
         <v>9.97468566894531</v>
       </c>
       <c r="G887" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -29551,7 +29554,7 @@
         <v>9.96969127655029</v>
       </c>
       <c r="G899" t="s">
-        <v>644</v>
+        <v>547</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29577,7 +29580,7 @@
         <v>9.98966979980469</v>
       </c>
       <c r="G900" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29811,7 +29814,7 @@
         <v>9.73992824554443</v>
       </c>
       <c r="G909" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -30669,7 +30672,7 @@
         <v>9.65002059936523</v>
       </c>
       <c r="G942" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -38287,7 +38290,7 @@
         <v>9.54013538360596</v>
       </c>
       <c r="G1235" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -57241,7 +57244,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1964" t="s">
-        <v>395</v>
+        <v>1415</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -57267,7 +57270,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1965" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -57293,7 +57296,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1966" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -57319,7 +57322,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -57345,7 +57348,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1968" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -57371,7 +57374,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1969" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -57397,7 +57400,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G1970" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -57423,7 +57426,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1971" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -57449,7 +57452,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1972" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -57475,7 +57478,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1973" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -57501,7 +57504,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1974" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -57527,7 +57530,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G1975" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -57553,7 +57556,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1976" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -57579,7 +57582,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1977" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -57605,7 +57608,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1978" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -57631,7 +57634,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1979" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -57657,7 +57660,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1980" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -57683,7 +57686,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1981" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -57709,7 +57712,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1982" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -57735,7 +57738,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G1983" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -57761,7 +57764,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1984" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -57787,7 +57790,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1985" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -57813,7 +57816,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G1986" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -57839,7 +57842,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1987" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -57865,7 +57868,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G1988" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -57891,7 +57894,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G1989" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -57917,7 +57920,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1990" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -57943,7 +57946,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G1991" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -57969,7 +57972,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1992" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -57995,7 +57998,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1993" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -58021,7 +58024,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1994" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -58047,7 +58050,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1995" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -58073,7 +58076,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G1996" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -58099,7 +58102,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1997" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -58125,7 +58128,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G1998" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -58151,7 +58154,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -58177,7 +58180,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G2000" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -58203,7 +58206,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G2001" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -58229,7 +58232,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G2002" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -58255,7 +58258,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2003" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -58281,7 +58284,7 @@
         <v>10.5</v>
       </c>
       <c r="G2004" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -58307,7 +58310,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G2005" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -58333,7 +58336,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2006" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -58359,7 +58362,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2007" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -58385,7 +58388,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G2008" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -58411,7 +58414,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2009" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -58437,7 +58440,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2010" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -58463,7 +58466,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2011" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -58489,7 +58492,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2012" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -58515,7 +58518,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G2013" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -58541,7 +58544,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G2014" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -58567,7 +58570,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G2015" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -58593,7 +58596,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2016" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -58619,7 +58622,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G2017" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -58645,7 +58648,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G2018" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -58671,7 +58674,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2019" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -58697,7 +58700,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G2020" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -58723,7 +58726,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2021" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -58749,7 +58752,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2022" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -58775,7 +58778,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G2023" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -58801,7 +58804,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G2024" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -58827,7 +58830,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2025" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -58853,7 +58856,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2026" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -58879,7 +58882,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G2027" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -58905,7 +58908,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G2028" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -58931,7 +58934,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2029" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -58957,7 +58960,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G2030" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -58983,7 +58986,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G2031" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -59009,7 +59012,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2032" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -59035,7 +59038,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2033" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -59061,7 +59064,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2034" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -59087,7 +59090,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G2035" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -59113,7 +59116,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2036" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -59139,7 +59142,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2037" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -59165,7 +59168,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2038" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -59191,7 +59194,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G2039" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -59217,7 +59220,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2040" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -59243,7 +59246,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G2041" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -59269,7 +59272,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2042" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -59295,7 +59298,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G2043" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -59321,7 +59324,7 @@
         <v>11</v>
       </c>
       <c r="G2044" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -59347,7 +59350,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G2045" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -59373,7 +59376,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G2046" t="s">
-        <v>1482</v>
+        <v>415</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -59399,7 +59402,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G2047" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -59711,7 +59714,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G2059" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -59841,7 +59844,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2064" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -60153,7 +60156,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G2076" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -60179,7 +60182,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G2077" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -60413,7 +60416,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G2086" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -60543,7 +60546,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2091" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -61245,7 +61248,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2118" t="s">
-        <v>395</v>
+        <v>1415</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -73525,7 +73528,7 @@
     </row>
     <row r="2591">
       <c r="A2591" s="1" t="n">
-        <v>46093.6911574074</v>
+        <v>46093.3333333333</v>
       </c>
       <c r="B2591" t="n">
         <v>296960</v>
@@ -73546,6 +73549,56 @@
         <v>1944</v>
       </c>
       <c r="H2591" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2592">
+      <c r="A2592" s="1" t="n">
+        <v>46094.3333333333</v>
+      </c>
+      <c r="B2592" t="n">
+        <v>329288</v>
+      </c>
+      <c r="C2592" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="D2592" t="n">
+        <v>8.5649995803833</v>
+      </c>
+      <c r="E2592" t="n">
+        <v>8.64500045776367</v>
+      </c>
+      <c r="F2592"/>
+      <c r="G2592" t="s">
+        <v>1945</v>
+      </c>
+      <c r="H2592" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2593">
+      <c r="A2593" s="1" t="n">
+        <v>46094.6911458333</v>
+      </c>
+      <c r="B2593" t="n">
+        <v>329288</v>
+      </c>
+      <c r="C2593" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="D2593" t="n">
+        <v>8.5649995803833</v>
+      </c>
+      <c r="E2593" t="n">
+        <v>8.64500045776367</v>
+      </c>
+      <c r="F2593" t="n">
+        <v>8.77000045776367</v>
+      </c>
+      <c r="G2593" t="s">
+        <v>1865</v>
+      </c>
+      <c r="H2593" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1955" uniqueCount="1955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="1956">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16937780380249</t>
+    <t xml:space="preserve">7.16937875747681</t>
   </si>
   <si>
     <t xml:space="preserve">BRE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13994836807251</t>
+    <t xml:space="preserve">7.13994884490967</t>
   </si>
   <si>
     <t xml:space="preserve">6.92740154266357</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52519750595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54154634475708</t>
+    <t xml:space="preserve">6.52519702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54154682159424</t>
   </si>
   <si>
     <t xml:space="preserve">6.42873382568359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60040616989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78188848495483</t>
+    <t xml:space="preserve">6.60040664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78188800811768</t>
   </si>
   <si>
     <t xml:space="preserve">6.55135679244995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21291637420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19820213317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27504587173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94641542434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2031078338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24888610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3061089515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31919050216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38785934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23090076446533</t>
+    <t xml:space="preserve">6.21291589736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19820165634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27504539489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94641494750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20310688018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2488865852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30610942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31918954849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38785886764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23089981079102</t>
   </si>
   <si>
     <t xml:space="preserve">6.16713714599609</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">5.70443773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35945844650269</t>
+    <t xml:space="preserve">5.35945796966553</t>
   </si>
   <si>
     <t xml:space="preserve">5.5164155960083</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">5.72242212295532</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67500782012939</t>
+    <t xml:space="preserve">5.67500877380371</t>
   </si>
   <si>
     <t xml:space="preserve">5.73223304748535</t>
@@ -134,34 +134,34 @@
     <t xml:space="preserve">5.97420930862427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11972284317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14097738265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10010290145874</t>
+    <t xml:space="preserve">6.11972188949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14097785949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1001033782959</t>
   </si>
   <si>
     <t xml:space="preserve">6.23744058609009</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11154794692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9758448600769</t>
+    <t xml:space="preserve">6.11154699325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97584581375122</t>
   </si>
   <si>
     <t xml:space="preserve">6.07394313812256</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12953329086304</t>
+    <t xml:space="preserve">6.12953233718872</t>
   </si>
   <si>
     <t xml:space="preserve">6.2194561958313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35188961029053</t>
+    <t xml:space="preserve">6.35188913345337</t>
   </si>
   <si>
     <t xml:space="preserve">6.32409524917603</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">7.04675579071045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08272457122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1170597076416</t>
+    <t xml:space="preserve">7.08272504806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11705923080444</t>
   </si>
   <si>
     <t xml:space="preserve">7.07945442199707</t>
@@ -185,79 +185,79 @@
     <t xml:space="preserve">7.07127904891968</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06637525558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16120386123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14321899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24949216842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1415843963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22987174987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07618427276611</t>
+    <t xml:space="preserve">7.06637477874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16120433807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14321994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24949169158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14158487319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22987222671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07618379592896</t>
   </si>
   <si>
     <t xml:space="preserve">7.26911211013794</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1530294418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15139293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31489133834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43097448348999</t>
+    <t xml:space="preserve">7.15302801132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15139389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31489086151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43097496032715</t>
   </si>
   <si>
     <t xml:space="preserve">7.4031810760498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3557653427124</t>
+    <t xml:space="preserve">7.35576581954956</t>
   </si>
   <si>
     <t xml:space="preserve">7.14485359191895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18899774551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16283845901489</t>
+    <t xml:space="preserve">7.18899869918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16283798217773</t>
   </si>
   <si>
     <t xml:space="preserve">7.27401733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30998802185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3574013710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40644884109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42280006408691</t>
+    <t xml:space="preserve">7.30998754501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35740041732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40644931793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42279958724976</t>
   </si>
   <si>
     <t xml:space="preserve">7.39337110519409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43914937973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47184753417969</t>
+    <t xml:space="preserve">7.43914842605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47184896469116</t>
   </si>
   <si>
     <t xml:space="preserve">7.51108837127686</t>
@@ -269,58 +269,58 @@
     <t xml:space="preserve">7.71546173095703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63534736633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68276119232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74162101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66968297958374</t>
+    <t xml:space="preserve">7.63534593582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68276166915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7416205406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66968250274658</t>
   </si>
   <si>
     <t xml:space="preserve">7.72200059890747</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63044261932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7105565071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85606861114502</t>
+    <t xml:space="preserve">7.63044166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71055746078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85606908798218</t>
   </si>
   <si>
     <t xml:space="preserve">8.47735977172852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50188541412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51006126403809</t>
+    <t xml:space="preserve">8.50188636779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51005935668945</t>
   </si>
   <si>
     <t xml:space="preserve">8.55093479156494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42831230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36291313171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35473728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41196155548096</t>
+    <t xml:space="preserve">8.42831134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36291217803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.354736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41196346282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.51991558074951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45348358154297</t>
+    <t xml:space="preserve">8.45348262786865</t>
   </si>
   <si>
     <t xml:space="preserve">8.51161098480225</t>
@@ -329,49 +329,49 @@
     <t xml:space="preserve">8.46178531646729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47008991241455</t>
+    <t xml:space="preserve">8.47009086608887</t>
   </si>
   <si>
     <t xml:space="preserve">8.61125755310059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63617038726807</t>
+    <t xml:space="preserve">8.63617134094238</t>
   </si>
   <si>
     <t xml:space="preserve">8.72751426696777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96002674102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86868286132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86037826538086</t>
+    <t xml:space="preserve">8.96002578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86868190765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86037921905518</t>
   </si>
   <si>
     <t xml:space="preserve">8.58634662628174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27577495574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10969638824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30400943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3123140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60295486450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61956214904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56973743438721</t>
+    <t xml:space="preserve">8.27577590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10969543457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30401039123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31231498718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60295391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61956310272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56973838806152</t>
   </si>
   <si>
     <t xml:space="preserve">8.71921062469482</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">8.25916862487793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64135026931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25418567657471</t>
+    <t xml:space="preserve">7.64135074615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25418663024902</t>
   </si>
   <si>
     <t xml:space="preserve">8.0598726272583</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">8.23757743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84728908538818</t>
+    <t xml:space="preserve">7.84728860855103</t>
   </si>
   <si>
     <t xml:space="preserve">7.67954874038696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67788791656494</t>
+    <t xml:space="preserve">7.6778883934021</t>
   </si>
   <si>
     <t xml:space="preserve">7.95524024963379</t>
@@ -410,31 +410,31 @@
     <t xml:space="preserve">8.02831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05489063262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97849273681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14457321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11301708221436</t>
+    <t xml:space="preserve">8.05488872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97849178314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14457225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11301612854004</t>
   </si>
   <si>
     <t xml:space="preserve">8.23425674438477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10471343994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21100616455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16782474517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32061862945557</t>
+    <t xml:space="preserve">8.10471248626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21100425720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16782569885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3206205368042</t>
   </si>
   <si>
     <t xml:space="preserve">8.37044239044189</t>
@@ -443,31 +443,31 @@
     <t xml:space="preserve">8.41196250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50330448150635</t>
+    <t xml:space="preserve">8.50330543518066</t>
   </si>
   <si>
     <t xml:space="preserve">8.36213779449463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67769145965576</t>
+    <t xml:space="preserve">8.67769050598145</t>
   </si>
   <si>
     <t xml:space="preserve">8.76903438568115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53652191162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55312919616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64447498321533</t>
+    <t xml:space="preserve">8.53652286529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55313110351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6444730758667</t>
   </si>
   <si>
     <t xml:space="preserve">8.73581886291504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68599414825439</t>
+    <t xml:space="preserve">8.68599510192871</t>
   </si>
   <si>
     <t xml:space="preserve">8.7441234588623</t>
@@ -479,31 +479,31 @@
     <t xml:space="preserve">8.48669815063477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44517803192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47839546203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40365695953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42856979370117</t>
+    <t xml:space="preserve">8.4451789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4783935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40365791320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42857074737549</t>
   </si>
   <si>
     <t xml:space="preserve">8.65277767181396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69429779052734</t>
+    <t xml:space="preserve">8.69429874420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.71090602874756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89359474182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84377098083496</t>
+    <t xml:space="preserve">8.89359569549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84377193450928</t>
   </si>
   <si>
     <t xml:space="preserve">8.88529014587402</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">8.80224990844727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81886005401611</t>
+    <t xml:space="preserve">8.8188591003418</t>
   </si>
   <si>
     <t xml:space="preserve">8.90189838409424</t>
@@ -527,25 +527,25 @@
     <t xml:space="preserve">8.81055545806885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6278657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70260143280029</t>
+    <t xml:space="preserve">8.62786674499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70260238647461</t>
   </si>
   <si>
     <t xml:space="preserve">8.82716178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75242710113525</t>
+    <t xml:space="preserve">8.75242614746094</t>
   </si>
   <si>
     <t xml:space="preserve">9.04306697845459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14271354675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2838830947876</t>
+    <t xml:space="preserve">9.14271545410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28388404846191</t>
   </si>
   <si>
     <t xml:space="preserve">9.35031509399414</t>
@@ -554,16 +554,16 @@
     <t xml:space="preserve">9.35861778259277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15102005004883</t>
+    <t xml:space="preserve">9.15101909637451</t>
   </si>
   <si>
     <t xml:space="preserve">8.93511486053467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7773380279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19253921508789</t>
+    <t xml:space="preserve">8.77733993530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19253826141357</t>
   </si>
   <si>
     <t xml:space="preserve">9.44996356964111</t>
@@ -578,10 +578,10 @@
     <t xml:space="preserve">9.1344108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91850662231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9268102645874</t>
+    <t xml:space="preserve">8.91850757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92681121826172</t>
   </si>
   <si>
     <t xml:space="preserve">9.00985240936279</t>
@@ -590,31 +590,31 @@
     <t xml:space="preserve">8.98493766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76072978973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11780548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.225754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95172119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06797885894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07628345489502</t>
+    <t xml:space="preserve">8.7607307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11780261993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22575569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95172023773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06797790527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0762825012207</t>
   </si>
   <si>
     <t xml:space="preserve">9.20084285736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31709957122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36692428588867</t>
+    <t xml:space="preserve">9.31710052490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36692333221436</t>
   </si>
   <si>
     <t xml:space="preserve">9.49148273468018</t>
@@ -623,16 +623,16 @@
     <t xml:space="preserve">9.54961204528809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96481227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0229396820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82364273071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93990039825439</t>
+    <t xml:space="preserve">9.96481132507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0229406356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82364368438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93990135192871</t>
   </si>
   <si>
     <t xml:space="preserve">9.98141956329346</t>
@@ -641,22 +641,22 @@
     <t xml:space="preserve">10.0063323974609</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0561561584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2056274414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2305402755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2139339447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1973237991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1558046340942</t>
+    <t xml:space="preserve">10.0561571121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2056283950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.230541229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2139329910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1973247528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1558055877686</t>
   </si>
   <si>
     <t xml:space="preserve">10.1225891113281</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">10.1807165145874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475009918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2222356796265</t>
+    <t xml:space="preserve">10.147500038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2222366333008</t>
   </si>
   <si>
     <t xml:space="preserve">10.1308927536011</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">10.0810670852661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0727643966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.529483795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4464426040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5211811065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3883171081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4713563919067</t>
+    <t xml:space="preserve">10.0727634429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5294847488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4464445114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5211801528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.38831615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4713554382324</t>
   </si>
   <si>
     <t xml:space="preserve">10.6872606277466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7204761505127</t>
+    <t xml:space="preserve">10.720477104187</t>
   </si>
   <si>
     <t xml:space="preserve">10.6540451049805</t>
@@ -716,22 +716,22 @@
     <t xml:space="preserve">10.4049253463745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6457414627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7952136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.96129322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9280786514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7703018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7786054611206</t>
+    <t xml:space="preserve">10.6457405090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7952127456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9612941741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9280767440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.770299911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7786045074463</t>
   </si>
   <si>
     <t xml:space="preserve">10.869948387146</t>
@@ -743,22 +743,22 @@
     <t xml:space="preserve">11.0360288619995</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8948612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0443325042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.251932144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1771974563599</t>
+    <t xml:space="preserve">10.8948602676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0443334579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2519340515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1771984100342</t>
   </si>
   <si>
     <t xml:space="preserve">11.2270212173462</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2602376937866</t>
+    <t xml:space="preserve">11.2602386474609</t>
   </si>
   <si>
     <t xml:space="preserve">11.2851505279541</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">11.3432788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.393102645874</t>
+    <t xml:space="preserve">11.3931016921997</t>
   </si>
   <si>
     <t xml:space="preserve">11.4512300491333</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">11.5093584060669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5010547637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5176620483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.741870880127</t>
+    <t xml:space="preserve">11.5010538101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5176630020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7418699264526</t>
   </si>
   <si>
     <t xml:space="preserve">11.7584781646729</t>
@@ -791,16 +791,16 @@
     <t xml:space="preserve">11.6920461654663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.683741569519</t>
+    <t xml:space="preserve">11.6837425231934</t>
   </si>
   <si>
     <t xml:space="preserve">11.7252626419067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7667827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7169570922852</t>
+    <t xml:space="preserve">11.7667837142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7169580459595</t>
   </si>
   <si>
     <t xml:space="preserve">11.5923976898193</t>
@@ -809,37 +809,37 @@
     <t xml:space="preserve">11.7003498077393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.542573928833</t>
+    <t xml:space="preserve">11.5425748825073</t>
   </si>
   <si>
     <t xml:space="preserve">11.9577741622925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0574216842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9162540435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9909906387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9826860427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1487665176392</t>
+    <t xml:space="preserve">12.0574226379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9162549972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9909896850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.98268699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1487674713135</t>
   </si>
   <si>
     <t xml:space="preserve">12.0491199493408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2899351119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3895835876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3148460388184</t>
+    <t xml:space="preserve">12.2899360656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3895826339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.314845085144</t>
   </si>
   <si>
     <t xml:space="preserve">12.5058393478394</t>
@@ -848,37 +848,37 @@
     <t xml:space="preserve">12.5390548706055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2733268737793</t>
+    <t xml:space="preserve">12.2733278274536</t>
   </si>
   <si>
     <t xml:space="preserve">12.1902866363525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1985921859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0823345184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.64222240448</t>
+    <t xml:space="preserve">12.1985902786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0823335647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6422233581543</t>
   </si>
   <si>
     <t xml:space="preserve">11.550877571106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8083009719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9346389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9514827728271</t>
+    <t xml:space="preserve">11.8083019256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9346399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9514837265015</t>
   </si>
   <si>
     <t xml:space="preserve">12.0609760284424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1620454788208</t>
+    <t xml:space="preserve">12.1620445251465</t>
   </si>
   <si>
     <t xml:space="preserve">11.783034324646</t>
@@ -887,22 +887,22 @@
     <t xml:space="preserve">11.6566972732544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8083019256592</t>
+    <t xml:space="preserve">11.8083028793335</t>
   </si>
   <si>
     <t xml:space="preserve">11.7577667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5977411270142</t>
+    <t xml:space="preserve">11.5977401733398</t>
   </si>
   <si>
     <t xml:space="preserve">11.5640506744385</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3029537200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2018842697144</t>
+    <t xml:space="preserve">11.3029546737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2018852233887</t>
   </si>
   <si>
     <t xml:space="preserve">11.1934614181519</t>
@@ -911,25 +911,25 @@
     <t xml:space="preserve">11.0334339141846</t>
   </si>
   <si>
-    <t xml:space="preserve">10.957631111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2355737686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4208679199219</t>
+    <t xml:space="preserve">10.9576320648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2355728149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4208688735962</t>
   </si>
   <si>
     <t xml:space="preserve">11.2271518707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2861070632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.168194770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.923942565918</t>
+    <t xml:space="preserve">11.2861089706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1681938171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9239416122437</t>
   </si>
   <si>
     <t xml:space="preserve">11.0250120162964</t>
@@ -938,28 +938,28 @@
     <t xml:space="preserve">10.763916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9492092132568</t>
+    <t xml:space="preserve">10.9492101669312</t>
   </si>
   <si>
     <t xml:space="preserve">10.5786218643188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7891826629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7386493682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6544227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7554941177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4292907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5219383239746</t>
+    <t xml:space="preserve">10.7891845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7386474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6544237136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7554922103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4292917251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5219392776489</t>
   </si>
   <si>
     <t xml:space="preserve">11.294529914856</t>
@@ -968,10 +968,10 @@
     <t xml:space="preserve">11.6398525238037</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4629802703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4124450683594</t>
+    <t xml:space="preserve">11.4629793167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.412446975708</t>
   </si>
   <si>
     <t xml:space="preserve">11.361909866333</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">11.3197984695435</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2103071212769</t>
+    <t xml:space="preserve">11.2103080749512</t>
   </si>
   <si>
     <t xml:space="preserve">10.9997444152832</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">11.0081672668457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8902530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9323663711548</t>
+    <t xml:space="preserve">10.8902540206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9323654174805</t>
   </si>
   <si>
     <t xml:space="preserve">10.8734073638916</t>
@@ -1007,16 +1007,16 @@
     <t xml:space="preserve">10.6796913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7807607650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8649864196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7049579620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9155197143555</t>
+    <t xml:space="preserve">10.78076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8649854660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7049598693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9155206680298</t>
   </si>
   <si>
     <t xml:space="preserve">11.2608404159546</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">11.151349067688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0839700698853</t>
+    <t xml:space="preserve">11.0839691162109</t>
   </si>
   <si>
     <t xml:space="preserve">11.0502796173096</t>
@@ -1034,25 +1034,25 @@
     <t xml:space="preserve">11.2524194717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3282203674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3787565231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3956003189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5050945281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4040250778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.555627822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6819648742676</t>
+    <t xml:space="preserve">11.3282222747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.378755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3955993652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5050935745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4040241241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5556268692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6819658279419</t>
   </si>
   <si>
     <t xml:space="preserve">11.7493448257446</t>
@@ -1070,58 +1070,58 @@
     <t xml:space="preserve">12.0525531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0946674346924</t>
+    <t xml:space="preserve">12.0946664810181</t>
   </si>
   <si>
     <t xml:space="preserve">12.1536235809326</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0357074737549</t>
+    <t xml:space="preserve">12.0357093811035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0778207778931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0441303253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1788911819458</t>
+    <t xml:space="preserve">12.0441312789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1788892745972</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3136510848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3220720291138</t>
+    <t xml:space="preserve">12.3136520385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3220729827881</t>
   </si>
   <si>
     <t xml:space="preserve">12.3726072311401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.204158782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2883815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2968053817749</t>
+    <t xml:space="preserve">12.2041578292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2883825302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2968063354492</t>
   </si>
   <si>
     <t xml:space="preserve">11.7914552688599</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7325000762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8167247772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0104417800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0020189285278</t>
+    <t xml:space="preserve">11.7325010299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.816722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.010440826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0020198822021</t>
   </si>
   <si>
     <t xml:space="preserve">11.9683303833008</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">11.9262161254883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.311375617981</t>
+    <t xml:space="preserve">11.3113765716553</t>
   </si>
   <si>
     <t xml:space="preserve">10.8144512176514</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">10.8986759185791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8228731155396</t>
+    <t xml:space="preserve">10.8228721618652</t>
   </si>
   <si>
     <t xml:space="preserve">11.0165910720825</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">10.9407873153687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7723388671875</t>
+    <t xml:space="preserve">10.7723379135132</t>
   </si>
   <si>
     <t xml:space="preserve">10.7976055145264</t>
@@ -1160,16 +1160,16 @@
     <t xml:space="preserve">10.7302255630493</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7218017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6628456115723</t>
+    <t xml:space="preserve">10.7218027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6628465652466</t>
   </si>
   <si>
     <t xml:space="preserve">10.6123104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8060283660889</t>
+    <t xml:space="preserve">10.8060293197632</t>
   </si>
   <si>
     <t xml:space="preserve">10.6881141662598</t>
@@ -1181,22 +1181,22 @@
     <t xml:space="preserve">10.6712694168091</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4691286087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4859733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0923910140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1597709655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1345043182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1429281234741</t>
+    <t xml:space="preserve">10.4691305160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4859743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0923929214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1597700119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.134503364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1429271697998</t>
   </si>
   <si>
     <t xml:space="preserve">11.218729019165</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">11.3450660705566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4270181655884</t>
+    <t xml:space="preserve">10.4270172119141</t>
   </si>
   <si>
     <t xml:space="preserve">10.3175239562988</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">10.2838344573975</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1911878585815</t>
+    <t xml:space="preserve">10.1911869049072</t>
   </si>
   <si>
     <t xml:space="preserve">10.1574974060059</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">10.1659212112427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1069641113281</t>
+    <t xml:space="preserve">10.1069622039795</t>
   </si>
   <si>
     <t xml:space="preserve">10.0985412597656</t>
@@ -1244,28 +1244,28 @@
     <t xml:space="preserve">9.98904800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0058927536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7195291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68583965301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48370170593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37420749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.115385055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3091011047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5954647064209</t>
+    <t xml:space="preserve">10.0058946609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71952819824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68584156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4837007522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3742094039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1153860092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3091020584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5954656600952</t>
   </si>
   <si>
     <t xml:space="preserve">10.7133808135986</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">10.4522838592529</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4017496109009</t>
+    <t xml:space="preserve">10.4017505645752</t>
   </si>
   <si>
     <t xml:space="preserve">10.5617771148682</t>
@@ -1292,19 +1292,19 @@
     <t xml:space="preserve">10.5449314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342791557312</t>
+    <t xml:space="preserve">10.3427925109863</t>
   </si>
   <si>
     <t xml:space="preserve">10.4438619613647</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4101724624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4185943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4354400634766</t>
+    <t xml:space="preserve">10.4101715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4185934066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4354391098022</t>
   </si>
   <si>
     <t xml:space="preserve">10.2585668563843</t>
@@ -1319,10 +1319,10 @@
     <t xml:space="preserve">10.1490755081177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0418567657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.536509513855</t>
+    <t xml:space="preserve">11.0418577194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5365085601807</t>
   </si>
   <si>
     <t xml:space="preserve">10.2754125595093</t>
@@ -1337,22 +1337,22 @@
     <t xml:space="preserve">9.93851470947266</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0500860214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.384801864624</t>
+    <t xml:space="preserve">10.0500869750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3848028182983</t>
   </si>
   <si>
     <t xml:space="preserve">10.3075609207153</t>
   </si>
   <si>
-    <t xml:space="preserve">10.771014213562</t>
+    <t xml:space="preserve">10.7710151672363</t>
   </si>
   <si>
     <t xml:space="preserve">10.6766080856323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.599365234375</t>
+    <t xml:space="preserve">10.5993661880493</t>
   </si>
   <si>
     <t xml:space="preserve">10.2303190231323</t>
@@ -1361,22 +1361,22 @@
     <t xml:space="preserve">10.470627784729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.504958152771</t>
+    <t xml:space="preserve">10.5049571990967</t>
   </si>
   <si>
     <t xml:space="preserve">10.642276763916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6851892471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6594429016113</t>
+    <t xml:space="preserve">10.6851902008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.659441947937</t>
   </si>
   <si>
     <t xml:space="preserve">10.7109375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.93408203125</t>
+    <t xml:space="preserve">10.9340810775757</t>
   </si>
   <si>
     <t xml:space="preserve">10.6508598327637</t>
@@ -1403,16 +1403,16 @@
     <t xml:space="preserve">9.92135047912598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0758333206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0586700439453</t>
+    <t xml:space="preserve">10.075834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.058669090271</t>
   </si>
   <si>
     <t xml:space="preserve">9.89560127258301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94709587097168</t>
+    <t xml:space="preserve">9.947096824646</t>
   </si>
   <si>
     <t xml:space="preserve">9.74111652374268</t>
@@ -1427,19 +1427,19 @@
     <t xml:space="preserve">9.87843608856201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99001026153564</t>
+    <t xml:space="preserve">9.99000930786133</t>
   </si>
   <si>
     <t xml:space="preserve">10.2560653686523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2903957366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2732305526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.51353931427</t>
+    <t xml:space="preserve">10.2903966903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2732315063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135402679443</t>
   </si>
   <si>
     <t xml:space="preserve">10.48779296875</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">10.3333082199097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.084415435791</t>
+    <t xml:space="preserve">10.0844144821167</t>
   </si>
   <si>
     <t xml:space="preserve">10.127329826355</t>
@@ -1460,73 +1460,73 @@
     <t xml:space="preserve">10.0157556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0329217910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84410572052002</t>
+    <t xml:space="preserve">10.032922744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84410667419434</t>
   </si>
   <si>
     <t xml:space="preserve">10.04150390625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.23890209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78402996063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70678615570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77544689178467</t>
+    <t xml:space="preserve">10.2389011383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78402900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.706787109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77544593811035</t>
   </si>
   <si>
     <t xml:space="preserve">9.68103981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56088638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59521579742432</t>
+    <t xml:space="preserve">9.56088542938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59521484375</t>
   </si>
   <si>
     <t xml:space="preserve">9.68962287902832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47505855560303</t>
+    <t xml:space="preserve">9.47505950927734</t>
   </si>
   <si>
     <t xml:space="preserve">9.483642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62954521179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91276550292969</t>
+    <t xml:space="preserve">9.62954616546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.912766456604</t>
   </si>
   <si>
     <t xml:space="preserve">9.88701915740967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75828266143799</t>
+    <t xml:space="preserve">9.7582836151123</t>
   </si>
   <si>
     <t xml:space="preserve">9.56946754455566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57804870605469</t>
+    <t xml:space="preserve">9.57804775238037</t>
   </si>
   <si>
     <t xml:space="preserve">9.73253345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.612380027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71536922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82694053649902</t>
+    <t xml:space="preserve">9.61237907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71537017822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82694149017334</t>
   </si>
   <si>
     <t xml:space="preserve">10.187406539917</t>
@@ -1535,13 +1535,13 @@
     <t xml:space="preserve">10.2217350006104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99859237670898</t>
+    <t xml:space="preserve">9.99859142303467</t>
   </si>
   <si>
     <t xml:space="preserve">9.96426200866699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86985397338867</t>
+    <t xml:space="preserve">9.86985492706299</t>
   </si>
   <si>
     <t xml:space="preserve">9.69820404052734</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">9.86127185821533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52655506134033</t>
+    <t xml:space="preserve">9.52655601501465</t>
   </si>
   <si>
     <t xml:space="preserve">9.21758651733398</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">8.52669525146484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4408712387085</t>
+    <t xml:space="preserve">8.44087028503418</t>
   </si>
   <si>
     <t xml:space="preserve">8.12331962585449</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">8.43228912353516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5224027633667</t>
+    <t xml:space="preserve">8.52240371704102</t>
   </si>
   <si>
     <t xml:space="preserve">8.41083240509033</t>
@@ -1589,19 +1589,19 @@
     <t xml:space="preserve">8.23060035705566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08469676971436</t>
+    <t xml:space="preserve">8.08469772338867</t>
   </si>
   <si>
     <t xml:space="preserve">8.35504627227783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22630882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48378467559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39366722106934</t>
+    <t xml:space="preserve">8.22630977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48378276824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39366817474365</t>
   </si>
   <si>
     <t xml:space="preserve">8.57818984985352</t>
@@ -1616,37 +1616,37 @@
     <t xml:space="preserve">8.23489189147949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11473751068115</t>
+    <t xml:space="preserve">8.11473655700684</t>
   </si>
   <si>
     <t xml:space="preserve">8.02032947540283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79289293289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72852373123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77143621444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83151340484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00316429138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02891063690186</t>
+    <t xml:space="preserve">7.792893409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72852420806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77143669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83151483535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00316333770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02891159057617</t>
   </si>
   <si>
     <t xml:space="preserve">8.00745487213135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25205707550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28638744354248</t>
+    <t xml:space="preserve">8.25205612182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28638648986816</t>
   </si>
   <si>
     <t xml:space="preserve">8.61681175231934</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">8.608229637146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54815101623535</t>
+    <t xml:space="preserve">8.54815006256104</t>
   </si>
   <si>
     <t xml:space="preserve">8.75413227081299</t>
@@ -1667,40 +1667,40 @@
     <t xml:space="preserve">8.46232795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16193962097168</t>
+    <t xml:space="preserve">8.161940574646</t>
   </si>
   <si>
     <t xml:space="preserve">8.19197845458984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98170804977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0889892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3378791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81435108184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69848680496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99887466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81864070892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8658447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58691310882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63411808013916</t>
+    <t xml:space="preserve">7.98170709609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08898830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33788108825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8143515586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69848585128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99887418746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81864023208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86584377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58691263198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63411712646484</t>
   </si>
   <si>
     <t xml:space="preserve">7.68990278244019</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">7.6598653793335</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96454381942749</t>
+    <t xml:space="preserve">7.96454429626465</t>
   </si>
   <si>
     <t xml:space="preserve">7.93879556655884</t>
@@ -1739,46 +1739,46 @@
     <t xml:space="preserve">8.496657371521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50094795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46661853790283</t>
+    <t xml:space="preserve">8.50094699859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46661758422852</t>
   </si>
   <si>
     <t xml:space="preserve">8.59964847564697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85712146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56960773468018</t>
+    <t xml:space="preserve">8.85712051391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56960678100586</t>
   </si>
   <si>
     <t xml:space="preserve">8.56531810760498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55673408508301</t>
+    <t xml:space="preserve">8.55673313140869</t>
   </si>
   <si>
     <t xml:space="preserve">8.53956985473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50523948669434</t>
+    <t xml:space="preserve">8.50524044036865</t>
   </si>
   <si>
     <t xml:space="preserve">8.50953102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24776554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15335750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39795780181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58248043060303</t>
+    <t xml:space="preserve">8.24776458740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15335845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39795875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58248138427734</t>
   </si>
   <si>
     <t xml:space="preserve">8.77129650115967</t>
@@ -1793,55 +1793,55 @@
     <t xml:space="preserve">8.96869373321533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.020188331604</t>
+    <t xml:space="preserve">9.02018737792969</t>
   </si>
   <si>
     <t xml:space="preserve">9.28624439239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31199264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08026504516602</t>
+    <t xml:space="preserve">9.31199359893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08026599884033</t>
   </si>
   <si>
     <t xml:space="preserve">9.131760597229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32057476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.942946434021</t>
+    <t xml:space="preserve">9.32057571411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94294452667236</t>
   </si>
   <si>
     <t xml:space="preserve">8.814208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78846073150635</t>
+    <t xml:space="preserve">8.78845977783203</t>
   </si>
   <si>
     <t xml:space="preserve">8.79704475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74554920196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72838497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.908616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14034366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42356586456299</t>
+    <t xml:space="preserve">8.74554824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72838401794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90861701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14034461975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42356491088867</t>
   </si>
   <si>
     <t xml:space="preserve">9.26049709320068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18325614929199</t>
+    <t xml:space="preserve">9.18325519561768</t>
   </si>
   <si>
     <t xml:space="preserve">9.00302410125732</t>
@@ -1856,28 +1856,28 @@
     <t xml:space="preserve">8.65114116668701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.685471534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67688941955566</t>
+    <t xml:space="preserve">8.68547058105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67689037322998</t>
   </si>
   <si>
     <t xml:space="preserve">8.87428665161133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51797103881836</t>
+    <t xml:space="preserve">9.51797199249268</t>
   </si>
   <si>
     <t xml:space="preserve">9.44073009490967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41498279571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64670848846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0672512054443</t>
+    <t xml:space="preserve">9.41498184204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64671039581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0672521591187</t>
   </si>
   <si>
     <t xml:space="preserve">9.93851375579834</t>
@@ -1886,16 +1886,16 @@
     <t xml:space="preserve">10.1959886550903</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80977725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62096309661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50938892364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86570358276367</t>
+    <t xml:space="preserve">9.80977630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62096118927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50938987731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86570167541504</t>
   </si>
   <si>
     <t xml:space="preserve">8.95152854919434</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">8.83995628356934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75851821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77167415618896</t>
+    <t xml:space="preserve">8.75851726531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77167510986328</t>
   </si>
   <si>
     <t xml:space="preserve">8.74097442626953</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">8.42080783843994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53483963012695</t>
+    <t xml:space="preserve">8.53484058380127</t>
   </si>
   <si>
     <t xml:space="preserve">8.57869815826416</t>
@@ -1925,13 +1925,13 @@
     <t xml:space="preserve">8.58747005462646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47343730926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55238342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42957973480225</t>
+    <t xml:space="preserve">8.47343826293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55238246917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42957878112793</t>
   </si>
   <si>
     <t xml:space="preserve">8.18397235870361</t>
@@ -1940,13 +1940,13 @@
     <t xml:space="preserve">8.37695026397705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56992626190186</t>
+    <t xml:space="preserve">8.56992530822754</t>
   </si>
   <si>
     <t xml:space="preserve">8.67957305908203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66202831268311</t>
+    <t xml:space="preserve">8.66202735900879</t>
   </si>
   <si>
     <t xml:space="preserve">8.89447975158691</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">8.72781753540039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72343063354492</t>
+    <t xml:space="preserve">8.72342967987061</t>
   </si>
   <si>
     <t xml:space="preserve">8.93833637237549</t>
@@ -1970,22 +1970,22 @@
     <t xml:space="preserve">9.06113910675049</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00850963592529</t>
+    <t xml:space="preserve">9.00851058959961</t>
   </si>
   <si>
     <t xml:space="preserve">8.85062026977539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71465873718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88570785522461</t>
+    <t xml:space="preserve">8.71465969085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88570690155029</t>
   </si>
   <si>
     <t xml:space="preserve">9.11377048492432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05236911773682</t>
+    <t xml:space="preserve">9.0523681640625</t>
   </si>
   <si>
     <t xml:space="preserve">9.28043270111084</t>
@@ -1994,19 +1994,19 @@
     <t xml:space="preserve">9.32428932189941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23657417297363</t>
+    <t xml:space="preserve">9.23657512664795</t>
   </si>
   <si>
     <t xml:space="preserve">8.9295654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80676174163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78921985626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49536895751953</t>
+    <t xml:space="preserve">8.80676078796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78921890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49536800384521</t>
   </si>
   <si>
     <t xml:space="preserve">8.45589542388916</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">8.62255764007568</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92079448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07868480682373</t>
+    <t xml:space="preserve">8.9207935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07868385314941</t>
   </si>
   <si>
     <t xml:space="preserve">9.0172815322876</t>
@@ -2033,13 +2033,13 @@
     <t xml:space="preserve">8.13134288787842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17081546783447</t>
+    <t xml:space="preserve">8.17081451416016</t>
   </si>
   <si>
     <t xml:space="preserve">7.96029567718506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77170372009277</t>
+    <t xml:space="preserve">7.77170419692993</t>
   </si>
   <si>
     <t xml:space="preserve">7.61819887161255</t>
@@ -2048,22 +2048,22 @@
     <t xml:space="preserve">7.64890050888062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63135671615601</t>
+    <t xml:space="preserve">7.63135766983032</t>
   </si>
   <si>
     <t xml:space="preserve">7.38574981689453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29803371429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22347354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20593166351318</t>
+    <t xml:space="preserve">7.29803419113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39013624191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22347402572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20593214035034</t>
   </si>
   <si>
     <t xml:space="preserve">7.28048992156982</t>
@@ -2072,43 +2072,43 @@
     <t xml:space="preserve">7.27171802520752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51293897628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39890813827515</t>
+    <t xml:space="preserve">7.51293849945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39890766143799</t>
   </si>
   <si>
     <t xml:space="preserve">7.26733255386353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19277334213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44276571273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45153856277466</t>
+    <t xml:space="preserve">7.19277381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4427661895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45153903961182</t>
   </si>
   <si>
     <t xml:space="preserve">7.32873439788818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53048372268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79363346099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98661136627197</t>
+    <t xml:space="preserve">7.53048324584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79363298416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98661088943481</t>
   </si>
   <si>
     <t xml:space="preserve">8.0611686706543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22344589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28923225402832</t>
+    <t xml:space="preserve">8.2234468460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28923320770264</t>
   </si>
   <si>
     <t xml:space="preserve">8.35063457489014</t>
@@ -2117,31 +2117,31 @@
     <t xml:space="preserve">8.21905899047852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1927433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30239105224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87257814407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72346019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60942888259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74100351333618</t>
+    <t xml:space="preserve">8.19274425506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30239009857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87257862091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72346067428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60942840576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74100255966187</t>
   </si>
   <si>
     <t xml:space="preserve">7.83310556411743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84187793731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67521572113037</t>
+    <t xml:space="preserve">7.84187746047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67521524429321</t>
   </si>
   <si>
     <t xml:space="preserve">7.50855445861816</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">7.31557655334473</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4734673500061</t>
+    <t xml:space="preserve">7.47346782684326</t>
   </si>
   <si>
     <t xml:space="preserve">7.85064935684204</t>
@@ -2171,10 +2171,10 @@
     <t xml:space="preserve">8.00854015350342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04362773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80679035186768</t>
+    <t xml:space="preserve">8.04362678527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80679082870483</t>
   </si>
   <si>
     <t xml:space="preserve">7.91643714904785</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">8.18835926055908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25414562225342</t>
+    <t xml:space="preserve">8.25414657592773</t>
   </si>
   <si>
     <t xml:space="preserve">8.29361915588379</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">8.65325736999512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3725643157959</t>
+    <t xml:space="preserve">8.37256336212158</t>
   </si>
   <si>
     <t xml:space="preserve">8.43835067749023</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">9.12254238128662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14885711669922</t>
+    <t xml:space="preserve">9.1488561630249</t>
   </si>
   <si>
     <t xml:space="preserve">9.37692070007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56112575531006</t>
+    <t xml:space="preserve">9.56112480163574</t>
   </si>
   <si>
     <t xml:space="preserve">9.75410175323486</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">9.70147323608398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47340869903564</t>
+    <t xml:space="preserve">9.47340965270996</t>
   </si>
   <si>
     <t xml:space="preserve">9.35060501098633</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">9.49095153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24534606933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42077922821045</t>
+    <t xml:space="preserve">9.24534511566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42078018188477</t>
   </si>
   <si>
     <t xml:space="preserve">9.31551933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48218154907227</t>
+    <t xml:space="preserve">9.48218250274658</t>
   </si>
   <si>
     <t xml:space="preserve">9.64884281158447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72778701782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80673313140869</t>
+    <t xml:space="preserve">9.72778797149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80673217773438</t>
   </si>
   <si>
     <t xml:space="preserve">9.77164745330811</t>
@@ -2261,10 +2261,10 @@
     <t xml:space="preserve">9.81550407409668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86813449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92076301574707</t>
+    <t xml:space="preserve">9.86813354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92076396942139</t>
   </si>
   <si>
     <t xml:space="preserve">9.99971008300781</t>
@@ -2273,19 +2273,19 @@
     <t xml:space="preserve">9.87690734863281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84182071685791</t>
+    <t xml:space="preserve">9.84181976318359</t>
   </si>
   <si>
     <t xml:space="preserve">9.89445018768311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98216533660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0698833465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96462345123291</t>
+    <t xml:space="preserve">9.9821662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0698823928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96462249755859</t>
   </si>
   <si>
     <t xml:space="preserve">9.67515754699707</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.68392848968506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69270038604736</t>
+    <t xml:space="preserve">9.69270133972168</t>
   </si>
   <si>
     <t xml:space="preserve">9.76287460327148</t>
@@ -2321,16 +2321,16 @@
     <t xml:space="preserve">9.73655986785889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57866954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30674839019775</t>
+    <t xml:space="preserve">9.57866859436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30674743652344</t>
   </si>
   <si>
     <t xml:space="preserve">9.21025943756104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33306217193604</t>
+    <t xml:space="preserve">9.33306121826172</t>
   </si>
   <si>
     <t xml:space="preserve">9.20148754119873</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">9.13131332397461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0874547958374</t>
+    <t xml:space="preserve">9.08745384216309</t>
   </si>
   <si>
     <t xml:space="preserve">9.43832302093506</t>
@@ -2354,37 +2354,37 @@
     <t xml:space="preserve">9.42955017089844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21902942657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25411701202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15762901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09622573852539</t>
+    <t xml:space="preserve">9.21903038024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25411796569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15762996673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09622669219971</t>
   </si>
   <si>
     <t xml:space="preserve">8.39449310302734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33747673034668</t>
+    <t xml:space="preserve">8.33747577667236</t>
   </si>
   <si>
     <t xml:space="preserve">8.34186267852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10502910614014</t>
+    <t xml:space="preserve">8.10502815246582</t>
   </si>
   <si>
     <t xml:space="preserve">7.92959403991699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4997820854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60065650939941</t>
+    <t xml:space="preserve">7.49978160858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60065698623657</t>
   </si>
   <si>
     <t xml:space="preserve">7.4296088218689</t>
@@ -2393,22 +2393,22 @@
     <t xml:space="preserve">7.11821460723877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18400192260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57875633239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64892959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55682611465454</t>
+    <t xml:space="preserve">7.18400239944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57875680923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64892911911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5568265914917</t>
   </si>
   <si>
     <t xml:space="preserve">6.14017200469971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3857798576355</t>
+    <t xml:space="preserve">6.38577938079834</t>
   </si>
   <si>
     <t xml:space="preserve">5.87702226638794</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">7.72784471511841</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82436275482178</t>
+    <t xml:space="preserve">6.82436323165894</t>
   </si>
   <si>
     <t xml:space="preserve">7.02172565460205</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">6.4734959602356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31560611724854</t>
+    <t xml:space="preserve">6.31560564041138</t>
   </si>
   <si>
     <t xml:space="preserve">5.83316421508789</t>
@@ -2444,37 +2444,37 @@
     <t xml:space="preserve">5.9603533744812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85070705413818</t>
+    <t xml:space="preserve">5.85070753097534</t>
   </si>
   <si>
     <t xml:space="preserve">5.61387252807617</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18405961990356</t>
+    <t xml:space="preserve">5.18406009674072</t>
   </si>
   <si>
     <t xml:space="preserve">5.47352504730225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54369783401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89895105361938</t>
+    <t xml:space="preserve">5.54369831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89895057678223</t>
   </si>
   <si>
     <t xml:space="preserve">5.82439231872559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64895868301392</t>
+    <t xml:space="preserve">5.64895820617676</t>
   </si>
   <si>
     <t xml:space="preserve">5.69720315933228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92965221405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06122779846191</t>
+    <t xml:space="preserve">5.92965173721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06122732162476</t>
   </si>
   <si>
     <t xml:space="preserve">6.0085973739624</t>
@@ -2504,46 +2504,46 @@
     <t xml:space="preserve">6.72348928451538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48665332794189</t>
+    <t xml:space="preserve">6.48665380477905</t>
   </si>
   <si>
     <t xml:space="preserve">6.4822678565979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36385059356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22788906097412</t>
+    <t xml:space="preserve">6.36385107040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22788953781128</t>
   </si>
   <si>
     <t xml:space="preserve">5.77176237106323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82000637054443</t>
+    <t xml:space="preserve">5.82000684738159</t>
   </si>
   <si>
     <t xml:space="preserve">6.26297521591187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23227548599243</t>
+    <t xml:space="preserve">6.23227596282959</t>
   </si>
   <si>
     <t xml:space="preserve">6.21911764144897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39455080032349</t>
+    <t xml:space="preserve">6.39455032348633</t>
   </si>
   <si>
     <t xml:space="preserve">6.59629964828491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16207265853882</t>
+    <t xml:space="preserve">7.16207218170166</t>
   </si>
   <si>
     <t xml:space="preserve">7.51732540130615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37259340286255</t>
+    <t xml:space="preserve">7.37259244918823</t>
   </si>
   <si>
     <t xml:space="preserve">7.33312034606934</t>
@@ -2564,25 +2564,25 @@
     <t xml:space="preserve">7.10067176818848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35504913330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35066366195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21031713485718</t>
+    <t xml:space="preserve">7.35504961013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35066413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21031665802002</t>
   </si>
   <si>
     <t xml:space="preserve">7.23224592208862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17522954940796</t>
+    <t xml:space="preserve">7.17523002624512</t>
   </si>
   <si>
     <t xml:space="preserve">7.10505676269531</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20154523849487</t>
+    <t xml:space="preserve">7.20154476165771</t>
   </si>
   <si>
     <t xml:space="preserve">7.24540328979492</t>
@@ -2594,31 +2594,31 @@
     <t xml:space="preserve">7.17084407806396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40767955780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25856113433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3682074546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32434892654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14891529083252</t>
+    <t xml:space="preserve">7.40767860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25856065750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36820697784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32434844970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14891481399536</t>
   </si>
   <si>
     <t xml:space="preserve">7.24978876113892</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43838119506836</t>
+    <t xml:space="preserve">7.43838024139404</t>
   </si>
   <si>
     <t xml:space="preserve">7.16645860671997</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70156002044678</t>
+    <t xml:space="preserve">6.70156049728394</t>
   </si>
   <si>
     <t xml:space="preserve">6.61384248733521</t>
@@ -2627,10 +2627,10 @@
     <t xml:space="preserve">6.69278812408447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75419044494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68401670455933</t>
+    <t xml:space="preserve">6.75418996810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68401718139648</t>
   </si>
   <si>
     <t xml:space="preserve">6.71033143997192</t>
@@ -2639,7 +2639,7 @@
     <t xml:space="preserve">6.83313465118408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06119775772095</t>
+    <t xml:space="preserve">7.06119871139526</t>
   </si>
   <si>
     <t xml:space="preserve">7.1401424407959</t>
@@ -2648,10 +2648,10 @@
     <t xml:space="preserve">7.05681228637695</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04804134368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00856781005859</t>
+    <t xml:space="preserve">7.04804086685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00856733322144</t>
   </si>
   <si>
     <t xml:space="preserve">6.94716691970825</t>
@@ -2660,70 +2660,70 @@
     <t xml:space="preserve">7.07435607910156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08751344680786</t>
+    <t xml:space="preserve">7.0875129699707</t>
   </si>
   <si>
     <t xml:space="preserve">7.09628534317017</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01734018325806</t>
+    <t xml:space="preserve">7.0173397064209</t>
   </si>
   <si>
     <t xml:space="preserve">7.35943508148193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29364824295044</t>
+    <t xml:space="preserve">7.29364776611328</t>
   </si>
   <si>
     <t xml:space="preserve">7.4910101890564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60504245758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97345352172852</t>
+    <t xml:space="preserve">7.60504198074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9734525680542</t>
   </si>
   <si>
     <t xml:space="preserve">7.57434034347534</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41206502914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88576507568359</t>
+    <t xml:space="preserve">7.41206550598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88576412200928</t>
   </si>
   <si>
     <t xml:space="preserve">6.9910249710083</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0392689704895</t>
+    <t xml:space="preserve">7.03926849365234</t>
   </si>
   <si>
     <t xml:space="preserve">7.06997013092041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31119155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48223924636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86380672454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92082262039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9997673034668</t>
+    <t xml:space="preserve">7.31119108200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48223972320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86380624771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.920823097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99976682662964</t>
   </si>
   <si>
     <t xml:space="preserve">7.73661756515503</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68837308883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61381387710571</t>
+    <t xml:space="preserve">7.68837356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61381483078003</t>
   </si>
   <si>
     <t xml:space="preserve">7.62697172164917</t>
@@ -2732,31 +2732,31 @@
     <t xml:space="preserve">7.57872772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77609014511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80240535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96906614303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99099588394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15327167510986</t>
+    <t xml:space="preserve">7.77608966827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240488052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96906661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99099540710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15327072143555</t>
   </si>
   <si>
     <t xml:space="preserve">8.54799747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56995487213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82433366775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66644477844238</t>
+    <t xml:space="preserve">7.56995534896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82433462142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66644382476807</t>
   </si>
   <si>
     <t xml:space="preserve">7.71907424926758</t>
@@ -2768,16 +2768,16 @@
     <t xml:space="preserve">7.86819267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22780132293701</t>
+    <t xml:space="preserve">9.22780227661133</t>
   </si>
   <si>
     <t xml:space="preserve">9.17517280578613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39446449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83304786682129</t>
+    <t xml:space="preserve">9.39446353912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83304691314697</t>
   </si>
   <si>
     <t xml:space="preserve">9.58744144439697</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">9.53481101989746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46463680267334</t>
+    <t xml:space="preserve">9.46463775634766</t>
   </si>
   <si>
     <t xml:space="preserve">9.50849628448486</t>
@@ -2810,19 +2810,19 @@
     <t xml:space="preserve">9.61375617980957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49972534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03482437133789</t>
+    <t xml:space="preserve">9.49972438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03482532501221</t>
   </si>
   <si>
     <t xml:space="preserve">9.74533176422119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90322303771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0961980819702</t>
+    <t xml:space="preserve">9.90322208404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0961971282959</t>
   </si>
   <si>
     <t xml:space="preserve">10.1225128173828</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">9.93830871582031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66638660430908</t>
+    <t xml:space="preserve">9.6663875579834</t>
   </si>
   <si>
     <t xml:space="preserve">9.88567638397217</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">9.44709491729736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82427597045898</t>
+    <t xml:space="preserve">9.82427501678467</t>
   </si>
   <si>
     <t xml:space="preserve">9.56989765167236</t>
@@ -2867,10 +2867,10 @@
     <t xml:space="preserve">9.34183502197266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19271469116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18394470214844</t>
+    <t xml:space="preserve">9.19271564483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18394374847412</t>
   </si>
   <si>
     <t xml:space="preserve">8.90324878692627</t>
@@ -2882,28 +2882,28 @@
     <t xml:space="preserve">8.84184741973877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9997386932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97342300415039</t>
+    <t xml:space="preserve">8.99973964691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97342395782471</t>
   </si>
   <si>
     <t xml:space="preserve">9.18857097625732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.198073387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1890983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43138885498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57496929168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72752285003662</t>
+    <t xml:space="preserve">9.19807243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18909931182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43138980865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5749683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7275218963623</t>
   </si>
   <si>
     <t xml:space="preserve">9.79931259155273</t>
@@ -2915,22 +2915,22 @@
     <t xml:space="preserve">9.94289207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98776054382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79033851623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74547004699707</t>
+    <t xml:space="preserve">9.98776149749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79033756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74546909332275</t>
   </si>
   <si>
     <t xml:space="preserve">9.68265342712402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70060157775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52112674713135</t>
+    <t xml:space="preserve">9.70060253143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52112579345703</t>
   </si>
   <si>
     <t xml:space="preserve">9.51215362548828</t>
@@ -2945,10 +2945,10 @@
     <t xml:space="preserve">9.63778495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61086463928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69162845611572</t>
+    <t xml:space="preserve">9.61086368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69162750244141</t>
   </si>
   <si>
     <t xml:space="preserve">9.5031795501709</t>
@@ -2957,13 +2957,13 @@
     <t xml:space="preserve">9.58394336700439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60189056396484</t>
+    <t xml:space="preserve">9.60188961029053</t>
   </si>
   <si>
     <t xml:space="preserve">9.55702114105225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5480489730835</t>
+    <t xml:space="preserve">9.54804801940918</t>
   </si>
   <si>
     <t xml:space="preserve">9.35960006713867</t>
@@ -2975,16 +2975,16 @@
     <t xml:space="preserve">9.64675903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29678344726562</t>
+    <t xml:space="preserve">9.29678249359131</t>
   </si>
   <si>
     <t xml:space="preserve">9.33267784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3865213394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39549541473389</t>
+    <t xml:space="preserve">9.38652038574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39549446105957</t>
   </si>
   <si>
     <t xml:space="preserve">9.7723913192749</t>
@@ -2996,19 +2996,19 @@
     <t xml:space="preserve">10.3915786743164</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5800256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6518154144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6877107620239</t>
+    <t xml:space="preserve">10.5800266265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.651816368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6877117156982</t>
   </si>
   <si>
     <t xml:space="preserve">10.7415542602539</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8582124710083</t>
+    <t xml:space="preserve">10.8582134246826</t>
   </si>
   <si>
     <t xml:space="preserve">10.9389753341675</t>
@@ -3017,10 +3017,10 @@
     <t xml:space="preserve">10.9838438034058</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0556335449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1005020141602</t>
+    <t xml:space="preserve">11.0556344985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1005029678345</t>
   </si>
   <si>
     <t xml:space="preserve">11.0915288925171</t>
@@ -3032,31 +3032,31 @@
     <t xml:space="preserve">11.019739151001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9300012588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312902450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0376863479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0107650756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9748697280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8761587142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9120540618896</t>
+    <t xml:space="preserve">10.9300031661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0107669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9748706817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8761596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.912055015564</t>
   </si>
   <si>
     <t xml:space="preserve">11.0466613769531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.921028137207</t>
+    <t xml:space="preserve">10.9210271835327</t>
   </si>
   <si>
     <t xml:space="preserve">10.8941068649292</t>
@@ -3071,43 +3071,43 @@
     <t xml:space="preserve">10.75950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7864217758179</t>
+    <t xml:space="preserve">10.7864227294922</t>
   </si>
   <si>
     <t xml:space="preserve">10.8402643203735</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4274730682373</t>
+    <t xml:space="preserve">10.427472114563</t>
   </si>
   <si>
     <t xml:space="preserve">10.2569723129272</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90699672698975</t>
+    <t xml:space="preserve">9.90699768066406</t>
   </si>
   <si>
     <t xml:space="preserve">9.96083927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1223669052124</t>
+    <t xml:space="preserve">10.1223659515381</t>
   </si>
   <si>
     <t xml:space="preserve">10.1313400268555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1403141021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0954456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87110233306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80828666687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56599617004395</t>
+    <t xml:space="preserve">10.1403150558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0954446792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87110137939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8082857131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56599521636963</t>
   </si>
   <si>
     <t xml:space="preserve">9.47625923156738</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">9.67368030548096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70957469940186</t>
+    <t xml:space="preserve">9.70957374572754</t>
   </si>
   <si>
     <t xml:space="preserve">9.75444412231445</t>
@@ -3143,10 +3143,10 @@
     <t xml:space="preserve">10.1672353744507</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1492872238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2031297683716</t>
+    <t xml:space="preserve">10.1492881774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2031288146973</t>
   </si>
   <si>
     <t xml:space="preserve">10.1851825714111</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">10.2838935852051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3377361297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4454212188721</t>
+    <t xml:space="preserve">10.3377370834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4454202651978</t>
   </si>
   <si>
     <t xml:space="preserve">10.5172109603882</t>
@@ -3170,16 +3170,16 @@
     <t xml:space="preserve">10.3018407821655</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4184989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4364461898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7774486541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8492374420166</t>
+    <t xml:space="preserve">10.4184999465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4364471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7774496078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8492393493652</t>
   </si>
   <si>
     <t xml:space="preserve">10.6966857910156</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">10.7684745788574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5620784759521</t>
+    <t xml:space="preserve">10.5620794296265</t>
   </si>
   <si>
     <t xml:space="preserve">10.0864715576172</t>
@@ -3200,13 +3200,13 @@
     <t xml:space="preserve">10.490288734436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5979747772217</t>
+    <t xml:space="preserve">10.5979738235474</t>
   </si>
   <si>
     <t xml:space="preserve">10.8671855926514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1453714370728</t>
+    <t xml:space="preserve">11.1453704833984</t>
   </si>
   <si>
     <t xml:space="preserve">10.9658975601196</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">11.1722927093506</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2440824508667</t>
+    <t xml:space="preserve">11.2440814971924</t>
   </si>
   <si>
     <t xml:space="preserve">11.2261343002319</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">11.4594526290894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6299524307251</t>
+    <t xml:space="preserve">11.6299533843994</t>
   </si>
   <si>
     <t xml:space="preserve">11.8004531860352</t>
@@ -3248,40 +3248,40 @@
     <t xml:space="preserve">11.6568737030029</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8453216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2171611785889</t>
+    <t xml:space="preserve">11.8453226089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2171621322632</t>
   </si>
   <si>
     <t xml:space="preserve">11.2081871032715</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3248453140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2620296478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1363973617554</t>
+    <t xml:space="preserve">11.3248462677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2620306015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1363983154297</t>
   </si>
   <si>
     <t xml:space="preserve">10.8223180770874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3287620544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5351572036743</t>
+    <t xml:space="preserve">10.3287630081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5351581573486</t>
   </si>
   <si>
     <t xml:space="preserve">10.373631477356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5441312789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7056579589844</t>
+    <t xml:space="preserve">10.544132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.705659866333</t>
   </si>
   <si>
     <t xml:space="preserve">10.6159219741821</t>
@@ -3293,16 +3293,16 @@
     <t xml:space="preserve">10.7146320343018</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6248950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4005517959595</t>
+    <t xml:space="preserve">10.6248960494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4005527496338</t>
   </si>
   <si>
     <t xml:space="preserve">10.6069469451904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44933795928955</t>
+    <t xml:space="preserve">9.44933700561523</t>
   </si>
   <si>
     <t xml:space="preserve">8.81668853759766</t>
@@ -3311,13 +3311,13 @@
     <t xml:space="preserve">8.01354122161865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0225133895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1571216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48914813995361</t>
+    <t xml:space="preserve">8.02251243591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15712070465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48914909362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.20198917388916</t>
@@ -3329,16 +3329,16 @@
     <t xml:space="preserve">8.53850269317627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67759704589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09038829803467</t>
+    <t xml:space="preserve">8.67759609222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09038734436035</t>
   </si>
   <si>
     <t xml:space="preserve">8.96924209594727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01859855651855</t>
+    <t xml:space="preserve">9.01859760284424</t>
   </si>
   <si>
     <t xml:space="preserve">9.1083345413208</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">9.13525676727295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98270320892334</t>
+    <t xml:space="preserve">8.98270416259766</t>
   </si>
   <si>
     <t xml:space="preserve">8.79874229431152</t>
@@ -3362,67 +3362,67 @@
     <t xml:space="preserve">9.34165287017822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25191593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08141422271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97373008728027</t>
+    <t xml:space="preserve">9.25191402435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08141326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97372913360596</t>
   </si>
   <si>
     <t xml:space="preserve">9.036545753479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83015060424805</t>
+    <t xml:space="preserve">8.83014965057373</t>
   </si>
   <si>
     <t xml:space="preserve">8.43979167938232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26480484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36351585388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27377891540527</t>
+    <t xml:space="preserve">8.26480579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36351490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27377796173096</t>
   </si>
   <si>
     <t xml:space="preserve">8.30967330932617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35005569458008</t>
+    <t xml:space="preserve">8.35005474090576</t>
   </si>
   <si>
     <t xml:space="preserve">8.36800193786621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51606941223145</t>
+    <t xml:space="preserve">8.51606845855713</t>
   </si>
   <si>
     <t xml:space="preserve">8.94232177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70900344848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5743989944458</t>
+    <t xml:space="preserve">8.70900440216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57439804077148</t>
   </si>
   <si>
     <t xml:space="preserve">8.45773887634277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46671390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61478042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4936351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30070018768311</t>
+    <t xml:space="preserve">8.46671485900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61477947235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49363422393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30069923400879</t>
   </si>
   <si>
     <t xml:space="preserve">8.18404102325439</t>
@@ -3431,13 +3431,13 @@
     <t xml:space="preserve">8.25134372711182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12571239471436</t>
+    <t xml:space="preserve">8.12571144104004</t>
   </si>
   <si>
     <t xml:space="preserve">8.88399124145508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65573310852051</t>
+    <t xml:space="preserve">9.65573215484619</t>
   </si>
   <si>
     <t xml:space="preserve">9.6856861114502</t>
@@ -3449,34 +3449,34 @@
     <t xml:space="preserve">9.63044357299805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87902927398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0539627075195</t>
+    <t xml:space="preserve">9.87903022766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0539617538452</t>
   </si>
   <si>
     <t xml:space="preserve">10.2104806900024</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95268726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98030662536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.035548210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89744567871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0631694793701</t>
+    <t xml:space="preserve">9.95268630981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98030757904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0355491638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89744472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0631704330444</t>
   </si>
   <si>
     <t xml:space="preserve">10.1184110641479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1552391052246</t>
+    <t xml:space="preserve">10.1552381515503</t>
   </si>
   <si>
     <t xml:space="preserve">9.63965129852295</t>
@@ -3488,16 +3488,16 @@
     <t xml:space="preserve">9.22533893585205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44630527496338</t>
+    <t xml:space="preserve">9.4463062286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.87087249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95833778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98595905303955</t>
+    <t xml:space="preserve">8.95833873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98596000671387</t>
   </si>
   <si>
     <t xml:space="preserve">9.02278614044189</t>
@@ -3509,13 +3509,13 @@
     <t xml:space="preserve">8.66832065582275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62228584289551</t>
+    <t xml:space="preserve">8.62228488922119</t>
   </si>
   <si>
     <t xml:space="preserve">8.67292404174805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77419948577881</t>
+    <t xml:space="preserve">8.77419853210449</t>
   </si>
   <si>
     <t xml:space="preserve">8.73737239837646</t>
@@ -3533,25 +3533,25 @@
     <t xml:space="preserve">8.35988807678223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80642318725586</t>
+    <t xml:space="preserve">8.80642414093018</t>
   </si>
   <si>
     <t xml:space="preserve">9.08263206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8570613861084</t>
+    <t xml:space="preserve">8.85706233978271</t>
   </si>
   <si>
     <t xml:space="preserve">8.88928604125977</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82023525238037</t>
+    <t xml:space="preserve">8.82023429870605</t>
   </si>
   <si>
     <t xml:space="preserve">8.60847568511963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90309715270996</t>
+    <t xml:space="preserve">8.90309619903564</t>
   </si>
   <si>
     <t xml:space="preserve">9.00437259674072</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">8.99976921081543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71895885467529</t>
+    <t xml:space="preserve">8.71895790100098</t>
   </si>
   <si>
     <t xml:space="preserve">8.86166572570801</t>
@@ -3581,22 +3581,22 @@
     <t xml:space="preserve">9.47392654418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5936164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6488561630249</t>
+    <t xml:space="preserve">9.59361553192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64885711669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.77775478363037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72251415252686</t>
+    <t xml:space="preserve">9.72251319885254</t>
   </si>
   <si>
     <t xml:space="preserve">9.55678844451904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75934028625488</t>
+    <t xml:space="preserve">9.7593412399292</t>
   </si>
   <si>
     <t xml:space="preserve">9.73171901702881</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">9.53837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21613216400146</t>
+    <t xml:space="preserve">9.21613311767578</t>
   </si>
   <si>
     <t xml:space="preserve">8.84325122833252</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">9.00897598266602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92611408233643</t>
+    <t xml:space="preserve">8.92611312866211</t>
   </si>
   <si>
     <t xml:space="preserve">8.59466457366943</t>
@@ -3659,16 +3659,16 @@
     <t xml:space="preserve">8.76959609985352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75578594207764</t>
+    <t xml:space="preserve">8.75578689575195</t>
   </si>
   <si>
     <t xml:space="preserve">8.7926139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51640605926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3138542175293</t>
+    <t xml:space="preserve">8.51640510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31385326385498</t>
   </si>
   <si>
     <t xml:space="preserve">8.33226776123047</t>
@@ -3683,28 +3683,28 @@
     <t xml:space="preserve">8.01923179626465</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77985191345215</t>
+    <t xml:space="preserve">7.77985143661499</t>
   </si>
   <si>
     <t xml:space="preserve">7.88112878799438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83049058914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82588672637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4944372177124</t>
+    <t xml:space="preserve">7.83049011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82588720321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49443769454956</t>
   </si>
   <si>
     <t xml:space="preserve">7.82128238677979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97319746017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31845760345459</t>
+    <t xml:space="preserve">7.9731969833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31845664978027</t>
   </si>
   <si>
     <t xml:space="preserve">8.2217845916748</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">8.29543972015381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68213081359863</t>
+    <t xml:space="preserve">8.68213176727295</t>
   </si>
   <si>
     <t xml:space="preserve">8.47037124633789</t>
@@ -3734,10 +3734,10 @@
     <t xml:space="preserve">8.73276805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90769958496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91690731048584</t>
+    <t xml:space="preserve">8.90770053863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91690826416016</t>
   </si>
   <si>
     <t xml:space="preserve">8.97214889526367</t>
@@ -3749,13 +3749,13 @@
     <t xml:space="preserve">9.19311428070068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54758071899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82378959655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79616928100586</t>
+    <t xml:space="preserve">9.54758167266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8237886428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79616832733154</t>
   </si>
   <si>
     <t xml:space="preserve">9.74092674255371</t>
@@ -3773,40 +3773,40 @@
     <t xml:space="preserve">10.8641719818115</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7260665893555</t>
+    <t xml:space="preserve">10.7260675430298</t>
   </si>
   <si>
     <t xml:space="preserve">10.6892404556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7444829940796</t>
+    <t xml:space="preserve">10.7444820404053</t>
   </si>
   <si>
     <t xml:space="preserve">10.5143089294434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.339376449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841358184814</t>
+    <t xml:space="preserve">10.2381019592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3393774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841348648071</t>
   </si>
   <si>
     <t xml:space="preserve">10.3209638595581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1368246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1828603744507</t>
+    <t xml:space="preserve">10.1368255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1828594207764</t>
   </si>
   <si>
     <t xml:space="preserve">10.3485841751099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1920652389526</t>
+    <t xml:space="preserve">10.192066192627</t>
   </si>
   <si>
     <t xml:space="preserve">10.0815830230713</t>
@@ -3821,13 +3821,13 @@
     <t xml:space="preserve">9.94347953796387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86061668395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7501335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6580638885498</t>
+    <t xml:space="preserve">9.86061763763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75013446807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65806484222412</t>
   </si>
   <si>
     <t xml:space="preserve">9.60282325744629</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">10.146032333374</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1276178359985</t>
+    <t xml:space="preserve">10.1276168823242</t>
   </si>
   <si>
     <t xml:space="preserve">10.2473077774048</t>
@@ -3854,10 +3854,10 @@
     <t xml:space="preserve">10.4866886138916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5327224731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7721033096313</t>
+    <t xml:space="preserve">10.5327215194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.772102355957</t>
   </si>
   <si>
     <t xml:space="preserve">10.6800336837769</t>
@@ -3869,13 +3869,13 @@
     <t xml:space="preserve">10.7352743148804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5695495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6616201400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9286193847656</t>
+    <t xml:space="preserve">10.5695505142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6616191864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9286203384399</t>
   </si>
   <si>
     <t xml:space="preserve">10.9654483795166</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">12.2912454605103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3372793197632</t>
+    <t xml:space="preserve">12.3372802734375</t>
   </si>
   <si>
     <t xml:space="preserve">12.1623487472534</t>
@@ -3929,10 +3929,10 @@
     <t xml:space="preserve">12.8620748519897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7275247573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7367334365845</t>
+    <t xml:space="preserve">13.7275257110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7367324829102</t>
   </si>
   <si>
     <t xml:space="preserve">13.4789390563965</t>
@@ -3944,10 +3944,10 @@
     <t xml:space="preserve">12.5950736999512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8252468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8896961212158</t>
+    <t xml:space="preserve">12.8252477645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896951675415</t>
   </si>
   <si>
     <t xml:space="preserve">12.5582466125488</t>
@@ -3959,10 +3959,10 @@
     <t xml:space="preserve">12.6134872436523</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0058298110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.913761138916</t>
+    <t xml:space="preserve">12.0058307647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9137601852417</t>
   </si>
   <si>
     <t xml:space="preserve">12.171555519104</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">12.4293489456177</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7700052261353</t>
+    <t xml:space="preserve">12.7700042724609</t>
   </si>
   <si>
     <t xml:space="preserve">12.2728319168091</t>
@@ -4016,22 +4016,22 @@
     <t xml:space="preserve">12.1991758346558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2544183731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6503143310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0738334655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2855930328369</t>
+    <t xml:space="preserve">12.2544174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.650315284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0738344192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2855939865112</t>
   </si>
   <si>
     <t xml:space="preserve">13.2579717636108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1751098632812</t>
+    <t xml:space="preserve">13.1751108169556</t>
   </si>
   <si>
     <t xml:space="preserve">13.2119388580322</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">13.2947998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3417453765869</t>
+    <t xml:space="preserve">13.3417444229126</t>
   </si>
   <si>
     <t xml:space="preserve">13.1821327209473</t>
@@ -4061,7 +4061,7 @@
     <t xml:space="preserve">13.2854108810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3323564529419</t>
+    <t xml:space="preserve">13.3323554992676</t>
   </si>
   <si>
     <t xml:space="preserve">13.3511343002319</t>
@@ -4082,19 +4082,19 @@
     <t xml:space="preserve">13.4168567657471</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4544134140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4919681549072</t>
+    <t xml:space="preserve">13.4544124603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4919691085815</t>
   </si>
   <si>
     <t xml:space="preserve">13.6140260696411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9895849227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9614171981812</t>
+    <t xml:space="preserve">13.9895839691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9614181518555</t>
   </si>
   <si>
     <t xml:space="preserve">13.7548599243164</t>
@@ -4106,13 +4106,13 @@
     <t xml:space="preserve">13.5952472686768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5201349258423</t>
+    <t xml:space="preserve">13.5201358795166</t>
   </si>
   <si>
     <t xml:space="preserve">12.703293800354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3840684890747</t>
+    <t xml:space="preserve">12.3840675354004</t>
   </si>
   <si>
     <t xml:space="preserve">12.3652906417847</t>
@@ -4127,19 +4127,19 @@
     <t xml:space="preserve">12.5061254501343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6000156402588</t>
+    <t xml:space="preserve">12.6000146865845</t>
   </si>
   <si>
     <t xml:space="preserve">12.7502393722534</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6469612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6281814575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5249032974243</t>
+    <t xml:space="preserve">12.6469602584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6281824111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5249042510986</t>
   </si>
   <si>
     <t xml:space="preserve">12.5342931747437</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">12.2526226043701</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4028463363647</t>
+    <t xml:space="preserve">12.4028472900391</t>
   </si>
   <si>
     <t xml:space="preserve">12.3277349472046</t>
@@ -4172,19 +4172,19 @@
     <t xml:space="preserve">12.5155143737793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4310140609741</t>
+    <t xml:space="preserve">12.4310131072998</t>
   </si>
   <si>
     <t xml:space="preserve">12.1211767196655</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0836210250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4122352600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0930099487305</t>
+    <t xml:space="preserve">12.0836219787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4122362136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0930109024048</t>
   </si>
   <si>
     <t xml:space="preserve">12.2338447570801</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">12.0648441314697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2056789398193</t>
+    <t xml:space="preserve">12.205677986145</t>
   </si>
   <si>
     <t xml:space="preserve">11.9991207122803</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">11.9240083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7268400192261</t>
+    <t xml:space="preserve">11.7268390655518</t>
   </si>
   <si>
     <t xml:space="preserve">11.9146194458008</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">11.9897317886353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554552078247</t>
+    <t xml:space="preserve">12.0554542541504</t>
   </si>
   <si>
     <t xml:space="preserve">12.0460653305054</t>
@@ -4238,10 +4238,10 @@
     <t xml:space="preserve">12.0742321014404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9709529876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8770627975464</t>
+    <t xml:space="preserve">11.9709539413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8770637512207</t>
   </si>
   <si>
     <t xml:space="preserve">11.7737846374512</t>
@@ -4268,13 +4268,13 @@
     <t xml:space="preserve">11.4545593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5108938217163</t>
+    <t xml:space="preserve">11.510892868042</t>
   </si>
   <si>
     <t xml:space="preserve">11.670506477356</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4076147079468</t>
+    <t xml:space="preserve">11.4076137542725</t>
   </si>
   <si>
     <t xml:space="preserve">11.3606700897217</t>
@@ -4301,10 +4301,10 @@
     <t xml:space="preserve">10.8254976272583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7785520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6001625061035</t>
+    <t xml:space="preserve">10.7785530090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6001615524292</t>
   </si>
   <si>
     <t xml:space="preserve">10.7034406661987</t>
@@ -4316,10 +4316,10 @@
     <t xml:space="preserve">10.7503852844238</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7222194671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6471061706543</t>
+    <t xml:space="preserve">10.7222185134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6471071243286</t>
   </si>
   <si>
     <t xml:space="preserve">10.31849193573</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">9.68004131317139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68943023681641</t>
+    <t xml:space="preserve">9.68943119049072</t>
   </si>
   <si>
     <t xml:space="preserve">9.71759796142578</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">9.94293308258057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85843276977539</t>
+    <t xml:space="preserve">9.85843181610107</t>
   </si>
   <si>
     <t xml:space="preserve">10.1776580810547</t>
@@ -4394,7 +4394,7 @@
     <t xml:space="preserve">10.018045425415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0649909973145</t>
+    <t xml:space="preserve">10.0649900436401</t>
   </si>
   <si>
     <t xml:space="preserve">9.89598751068115</t>
@@ -4412,10 +4412,10 @@
     <t xml:space="preserve">10.2527694702148</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1307125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2809371948242</t>
+    <t xml:space="preserve">10.1307134628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2809362411499</t>
   </si>
   <si>
     <t xml:space="preserve">10.1964349746704</t>
@@ -4424,7 +4424,7 @@
     <t xml:space="preserve">10.3560485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">10.506272315979</t>
+    <t xml:space="preserve">10.5062713623047</t>
   </si>
   <si>
     <t xml:space="preserve">10.4029932022095</t>
@@ -4436,7 +4436,7 @@
     <t xml:space="preserve">9.97109985351562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4874935150146</t>
+    <t xml:space="preserve">10.487494468689</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405498504639</t>
@@ -4451,7 +4451,7 @@
     <t xml:space="preserve">10.6658849716187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5719947814941</t>
+    <t xml:space="preserve">10.5719957351685</t>
   </si>
   <si>
     <t xml:space="preserve">10.4499387741089</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">10.309103012085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2621583938599</t>
+    <t xml:space="preserve">10.2621593475342</t>
   </si>
   <si>
     <t xml:space="preserve">10.1870470046997</t>
@@ -4484,7 +4484,7 @@
     <t xml:space="preserve">10.1401023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058248519897</t>
+    <t xml:space="preserve">10.2058238983154</t>
   </si>
   <si>
     <t xml:space="preserve">10.6095514297485</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">10.7409963607788</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9099979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7316083908081</t>
+    <t xml:space="preserve">10.9099988937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7316074371338</t>
   </si>
   <si>
     <t xml:space="preserve">10.8912210464478</t>
@@ -4532,7 +4532,7 @@
     <t xml:space="preserve">10.7128295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7879409790039</t>
+    <t xml:space="preserve">10.7879419326782</t>
   </si>
   <si>
     <t xml:space="preserve">10.9287767410278</t>
@@ -4547,7 +4547,7 @@
     <t xml:space="preserve">11.0602216720581</t>
   </si>
   <si>
-    <t xml:space="preserve">11.003888130188</t>
+    <t xml:space="preserve">11.0038890838623</t>
   </si>
   <si>
     <t xml:space="preserve">10.8818321228027</t>
@@ -4571,7 +4571,7 @@
     <t xml:space="preserve">11.1728897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2949466705322</t>
+    <t xml:space="preserve">11.2949457168579</t>
   </si>
   <si>
     <t xml:space="preserve">11.1447229385376</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">11.0508337020874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2480020523071</t>
+    <t xml:space="preserve">11.2480010986328</t>
   </si>
   <si>
     <t xml:space="preserve">11.3982257843018</t>
@@ -4595,16 +4595,16 @@
     <t xml:space="preserve">11.3418912887573</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1259450912476</t>
+    <t xml:space="preserve">11.1259460449219</t>
   </si>
   <si>
     <t xml:space="preserve">11.2386131286621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292232513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9757213592529</t>
+    <t xml:space="preserve">11.2292242050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9757204055786</t>
   </si>
   <si>
     <t xml:space="preserve">11.6104164123535</t>
@@ -4625,10 +4625,10 @@
     <t xml:space="preserve">11.4094924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3249921798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1090450286865</t>
+    <t xml:space="preserve">11.3249912261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1090440750122</t>
   </si>
   <si>
     <t xml:space="preserve">10.4705944061279</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">10.4536933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3691921234131</t>
+    <t xml:space="preserve">10.3691930770874</t>
   </si>
   <si>
     <t xml:space="preserve">10.4799823760986</t>
@@ -5877,6 +5877,9 @@
   </si>
   <si>
     <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10000038146973</t>
   </si>
 </sst>
 </file>
@@ -73777,9 +73780,11 @@
       <c r="E2599" t="n">
         <v>7.78000020980835</v>
       </c>
-      <c r="F2599"/>
+      <c r="F2599" t="n">
+        <v>7.7649998664856</v>
+      </c>
       <c r="G2599" t="s">
-        <v>1954</v>
+        <v>1786</v>
       </c>
       <c r="H2599" t="s">
         <v>9</v>
@@ -73787,27 +73792,51 @@
     </row>
     <row r="2600">
       <c r="A2600" s="1" t="n">
-        <v>46105.6912731481</v>
+        <v>46106.3333333333</v>
       </c>
       <c r="B2600" t="n">
-        <v>629596</v>
+        <v>753515</v>
       </c>
       <c r="C2600" t="n">
+        <v>8.17000007629395</v>
+      </c>
+      <c r="D2600" t="n">
         <v>7.8600001335144</v>
       </c>
-      <c r="D2600" t="n">
-        <v>7.65999984741211</v>
-      </c>
       <c r="E2600" t="n">
-        <v>7.78000020980835</v>
-      </c>
-      <c r="F2600" t="n">
-        <v>7.7649998664856</v>
-      </c>
+        <v>7.89499998092651</v>
+      </c>
+      <c r="F2600"/>
       <c r="G2600" t="s">
-        <v>1786</v>
+        <v>1954</v>
       </c>
       <c r="H2600" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2601">
+      <c r="A2601" s="1" t="n">
+        <v>46106.6910185185</v>
+      </c>
+      <c r="B2601" t="n">
+        <v>753515</v>
+      </c>
+      <c r="C2601" t="n">
+        <v>8.17000007629395</v>
+      </c>
+      <c r="D2601" t="n">
+        <v>7.8600001335144</v>
+      </c>
+      <c r="E2601" t="n">
+        <v>7.89499998092651</v>
+      </c>
+      <c r="F2601" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="G2601" t="s">
+        <v>1955</v>
+      </c>
+      <c r="H2601" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BRE.MI.xlsx
+++ b/data/BRE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1959" uniqueCount="1959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="1960">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16937828063965</t>
+    <t xml:space="preserve">7.16937780380249</t>
   </si>
   <si>
     <t xml:space="preserve">BRE.MI</t>
@@ -47,37 +47,37 @@
     <t xml:space="preserve">7.13994884490967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92740106582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52519702911377</t>
+    <t xml:space="preserve">6.92740201950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52519750595093</t>
   </si>
   <si>
     <t xml:space="preserve">6.54154682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42873382568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60040616989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78188848495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55135726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21291589736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19820261001587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27504587173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94641494750977</t>
+    <t xml:space="preserve">6.42873334884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60040664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78188800811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55135679244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21291446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19820213317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27504539489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94641542434692</t>
   </si>
   <si>
     <t xml:space="preserve">6.20310688018799</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">6.24888610839844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3061089515686</t>
+    <t xml:space="preserve">6.30610942840576</t>
   </si>
   <si>
     <t xml:space="preserve">6.31918954849243</t>
@@ -95,64 +95,64 @@
     <t xml:space="preserve">6.38785886764526</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23090076446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16713666915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05922794342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99219465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86466598510742</t>
+    <t xml:space="preserve">6.23090028762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16713714599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05922842025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99219417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86466550827026</t>
   </si>
   <si>
     <t xml:space="preserve">5.70443820953369</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35945749282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51641464233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72242259979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67500829696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73223304748535</t>
+    <t xml:space="preserve">5.35945796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51641511917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72242307662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67500877380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73223352432251</t>
   </si>
   <si>
     <t xml:space="preserve">6.03960847854614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97420930862427</t>
+    <t xml:space="preserve">5.97420978546143</t>
   </si>
   <si>
     <t xml:space="preserve">6.11972284317017</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14097690582275</t>
+    <t xml:space="preserve">6.14097738265991</t>
   </si>
   <si>
     <t xml:space="preserve">6.10010242462158</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23744010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11154699325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97584438323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07394313812256</t>
+    <t xml:space="preserve">6.23744106292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11154747009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9758448600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07394361495972</t>
   </si>
   <si>
     <t xml:space="preserve">6.12953281402588</t>
@@ -161,58 +161,58 @@
     <t xml:space="preserve">6.2194561958313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35189008712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32409524917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04675626754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08272409439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11705923080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07945442199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12032985687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07127904891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06637573242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16120290756226</t>
+    <t xml:space="preserve">6.35188961029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32409572601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04675579071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08272457122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11705875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07945489883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1203293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07127952575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06637477874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16120386123657</t>
   </si>
   <si>
     <t xml:space="preserve">7.14321947097778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24949169158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14158487319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22987222671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07618427276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26911211013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15302753448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15139389038086</t>
+    <t xml:space="preserve">7.24949216842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1415843963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22987270355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07618379592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26911354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15302848815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1513934135437</t>
   </si>
   <si>
     <t xml:space="preserve">7.31489133834839</t>
@@ -221,52 +221,52 @@
     <t xml:space="preserve">7.43097496032715</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40318059921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35576581954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1448540687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18899822235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16283798217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27401638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30998611450195</t>
+    <t xml:space="preserve">7.40318012237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35576629638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14485359191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18899774551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16283893585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27401542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30998659133911</t>
   </si>
   <si>
     <t xml:space="preserve">7.3574013710022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4064507484436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42279863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39337110519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43914985656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47184944152832</t>
+    <t xml:space="preserve">7.40645027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4227991104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39337205886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4391508102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47184896469116</t>
   </si>
   <si>
     <t xml:space="preserve">7.51108837127686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76778173446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71546220779419</t>
+    <t xml:space="preserve">7.76778030395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71546125411987</t>
   </si>
   <si>
     <t xml:space="preserve">7.63534736633301</t>
@@ -275,40 +275,40 @@
     <t xml:space="preserve">7.68276214599609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74162149429321</t>
+    <t xml:space="preserve">7.74162101745605</t>
   </si>
   <si>
     <t xml:space="preserve">7.66968202590942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72200059890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63044214248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71055459976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85607004165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47736072540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50188446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51006126403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55093574523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42831230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36291313171387</t>
+    <t xml:space="preserve">7.72199964523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63044309616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71055746078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85606908798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47736167907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50188636779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51006031036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55093383789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42831325531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36291217803955</t>
   </si>
   <si>
     <t xml:space="preserve">8.35473728179932</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">8.41196155548096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45348167419434</t>
+    <t xml:space="preserve">8.51991653442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45348262786865</t>
   </si>
   <si>
     <t xml:space="preserve">8.51161098480225</t>
@@ -332,28 +332,28 @@
     <t xml:space="preserve">8.47008991241455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61125755310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63617038726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72751426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96002769470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86868286132812</t>
+    <t xml:space="preserve">8.6112585067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63617134094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72751331329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96002674102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86868190765381</t>
   </si>
   <si>
     <t xml:space="preserve">8.86037921905518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58634757995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27577590942383</t>
+    <t xml:space="preserve">8.58634567260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27577495574951</t>
   </si>
   <si>
     <t xml:space="preserve">8.10969638824463</t>
@@ -362,40 +362,40 @@
     <t xml:space="preserve">8.30400943756104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31231307983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60295295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61956310272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56973743438721</t>
+    <t xml:space="preserve">8.3123140335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60295391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61956214904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56973838806152</t>
   </si>
   <si>
     <t xml:space="preserve">8.71921062469482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25916957855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64134883880615</t>
+    <t xml:space="preserve">8.25916862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64134931564331</t>
   </si>
   <si>
     <t xml:space="preserve">8.25418663024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0598726272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20602226257324</t>
+    <t xml:space="preserve">8.05987167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20602321624756</t>
   </si>
   <si>
     <t xml:space="preserve">8.23757839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84729099273682</t>
+    <t xml:space="preserve">7.8472900390625</t>
   </si>
   <si>
     <t xml:space="preserve">7.6795482635498</t>
@@ -404,40 +404,40 @@
     <t xml:space="preserve">7.6778883934021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95524120330811</t>
+    <t xml:space="preserve">7.95524024963379</t>
   </si>
   <si>
     <t xml:space="preserve">8.02831745147705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05488872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97849225997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14457225799561</t>
+    <t xml:space="preserve">8.05488967895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97849321365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14457321166992</t>
   </si>
   <si>
     <t xml:space="preserve">8.11301803588867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23425579071045</t>
+    <t xml:space="preserve">8.23425674438477</t>
   </si>
   <si>
     <t xml:space="preserve">8.10471343994141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21100425720215</t>
+    <t xml:space="preserve">8.21100521087646</t>
   </si>
   <si>
     <t xml:space="preserve">8.16782474517822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32061862945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37044334411621</t>
+    <t xml:space="preserve">8.32061767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37044239044189</t>
   </si>
   <si>
     <t xml:space="preserve">8.41196250915527</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">8.50330543518066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36213874816895</t>
+    <t xml:space="preserve">8.36213684082031</t>
   </si>
   <si>
     <t xml:space="preserve">8.67769050598145</t>
@@ -455,61 +455,61 @@
     <t xml:space="preserve">8.76903533935547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53652095794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55312919616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64447498321533</t>
+    <t xml:space="preserve">8.53652286529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55313014984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.